--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2026,13 +2026,13 @@
         <v>1289.473422851562</v>
       </c>
       <c r="E21" t="n">
-        <v>1088.130806477865</v>
+        <v>1088.130807291667</v>
       </c>
       <c r="F21" t="n">
-        <v>1022.508684692383</v>
+        <v>1022.508684387207</v>
       </c>
       <c r="G21" t="n">
-        <v>5.569075155486258</v>
+        <v>5.569075223766218</v>
       </c>
       <c r="H21" t="n">
         <v>1677.5</v>
@@ -3338,19 +3338,19 @@
         <v>629.6343754069011</v>
       </c>
       <c r="F38" t="n">
-        <v>592.5793426513671</v>
+        <v>592.579342956543</v>
       </c>
       <c r="G38" t="n">
-        <v>6.256151074608107</v>
+        <v>6.256151013039757</v>
       </c>
       <c r="H38" t="n">
         <v>844</v>
       </c>
       <c r="I38" t="n">
-        <v>399.8350028638013</v>
+        <v>399.8349725758499</v>
       </c>
       <c r="J38" t="n">
-        <v>97.08129462302782</v>
+        <v>97.08130955215881</v>
       </c>
       <c r="K38" t="n">
         <v>7.106598984771573</v>
@@ -3418,16 +3418,16 @@
         <v>875.9103137207031</v>
       </c>
       <c r="G39" t="n">
-        <v>5.599778821782664</v>
+        <v>5.599778899487218</v>
       </c>
       <c r="H39" t="n">
         <v>1269.800048828125</v>
       </c>
       <c r="I39" t="n">
-        <v>594.6744698202933</v>
+        <v>594.6745299041222</v>
       </c>
       <c r="J39" t="n">
-        <v>99.72270737144476</v>
+        <v>99.72268719216287</v>
       </c>
       <c r="K39" t="n">
         <v>6.912528503115944</v>
@@ -4262,10 +4262,10 @@
         <v>245.2917078653971</v>
       </c>
       <c r="F50" t="n">
-        <v>233.937264175415</v>
+        <v>233.937264251709</v>
       </c>
       <c r="G50" t="n">
-        <v>6.891633200614633</v>
+        <v>6.891633198212199</v>
       </c>
       <c r="H50" t="n">
         <v>388.75</v>
@@ -5565,25 +5565,25 @@
         <v>12097</v>
       </c>
       <c r="D67" t="n">
-        <v>11009.6391015625</v>
+        <v>11009.639140625</v>
       </c>
       <c r="E67" t="n">
-        <v>10596.02940104167</v>
+        <v>10596.02934244792</v>
       </c>
       <c r="F67" t="n">
-        <v>10190.40309814453</v>
+        <v>10190.40307617188</v>
       </c>
       <c r="G67" t="n">
-        <v>3.139077086807207</v>
+        <v>3.139077272187496</v>
       </c>
       <c r="H67" t="n">
         <v>12865.82946046676</v>
       </c>
       <c r="I67" t="n">
-        <v>6613.373792726331</v>
+        <v>6613.3742727433</v>
       </c>
       <c r="J67" t="n">
-        <v>82.91722771370935</v>
+        <v>82.91721443707181</v>
       </c>
       <c r="K67" t="n">
         <v>6.355538236478098</v>
@@ -6957,19 +6957,19 @@
         <v>77.21143274943034</v>
       </c>
       <c r="F85" t="n">
-        <v>72.82457176208496</v>
+        <v>72.82457172393799</v>
       </c>
       <c r="G85" t="n">
-        <v>4.028001885936061</v>
+        <v>4.028001774757217</v>
       </c>
       <c r="H85" t="n">
         <v>94.5</v>
       </c>
       <c r="I85" t="n">
-        <v>51.9266784920807</v>
+        <v>51.92667471478926</v>
       </c>
       <c r="J85" t="n">
-        <v>62.15170966709043</v>
+        <v>62.15172146245897</v>
       </c>
       <c r="K85" t="n">
         <v>12.23278316516951</v>
@@ -8035,10 +8035,10 @@
         <v>230.5883953857422</v>
       </c>
       <c r="F99" t="n">
-        <v>220.5138857269287</v>
+        <v>220.5138858032226</v>
       </c>
       <c r="G99" t="n">
-        <v>3.143815300451069</v>
+        <v>3.143815262521299</v>
       </c>
       <c r="H99" t="n">
         <v>289.6499938964844</v>
@@ -8725,13 +8725,13 @@
         <v>4947.8980078125</v>
       </c>
       <c r="E108" t="n">
-        <v>4530.501002604166</v>
+        <v>4530.501004231771</v>
       </c>
       <c r="F108" t="n">
-        <v>4359.918780517578</v>
+        <v>4359.918782958985</v>
       </c>
       <c r="G108" t="n">
-        <v>3.335265610115368</v>
+        <v>3.335265458700043</v>
       </c>
       <c r="H108" t="n">
         <v>5250</v>
@@ -9264,22 +9264,22 @@
         <v>1839.062414550781</v>
       </c>
       <c r="E115" t="n">
-        <v>1600.098317057292</v>
+        <v>1600.098318684896</v>
       </c>
       <c r="F115" t="n">
         <v>1557.674750976563</v>
       </c>
       <c r="G115" t="n">
-        <v>2.630118662035263</v>
+        <v>2.630118703307027</v>
       </c>
       <c r="H115" t="n">
         <v>1988.900024414062</v>
       </c>
       <c r="I115" t="n">
-        <v>1266.161452106784</v>
+        <v>1266.16157090969</v>
       </c>
       <c r="J115" t="n">
-        <v>50.77066173698366</v>
+        <v>50.77064759029564</v>
       </c>
       <c r="K115" t="n">
         <v>4.185438680673781</v>
@@ -11805,7 +11805,7 @@
         <v>4395.985185546875</v>
       </c>
       <c r="E148" t="n">
-        <v>3694.642097981771</v>
+        <v>3694.642096354167</v>
       </c>
       <c r="F148" t="n">
         <v>3510.719942626953</v>
@@ -13582,7 +13582,7 @@
         <v>1100.486620483398</v>
       </c>
       <c r="G171" t="n">
-        <v>2.213079753303537</v>
+        <v>2.213079840219501</v>
       </c>
       <c r="H171" t="n">
         <v>1596.696405272527</v>
@@ -13810,19 +13810,19 @@
         <v>295.5614790852865</v>
       </c>
       <c r="F174" t="n">
-        <v>284.2275991058349</v>
+        <v>284.2275992584229</v>
       </c>
       <c r="G174" t="n">
-        <v>1.302283112135982</v>
+        <v>1.302283138974003</v>
       </c>
       <c r="H174" t="n">
         <v>359.3387168134344</v>
       </c>
       <c r="I174" t="n">
-        <v>206.1210871445057</v>
+        <v>206.1211021779015</v>
       </c>
       <c r="J174" t="n">
-        <v>47.97127466447581</v>
+        <v>47.97126387222441</v>
       </c>
       <c r="K174" t="n">
         <v>17.8159727257162</v>
@@ -14118,10 +14118,10 @@
         <v>1444.400021972656</v>
       </c>
       <c r="F178" t="n">
-        <v>1518.129982910156</v>
+        <v>1518.129981079102</v>
       </c>
       <c r="G178" t="n">
-        <v>0.7553149052574648</v>
+        <v>0.755314824547737</v>
       </c>
       <c r="H178" t="n">
         <v>2021.199951171875</v>
@@ -14346,13 +14346,13 @@
         <v>460.3666107177734</v>
       </c>
       <c r="E181" t="n">
-        <v>464.3686496988933</v>
+        <v>464.3686503092448</v>
       </c>
       <c r="F181" t="n">
-        <v>454.349242553711</v>
+        <v>454.3492445373535</v>
       </c>
       <c r="G181" t="n">
-        <v>1.51643936693826</v>
+        <v>1.516439464047603</v>
       </c>
       <c r="H181" t="n">
         <v>529.9163379046904</v>
@@ -15584,7 +15584,7 @@
         <v>509.3152810668946</v>
       </c>
       <c r="G197" t="n">
-        <v>1.814851970470621</v>
+        <v>1.814851908357196</v>
       </c>
       <c r="H197" t="n">
         <v>609.0499877929688</v>
@@ -16040,13 +16040,13 @@
         <v>8833.90373046875</v>
       </c>
       <c r="E203" t="n">
-        <v>8194.705794270832</v>
+        <v>8194.705791015625</v>
       </c>
       <c r="F203" t="n">
-        <v>7918.108576660156</v>
+        <v>7918.108581542969</v>
       </c>
       <c r="G203" t="n">
-        <v>1.696128486660298</v>
+        <v>1.696128485596615</v>
       </c>
       <c r="H203" t="n">
         <v>9039.4765625</v>
@@ -16505,10 +16505,10 @@
         <v>403.4364182535807</v>
       </c>
       <c r="F209" t="n">
-        <v>398.0689994812012</v>
+        <v>398.0689997863769</v>
       </c>
       <c r="G209" t="n">
-        <v>0.8253057498218253</v>
+        <v>0.8253055933145292</v>
       </c>
       <c r="H209" t="n">
         <v>490.7000122070312</v>
@@ -17038,7 +17038,7 @@
         <v>198.9299926757812</v>
       </c>
       <c r="D216" t="n">
-        <v>174.4592477416992</v>
+        <v>174.459248046875</v>
       </c>
       <c r="E216" t="n">
         <v>149.393951365153</v>
@@ -17047,7 +17047,7 @@
         <v>151.3906978225708</v>
       </c>
       <c r="G216" t="n">
-        <v>-0.2625996097652794</v>
+        <v>-0.2625995095031364</v>
       </c>
       <c r="H216" t="n">
         <v>212.3300018310547</v>
@@ -17657,16 +17657,16 @@
         <v>1355.512041015625</v>
       </c>
       <c r="E224" t="n">
-        <v>1400.955205891927</v>
+        <v>1400.955208333333</v>
       </c>
       <c r="F224" t="n">
-        <v>1324.914421386719</v>
+        <v>1324.914418334961</v>
       </c>
       <c r="G224" t="n">
-        <v>2.29908039565101</v>
+        <v>2.299080401068365</v>
       </c>
       <c r="H224" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I224" t="n">
         <v>941.3310566553616</v>
@@ -17675,7 +17675,7 @@
         <v>50.02160410913829</v>
       </c>
       <c r="K224" t="n">
-        <v>25.10503114627272</v>
+        <v>25.10502208870538</v>
       </c>
       <c r="L224" t="n">
         <v>78.05555555555556</v>
@@ -18356,7 +18356,7 @@
         <v>306.7464488220215</v>
       </c>
       <c r="G233" t="n">
-        <v>2.546704729002824</v>
+        <v>2.546704624382978</v>
       </c>
       <c r="H233" t="n">
         <v>380.4567148307952</v>
@@ -18427,13 +18427,13 @@
         <v>1111.764846191406</v>
       </c>
       <c r="E234" t="n">
-        <v>1002.457799072266</v>
+        <v>1002.457798258464</v>
       </c>
       <c r="F234" t="n">
-        <v>984.0659790039062</v>
+        <v>984.0659805297852</v>
       </c>
       <c r="G234" t="n">
-        <v>0.6728458447696317</v>
+        <v>0.6728456551366113</v>
       </c>
       <c r="H234" t="n">
         <v>1331.075409591023</v>
@@ -20663,10 +20663,10 @@
         <v>338.9012768554687</v>
       </c>
       <c r="F263" t="n">
-        <v>333.2697012329102</v>
+        <v>333.269701385498</v>
       </c>
       <c r="G263" t="n">
-        <v>0.8907876790666069</v>
+        <v>0.8907877718639989</v>
       </c>
       <c r="H263" t="n">
         <v>428.7550602808859</v>
@@ -21199,13 +21199,13 @@
         <v>287.6611639404297</v>
       </c>
       <c r="E270" t="n">
-        <v>283.5088434855143</v>
+        <v>283.5088430786133</v>
       </c>
       <c r="F270" t="n">
-        <v>266.8796362304687</v>
+        <v>266.8796357727051</v>
       </c>
       <c r="G270" t="n">
-        <v>1.686196665518791</v>
+        <v>1.686196698019393</v>
       </c>
       <c r="H270" t="n">
         <v>367.499792159746</v>
@@ -21895,10 +21895,10 @@
         <v>1378.664289550781</v>
       </c>
       <c r="F279" t="n">
-        <v>1350.217307739258</v>
+        <v>1350.217305297851</v>
       </c>
       <c r="G279" t="n">
-        <v>1.540566345492489</v>
+        <v>1.540566394928455</v>
       </c>
       <c r="H279" t="n">
         <v>1553</v>
@@ -22046,13 +22046,13 @@
         <v>1145.806799316406</v>
       </c>
       <c r="E281" t="n">
-        <v>1104.81850382487</v>
+        <v>1104.818503417969</v>
       </c>
       <c r="F281" t="n">
-        <v>1068.224576721191</v>
+        <v>1068.224574584961</v>
       </c>
       <c r="G281" t="n">
-        <v>1.540397909332314</v>
+        <v>1.540398089192774</v>
       </c>
       <c r="H281" t="n">
         <v>1238.748718225596</v>
@@ -22816,13 +22816,13 @@
         <v>217.2804119873047</v>
       </c>
       <c r="E291" t="n">
-        <v>199.7377449544271</v>
+        <v>199.7377451578776</v>
       </c>
       <c r="F291" t="n">
-        <v>209.2927758789062</v>
+        <v>209.2927758026123</v>
       </c>
       <c r="G291" t="n">
-        <v>-1.033718270280792</v>
+        <v>-1.033718556281427</v>
       </c>
       <c r="H291" t="n">
         <v>283.3906875081819</v>
@@ -23047,13 +23047,13 @@
         <v>4448.775986328125</v>
       </c>
       <c r="E294" t="n">
-        <v>4235.811085611979</v>
+        <v>4235.811100260416</v>
       </c>
       <c r="F294" t="n">
-        <v>4294.135028076172</v>
+        <v>4294.135036621094</v>
       </c>
       <c r="G294" t="n">
-        <v>-0.1113609167381013</v>
+        <v>-0.1113607463331334</v>
       </c>
       <c r="H294" t="n">
         <v>5038.987542214121</v>
@@ -24205,19 +24205,19 @@
         <v>380.4406172688802</v>
       </c>
       <c r="F309" t="n">
-        <v>364.4669171905518</v>
+        <v>364.466918334961</v>
       </c>
       <c r="G309" t="n">
-        <v>4.415040808515558</v>
+        <v>4.415040702751538</v>
       </c>
       <c r="H309" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I309" t="n">
-        <v>191.8556371798532</v>
+        <v>191.8556220656042</v>
       </c>
       <c r="J309" t="n">
-        <v>88.16231063441936</v>
+        <v>88.16232545771197</v>
       </c>
       <c r="K309" t="n">
         <v>22.81803509501646</v>
@@ -25046,19 +25046,19 @@
         <v>426.3999938964844</v>
       </c>
       <c r="D320" t="n">
-        <v>410.6988409423828</v>
+        <v>410.6988391113281</v>
       </c>
       <c r="E320" t="n">
-        <v>428.8229728190104</v>
+        <v>428.8229732259115</v>
       </c>
       <c r="F320" t="n">
-        <v>419.6957844543457</v>
+        <v>419.6957847595215</v>
       </c>
       <c r="G320" t="n">
-        <v>1.119874667864651</v>
+        <v>1.119874592689918</v>
       </c>
       <c r="H320" t="n">
-        <v>478.7148398145708</v>
+        <v>478.7148709533388</v>
       </c>
       <c r="I320" t="n">
         <v>355.1755291130353</v>
@@ -25067,7 +25067,7 @@
         <v>20.05331419124368</v>
       </c>
       <c r="K320" t="n">
-        <v>12.26896028774023</v>
+        <v>12.26896759045328</v>
       </c>
       <c r="L320" t="n">
         <v>59.58333333333334</v>
@@ -25434,16 +25434,16 @@
         <v>1264.286374511719</v>
       </c>
       <c r="E325" t="n">
-        <v>1089.335328776042</v>
+        <v>1089.335329589844</v>
       </c>
       <c r="F325" t="n">
-        <v>1146.378231811523</v>
+        <v>1146.378229980469</v>
       </c>
       <c r="G325" t="n">
-        <v>-0.1315403856481767</v>
+        <v>-0.1315402796544851</v>
       </c>
       <c r="H325" t="n">
-        <v>1423.547927723126</v>
+        <v>1423.548053270148</v>
       </c>
       <c r="I325" t="n">
         <v>905.5050975494345</v>
@@ -25452,7 +25452,7 @@
         <v>38.13285559773889</v>
       </c>
       <c r="K325" t="n">
-        <v>13.81099073803589</v>
+        <v>13.81100077537336</v>
       </c>
       <c r="L325" t="n">
         <v>57.36111111111111</v>
@@ -28209,13 +28209,13 @@
         <v>768.3030094401041</v>
       </c>
       <c r="F361" t="n">
-        <v>793.2835162353516</v>
+        <v>793.2835140991211</v>
       </c>
       <c r="G361" t="n">
-        <v>-1.815264945375206</v>
+        <v>-1.815264987260756</v>
       </c>
       <c r="H361" t="n">
-        <v>1203.336364622007</v>
+        <v>1203.336240887604</v>
       </c>
       <c r="I361" t="n">
         <v>648.9423872407145</v>
@@ -28224,7 +28224,7 @@
         <v>29.7572795904645</v>
       </c>
       <c r="K361" t="n">
-        <v>42.90557354866511</v>
+        <v>42.90555885424033</v>
       </c>
       <c r="L361" t="n">
         <v>36.52777777777778</v>
@@ -29364,10 +29364,10 @@
         <v>1145.544513753255</v>
       </c>
       <c r="F376" t="n">
-        <v>1167.715068664551</v>
+        <v>1167.715065002441</v>
       </c>
       <c r="G376" t="n">
-        <v>-0.1477861894789823</v>
+        <v>-0.147786137827266</v>
       </c>
       <c r="H376" t="n">
         <v>1378.852549646065</v>
@@ -29441,10 +29441,10 @@
         <v>731.3741756184896</v>
       </c>
       <c r="F377" t="n">
-        <v>745.822092590332</v>
+        <v>745.8220916748047</v>
       </c>
       <c r="G377" t="n">
-        <v>-0.3708867261926985</v>
+        <v>-0.3708869297216921</v>
       </c>
       <c r="H377" t="n">
         <v>879.2203373423794</v>
@@ -29678,7 +29678,7 @@
         <v>-0.1747577699071856</v>
       </c>
       <c r="H380" t="n">
-        <v>561.4378970396333</v>
+        <v>561.4379586860567</v>
       </c>
       <c r="I380" t="n">
         <v>420.1655789001589</v>
@@ -29687,7 +29687,7 @@
         <v>18.82220369094856</v>
       </c>
       <c r="K380" t="n">
-        <v>12.45626380363212</v>
+        <v>12.45627615143849</v>
       </c>
       <c r="L380" t="n">
         <v>46.66666666666666</v>
@@ -29826,10 +29826,10 @@
         <v>5181.948326822917</v>
       </c>
       <c r="F382" t="n">
-        <v>5294.274338378907</v>
+        <v>5294.27435546875</v>
       </c>
       <c r="G382" t="n">
-        <v>0.1306648902510865</v>
+        <v>0.1306649822981232</v>
       </c>
       <c r="H382" t="n">
         <v>6175.521739453033</v>
@@ -32293,7 +32293,7 @@
         <v>4765.07439086914</v>
       </c>
       <c r="G414" t="n">
-        <v>-0.2321520537239552</v>
+        <v>-0.2321520027261492</v>
       </c>
       <c r="H414" t="n">
         <v>5612.405266256894</v>
@@ -32752,19 +32752,19 @@
         <v>361.9558243815104</v>
       </c>
       <c r="F420" t="n">
-        <v>354.0407514953613</v>
+        <v>354.0407511901856</v>
       </c>
       <c r="G420" t="n">
-        <v>0.2685239621694313</v>
+        <v>0.2685238324092953</v>
       </c>
       <c r="H420" t="n">
         <v>409.9712889887167</v>
       </c>
       <c r="I420" t="n">
-        <v>309.838511773213</v>
+        <v>309.8384816659088</v>
       </c>
       <c r="J420" t="n">
-        <v>7.604439483145109</v>
+        <v>7.604449939172286</v>
       </c>
       <c r="K420" t="n">
         <v>22.96679558908645</v>
@@ -33060,10 +33060,10 @@
         <v>741.6845418294271</v>
       </c>
       <c r="F424" t="n">
-        <v>738.9757223510742</v>
+        <v>738.9757214355469</v>
       </c>
       <c r="G424" t="n">
-        <v>-0.2926390035483006</v>
+        <v>-0.2926388807424463</v>
       </c>
       <c r="H424" t="n">
         <v>837.8765073351432</v>
@@ -33442,22 +33442,22 @@
         <v>340.2564538574219</v>
       </c>
       <c r="E429" t="n">
-        <v>341.474931640625</v>
+        <v>341.4749318440755</v>
       </c>
       <c r="F429" t="n">
-        <v>334.7672491455078</v>
+        <v>334.7672499084472</v>
       </c>
       <c r="G429" t="n">
-        <v>0.01181995651469148</v>
+        <v>0.01181986530560675</v>
       </c>
       <c r="H429" t="n">
         <v>386.0870554430863</v>
       </c>
       <c r="I429" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J429" t="n">
-        <v>11.18937962168676</v>
+        <v>11.18936778251898</v>
       </c>
       <c r="K429" t="n">
         <v>22.84030239842203</v>
@@ -34141,7 +34141,7 @@
         <v>169.8823271942139</v>
       </c>
       <c r="G438" t="n">
-        <v>2.074713929496341</v>
+        <v>2.074713976289044</v>
       </c>
       <c r="H438" t="n">
         <v>211.8067938496122</v>
@@ -34366,13 +34366,13 @@
         <v>156.6641122436523</v>
       </c>
       <c r="E441" t="n">
-        <v>159.7786433919271</v>
+        <v>159.7786432902018</v>
       </c>
       <c r="F441" t="n">
-        <v>155.0355159759521</v>
+        <v>155.0355158233642</v>
       </c>
       <c r="G441" t="n">
-        <v>0.865891046293199</v>
+        <v>0.8658909970862494</v>
       </c>
       <c r="H441" t="n">
         <v>203.5447632528218</v>
@@ -34597,13 +34597,13 @@
         <v>405.8715234375</v>
       </c>
       <c r="E444" t="n">
-        <v>421.2447585042318</v>
+        <v>421.2447578938802</v>
       </c>
       <c r="F444" t="n">
-        <v>417.7933151245117</v>
+        <v>417.7933146667481</v>
       </c>
       <c r="G444" t="n">
-        <v>-0.1533241544950825</v>
+        <v>-0.1533241182523848</v>
       </c>
       <c r="H444" t="n">
         <v>472.8081629796919</v>
@@ -34757,7 +34757,7 @@
         <v>2558.468214111328</v>
       </c>
       <c r="G446" t="n">
-        <v>-0.5044697953961674</v>
+        <v>-0.5044698426282745</v>
       </c>
       <c r="H446" t="n">
         <v>3339</v>
@@ -35524,10 +35524,10 @@
         <v>2257.847731933594</v>
       </c>
       <c r="F456" t="n">
-        <v>2284.035449829102</v>
+        <v>2284.035446166992</v>
       </c>
       <c r="G456" t="n">
-        <v>0.08972654181149675</v>
+        <v>0.08972659549646433</v>
       </c>
       <c r="H456" t="n">
         <v>2765.379504159864</v>
@@ -35681,7 +35681,7 @@
         <v>1505.069541625977</v>
       </c>
       <c r="G458" t="n">
-        <v>0.1964701405315461</v>
+        <v>0.196470221956635</v>
       </c>
       <c r="H458" t="n">
         <v>1765.922465821425</v>
@@ -35752,16 +35752,16 @@
         <v>5488.17763671875</v>
       </c>
       <c r="E459" t="n">
-        <v>5448.350071614584</v>
+        <v>5448.350068359375</v>
       </c>
       <c r="F459" t="n">
-        <v>5487.904418945312</v>
+        <v>5487.904428710937</v>
       </c>
       <c r="G459" t="n">
-        <v>-0.5373536230055542</v>
+        <v>-0.5373536660647105</v>
       </c>
       <c r="H459" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I459" t="n">
         <v>5051</v>
@@ -35770,7 +35770,7 @@
         <v>0.7226291823401398</v>
       </c>
       <c r="K459" t="n">
-        <v>15.489610284057</v>
+        <v>15.4896199963023</v>
       </c>
       <c r="L459" t="n">
         <v>37.77777777777778</v>
@@ -35906,16 +35906,16 @@
         <v>19.62470390319824</v>
       </c>
       <c r="E461" t="n">
-        <v>20.61371276855469</v>
+        <v>20.6137127049764</v>
       </c>
       <c r="F461" t="n">
-        <v>20.6421718788147</v>
+        <v>20.64217186927796</v>
       </c>
       <c r="G461" t="n">
-        <v>-1.359108475746817</v>
+        <v>-1.359108566272171</v>
       </c>
       <c r="H461" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I461" t="n">
         <v>18.76000022888184</v>
@@ -35924,7 +35924,7 @@
         <v>4.69082702574708</v>
       </c>
       <c r="K461" t="n">
-        <v>21.36080951964332</v>
+        <v>21.36079933612049</v>
       </c>
       <c r="L461" t="n">
         <v>36.66666666666666</v>
@@ -36063,19 +36063,19 @@
         <v>36543.73829427084</v>
       </c>
       <c r="F463" t="n">
-        <v>36194.47250976563</v>
+        <v>36194.4725390625</v>
       </c>
       <c r="G463" t="n">
-        <v>-1.097501907190834</v>
+        <v>-1.097501800744238</v>
       </c>
       <c r="H463" t="n">
         <v>45150.8475731383</v>
       </c>
       <c r="I463" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J463" t="n">
-        <v>19.7787377622701</v>
+        <v>19.77872994242777</v>
       </c>
       <c r="K463" t="n">
         <v>27.67099554117998</v>
@@ -36297,7 +36297,7 @@
         <v>946.9251034545898</v>
       </c>
       <c r="G466" t="n">
-        <v>0.5072746797161187</v>
+        <v>0.5072746146043583</v>
       </c>
       <c r="H466" t="n">
         <v>1224.72508309492</v>
@@ -36368,22 +36368,22 @@
         <v>238.5343508911133</v>
       </c>
       <c r="E467" t="n">
-        <v>226.782133992513</v>
+        <v>226.7821342976888</v>
       </c>
       <c r="F467" t="n">
-        <v>226.7291130065918</v>
+        <v>226.7291125488281</v>
       </c>
       <c r="G467" t="n">
-        <v>-1.411909953539581</v>
+        <v>-1.411909890937324</v>
       </c>
       <c r="H467" t="n">
         <v>286.0804516993438</v>
       </c>
       <c r="I467" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J467" t="n">
-        <v>23.62692610641624</v>
+        <v>23.62693699990319</v>
       </c>
       <c r="K467" t="n">
         <v>34.57543006641926</v>
@@ -36685,7 +36685,7 @@
         <v>-0.7619443260455383</v>
       </c>
       <c r="H471" t="n">
-        <v>796.6711586352184</v>
+        <v>796.6710965617623</v>
       </c>
       <c r="I471" t="n">
         <v>553.7186859929476</v>
@@ -36694,7 +36694,7 @@
         <v>20.85559493210862</v>
       </c>
       <c r="K471" t="n">
-        <v>19.04828812058528</v>
+        <v>19.04827884481495</v>
       </c>
       <c r="L471" t="n">
         <v>32.5</v>
@@ -37446,13 +37446,13 @@
         <v>300.7577362060547</v>
       </c>
       <c r="E481" t="n">
-        <v>273.6666665649414</v>
+        <v>273.6666661580404</v>
       </c>
       <c r="F481" t="n">
-        <v>289.1837824249267</v>
+        <v>289.1837828826904</v>
       </c>
       <c r="G481" t="n">
-        <v>-2.473801627459249</v>
+        <v>-2.473801523266772</v>
       </c>
       <c r="H481" t="n">
         <v>411.0263372414121</v>
@@ -38527,19 +38527,19 @@
         <v>260.6732721964518</v>
       </c>
       <c r="F495" t="n">
-        <v>254.7806271362305</v>
+        <v>254.7806270599365</v>
       </c>
       <c r="G495" t="n">
-        <v>-0.2343422396177242</v>
+        <v>-0.2343422992972632</v>
       </c>
       <c r="H495" t="n">
         <v>306.197022156633</v>
       </c>
       <c r="I495" t="n">
-        <v>220.3071254131767</v>
+        <v>220.307140654885</v>
       </c>
       <c r="J495" t="n">
-        <v>5.534489437850021</v>
+        <v>5.534482136561958</v>
       </c>
       <c r="K495" t="n">
         <v>31.69764393833676</v>
@@ -38681,10 +38681,10 @@
         <v>845.2377392578124</v>
       </c>
       <c r="F497" t="n">
-        <v>859.9790991210938</v>
+        <v>859.9790994262695</v>
       </c>
       <c r="G497" t="n">
-        <v>-0.6961920619410811</v>
+        <v>-0.6961920267017252</v>
       </c>
       <c r="H497" t="n">
         <v>962.6932158005569</v>
@@ -39069,7 +39069,7 @@
         <v>392.5596336364746</v>
       </c>
       <c r="G502" t="n">
-        <v>-0.1889085268849011</v>
+        <v>-0.1889084107150829</v>
       </c>
       <c r="H502" t="n">
         <v>476.8288845013619</v>
@@ -39146,7 +39146,7 @@
         <v>385.6463909912109</v>
       </c>
       <c r="G503" t="n">
-        <v>-2.411459376116254</v>
+        <v>-2.411459413797767</v>
       </c>
       <c r="H503" t="n">
         <v>483.5386775606495</v>
@@ -39451,10 +39451,10 @@
         <v>2445.858313802084</v>
       </c>
       <c r="F507" t="n">
-        <v>2453.707316894531</v>
+        <v>2453.707322998047</v>
       </c>
       <c r="G507" t="n">
-        <v>-0.9390715666567906</v>
+        <v>-0.9390714178847293</v>
       </c>
       <c r="H507" t="n">
         <v>3039.742428602358</v>
@@ -39608,10 +39608,10 @@
         <v>215.6173418426514</v>
       </c>
       <c r="G509" t="n">
-        <v>-1.244240961628351</v>
+        <v>-1.244240996137269</v>
       </c>
       <c r="H509" t="n">
-        <v>272.099752952214</v>
+        <v>272.0997840702363</v>
       </c>
       <c r="I509" t="n">
         <v>173.9540675101702</v>
@@ -39620,7 +39620,7 @@
         <v>20.23288497364768</v>
       </c>
       <c r="K509" t="n">
-        <v>30.09790145482176</v>
+        <v>30.09791633314986</v>
       </c>
       <c r="L509" t="n">
         <v>32.77777777777778</v>
@@ -39679,16 +39679,16 @@
         <v>711.817275390625</v>
       </c>
       <c r="E510" t="n">
-        <v>739.6160359700521</v>
+        <v>739.6160351562499</v>
       </c>
       <c r="F510" t="n">
-        <v>761.8982760620117</v>
+        <v>761.8982751464844</v>
       </c>
       <c r="G510" t="n">
-        <v>-3.954038680841809</v>
+        <v>-3.954038722355002</v>
       </c>
       <c r="H510" t="n">
-        <v>1117.559301306357</v>
+        <v>1117.559425954049</v>
       </c>
       <c r="I510" t="n">
         <v>612.1496526863262</v>
@@ -39697,7 +39697,7 @@
         <v>17.97768879517707</v>
       </c>
       <c r="K510" t="n">
-        <v>54.74373891120745</v>
+        <v>54.74375617064948</v>
       </c>
       <c r="L510" t="n">
         <v>32.63888888888889</v>
@@ -39756,16 +39756,16 @@
         <v>434.2975555419922</v>
       </c>
       <c r="E511" t="n">
-        <v>425.6674151611328</v>
+        <v>425.6674149576823</v>
       </c>
       <c r="F511" t="n">
-        <v>444.9950204467773</v>
+        <v>444.9950192260742</v>
       </c>
       <c r="G511" t="n">
-        <v>-1.851809647466673</v>
+        <v>-1.851809553357686</v>
       </c>
       <c r="H511" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I511" t="n">
         <v>363.2227809620478</v>
@@ -39774,7 +39774,7 @@
         <v>14.98452624317181</v>
       </c>
       <c r="K511" t="n">
-        <v>27.78852208844724</v>
+        <v>27.78853731659288</v>
       </c>
       <c r="L511" t="n">
         <v>32.36111111111111</v>
@@ -39910,13 +39910,13 @@
         <v>341.3380230712891</v>
       </c>
       <c r="E513" t="n">
-        <v>341.7155609130859</v>
+        <v>341.7155623372396</v>
       </c>
       <c r="F513" t="n">
-        <v>343.0791777038574</v>
+        <v>343.0791789245606</v>
       </c>
       <c r="G513" t="n">
-        <v>-0.8730202001900556</v>
+        <v>-0.8730200660024168</v>
       </c>
       <c r="H513" t="n">
         <v>381.3442016302781</v>
@@ -40147,7 +40147,7 @@
         <v>580.7664199829102</v>
       </c>
       <c r="G516" t="n">
-        <v>-0.002444167572479561</v>
+        <v>-0.002444009938962211</v>
       </c>
       <c r="H516" t="n">
         <v>732.5560380476754</v>
@@ -40221,10 +40221,10 @@
         <v>2010.541654459635</v>
       </c>
       <c r="F517" t="n">
-        <v>2081.286513061523</v>
+        <v>2081.286514282227</v>
       </c>
       <c r="G517" t="n">
-        <v>-1.200871542806969</v>
+        <v>-1.20087137035757</v>
       </c>
       <c r="H517" t="n">
         <v>2486.766809421043</v>
@@ -40458,7 +40458,7 @@
         <v>-0.9367918370739026</v>
       </c>
       <c r="H520" t="n">
-        <v>1045.658313207837</v>
+        <v>1045.658437762529</v>
       </c>
       <c r="I520" t="n">
         <v>666.0087356197063</v>
@@ -40467,7 +40467,7 @@
         <v>22.20560795749122</v>
       </c>
       <c r="K520" t="n">
-        <v>28.4750315569311</v>
+        <v>28.4750468603699</v>
       </c>
       <c r="L520" t="n">
         <v>28.19444444444444</v>
@@ -40526,13 +40526,13 @@
         <v>2826.932177734375</v>
       </c>
       <c r="E521" t="n">
-        <v>2832.423523763021</v>
+        <v>2832.423520507813</v>
       </c>
       <c r="F521" t="n">
-        <v>2757.152436523438</v>
+        <v>2757.152440185547</v>
       </c>
       <c r="G521" t="n">
-        <v>-0.909874727761073</v>
+        <v>-0.9098746396194679</v>
       </c>
       <c r="H521" t="n">
         <v>3415.14446256242</v>
@@ -40609,7 +40609,7 @@
         <v>3548.134403076172</v>
       </c>
       <c r="G522" t="n">
-        <v>-0.5441754060628745</v>
+        <v>-0.5441753380015402</v>
       </c>
       <c r="H522" t="n">
         <v>4586.205351504792</v>
@@ -40757,13 +40757,13 @@
         <v>1279.910549316406</v>
       </c>
       <c r="E524" t="n">
-        <v>1260.421276448568</v>
+        <v>1260.421268310547</v>
       </c>
       <c r="F524" t="n">
-        <v>1346.872145690918</v>
+        <v>1346.872137756348</v>
       </c>
       <c r="G524" t="n">
-        <v>-1.743534731800211</v>
+        <v>-1.743534610643105</v>
       </c>
       <c r="H524" t="n">
         <v>1729.008500794829</v>
@@ -42608,19 +42608,19 @@
         <v>945.5330428059896</v>
       </c>
       <c r="F548" t="n">
-        <v>926.8373138427735</v>
+        <v>926.8373162841797</v>
       </c>
       <c r="G548" t="n">
-        <v>-0.3407756473247758</v>
+        <v>-0.3407757772403652</v>
       </c>
       <c r="H548" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I548" t="n">
-        <v>743.4272688553443</v>
+        <v>743.4273285628773</v>
       </c>
       <c r="J548" t="n">
-        <v>2.975774479148008</v>
+        <v>2.975766208764052</v>
       </c>
       <c r="K548" t="n">
         <v>67.56705905619663</v>
@@ -42839,10 +42839,10 @@
         <v>1649.390045572917</v>
       </c>
       <c r="F551" t="n">
-        <v>1760.007505493164</v>
+        <v>1760.007496948242</v>
       </c>
       <c r="G551" t="n">
-        <v>-2.855161486254454</v>
+        <v>-2.855161630628267</v>
       </c>
       <c r="H551" t="n">
         <v>2528.447285363935</v>
@@ -43843,7 +43843,7 @@
         <v>547.5376295471192</v>
       </c>
       <c r="G564" t="n">
-        <v>-3.526872548685667</v>
+        <v>-3.52687260055955</v>
       </c>
       <c r="H564" t="n">
         <v>872.0425606177564</v>
@@ -44225,10 +44225,10 @@
         <v>362.581994527181</v>
       </c>
       <c r="F569" t="n">
-        <v>361.6640578460693</v>
+        <v>361.6640581512451</v>
       </c>
       <c r="G569" t="n">
-        <v>-2.376798634575972</v>
+        <v>-2.376798552200532</v>
       </c>
       <c r="H569" t="n">
         <v>487.9415273208757</v>
@@ -44536,7 +44536,7 @@
         <v>324.9440606689453</v>
       </c>
       <c r="G573" t="n">
-        <v>-1.264636296387656</v>
+        <v>-1.264636204831637</v>
       </c>
       <c r="H573" t="n">
         <v>391.6499938964844</v>
@@ -44610,10 +44610,10 @@
         <v>144.5362440999349</v>
       </c>
       <c r="F574" t="n">
-        <v>147.9464297485352</v>
+        <v>147.9464302062988</v>
       </c>
       <c r="G574" t="n">
-        <v>-1.583224360024915</v>
+        <v>-1.583224155409146</v>
       </c>
       <c r="H574" t="n">
         <v>184.9587904135824</v>
@@ -44841,10 +44841,10 @@
         <v>132474.8955729167</v>
       </c>
       <c r="F577" t="n">
-        <v>136182.18796875</v>
+        <v>136182.188203125</v>
       </c>
       <c r="G577" t="n">
-        <v>-1.985175298018704</v>
+        <v>-1.985175129331251</v>
       </c>
       <c r="H577" t="n">
         <v>163308.4863287346</v>
@@ -45839,13 +45839,13 @@
         <v>441.1740155029297</v>
       </c>
       <c r="E590" t="n">
-        <v>464.7930312093099</v>
+        <v>464.7930308024089</v>
       </c>
       <c r="F590" t="n">
-        <v>468.1580233764648</v>
+        <v>468.158023223877</v>
       </c>
       <c r="G590" t="n">
-        <v>-0.9592333802828201</v>
+        <v>-0.9592332527086467</v>
       </c>
       <c r="H590" t="n">
         <v>555.1842484654879</v>
@@ -46153,7 +46153,7 @@
         <v>129.9487512588501</v>
       </c>
       <c r="G594" t="n">
-        <v>-1.948903759964582</v>
+        <v>-1.948903703519911</v>
       </c>
       <c r="H594" t="n">
         <v>187.6354050126281</v>
@@ -46301,13 +46301,13 @@
         <v>482.4010290527344</v>
       </c>
       <c r="E596" t="n">
-        <v>533.6281477864584</v>
+        <v>533.6281469726563</v>
       </c>
       <c r="F596" t="n">
-        <v>537.3891604614258</v>
+        <v>537.3891635131836</v>
       </c>
       <c r="G596" t="n">
-        <v>-1.523105102909528</v>
+        <v>-1.523104819032406</v>
       </c>
       <c r="H596" t="n">
         <v>653.9340000086492</v>
@@ -46846,10 +46846,10 @@
         <v>1102.225216369629</v>
       </c>
       <c r="G603" t="n">
-        <v>-1.987856397981702</v>
+        <v>-1.987856504371377</v>
       </c>
       <c r="H603" t="n">
-        <v>1400.476649260813</v>
+        <v>1400.476774401248</v>
       </c>
       <c r="I603" t="n">
         <v>941.5197177909594</v>
@@ -46858,7 +46858,7 @@
         <v>6.211264735511857</v>
       </c>
       <c r="K603" t="n">
-        <v>40.04766492608125</v>
+        <v>40.04767744012483</v>
       </c>
       <c r="L603" t="n">
         <v>23.61111111111111</v>
@@ -46920,13 +46920,13 @@
         <v>123.4198331705729</v>
       </c>
       <c r="F604" t="n">
-        <v>126.0003953933716</v>
+        <v>126.000394744873</v>
       </c>
       <c r="G604" t="n">
-        <v>-1.356101972154489</v>
+        <v>-1.356102037958851</v>
       </c>
       <c r="H604" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I604" t="n">
         <v>112.8155071321618</v>
@@ -46935,7 +46935,7 @@
         <v>0.9435671995066341</v>
       </c>
       <c r="K604" t="n">
-        <v>36.89847395072119</v>
+        <v>36.8984584299136</v>
       </c>
       <c r="L604" t="n">
         <v>23.47222222222222</v>
@@ -46991,28 +46991,28 @@
         <v>172.7599945068359</v>
       </c>
       <c r="D605" t="n">
-        <v>191.9940640258789</v>
+        <v>191.9940634155273</v>
       </c>
       <c r="E605" t="n">
-        <v>193.6329960123698</v>
+        <v>193.6329965209961</v>
       </c>
       <c r="F605" t="n">
-        <v>197.4191023254394</v>
+        <v>197.4191028594971</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.340041809422588</v>
+        <v>-2.340041803240445</v>
       </c>
       <c r="H605" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I605" t="n">
-        <v>156.7442971017576</v>
+        <v>156.7443123050878</v>
       </c>
       <c r="J605" t="n">
-        <v>10.21772255910594</v>
+        <v>10.21771186859726</v>
       </c>
       <c r="K605" t="n">
-        <v>38.46880723958363</v>
+        <v>38.46878936339935</v>
       </c>
       <c r="L605" t="n">
         <v>23.19444444444445</v>
@@ -47305,10 +47305,10 @@
         <v>7781.855380859375</v>
       </c>
       <c r="F609" t="n">
-        <v>7839.586865234375</v>
+        <v>7839.586875</v>
       </c>
       <c r="G609" t="n">
-        <v>-1.336765150056229</v>
+        <v>-1.336765209043311</v>
       </c>
       <c r="H609" t="n">
         <v>10255.65092965882</v>
@@ -47687,16 +47687,16 @@
         <v>67.53223892211913</v>
       </c>
       <c r="E614" t="n">
-        <v>71.26353902180989</v>
+        <v>71.26353917439779</v>
       </c>
       <c r="F614" t="n">
-        <v>71.87717212677002</v>
+        <v>71.87717205047608</v>
       </c>
       <c r="G614" t="n">
-        <v>-2.534760887161802</v>
+        <v>-2.534760940200154</v>
       </c>
       <c r="H614" t="n">
-        <v>93.44221530383422</v>
+        <v>93.44222215601812</v>
       </c>
       <c r="I614" t="n">
         <v>62.68610889438828</v>
@@ -47705,7 +47705,7 @@
         <v>5.573629425099424</v>
       </c>
       <c r="K614" t="n">
-        <v>41.19403879260231</v>
+        <v>41.19404914646127</v>
       </c>
       <c r="L614" t="n">
         <v>20.27777777777778</v>
@@ -48312,7 +48312,7 @@
         <v>-2.624171185276525</v>
       </c>
       <c r="H622" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I622" t="n">
         <v>185.2067002350832</v>
@@ -48321,7 +48321,7 @@
         <v>15.69236102175982</v>
       </c>
       <c r="K622" t="n">
-        <v>43.77872705013932</v>
+        <v>43.77871212662874</v>
       </c>
       <c r="L622" t="n">
         <v>18.33333333333333</v>
@@ -49079,7 +49079,7 @@
         <v>2200.836365966797</v>
       </c>
       <c r="G632" t="n">
-        <v>-1.984191457961626</v>
+        <v>-1.984191191530749</v>
       </c>
       <c r="H632" t="n">
         <v>2619.749708059458</v>
@@ -49381,16 +49381,16 @@
         <v>91.70302947998047</v>
       </c>
       <c r="E636" t="n">
-        <v>93.59483810424804</v>
+        <v>93.59483784993489</v>
       </c>
       <c r="F636" t="n">
-        <v>97.34520015716552</v>
+        <v>97.34520004272461</v>
       </c>
       <c r="G636" t="n">
-        <v>-2.893821235787553</v>
+        <v>-2.893821128234797</v>
       </c>
       <c r="H636" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I636" t="n">
         <v>76.65010804466255</v>
@@ -49399,7 +49399,7 @@
         <v>8.153796048890971</v>
       </c>
       <c r="K636" t="n">
-        <v>50.57575330821413</v>
+        <v>50.57576279477218</v>
       </c>
       <c r="L636" t="n">
         <v>14.58333333333333</v>
@@ -49772,7 +49772,7 @@
         <v>1739.980589599609</v>
       </c>
       <c r="G641" t="n">
-        <v>-4.036566111150941</v>
+        <v>-4.036565949634308</v>
       </c>
       <c r="H641" t="n">
         <v>2504.019782423858</v>
@@ -50080,7 +50080,7 @@
         <v>301.0580475616455</v>
       </c>
       <c r="G645" t="n">
-        <v>-3.298790736273993</v>
+        <v>-3.298790831064236</v>
       </c>
       <c r="H645" t="n">
         <v>398.6210131186603</v>
@@ -51229,13 +51229,13 @@
         <v>990.5183642578126</v>
       </c>
       <c r="E660" t="n">
-        <v>1038.819401855469</v>
+        <v>1038.819405924479</v>
       </c>
       <c r="F660" t="n">
-        <v>1072.215469360352</v>
+        <v>1072.215469970703</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.102908743145271</v>
+        <v>-2.102908578307239</v>
       </c>
       <c r="H660" t="n">
         <v>1255.178432949836</v>
@@ -51771,13 +51771,13 @@
         <v>189.0392256673177</v>
       </c>
       <c r="F667" t="n">
-        <v>203.530721206665</v>
+        <v>203.5307217407227</v>
       </c>
       <c r="G667" t="n">
-        <v>-2.977184171150138</v>
+        <v>-2.977184092997809</v>
       </c>
       <c r="H667" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I667" t="n">
         <v>165.1600036621094</v>
@@ -51786,7 +51786,7 @@
         <v>1.356254652886579</v>
       </c>
       <c r="K667" t="n">
-        <v>57.24044677284961</v>
+        <v>57.24046503193239</v>
       </c>
       <c r="L667" t="n">
         <v>8.888888888888889</v>
@@ -52541,13 +52541,13 @@
         <v>289.4460902913411</v>
       </c>
       <c r="F677" t="n">
-        <v>304.2117446899414</v>
+        <v>304.2117442321778</v>
       </c>
       <c r="G677" t="n">
-        <v>-4.261203326942564</v>
+        <v>-4.261203333081376</v>
       </c>
       <c r="H677" t="n">
-        <v>406.5707952146441</v>
+        <v>406.5707642578344</v>
       </c>
       <c r="I677" t="n">
         <v>255.5</v>
@@ -52556,7 +52556,7 @@
         <v>1.702546420162676</v>
       </c>
       <c r="K677" t="n">
-        <v>56.46364659028706</v>
+        <v>56.46363467694901</v>
       </c>
       <c r="L677" t="n">
         <v>7.5</v>
@@ -53160,7 +53160,7 @@
         <v>442.0350219726562</v>
       </c>
       <c r="G685" t="n">
-        <v>-3.177441695783523</v>
+        <v>-3.177441598701747</v>
       </c>
       <c r="H685" t="n">
         <v>602.0840578111723</v>
@@ -54851,10 +54851,10 @@
         <v>503.1672961425782</v>
       </c>
       <c r="F707" t="n">
-        <v>550.5517208862304</v>
+        <v>550.5517205810547</v>
       </c>
       <c r="G707" t="n">
-        <v>-4.809176141327609</v>
+        <v>-4.809176244320302</v>
       </c>
       <c r="H707" t="n">
         <v>845.3898333433813</v>
@@ -54931,7 +54931,7 @@
         <v>453.1180693054199</v>
       </c>
       <c r="G708" t="n">
-        <v>-5.319656364003977</v>
+        <v>-5.319656001752982</v>
       </c>
       <c r="H708" t="n">
         <v>606.7970321970149</v>
@@ -55393,7 +55393,7 @@
         <v>401.4955911254883</v>
       </c>
       <c r="G714" t="n">
-        <v>-4.77280123408681</v>
+        <v>-4.772801303014118</v>
       </c>
       <c r="H714" t="n">
         <v>541.6977805031639</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1647,16 +1647,16 @@
         <v>1290.538489685058</v>
       </c>
       <c r="G16" t="n">
-        <v>8.214518402589954</v>
+        <v>8.2145183472065</v>
       </c>
       <c r="H16" t="n">
         <v>1981.800048828125</v>
       </c>
       <c r="I16" t="n">
-        <v>821.6033975811163</v>
+        <v>821.6033372206257</v>
       </c>
       <c r="J16" t="n">
-        <v>139.6533419648623</v>
+        <v>139.6533595714039</v>
       </c>
       <c r="K16" t="n">
         <v>0.6500786606462583</v>
@@ -2026,13 +2026,13 @@
         <v>1289.473422851562</v>
       </c>
       <c r="E21" t="n">
-        <v>1088.130807291667</v>
+        <v>1088.130806477865</v>
       </c>
       <c r="F21" t="n">
-        <v>1022.508684387207</v>
+        <v>1022.508684692383</v>
       </c>
       <c r="G21" t="n">
-        <v>5.569075223766218</v>
+        <v>5.569075155486258</v>
       </c>
       <c r="H21" t="n">
         <v>1677.5</v>
@@ -4262,10 +4262,10 @@
         <v>245.2917078653971</v>
       </c>
       <c r="F50" t="n">
-        <v>233.937264251709</v>
+        <v>233.937264175415</v>
       </c>
       <c r="G50" t="n">
-        <v>6.891633198212199</v>
+        <v>6.891633200614633</v>
       </c>
       <c r="H50" t="n">
         <v>388.75</v>
@@ -5035,7 +5035,7 @@
         <v>6853.579338378906</v>
       </c>
       <c r="G60" t="n">
-        <v>4.568570401122307</v>
+        <v>4.568570362170732</v>
       </c>
       <c r="H60" t="n">
         <v>8949.5</v>
@@ -5565,25 +5565,25 @@
         <v>12097</v>
       </c>
       <c r="D67" t="n">
-        <v>11009.639140625</v>
+        <v>11009.6391015625</v>
       </c>
       <c r="E67" t="n">
-        <v>10596.02934244792</v>
+        <v>10596.02938802083</v>
       </c>
       <c r="F67" t="n">
-        <v>10190.40307617188</v>
+        <v>10190.40311279297</v>
       </c>
       <c r="G67" t="n">
-        <v>3.139077272187496</v>
+        <v>3.139077107638832</v>
       </c>
       <c r="H67" t="n">
         <v>12865.82946046676</v>
       </c>
       <c r="I67" t="n">
-        <v>6613.3742727433</v>
+        <v>6613.373792726331</v>
       </c>
       <c r="J67" t="n">
-        <v>82.91721443707181</v>
+        <v>82.91722771370935</v>
       </c>
       <c r="K67" t="n">
         <v>6.355538236478098</v>
@@ -7576,7 +7576,7 @@
         <v>1008.315387268066</v>
       </c>
       <c r="G93" t="n">
-        <v>3.762152627304705</v>
+        <v>3.76215252954657</v>
       </c>
       <c r="H93" t="n">
         <v>1269.5</v>
@@ -8035,10 +8035,10 @@
         <v>230.5883953857422</v>
       </c>
       <c r="F99" t="n">
-        <v>220.5138858032226</v>
+        <v>220.5138857269287</v>
       </c>
       <c r="G99" t="n">
-        <v>3.143815262521299</v>
+        <v>3.143815300451069</v>
       </c>
       <c r="H99" t="n">
         <v>289.6499938964844</v>
@@ -8343,10 +8343,10 @@
         <v>612.2455529785157</v>
       </c>
       <c r="F103" t="n">
-        <v>603.4321856689453</v>
+        <v>603.4321853637696</v>
       </c>
       <c r="G103" t="n">
-        <v>2.431914858605744</v>
+        <v>2.43191470067643</v>
       </c>
       <c r="H103" t="n">
         <v>769</v>
@@ -9646,16 +9646,16 @@
         <v>1074.800048828125</v>
       </c>
       <c r="D120" t="n">
-        <v>1023.6475</v>
+        <v>1023.647503662109</v>
       </c>
       <c r="E120" t="n">
-        <v>926.5439957682291</v>
+        <v>926.5439973958333</v>
       </c>
       <c r="F120" t="n">
-        <v>899.1548605346679</v>
+        <v>899.1548626708984</v>
       </c>
       <c r="G120" t="n">
-        <v>2.308718447682256</v>
+        <v>2.308718406544963</v>
       </c>
       <c r="H120" t="n">
         <v>1111</v>
@@ -12812,7 +12812,7 @@
         <v>994.3643133544922</v>
       </c>
       <c r="G161" t="n">
-        <v>3.331079102438195</v>
+        <v>3.331079135207449</v>
       </c>
       <c r="H161" t="n">
         <v>1153.699951171875</v>
@@ -13582,7 +13582,7 @@
         <v>1100.486620483398</v>
       </c>
       <c r="G171" t="n">
-        <v>2.213079840219501</v>
+        <v>2.213079753303537</v>
       </c>
       <c r="H171" t="n">
         <v>1596.696405272527</v>
@@ -13807,13 +13807,13 @@
         <v>306.0007946777343</v>
       </c>
       <c r="E174" t="n">
-        <v>295.5614790852865</v>
+        <v>295.5614795939127</v>
       </c>
       <c r="F174" t="n">
-        <v>284.2275992584229</v>
+        <v>284.2275999450683</v>
       </c>
       <c r="G174" t="n">
-        <v>1.302283138974003</v>
+        <v>1.302283053148212</v>
       </c>
       <c r="H174" t="n">
         <v>359.3387168134344</v>
@@ -14121,7 +14121,7 @@
         <v>1518.129981079102</v>
       </c>
       <c r="G178" t="n">
-        <v>0.755314824547737</v>
+        <v>0.755314865361556</v>
       </c>
       <c r="H178" t="n">
         <v>2021.199951171875</v>
@@ -14346,13 +14346,13 @@
         <v>460.3666107177734</v>
       </c>
       <c r="E181" t="n">
-        <v>464.3686503092448</v>
+        <v>464.3686496988933</v>
       </c>
       <c r="F181" t="n">
-        <v>454.3492445373535</v>
+        <v>454.349242553711</v>
       </c>
       <c r="G181" t="n">
-        <v>1.516439464047603</v>
+        <v>1.51643936693826</v>
       </c>
       <c r="H181" t="n">
         <v>529.9163379046904</v>
@@ -17044,10 +17044,10 @@
         <v>149.393951365153</v>
       </c>
       <c r="F216" t="n">
-        <v>151.3906978225708</v>
+        <v>151.3906974411011</v>
       </c>
       <c r="G216" t="n">
-        <v>-0.2625995095031364</v>
+        <v>-0.2625995101630862</v>
       </c>
       <c r="H216" t="n">
         <v>212.3300018310547</v>
@@ -17355,7 +17355,7 @@
         <v>932.8334811401368</v>
       </c>
       <c r="G220" t="n">
-        <v>-1.700937860540408</v>
+        <v>-1.700937734094532</v>
       </c>
       <c r="H220" t="n">
         <v>1352</v>
@@ -17657,16 +17657,16 @@
         <v>1355.512041015625</v>
       </c>
       <c r="E224" t="n">
-        <v>1400.955208333333</v>
+        <v>1400.955205891927</v>
       </c>
       <c r="F224" t="n">
-        <v>1324.914418334961</v>
+        <v>1324.914420166016</v>
       </c>
       <c r="G224" t="n">
-        <v>2.299080401068365</v>
+        <v>2.299080518342556</v>
       </c>
       <c r="H224" t="n">
-        <v>1766.733060850261</v>
+        <v>1766.733188761222</v>
       </c>
       <c r="I224" t="n">
         <v>941.3310566553616</v>
@@ -17675,7 +17675,7 @@
         <v>50.02160410913829</v>
       </c>
       <c r="K224" t="n">
-        <v>25.10502208870538</v>
+        <v>25.10503114627272</v>
       </c>
       <c r="L224" t="n">
         <v>78.05555555555556</v>
@@ -18199,10 +18199,10 @@
         <v>1675.087139485677</v>
       </c>
       <c r="F231" t="n">
-        <v>1680.709583129883</v>
+        <v>1680.709582519531</v>
       </c>
       <c r="G231" t="n">
-        <v>1.039188269096125</v>
+        <v>1.039188158256055</v>
       </c>
       <c r="H231" t="n">
         <v>1952.5</v>
@@ -18276,10 +18276,10 @@
         <v>995.9606477864584</v>
       </c>
       <c r="F232" t="n">
-        <v>955.2263659667968</v>
+        <v>955.2263647460937</v>
       </c>
       <c r="G232" t="n">
-        <v>2.754663298163007</v>
+        <v>2.75466323431548</v>
       </c>
       <c r="H232" t="n">
         <v>1303.791320684363</v>
@@ -18350,13 +18350,13 @@
         <v>346.8080181884766</v>
       </c>
       <c r="E233" t="n">
-        <v>311.1581471761068</v>
+        <v>311.1581469726563</v>
       </c>
       <c r="F233" t="n">
-        <v>306.7464488220215</v>
+        <v>306.746448059082</v>
       </c>
       <c r="G233" t="n">
-        <v>2.546704624382978</v>
+        <v>2.546704787808185</v>
       </c>
       <c r="H233" t="n">
         <v>380.4567148307952</v>
@@ -18427,13 +18427,13 @@
         <v>1111.764846191406</v>
       </c>
       <c r="E234" t="n">
-        <v>1002.457798258464</v>
+        <v>1002.457799072266</v>
       </c>
       <c r="F234" t="n">
-        <v>984.0659805297852</v>
+        <v>984.0659790039062</v>
       </c>
       <c r="G234" t="n">
-        <v>0.6728456551366113</v>
+        <v>0.6728458447696317</v>
       </c>
       <c r="H234" t="n">
         <v>1331.075409591023</v>
@@ -18812,16 +18812,16 @@
         <v>1877.341997070313</v>
       </c>
       <c r="E239" t="n">
-        <v>1770.329894205729</v>
+        <v>1770.329895833333</v>
       </c>
       <c r="F239" t="n">
-        <v>1768.468275146484</v>
+        <v>1768.468278808594</v>
       </c>
       <c r="G239" t="n">
-        <v>-0.2496195193062101</v>
+        <v>-0.2496195187905781</v>
       </c>
       <c r="H239" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I239" t="n">
         <v>1353.205955540699</v>
@@ -18830,7 +18830,7 @@
         <v>49.52639072635292</v>
       </c>
       <c r="K239" t="n">
-        <v>12.16131142014325</v>
+        <v>12.16132379430404</v>
       </c>
       <c r="L239" t="n">
         <v>65.69444444444444</v>
@@ -21279,19 +21279,19 @@
         <v>723.4834842936198</v>
       </c>
       <c r="F271" t="n">
-        <v>675.3895104980469</v>
+        <v>675.3895097351074</v>
       </c>
       <c r="G271" t="n">
-        <v>3.184332877048979</v>
+        <v>3.184332880760632</v>
       </c>
       <c r="H271" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I271" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J271" t="n">
-        <v>46.5340870832869</v>
+        <v>46.53406988101598</v>
       </c>
       <c r="K271" t="n">
         <v>51.90153539746832</v>
@@ -21738,13 +21738,13 @@
         <v>5361.79875</v>
       </c>
       <c r="E277" t="n">
-        <v>5182.173863932292</v>
+        <v>5182.173860677083</v>
       </c>
       <c r="F277" t="n">
-        <v>4946.330826416016</v>
+        <v>4946.33081665039</v>
       </c>
       <c r="G277" t="n">
-        <v>2.093080657930901</v>
+        <v>2.09308071359553</v>
       </c>
       <c r="H277" t="n">
         <v>6049.821052103703</v>
@@ -21895,10 +21895,10 @@
         <v>1378.664289550781</v>
       </c>
       <c r="F279" t="n">
-        <v>1350.217305297851</v>
+        <v>1350.217307739258</v>
       </c>
       <c r="G279" t="n">
-        <v>1.540566394928455</v>
+        <v>1.540566345492489</v>
       </c>
       <c r="H279" t="n">
         <v>1553</v>
@@ -22511,10 +22511,10 @@
         <v>1828.632711588542</v>
       </c>
       <c r="F287" t="n">
-        <v>1799.771480712891</v>
+        <v>1799.771480102539</v>
       </c>
       <c r="G287" t="n">
-        <v>1.155432783880483</v>
+        <v>1.155432818977764</v>
       </c>
       <c r="H287" t="n">
         <v>2046.900024414062</v>
@@ -23047,13 +23047,13 @@
         <v>4448.775986328125</v>
       </c>
       <c r="E294" t="n">
-        <v>4235.811100260416</v>
+        <v>4235.811085611979</v>
       </c>
       <c r="F294" t="n">
-        <v>4294.135036621094</v>
+        <v>4294.135028076172</v>
       </c>
       <c r="G294" t="n">
-        <v>-0.1113607463331334</v>
+        <v>-0.1113609167381013</v>
       </c>
       <c r="H294" t="n">
         <v>5038.987542214121</v>
@@ -23204,13 +23204,13 @@
         <v>5118.925283203125</v>
       </c>
       <c r="F296" t="n">
-        <v>5400.457785644531</v>
+        <v>5400.457780761719</v>
       </c>
       <c r="G296" t="n">
-        <v>-0.8420364444044814</v>
+        <v>-0.8420363118115781</v>
       </c>
       <c r="H296" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I296" t="n">
         <v>4229.809203861739</v>
@@ -23219,7 +23219,7 @@
         <v>30.40777335686897</v>
       </c>
       <c r="K296" t="n">
-        <v>18.79358613020876</v>
+        <v>18.79359513235668</v>
       </c>
       <c r="L296" t="n">
         <v>53.47222222222222</v>
@@ -23592,7 +23592,7 @@
         <v>822.6168963623047</v>
       </c>
       <c r="G301" t="n">
-        <v>-0.5298910559640491</v>
+        <v>-0.5298911293761366</v>
       </c>
       <c r="H301" t="n">
         <v>1067.69503349979</v>
@@ -24205,19 +24205,19 @@
         <v>380.4406172688802</v>
       </c>
       <c r="F309" t="n">
-        <v>364.466918334961</v>
+        <v>364.4669171905518</v>
       </c>
       <c r="G309" t="n">
-        <v>4.415040702751538</v>
+        <v>4.415040831337769</v>
       </c>
       <c r="H309" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I309" t="n">
-        <v>191.8556220656042</v>
+        <v>191.8556371798532</v>
       </c>
       <c r="J309" t="n">
-        <v>88.16232545771197</v>
+        <v>88.16231063441936</v>
       </c>
       <c r="K309" t="n">
         <v>22.81803509501646</v>
@@ -25049,7 +25049,7 @@
         <v>410.6988391113281</v>
       </c>
       <c r="E320" t="n">
-        <v>428.8229732259115</v>
+        <v>428.8229736328125</v>
       </c>
       <c r="F320" t="n">
         <v>419.6957847595215</v>
@@ -26053,10 +26053,10 @@
         <v>1364.899300130208</v>
       </c>
       <c r="F333" t="n">
-        <v>1366.992267456055</v>
+        <v>1366.992270507812</v>
       </c>
       <c r="G333" t="n">
-        <v>0.754302152960018</v>
+        <v>0.7543021965887409</v>
       </c>
       <c r="H333" t="n">
         <v>1563.400024414062</v>
@@ -29364,10 +29364,10 @@
         <v>1145.544513753255</v>
       </c>
       <c r="F376" t="n">
-        <v>1167.715065002441</v>
+        <v>1167.715068664551</v>
       </c>
       <c r="G376" t="n">
-        <v>-0.147786137827266</v>
+        <v>-0.1477861894789823</v>
       </c>
       <c r="H376" t="n">
         <v>1378.852549646065</v>
@@ -29441,10 +29441,10 @@
         <v>731.3741756184896</v>
       </c>
       <c r="F377" t="n">
-        <v>745.8220916748047</v>
+        <v>745.822092590332</v>
       </c>
       <c r="G377" t="n">
-        <v>-0.3708869297216921</v>
+        <v>-0.3708867261926985</v>
       </c>
       <c r="H377" t="n">
         <v>879.2203373423794</v>
@@ -29672,13 +29672,13 @@
         <v>488.4894838460286</v>
       </c>
       <c r="F380" t="n">
-        <v>492.7654718017578</v>
+        <v>492.7654722595215</v>
       </c>
       <c r="G380" t="n">
-        <v>-0.1747577699071856</v>
+        <v>-0.1747577080301488</v>
       </c>
       <c r="H380" t="n">
-        <v>561.4379586860567</v>
+        <v>561.4378970396333</v>
       </c>
       <c r="I380" t="n">
         <v>420.1655789001589</v>
@@ -29687,7 +29687,7 @@
         <v>18.82220369094856</v>
       </c>
       <c r="K380" t="n">
-        <v>12.45627615143849</v>
+        <v>12.45626380363212</v>
       </c>
       <c r="L380" t="n">
         <v>46.66666666666666</v>
@@ -29826,10 +29826,10 @@
         <v>5181.948326822917</v>
       </c>
       <c r="F382" t="n">
-        <v>5294.27435546875</v>
+        <v>5294.274338378907</v>
       </c>
       <c r="G382" t="n">
-        <v>0.1306649822981232</v>
+        <v>0.1306648902510865</v>
       </c>
       <c r="H382" t="n">
         <v>6175.521739453033</v>
@@ -32598,13 +32598,13 @@
         <v>77.47344223022461</v>
       </c>
       <c r="F418" t="n">
-        <v>77.33723175048829</v>
+        <v>77.33723197937012</v>
       </c>
       <c r="G418" t="n">
-        <v>-0.5463467586301118</v>
+        <v>-0.5463467082340356</v>
       </c>
       <c r="H418" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I418" t="n">
         <v>71.42454681386315</v>
@@ -32613,7 +32613,7 @@
         <v>6.93802153546601</v>
       </c>
       <c r="K418" t="n">
-        <v>14.42487073488403</v>
+        <v>14.42488088285532</v>
       </c>
       <c r="L418" t="n">
         <v>43.88888888888889</v>
@@ -33054,16 +33054,16 @@
         <v>711</v>
       </c>
       <c r="D424" t="n">
-        <v>765.6322778320313</v>
+        <v>765.6322802734375</v>
       </c>
       <c r="E424" t="n">
-        <v>741.6845418294271</v>
+        <v>741.6845438639323</v>
       </c>
       <c r="F424" t="n">
-        <v>738.9757214355469</v>
+        <v>738.9757235717774</v>
       </c>
       <c r="G424" t="n">
-        <v>-0.2926388807424463</v>
+        <v>-0.2926390441220894</v>
       </c>
       <c r="H424" t="n">
         <v>837.8765073351432</v>
@@ -34141,7 +34141,7 @@
         <v>169.8823271942139</v>
       </c>
       <c r="G438" t="n">
-        <v>2.074713976289044</v>
+        <v>2.074713929496341</v>
       </c>
       <c r="H438" t="n">
         <v>211.8067938496122</v>
@@ -34366,13 +34366,13 @@
         <v>156.6641122436523</v>
       </c>
       <c r="E441" t="n">
-        <v>159.7786432902018</v>
+        <v>159.7786433919271</v>
       </c>
       <c r="F441" t="n">
-        <v>155.0355158233642</v>
+        <v>155.0355159759521</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8658909970862494</v>
+        <v>0.865891046293199</v>
       </c>
       <c r="H441" t="n">
         <v>203.5447632528218</v>
@@ -35219,7 +35219,7 @@
         <v>283.8766855621338</v>
       </c>
       <c r="G452" t="n">
-        <v>-0.2354851375280242</v>
+        <v>-0.2354850840294187</v>
       </c>
       <c r="H452" t="n">
         <v>324.9500122070312</v>
@@ -35524,10 +35524,10 @@
         <v>2257.847731933594</v>
       </c>
       <c r="F456" t="n">
-        <v>2284.035446166992</v>
+        <v>2284.03543762207</v>
       </c>
       <c r="G456" t="n">
-        <v>0.08972659549646433</v>
+        <v>0.08972670291438334</v>
       </c>
       <c r="H456" t="n">
         <v>2765.379504159864</v>
@@ -35912,7 +35912,7 @@
         <v>20.64217186927796</v>
       </c>
       <c r="G461" t="n">
-        <v>-1.359108566272171</v>
+        <v>-1.359108521319186</v>
       </c>
       <c r="H461" t="n">
         <v>23.83526024888653</v>
@@ -36063,22 +36063,22 @@
         <v>36543.73829427084</v>
       </c>
       <c r="F463" t="n">
-        <v>36194.4725390625</v>
+        <v>36194.47237304688</v>
       </c>
       <c r="G463" t="n">
-        <v>-1.097501800744238</v>
+        <v>-1.097501647370969</v>
       </c>
       <c r="H463" t="n">
-        <v>45150.8475731383</v>
+        <v>45150.85152546577</v>
       </c>
       <c r="I463" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J463" t="n">
-        <v>19.77872994242777</v>
+        <v>19.7787377622701</v>
       </c>
       <c r="K463" t="n">
-        <v>27.67099554117998</v>
+        <v>27.67100671699638</v>
       </c>
       <c r="L463" t="n">
         <v>35.97222222222222</v>
@@ -36291,13 +36291,13 @@
         <v>905.76228515625</v>
       </c>
       <c r="E466" t="n">
-        <v>968.1568168131511</v>
+        <v>968.156815999349</v>
       </c>
       <c r="F466" t="n">
-        <v>946.9251034545898</v>
+        <v>946.9251007080078</v>
       </c>
       <c r="G466" t="n">
-        <v>0.5072746146043583</v>
+        <v>0.5072747137508271</v>
       </c>
       <c r="H466" t="n">
         <v>1224.72508309492</v>
@@ -36368,25 +36368,25 @@
         <v>238.5343508911133</v>
       </c>
       <c r="E467" t="n">
-        <v>226.7821342976888</v>
+        <v>226.782133992513</v>
       </c>
       <c r="F467" t="n">
-        <v>226.7291125488281</v>
+        <v>226.729112701416</v>
       </c>
       <c r="G467" t="n">
-        <v>-1.411909890937324</v>
+        <v>-1.41190995541316</v>
       </c>
       <c r="H467" t="n">
-        <v>286.0804516993438</v>
+        <v>286.0804190389319</v>
       </c>
       <c r="I467" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J467" t="n">
-        <v>23.62693699990319</v>
+        <v>23.62692610641624</v>
       </c>
       <c r="K467" t="n">
-        <v>34.57543006641926</v>
+        <v>34.57541470259782</v>
       </c>
       <c r="L467" t="n">
         <v>34.30555555555556</v>
@@ -37375,10 +37375,10 @@
         <v>259.730538482666</v>
       </c>
       <c r="G480" t="n">
-        <v>-1.559457167935097</v>
+        <v>-1.559457111004581</v>
       </c>
       <c r="H480" t="n">
-        <v>344.158759632922</v>
+        <v>344.1587283047078</v>
       </c>
       <c r="I480" t="n">
         <v>191.2413512696417</v>
@@ -37387,7 +37387,7 @@
         <v>30.25948570041095</v>
       </c>
       <c r="K480" t="n">
-        <v>38.15533651386485</v>
+        <v>38.15532393780848</v>
       </c>
       <c r="L480" t="n">
         <v>25.55555555555555</v>
@@ -37443,16 +37443,16 @@
         <v>265.8500061035156</v>
       </c>
       <c r="D481" t="n">
-        <v>300.7577362060547</v>
+        <v>300.7577349853516</v>
       </c>
       <c r="E481" t="n">
-        <v>273.6666661580404</v>
+        <v>273.6666670735677</v>
       </c>
       <c r="F481" t="n">
-        <v>289.1837828826904</v>
+        <v>289.1837829589844</v>
       </c>
       <c r="G481" t="n">
-        <v>-2.473801523266772</v>
+        <v>-2.473801823750543</v>
       </c>
       <c r="H481" t="n">
         <v>411.0263372414121</v>
@@ -38293,16 +38293,16 @@
         <v>631.4603759765625</v>
       </c>
       <c r="E492" t="n">
-        <v>616.4164790852865</v>
+        <v>616.4164782714844</v>
       </c>
       <c r="F492" t="n">
-        <v>623.8182107543945</v>
+        <v>623.8182089233399</v>
       </c>
       <c r="G492" t="n">
-        <v>-2.023358508508166</v>
+        <v>-2.023358514327023</v>
       </c>
       <c r="H492" t="n">
-        <v>848.8263661382125</v>
+        <v>848.8262434052705</v>
       </c>
       <c r="I492" t="n">
         <v>495.5999980879241</v>
@@ -38311,7 +38311,7 @@
         <v>24.09201016398978</v>
       </c>
       <c r="K492" t="n">
-        <v>38.02054733954674</v>
+        <v>38.02052738297081</v>
       </c>
       <c r="L492" t="n">
         <v>47.22222222222222</v>
@@ -38527,19 +38527,19 @@
         <v>260.6732721964518</v>
       </c>
       <c r="F495" t="n">
-        <v>254.7806270599365</v>
+        <v>254.7806271362305</v>
       </c>
       <c r="G495" t="n">
-        <v>-0.2343422992972632</v>
+        <v>-0.2343422694224939</v>
       </c>
       <c r="H495" t="n">
         <v>306.197022156633</v>
       </c>
       <c r="I495" t="n">
-        <v>220.307140654885</v>
+        <v>220.3071254131767</v>
       </c>
       <c r="J495" t="n">
-        <v>5.534482136561958</v>
+        <v>5.534489437850021</v>
       </c>
       <c r="K495" t="n">
         <v>31.69764393833676</v>
@@ -38601,13 +38601,13 @@
         <v>1342.618000488281</v>
       </c>
       <c r="E496" t="n">
-        <v>1439.711363932292</v>
+        <v>1439.711361490885</v>
       </c>
       <c r="F496" t="n">
-        <v>1405.491254882812</v>
+        <v>1405.491257324219</v>
       </c>
       <c r="G496" t="n">
-        <v>-0.1567580397263013</v>
+        <v>-0.156757952874087</v>
       </c>
       <c r="H496" t="n">
         <v>1817.803954384172</v>
@@ -38681,10 +38681,10 @@
         <v>845.2377392578124</v>
       </c>
       <c r="F497" t="n">
-        <v>859.9790994262695</v>
+        <v>859.9790991210938</v>
       </c>
       <c r="G497" t="n">
-        <v>-0.6961920267017252</v>
+        <v>-0.6961920619410811</v>
       </c>
       <c r="H497" t="n">
         <v>962.6932158005569</v>
@@ -39066,10 +39066,10 @@
         <v>406.7520330810547</v>
       </c>
       <c r="F502" t="n">
-        <v>392.5596336364746</v>
+        <v>392.5596334838867</v>
       </c>
       <c r="G502" t="n">
-        <v>-0.1889084107150829</v>
+        <v>-0.1889084882349179</v>
       </c>
       <c r="H502" t="n">
         <v>476.8288845013619</v>
@@ -39457,7 +39457,7 @@
         <v>-0.9390714178847293</v>
       </c>
       <c r="H507" t="n">
-        <v>3039.742428602358</v>
+        <v>3039.742679715149</v>
       </c>
       <c r="I507" t="n">
         <v>2053.692522278021</v>
@@ -39466,7 +39466,7 @@
         <v>13.89241449861769</v>
       </c>
       <c r="K507" t="n">
-        <v>29.9590606499512</v>
+        <v>29.95907138585501</v>
       </c>
       <c r="L507" t="n">
         <v>33.19444444444444</v>
@@ -39910,13 +39910,13 @@
         <v>341.3380230712891</v>
       </c>
       <c r="E513" t="n">
-        <v>341.7155623372396</v>
+        <v>341.7155635579427</v>
       </c>
       <c r="F513" t="n">
-        <v>343.0791789245606</v>
+        <v>343.0791807556153</v>
       </c>
       <c r="G513" t="n">
-        <v>-0.8730200660024168</v>
+        <v>-0.873020367303412</v>
       </c>
       <c r="H513" t="n">
         <v>381.3442016302781</v>
@@ -40147,7 +40147,7 @@
         <v>580.7664199829102</v>
       </c>
       <c r="G516" t="n">
-        <v>-0.002444009938962211</v>
+        <v>-0.002444167572479561</v>
       </c>
       <c r="H516" t="n">
         <v>732.5560380476754</v>
@@ -40760,10 +40760,10 @@
         <v>1260.421268310547</v>
       </c>
       <c r="F524" t="n">
-        <v>1346.872137756348</v>
+        <v>1346.872138977051</v>
       </c>
       <c r="G524" t="n">
-        <v>-1.743534610643105</v>
+        <v>-1.743534609090447</v>
       </c>
       <c r="H524" t="n">
         <v>1729.008500794829</v>
@@ -41145,10 +41145,10 @@
         <v>2636.518364257813</v>
       </c>
       <c r="F529" t="n">
-        <v>2712.691085205078</v>
+        <v>2712.691076660156</v>
       </c>
       <c r="G529" t="n">
-        <v>-1.296486553989162</v>
+        <v>-1.296486645701023</v>
       </c>
       <c r="H529" t="n">
         <v>3198.009229338596</v>
@@ -42380,7 +42380,7 @@
         <v>25442.9180078125</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.399911808952714</v>
+        <v>-1.399911771637352</v>
       </c>
       <c r="H545" t="n">
         <v>30121.12523234443</v>
@@ -42608,19 +42608,19 @@
         <v>945.5330428059896</v>
       </c>
       <c r="F548" t="n">
-        <v>926.8373162841797</v>
+        <v>926.8373138427735</v>
       </c>
       <c r="G548" t="n">
-        <v>-0.3407757772403652</v>
+        <v>-0.3407756473247758</v>
       </c>
       <c r="H548" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I548" t="n">
-        <v>743.4273285628773</v>
+        <v>743.4272688553443</v>
       </c>
       <c r="J548" t="n">
-        <v>2.975766208764052</v>
+        <v>2.975774479148008</v>
       </c>
       <c r="K548" t="n">
         <v>67.56705905619663</v>
@@ -43538,7 +43538,7 @@
         <v>-2.761912463228844</v>
       </c>
       <c r="H560" t="n">
-        <v>1486.026668543064</v>
+        <v>1486.026544311489</v>
       </c>
       <c r="I560" t="n">
         <v>863.7720549794727</v>
@@ -43547,7 +43547,7 @@
         <v>12.54705669277125</v>
       </c>
       <c r="K560" t="n">
-        <v>52.85980879738461</v>
+        <v>52.8597960183308</v>
       </c>
       <c r="L560" t="n">
         <v>13.75</v>
@@ -43834,25 +43834,25 @@
         <v>493.5499877929688</v>
       </c>
       <c r="D564" t="n">
-        <v>528.5924725341797</v>
+        <v>528.5924688720703</v>
       </c>
       <c r="E564" t="n">
-        <v>512.7890651448567</v>
+        <v>512.7890637207031</v>
       </c>
       <c r="F564" t="n">
-        <v>547.5376295471192</v>
+        <v>547.5376281738281</v>
       </c>
       <c r="G564" t="n">
-        <v>-3.52687260055955</v>
+        <v>-3.526872660967284</v>
       </c>
       <c r="H564" t="n">
         <v>872.0425606177564</v>
       </c>
       <c r="I564" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J564" t="n">
-        <v>21.52897956232433</v>
+        <v>21.52897053772853</v>
       </c>
       <c r="K564" t="n">
         <v>76.68778891421132</v>
@@ -43997,7 +43997,7 @@
         <v>392.4845338439941</v>
       </c>
       <c r="G566" t="n">
-        <v>-2.971196725672132</v>
+        <v>-2.971196872078119</v>
       </c>
       <c r="H566" t="n">
         <v>574.7140242073417</v>
@@ -44610,10 +44610,10 @@
         <v>144.5362440999349</v>
       </c>
       <c r="F574" t="n">
-        <v>147.9464302062988</v>
+        <v>147.9464296722412</v>
       </c>
       <c r="G574" t="n">
-        <v>-1.583224155409146</v>
+        <v>-1.583224410777107</v>
       </c>
       <c r="H574" t="n">
         <v>184.9587904135824</v>
@@ -45839,22 +45839,22 @@
         <v>441.1740155029297</v>
       </c>
       <c r="E590" t="n">
-        <v>464.7930308024089</v>
+        <v>464.7930301920573</v>
       </c>
       <c r="F590" t="n">
-        <v>468.158023223877</v>
+        <v>468.1580224609375</v>
       </c>
       <c r="G590" t="n">
-        <v>-0.9592332527086467</v>
+        <v>-0.9592333821407006</v>
       </c>
       <c r="H590" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I590" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J590" t="n">
-        <v>9.680345174963145</v>
+        <v>9.680327601519156</v>
       </c>
       <c r="K590" t="n">
         <v>33.29753864717597</v>
@@ -46153,7 +46153,7 @@
         <v>129.9487512588501</v>
       </c>
       <c r="G594" t="n">
-        <v>-1.948903703519911</v>
+        <v>-1.948903759964582</v>
       </c>
       <c r="H594" t="n">
         <v>187.6354050126281</v>
@@ -46301,13 +46301,13 @@
         <v>482.4010290527344</v>
       </c>
       <c r="E596" t="n">
-        <v>533.6281469726563</v>
+        <v>533.6281465657552</v>
       </c>
       <c r="F596" t="n">
-        <v>537.3891635131836</v>
+        <v>537.3891607666015</v>
       </c>
       <c r="G596" t="n">
-        <v>-1.523104819032406</v>
+        <v>-1.523104881770254</v>
       </c>
       <c r="H596" t="n">
         <v>653.9340000086492</v>
@@ -46843,10 +46843,10 @@
         <v>1071.305799560547</v>
       </c>
       <c r="F603" t="n">
-        <v>1102.225216369629</v>
+        <v>1102.22521697998</v>
       </c>
       <c r="G603" t="n">
-        <v>-1.987856504371377</v>
+        <v>-1.987856396902843</v>
       </c>
       <c r="H603" t="n">
         <v>1400.476774401248</v>
@@ -46920,13 +46920,13 @@
         <v>123.4198331705729</v>
       </c>
       <c r="F604" t="n">
-        <v>126.000394744873</v>
+        <v>126.0003953933716</v>
       </c>
       <c r="G604" t="n">
-        <v>-1.356102037958851</v>
+        <v>-1.356101972154489</v>
       </c>
       <c r="H604" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I604" t="n">
         <v>112.8155071321618</v>
@@ -46935,7 +46935,7 @@
         <v>0.9435671995066341</v>
       </c>
       <c r="K604" t="n">
-        <v>36.8984584299136</v>
+        <v>36.89847395072119</v>
       </c>
       <c r="L604" t="n">
         <v>23.47222222222222</v>
@@ -46997,13 +46997,13 @@
         <v>193.6329965209961</v>
       </c>
       <c r="F605" t="n">
-        <v>197.4191028594971</v>
+        <v>197.4191026306152</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.340041803240445</v>
+        <v>-2.340041916464486</v>
       </c>
       <c r="H605" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I605" t="n">
         <v>156.7443123050878</v>
@@ -47012,7 +47012,7 @@
         <v>10.21771186859726</v>
       </c>
       <c r="K605" t="n">
-        <v>38.46878936339935</v>
+        <v>38.46880723958363</v>
       </c>
       <c r="L605" t="n">
         <v>23.19444444444445</v>
@@ -47231,7 +47231,7 @@
         <v>1904.033421020508</v>
       </c>
       <c r="G608" t="n">
-        <v>-1.326595270761888</v>
+        <v>-1.326595208340176</v>
       </c>
       <c r="H608" t="n">
         <v>2484.339731207416</v>
@@ -47305,10 +47305,10 @@
         <v>7781.855380859375</v>
       </c>
       <c r="F609" t="n">
-        <v>7839.586875</v>
+        <v>7839.586865234375</v>
       </c>
       <c r="G609" t="n">
-        <v>-1.336765209043311</v>
+        <v>-1.336765150056229</v>
       </c>
       <c r="H609" t="n">
         <v>10255.65092965882</v>
@@ -47687,16 +47687,16 @@
         <v>67.53223892211913</v>
       </c>
       <c r="E614" t="n">
-        <v>71.26353917439779</v>
+        <v>71.26353902180989</v>
       </c>
       <c r="F614" t="n">
-        <v>71.87717205047608</v>
+        <v>71.87717212677002</v>
       </c>
       <c r="G614" t="n">
-        <v>-2.534760940200154</v>
+        <v>-2.534760887161802</v>
       </c>
       <c r="H614" t="n">
-        <v>93.44222215601812</v>
+        <v>93.44221530383422</v>
       </c>
       <c r="I614" t="n">
         <v>62.68610889438828</v>
@@ -47705,7 +47705,7 @@
         <v>5.573629425099424</v>
       </c>
       <c r="K614" t="n">
-        <v>41.19404914646127</v>
+        <v>41.19403879260231</v>
       </c>
       <c r="L614" t="n">
         <v>20.27777777777778</v>
@@ -48312,7 +48312,7 @@
         <v>-2.624171185276525</v>
       </c>
       <c r="H622" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I622" t="n">
         <v>185.2067002350832</v>
@@ -48321,7 +48321,7 @@
         <v>15.69236102175982</v>
       </c>
       <c r="K622" t="n">
-        <v>43.77871212662874</v>
+        <v>43.77872705013932</v>
       </c>
       <c r="L622" t="n">
         <v>18.33333333333333</v>
@@ -49079,7 +49079,7 @@
         <v>2200.836365966797</v>
       </c>
       <c r="G632" t="n">
-        <v>-1.984191191530749</v>
+        <v>-1.984191457961626</v>
       </c>
       <c r="H632" t="n">
         <v>2619.749708059458</v>
@@ -49150,16 +49150,16 @@
         <v>2286.745529785156</v>
       </c>
       <c r="E633" t="n">
-        <v>2342.139427897135</v>
+        <v>2342.139411621094</v>
       </c>
       <c r="F633" t="n">
-        <v>2530.737529907226</v>
+        <v>2530.73751159668</v>
       </c>
       <c r="G633" t="n">
-        <v>-2.8369522325144</v>
+        <v>-2.83695234353234</v>
       </c>
       <c r="H633" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I633" t="n">
         <v>1966.020518717901</v>
@@ -49168,7 +49168,7 @@
         <v>11.9418657066372</v>
       </c>
       <c r="K633" t="n">
-        <v>49.36212163844849</v>
+        <v>49.36211011628193</v>
       </c>
       <c r="L633" t="n">
         <v>15.69444444444444</v>
@@ -49387,7 +49387,7 @@
         <v>97.34520004272461</v>
       </c>
       <c r="G636" t="n">
-        <v>-2.893821128234797</v>
+        <v>-2.89382105433057</v>
       </c>
       <c r="H636" t="n">
         <v>124.8273096544699</v>
@@ -50003,10 +50003,10 @@
         <v>311.2939810943603</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.675344043609884</v>
+        <v>-2.675343997180257</v>
       </c>
       <c r="H644" t="n">
-        <v>408.554305468849</v>
+        <v>408.5542426067486</v>
       </c>
       <c r="I644" t="n">
         <v>243.9284560598348</v>
@@ -50015,7 +50015,7 @@
         <v>6.547632078125321</v>
       </c>
       <c r="K644" t="n">
-        <v>57.19673530718596</v>
+        <v>57.19671112015177</v>
       </c>
       <c r="L644" t="n">
         <v>12.77777777777778</v>
@@ -50080,7 +50080,7 @@
         <v>301.0580475616455</v>
       </c>
       <c r="G645" t="n">
-        <v>-3.298790831064236</v>
+        <v>-3.298790736273993</v>
       </c>
       <c r="H645" t="n">
         <v>398.6210131186603</v>
@@ -50619,7 +50619,7 @@
         <v>352.6651625061035</v>
       </c>
       <c r="G652" t="n">
-        <v>-2.426801242853549</v>
+        <v>-2.426801078083385</v>
       </c>
       <c r="H652" t="n">
         <v>467.1017114386881</v>
@@ -50773,7 +50773,7 @@
         <v>451.5902569580078</v>
       </c>
       <c r="G654" t="n">
-        <v>-2.790567319521753</v>
+        <v>-2.790567191803683</v>
       </c>
       <c r="H654" t="n">
         <v>538.5337830249387</v>
@@ -51229,13 +51229,13 @@
         <v>990.5183642578126</v>
       </c>
       <c r="E660" t="n">
-        <v>1038.819405924479</v>
+        <v>1038.819401855469</v>
       </c>
       <c r="F660" t="n">
-        <v>1072.215469970703</v>
+        <v>1072.215469360352</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.102908578307239</v>
+        <v>-2.102908797700664</v>
       </c>
       <c r="H660" t="n">
         <v>1255.178432949836</v>
@@ -51771,13 +51771,13 @@
         <v>189.0392256673177</v>
       </c>
       <c r="F667" t="n">
-        <v>203.5307217407227</v>
+        <v>203.530721206665</v>
       </c>
       <c r="G667" t="n">
-        <v>-2.977184092997809</v>
+        <v>-2.977184171150138</v>
       </c>
       <c r="H667" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I667" t="n">
         <v>165.1600036621094</v>
@@ -51786,7 +51786,7 @@
         <v>1.356254652886579</v>
       </c>
       <c r="K667" t="n">
-        <v>57.24046503193239</v>
+        <v>57.24044677284961</v>
       </c>
       <c r="L667" t="n">
         <v>8.888888888888889</v>
@@ -52073,16 +52073,16 @@
         <v>648.6500244140625</v>
       </c>
       <c r="D671" t="n">
-        <v>676.5281762695313</v>
+        <v>676.5281750488281</v>
       </c>
       <c r="E671" t="n">
-        <v>683.9323099772135</v>
+        <v>683.9323132324218</v>
       </c>
       <c r="F671" t="n">
-        <v>733.6485464477539</v>
+        <v>733.6485498046875</v>
       </c>
       <c r="G671" t="n">
-        <v>-4.461155002757067</v>
+        <v>-4.461154831381453</v>
       </c>
       <c r="H671" t="n">
         <v>1223.985164326833</v>
@@ -52541,13 +52541,13 @@
         <v>289.4460902913411</v>
       </c>
       <c r="F677" t="n">
-        <v>304.2117442321778</v>
+        <v>304.2117446899414</v>
       </c>
       <c r="G677" t="n">
-        <v>-4.261203333081376</v>
+        <v>-4.261203326942564</v>
       </c>
       <c r="H677" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I677" t="n">
         <v>255.5</v>
@@ -52556,7 +52556,7 @@
         <v>1.702546420162676</v>
       </c>
       <c r="K677" t="n">
-        <v>56.46363467694901</v>
+        <v>56.46364659028706</v>
       </c>
       <c r="L677" t="n">
         <v>7.5</v>
@@ -53160,7 +53160,7 @@
         <v>442.0350219726562</v>
       </c>
       <c r="G685" t="n">
-        <v>-3.177441598701747</v>
+        <v>-3.177441695783523</v>
       </c>
       <c r="H685" t="n">
         <v>602.0840578111723</v>
@@ -53696,10 +53696,10 @@
         <v>257.3497201538086</v>
       </c>
       <c r="F692" t="n">
-        <v>275.3010910797119</v>
+        <v>275.3010913848877</v>
       </c>
       <c r="G692" t="n">
-        <v>-3.986736983053418</v>
+        <v>-3.986737080999347</v>
       </c>
       <c r="H692" t="n">
         <v>398.2045017598045</v>
@@ -53847,13 +53847,13 @@
         <v>2574.887333984375</v>
       </c>
       <c r="E694" t="n">
-        <v>2807.131383463542</v>
+        <v>2807.131388346354</v>
       </c>
       <c r="F694" t="n">
-        <v>2914.296950683594</v>
+        <v>2914.296954345703</v>
       </c>
       <c r="G694" t="n">
-        <v>-4.060669957925733</v>
+        <v>-4.060669875922274</v>
       </c>
       <c r="H694" t="n">
         <v>3812.926349899466</v>
@@ -54614,16 +54614,16 @@
         <v>410.3500061035156</v>
       </c>
       <c r="D704" t="n">
-        <v>468.8275463867187</v>
+        <v>468.8275451660156</v>
       </c>
       <c r="E704" t="n">
-        <v>504.5649005126953</v>
+        <v>504.5648966471354</v>
       </c>
       <c r="F704" t="n">
-        <v>513.8932070922851</v>
+        <v>513.8932041931153</v>
       </c>
       <c r="G704" t="n">
-        <v>-4.560797277878081</v>
+        <v>-4.560797302434693</v>
       </c>
       <c r="H704" t="n">
         <v>814.1878618458627</v>
@@ -54851,10 +54851,10 @@
         <v>503.1672961425782</v>
       </c>
       <c r="F707" t="n">
-        <v>550.5517205810547</v>
+        <v>550.5517208862304</v>
       </c>
       <c r="G707" t="n">
-        <v>-4.809176244320302</v>
+        <v>-4.809176141327609</v>
       </c>
       <c r="H707" t="n">
         <v>845.3898333433813</v>
@@ -54925,13 +54925,13 @@
         <v>355.488359375</v>
       </c>
       <c r="E708" t="n">
-        <v>426.6048714192708</v>
+        <v>426.6048728434245</v>
       </c>
       <c r="F708" t="n">
         <v>453.1180693054199</v>
       </c>
       <c r="G708" t="n">
-        <v>-5.319656001752982</v>
+        <v>-5.319656303628806</v>
       </c>
       <c r="H708" t="n">
         <v>606.7970321970149</v>
@@ -55310,13 +55310,13 @@
         <v>257.2635494995117</v>
       </c>
       <c r="E713" t="n">
-        <v>282.9648509724935</v>
+        <v>282.964850769043</v>
       </c>
       <c r="F713" t="n">
-        <v>295.6710472869873</v>
+        <v>295.6710478973389</v>
       </c>
       <c r="G713" t="n">
-        <v>-3.982220965591698</v>
+        <v>-3.982220719803964</v>
       </c>
       <c r="H713" t="n">
         <v>421.2767588033022</v>
@@ -55393,7 +55393,7 @@
         <v>401.4955911254883</v>
       </c>
       <c r="G714" t="n">
-        <v>-4.772801303014118</v>
+        <v>-4.77280123408681</v>
       </c>
       <c r="H714" t="n">
         <v>541.6977805031639</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1345,10 +1345,10 @@
         <v>817.5499877929688</v>
       </c>
       <c r="I12" t="n">
-        <v>262.0239102537355</v>
+        <v>262.023880250306</v>
       </c>
       <c r="J12" t="n">
-        <v>191.4810328799418</v>
+        <v>191.4810662564059</v>
       </c>
       <c r="K12" t="n">
         <v>7.04418825439852</v>
@@ -1499,10 +1499,10 @@
         <v>1982</v>
       </c>
       <c r="I14" t="n">
-        <v>821.6033975811163</v>
+        <v>821.6033372206257</v>
       </c>
       <c r="J14" t="n">
-        <v>137.8276435750843</v>
+        <v>137.8276610474978</v>
       </c>
       <c r="K14" t="n">
         <v>1.432958034800413</v>
@@ -3412,13 +3412,13 @@
         <v>330.3605157470703</v>
       </c>
       <c r="E39" t="n">
-        <v>250.0278811645508</v>
+        <v>250.027880859375</v>
       </c>
       <c r="F39" t="n">
-        <v>237.5666033935547</v>
+        <v>237.5666033172607</v>
       </c>
       <c r="G39" t="n">
-        <v>7.283150690223228</v>
+        <v>7.283150360065149</v>
       </c>
       <c r="H39" t="n">
         <v>388.75</v>
@@ -5879,10 +5879,10 @@
         <v>10686.42411458333</v>
       </c>
       <c r="F71" t="n">
-        <v>10263.91961914062</v>
+        <v>10263.91963623047</v>
       </c>
       <c r="G71" t="n">
-        <v>2.962031050632397</v>
+        <v>2.962031121203235</v>
       </c>
       <c r="H71" t="n">
         <v>12865.82946046676</v>
@@ -6338,13 +6338,13 @@
         <v>158.6029998779297</v>
       </c>
       <c r="E77" t="n">
-        <v>139.676395111084</v>
+        <v>139.6763952636719</v>
       </c>
       <c r="F77" t="n">
-        <v>134.1938622665405</v>
+        <v>134.1938621902466</v>
       </c>
       <c r="G77" t="n">
-        <v>4.71223518701358</v>
+        <v>4.712235096312045</v>
       </c>
       <c r="H77" t="n">
         <v>173.2700042724609</v>
@@ -8497,10 +8497,10 @@
         <v>1615.586608886719</v>
       </c>
       <c r="F105" t="n">
-        <v>1567.112338867187</v>
+        <v>1567.112346801758</v>
       </c>
       <c r="G105" t="n">
-        <v>2.589273140492754</v>
+        <v>2.589273004071679</v>
       </c>
       <c r="H105" t="n">
         <v>2038.599975585938</v>
@@ -9421,10 +9421,10 @@
         <v>1000.71230875651</v>
       </c>
       <c r="F117" t="n">
-        <v>958.3113201904297</v>
+        <v>958.3113189697266</v>
       </c>
       <c r="G117" t="n">
-        <v>2.668703894725644</v>
+        <v>2.668703864648236</v>
       </c>
       <c r="H117" t="n">
         <v>1303.791320684363</v>
@@ -9655,7 +9655,7 @@
         <v>512.2861003112793</v>
       </c>
       <c r="G120" t="n">
-        <v>1.995029870759502</v>
+        <v>1.995029932731507</v>
       </c>
       <c r="H120" t="n">
         <v>609.0499877929688</v>
@@ -10816,10 +10816,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I135" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J135" t="n">
-        <v>108.533012268178</v>
+        <v>108.5330330333436</v>
       </c>
       <c r="K135" t="n">
         <v>21.74800021955521</v>
@@ -10878,16 +10878,16 @@
         <v>228.1499938964844</v>
       </c>
       <c r="D136" t="n">
-        <v>179.2336880493164</v>
+        <v>179.2336889648437</v>
       </c>
       <c r="E136" t="n">
         <v>151.4048608907064</v>
       </c>
       <c r="F136" t="n">
-        <v>152.4800243759155</v>
+        <v>152.4800242996216</v>
       </c>
       <c r="G136" t="n">
-        <v>0.9399780014124559</v>
+        <v>0.9399778489459054</v>
       </c>
       <c r="H136" t="n">
         <v>233.3500061035156</v>
@@ -13197,7 +13197,7 @@
         <v>1510.289041748047</v>
       </c>
       <c r="G166" t="n">
-        <v>2.437627677812659</v>
+        <v>2.43762759299837</v>
       </c>
       <c r="H166" t="n">
         <v>2066</v>
@@ -13345,13 +13345,13 @@
         <v>7394.512578125</v>
       </c>
       <c r="E168" t="n">
-        <v>6851.876295572917</v>
+        <v>6851.876285807291</v>
       </c>
       <c r="F168" t="n">
         <v>6422.329853515625</v>
       </c>
       <c r="G168" t="n">
-        <v>4.238464872446723</v>
+        <v>4.23846478983656</v>
       </c>
       <c r="H168" t="n">
         <v>7832.294844565128</v>
@@ -14118,19 +14118,19 @@
         <v>1404.433599446615</v>
       </c>
       <c r="F178" t="n">
-        <v>1333.20635925293</v>
+        <v>1333.206362304687</v>
       </c>
       <c r="G178" t="n">
-        <v>2.434953244985705</v>
+        <v>2.434953287313646</v>
       </c>
       <c r="H178" t="n">
         <v>1766.733060850261</v>
       </c>
       <c r="I178" t="n">
-        <v>941.3310566553616</v>
+        <v>941.3309959266335</v>
       </c>
       <c r="J178" t="n">
-        <v>52.13563447851433</v>
+        <v>52.13564429334421</v>
       </c>
       <c r="K178" t="n">
         <v>23.36660086370084</v>
@@ -14346,22 +14346,22 @@
         <v>301.9580078125</v>
       </c>
       <c r="E181" t="n">
-        <v>296.5323236083984</v>
+        <v>296.5323237101237</v>
       </c>
       <c r="F181" t="n">
-        <v>284.9551756286621</v>
+        <v>284.9551770019531</v>
       </c>
       <c r="G181" t="n">
-        <v>1.175585121432166</v>
+        <v>1.175585115700017</v>
       </c>
       <c r="H181" t="n">
         <v>359.3387168134344</v>
       </c>
       <c r="I181" t="n">
-        <v>206.1210871445057</v>
+        <v>206.1211021779015</v>
       </c>
       <c r="J181" t="n">
-        <v>45.10888247635967</v>
+        <v>45.1088718928762</v>
       </c>
       <c r="K181" t="n">
         <v>20.13998979627929</v>
@@ -14965,10 +14965,10 @@
         <v>1454.843120930989</v>
       </c>
       <c r="F189" t="n">
-        <v>1519.103559570312</v>
+        <v>1519.103561401367</v>
       </c>
       <c r="G189" t="n">
-        <v>0.5931285256367991</v>
+        <v>0.5931286875433761</v>
       </c>
       <c r="H189" t="n">
         <v>2021.199951171875</v>
@@ -15581,13 +15581,13 @@
         <v>1777.473986816406</v>
       </c>
       <c r="F197" t="n">
-        <v>1772.605222167969</v>
+        <v>1772.605225219727</v>
       </c>
       <c r="G197" t="n">
-        <v>0.2844327763934507</v>
+        <v>0.2844327412737657</v>
       </c>
       <c r="H197" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I197" t="n">
         <v>1353.205955540699</v>
@@ -15596,7 +15596,7 @@
         <v>57.77347056878131</v>
       </c>
       <c r="K197" t="n">
-        <v>6.298454457063762</v>
+        <v>6.298466184406726</v>
       </c>
       <c r="L197" t="n">
         <v>69.90291262135922</v>
@@ -16194,13 +16194,13 @@
         <v>1110.357338867188</v>
       </c>
       <c r="E205" t="n">
-        <v>1007.406536458333</v>
+        <v>1007.406536865234</v>
       </c>
       <c r="F205" t="n">
-        <v>985.3628475952148</v>
+        <v>985.3628460693359</v>
       </c>
       <c r="G205" t="n">
-        <v>0.7101390192632673</v>
+        <v>0.7101391460201167</v>
       </c>
       <c r="H205" t="n">
         <v>1331.075409591023</v>
@@ -16351,10 +16351,10 @@
         <v>4398.334536132813</v>
       </c>
       <c r="F207" t="n">
-        <v>4378.011828613281</v>
+        <v>4378.011849365234</v>
       </c>
       <c r="G207" t="n">
-        <v>0.6974657313333132</v>
+        <v>0.6974655583669165</v>
       </c>
       <c r="H207" t="n">
         <v>5149.89990234375</v>
@@ -16893,7 +16893,7 @@
         <v>939.225329284668</v>
       </c>
       <c r="G214" t="n">
-        <v>-0.4462643033971259</v>
+        <v>-0.4462643678029843</v>
       </c>
       <c r="H214" t="n">
         <v>1475</v>
@@ -17278,7 +17278,7 @@
         <v>998.2338751220703</v>
       </c>
       <c r="G219" t="n">
-        <v>2.685044465006126</v>
+        <v>2.685044400535452</v>
       </c>
       <c r="H219" t="n">
         <v>1153.699951171875</v>
@@ -18966,13 +18966,13 @@
         <v>1839.764094238281</v>
       </c>
       <c r="E241" t="n">
-        <v>1695.571222330729</v>
+        <v>1695.571221516927</v>
       </c>
       <c r="F241" t="n">
-        <v>1674.466809692383</v>
+        <v>1674.466813354492</v>
       </c>
       <c r="G241" t="n">
-        <v>0.7942574333751118</v>
+        <v>0.7942574686560677</v>
       </c>
       <c r="H241" t="n">
         <v>1983.954544928268</v>
@@ -19046,10 +19046,10 @@
         <v>311.5948203531901</v>
       </c>
       <c r="F242" t="n">
-        <v>307.5606245422363</v>
+        <v>307.5606246948242</v>
       </c>
       <c r="G242" t="n">
-        <v>2.31407790099194</v>
+        <v>2.314077692077321</v>
       </c>
       <c r="H242" t="n">
         <v>380.4567148307952</v>
@@ -20201,10 +20201,10 @@
         <v>714.5667757161458</v>
       </c>
       <c r="F257" t="n">
-        <v>723.5174594116211</v>
+        <v>723.5174609375</v>
       </c>
       <c r="G257" t="n">
-        <v>1.404139987548425</v>
+        <v>1.404139854428665</v>
       </c>
       <c r="H257" t="n">
         <v>936.2409542546694</v>
@@ -20432,10 +20432,10 @@
         <v>338.585043741862</v>
       </c>
       <c r="F260" t="n">
-        <v>334.1569720458984</v>
+        <v>334.1569721984863</v>
       </c>
       <c r="G260" t="n">
-        <v>1.00855103986226</v>
+        <v>1.008551225754117</v>
       </c>
       <c r="H260" t="n">
         <v>428.7550602808859</v>
@@ -20897,7 +20897,7 @@
         <v>267.8263538360596</v>
       </c>
       <c r="G266" t="n">
-        <v>1.793260766546245</v>
+        <v>1.793260884614956</v>
       </c>
       <c r="H266" t="n">
         <v>367.499792159746</v>
@@ -21202,10 +21202,10 @@
         <v>5208.114186197917</v>
       </c>
       <c r="F270" t="n">
-        <v>4963.660657958984</v>
+        <v>4963.660660400391</v>
       </c>
       <c r="G270" t="n">
-        <v>1.76159579644577</v>
+        <v>1.761595591829002</v>
       </c>
       <c r="H270" t="n">
         <v>6049.821052103703</v>
@@ -22126,10 +22126,10 @@
         <v>1833.429462890625</v>
       </c>
       <c r="F282" t="n">
-        <v>1801.069285888672</v>
+        <v>1801.069286499024</v>
       </c>
       <c r="G282" t="n">
-        <v>0.914905207033323</v>
+        <v>0.9149052412316561</v>
       </c>
       <c r="H282" t="n">
         <v>2046.900024414062</v>
@@ -24895,16 +24895,16 @@
         <v>1272.59537109375</v>
       </c>
       <c r="E318" t="n">
-        <v>1090.962322591146</v>
+        <v>1090.96232421875</v>
       </c>
       <c r="F318" t="n">
-        <v>1145.154410400391</v>
+        <v>1145.154407348633</v>
       </c>
       <c r="G318" t="n">
-        <v>-0.2145216467417943</v>
+        <v>-0.2145215411718637</v>
       </c>
       <c r="H318" t="n">
-        <v>1423.548053270148</v>
+        <v>1423.547927723126</v>
       </c>
       <c r="I318" t="n">
         <v>905.5050975494345</v>
@@ -24913,7 +24913,7 @@
         <v>38.17701905356397</v>
       </c>
       <c r="K318" t="n">
-        <v>13.77462506586986</v>
+        <v>13.77461503174049</v>
       </c>
       <c r="L318" t="n">
         <v>59.63938973647711</v>
@@ -25517,7 +25517,7 @@
         <v>560.9133836364746</v>
       </c>
       <c r="G326" t="n">
-        <v>0.7469957955187567</v>
+        <v>0.7469957126845506</v>
       </c>
       <c r="H326" t="n">
         <v>784.8771245029434</v>
@@ -25594,7 +25594,7 @@
         <v>44.10581880569458</v>
       </c>
       <c r="G327" t="n">
-        <v>-1.296106463346869</v>
+        <v>-1.296106547609066</v>
       </c>
       <c r="H327" t="n">
         <v>57.70003380709684</v>
@@ -25976,10 +25976,10 @@
         <v>1364.349932454427</v>
       </c>
       <c r="F332" t="n">
-        <v>1365.975592041016</v>
+        <v>1365.975588989258</v>
       </c>
       <c r="G332" t="n">
-        <v>0.3810666364166826</v>
+        <v>0.3810665922476142</v>
       </c>
       <c r="H332" t="n">
         <v>1563.400024414062</v>
@@ -26592,13 +26592,13 @@
         <v>5112.294235026042</v>
       </c>
       <c r="F340" t="n">
-        <v>5382.681198730469</v>
+        <v>5382.681196289062</v>
       </c>
       <c r="G340" t="n">
-        <v>-1.052445069386654</v>
+        <v>-1.052444936637964</v>
       </c>
       <c r="H340" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I340" t="n">
         <v>4229.809203861739</v>
@@ -26607,7 +26607,7 @@
         <v>28.04360052588875</v>
       </c>
       <c r="K340" t="n">
-        <v>20.98696844428205</v>
+        <v>20.98697761264392</v>
       </c>
       <c r="L340" t="n">
         <v>50.48543689320388</v>
@@ -28822,13 +28822,13 @@
         <v>369.1938208007812</v>
       </c>
       <c r="E369" t="n">
-        <v>380.2193927001953</v>
+        <v>380.2193922932943</v>
       </c>
       <c r="F369" t="n">
-        <v>366.8819265747071</v>
+        <v>366.8819276428223</v>
       </c>
       <c r="G369" t="n">
-        <v>3.931633434616222</v>
+        <v>3.931633377794785</v>
       </c>
       <c r="H369" t="n">
         <v>443.3731066930094</v>
@@ -29672,10 +29672,10 @@
         <v>5170.9726171875</v>
       </c>
       <c r="F380" t="n">
-        <v>5275.108857421875</v>
+        <v>5275.108869628906</v>
       </c>
       <c r="G380" t="n">
-        <v>-0.4109831638539951</v>
+        <v>-0.410983208808835</v>
       </c>
       <c r="H380" t="n">
         <v>6175.521739453033</v>
@@ -29752,7 +29752,7 @@
         <v>492.5059671020508</v>
       </c>
       <c r="G381" t="n">
-        <v>-0.1536752965209387</v>
+        <v>-0.1536754818416641</v>
       </c>
       <c r="H381" t="n">
         <v>556.6591363218392</v>
@@ -29826,13 +29826,13 @@
         <v>5431.071077473958</v>
       </c>
       <c r="F382" t="n">
-        <v>5476.507272949219</v>
+        <v>5476.507263183594</v>
       </c>
       <c r="G382" t="n">
-        <v>-0.7264035861213602</v>
+        <v>-0.7264035434729421</v>
       </c>
       <c r="H382" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I382" t="n">
         <v>5051</v>
@@ -29841,7 +29841,7 @@
         <v>8.226093842803394</v>
       </c>
       <c r="K382" t="n">
-        <v>7.482565029029153</v>
+        <v>7.482555990147244</v>
       </c>
       <c r="L382" t="n">
         <v>49.65325936199723</v>
@@ -30596,19 +30596,19 @@
         <v>36573.18212239583</v>
       </c>
       <c r="F392" t="n">
-        <v>36124.1803515625</v>
+        <v>36124.18018554687</v>
       </c>
       <c r="G392" t="n">
-        <v>-1.006313194262665</v>
+        <v>-1.00631356973081</v>
       </c>
       <c r="H392" t="n">
         <v>45150.8475731383</v>
       </c>
       <c r="I392" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J392" t="n">
-        <v>23.28420104352811</v>
+        <v>23.28420909222768</v>
       </c>
       <c r="K392" t="n">
         <v>24.04079003609423</v>
@@ -31209,7 +31209,7 @@
         <v>410.7208337402344</v>
       </c>
       <c r="E400" t="n">
-        <v>429.2404427083333</v>
+        <v>429.2404423014323</v>
       </c>
       <c r="F400" t="n">
         <v>421.095445098877</v>
@@ -31677,7 +31677,7 @@
         <v>323.8530313110352</v>
       </c>
       <c r="G406" t="n">
-        <v>-1.453573919215001</v>
+        <v>-1.45357387345838</v>
       </c>
       <c r="H406" t="n">
         <v>391.6499938964844</v>
@@ -32210,22 +32210,22 @@
         <v>2272.252084960937</v>
       </c>
       <c r="E413" t="n">
-        <v>2241.517686360677</v>
+        <v>2241.517652180989</v>
       </c>
       <c r="F413" t="n">
-        <v>2281.55342590332</v>
+        <v>2281.553401489258</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.1211643613030944</v>
+        <v>-0.1211645760923918</v>
       </c>
       <c r="H413" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I413" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J413" t="n">
-        <v>15.38988634595284</v>
+        <v>15.3898935063798</v>
       </c>
       <c r="K413" t="n">
         <v>22.07563874774283</v>
@@ -32906,10 +32906,10 @@
         <v>741.2197574869791</v>
       </c>
       <c r="F422" t="n">
-        <v>737.6684567260742</v>
+        <v>737.6684564208985</v>
       </c>
       <c r="G422" t="n">
-        <v>-0.46140295085636</v>
+        <v>-0.4614028280780613</v>
       </c>
       <c r="H422" t="n">
         <v>837.8765073351432</v>
@@ -32983,13 +32983,13 @@
         <v>1083.110129801432</v>
       </c>
       <c r="F423" t="n">
-        <v>1082.00085357666</v>
+        <v>1082.000853271484</v>
       </c>
       <c r="G423" t="n">
-        <v>-1.042598155207208</v>
+        <v>-1.042598155498209</v>
       </c>
       <c r="H423" t="n">
-        <v>1341.921447537333</v>
+        <v>1341.921323996723</v>
       </c>
       <c r="I423" t="n">
         <v>885.652283987356</v>
@@ -32998,7 +32998,7 @@
         <v>22.13596359757346</v>
       </c>
       <c r="K423" t="n">
-        <v>24.05671702985133</v>
+        <v>24.05670560888293</v>
       </c>
       <c r="L423" t="n">
         <v>35.64493758668516</v>
@@ -33901,16 +33901,16 @@
         <v>274</v>
       </c>
       <c r="D435" t="n">
-        <v>300.9779711914063</v>
+        <v>300.9779718017578</v>
       </c>
       <c r="E435" t="n">
-        <v>272.9627783203125</v>
+        <v>272.9627778116862</v>
       </c>
       <c r="F435" t="n">
-        <v>287.335446472168</v>
+        <v>287.3354447174072</v>
       </c>
       <c r="G435" t="n">
-        <v>-2.72539168841488</v>
+        <v>-2.725391704605284</v>
       </c>
       <c r="H435" t="n">
         <v>411.0263372414121</v>
@@ -34449,7 +34449,7 @@
         <v>169.9376923370361</v>
       </c>
       <c r="G442" t="n">
-        <v>1.53399294170129</v>
+        <v>1.53399289541809</v>
       </c>
       <c r="H442" t="n">
         <v>211.8067938496122</v>
@@ -34609,10 +34609,10 @@
         <v>1670.788050106015</v>
       </c>
       <c r="I444" t="n">
-        <v>1005.677891365182</v>
+        <v>1005.677830777716</v>
       </c>
       <c r="J444" t="n">
-        <v>24.51302369509643</v>
+        <v>24.51303119643367</v>
       </c>
       <c r="K444" t="n">
         <v>33.42821556113324</v>
@@ -35989,7 +35989,7 @@
         <v>1504.390939331055</v>
       </c>
       <c r="G462" t="n">
-        <v>-0.02729215201979773</v>
+        <v>-0.02729207092140307</v>
       </c>
       <c r="H462" t="n">
         <v>1765.922465821425</v>
@@ -36143,7 +36143,7 @@
         <v>354.2419888305664</v>
       </c>
       <c r="G464" t="n">
-        <v>0.3093429109216617</v>
+        <v>0.3093428242388896</v>
       </c>
       <c r="H464" t="n">
         <v>409.9712889887167</v>
@@ -36602,10 +36602,10 @@
         <v>1999.666101888021</v>
       </c>
       <c r="F470" t="n">
-        <v>2071.239389648437</v>
+        <v>2071.239388427734</v>
       </c>
       <c r="G470" t="n">
-        <v>-1.537037010585041</v>
+        <v>-1.53703701147696</v>
       </c>
       <c r="H470" t="n">
         <v>2486.766809421043</v>
@@ -36990,7 +36990,7 @@
         <v>581.6085266113281</v>
       </c>
       <c r="G475" t="n">
-        <v>0.2917750693367749</v>
+        <v>0.2917751221144238</v>
       </c>
       <c r="H475" t="n">
         <v>732.5560380476754</v>
@@ -37061,13 +37061,13 @@
         <v>892.4048303222656</v>
       </c>
       <c r="E476" t="n">
-        <v>967.5367220052084</v>
+        <v>967.5367224121094</v>
       </c>
       <c r="F476" t="n">
-        <v>944.8833834838867</v>
+        <v>944.8833859252929</v>
       </c>
       <c r="G476" t="n">
-        <v>0.0599988242070415</v>
+        <v>0.05999872704245401</v>
       </c>
       <c r="H476" t="n">
         <v>1224.72508309492</v>
@@ -38373,10 +38373,10 @@
         <v>259.6745975748698</v>
       </c>
       <c r="F493" t="n">
-        <v>254.7197316741943</v>
+        <v>254.7197317504883</v>
       </c>
       <c r="G493" t="n">
-        <v>-0.2227575365013612</v>
+        <v>-0.2227575364347922</v>
       </c>
       <c r="H493" t="n">
         <v>306.197022156633</v>
@@ -38450,10 +38450,10 @@
         <v>2582.278672688802</v>
       </c>
       <c r="F494" t="n">
-        <v>2542.024161987305</v>
+        <v>2542.024159545898</v>
       </c>
       <c r="G494" t="n">
-        <v>-0.9344655730386786</v>
+        <v>-0.9344655739277674</v>
       </c>
       <c r="H494" t="n">
         <v>3329.438873827357</v>
@@ -38607,7 +38607,7 @@
         <v>384.0083006286621</v>
       </c>
       <c r="G496" t="n">
-        <v>-2.51529143692536</v>
+        <v>-2.515291399163588</v>
       </c>
       <c r="H496" t="n">
         <v>483.5386775606495</v>
@@ -38835,13 +38835,13 @@
         <v>615.4447692871094</v>
       </c>
       <c r="F499" t="n">
-        <v>622.5301193237304</v>
+        <v>622.5301214599609</v>
       </c>
       <c r="G499" t="n">
-        <v>-1.975068732483332</v>
+        <v>-1.975068725839679</v>
       </c>
       <c r="H499" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I499" t="n">
         <v>495.5999980879241</v>
@@ -38850,7 +38850,7 @@
         <v>21.87247827487777</v>
       </c>
       <c r="K499" t="n">
-        <v>40.53414625915075</v>
+        <v>40.53415641916251</v>
       </c>
       <c r="L499" t="n">
         <v>37.5866851595007</v>
@@ -38912,19 +38912,19 @@
         <v>841.7779325358073</v>
       </c>
       <c r="F500" t="n">
-        <v>858.1326733398438</v>
+        <v>858.1326736450195</v>
       </c>
       <c r="G500" t="n">
-        <v>-0.8544717960110693</v>
+        <v>-0.8544717607521846</v>
       </c>
       <c r="H500" t="n">
         <v>962.6932158005569</v>
       </c>
       <c r="I500" t="n">
-        <v>726.0614279588375</v>
+        <v>726.0613673587077</v>
       </c>
       <c r="J500" t="n">
-        <v>7.22233271482029</v>
+        <v>7.222341664046317</v>
       </c>
       <c r="K500" t="n">
         <v>23.66001487483069</v>
@@ -39525,13 +39525,13 @@
         <v>1290.233278808594</v>
       </c>
       <c r="E508" t="n">
-        <v>1252.302583414714</v>
+        <v>1252.302576090495</v>
       </c>
       <c r="F508" t="n">
-        <v>1338.571838684082</v>
+        <v>1338.571831970215</v>
       </c>
       <c r="G508" t="n">
-        <v>-2.080657348317849</v>
+        <v>-2.080657445975687</v>
       </c>
       <c r="H508" t="n">
         <v>1729.008500794829</v>
@@ -39910,25 +39910,25 @@
         <v>236.5737225341797</v>
       </c>
       <c r="E513" t="n">
-        <v>226.0604458618164</v>
+        <v>226.0604455566406</v>
       </c>
       <c r="F513" t="n">
-        <v>226.2882953643799</v>
+        <v>226.2882957458496</v>
       </c>
       <c r="G513" t="n">
-        <v>-1.598708903333468</v>
+        <v>-1.598708802743587</v>
       </c>
       <c r="H513" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I513" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J513" t="n">
-        <v>22.06836531285579</v>
+        <v>22.06835455670364</v>
       </c>
       <c r="K513" t="n">
-        <v>36.29367668300989</v>
+        <v>36.29369224299695</v>
       </c>
       <c r="L513" t="n">
         <v>32.31622746185853</v>
@@ -40446,16 +40446,16 @@
         <v>312</v>
       </c>
       <c r="D520" t="n">
-        <v>338.2681286621093</v>
+        <v>338.268129272461</v>
       </c>
       <c r="E520" t="n">
-        <v>340.7909006754557</v>
+        <v>340.7909025065104</v>
       </c>
       <c r="F520" t="n">
-        <v>342.3801820373535</v>
+        <v>342.3801829528809</v>
       </c>
       <c r="G520" t="n">
-        <v>-0.9427569534502633</v>
+        <v>-0.9427570821444298</v>
       </c>
       <c r="H520" t="n">
         <v>381.3442016302781</v>
@@ -41225,10 +41225,10 @@
         <v>258.757667388916</v>
       </c>
       <c r="G530" t="n">
-        <v>-1.296616809816953</v>
+        <v>-1.296616867267075</v>
       </c>
       <c r="H530" t="n">
-        <v>329.6445362713373</v>
+        <v>329.6445669998864</v>
       </c>
       <c r="I530" t="n">
         <v>191.2413512696417</v>
@@ -41237,7 +41237,7 @@
         <v>24.28274068230316</v>
       </c>
       <c r="K530" t="n">
-        <v>38.69258937625628</v>
+        <v>38.69260230479468</v>
       </c>
       <c r="L530" t="n">
         <v>25.93619972260749</v>
@@ -42762,10 +42762,10 @@
         <v>1642.430163574219</v>
       </c>
       <c r="F550" t="n">
-        <v>1748.944118041992</v>
+        <v>1748.944111938476</v>
       </c>
       <c r="G550" t="n">
-        <v>-3.07041503610308</v>
+        <v>-3.070415112065594</v>
       </c>
       <c r="H550" t="n">
         <v>2516.496292929891</v>
@@ -43153,7 +43153,7 @@
         <v>-2.249399045657785</v>
       </c>
       <c r="H555" t="n">
-        <v>632.5128493651639</v>
+        <v>632.5129117162858</v>
       </c>
       <c r="I555" t="n">
         <v>351.0001816860465</v>
@@ -43162,7 +43162,7 @@
         <v>19.99994136292933</v>
       </c>
       <c r="K555" t="n">
-        <v>50.16923813721701</v>
+        <v>50.16925294042692</v>
       </c>
       <c r="L555" t="n">
         <v>17.05963938973648</v>
@@ -44065,28 +44065,28 @@
         <v>464.3999938964844</v>
       </c>
       <c r="D567" t="n">
-        <v>522.3154992675782</v>
+        <v>522.3155017089844</v>
       </c>
       <c r="E567" t="n">
-        <v>509.7762384033203</v>
+        <v>509.7762394205729</v>
       </c>
       <c r="F567" t="n">
-        <v>542.3397724914551</v>
+        <v>542.3397735595703</v>
       </c>
       <c r="G567" t="n">
-        <v>-3.400488954140835</v>
+        <v>-3.400488895163101</v>
       </c>
       <c r="H567" t="n">
-        <v>871.6508349907555</v>
+        <v>871.6507729376511</v>
       </c>
       <c r="I567" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J567" t="n">
-        <v>14.35124014153848</v>
+        <v>14.35124863312462</v>
       </c>
       <c r="K567" t="n">
-        <v>87.69398071634085</v>
+        <v>87.69396735434579</v>
       </c>
       <c r="L567" t="n">
         <v>6.102635228848821</v>
@@ -44145,13 +44145,13 @@
         <v>349.77103515625</v>
       </c>
       <c r="E568" t="n">
-        <v>421.0952341715495</v>
+        <v>421.0952331542969</v>
       </c>
       <c r="F568" t="n">
         <v>447.9658860778808</v>
       </c>
       <c r="G568" t="n">
-        <v>-5.197350171031156</v>
+        <v>-5.19734992612142</v>
       </c>
       <c r="H568" t="n">
         <v>606.7970321970149</v>
@@ -44764,10 +44764,10 @@
         <v>143.2126276652018</v>
       </c>
       <c r="F576" t="n">
-        <v>147.4422113800049</v>
+        <v>147.4422114562988</v>
       </c>
       <c r="G576" t="n">
-        <v>-1.691303549824619</v>
+        <v>-1.691303548964285</v>
       </c>
       <c r="H576" t="n">
         <v>184.9587904135824</v>
@@ -44838,22 +44838,22 @@
         <v>434.4424822998047</v>
       </c>
       <c r="E577" t="n">
-        <v>463.4975423177083</v>
+        <v>463.4975415039062</v>
       </c>
       <c r="F577" t="n">
-        <v>466.6075784301758</v>
+        <v>466.607578125</v>
       </c>
       <c r="G577" t="n">
-        <v>-1.103612912283469</v>
+        <v>-1.103613104899714</v>
       </c>
       <c r="H577" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I577" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J577" t="n">
-        <v>11.11552357822856</v>
+        <v>11.1155324799264</v>
       </c>
       <c r="K577" t="n">
         <v>31.57583419930909</v>
@@ -45309,7 +45309,7 @@
         <v>-1.150607895174105</v>
       </c>
       <c r="H583" t="n">
-        <v>3039.742679715149</v>
+        <v>3039.742428602358</v>
       </c>
       <c r="I583" t="n">
         <v>2053.692522278021</v>
@@ -45318,7 +45318,7 @@
         <v>11.01954042618569</v>
       </c>
       <c r="K583" t="n">
-        <v>33.32204735592759</v>
+        <v>33.32203634220869</v>
       </c>
       <c r="L583" t="n">
         <v>27.73925104022191</v>
@@ -45460,7 +45460,7 @@
         <v>1497.475510864258</v>
       </c>
       <c r="G585" t="n">
-        <v>-1.682090636838263</v>
+        <v>-1.682090715636331</v>
       </c>
       <c r="H585" t="n">
         <v>1968.512241214338</v>
@@ -45685,16 +45685,16 @@
         <v>188.5892001342773</v>
       </c>
       <c r="E588" t="n">
-        <v>192.9455055745443</v>
+        <v>192.9455052693685</v>
       </c>
       <c r="F588" t="n">
-        <v>195.9629097747803</v>
+        <v>195.96291015625</v>
       </c>
       <c r="G588" t="n">
-        <v>-2.619341619524451</v>
+        <v>-2.619341503799122</v>
       </c>
       <c r="H588" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I588" t="n">
         <v>156.7443123050878</v>
@@ -45703,7 +45703,7 @@
         <v>11.59575463796112</v>
       </c>
       <c r="K588" t="n">
-        <v>36.75892195570349</v>
+        <v>36.75890430026369</v>
       </c>
       <c r="L588" t="n">
         <v>26.49098474341193</v>
@@ -46070,16 +46070,16 @@
         <v>19.50095306396484</v>
       </c>
       <c r="E593" t="n">
-        <v>20.51505533854167</v>
+        <v>20.51505537668864</v>
       </c>
       <c r="F593" t="n">
-        <v>20.58417533874512</v>
+        <v>20.58417538642883</v>
       </c>
       <c r="G593" t="n">
-        <v>-1.278245718907434</v>
+        <v>-1.278245761137786</v>
       </c>
       <c r="H593" t="n">
-        <v>23.83526024888653</v>
+        <v>23.83526224893035</v>
       </c>
       <c r="I593" t="n">
         <v>18.3799991607666</v>
@@ -46088,7 +46088,7 @@
         <v>0.5440717412174001</v>
       </c>
       <c r="K593" t="n">
-        <v>28.97868419536847</v>
+        <v>28.97869501811667</v>
       </c>
       <c r="L593" t="n">
         <v>24.82662968099861</v>
@@ -46227,13 +46227,13 @@
         <v>123.0733443196615</v>
       </c>
       <c r="F595" t="n">
-        <v>125.3112440109253</v>
+        <v>125.3112445068359</v>
       </c>
       <c r="G595" t="n">
-        <v>-1.575130546515657</v>
+        <v>-1.575130658341728</v>
       </c>
       <c r="H595" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I595" t="n">
         <v>110.3499984741211</v>
@@ -46242,7 +46242,7 @@
         <v>4.630721052116682</v>
       </c>
       <c r="K595" t="n">
-        <v>35.02508395647732</v>
+        <v>35.02509926489184</v>
       </c>
       <c r="L595" t="n">
         <v>24.13314840499307</v>
@@ -47921,10 +47921,10 @@
         <v>1066.448661295573</v>
       </c>
       <c r="F617" t="n">
-        <v>1096.58295715332</v>
+        <v>1096.582956542969</v>
       </c>
       <c r="G617" t="n">
-        <v>-1.936251587228999</v>
+        <v>-1.936251588285853</v>
       </c>
       <c r="H617" t="n">
         <v>1400.476774401248</v>
@@ -48306,10 +48306,10 @@
         <v>7743.429632161458</v>
       </c>
       <c r="F622" t="n">
-        <v>7816.933833007813</v>
+        <v>7816.933830566406</v>
       </c>
       <c r="G622" t="n">
-        <v>-1.288411470935036</v>
+        <v>-1.288411319168969</v>
       </c>
       <c r="H622" t="n">
         <v>10255.65092965882</v>
@@ -48614,10 +48614,10 @@
         <v>529.7395139567058</v>
       </c>
       <c r="F626" t="n">
-        <v>535.2195509338379</v>
+        <v>535.219549407959</v>
       </c>
       <c r="G626" t="n">
-        <v>-1.602816650482053</v>
+        <v>-1.602816820595265</v>
       </c>
       <c r="H626" t="n">
         <v>653.9340000086492</v>
@@ -49227,16 +49227,16 @@
         <v>119.7978108215332</v>
       </c>
       <c r="E634" t="n">
-        <v>123.2341685994466</v>
+        <v>123.2341687011719</v>
       </c>
       <c r="F634" t="n">
         <v>126.2771722793579</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.536466755273226</v>
+        <v>-2.536466812664973</v>
       </c>
       <c r="H634" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I634" t="n">
         <v>104.7068431385872</v>
@@ -49245,7 +49245,7 @@
         <v>4.176573909958581</v>
       </c>
       <c r="K634" t="n">
-        <v>41.27625607132437</v>
+        <v>41.27627054326495</v>
       </c>
       <c r="L634" t="n">
         <v>15.53398058252427</v>
@@ -49390,7 +49390,7 @@
         <v>-2.543799415100356</v>
       </c>
       <c r="H636" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I636" t="n">
         <v>185.2067002350832</v>
@@ -49399,7 +49399,7 @@
         <v>13.72158504516692</v>
       </c>
       <c r="K636" t="n">
-        <v>46.27038825151091</v>
+        <v>46.2703730693784</v>
       </c>
       <c r="L636" t="n">
         <v>15.25658807212205</v>
@@ -49763,19 +49763,19 @@
         <v>82.40000152587891</v>
       </c>
       <c r="D641" t="n">
-        <v>90.14859863281249</v>
+        <v>90.14859848022461</v>
       </c>
       <c r="E641" t="n">
-        <v>92.99425989786783</v>
+        <v>92.9942594909668</v>
       </c>
       <c r="F641" t="n">
-        <v>96.51349037170411</v>
+        <v>96.51348999023438</v>
       </c>
       <c r="G641" t="n">
-        <v>-3.126390677301705</v>
+        <v>-3.126390911825871</v>
       </c>
       <c r="H641" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I641" t="n">
         <v>76.65010804466255</v>
@@ -49784,7 +49784,7 @@
         <v>7.501481247575037</v>
       </c>
       <c r="K641" t="n">
-        <v>51.48944111476668</v>
+        <v>51.48945065888879</v>
       </c>
       <c r="L641" t="n">
         <v>14.5631067961165</v>
@@ -50847,13 +50847,13 @@
         <v>1030.139160970052</v>
       </c>
       <c r="F655" t="n">
-        <v>1067.116436157227</v>
+        <v>1067.11643371582</v>
       </c>
       <c r="G655" t="n">
-        <v>-2.280650145478746</v>
+        <v>-2.280650041343146</v>
       </c>
       <c r="H655" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I655" t="n">
         <v>855.1500244140625</v>
@@ -50862,7 +50862,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K655" t="n">
-        <v>42.63391283520865</v>
+        <v>42.63389867229614</v>
       </c>
       <c r="L655" t="n">
         <v>11.78918169209431</v>
@@ -51235,10 +51235,10 @@
         <v>553.3068879699707</v>
       </c>
       <c r="G660" t="n">
-        <v>-4.142620220214022</v>
+        <v>-4.142620372253503</v>
       </c>
       <c r="H660" t="n">
-        <v>729.6617501297184</v>
+        <v>729.6618113637422</v>
       </c>
       <c r="I660" t="n">
         <v>446.5</v>
@@ -51247,7 +51247,7 @@
         <v>6.774916013437848</v>
       </c>
       <c r="K660" t="n">
-        <v>53.04913479385807</v>
+        <v>53.04914763791133</v>
       </c>
       <c r="L660" t="n">
         <v>10.67961165048544</v>
@@ -51312,7 +51312,7 @@
         <v>1721.562213745117</v>
       </c>
       <c r="G661" t="n">
-        <v>-4.398894211948123</v>
+        <v>-4.398893985128193</v>
       </c>
       <c r="H661" t="n">
         <v>2504.019782423858</v>
@@ -51463,13 +51463,13 @@
         <v>187.2104787190755</v>
       </c>
       <c r="F663" t="n">
-        <v>201.6740324401856</v>
+        <v>201.6740328216553</v>
       </c>
       <c r="G663" t="n">
-        <v>-3.261069383740989</v>
+        <v>-3.261069413176998</v>
       </c>
       <c r="H663" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I663" t="n">
         <v>163.3000030517578</v>
@@ -51478,7 +51478,7 @@
         <v>2.161664858131118</v>
       </c>
       <c r="K663" t="n">
-        <v>57.77767512531289</v>
+        <v>57.77769344677972</v>
       </c>
       <c r="L663" t="n">
         <v>10.124826629681</v>
@@ -52159,7 +52159,7 @@
         <v>439.0059243774414</v>
       </c>
       <c r="G672" t="n">
-        <v>-3.280098538271659</v>
+        <v>-3.280098700845768</v>
       </c>
       <c r="H672" t="n">
         <v>602.0840578111723</v>
@@ -52227,19 +52227,19 @@
         <v>638.2999877929688</v>
       </c>
       <c r="D673" t="n">
-        <v>675.3965588378907</v>
+        <v>675.3965600585938</v>
       </c>
       <c r="E673" t="n">
-        <v>676.9543359375</v>
+        <v>676.9543334960938</v>
       </c>
       <c r="F673" t="n">
-        <v>726.1646520996094</v>
+        <v>726.1646493530274</v>
       </c>
       <c r="G673" t="n">
-        <v>-4.42761495491707</v>
+        <v>-4.427615009308816</v>
       </c>
       <c r="H673" t="n">
-        <v>1211.101032727737</v>
+        <v>1211.101157071308</v>
       </c>
       <c r="I673" t="n">
         <v>577.3964738257137</v>
@@ -52248,7 +52248,7 @@
         <v>10.54795391522234</v>
       </c>
       <c r="K673" t="n">
-        <v>89.73853296086159</v>
+        <v>89.73855244128978</v>
       </c>
       <c r="L673" t="n">
         <v>8.599167822468793</v>
@@ -52310,10 +52310,10 @@
         <v>258.4673684692383</v>
       </c>
       <c r="F674" t="n">
-        <v>268.8172454071045</v>
+        <v>268.8172447967529</v>
       </c>
       <c r="G674" t="n">
-        <v>-3.073745154855201</v>
+        <v>-3.073745321600185</v>
       </c>
       <c r="H674" t="n">
         <v>368.6380196487317</v>
@@ -53927,10 +53927,10 @@
         <v>498.0930407714844</v>
       </c>
       <c r="F695" t="n">
-        <v>543.4515539550781</v>
+        <v>543.4515545654297</v>
       </c>
       <c r="G695" t="n">
-        <v>-4.836000935107942</v>
+        <v>-4.836000726518841</v>
       </c>
       <c r="H695" t="n">
         <v>845.3898333433813</v>
@@ -54931,7 +54931,7 @@
         <v>397.7748913574219</v>
       </c>
       <c r="G708" t="n">
-        <v>-4.489172874661362</v>
+        <v>-4.489172804674279</v>
       </c>
       <c r="H708" t="n">
         <v>541.6977805031639</v>
@@ -55159,10 +55159,10 @@
         <v>359.0312166341146</v>
       </c>
       <c r="F711" t="n">
-        <v>359.5974418640137</v>
+        <v>359.5974417114258</v>
       </c>
       <c r="G711" t="n">
-        <v>-2.435622146661642</v>
+        <v>-2.435622147669958</v>
       </c>
       <c r="H711" t="n">
         <v>487.9415273208757</v>
@@ -55775,10 +55775,10 @@
         <v>671.6656205240886</v>
       </c>
       <c r="F719" t="n">
-        <v>783.4789926147461</v>
+        <v>783.4789965820313</v>
       </c>
       <c r="G719" t="n">
-        <v>-7.988988712026779</v>
+        <v>-7.988988674804953</v>
       </c>
       <c r="H719" t="n">
         <v>1313.886868193049</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1576,10 +1576,10 @@
         <v>2055.300048828125</v>
       </c>
       <c r="I15" t="n">
-        <v>821.6033372206257</v>
+        <v>821.6033975811163</v>
       </c>
       <c r="J15" t="n">
-        <v>144.2784624986326</v>
+        <v>144.2784445523</v>
       </c>
       <c r="K15" t="n">
         <v>2.406579413459142</v>
@@ -3255,16 +3255,16 @@
         <v>1517.800048828125</v>
       </c>
       <c r="D37" t="n">
-        <v>1315.662573242188</v>
+        <v>1315.662570800781</v>
       </c>
       <c r="E37" t="n">
-        <v>1163.400297851563</v>
+        <v>1163.400302734375</v>
       </c>
       <c r="F37" t="n">
-        <v>1056.642496032715</v>
+        <v>1056.642501831055</v>
       </c>
       <c r="G37" t="n">
-        <v>7.875394490294063</v>
+        <v>7.875394242015066</v>
       </c>
       <c r="H37" t="n">
         <v>1568.943822130586</v>
@@ -3335,13 +3335,13 @@
         <v>11362.7619140625</v>
       </c>
       <c r="E38" t="n">
-        <v>10778.5609375</v>
+        <v>10778.56091145833</v>
       </c>
       <c r="F38" t="n">
-        <v>10355.55629150391</v>
+        <v>10355.55625</v>
       </c>
       <c r="G38" t="n">
-        <v>3.013047842286398</v>
+        <v>3.013047654582901</v>
       </c>
       <c r="H38" t="n">
         <v>13287</v>
@@ -4028,13 +4028,13 @@
         <v>251.629248046875</v>
       </c>
       <c r="E47" t="n">
-        <v>234.8898664347331</v>
+        <v>234.8898665364583</v>
       </c>
       <c r="F47" t="n">
-        <v>223.4752029418945</v>
+        <v>223.4752031707764</v>
       </c>
       <c r="G47" t="n">
-        <v>4.12555390204199</v>
+        <v>4.1255537495831</v>
       </c>
       <c r="H47" t="n">
         <v>318.8999938964844</v>
@@ -4105,13 +4105,13 @@
         <v>336.814931640625</v>
       </c>
       <c r="E48" t="n">
-        <v>255.1579315185547</v>
+        <v>255.1579312133789</v>
       </c>
       <c r="F48" t="n">
         <v>241.5448671722412</v>
       </c>
       <c r="G48" t="n">
-        <v>7.519317145278115</v>
+        <v>7.519317072249132</v>
       </c>
       <c r="H48" t="n">
         <v>388.75</v>
@@ -4416,10 +4416,10 @@
         <v>552.354971110026</v>
       </c>
       <c r="F52" t="n">
-        <v>531.4078544616699</v>
+        <v>531.4078535461426</v>
       </c>
       <c r="G52" t="n">
-        <v>5.452836398685723</v>
+        <v>5.452836440523057</v>
       </c>
       <c r="H52" t="n">
         <v>795.731978165477</v>
@@ -5722,13 +5722,13 @@
         <v>2618.773364257812</v>
       </c>
       <c r="E69" t="n">
-        <v>2196.025180664063</v>
+        <v>2196.025184733073</v>
       </c>
       <c r="F69" t="n">
         <v>2102.622564086914</v>
       </c>
       <c r="G69" t="n">
-        <v>4.344305239947932</v>
+        <v>4.344305145132821</v>
       </c>
       <c r="H69" t="n">
         <v>2990</v>
@@ -6264,10 +6264,10 @@
         <v>1017.794586181641</v>
       </c>
       <c r="F76" t="n">
-        <v>969.7187844848632</v>
+        <v>969.7187832641602</v>
       </c>
       <c r="G76" t="n">
-        <v>3.054238615070481</v>
+        <v>3.05423858561038</v>
       </c>
       <c r="H76" t="n">
         <v>1368.900024414062</v>
@@ -7955,22 +7955,22 @@
         <v>1888.977465820313</v>
       </c>
       <c r="E98" t="n">
-        <v>1636.658455403646</v>
+        <v>1636.658461914062</v>
       </c>
       <c r="F98" t="n">
-        <v>1580.8235546875</v>
+        <v>1580.823547363281</v>
       </c>
       <c r="G98" t="n">
-        <v>2.789866256054152</v>
+        <v>2.789866432517041</v>
       </c>
       <c r="H98" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I98" t="n">
-        <v>1266.161452106784</v>
+        <v>1266.16157090969</v>
       </c>
       <c r="J98" t="n">
-        <v>54.19045063958193</v>
+        <v>54.19043617201793</v>
       </c>
       <c r="K98" t="n">
         <v>4.420423326302436</v>
@@ -9806,10 +9806,10 @@
         <v>8296.183313802083</v>
       </c>
       <c r="F122" t="n">
-        <v>8008.86044921875</v>
+        <v>8008.860454101563</v>
       </c>
       <c r="G122" t="n">
-        <v>2.139759124898211</v>
+        <v>2.139759091763405</v>
       </c>
       <c r="H122" t="n">
         <v>9070.5</v>
@@ -10354,10 +10354,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I129" t="n">
-        <v>1175.257470329055</v>
+        <v>1175.257587358084</v>
       </c>
       <c r="J129" t="n">
-        <v>115.127332746946</v>
+        <v>115.1273113251376</v>
       </c>
       <c r="K129" t="n">
         <v>18.01605787300149</v>
@@ -10502,7 +10502,7 @@
         <v>949.0175143432617</v>
       </c>
       <c r="G131" t="n">
-        <v>1.298419792347549</v>
+        <v>1.298419726352518</v>
       </c>
       <c r="H131" t="n">
         <v>1533.599975585938</v>
@@ -12347,19 +12347,19 @@
         <v>1411.251926269531</v>
       </c>
       <c r="F155" t="n">
-        <v>1343.78151550293</v>
+        <v>1343.78151184082</v>
       </c>
       <c r="G155" t="n">
-        <v>2.687230931722628</v>
+        <v>2.687230843454036</v>
       </c>
       <c r="H155" t="n">
         <v>1766.733188761222</v>
       </c>
       <c r="I155" t="n">
-        <v>941.3309959266335</v>
+        <v>941.3310566553616</v>
       </c>
       <c r="J155" t="n">
-        <v>59.05138125171918</v>
+        <v>59.05137099072968</v>
       </c>
       <c r="K155" t="n">
         <v>18.00248773574835</v>
@@ -12883,13 +12883,13 @@
         <v>7402.708798828125</v>
       </c>
       <c r="E162" t="n">
-        <v>6907.080244140625</v>
+        <v>6907.08025390625</v>
       </c>
       <c r="F162" t="n">
-        <v>6484.960087890625</v>
+        <v>6484.960085449219</v>
       </c>
       <c r="G162" t="n">
-        <v>4.022386928281274</v>
+        <v>4.022386929856525</v>
       </c>
       <c r="H162" t="n">
         <v>7832.294844565128</v>
@@ -12966,7 +12966,7 @@
         <v>1120.163899841309</v>
       </c>
       <c r="G163" t="n">
-        <v>3.169663096194597</v>
+        <v>3.169663067196304</v>
       </c>
       <c r="H163" t="n">
         <v>1596.696405272527</v>
@@ -13890,7 +13890,7 @@
         <v>125.8971967315674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.366641301270466</v>
+        <v>1.366641332404406</v>
       </c>
       <c r="H175" t="n">
         <v>150.8288738594787</v>
@@ -15042,10 +15042,10 @@
         <v>312.2791827392578</v>
       </c>
       <c r="F190" t="n">
-        <v>308.9876019287109</v>
+        <v>308.9876016235352</v>
       </c>
       <c r="G190" t="n">
-        <v>1.890258553879165</v>
+        <v>1.890258760852448</v>
       </c>
       <c r="H190" t="n">
         <v>380.4567148307952</v>
@@ -15501,13 +15501,13 @@
         <v>1830.872600097656</v>
       </c>
       <c r="E196" t="n">
-        <v>1706.914969889323</v>
+        <v>1706.914968261719</v>
       </c>
       <c r="F196" t="n">
         <v>1680.250371704102</v>
       </c>
       <c r="G196" t="n">
-        <v>0.9512679054807016</v>
+        <v>0.9512679425001114</v>
       </c>
       <c r="H196" t="n">
         <v>1983.954544928268</v>
@@ -15963,13 +15963,13 @@
         <v>1909.310334472656</v>
       </c>
       <c r="E202" t="n">
-        <v>1780.732895507813</v>
+        <v>1780.732888183594</v>
       </c>
       <c r="F202" t="n">
-        <v>1773.22154296875</v>
+        <v>1773.221539306641</v>
       </c>
       <c r="G202" t="n">
-        <v>1.156949633299176</v>
+        <v>1.156949987931721</v>
       </c>
       <c r="H202" t="n">
         <v>2256.187656125729</v>
@@ -16274,19 +16274,19 @@
         <v>403.5423270670573</v>
       </c>
       <c r="F206" t="n">
-        <v>399.2017221069336</v>
+        <v>399.2017225646973</v>
       </c>
       <c r="G206" t="n">
-        <v>0.8505165249111712</v>
+        <v>0.8505165239276025</v>
       </c>
       <c r="H206" t="n">
         <v>489.5369231157038</v>
       </c>
       <c r="I206" t="n">
-        <v>331.4688100886702</v>
+        <v>331.4688402352409</v>
       </c>
       <c r="J206" t="n">
-        <v>27.41772174297006</v>
+        <v>27.41771015452827</v>
       </c>
       <c r="K206" t="n">
         <v>15.90787641559095</v>
@@ -17352,10 +17352,10 @@
         <v>1472.002293294271</v>
       </c>
       <c r="F220" t="n">
-        <v>1515.677481689453</v>
+        <v>1515.677483520508</v>
       </c>
       <c r="G220" t="n">
-        <v>0.1405152799396348</v>
+        <v>0.1405154412995158</v>
       </c>
       <c r="H220" t="n">
         <v>2021.199951171875</v>
@@ -18738,10 +18738,10 @@
         <v>465.1862990315755</v>
       </c>
       <c r="F238" t="n">
-        <v>458.1383093261718</v>
+        <v>458.1383076477051</v>
       </c>
       <c r="G238" t="n">
-        <v>1.732828281010912</v>
+        <v>1.732828184058377</v>
       </c>
       <c r="H238" t="n">
         <v>529.9163379046904</v>
@@ -19739,10 +19739,10 @@
         <v>1015.657439371745</v>
       </c>
       <c r="F251" t="n">
-        <v>989.2291995239258</v>
+        <v>989.2291986083984</v>
       </c>
       <c r="G251" t="n">
-        <v>0.9104186124474722</v>
+        <v>0.9104186761260014</v>
       </c>
       <c r="H251" t="n">
         <v>1331.075409591023</v>
@@ -20124,10 +20124,10 @@
         <v>165.6315799967448</v>
       </c>
       <c r="F256" t="n">
-        <v>164.8116391754151</v>
+        <v>164.8116390991211</v>
       </c>
       <c r="G256" t="n">
-        <v>0.05554015263093959</v>
+        <v>0.05554015265665235</v>
       </c>
       <c r="H256" t="n">
         <v>181.8519567776652</v>
@@ -20740,10 +20740,10 @@
         <v>36710.01061197917</v>
       </c>
       <c r="F264" t="n">
-        <v>36129.27927734375</v>
+        <v>36129.2791796875</v>
       </c>
       <c r="G264" t="n">
-        <v>-0.6884363494813139</v>
+        <v>-0.6884367245523215</v>
       </c>
       <c r="H264" t="n">
         <v>43614.20556091995</v>
@@ -20971,19 +20971,19 @@
         <v>298.1120263671875</v>
       </c>
       <c r="F267" t="n">
-        <v>286.1809645080567</v>
+        <v>286.1809648895264</v>
       </c>
       <c r="G267" t="n">
-        <v>1.156280934905141</v>
+        <v>1.156281069743104</v>
       </c>
       <c r="H267" t="n">
         <v>359.3387168134344</v>
       </c>
       <c r="I267" t="n">
-        <v>206.1210871445057</v>
+        <v>206.1211021779015</v>
       </c>
       <c r="J267" t="n">
-        <v>39.72369542088208</v>
+        <v>39.72368523016601</v>
       </c>
       <c r="K267" t="n">
         <v>24.77038778244252</v>
@@ -21664,10 +21664,10 @@
         <v>1838.262978515625</v>
       </c>
       <c r="F276" t="n">
-        <v>1802.981233520508</v>
+        <v>1802.981232299805</v>
       </c>
       <c r="G276" t="n">
-        <v>0.699556789295297</v>
+        <v>0.6995567554446191</v>
       </c>
       <c r="H276" t="n">
         <v>2046.900024414062</v>
@@ -23053,16 +23053,16 @@
         <v>369.2434732055664</v>
       </c>
       <c r="G294" t="n">
-        <v>3.392585115637758</v>
+        <v>3.392584828494005</v>
       </c>
       <c r="H294" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I294" t="n">
-        <v>191.8556371798532</v>
+        <v>191.8556220656042</v>
       </c>
       <c r="J294" t="n">
-        <v>86.96349895143886</v>
+        <v>86.96351368028994</v>
       </c>
       <c r="K294" t="n">
         <v>23.60554547099019</v>
@@ -23361,7 +23361,7 @@
         <v>269.420802078247</v>
       </c>
       <c r="G298" t="n">
-        <v>1.948641819648156</v>
+        <v>1.948641760783865</v>
       </c>
       <c r="H298" t="n">
         <v>367.499792159746</v>
@@ -23666,10 +23666,10 @@
         <v>5220.916038411458</v>
       </c>
       <c r="F302" t="n">
-        <v>4977.822921142578</v>
+        <v>4977.822918701172</v>
       </c>
       <c r="G302" t="n">
-        <v>1.5767515409296</v>
+        <v>1.576751642924168</v>
       </c>
       <c r="H302" t="n">
         <v>6049.821052103703</v>
@@ -23820,10 +23820,10 @@
         <v>1384.254513346354</v>
       </c>
       <c r="F304" t="n">
-        <v>1357.368189086914</v>
+        <v>1357.368188476562</v>
       </c>
       <c r="G304" t="n">
-        <v>1.253239789620464</v>
+        <v>1.253239928490824</v>
       </c>
       <c r="H304" t="n">
         <v>1553</v>
@@ -24051,10 +24051,10 @@
         <v>1365.088555501302</v>
       </c>
       <c r="F307" t="n">
-        <v>1365.882330322266</v>
+        <v>1365.882327880859</v>
       </c>
       <c r="G307" t="n">
-        <v>0.1253248836519338</v>
+        <v>0.1253248390786332</v>
       </c>
       <c r="H307" t="n">
         <v>1563.400024414062</v>
@@ -24122,19 +24122,19 @@
         <v>426.1000061035156</v>
       </c>
       <c r="D308" t="n">
-        <v>411.2546661376953</v>
+        <v>411.2546649169922</v>
       </c>
       <c r="E308" t="n">
-        <v>429.7601845296224</v>
+        <v>429.760185546875</v>
       </c>
       <c r="F308" t="n">
-        <v>422.5457289123535</v>
+        <v>422.5457287597656</v>
       </c>
       <c r="G308" t="n">
-        <v>1.357816896511288</v>
+        <v>1.357816897008246</v>
       </c>
       <c r="H308" t="n">
-        <v>478.7148398145708</v>
+        <v>478.7148709533388</v>
       </c>
       <c r="I308" t="n">
         <v>355.1755291130353</v>
@@ -24143,7 +24143,7 @@
         <v>19.96885234959656</v>
       </c>
       <c r="K308" t="n">
-        <v>12.34800116343417</v>
+        <v>12.34800847128856</v>
       </c>
       <c r="L308" t="n">
         <v>60.47156726768377</v>
@@ -24436,10 +24436,10 @@
         <v>1097.080819498698</v>
       </c>
       <c r="F312" t="n">
-        <v>1142.093256835938</v>
+        <v>1142.093260498047</v>
       </c>
       <c r="G312" t="n">
-        <v>-0.5104880289129143</v>
+        <v>-0.5104879743871527</v>
       </c>
       <c r="H312" t="n">
         <v>1409.944064008135</v>
@@ -24510,13 +24510,13 @@
         <v>4542.822724609375</v>
       </c>
       <c r="E313" t="n">
-        <v>4236.807749023437</v>
+        <v>4236.807755533854</v>
       </c>
       <c r="F313" t="n">
-        <v>4302.876114501953</v>
+        <v>4302.876119384766</v>
       </c>
       <c r="G313" t="n">
-        <v>0.4646390078178353</v>
+        <v>0.4646388354858422</v>
       </c>
       <c r="H313" t="n">
         <v>5005.771680286142</v>
@@ -25745,10 +25745,10 @@
         <v>729.4431587727864</v>
       </c>
       <c r="F329" t="n">
-        <v>744.862698059082</v>
+        <v>744.8626977539062</v>
       </c>
       <c r="G329" t="n">
-        <v>-0.1937057803936493</v>
+        <v>-0.1937057804728748</v>
       </c>
       <c r="H329" t="n">
         <v>879.2203373423794</v>
@@ -27901,10 +27901,10 @@
         <v>5168.97748046875</v>
       </c>
       <c r="F357" t="n">
-        <v>5260.433544921875</v>
+        <v>5260.433537597656</v>
       </c>
       <c r="G357" t="n">
-        <v>-0.9167137833465566</v>
+        <v>-0.9167136934837505</v>
       </c>
       <c r="H357" t="n">
         <v>6175.521739453033</v>
@@ -27978,10 +27978,10 @@
         <v>579.5693098958334</v>
       </c>
       <c r="F358" t="n">
-        <v>561.4509989929199</v>
+        <v>561.4509992980957</v>
       </c>
       <c r="G358" t="n">
-        <v>0.5915380990633823</v>
+        <v>0.5915382087395393</v>
       </c>
       <c r="H358" t="n">
         <v>784.8771245029434</v>
@@ -28209,10 +28209,10 @@
         <v>1145.369587809245</v>
       </c>
       <c r="F361" t="n">
-        <v>1164.901219177246</v>
+        <v>1164.90121673584</v>
       </c>
       <c r="G361" t="n">
-        <v>-0.4903318480295904</v>
+        <v>-0.4903317452870315</v>
       </c>
       <c r="H361" t="n">
         <v>1378.852549646065</v>
@@ -28594,13 +28594,13 @@
         <v>739.7274979654948</v>
       </c>
       <c r="F366" t="n">
-        <v>757.9121447753906</v>
+        <v>757.9121438598632</v>
       </c>
       <c r="G366" t="n">
-        <v>-2.529212610300102</v>
+        <v>-2.529212613278031</v>
       </c>
       <c r="H366" t="n">
-        <v>1117.559301306357</v>
+        <v>1117.559425954049</v>
       </c>
       <c r="I366" t="n">
         <v>612.1496526863262</v>
@@ -28609,7 +28609,7 @@
         <v>31.66714976688965</v>
       </c>
       <c r="K366" t="n">
-        <v>38.65500016207899</v>
+        <v>38.65501562705325</v>
       </c>
       <c r="L366" t="n">
         <v>50.7628294036061</v>
@@ -28979,10 +28979,10 @@
         <v>200.040051167806</v>
       </c>
       <c r="F371" t="n">
-        <v>207.4594385528565</v>
+        <v>207.4594389343262</v>
       </c>
       <c r="G371" t="n">
-        <v>-1.504503899266363</v>
+        <v>-1.504503753833142</v>
       </c>
       <c r="H371" t="n">
         <v>278.3389924341271</v>
@@ -30519,10 +30519,10 @@
         <v>338.5830503336588</v>
       </c>
       <c r="F391" t="n">
-        <v>335.0915635681152</v>
+        <v>335.0915637207031</v>
       </c>
       <c r="G391" t="n">
-        <v>1.071609694038878</v>
+        <v>1.071609786580363</v>
       </c>
       <c r="H391" t="n">
         <v>428.7550602808859</v>
@@ -31517,13 +31517,13 @@
         <v>753.4573889160156</v>
       </c>
       <c r="E404" t="n">
-        <v>740.7510111490885</v>
+        <v>740.7510091145833</v>
       </c>
       <c r="F404" t="n">
-        <v>736.3989730834961</v>
+        <v>736.3989724731446</v>
       </c>
       <c r="G404" t="n">
-        <v>-0.6180670738096139</v>
+        <v>-0.6180672380425078</v>
       </c>
       <c r="H404" t="n">
         <v>837.8765073351432</v>
@@ -31751,13 +31751,13 @@
         <v>1082.494107666016</v>
       </c>
       <c r="F407" t="n">
-        <v>1080.972903137207</v>
+        <v>1080.97290222168</v>
       </c>
       <c r="G407" t="n">
-        <v>-0.9072650865513232</v>
+        <v>-0.907265142756053</v>
       </c>
       <c r="H407" t="n">
-        <v>1300.436795781491</v>
+        <v>1300.436668328248</v>
       </c>
       <c r="I407" t="n">
         <v>885.652283987356</v>
@@ -31766,7 +31766,7 @@
         <v>20.96169887407182</v>
       </c>
       <c r="K407" t="n">
-        <v>21.3886620470161</v>
+        <v>21.38865014995293</v>
       </c>
       <c r="L407" t="n">
         <v>40.91539528432732</v>
@@ -32133,13 +32133,13 @@
         <v>298.6186181640625</v>
       </c>
       <c r="E412" t="n">
-        <v>273.0273678588867</v>
+        <v>273.0273685709635</v>
       </c>
       <c r="F412" t="n">
-        <v>285.6348247528076</v>
+        <v>285.6348243713379</v>
       </c>
       <c r="G412" t="n">
-        <v>-2.815854856295075</v>
+        <v>-2.815854859949796</v>
       </c>
       <c r="H412" t="n">
         <v>390.5481555478003</v>
@@ -33679,7 +33679,7 @@
         <v>2553.788489990234</v>
       </c>
       <c r="G432" t="n">
-        <v>-1.503884362382546</v>
+        <v>-1.503884408755352</v>
       </c>
       <c r="H432" t="n">
         <v>2960.01877635178</v>
@@ -34061,10 +34061,10 @@
         <v>1247.107093505859</v>
       </c>
       <c r="F437" t="n">
-        <v>1329.861235046387</v>
+        <v>1329.86123626709</v>
       </c>
       <c r="G437" t="n">
-        <v>-2.424624153051647</v>
+        <v>-2.424624019788224</v>
       </c>
       <c r="H437" t="n">
         <v>1729.008500794829</v>
@@ -34215,10 +34215,10 @@
         <v>77.47305587768555</v>
       </c>
       <c r="F439" t="n">
-        <v>77.37549713134766</v>
+        <v>77.37549724578858</v>
       </c>
       <c r="G439" t="n">
-        <v>-0.1080551059435275</v>
+        <v>-0.1080552041731075</v>
       </c>
       <c r="H439" t="n">
         <v>86.59303970157107</v>
@@ -34982,16 +34982,16 @@
         <v>503.3993206787109</v>
       </c>
       <c r="E449" t="n">
-        <v>485.9179475911458</v>
+        <v>485.9179461669922</v>
       </c>
       <c r="F449" t="n">
-        <v>490.7460380554199</v>
+        <v>490.7460363769531</v>
       </c>
       <c r="G449" t="n">
-        <v>-0.2802010206126027</v>
+        <v>-0.2802011452444519</v>
       </c>
       <c r="H449" t="n">
-        <v>547.7380341214969</v>
+        <v>547.7379722645398</v>
       </c>
       <c r="I449" t="n">
         <v>419.3328127807616</v>
@@ -35000,7 +35000,7 @@
         <v>10.05578050036464</v>
       </c>
       <c r="K449" t="n">
-        <v>18.68646459837418</v>
+        <v>18.68645119491654</v>
       </c>
       <c r="L449" t="n">
         <v>36.89320388349515</v>
@@ -36756,10 +36756,10 @@
         <v>383.7009169514974</v>
       </c>
       <c r="F472" t="n">
-        <v>394.6485163879395</v>
+        <v>394.6485162353516</v>
       </c>
       <c r="G472" t="n">
-        <v>-3.722195663525818</v>
+        <v>-3.722195485713897</v>
       </c>
       <c r="H472" t="n">
         <v>541.0236304500187</v>
@@ -37754,22 +37754,22 @@
         <v>2276.71484375</v>
       </c>
       <c r="E485" t="n">
-        <v>2226.59209391276</v>
+        <v>2226.592064615885</v>
       </c>
       <c r="F485" t="n">
-        <v>2276.099978637695</v>
+        <v>2276.099962768555</v>
       </c>
       <c r="G485" t="n">
-        <v>-0.427594122811259</v>
+        <v>-0.4275940726060412</v>
       </c>
       <c r="H485" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I485" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J485" t="n">
-        <v>11.31484519965893</v>
+        <v>11.31485210721246</v>
       </c>
       <c r="K485" t="n">
         <v>26.54461366267797</v>
@@ -37834,13 +37834,13 @@
         <v>5429.506998697917</v>
       </c>
       <c r="F486" t="n">
-        <v>5470.209602050782</v>
+        <v>5470.209609375</v>
       </c>
       <c r="G486" t="n">
-        <v>-0.7492673820705176</v>
+        <v>-0.7492675129687432</v>
       </c>
       <c r="H486" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I486" t="n">
         <v>5051</v>
@@ -37849,7 +37849,7 @@
         <v>4.414967333201347</v>
       </c>
       <c r="K486" t="n">
-        <v>11.40564890408418</v>
+        <v>11.40565827288356</v>
       </c>
       <c r="L486" t="n">
         <v>42.1636615811373</v>
@@ -37991,7 +37991,7 @@
         <v>4764.205091552734</v>
       </c>
       <c r="G488" t="n">
-        <v>-0.08184066960398306</v>
+        <v>-0.08184072076490301</v>
       </c>
       <c r="H488" t="n">
         <v>5612.405266256894</v>
@@ -38370,13 +38370,13 @@
         <v>477.9314776611328</v>
       </c>
       <c r="E493" t="n">
-        <v>526.2697357177734</v>
+        <v>526.2697353108724</v>
       </c>
       <c r="F493" t="n">
-        <v>533.598900604248</v>
+        <v>533.5989018249512</v>
       </c>
       <c r="G493" t="n">
-        <v>-1.506682485962851</v>
+        <v>-1.506682371604862</v>
       </c>
       <c r="H493" t="n">
         <v>653.9340000086492</v>
@@ -38447,22 +38447,22 @@
         <v>430.9691821289063</v>
       </c>
       <c r="E494" t="n">
-        <v>462.6965879313151</v>
+        <v>462.6965881347656</v>
       </c>
       <c r="F494" t="n">
-        <v>465.562088470459</v>
+        <v>465.5620889282226</v>
       </c>
       <c r="G494" t="n">
-        <v>-1.128613300688019</v>
+        <v>-1.128613395708888</v>
       </c>
       <c r="H494" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I494" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J494" t="n">
-        <v>14.49941201025051</v>
+        <v>14.49942118303877</v>
       </c>
       <c r="K494" t="n">
         <v>27.68727324110241</v>
@@ -39140,25 +39140,25 @@
         <v>231.160930480957</v>
       </c>
       <c r="E503" t="n">
-        <v>224.4955261230469</v>
+        <v>224.4955264282227</v>
       </c>
       <c r="F503" t="n">
-        <v>225.6140670013428</v>
+        <v>225.6140672302246</v>
       </c>
       <c r="G503" t="n">
-        <v>-1.364058386127009</v>
+        <v>-1.364058483461705</v>
       </c>
       <c r="H503" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I503" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J503" t="n">
-        <v>20.02128795617528</v>
+        <v>20.0212985319485</v>
       </c>
       <c r="K503" t="n">
-        <v>38.61828291038911</v>
+        <v>38.61829873576517</v>
       </c>
       <c r="L503" t="n">
         <v>34.81276005547851</v>
@@ -40458,7 +40458,7 @@
         <v>-1.836345783645466</v>
       </c>
       <c r="H520" t="n">
-        <v>848.8263047717415</v>
+        <v>848.8262434052705</v>
       </c>
       <c r="I520" t="n">
         <v>495.5999980879241</v>
@@ -40467,7 +40467,7 @@
         <v>21.03510449964094</v>
       </c>
       <c r="K520" t="n">
-        <v>41.50643316149214</v>
+        <v>41.50642293118896</v>
       </c>
       <c r="L520" t="n">
         <v>29.95839112343966</v>
@@ -40609,7 +40609,7 @@
         <v>33.80074458122253</v>
       </c>
       <c r="G522" t="n">
-        <v>-1.987491731455793</v>
+        <v>-1.987492002497948</v>
       </c>
       <c r="H522" t="n">
         <v>40.26070662850351</v>
@@ -40763,10 +40763,10 @@
         <v>237.1050746917725</v>
       </c>
       <c r="G524" t="n">
-        <v>-2.104239039780009</v>
+        <v>-2.104239101454708</v>
       </c>
       <c r="H524" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I524" t="n">
         <v>185.2067002350832</v>
@@ -40775,7 +40775,7 @@
         <v>22.80873027786765</v>
       </c>
       <c r="K524" t="n">
-        <v>35.44721421268164</v>
+        <v>35.44720015394032</v>
       </c>
       <c r="L524" t="n">
         <v>28.84882108183079</v>
@@ -41222,10 +41222,10 @@
         <v>207.7894618733724</v>
       </c>
       <c r="F530" t="n">
-        <v>211.6584394836426</v>
+        <v>211.6584396362305</v>
       </c>
       <c r="G530" t="n">
-        <v>-1.249598678812536</v>
+        <v>-1.249598748224068</v>
       </c>
       <c r="H530" t="n">
         <v>260.4933484681973</v>
@@ -41296,13 +41296,13 @@
         <v>372.3288641357422</v>
       </c>
       <c r="E531" t="n">
-        <v>403.2165755208333</v>
+        <v>403.2165763346354</v>
       </c>
       <c r="F531" t="n">
-        <v>392.7666505432129</v>
+        <v>392.7666499328614</v>
       </c>
       <c r="G531" t="n">
-        <v>-0.001111238827433692</v>
+        <v>-0.001111238829154537</v>
       </c>
       <c r="H531" t="n">
         <v>476.8288845013619</v>
@@ -42454,10 +42454,10 @@
         <v>2436.246567382812</v>
       </c>
       <c r="F546" t="n">
-        <v>2435.093383789062</v>
+        <v>2435.09337890625</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.372245868955835</v>
+        <v>-1.372245774143166</v>
       </c>
       <c r="H546" t="n">
         <v>2972.124194159559</v>
@@ -42990,16 +42990,16 @@
         <v>456.2483013916016</v>
       </c>
       <c r="E553" t="n">
-        <v>496.2405291748047</v>
+        <v>496.2405326334635</v>
       </c>
       <c r="F553" t="n">
-        <v>505.8120706176758</v>
+        <v>505.8120732116699</v>
       </c>
       <c r="G553" t="n">
-        <v>-3.913639601340335</v>
+        <v>-3.913639637758948</v>
       </c>
       <c r="H553" t="n">
-        <v>758.5896367271307</v>
+        <v>758.589574672296</v>
       </c>
       <c r="I553" t="n">
         <v>400.6499938964844</v>
@@ -43008,7 +43008,7 @@
         <v>17.12217824749045</v>
       </c>
       <c r="K553" t="n">
-        <v>61.66001848207367</v>
+        <v>61.66000525781481</v>
       </c>
       <c r="L553" t="n">
         <v>13.17614424410541</v>
@@ -43144,16 +43144,16 @@
         <v>353.3964935302735</v>
       </c>
       <c r="E555" t="n">
-        <v>416.9898107910156</v>
+        <v>416.9898105875651</v>
       </c>
       <c r="F555" t="n">
-        <v>444.7202917480469</v>
+        <v>444.7202911376953</v>
       </c>
       <c r="G555" t="n">
-        <v>-4.775306590035832</v>
+        <v>-4.775306596276685</v>
       </c>
       <c r="H555" t="n">
-        <v>605.9581114957105</v>
+        <v>605.9581737112406</v>
       </c>
       <c r="I555" t="n">
         <v>326.057353105007</v>
@@ -43162,7 +43162,7 @@
         <v>23.88925088186522</v>
       </c>
       <c r="K555" t="n">
-        <v>50.0081923961291</v>
+        <v>50.00820779791852</v>
       </c>
       <c r="L555" t="n">
         <v>11.6504854368932</v>
@@ -43372,19 +43372,19 @@
         <v>629.7999877929688</v>
       </c>
       <c r="D558" t="n">
-        <v>673.1282971191406</v>
+        <v>673.1282983398437</v>
       </c>
       <c r="E558" t="n">
-        <v>671.6738757324218</v>
+        <v>671.6738781738281</v>
       </c>
       <c r="F558" t="n">
-        <v>718.9095669555664</v>
+        <v>718.9095693969726</v>
       </c>
       <c r="G558" t="n">
-        <v>-4.383153589633659</v>
+        <v>-4.383153653021166</v>
       </c>
       <c r="H558" t="n">
-        <v>1181.515387363553</v>
+        <v>1181.515511428121</v>
       </c>
       <c r="I558" t="n">
         <v>577.3964738257137</v>
@@ -43393,7 +43393,7 @@
         <v>9.075828541182428</v>
       </c>
       <c r="K558" t="n">
-        <v>87.60168470373912</v>
+        <v>87.60170440278172</v>
       </c>
       <c r="L558" t="n">
         <v>8.876560332871012</v>
@@ -43609,13 +43609,13 @@
         <v>507.9299729410807</v>
       </c>
       <c r="F561" t="n">
-        <v>537.1996995544433</v>
+        <v>537.1996977233887</v>
       </c>
       <c r="G561" t="n">
-        <v>-3.524954682603154</v>
+        <v>-3.524954799943025</v>
       </c>
       <c r="H561" t="n">
-        <v>828.2152046613147</v>
+        <v>828.2152668923007</v>
       </c>
       <c r="I561" t="n">
         <v>406.1171468902937</v>
@@ -43624,7 +43624,7 @@
         <v>14.00651352578135</v>
       </c>
       <c r="K561" t="n">
-        <v>78.88017379294054</v>
+        <v>78.88018723375826</v>
       </c>
       <c r="L561" t="n">
         <v>6.796116504854369</v>
@@ -43985,19 +43985,19 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>235.25</v>
+        <v>244.3500061035156</v>
       </c>
       <c r="D566" t="n">
-        <v>557.9621734619141</v>
+        <v>551.1681958007813</v>
       </c>
       <c r="E566" t="n">
-        <v>558.6411279296875</v>
+        <v>556.5813108317058</v>
       </c>
       <c r="F566" t="n">
-        <v>557.7298776245117</v>
+        <v>556.2315022277832</v>
       </c>
       <c r="G566" t="n">
-        <v>-1.991903247960825</v>
+        <v>-2.42424733354818</v>
       </c>
       <c r="H566" t="n">
         <v>753.9000244140625</v>
@@ -44006,10 +44006,10 @@
         <v>214.1000061035156</v>
       </c>
       <c r="J566" t="n">
-        <v>9.878558287503525</v>
+        <v>14.12891132070981</v>
       </c>
       <c r="K566" t="n">
-        <v>220.4675980506111</v>
+        <v>208.5328445192192</v>
       </c>
       <c r="L566" t="n">
         <v>0.2773925104022191</v>
@@ -44302,10 +44302,10 @@
         <v>142.0476087443034</v>
       </c>
       <c r="F570" t="n">
-        <v>146.9962475585938</v>
+        <v>146.9962474822998</v>
       </c>
       <c r="G570" t="n">
-        <v>-1.619052316524716</v>
+        <v>-1.619052267116505</v>
       </c>
       <c r="H570" t="n">
         <v>184.9587904135824</v>
@@ -45380,13 +45380,13 @@
         <v>122.7193290201823</v>
       </c>
       <c r="F584" t="n">
-        <v>124.6486833190918</v>
+        <v>124.648683052063</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.867549866906715</v>
+        <v>-1.867549517178491</v>
       </c>
       <c r="H584" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I584" t="n">
         <v>110.3499984741211</v>
@@ -45395,7 +45395,7 @@
         <v>2.1295863222619</v>
       </c>
       <c r="K584" t="n">
-        <v>38.33183903869131</v>
+        <v>38.33182335537655</v>
       </c>
       <c r="L584" t="n">
         <v>25.65880721220527</v>
@@ -45765,13 +45765,13 @@
         <v>130957.3200520833</v>
       </c>
       <c r="F589" t="n">
-        <v>134792.03921875</v>
+        <v>134792.0390625</v>
       </c>
       <c r="G589" t="n">
-        <v>-2.100468994956195</v>
+        <v>-2.10046899733991</v>
       </c>
       <c r="H589" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I589" t="n">
         <v>121787.4350540836</v>
@@ -45780,7 +45780,7 @@
         <v>1.845481797788318</v>
       </c>
       <c r="K589" t="n">
-        <v>31.66322919235265</v>
+        <v>31.6632420577639</v>
       </c>
       <c r="L589" t="n">
         <v>24.6879334257975</v>
@@ -45848,7 +45848,7 @@
         <v>-0.592056154740972</v>
       </c>
       <c r="H590" t="n">
-        <v>523.4329909937741</v>
+        <v>523.4329289989834</v>
       </c>
       <c r="I590" t="n">
         <v>394.4382907843191</v>
@@ -45857,7 +45857,7 @@
         <v>5.960811100758079</v>
       </c>
       <c r="K590" t="n">
-        <v>25.23818057325284</v>
+        <v>25.23816574018933</v>
       </c>
       <c r="L590" t="n">
         <v>24.41054091539528</v>
@@ -46840,13 +46840,13 @@
         <v>185.74625</v>
       </c>
       <c r="E603" t="n">
-        <v>192.3783167521159</v>
+        <v>192.3783170572917</v>
       </c>
       <c r="F603" t="n">
-        <v>195.0438655853272</v>
+        <v>195.0438658905029</v>
       </c>
       <c r="G603" t="n">
-        <v>-2.607567889558449</v>
+        <v>-2.607567885584916</v>
       </c>
       <c r="H603" t="n">
         <v>239.2186883393384</v>
@@ -46997,10 +46997,10 @@
         <v>1062.479805094401</v>
       </c>
       <c r="F605" t="n">
-        <v>1090.782477722168</v>
+        <v>1090.782477111816</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.063780749613098</v>
+        <v>-2.06378075074406</v>
       </c>
       <c r="H605" t="n">
         <v>1395.129939548488</v>
@@ -47074,13 +47074,13 @@
         <v>7688.377086588542</v>
       </c>
       <c r="F606" t="n">
-        <v>7787.453745117187</v>
+        <v>7787.453747558594</v>
       </c>
       <c r="G606" t="n">
-        <v>-1.271150800111465</v>
+        <v>-1.271150708042368</v>
       </c>
       <c r="H606" t="n">
-        <v>9653.120359649309</v>
+        <v>9653.121370296873</v>
       </c>
       <c r="I606" t="n">
         <v>6922</v>
@@ -47089,7 +47089,7 @@
         <v>2.167003756139851</v>
       </c>
       <c r="K606" t="n">
-        <v>36.49774264209995</v>
+        <v>36.49775693293089</v>
       </c>
       <c r="L606" t="n">
         <v>20.80443828016643</v>
@@ -47148,13 +47148,13 @@
         <v>115.4739770507812</v>
       </c>
       <c r="E607" t="n">
-        <v>121.1187431844075</v>
+        <v>121.1187430826823</v>
       </c>
       <c r="F607" t="n">
-        <v>123.8878695678711</v>
+        <v>123.8878693771362</v>
       </c>
       <c r="G607" t="n">
-        <v>-2.501114819927197</v>
+        <v>-2.5011147651405</v>
       </c>
       <c r="H607" t="n">
         <v>156.8181640954093</v>
@@ -47690,10 +47690,10 @@
         <v>1471.633913574219</v>
       </c>
       <c r="F614" t="n">
-        <v>1491.384322509766</v>
+        <v>1491.384323120117</v>
       </c>
       <c r="G614" t="n">
-        <v>-1.71142991832377</v>
+        <v>-1.711429878099002</v>
       </c>
       <c r="H614" t="n">
         <v>1965.628830677411</v>
@@ -47998,10 +47998,10 @@
         <v>20.42095072428386</v>
       </c>
       <c r="F618" t="n">
-        <v>20.50834037780762</v>
+        <v>20.5083403968811</v>
       </c>
       <c r="G618" t="n">
-        <v>-1.278661014509896</v>
+        <v>-1.278661058656094</v>
       </c>
       <c r="H618" t="n">
         <v>23.83526024888653</v>
@@ -49073,16 +49073,16 @@
         <v>2289.488012695313</v>
       </c>
       <c r="E632" t="n">
-        <v>2303.345184733073</v>
+        <v>2303.345173339844</v>
       </c>
       <c r="F632" t="n">
-        <v>2484.526566772461</v>
+        <v>2484.52655456543</v>
       </c>
       <c r="G632" t="n">
-        <v>-3.469682702261068</v>
+        <v>-3.469682810280728</v>
       </c>
       <c r="H632" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I632" t="n">
         <v>1966.020518717901</v>
@@ -49091,7 +49091,7 @@
         <v>5.899199941093825</v>
       </c>
       <c r="K632" t="n">
-        <v>57.88480528096531</v>
+        <v>57.88479310133767</v>
       </c>
       <c r="L632" t="n">
         <v>15.53398058252427</v>
@@ -49156,7 +49156,7 @@
         <v>435.1267344665528</v>
       </c>
       <c r="G633" t="n">
-        <v>-3.404032935952583</v>
+        <v>-3.404032870511231</v>
       </c>
       <c r="H633" t="n">
         <v>570.5579909394708</v>
@@ -49926,7 +49926,7 @@
         <v>95.87017982482911</v>
       </c>
       <c r="G643" t="n">
-        <v>-3.180090822509551</v>
+        <v>-3.180090785209799</v>
       </c>
       <c r="H643" t="n">
         <v>124.8273096544699</v>
@@ -50000,10 +50000,10 @@
         <v>1291.995585123698</v>
       </c>
       <c r="F644" t="n">
-        <v>1321.459875488281</v>
+        <v>1321.45987487793</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.386999949334179</v>
+        <v>-2.386999994419359</v>
       </c>
       <c r="H644" t="n">
         <v>1627.061020109863</v>
@@ -50385,13 +50385,13 @@
         <v>1017.459152018229</v>
       </c>
       <c r="F649" t="n">
-        <v>1060.007167358398</v>
+        <v>1060.007169189453</v>
       </c>
       <c r="G649" t="n">
-        <v>-2.420704782863015</v>
+        <v>-2.420704723956724</v>
       </c>
       <c r="H649" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I649" t="n">
         <v>855.1500244140625</v>
@@ -50400,7 +50400,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K649" t="n">
-        <v>42.63391283520865</v>
+        <v>42.63389867229614</v>
       </c>
       <c r="L649" t="n">
         <v>12.48266296809986</v>
@@ -50462,13 +50462,13 @@
         <v>286.2021783447266</v>
       </c>
       <c r="F650" t="n">
-        <v>298.2570054626465</v>
+        <v>298.2570056152344</v>
       </c>
       <c r="G650" t="n">
-        <v>-4.286463795060103</v>
+        <v>-4.286463886697101</v>
       </c>
       <c r="H650" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I650" t="n">
         <v>255.5</v>
@@ -50477,7 +50477,7 @@
         <v>5.283757338551864</v>
       </c>
       <c r="K650" t="n">
-        <v>51.14154805123956</v>
+        <v>51.14155955934725</v>
       </c>
       <c r="L650" t="n">
         <v>12.34396671289875</v>
@@ -51158,7 +51158,7 @@
         <v>1694.180337524414</v>
       </c>
       <c r="G659" t="n">
-        <v>-4.901237464916298</v>
+        <v>-4.901237497497723</v>
       </c>
       <c r="H659" t="n">
         <v>2504.019782423858</v>
@@ -51232,13 +51232,13 @@
         <v>296.3036335245768</v>
       </c>
       <c r="F660" t="n">
-        <v>307.5067194366455</v>
+        <v>307.5067198944092</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.547029931586431</v>
+        <v>-2.547029739389561</v>
       </c>
       <c r="H660" t="n">
-        <v>396.5816020628056</v>
+        <v>396.5816646357411</v>
       </c>
       <c r="I660" t="n">
         <v>243.9284560598348</v>
@@ -51247,7 +51247,7 @@
         <v>6.650121145632348</v>
       </c>
       <c r="K660" t="n">
-        <v>52.4434408484393</v>
+        <v>52.44346490107699</v>
       </c>
       <c r="L660" t="n">
         <v>10.54091539528433</v>
@@ -51546,7 +51546,7 @@
         <v>-4.038459585346654</v>
       </c>
       <c r="H664" t="n">
-        <v>3469.396141243416</v>
+        <v>3469.395895156339</v>
       </c>
       <c r="I664" t="n">
         <v>1805.687062514093</v>
@@ -51555,7 +51555,7 @@
         <v>9.121899653566556</v>
       </c>
       <c r="K664" t="n">
-        <v>76.07572565246539</v>
+        <v>76.07571316327164</v>
       </c>
       <c r="L664" t="n">
         <v>9.986130374479888</v>
@@ -51617,10 +51617,10 @@
         <v>2755.432490234375</v>
       </c>
       <c r="F665" t="n">
-        <v>2862.996900634766</v>
+        <v>2862.996896972656</v>
       </c>
       <c r="G665" t="n">
-        <v>-3.925383721688003</v>
+        <v>-3.925383805223126</v>
       </c>
       <c r="H665" t="n">
         <v>3812.926349899466</v>
@@ -52313,7 +52313,7 @@
         <v>547.7069464111328</v>
       </c>
       <c r="G674" t="n">
-        <v>-4.113724884557424</v>
+        <v>-4.113725038243999</v>
       </c>
       <c r="H674" t="n">
         <v>725.6811213920008</v>
@@ -53311,10 +53311,10 @@
         <v>493.8067075602214</v>
       </c>
       <c r="F687" t="n">
-        <v>536.3697608947754</v>
+        <v>536.3697615051269</v>
       </c>
       <c r="G687" t="n">
-        <v>-5.138883081877898</v>
+        <v>-5.138882922733434</v>
       </c>
       <c r="H687" t="n">
         <v>799.7128098861871</v>
@@ -53388,10 +53388,10 @@
         <v>276.8652786254883</v>
       </c>
       <c r="F688" t="n">
-        <v>289.3636045074463</v>
+        <v>289.3636037445069</v>
       </c>
       <c r="G688" t="n">
-        <v>-4.124337590536554</v>
+        <v>-4.124337649434551</v>
       </c>
       <c r="H688" t="n">
         <v>386.0274005660562</v>
@@ -54466,10 +54466,10 @@
         <v>249.6811647542318</v>
       </c>
       <c r="F702" t="n">
-        <v>269.3974154663086</v>
+        <v>269.3974150085449</v>
       </c>
       <c r="G702" t="n">
-        <v>-4.223726787469806</v>
+        <v>-4.223726898257308</v>
       </c>
       <c r="H702" t="n">
         <v>398.2045017598045</v>
@@ -55236,10 +55236,10 @@
         <v>353.178930867513</v>
       </c>
       <c r="F712" t="n">
-        <v>356.3174865722656</v>
+        <v>356.3174864196777</v>
       </c>
       <c r="G712" t="n">
-        <v>-2.81540307394057</v>
+        <v>-2.81540311555849</v>
       </c>
       <c r="H712" t="n">
         <v>487.9415273208757</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1884,10 +1884,10 @@
         <v>1355</v>
       </c>
       <c r="I19" t="n">
-        <v>594.6744698202933</v>
+        <v>594.6745299041222</v>
       </c>
       <c r="J19" t="n">
-        <v>123.5004263740434</v>
+        <v>123.5004037923442</v>
       </c>
       <c r="K19" t="n">
         <v>1.948688954165734</v>
@@ -3255,16 +3255,16 @@
         <v>1517.800048828125</v>
       </c>
       <c r="D37" t="n">
-        <v>1315.662570800781</v>
+        <v>1315.662573242188</v>
       </c>
       <c r="E37" t="n">
-        <v>1163.400302734375</v>
+        <v>1163.400297851563</v>
       </c>
       <c r="F37" t="n">
-        <v>1056.642501831055</v>
+        <v>1056.642496032715</v>
       </c>
       <c r="G37" t="n">
-        <v>7.875394242015066</v>
+        <v>7.875394490294063</v>
       </c>
       <c r="H37" t="n">
         <v>1568.943822130586</v>
@@ -3335,13 +3335,13 @@
         <v>11362.7619140625</v>
       </c>
       <c r="E38" t="n">
-        <v>10778.56091145833</v>
+        <v>10778.5609375</v>
       </c>
       <c r="F38" t="n">
-        <v>10355.55625</v>
+        <v>10355.55629150391</v>
       </c>
       <c r="G38" t="n">
-        <v>3.013047654582901</v>
+        <v>3.013047842286398</v>
       </c>
       <c r="H38" t="n">
         <v>13287</v>
@@ -4028,13 +4028,13 @@
         <v>251.629248046875</v>
       </c>
       <c r="E47" t="n">
-        <v>234.8898665364583</v>
+        <v>234.8898664347331</v>
       </c>
       <c r="F47" t="n">
-        <v>223.4752031707764</v>
+        <v>223.4752029418945</v>
       </c>
       <c r="G47" t="n">
-        <v>4.1255537495831</v>
+        <v>4.125553828012385</v>
       </c>
       <c r="H47" t="n">
         <v>318.8999938964844</v>
@@ -4105,7 +4105,7 @@
         <v>336.814931640625</v>
       </c>
       <c r="E48" t="n">
-        <v>255.1579312133789</v>
+        <v>255.1579315185547</v>
       </c>
       <c r="F48" t="n">
         <v>241.5448671722412</v>
@@ -4416,10 +4416,10 @@
         <v>552.354971110026</v>
       </c>
       <c r="F52" t="n">
-        <v>531.4078535461426</v>
+        <v>531.4078544616699</v>
       </c>
       <c r="G52" t="n">
-        <v>5.452836440523057</v>
+        <v>5.452836398685723</v>
       </c>
       <c r="H52" t="n">
         <v>795.731978165477</v>
@@ -5796,16 +5796,16 @@
         <v>217.9900054931641</v>
       </c>
       <c r="D70" t="n">
-        <v>187.9840307617187</v>
+        <v>187.9840310668945</v>
       </c>
       <c r="E70" t="n">
-        <v>153.5468329874674</v>
+        <v>153.5468323262533</v>
       </c>
       <c r="F70" t="n">
-        <v>153.119895324707</v>
+        <v>153.1198942184448</v>
       </c>
       <c r="G70" t="n">
-        <v>2.668826811594216</v>
+        <v>2.6688269364332</v>
       </c>
       <c r="H70" t="n">
         <v>225.4841360491864</v>
@@ -6033,10 +6033,10 @@
         <v>78.31236877441407</v>
       </c>
       <c r="F73" t="n">
-        <v>74.16252910614014</v>
+        <v>74.16252918243408</v>
       </c>
       <c r="G73" t="n">
-        <v>4.158175448955626</v>
+        <v>4.158175556107269</v>
       </c>
       <c r="H73" t="n">
         <v>94.5</v>
@@ -7958,10 +7958,10 @@
         <v>1636.658461914062</v>
       </c>
       <c r="F98" t="n">
-        <v>1580.823547363281</v>
+        <v>1580.82354675293</v>
       </c>
       <c r="G98" t="n">
-        <v>2.789866432517041</v>
+        <v>2.789866433624244</v>
       </c>
       <c r="H98" t="n">
         <v>2038.599975585938</v>
@@ -8035,10 +8035,10 @@
         <v>4583.438225911458</v>
       </c>
       <c r="F99" t="n">
-        <v>4419.633129882813</v>
+        <v>4419.633125</v>
       </c>
       <c r="G99" t="n">
-        <v>3.104796606312177</v>
+        <v>3.104796668572307</v>
       </c>
       <c r="H99" t="n">
         <v>5250</v>
@@ -8494,13 +8494,13 @@
         <v>1042.462784423828</v>
       </c>
       <c r="E105" t="n">
-        <v>939.986836344401</v>
+        <v>939.9868379720052</v>
       </c>
       <c r="F105" t="n">
-        <v>913.1076919555665</v>
+        <v>913.1076937866211</v>
       </c>
       <c r="G105" t="n">
-        <v>3.20776389060371</v>
+        <v>3.207763848364609</v>
       </c>
       <c r="H105" t="n">
         <v>1148</v>
@@ -10724,16 +10724,16 @@
         <v>209.6199951171875</v>
       </c>
       <c r="D134" t="n">
-        <v>183.576549987793</v>
+        <v>183.5765505981445</v>
       </c>
       <c r="E134" t="n">
-        <v>153.96806543986</v>
+        <v>153.9680655415853</v>
       </c>
       <c r="F134" t="n">
-        <v>154.0113036727905</v>
+        <v>154.0113033676147</v>
       </c>
       <c r="G134" t="n">
-        <v>2.074143541758322</v>
+        <v>2.074143442725163</v>
       </c>
       <c r="H134" t="n">
         <v>233.3500061035156</v>
@@ -11577,19 +11577,19 @@
         <v>1963.816569010417</v>
       </c>
       <c r="F145" t="n">
-        <v>1847.420806884766</v>
+        <v>1847.420808105469</v>
       </c>
       <c r="G145" t="n">
-        <v>3.600551699160204</v>
+        <v>3.600551590315515</v>
       </c>
       <c r="H145" t="n">
         <v>2295</v>
       </c>
       <c r="I145" t="n">
-        <v>1174.091262727543</v>
+        <v>1174.091384580817</v>
       </c>
       <c r="J145" t="n">
-        <v>71.0258873177537</v>
+        <v>71.02586956780297</v>
       </c>
       <c r="K145" t="n">
         <v>14.29282868525896</v>
@@ -12350,7 +12350,7 @@
         <v>1343.78151184082</v>
       </c>
       <c r="G155" t="n">
-        <v>2.687230843454036</v>
+        <v>2.687230891348391</v>
       </c>
       <c r="H155" t="n">
         <v>1766.733188761222</v>
@@ -12883,13 +12883,13 @@
         <v>7402.708798828125</v>
       </c>
       <c r="E162" t="n">
-        <v>6907.08025390625</v>
+        <v>6907.080244140625</v>
       </c>
       <c r="F162" t="n">
-        <v>6484.960085449219</v>
+        <v>6484.960087890625</v>
       </c>
       <c r="G162" t="n">
-        <v>4.022386929856525</v>
+        <v>4.022386928281274</v>
       </c>
       <c r="H162" t="n">
         <v>7832.294844565128</v>
@@ -12966,7 +12966,7 @@
         <v>1120.163899841309</v>
       </c>
       <c r="G163" t="n">
-        <v>3.169663067196304</v>
+        <v>3.169663096194597</v>
       </c>
       <c r="H163" t="n">
         <v>1596.696405272527</v>
@@ -15042,10 +15042,10 @@
         <v>312.2791827392578</v>
       </c>
       <c r="F190" t="n">
-        <v>308.9876016235352</v>
+        <v>308.9876019287109</v>
       </c>
       <c r="G190" t="n">
-        <v>1.890258760852448</v>
+        <v>1.890258553879165</v>
       </c>
       <c r="H190" t="n">
         <v>380.4567148307952</v>
@@ -15501,13 +15501,13 @@
         <v>1830.872600097656</v>
       </c>
       <c r="E196" t="n">
-        <v>1706.914968261719</v>
+        <v>1706.914969889323</v>
       </c>
       <c r="F196" t="n">
-        <v>1680.250371704102</v>
+        <v>1680.25037109375</v>
       </c>
       <c r="G196" t="n">
-        <v>0.9512679425001114</v>
+        <v>0.9512679428489657</v>
       </c>
       <c r="H196" t="n">
         <v>1983.954544928268</v>
@@ -16274,19 +16274,19 @@
         <v>403.5423270670573</v>
       </c>
       <c r="F206" t="n">
-        <v>399.2017225646973</v>
+        <v>399.2017221069336</v>
       </c>
       <c r="G206" t="n">
-        <v>0.8505165239276025</v>
+        <v>0.8505165249111712</v>
       </c>
       <c r="H206" t="n">
         <v>489.5369231157038</v>
       </c>
       <c r="I206" t="n">
-        <v>331.4688402352409</v>
+        <v>331.4688100886702</v>
       </c>
       <c r="J206" t="n">
-        <v>27.41771015452827</v>
+        <v>27.41772174297006</v>
       </c>
       <c r="K206" t="n">
         <v>15.90787641559095</v>
@@ -16505,10 +16505,10 @@
         <v>1897.377635904948</v>
       </c>
       <c r="F209" t="n">
-        <v>1727.471846313477</v>
+        <v>1727.471849365234</v>
       </c>
       <c r="G209" t="n">
-        <v>7.177503447946676</v>
+        <v>7.177503312598743</v>
       </c>
       <c r="H209" t="n">
         <v>2714.261178227147</v>
@@ -18045,10 +18045,10 @@
         <v>619.35134765625</v>
       </c>
       <c r="F229" t="n">
-        <v>608.8622232055664</v>
+        <v>608.8622229003906</v>
       </c>
       <c r="G229" t="n">
-        <v>1.892793411973659</v>
+        <v>1.892793360902645</v>
       </c>
       <c r="H229" t="n">
         <v>769</v>
@@ -18738,10 +18738,10 @@
         <v>465.1862990315755</v>
       </c>
       <c r="F238" t="n">
-        <v>458.1383076477051</v>
+        <v>458.1383093261718</v>
       </c>
       <c r="G238" t="n">
-        <v>1.732828184058377</v>
+        <v>1.732828177599854</v>
       </c>
       <c r="H238" t="n">
         <v>529.9163379046904</v>
@@ -18966,13 +18966,13 @@
         <v>417.6021545410156</v>
       </c>
       <c r="E241" t="n">
-        <v>393.4513153076172</v>
+        <v>393.4513149007162</v>
       </c>
       <c r="F241" t="n">
-        <v>380.6291372680664</v>
+        <v>380.6291371154785</v>
       </c>
       <c r="G241" t="n">
-        <v>2.610149220204705</v>
+        <v>2.610149263486772</v>
       </c>
       <c r="H241" t="n">
         <v>480.9477017568404</v>
@@ -19431,10 +19431,10 @@
         <v>4419.141232096355</v>
       </c>
       <c r="F247" t="n">
-        <v>4390.190841064453</v>
+        <v>4390.1908203125</v>
       </c>
       <c r="G247" t="n">
-        <v>0.8015411925040183</v>
+        <v>0.8015413658398085</v>
       </c>
       <c r="H247" t="n">
         <v>5149.89990234375</v>
@@ -19739,10 +19739,10 @@
         <v>1015.657439371745</v>
       </c>
       <c r="F251" t="n">
-        <v>989.2291986083984</v>
+        <v>989.2291995239258</v>
       </c>
       <c r="G251" t="n">
-        <v>0.9104186761260014</v>
+        <v>0.9104186124474722</v>
       </c>
       <c r="H251" t="n">
         <v>1331.075409591023</v>
@@ -20124,10 +20124,10 @@
         <v>165.6315799967448</v>
       </c>
       <c r="F256" t="n">
-        <v>164.8116390991211</v>
+        <v>164.8116391754151</v>
       </c>
       <c r="G256" t="n">
-        <v>0.05554015265665235</v>
+        <v>0.05554015263093959</v>
       </c>
       <c r="H256" t="n">
         <v>181.8519567776652</v>
@@ -20740,19 +20740,19 @@
         <v>36710.01061197917</v>
       </c>
       <c r="F264" t="n">
-        <v>36129.2791796875</v>
+        <v>36129.27909179687</v>
       </c>
       <c r="G264" t="n">
-        <v>-0.6884367245523215</v>
+        <v>-0.6884368328507029</v>
       </c>
       <c r="H264" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I264" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J264" t="n">
-        <v>27.67027358065361</v>
+        <v>27.67028191570116</v>
       </c>
       <c r="K264" t="n">
         <v>15.70289311823834</v>
@@ -20968,13 +20968,13 @@
         <v>296.8419989013672</v>
       </c>
       <c r="E267" t="n">
-        <v>298.1120263671875</v>
+        <v>298.112026570638</v>
       </c>
       <c r="F267" t="n">
-        <v>286.1809648895264</v>
+        <v>286.1809655761719</v>
       </c>
       <c r="G267" t="n">
-        <v>1.156281069743104</v>
+        <v>1.15628101237788</v>
       </c>
       <c r="H267" t="n">
         <v>359.3387168134344</v>
@@ -23047,22 +23047,22 @@
         <v>369.4698675537109</v>
       </c>
       <c r="E294" t="n">
-        <v>380.7758846028646</v>
+        <v>380.7758850097656</v>
       </c>
       <c r="F294" t="n">
-        <v>369.2434732055664</v>
+        <v>369.2434729003906</v>
       </c>
       <c r="G294" t="n">
-        <v>3.392584828494005</v>
+        <v>3.392584919744968</v>
       </c>
       <c r="H294" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I294" t="n">
-        <v>191.8556220656042</v>
+        <v>191.8556371798532</v>
       </c>
       <c r="J294" t="n">
-        <v>86.96351368028994</v>
+        <v>86.96349895143886</v>
       </c>
       <c r="K294" t="n">
         <v>23.60554547099019</v>
@@ -23361,7 +23361,7 @@
         <v>269.420802078247</v>
       </c>
       <c r="G298" t="n">
-        <v>1.948641760783865</v>
+        <v>1.948641819648156</v>
       </c>
       <c r="H298" t="n">
         <v>367.499792159746</v>
@@ -23589,19 +23589,19 @@
         <v>732.549550374349</v>
       </c>
       <c r="F301" t="n">
-        <v>684.4648229980469</v>
+        <v>684.4648233032226</v>
       </c>
       <c r="G301" t="n">
-        <v>3.094635431972681</v>
+        <v>3.094635312079452</v>
       </c>
       <c r="H301" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I301" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J301" t="n">
-        <v>40.8449062429763</v>
+        <v>40.84492277737157</v>
       </c>
       <c r="K301" t="n">
         <v>58.03731066118163</v>
@@ -23666,10 +23666,10 @@
         <v>5220.916038411458</v>
       </c>
       <c r="F302" t="n">
-        <v>4977.822918701172</v>
+        <v>4977.822921142578</v>
       </c>
       <c r="G302" t="n">
-        <v>1.576751642924168</v>
+        <v>1.5767515409296</v>
       </c>
       <c r="H302" t="n">
         <v>6049.821052103703</v>
@@ -24051,10 +24051,10 @@
         <v>1365.088555501302</v>
       </c>
       <c r="F307" t="n">
-        <v>1365.882327880859</v>
+        <v>1365.882330322266</v>
       </c>
       <c r="G307" t="n">
-        <v>0.1253248390786332</v>
+        <v>0.1253248836519338</v>
       </c>
       <c r="H307" t="n">
         <v>1563.400024414062</v>
@@ -24122,19 +24122,19 @@
         <v>426.1000061035156</v>
       </c>
       <c r="D308" t="n">
-        <v>411.2546649169922</v>
+        <v>411.2546661376953</v>
       </c>
       <c r="E308" t="n">
-        <v>429.760185546875</v>
+        <v>429.7601845296224</v>
       </c>
       <c r="F308" t="n">
-        <v>422.5457287597656</v>
+        <v>422.5457289123535</v>
       </c>
       <c r="G308" t="n">
-        <v>1.357816897008246</v>
+        <v>1.357816896511288</v>
       </c>
       <c r="H308" t="n">
-        <v>478.7148709533388</v>
+        <v>478.7148398145708</v>
       </c>
       <c r="I308" t="n">
         <v>355.1755291130353</v>
@@ -24143,7 +24143,7 @@
         <v>19.96885234959656</v>
       </c>
       <c r="K308" t="n">
-        <v>12.34800847128856</v>
+        <v>12.34800116343417</v>
       </c>
       <c r="L308" t="n">
         <v>60.47156726768377</v>
@@ -24439,7 +24439,7 @@
         <v>1142.093260498047</v>
       </c>
       <c r="G312" t="n">
-        <v>-0.5104879743871527</v>
+        <v>-0.510488027284417</v>
       </c>
       <c r="H312" t="n">
         <v>1409.944064008135</v>
@@ -24510,16 +24510,16 @@
         <v>4542.822724609375</v>
       </c>
       <c r="E313" t="n">
-        <v>4236.807755533854</v>
+        <v>4236.80775390625</v>
       </c>
       <c r="F313" t="n">
-        <v>4302.876119384766</v>
+        <v>4302.876108398437</v>
       </c>
       <c r="G313" t="n">
-        <v>0.4646388354858422</v>
+        <v>0.4646390657473853</v>
       </c>
       <c r="H313" t="n">
-        <v>5005.771680286142</v>
+        <v>5005.771184298104</v>
       </c>
       <c r="I313" t="n">
         <v>3669.905008549105</v>
@@ -24528,7 +24528,7 @@
         <v>23.16395082353859</v>
       </c>
       <c r="K313" t="n">
-        <v>10.74716106827749</v>
+        <v>10.7471500950908</v>
       </c>
       <c r="L313" t="n">
         <v>58.52981969486824</v>
@@ -25745,10 +25745,10 @@
         <v>729.4431587727864</v>
       </c>
       <c r="F329" t="n">
-        <v>744.8626977539062</v>
+        <v>744.862698059082</v>
       </c>
       <c r="G329" t="n">
-        <v>-0.1937057804728748</v>
+        <v>-0.1937057803936493</v>
       </c>
       <c r="H329" t="n">
         <v>879.2203373423794</v>
@@ -26130,10 +26130,10 @@
         <v>410.6007462565104</v>
       </c>
       <c r="F334" t="n">
-        <v>415.7466404724121</v>
+        <v>415.7466415405273</v>
       </c>
       <c r="G334" t="n">
-        <v>-1.775933366042881</v>
+        <v>-1.775933396971374</v>
       </c>
       <c r="H334" t="n">
         <v>684.5682054144123</v>
@@ -28209,10 +28209,10 @@
         <v>1145.369587809245</v>
       </c>
       <c r="F361" t="n">
-        <v>1164.90121673584</v>
+        <v>1164.901219177246</v>
       </c>
       <c r="G361" t="n">
-        <v>-0.4903317452870315</v>
+        <v>-0.4903318480295904</v>
       </c>
       <c r="H361" t="n">
         <v>1378.852549646065</v>
@@ -29524,7 +29524,7 @@
         <v>0.04507901910639767</v>
       </c>
       <c r="H378" t="n">
-        <v>4340.557634646074</v>
+        <v>4340.558135822838</v>
       </c>
       <c r="I378" t="n">
         <v>3140</v>
@@ -29533,7 +29533,7 @@
         <v>13.05732484076434</v>
       </c>
       <c r="K378" t="n">
-        <v>22.26922914495983</v>
+        <v>22.26924326261517</v>
       </c>
       <c r="L378" t="n">
         <v>43.41192787794729</v>
@@ -30140,7 +30140,7 @@
         <v>-1.857723905058561</v>
       </c>
       <c r="H386" t="n">
-        <v>623.6463522815318</v>
+        <v>623.6462906209067</v>
       </c>
       <c r="I386" t="n">
         <v>351.0001816860465</v>
@@ -30149,7 +30149,7 @@
         <v>30.55548797689327</v>
       </c>
       <c r="K386" t="n">
-        <v>36.0930392321946</v>
+        <v>36.09302577652083</v>
       </c>
       <c r="L386" t="n">
         <v>32.73231622746186</v>
@@ -30211,19 +30211,19 @@
         <v>522.3315828450521</v>
       </c>
       <c r="F387" t="n">
-        <v>524.438603515625</v>
+        <v>524.4386027526856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.792389180053135</v>
+        <v>3.792389154435294</v>
       </c>
       <c r="H387" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I387" t="n">
-        <v>306.8420198526935</v>
+        <v>306.8419898026673</v>
       </c>
       <c r="J387" t="n">
-        <v>61.20673242013996</v>
+        <v>61.20674820763548</v>
       </c>
       <c r="K387" t="n">
         <v>52.82830673988417</v>
@@ -31517,13 +31517,13 @@
         <v>753.4573889160156</v>
       </c>
       <c r="E404" t="n">
-        <v>740.7510091145833</v>
+        <v>740.7510111490885</v>
       </c>
       <c r="F404" t="n">
-        <v>736.3989724731446</v>
+        <v>736.3989730834961</v>
       </c>
       <c r="G404" t="n">
-        <v>-0.6180672380425078</v>
+        <v>-0.6180670738096139</v>
       </c>
       <c r="H404" t="n">
         <v>837.8765073351432</v>
@@ -32136,10 +32136,10 @@
         <v>273.0273685709635</v>
       </c>
       <c r="F412" t="n">
-        <v>285.6348243713379</v>
+        <v>285.6348263549805</v>
       </c>
       <c r="G412" t="n">
-        <v>-2.815854859949796</v>
+        <v>-2.815854992308675</v>
       </c>
       <c r="H412" t="n">
         <v>390.5481555478003</v>
@@ -32364,13 +32364,13 @@
         <v>13160.73662109375</v>
       </c>
       <c r="E415" t="n">
-        <v>12660.236953125</v>
+        <v>12660.2369140625</v>
       </c>
       <c r="F415" t="n">
-        <v>12886.19338378906</v>
+        <v>12886.19333007813</v>
       </c>
       <c r="G415" t="n">
-        <v>-0.8565375528908348</v>
+        <v>-0.8565373329575077</v>
       </c>
       <c r="H415" t="n">
         <v>17899.76088444639</v>
@@ -33830,10 +33830,10 @@
         <v>288.0766564941407</v>
       </c>
       <c r="F434" t="n">
-        <v>282.796591720581</v>
+        <v>282.7965901184082</v>
       </c>
       <c r="G434" t="n">
-        <v>-0.007907655722949603</v>
+        <v>-0.007907817612451407</v>
       </c>
       <c r="H434" t="n">
         <v>323.4425459044702</v>
@@ -34058,13 +34058,13 @@
         <v>1298.442004394531</v>
       </c>
       <c r="E437" t="n">
-        <v>1247.107093505859</v>
+        <v>1247.107100016276</v>
       </c>
       <c r="F437" t="n">
-        <v>1329.86123626709</v>
+        <v>1329.861242980957</v>
       </c>
       <c r="G437" t="n">
-        <v>-2.424624019788224</v>
+        <v>-2.424624226330485</v>
       </c>
       <c r="H437" t="n">
         <v>1729.008500794829</v>
@@ -34982,16 +34982,16 @@
         <v>503.3993206787109</v>
       </c>
       <c r="E449" t="n">
-        <v>485.9179461669922</v>
+        <v>485.9179475911458</v>
       </c>
       <c r="F449" t="n">
-        <v>490.7460363769531</v>
+        <v>490.7460380554199</v>
       </c>
       <c r="G449" t="n">
-        <v>-0.2802011452444519</v>
+        <v>-0.2802009587745014</v>
       </c>
       <c r="H449" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I449" t="n">
         <v>419.3328127807616</v>
@@ -35000,7 +35000,7 @@
         <v>10.05578050036464</v>
       </c>
       <c r="K449" t="n">
-        <v>18.68645119491654</v>
+        <v>18.68646459837418</v>
       </c>
       <c r="L449" t="n">
         <v>36.89320388349515</v>
@@ -36756,10 +36756,10 @@
         <v>383.7009169514974</v>
       </c>
       <c r="F472" t="n">
-        <v>394.6485162353516</v>
+        <v>394.6485163879395</v>
       </c>
       <c r="G472" t="n">
-        <v>-3.722195485713897</v>
+        <v>-3.722195627686309</v>
       </c>
       <c r="H472" t="n">
         <v>541.0236304500187</v>
@@ -37603,10 +37603,10 @@
         <v>1425.876956380208</v>
       </c>
       <c r="F483" t="n">
-        <v>1405.134996948242</v>
+        <v>1405.134995727539</v>
       </c>
       <c r="G483" t="n">
-        <v>-0.1188786183668133</v>
+        <v>-0.1188785318019359</v>
       </c>
       <c r="H483" t="n">
         <v>1817.803954384172</v>
@@ -37754,22 +37754,22 @@
         <v>2276.71484375</v>
       </c>
       <c r="E485" t="n">
-        <v>2226.592064615885</v>
+        <v>2226.59209391276</v>
       </c>
       <c r="F485" t="n">
-        <v>2276.099962768555</v>
+        <v>2276.099978637695</v>
       </c>
       <c r="G485" t="n">
-        <v>-0.4275940726060412</v>
+        <v>-0.4275940696375713</v>
       </c>
       <c r="H485" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I485" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J485" t="n">
-        <v>11.31485210721246</v>
+        <v>11.31484519965893</v>
       </c>
       <c r="K485" t="n">
         <v>26.54461366267797</v>
@@ -38370,13 +38370,13 @@
         <v>477.9314776611328</v>
       </c>
       <c r="E493" t="n">
-        <v>526.2697353108724</v>
+        <v>526.2697357177734</v>
       </c>
       <c r="F493" t="n">
-        <v>533.5989018249512</v>
+        <v>533.598900604248</v>
       </c>
       <c r="G493" t="n">
-        <v>-1.506682371604862</v>
+        <v>-1.506682319518182</v>
       </c>
       <c r="H493" t="n">
         <v>653.9340000086492</v>
@@ -38447,22 +38447,22 @@
         <v>430.9691821289063</v>
       </c>
       <c r="E494" t="n">
-        <v>462.6965881347656</v>
+        <v>462.6965887451172</v>
       </c>
       <c r="F494" t="n">
-        <v>465.5620889282226</v>
+        <v>465.5620881652832</v>
       </c>
       <c r="G494" t="n">
-        <v>-1.128613395708888</v>
+        <v>-1.128613493655573</v>
       </c>
       <c r="H494" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I494" t="n">
-        <v>379.7399002549519</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J494" t="n">
-        <v>14.49942118303877</v>
+        <v>14.4994303558285</v>
       </c>
       <c r="K494" t="n">
         <v>27.68727324110241</v>
@@ -38681,19 +38681,19 @@
         <v>965.6785986328125</v>
       </c>
       <c r="F497" t="n">
-        <v>942.4370458984375</v>
+        <v>942.4370437622071</v>
       </c>
       <c r="G497" t="n">
-        <v>-0.415860685245284</v>
+        <v>-0.4158606219584193</v>
       </c>
       <c r="H497" t="n">
         <v>1224.72508309492</v>
       </c>
       <c r="I497" t="n">
-        <v>784.9091438882253</v>
+        <v>784.9092044208618</v>
       </c>
       <c r="J497" t="n">
-        <v>6.92957195469861</v>
+        <v>6.929563708230257</v>
       </c>
       <c r="K497" t="n">
         <v>45.92220909182525</v>
@@ -39140,25 +39140,25 @@
         <v>231.160930480957</v>
       </c>
       <c r="E503" t="n">
-        <v>224.4955264282227</v>
+        <v>224.4955261230469</v>
       </c>
       <c r="F503" t="n">
         <v>225.6140672302246</v>
       </c>
       <c r="G503" t="n">
-        <v>-1.364058483461705</v>
+        <v>-1.364058450561834</v>
       </c>
       <c r="H503" t="n">
-        <v>286.0804516993438</v>
+        <v>286.0804190389319</v>
       </c>
       <c r="I503" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J503" t="n">
-        <v>20.0212985319485</v>
+        <v>20.02128795617528</v>
       </c>
       <c r="K503" t="n">
-        <v>38.61829873576517</v>
+        <v>38.61828291038911</v>
       </c>
       <c r="L503" t="n">
         <v>34.81276005547851</v>
@@ -40295,13 +40295,13 @@
         <v>333.9067395019531</v>
       </c>
       <c r="E518" t="n">
-        <v>339.3453326416015</v>
+        <v>339.3453332519532</v>
       </c>
       <c r="F518" t="n">
-        <v>341.6456814575195</v>
+        <v>341.6456816101074</v>
       </c>
       <c r="G518" t="n">
-        <v>-0.9186447237045425</v>
+        <v>-0.9186448109896217</v>
       </c>
       <c r="H518" t="n">
         <v>381.3442016302781</v>
@@ -40609,7 +40609,7 @@
         <v>33.80074458122253</v>
       </c>
       <c r="G522" t="n">
-        <v>-1.987492002497948</v>
+        <v>-1.987491731455793</v>
       </c>
       <c r="H522" t="n">
         <v>40.26070662850351</v>
@@ -40683,10 +40683,10 @@
         <v>2579.294115397136</v>
       </c>
       <c r="F523" t="n">
-        <v>2540.314905395508</v>
+        <v>2540.314901733399</v>
       </c>
       <c r="G523" t="n">
-        <v>-1.029157270355119</v>
+        <v>-1.029157318892693</v>
       </c>
       <c r="H523" t="n">
         <v>3329.438873827357</v>
@@ -40763,10 +40763,10 @@
         <v>237.1050746917725</v>
       </c>
       <c r="G524" t="n">
-        <v>-2.104239101454708</v>
+        <v>-2.104239039780009</v>
       </c>
       <c r="H524" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I524" t="n">
         <v>185.2067002350832</v>
@@ -40775,7 +40775,7 @@
         <v>22.80873027786765</v>
       </c>
       <c r="K524" t="n">
-        <v>35.44720015394032</v>
+        <v>35.44721421268164</v>
       </c>
       <c r="L524" t="n">
         <v>28.84882108183079</v>
@@ -41222,10 +41222,10 @@
         <v>207.7894618733724</v>
       </c>
       <c r="F530" t="n">
-        <v>211.6584396362305</v>
+        <v>211.6584394836426</v>
       </c>
       <c r="G530" t="n">
-        <v>-1.249598748224068</v>
+        <v>-1.249598678812536</v>
       </c>
       <c r="H530" t="n">
         <v>260.4933484681973</v>
@@ -41296,13 +41296,13 @@
         <v>372.3288641357422</v>
       </c>
       <c r="E531" t="n">
-        <v>403.2165763346354</v>
+        <v>403.2165761311849</v>
       </c>
       <c r="F531" t="n">
-        <v>392.7666499328614</v>
+        <v>392.7666491699219</v>
       </c>
       <c r="G531" t="n">
-        <v>-0.001111238829154537</v>
+        <v>-0.001111316528590311</v>
       </c>
       <c r="H531" t="n">
         <v>476.8288845013619</v>
@@ -41684,13 +41684,13 @@
         <v>420.6172432454427</v>
       </c>
       <c r="F536" t="n">
-        <v>439.5798028564453</v>
+        <v>439.5798016357422</v>
       </c>
       <c r="G536" t="n">
-        <v>-2.352065229427469</v>
+        <v>-2.352065268903991</v>
       </c>
       <c r="H536" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I536" t="n">
         <v>363.2227809620478</v>
@@ -41699,7 +41699,7 @@
         <v>10.15278420692478</v>
       </c>
       <c r="K536" t="n">
-        <v>33.39383818072825</v>
+        <v>33.39385407684132</v>
       </c>
       <c r="L536" t="n">
         <v>24.5492371705964</v>
@@ -41838,13 +41838,13 @@
         <v>1637.291165364583</v>
       </c>
       <c r="F538" t="n">
-        <v>1732.310134277344</v>
+        <v>1732.310129394531</v>
       </c>
       <c r="G538" t="n">
-        <v>-3.285316892205126</v>
+        <v>-3.285316967073848</v>
       </c>
       <c r="H538" t="n">
-        <v>2339.801318384509</v>
+        <v>2339.80156593166</v>
       </c>
       <c r="I538" t="n">
         <v>1322.972836511248</v>
@@ -41853,7 +41853,7 @@
         <v>19.63964830918645</v>
       </c>
       <c r="K538" t="n">
-        <v>47.82671507477227</v>
+        <v>47.82673071459686</v>
       </c>
       <c r="L538" t="n">
         <v>23.43966712898752</v>
@@ -41992,10 +41992,10 @@
         <v>2841.105600585937</v>
       </c>
       <c r="F540" t="n">
-        <v>2748.9483984375</v>
+        <v>2748.948394775391</v>
       </c>
       <c r="G540" t="n">
-        <v>-0.8269079085746922</v>
+        <v>-0.8269079533420154</v>
       </c>
       <c r="H540" t="n">
         <v>3333.383184200957</v>
@@ -43144,13 +43144,13 @@
         <v>353.3964935302735</v>
       </c>
       <c r="E555" t="n">
-        <v>416.9898105875651</v>
+        <v>416.9898107910156</v>
       </c>
       <c r="F555" t="n">
-        <v>444.7202911376953</v>
+        <v>444.7202917480469</v>
       </c>
       <c r="G555" t="n">
-        <v>-4.775306596276685</v>
+        <v>-4.775306590035832</v>
       </c>
       <c r="H555" t="n">
         <v>605.9581737112406</v>
@@ -43846,7 +43846,7 @@
         <v>-4.171935485004951</v>
       </c>
       <c r="H564" t="n">
-        <v>546.5890454582147</v>
+        <v>546.5889842244101</v>
       </c>
       <c r="I564" t="n">
         <v>308.2000122070312</v>
@@ -43855,7 +43855,7 @@
         <v>0.7462646664088135</v>
       </c>
       <c r="K564" t="n">
-        <v>76.0351193102141</v>
+        <v>76.03509958918198</v>
       </c>
       <c r="L564" t="n">
         <v>4.438280166435506</v>
@@ -44382,16 +44382,16 @@
         <v>853.7973858642578</v>
       </c>
       <c r="G571" t="n">
-        <v>-1.198834128113246</v>
+        <v>-1.198834058330289</v>
       </c>
       <c r="H571" t="n">
         <v>962.6932158005569</v>
       </c>
       <c r="I571" t="n">
-        <v>726.0614279588375</v>
+        <v>726.0613673587077</v>
       </c>
       <c r="J571" t="n">
-        <v>3.744665532997282</v>
+        <v>3.744674191962605</v>
       </c>
       <c r="K571" t="n">
         <v>27.80527259217482</v>
@@ -45226,10 +45226,10 @@
         <v>915.8419104003906</v>
       </c>
       <c r="F582" t="n">
-        <v>921.7419055175782</v>
+        <v>921.7419030761719</v>
       </c>
       <c r="G582" t="n">
-        <v>-0.486673300168261</v>
+        <v>-0.4866732686639286</v>
       </c>
       <c r="H582" t="n">
         <v>1282.80960014975</v>
@@ -45303,10 +45303,10 @@
         <v>3005.409427083333</v>
       </c>
       <c r="F583" t="n">
-        <v>3153.555186767578</v>
+        <v>3153.55519165039</v>
       </c>
       <c r="G583" t="n">
-        <v>-2.397144508807714</v>
+        <v>-2.397144542060292</v>
       </c>
       <c r="H583" t="n">
         <v>3923.39201752828</v>
@@ -45380,13 +45380,13 @@
         <v>122.7193290201823</v>
       </c>
       <c r="F584" t="n">
-        <v>124.648683052063</v>
+        <v>124.6486833190918</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.867549517178491</v>
+        <v>-1.867549866906715</v>
       </c>
       <c r="H584" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I584" t="n">
         <v>110.3499984741211</v>
@@ -45395,7 +45395,7 @@
         <v>2.1295863222619</v>
       </c>
       <c r="K584" t="n">
-        <v>38.33182335537655</v>
+        <v>38.33183903869131</v>
       </c>
       <c r="L584" t="n">
         <v>25.65880721220527</v>
@@ -45765,13 +45765,13 @@
         <v>130957.3200520833</v>
       </c>
       <c r="F589" t="n">
-        <v>134792.0390625</v>
+        <v>134792.03921875</v>
       </c>
       <c r="G589" t="n">
-        <v>-2.10046899733991</v>
+        <v>-2.100468994956195</v>
       </c>
       <c r="H589" t="n">
-        <v>163308.5022863474</v>
+        <v>163308.4863287346</v>
       </c>
       <c r="I589" t="n">
         <v>121787.4350540836</v>
@@ -45780,7 +45780,7 @@
         <v>1.845481797788318</v>
       </c>
       <c r="K589" t="n">
-        <v>31.6632420577639</v>
+        <v>31.66322919235265</v>
       </c>
       <c r="L589" t="n">
         <v>24.6879334257975</v>
@@ -46837,28 +46837,28 @@
         <v>173.9900054931641</v>
       </c>
       <c r="D603" t="n">
-        <v>185.74625</v>
+        <v>185.7462503051758</v>
       </c>
       <c r="E603" t="n">
-        <v>192.3783170572917</v>
+        <v>192.3783165486654</v>
       </c>
       <c r="F603" t="n">
-        <v>195.0438658905029</v>
+        <v>195.0438655853272</v>
       </c>
       <c r="G603" t="n">
-        <v>-2.607567885584916</v>
+        <v>-2.607567704043812</v>
       </c>
       <c r="H603" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I603" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J603" t="n">
-        <v>11.00243634646796</v>
+        <v>11.00244711309058</v>
       </c>
       <c r="K603" t="n">
-        <v>37.48990217069517</v>
+        <v>37.48989329579029</v>
       </c>
       <c r="L603" t="n">
         <v>21.22052704576976</v>
@@ -46997,10 +46997,10 @@
         <v>1062.479805094401</v>
       </c>
       <c r="F605" t="n">
-        <v>1090.782477111816</v>
+        <v>1090.782477722168</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.06378075074406</v>
+        <v>-2.063780749613098</v>
       </c>
       <c r="H605" t="n">
         <v>1395.129939548488</v>
@@ -47074,13 +47074,13 @@
         <v>7688.377086588542</v>
       </c>
       <c r="F606" t="n">
-        <v>7787.453747558594</v>
+        <v>7787.453745117187</v>
       </c>
       <c r="G606" t="n">
-        <v>-1.271150708042368</v>
+        <v>-1.271150800111465</v>
       </c>
       <c r="H606" t="n">
-        <v>9653.121370296873</v>
+        <v>9653.120359649309</v>
       </c>
       <c r="I606" t="n">
         <v>6922</v>
@@ -47089,7 +47089,7 @@
         <v>2.167003756139851</v>
       </c>
       <c r="K606" t="n">
-        <v>36.49775693293089</v>
+        <v>36.49774264209995</v>
       </c>
       <c r="L606" t="n">
         <v>20.80443828016643</v>
@@ -47690,10 +47690,10 @@
         <v>1471.633913574219</v>
       </c>
       <c r="F614" t="n">
-        <v>1491.384323120117</v>
+        <v>1491.384322509766</v>
       </c>
       <c r="G614" t="n">
-        <v>-1.711429878099002</v>
+        <v>-1.71142991832377</v>
       </c>
       <c r="H614" t="n">
         <v>1965.628830677411</v>
@@ -48999,13 +48999,13 @@
         <v>1225.736416829427</v>
       </c>
       <c r="F631" t="n">
-        <v>1265.743474731445</v>
+        <v>1265.743472900391</v>
       </c>
       <c r="G631" t="n">
-        <v>-2.42287016611975</v>
+        <v>-2.422870215452266</v>
       </c>
       <c r="H631" t="n">
-        <v>1546.339069162078</v>
+        <v>1546.338945569448</v>
       </c>
       <c r="I631" t="n">
         <v>1081.099975585938</v>
@@ -49014,7 +49014,7 @@
         <v>1.424477362115928</v>
       </c>
       <c r="K631" t="n">
-        <v>41.02499490762222</v>
+        <v>41.02498363606457</v>
       </c>
       <c r="L631" t="n">
         <v>15.67267683772538</v>
@@ -49076,10 +49076,10 @@
         <v>2303.345173339844</v>
       </c>
       <c r="F632" t="n">
-        <v>2484.52655456543</v>
+        <v>2484.52655090332</v>
       </c>
       <c r="G632" t="n">
-        <v>-3.469682810280728</v>
+        <v>-3.469682677871755</v>
       </c>
       <c r="H632" t="n">
         <v>3287.161392369851</v>
@@ -49156,7 +49156,7 @@
         <v>435.1267344665528</v>
       </c>
       <c r="G633" t="n">
-        <v>-3.404032870511231</v>
+        <v>-3.404032935952583</v>
       </c>
       <c r="H633" t="n">
         <v>570.5579909394708</v>
@@ -49230,13 +49230,13 @@
         <v>122.5039993286133</v>
       </c>
       <c r="F634" t="n">
-        <v>125.5922718429565</v>
+        <v>125.5922719192505</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.548601573448783</v>
+        <v>-2.548601341178558</v>
       </c>
       <c r="H634" t="n">
-        <v>154.1041584954392</v>
+        <v>154.1041427094461</v>
       </c>
       <c r="I634" t="n">
         <v>104.7068431385872</v>
@@ -49245,7 +49245,7 @@
         <v>3.699050201848864</v>
       </c>
       <c r="K634" t="n">
-        <v>41.92683357587146</v>
+        <v>41.92681903728905</v>
       </c>
       <c r="L634" t="n">
         <v>15.11789181692094</v>
@@ -49920,13 +49920,13 @@
         <v>88.66075836181641</v>
       </c>
       <c r="E643" t="n">
-        <v>92.53722951253255</v>
+        <v>92.53722946166992</v>
       </c>
       <c r="F643" t="n">
-        <v>95.87017982482911</v>
+        <v>95.87017971038819</v>
       </c>
       <c r="G643" t="n">
-        <v>-3.180090785209799</v>
+        <v>-3.180090826184923</v>
       </c>
       <c r="H643" t="n">
         <v>124.8273096544699</v>
@@ -50382,16 +50382,16 @@
         <v>950.7499414062499</v>
       </c>
       <c r="E649" t="n">
-        <v>1017.459152018229</v>
+        <v>1017.459155273438</v>
       </c>
       <c r="F649" t="n">
-        <v>1060.007169189453</v>
+        <v>1060.007171020508</v>
       </c>
       <c r="G649" t="n">
-        <v>-2.420704723956724</v>
+        <v>-2.420704610224411</v>
       </c>
       <c r="H649" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I649" t="n">
         <v>855.1500244140625</v>
@@ -50400,7 +50400,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K649" t="n">
-        <v>42.63389867229614</v>
+        <v>42.63391283520865</v>
       </c>
       <c r="L649" t="n">
         <v>12.48266296809986</v>
@@ -51158,7 +51158,7 @@
         <v>1694.180337524414</v>
       </c>
       <c r="G659" t="n">
-        <v>-4.901237497497723</v>
+        <v>-4.901237464916298</v>
       </c>
       <c r="H659" t="n">
         <v>2504.019782423858</v>
@@ -51232,13 +51232,13 @@
         <v>296.3036335245768</v>
       </c>
       <c r="F660" t="n">
-        <v>307.5067198944092</v>
+        <v>307.5067194366455</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.547029739389561</v>
+        <v>-2.547029931586431</v>
       </c>
       <c r="H660" t="n">
-        <v>396.5816646357411</v>
+        <v>396.5816020628056</v>
       </c>
       <c r="I660" t="n">
         <v>243.9284560598348</v>
@@ -51247,7 +51247,7 @@
         <v>6.650121145632348</v>
       </c>
       <c r="K660" t="n">
-        <v>52.44346490107699</v>
+        <v>52.4434408484393</v>
       </c>
       <c r="L660" t="n">
         <v>10.54091539528433</v>
@@ -51386,13 +51386,13 @@
         <v>185.6980224609375</v>
       </c>
       <c r="F662" t="n">
-        <v>199.5555168914795</v>
+        <v>199.5555163574219</v>
       </c>
       <c r="G662" t="n">
-        <v>-3.697451971334176</v>
+        <v>-3.697452051777539</v>
       </c>
       <c r="H662" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I662" t="n">
         <v>161.6600036621094</v>
@@ -51401,7 +51401,7 @@
         <v>1.459854359080848</v>
       </c>
       <c r="K662" t="n">
-        <v>60.48074747578418</v>
+        <v>60.48072884043321</v>
       </c>
       <c r="L662" t="n">
         <v>10.26352288488211</v>
@@ -51617,10 +51617,10 @@
         <v>2755.432490234375</v>
       </c>
       <c r="F665" t="n">
-        <v>2862.996896972656</v>
+        <v>2862.996900634766</v>
       </c>
       <c r="G665" t="n">
-        <v>-3.925383805223126</v>
+        <v>-3.925383721688003</v>
       </c>
       <c r="H665" t="n">
         <v>3812.926349899466</v>
@@ -52310,10 +52310,10 @@
         <v>516.5421781412761</v>
       </c>
       <c r="F674" t="n">
-        <v>547.7069464111328</v>
+        <v>547.7069458007812</v>
       </c>
       <c r="G674" t="n">
-        <v>-4.113725038243999</v>
+        <v>-4.113724837724209</v>
       </c>
       <c r="H674" t="n">
         <v>725.6811213920008</v>
@@ -55698,10 +55698,10 @@
         <v>660.7392146809896</v>
       </c>
       <c r="F718" t="n">
-        <v>766.1414273071289</v>
+        <v>766.1414306640625</v>
       </c>
       <c r="G718" t="n">
-        <v>-8.512690479946738</v>
+        <v>-8.512690445822614</v>
       </c>
       <c r="H718" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1576,10 +1576,10 @@
         <v>2055.300048828125</v>
       </c>
       <c r="I15" t="n">
-        <v>821.6033975811163</v>
+        <v>821.6033372206257</v>
       </c>
       <c r="J15" t="n">
-        <v>144.2784445523</v>
+        <v>144.2784624986326</v>
       </c>
       <c r="K15" t="n">
         <v>2.406579413459142</v>
@@ -3335,13 +3335,13 @@
         <v>11362.7619140625</v>
       </c>
       <c r="E38" t="n">
-        <v>10778.5609375</v>
+        <v>10778.56091145833</v>
       </c>
       <c r="F38" t="n">
-        <v>10355.55629150391</v>
+        <v>10355.55627441406</v>
       </c>
       <c r="G38" t="n">
-        <v>3.013047842286398</v>
+        <v>3.013047697301197</v>
       </c>
       <c r="H38" t="n">
         <v>13287</v>
@@ -4034,7 +4034,7 @@
         <v>223.4752029418945</v>
       </c>
       <c r="G47" t="n">
-        <v>4.125553828012385</v>
+        <v>4.12555390204199</v>
       </c>
       <c r="H47" t="n">
         <v>318.8999938964844</v>
@@ -4105,7 +4105,7 @@
         <v>336.814931640625</v>
       </c>
       <c r="E48" t="n">
-        <v>255.1579315185547</v>
+        <v>255.1579312133789</v>
       </c>
       <c r="F48" t="n">
         <v>241.5448671722412</v>
@@ -4416,10 +4416,10 @@
         <v>552.354971110026</v>
       </c>
       <c r="F52" t="n">
-        <v>531.4078544616699</v>
+        <v>531.4078535461426</v>
       </c>
       <c r="G52" t="n">
-        <v>5.452836398685723</v>
+        <v>5.452836440523057</v>
       </c>
       <c r="H52" t="n">
         <v>795.731978165477</v>
@@ -4875,13 +4875,13 @@
         <v>160.6328002929687</v>
       </c>
       <c r="E58" t="n">
-        <v>140.758228302002</v>
+        <v>140.7582285563151</v>
       </c>
       <c r="F58" t="n">
-        <v>135.379672203064</v>
+        <v>135.37967212677</v>
       </c>
       <c r="G58" t="n">
-        <v>4.328527289543849</v>
+        <v>4.328527230748969</v>
       </c>
       <c r="H58" t="n">
         <v>173.2700042724609</v>
@@ -5722,13 +5722,13 @@
         <v>2618.773364257812</v>
       </c>
       <c r="E69" t="n">
-        <v>2196.025184733073</v>
+        <v>2196.025180664063</v>
       </c>
       <c r="F69" t="n">
         <v>2102.622564086914</v>
       </c>
       <c r="G69" t="n">
-        <v>4.344305145132821</v>
+        <v>4.344305239947932</v>
       </c>
       <c r="H69" t="n">
         <v>2990</v>
@@ -5796,16 +5796,16 @@
         <v>217.9900054931641</v>
       </c>
       <c r="D70" t="n">
-        <v>187.9840310668945</v>
+        <v>187.9840307617187</v>
       </c>
       <c r="E70" t="n">
-        <v>153.5468323262533</v>
+        <v>153.5468329874674</v>
       </c>
       <c r="F70" t="n">
-        <v>153.1198942184448</v>
+        <v>153.119895324707</v>
       </c>
       <c r="G70" t="n">
-        <v>2.6688269364332</v>
+        <v>2.668826811594216</v>
       </c>
       <c r="H70" t="n">
         <v>225.4841360491864</v>
@@ -6033,10 +6033,10 @@
         <v>78.31236877441407</v>
       </c>
       <c r="F73" t="n">
-        <v>74.16252918243408</v>
+        <v>74.16252910614014</v>
       </c>
       <c r="G73" t="n">
-        <v>4.158175556107269</v>
+        <v>4.158175448955626</v>
       </c>
       <c r="H73" t="n">
         <v>94.5</v>
@@ -8494,13 +8494,13 @@
         <v>1042.462784423828</v>
       </c>
       <c r="E105" t="n">
-        <v>939.9868379720052</v>
+        <v>939.986836344401</v>
       </c>
       <c r="F105" t="n">
-        <v>913.1076937866211</v>
+        <v>913.1076919555665</v>
       </c>
       <c r="G105" t="n">
-        <v>3.207763848364609</v>
+        <v>3.20776389060371</v>
       </c>
       <c r="H105" t="n">
         <v>1148</v>
@@ -9806,10 +9806,10 @@
         <v>8296.183313802083</v>
       </c>
       <c r="F122" t="n">
-        <v>8008.860454101563</v>
+        <v>8008.86044921875</v>
       </c>
       <c r="G122" t="n">
-        <v>2.139759091763405</v>
+        <v>2.139759124898211</v>
       </c>
       <c r="H122" t="n">
         <v>9070.5</v>
@@ -10354,10 +10354,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I129" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J129" t="n">
-        <v>115.1273113251376</v>
+        <v>115.127332746946</v>
       </c>
       <c r="K129" t="n">
         <v>18.01605787300149</v>
@@ -10724,16 +10724,16 @@
         <v>209.6199951171875</v>
       </c>
       <c r="D134" t="n">
-        <v>183.5765505981445</v>
+        <v>183.576549987793</v>
       </c>
       <c r="E134" t="n">
-        <v>153.9680655415853</v>
+        <v>153.96806543986</v>
       </c>
       <c r="F134" t="n">
-        <v>154.0113033676147</v>
+        <v>154.0113036727905</v>
       </c>
       <c r="G134" t="n">
-        <v>2.074143442725163</v>
+        <v>2.074143541758322</v>
       </c>
       <c r="H134" t="n">
         <v>233.3500061035156</v>
@@ -12347,10 +12347,10 @@
         <v>1411.251926269531</v>
       </c>
       <c r="F155" t="n">
-        <v>1343.78151184082</v>
+        <v>1343.78151550293</v>
       </c>
       <c r="G155" t="n">
-        <v>2.687230891348391</v>
+        <v>2.687231075405694</v>
       </c>
       <c r="H155" t="n">
         <v>1766.733188761222</v>
@@ -12809,10 +12809,10 @@
         <v>721.9353877766927</v>
       </c>
       <c r="F161" t="n">
-        <v>729.055185546875</v>
+        <v>729.0551843261719</v>
       </c>
       <c r="G161" t="n">
-        <v>2.19732436594926</v>
+        <v>2.19732450086576</v>
       </c>
       <c r="H161" t="n">
         <v>962</v>
@@ -12883,13 +12883,13 @@
         <v>7402.708798828125</v>
       </c>
       <c r="E162" t="n">
-        <v>6907.080244140625</v>
+        <v>6907.08025390625</v>
       </c>
       <c r="F162" t="n">
-        <v>6484.960087890625</v>
+        <v>6484.960085449219</v>
       </c>
       <c r="G162" t="n">
-        <v>4.022386928281274</v>
+        <v>4.022386929856525</v>
       </c>
       <c r="H162" t="n">
         <v>7832.294844565128</v>
@@ -15039,13 +15039,13 @@
         <v>344.6630480957031</v>
       </c>
       <c r="E190" t="n">
-        <v>312.2791827392578</v>
+        <v>312.2791817220052</v>
       </c>
       <c r="F190" t="n">
-        <v>308.9876019287109</v>
+        <v>308.9876008605957</v>
       </c>
       <c r="G190" t="n">
-        <v>1.890258553879165</v>
+        <v>1.890258919411303</v>
       </c>
       <c r="H190" t="n">
         <v>380.4567148307952</v>
@@ -15501,13 +15501,13 @@
         <v>1830.872600097656</v>
       </c>
       <c r="E196" t="n">
-        <v>1706.914969889323</v>
+        <v>1706.914968261719</v>
       </c>
       <c r="F196" t="n">
-        <v>1680.25037109375</v>
+        <v>1680.250369262695</v>
       </c>
       <c r="G196" t="n">
-        <v>0.9512679428489657</v>
+        <v>0.9512679068760521</v>
       </c>
       <c r="H196" t="n">
         <v>1983.954544928268</v>
@@ -18045,10 +18045,10 @@
         <v>619.35134765625</v>
       </c>
       <c r="F229" t="n">
-        <v>608.8622229003906</v>
+        <v>608.8622232055664</v>
       </c>
       <c r="G229" t="n">
-        <v>1.892793360902645</v>
+        <v>1.892793411973659</v>
       </c>
       <c r="H229" t="n">
         <v>769</v>
@@ -18741,7 +18741,7 @@
         <v>458.1383093261718</v>
       </c>
       <c r="G238" t="n">
-        <v>1.732828177599854</v>
+        <v>1.732828281010912</v>
       </c>
       <c r="H238" t="n">
         <v>529.9163379046904</v>
@@ -18966,13 +18966,13 @@
         <v>417.6021545410156</v>
       </c>
       <c r="E241" t="n">
-        <v>393.4513149007162</v>
+        <v>393.4513153076172</v>
       </c>
       <c r="F241" t="n">
-        <v>380.6291371154785</v>
+        <v>380.6291372680664</v>
       </c>
       <c r="G241" t="n">
-        <v>2.610149263486772</v>
+        <v>2.610149220204705</v>
       </c>
       <c r="H241" t="n">
         <v>480.9477017568404</v>
@@ -19431,10 +19431,10 @@
         <v>4419.141232096355</v>
       </c>
       <c r="F247" t="n">
-        <v>4390.1908203125</v>
+        <v>4390.190841064453</v>
       </c>
       <c r="G247" t="n">
-        <v>0.8015413658398085</v>
+        <v>0.8015411925040183</v>
       </c>
       <c r="H247" t="n">
         <v>5149.89990234375</v>
@@ -19739,10 +19739,10 @@
         <v>1015.657439371745</v>
       </c>
       <c r="F251" t="n">
-        <v>989.2291995239258</v>
+        <v>989.2291986083984</v>
       </c>
       <c r="G251" t="n">
-        <v>0.9104186124474722</v>
+        <v>0.9104186761260014</v>
       </c>
       <c r="H251" t="n">
         <v>1331.075409591023</v>
@@ -20740,19 +20740,19 @@
         <v>36710.01061197917</v>
       </c>
       <c r="F264" t="n">
-        <v>36129.27909179687</v>
+        <v>36129.27916992187</v>
       </c>
       <c r="G264" t="n">
-        <v>-0.6884368328507029</v>
+        <v>-0.6884365647844115</v>
       </c>
       <c r="H264" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I264" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J264" t="n">
-        <v>27.67028191570116</v>
+        <v>27.67027358065361</v>
       </c>
       <c r="K264" t="n">
         <v>15.70289311823834</v>
@@ -23047,13 +23047,13 @@
         <v>369.4698675537109</v>
       </c>
       <c r="E294" t="n">
-        <v>380.7758850097656</v>
+        <v>380.7758846028646</v>
       </c>
       <c r="F294" t="n">
-        <v>369.2434729003906</v>
+        <v>369.2434732055664</v>
       </c>
       <c r="G294" t="n">
-        <v>3.392584919744968</v>
+        <v>3.392585115637758</v>
       </c>
       <c r="H294" t="n">
         <v>443.3731066930094</v>
@@ -23589,19 +23589,19 @@
         <v>732.549550374349</v>
       </c>
       <c r="F301" t="n">
-        <v>684.4648233032226</v>
+        <v>684.4648229980469</v>
       </c>
       <c r="G301" t="n">
-        <v>3.094635312079452</v>
+        <v>3.094635431972681</v>
       </c>
       <c r="H301" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I301" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J301" t="n">
-        <v>40.84492277737157</v>
+        <v>40.8449062429763</v>
       </c>
       <c r="K301" t="n">
         <v>58.03731066118163</v>
@@ -23820,10 +23820,10 @@
         <v>1384.254513346354</v>
       </c>
       <c r="F304" t="n">
-        <v>1357.368188476562</v>
+        <v>1357.368189086914</v>
       </c>
       <c r="G304" t="n">
-        <v>1.253239928490824</v>
+        <v>1.253239789620464</v>
       </c>
       <c r="H304" t="n">
         <v>1553</v>
@@ -24122,19 +24122,19 @@
         <v>426.1000061035156</v>
       </c>
       <c r="D308" t="n">
-        <v>411.2546661376953</v>
+        <v>411.2546649169922</v>
       </c>
       <c r="E308" t="n">
-        <v>429.7601845296224</v>
+        <v>429.760185546875</v>
       </c>
       <c r="F308" t="n">
         <v>422.5457289123535</v>
       </c>
       <c r="G308" t="n">
-        <v>1.357816896511288</v>
+        <v>1.357816785214627</v>
       </c>
       <c r="H308" t="n">
-        <v>478.7148398145708</v>
+        <v>478.7148709533388</v>
       </c>
       <c r="I308" t="n">
         <v>355.1755291130353</v>
@@ -24143,7 +24143,7 @@
         <v>19.96885234959656</v>
       </c>
       <c r="K308" t="n">
-        <v>12.34800116343417</v>
+        <v>12.34800847128856</v>
       </c>
       <c r="L308" t="n">
         <v>60.47156726768377</v>
@@ -24439,7 +24439,7 @@
         <v>1142.093260498047</v>
       </c>
       <c r="G312" t="n">
-        <v>-0.510488027284417</v>
+        <v>-0.5104879743871527</v>
       </c>
       <c r="H312" t="n">
         <v>1409.944064008135</v>
@@ -24510,16 +24510,16 @@
         <v>4542.822724609375</v>
       </c>
       <c r="E313" t="n">
-        <v>4236.80775390625</v>
+        <v>4236.807755533854</v>
       </c>
       <c r="F313" t="n">
-        <v>4302.876108398437</v>
+        <v>4302.876119384766</v>
       </c>
       <c r="G313" t="n">
-        <v>0.4646390657473853</v>
+        <v>0.4646388354858422</v>
       </c>
       <c r="H313" t="n">
-        <v>5005.771184298104</v>
+        <v>5005.771680286142</v>
       </c>
       <c r="I313" t="n">
         <v>3669.905008549105</v>
@@ -24528,7 +24528,7 @@
         <v>23.16395082353859</v>
       </c>
       <c r="K313" t="n">
-        <v>10.7471500950908</v>
+        <v>10.74716106827749</v>
       </c>
       <c r="L313" t="n">
         <v>58.52981969486824</v>
@@ -25745,10 +25745,10 @@
         <v>729.4431587727864</v>
       </c>
       <c r="F329" t="n">
-        <v>744.862698059082</v>
+        <v>744.8626977539062</v>
       </c>
       <c r="G329" t="n">
-        <v>-0.1937057803936493</v>
+        <v>-0.1937057804728748</v>
       </c>
       <c r="H329" t="n">
         <v>879.2203373423794</v>
@@ -28594,13 +28594,13 @@
         <v>739.7274979654948</v>
       </c>
       <c r="F366" t="n">
-        <v>757.9121438598632</v>
+        <v>757.9121447753906</v>
       </c>
       <c r="G366" t="n">
-        <v>-2.529212613278031</v>
+        <v>-2.529212610300102</v>
       </c>
       <c r="H366" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I366" t="n">
         <v>612.1496526863262</v>
@@ -28609,7 +28609,7 @@
         <v>31.66714976688965</v>
       </c>
       <c r="K366" t="n">
-        <v>38.65501562705325</v>
+        <v>38.65500016207899</v>
       </c>
       <c r="L366" t="n">
         <v>50.7628294036061</v>
@@ -30057,10 +30057,10 @@
         <v>773.4360766601562</v>
       </c>
       <c r="F385" t="n">
-        <v>789.7837814331054</v>
+        <v>789.783779296875</v>
       </c>
       <c r="G385" t="n">
-        <v>-1.050336966035348</v>
+        <v>-1.050336968846488</v>
       </c>
       <c r="H385" t="n">
         <v>1132.843871688672</v>
@@ -30140,7 +30140,7 @@
         <v>-1.857723905058561</v>
       </c>
       <c r="H386" t="n">
-        <v>623.6462906209067</v>
+        <v>623.6463522815318</v>
       </c>
       <c r="I386" t="n">
         <v>351.0001816860465</v>
@@ -30149,7 +30149,7 @@
         <v>30.55548797689327</v>
       </c>
       <c r="K386" t="n">
-        <v>36.09302577652083</v>
+        <v>36.0930392321946</v>
       </c>
       <c r="L386" t="n">
         <v>32.73231622746186</v>
@@ -30211,19 +30211,19 @@
         <v>522.3315828450521</v>
       </c>
       <c r="F387" t="n">
-        <v>524.4386027526856</v>
+        <v>524.438603515625</v>
       </c>
       <c r="G387" t="n">
-        <v>3.792389154435294</v>
+        <v>3.792389180053135</v>
       </c>
       <c r="H387" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I387" t="n">
-        <v>306.8419898026673</v>
+        <v>306.8420198526935</v>
       </c>
       <c r="J387" t="n">
-        <v>61.20674820763548</v>
+        <v>61.20673242013996</v>
       </c>
       <c r="K387" t="n">
         <v>52.82830673988417</v>
@@ -30519,10 +30519,10 @@
         <v>338.5830503336588</v>
       </c>
       <c r="F391" t="n">
-        <v>335.0915637207031</v>
+        <v>335.0915635681152</v>
       </c>
       <c r="G391" t="n">
-        <v>1.071609786580363</v>
+        <v>1.071609694038878</v>
       </c>
       <c r="H391" t="n">
         <v>428.7550602808859</v>
@@ -31366,10 +31366,10 @@
         <v>2152.471216634115</v>
       </c>
       <c r="F402" t="n">
-        <v>2094.614436035156</v>
+        <v>2094.614432373047</v>
       </c>
       <c r="G402" t="n">
-        <v>0.007041461253542991</v>
+        <v>0.007041432122667501</v>
       </c>
       <c r="H402" t="n">
         <v>2625.96691593483</v>
@@ -31517,13 +31517,13 @@
         <v>753.4573889160156</v>
       </c>
       <c r="E404" t="n">
-        <v>740.7510111490885</v>
+        <v>740.7510091145833</v>
       </c>
       <c r="F404" t="n">
-        <v>736.3989730834961</v>
+        <v>736.3989715576172</v>
       </c>
       <c r="G404" t="n">
-        <v>-0.6180670738096139</v>
+        <v>-0.6180671978752272</v>
       </c>
       <c r="H404" t="n">
         <v>837.8765073351432</v>
@@ -31751,13 +31751,13 @@
         <v>1082.494107666016</v>
       </c>
       <c r="F407" t="n">
-        <v>1080.97290222168</v>
+        <v>1080.972903137207</v>
       </c>
       <c r="G407" t="n">
-        <v>-0.907265142756053</v>
+        <v>-0.9072650865513232</v>
       </c>
       <c r="H407" t="n">
-        <v>1300.436668328248</v>
+        <v>1300.436795781491</v>
       </c>
       <c r="I407" t="n">
         <v>885.652283987356</v>
@@ -31766,7 +31766,7 @@
         <v>20.96169887407182</v>
       </c>
       <c r="K407" t="n">
-        <v>21.38865014995293</v>
+        <v>21.3886620470161</v>
       </c>
       <c r="L407" t="n">
         <v>40.91539528432732</v>
@@ -32133,13 +32133,13 @@
         <v>298.6186181640625</v>
       </c>
       <c r="E412" t="n">
-        <v>273.0273685709635</v>
+        <v>273.0273678588867</v>
       </c>
       <c r="F412" t="n">
-        <v>285.6348263549805</v>
+        <v>285.6348247528076</v>
       </c>
       <c r="G412" t="n">
-        <v>-2.815854992308675</v>
+        <v>-2.815854805840601</v>
       </c>
       <c r="H412" t="n">
         <v>390.5481555478003</v>
@@ -32364,13 +32364,13 @@
         <v>13160.73662109375</v>
       </c>
       <c r="E415" t="n">
-        <v>12660.2369140625</v>
+        <v>12660.236953125</v>
       </c>
       <c r="F415" t="n">
-        <v>12886.19333007813</v>
+        <v>12886.19338378906</v>
       </c>
       <c r="G415" t="n">
-        <v>-0.8565373329575077</v>
+        <v>-0.8565375528908348</v>
       </c>
       <c r="H415" t="n">
         <v>17899.76088444639</v>
@@ -33214,10 +33214,10 @@
         <v>159.6345504760742</v>
       </c>
       <c r="F426" t="n">
-        <v>155.9747814941406</v>
+        <v>155.9747816467285</v>
       </c>
       <c r="G426" t="n">
-        <v>1.075229137438094</v>
+        <v>1.075229086403096</v>
       </c>
       <c r="H426" t="n">
         <v>203.5447632528218</v>
@@ -33522,10 +33522,10 @@
         <v>666.5102819824219</v>
       </c>
       <c r="F430" t="n">
-        <v>667.2752294921875</v>
+        <v>667.2752291870117</v>
       </c>
       <c r="G430" t="n">
-        <v>-0.5563141896407164</v>
+        <v>-0.5563142351209027</v>
       </c>
       <c r="H430" t="n">
         <v>792.3323631991859</v>
@@ -33679,7 +33679,7 @@
         <v>2553.788489990234</v>
       </c>
       <c r="G432" t="n">
-        <v>-1.503884408755352</v>
+        <v>-1.503884362382546</v>
       </c>
       <c r="H432" t="n">
         <v>2960.01877635178</v>
@@ -33830,10 +33830,10 @@
         <v>288.0766564941407</v>
       </c>
       <c r="F434" t="n">
-        <v>282.7965901184082</v>
+        <v>282.796591720581</v>
       </c>
       <c r="G434" t="n">
-        <v>-0.007907817612451407</v>
+        <v>-0.007907655722949603</v>
       </c>
       <c r="H434" t="n">
         <v>323.4425459044702</v>
@@ -33904,13 +33904,13 @@
         <v>402.3432794189453</v>
       </c>
       <c r="E435" t="n">
-        <v>418.3360628255209</v>
+        <v>418.3360630289714</v>
       </c>
       <c r="F435" t="n">
-        <v>417.4233612060547</v>
+        <v>417.4233609008789</v>
       </c>
       <c r="G435" t="n">
-        <v>-0.2196094812883187</v>
+        <v>-0.2196094086598599</v>
       </c>
       <c r="H435" t="n">
         <v>472.8081629796919</v>
@@ -34147,10 +34147,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I438" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J438" t="n">
-        <v>5.409761998408036</v>
+        <v>5.409751755640779</v>
       </c>
       <c r="K438" t="n">
         <v>25.52703041247848</v>
@@ -34215,10 +34215,10 @@
         <v>77.47305587768555</v>
       </c>
       <c r="F439" t="n">
-        <v>77.37549724578858</v>
+        <v>77.37549713134766</v>
       </c>
       <c r="G439" t="n">
-        <v>-0.1080552041731075</v>
+        <v>-0.1080551059435275</v>
       </c>
       <c r="H439" t="n">
         <v>86.59303970157107</v>
@@ -34677,10 +34677,10 @@
         <v>294.4729453531901</v>
       </c>
       <c r="F445" t="n">
-        <v>283.9795323944092</v>
+        <v>283.9795321655274</v>
       </c>
       <c r="G445" t="n">
-        <v>0.9589431494116063</v>
+        <v>0.9589432597268299</v>
       </c>
       <c r="H445" t="n">
         <v>387.4363949219129</v>
@@ -34982,16 +34982,16 @@
         <v>503.3993206787109</v>
       </c>
       <c r="E449" t="n">
-        <v>485.9179475911458</v>
+        <v>485.9179461669922</v>
       </c>
       <c r="F449" t="n">
-        <v>490.7460380554199</v>
+        <v>490.7460363769531</v>
       </c>
       <c r="G449" t="n">
-        <v>-0.2802009587745014</v>
+        <v>-0.2802011452444519</v>
       </c>
       <c r="H449" t="n">
-        <v>547.7380341214969</v>
+        <v>547.7379722645398</v>
       </c>
       <c r="I449" t="n">
         <v>419.3328127807616</v>
@@ -35000,7 +35000,7 @@
         <v>10.05578050036464</v>
       </c>
       <c r="K449" t="n">
-        <v>18.68646459837418</v>
+        <v>18.68645119491654</v>
       </c>
       <c r="L449" t="n">
         <v>36.89320388349515</v>
@@ -36759,7 +36759,7 @@
         <v>394.6485163879395</v>
       </c>
       <c r="G472" t="n">
-        <v>-3.722195627686309</v>
+        <v>-3.722195663525818</v>
       </c>
       <c r="H472" t="n">
         <v>541.0236304500187</v>
@@ -37754,22 +37754,22 @@
         <v>2276.71484375</v>
       </c>
       <c r="E485" t="n">
-        <v>2226.59209391276</v>
+        <v>2226.592064615885</v>
       </c>
       <c r="F485" t="n">
-        <v>2276.099978637695</v>
+        <v>2276.099962768555</v>
       </c>
       <c r="G485" t="n">
-        <v>-0.4275940696375713</v>
+        <v>-0.4275940726060412</v>
       </c>
       <c r="H485" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I485" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J485" t="n">
-        <v>11.31484519965893</v>
+        <v>11.31485210721246</v>
       </c>
       <c r="K485" t="n">
         <v>26.54461366267797</v>
@@ -37834,13 +37834,13 @@
         <v>5429.506998697917</v>
       </c>
       <c r="F486" t="n">
-        <v>5470.209609375</v>
+        <v>5470.209602050782</v>
       </c>
       <c r="G486" t="n">
-        <v>-0.7492675129687432</v>
+        <v>-0.7492673820705176</v>
       </c>
       <c r="H486" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I486" t="n">
         <v>5051</v>
@@ -37849,7 +37849,7 @@
         <v>4.414967333201347</v>
       </c>
       <c r="K486" t="n">
-        <v>11.40565827288356</v>
+        <v>11.40564890408418</v>
       </c>
       <c r="L486" t="n">
         <v>42.1636615811373</v>
@@ -38373,10 +38373,10 @@
         <v>526.2697357177734</v>
       </c>
       <c r="F493" t="n">
-        <v>533.598900604248</v>
+        <v>533.5989021301269</v>
       </c>
       <c r="G493" t="n">
-        <v>-1.506682319518182</v>
+        <v>-1.506682148829896</v>
       </c>
       <c r="H493" t="n">
         <v>653.9340000086492</v>
@@ -38447,22 +38447,22 @@
         <v>430.9691821289063</v>
       </c>
       <c r="E494" t="n">
-        <v>462.6965887451172</v>
+        <v>462.6965881347656</v>
       </c>
       <c r="F494" t="n">
-        <v>465.5620881652832</v>
+        <v>465.5620889282226</v>
       </c>
       <c r="G494" t="n">
-        <v>-1.128613493655573</v>
+        <v>-1.128613395708888</v>
       </c>
       <c r="H494" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I494" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J494" t="n">
-        <v>14.4994303558285</v>
+        <v>14.49942118303877</v>
       </c>
       <c r="K494" t="n">
         <v>27.68727324110241</v>
@@ -38681,19 +38681,19 @@
         <v>965.6785986328125</v>
       </c>
       <c r="F497" t="n">
-        <v>942.4370437622071</v>
+        <v>942.4370458984375</v>
       </c>
       <c r="G497" t="n">
-        <v>-0.4158606219584193</v>
+        <v>-0.415860685245284</v>
       </c>
       <c r="H497" t="n">
         <v>1224.72508309492</v>
       </c>
       <c r="I497" t="n">
-        <v>784.9092044208618</v>
+        <v>784.9091438882253</v>
       </c>
       <c r="J497" t="n">
-        <v>6.929563708230257</v>
+        <v>6.92957195469861</v>
       </c>
       <c r="K497" t="n">
         <v>45.92220909182525</v>
@@ -39140,25 +39140,25 @@
         <v>231.160930480957</v>
       </c>
       <c r="E503" t="n">
-        <v>224.4955261230469</v>
+        <v>224.4955264282227</v>
       </c>
       <c r="F503" t="n">
-        <v>225.6140672302246</v>
+        <v>225.6140676116943</v>
       </c>
       <c r="G503" t="n">
-        <v>-1.364058450561834</v>
+        <v>-1.364058283787539</v>
       </c>
       <c r="H503" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I503" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J503" t="n">
-        <v>20.02128795617528</v>
+        <v>20.0212985319485</v>
       </c>
       <c r="K503" t="n">
-        <v>38.61828291038911</v>
+        <v>38.61829873576517</v>
       </c>
       <c r="L503" t="n">
         <v>34.81276005547851</v>
@@ -40295,7 +40295,7 @@
         <v>333.9067395019531</v>
       </c>
       <c r="E518" t="n">
-        <v>339.3453332519532</v>
+        <v>339.3453334554036</v>
       </c>
       <c r="F518" t="n">
         <v>341.6456816101074</v>
@@ -40452,13 +40452,13 @@
         <v>613.7596057128907</v>
       </c>
       <c r="F520" t="n">
-        <v>619.8998611450195</v>
+        <v>619.8998629760742</v>
       </c>
       <c r="G520" t="n">
-        <v>-1.836345783645466</v>
+        <v>-1.836345825759267</v>
       </c>
       <c r="H520" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I520" t="n">
         <v>495.5999980879241</v>
@@ -40467,7 +40467,7 @@
         <v>21.03510449964094</v>
       </c>
       <c r="K520" t="n">
-        <v>41.50642293118896</v>
+        <v>41.50643316149214</v>
       </c>
       <c r="L520" t="n">
         <v>29.95839112343966</v>
@@ -40609,7 +40609,7 @@
         <v>33.80074458122253</v>
       </c>
       <c r="G522" t="n">
-        <v>-1.987491731455793</v>
+        <v>-1.987492002497948</v>
       </c>
       <c r="H522" t="n">
         <v>40.26070662850351</v>
@@ -41216,25 +41216,25 @@
         <v>199.3099975585938</v>
       </c>
       <c r="D530" t="n">
-        <v>212.8809286499023</v>
+        <v>212.8809283447266</v>
       </c>
       <c r="E530" t="n">
-        <v>207.7894618733724</v>
+        <v>207.7894613647461</v>
       </c>
       <c r="F530" t="n">
-        <v>211.6584394836426</v>
+        <v>211.6584387207031</v>
       </c>
       <c r="G530" t="n">
-        <v>-1.249598678812536</v>
+        <v>-1.249598753561654</v>
       </c>
       <c r="H530" t="n">
         <v>260.4933484681973</v>
       </c>
       <c r="I530" t="n">
-        <v>171.6534204603822</v>
+        <v>171.6534052563282</v>
       </c>
       <c r="J530" t="n">
-        <v>16.11187066592401</v>
+        <v>16.11188095043396</v>
       </c>
       <c r="K530" t="n">
         <v>30.69758248911556</v>
@@ -41296,22 +41296,22 @@
         <v>372.3288641357422</v>
       </c>
       <c r="E531" t="n">
-        <v>403.2165761311849</v>
+        <v>403.216576944987</v>
       </c>
       <c r="F531" t="n">
-        <v>392.7666491699219</v>
+        <v>392.766649017334</v>
       </c>
       <c r="G531" t="n">
-        <v>-0.001111316528590311</v>
+        <v>-0.00111135537766982</v>
       </c>
       <c r="H531" t="n">
         <v>476.8288845013619</v>
       </c>
       <c r="I531" t="n">
-        <v>317.6634042148347</v>
+        <v>317.6633741663369</v>
       </c>
       <c r="J531" t="n">
-        <v>6.401932207278027</v>
+        <v>6.40194227207771</v>
       </c>
       <c r="K531" t="n">
         <v>41.07363446785855</v>
@@ -41838,13 +41838,13 @@
         <v>1637.291165364583</v>
       </c>
       <c r="F538" t="n">
-        <v>1732.310129394531</v>
+        <v>1732.310134277344</v>
       </c>
       <c r="G538" t="n">
-        <v>-3.285316967073848</v>
+        <v>-3.285316892205126</v>
       </c>
       <c r="H538" t="n">
-        <v>2339.80156593166</v>
+        <v>2339.801318384509</v>
       </c>
       <c r="I538" t="n">
         <v>1322.972836511248</v>
@@ -41853,7 +41853,7 @@
         <v>19.63964830918645</v>
       </c>
       <c r="K538" t="n">
-        <v>47.82673071459686</v>
+        <v>47.82671507477227</v>
       </c>
       <c r="L538" t="n">
         <v>23.43966712898752</v>
@@ -41992,10 +41992,10 @@
         <v>2841.105600585937</v>
       </c>
       <c r="F540" t="n">
-        <v>2748.948394775391</v>
+        <v>2748.9483984375</v>
       </c>
       <c r="G540" t="n">
-        <v>-0.8269079533420154</v>
+        <v>-0.8269079085746922</v>
       </c>
       <c r="H540" t="n">
         <v>3333.383184200957</v>
@@ -42454,10 +42454,10 @@
         <v>2436.246567382812</v>
       </c>
       <c r="F546" t="n">
-        <v>2435.09337890625</v>
+        <v>2435.093383789062</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.372245774143166</v>
+        <v>-1.372245868955835</v>
       </c>
       <c r="H546" t="n">
         <v>2972.124194159559</v>
@@ -43144,13 +43144,13 @@
         <v>353.3964935302735</v>
       </c>
       <c r="E555" t="n">
-        <v>416.9898107910156</v>
+        <v>416.9898105875651</v>
       </c>
       <c r="F555" t="n">
-        <v>444.7202917480469</v>
+        <v>444.7202911376953</v>
       </c>
       <c r="G555" t="n">
-        <v>-4.775306590035832</v>
+        <v>-4.775306596276685</v>
       </c>
       <c r="H555" t="n">
         <v>605.9581737112406</v>
@@ -43609,13 +43609,13 @@
         <v>507.9299729410807</v>
       </c>
       <c r="F561" t="n">
-        <v>537.1996977233887</v>
+        <v>537.1996995544433</v>
       </c>
       <c r="G561" t="n">
-        <v>-3.524954799943025</v>
+        <v>-3.524954682603154</v>
       </c>
       <c r="H561" t="n">
-        <v>828.2152668923007</v>
+        <v>828.2152046613147</v>
       </c>
       <c r="I561" t="n">
         <v>406.1171468902937</v>
@@ -43624,7 +43624,7 @@
         <v>14.00651352578135</v>
       </c>
       <c r="K561" t="n">
-        <v>78.88018723375826</v>
+        <v>78.88017379294054</v>
       </c>
       <c r="L561" t="n">
         <v>6.796116504854369</v>
@@ -44299,13 +44299,13 @@
         <v>138.0243838500976</v>
       </c>
       <c r="E570" t="n">
-        <v>142.0476087443034</v>
+        <v>142.0476088460287</v>
       </c>
       <c r="F570" t="n">
-        <v>146.9962474822998</v>
+        <v>146.9962479400635</v>
       </c>
       <c r="G570" t="n">
-        <v>-1.619052267116505</v>
+        <v>-1.619052463095927</v>
       </c>
       <c r="H570" t="n">
         <v>184.9587904135824</v>
@@ -45226,10 +45226,10 @@
         <v>915.8419104003906</v>
       </c>
       <c r="F582" t="n">
-        <v>921.7419030761719</v>
+        <v>921.7419055175782</v>
       </c>
       <c r="G582" t="n">
-        <v>-0.4866732686639286</v>
+        <v>-0.486673300168261</v>
       </c>
       <c r="H582" t="n">
         <v>1282.80960014975</v>
@@ -45303,10 +45303,10 @@
         <v>3005.409427083333</v>
       </c>
       <c r="F583" t="n">
-        <v>3153.55519165039</v>
+        <v>3153.555186767578</v>
       </c>
       <c r="G583" t="n">
-        <v>-2.397144542060292</v>
+        <v>-2.397144508807714</v>
       </c>
       <c r="H583" t="n">
         <v>3923.39201752828</v>
@@ -45380,13 +45380,13 @@
         <v>122.7193290201823</v>
       </c>
       <c r="F584" t="n">
-        <v>124.6486833190918</v>
+        <v>124.648683052063</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.867549866906715</v>
+        <v>-1.867549517178491</v>
       </c>
       <c r="H584" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I584" t="n">
         <v>110.3499984741211</v>
@@ -45395,7 +45395,7 @@
         <v>2.1295863222619</v>
       </c>
       <c r="K584" t="n">
-        <v>38.33183903869131</v>
+        <v>38.33182335537655</v>
       </c>
       <c r="L584" t="n">
         <v>25.65880721220527</v>
@@ -45765,13 +45765,13 @@
         <v>130957.3200520833</v>
       </c>
       <c r="F589" t="n">
-        <v>134792.03921875</v>
+        <v>134792.0390625</v>
       </c>
       <c r="G589" t="n">
-        <v>-2.100468994956195</v>
+        <v>-2.10046899733991</v>
       </c>
       <c r="H589" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I589" t="n">
         <v>121787.4350540836</v>
@@ -45780,7 +45780,7 @@
         <v>1.845481797788318</v>
       </c>
       <c r="K589" t="n">
-        <v>31.66322919235265</v>
+        <v>31.6632420577639</v>
       </c>
       <c r="L589" t="n">
         <v>24.6879334257975</v>
@@ -45848,7 +45848,7 @@
         <v>-0.592056154740972</v>
       </c>
       <c r="H590" t="n">
-        <v>523.4329289989834</v>
+        <v>523.4329909937741</v>
       </c>
       <c r="I590" t="n">
         <v>394.4382907843191</v>
@@ -45857,7 +45857,7 @@
         <v>5.960811100758079</v>
       </c>
       <c r="K590" t="n">
-        <v>25.23816574018933</v>
+        <v>25.23818057325284</v>
       </c>
       <c r="L590" t="n">
         <v>24.41054091539528</v>
@@ -46837,25 +46837,25 @@
         <v>173.9900054931641</v>
       </c>
       <c r="D603" t="n">
-        <v>185.7462503051758</v>
+        <v>185.74625</v>
       </c>
       <c r="E603" t="n">
-        <v>192.3783165486654</v>
+        <v>192.3783171590169</v>
       </c>
       <c r="F603" t="n">
-        <v>195.0438655853272</v>
+        <v>195.0438652801514</v>
       </c>
       <c r="G603" t="n">
-        <v>-2.607567704043812</v>
+        <v>-2.607567670914424</v>
       </c>
       <c r="H603" t="n">
         <v>239.2186728978909</v>
       </c>
       <c r="I603" t="n">
-        <v>156.7442971017576</v>
+        <v>156.7443123050878</v>
       </c>
       <c r="J603" t="n">
-        <v>11.00244711309058</v>
+        <v>11.00243634646796</v>
       </c>
       <c r="K603" t="n">
         <v>37.48989329579029</v>
@@ -47148,13 +47148,13 @@
         <v>115.4739770507812</v>
       </c>
       <c r="E607" t="n">
-        <v>121.1187430826823</v>
+        <v>121.1187431844075</v>
       </c>
       <c r="F607" t="n">
-        <v>123.8878693771362</v>
+        <v>123.8878695678711</v>
       </c>
       <c r="G607" t="n">
-        <v>-2.5011147651405</v>
+        <v>-2.501114819927197</v>
       </c>
       <c r="H607" t="n">
         <v>156.8181640954093</v>
@@ -47690,10 +47690,10 @@
         <v>1471.633913574219</v>
       </c>
       <c r="F614" t="n">
-        <v>1491.384322509766</v>
+        <v>1491.384323120117</v>
       </c>
       <c r="G614" t="n">
-        <v>-1.71142991832377</v>
+        <v>-1.71142983856265</v>
       </c>
       <c r="H614" t="n">
         <v>1965.628830677411</v>
@@ -47998,10 +47998,10 @@
         <v>20.42095072428386</v>
       </c>
       <c r="F618" t="n">
-        <v>20.5083403968811</v>
+        <v>20.50834037780762</v>
       </c>
       <c r="G618" t="n">
-        <v>-1.278661058656094</v>
+        <v>-1.278661014509896</v>
       </c>
       <c r="H618" t="n">
         <v>23.83526024888653</v>
@@ -48999,13 +48999,13 @@
         <v>1225.736416829427</v>
       </c>
       <c r="F631" t="n">
-        <v>1265.743472900391</v>
+        <v>1265.743474731445</v>
       </c>
       <c r="G631" t="n">
-        <v>-2.422870215452266</v>
+        <v>-2.42287016611975</v>
       </c>
       <c r="H631" t="n">
-        <v>1546.338945569448</v>
+        <v>1546.339069162078</v>
       </c>
       <c r="I631" t="n">
         <v>1081.099975585938</v>
@@ -49014,7 +49014,7 @@
         <v>1.424477362115928</v>
       </c>
       <c r="K631" t="n">
-        <v>41.02498363606457</v>
+        <v>41.02499490762222</v>
       </c>
       <c r="L631" t="n">
         <v>15.67267683772538</v>
@@ -49073,16 +49073,16 @@
         <v>2289.488012695313</v>
       </c>
       <c r="E632" t="n">
-        <v>2303.345173339844</v>
+        <v>2303.345184733073</v>
       </c>
       <c r="F632" t="n">
-        <v>2484.52655090332</v>
+        <v>2484.526560668945</v>
       </c>
       <c r="G632" t="n">
-        <v>-3.469682677871755</v>
+        <v>-3.469682710488986</v>
       </c>
       <c r="H632" t="n">
-        <v>3287.161392369851</v>
+        <v>3287.161645949698</v>
       </c>
       <c r="I632" t="n">
         <v>1966.020518717901</v>
@@ -49091,7 +49091,7 @@
         <v>5.899199941093825</v>
       </c>
       <c r="K632" t="n">
-        <v>57.88479310133767</v>
+        <v>57.88480528096531</v>
       </c>
       <c r="L632" t="n">
         <v>15.53398058252427</v>
@@ -49156,7 +49156,7 @@
         <v>435.1267344665528</v>
       </c>
       <c r="G633" t="n">
-        <v>-3.404032935952583</v>
+        <v>-3.404032870511231</v>
       </c>
       <c r="H633" t="n">
         <v>570.5579909394708</v>
@@ -49230,13 +49230,13 @@
         <v>122.5039993286133</v>
       </c>
       <c r="F634" t="n">
-        <v>125.5922719192505</v>
+        <v>125.5922718429565</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.548601341178558</v>
+        <v>-2.548601573448783</v>
       </c>
       <c r="H634" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I634" t="n">
         <v>104.7068431385872</v>
@@ -49245,7 +49245,7 @@
         <v>3.699050201848864</v>
       </c>
       <c r="K634" t="n">
-        <v>41.92681903728905</v>
+        <v>41.92683357587146</v>
       </c>
       <c r="L634" t="n">
         <v>15.11789181692094</v>
@@ -49920,16 +49920,16 @@
         <v>88.66075836181641</v>
       </c>
       <c r="E643" t="n">
-        <v>92.53722946166992</v>
+        <v>92.53722956339519</v>
       </c>
       <c r="F643" t="n">
-        <v>95.87017971038819</v>
+        <v>95.87017993927002</v>
       </c>
       <c r="G643" t="n">
-        <v>-3.180090826184923</v>
+        <v>-3.180090744234687</v>
       </c>
       <c r="H643" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I643" t="n">
         <v>76.65010804466255</v>
@@ -49938,7 +49938,7 @@
         <v>8.10160967036162</v>
       </c>
       <c r="K643" t="n">
-        <v>50.64845369899198</v>
+        <v>50.64844420785426</v>
       </c>
       <c r="L643" t="n">
         <v>13.73092926490985</v>
@@ -50000,10 +50000,10 @@
         <v>1291.995585123698</v>
       </c>
       <c r="F644" t="n">
-        <v>1321.45987487793</v>
+        <v>1321.459875488281</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.386999994419359</v>
+        <v>-2.386999949334179</v>
       </c>
       <c r="H644" t="n">
         <v>1627.061020109863</v>
@@ -50382,16 +50382,16 @@
         <v>950.7499414062499</v>
       </c>
       <c r="E649" t="n">
-        <v>1017.459155273438</v>
+        <v>1017.459152018229</v>
       </c>
       <c r="F649" t="n">
-        <v>1060.007171020508</v>
+        <v>1060.007169189453</v>
       </c>
       <c r="G649" t="n">
-        <v>-2.420704610224411</v>
+        <v>-2.420704723956724</v>
       </c>
       <c r="H649" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I649" t="n">
         <v>855.1500244140625</v>
@@ -50400,7 +50400,7 @@
         <v>2.905919999588891</v>
       </c>
       <c r="K649" t="n">
-        <v>42.63391283520865</v>
+        <v>42.63389867229614</v>
       </c>
       <c r="L649" t="n">
         <v>12.48266296809986</v>
@@ -51232,13 +51232,13 @@
         <v>296.3036335245768</v>
       </c>
       <c r="F660" t="n">
-        <v>307.5067194366455</v>
+        <v>307.5067198944092</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.547029931586431</v>
+        <v>-2.547029739389561</v>
       </c>
       <c r="H660" t="n">
-        <v>396.5816020628056</v>
+        <v>396.5816333492734</v>
       </c>
       <c r="I660" t="n">
         <v>243.9284560598348</v>
@@ -51247,7 +51247,7 @@
         <v>6.650121145632348</v>
       </c>
       <c r="K660" t="n">
-        <v>52.4434408484393</v>
+        <v>52.44345287475816</v>
       </c>
       <c r="L660" t="n">
         <v>10.54091539528433</v>
@@ -53388,10 +53388,10 @@
         <v>276.8652786254883</v>
       </c>
       <c r="F688" t="n">
-        <v>289.3636037445069</v>
+        <v>289.3636045074463</v>
       </c>
       <c r="G688" t="n">
-        <v>-4.124337649434551</v>
+        <v>-4.124337590536554</v>
       </c>
       <c r="H688" t="n">
         <v>386.0274005660562</v>
@@ -55698,10 +55698,10 @@
         <v>660.7392146809896</v>
       </c>
       <c r="F718" t="n">
-        <v>766.1414306640625</v>
+        <v>766.1414273071289</v>
       </c>
       <c r="G718" t="n">
-        <v>-8.512690445822614</v>
+        <v>-8.512690479946738</v>
       </c>
       <c r="H718" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1499,10 +1499,10 @@
         <v>2055.300048828125</v>
       </c>
       <c r="I14" t="n">
-        <v>841.4672483994065</v>
+        <v>841.4671897137645</v>
       </c>
       <c r="J14" t="n">
-        <v>135.7786359212266</v>
+        <v>135.7786523649107</v>
       </c>
       <c r="K14" t="n">
         <v>3.593752461095012</v>
@@ -2269,10 +2269,10 @@
         <v>1357.900024414062</v>
       </c>
       <c r="I24" t="n">
-        <v>594.6744698202933</v>
+        <v>594.6745299041222</v>
       </c>
       <c r="J24" t="n">
-        <v>112.3851054816041</v>
+        <v>112.3850840229579</v>
       </c>
       <c r="K24" t="n">
         <v>7.513857831675574</v>
@@ -2568,10 +2568,10 @@
         <v>655.1678442382813</v>
       </c>
       <c r="F28" t="n">
-        <v>614.6078900146484</v>
+        <v>614.6078901672363</v>
       </c>
       <c r="G28" t="n">
-        <v>5.836161650620131</v>
+        <v>5.836161815942442</v>
       </c>
       <c r="H28" t="n">
         <v>844</v>
@@ -2799,10 +2799,10 @@
         <v>10869.85709635417</v>
       </c>
       <c r="F31" t="n">
-        <v>10437.05027587891</v>
+        <v>10437.05026367188</v>
       </c>
       <c r="G31" t="n">
-        <v>3.312993255113517</v>
+        <v>3.312993408920728</v>
       </c>
       <c r="H31" t="n">
         <v>13996</v>
@@ -3726,7 +3726,7 @@
         <v>225.895284576416</v>
       </c>
       <c r="G43" t="n">
-        <v>4.592414891553465</v>
+        <v>4.592414854606131</v>
       </c>
       <c r="H43" t="n">
         <v>321.3999938964844</v>
@@ -3880,7 +3880,7 @@
         <v>3637.369436035156</v>
       </c>
       <c r="G45" t="n">
-        <v>5.51929794027648</v>
+        <v>5.519297865542794</v>
       </c>
       <c r="H45" t="n">
         <v>4843</v>
@@ -4179,16 +4179,16 @@
         <v>230.0700073242188</v>
       </c>
       <c r="D49" t="n">
-        <v>193.0581924438476</v>
+        <v>193.0581918334961</v>
       </c>
       <c r="E49" t="n">
-        <v>155.5897725931803</v>
+        <v>155.5897733561198</v>
       </c>
       <c r="F49" t="n">
-        <v>154.3818590164184</v>
+        <v>154.3818601989746</v>
       </c>
       <c r="G49" t="n">
-        <v>3.34929663126462</v>
+        <v>3.349296551965142</v>
       </c>
       <c r="H49" t="n">
         <v>235.75</v>
@@ -4256,16 +4256,16 @@
         <v>205.0899963378906</v>
       </c>
       <c r="D50" t="n">
-        <v>185.0763525390625</v>
+        <v>185.0763528442383</v>
       </c>
       <c r="E50" t="n">
-        <v>155.9071701558431</v>
+        <v>155.9071700541178</v>
       </c>
       <c r="F50" t="n">
-        <v>154.6964868545532</v>
+        <v>154.6964866256714</v>
       </c>
       <c r="G50" t="n">
-        <v>2.533514453384589</v>
+        <v>2.533514560926253</v>
       </c>
       <c r="H50" t="n">
         <v>233.3500061035156</v>
@@ -5728,7 +5728,7 @@
         <v>1591.834495849609</v>
       </c>
       <c r="G69" t="n">
-        <v>2.992658222217814</v>
+        <v>2.992658181545882</v>
       </c>
       <c r="H69" t="n">
         <v>2038.599975585938</v>
@@ -7339,13 +7339,13 @@
         <v>1044.189058837891</v>
       </c>
       <c r="E90" t="n">
-        <v>945.850966796875</v>
+        <v>945.8509688313802</v>
       </c>
       <c r="F90" t="n">
-        <v>918.3966165161132</v>
+        <v>918.3966180419922</v>
       </c>
       <c r="G90" t="n">
-        <v>3.279131487184794</v>
+        <v>3.279131410669622</v>
       </c>
       <c r="H90" t="n">
         <v>1148</v>
@@ -9110,13 +9110,13 @@
         <v>340.3660192871094</v>
       </c>
       <c r="E113" t="n">
-        <v>259.0081260172526</v>
+        <v>259.0081261189779</v>
       </c>
       <c r="F113" t="n">
-        <v>244.313228225708</v>
+        <v>244.313228302002</v>
       </c>
       <c r="G113" t="n">
-        <v>7.166143670571268</v>
+        <v>7.16614373990101</v>
       </c>
       <c r="H113" t="n">
         <v>388.75</v>
@@ -9960,10 +9960,10 @@
         <v>1417.508198242188</v>
       </c>
       <c r="F124" t="n">
-        <v>1352.940924072266</v>
+        <v>1352.940920410156</v>
       </c>
       <c r="G124" t="n">
-        <v>3.04363578260165</v>
+        <v>3.04363559948726</v>
       </c>
       <c r="H124" t="n">
         <v>1766.733188761222</v>
@@ -11038,10 +11038,10 @@
         <v>728.6689595540364</v>
       </c>
       <c r="F138" t="n">
-        <v>733.1653747558594</v>
+        <v>733.1653762817383</v>
       </c>
       <c r="G138" t="n">
-        <v>2.500909918623329</v>
+        <v>2.500909869555779</v>
       </c>
       <c r="H138" t="n">
         <v>1002.400024414062</v>
@@ -12193,10 +12193,10 @@
         <v>4595.71060546875</v>
       </c>
       <c r="F153" t="n">
-        <v>4441.258188476562</v>
+        <v>4441.25818359375</v>
       </c>
       <c r="G153" t="n">
-        <v>3.019674807991701</v>
+        <v>3.019674840582387</v>
       </c>
       <c r="H153" t="n">
         <v>5250</v>
@@ -13120,7 +13120,7 @@
         <v>1127.398363647461</v>
       </c>
       <c r="G165" t="n">
-        <v>3.508969194973011</v>
+        <v>3.508969281979146</v>
       </c>
       <c r="H165" t="n">
         <v>1596.696405272527</v>
@@ -14811,13 +14811,13 @@
         <v>1788.325852864583</v>
       </c>
       <c r="F187" t="n">
-        <v>1779.015993652344</v>
+        <v>1779.015999145508</v>
       </c>
       <c r="G187" t="n">
-        <v>1.541715798403165</v>
+        <v>1.541715758194906</v>
       </c>
       <c r="H187" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I187" t="n">
         <v>1345.285007075603</v>
@@ -14826,7 +14826,7 @@
         <v>45.86500544548524</v>
       </c>
       <c r="K187" t="n">
-        <v>14.97670337682986</v>
+        <v>14.97669061737585</v>
       </c>
       <c r="L187" t="n">
         <v>61.82572614107884</v>
@@ -15655,13 +15655,13 @@
         <v>7354.229365234375</v>
       </c>
       <c r="E198" t="n">
-        <v>6929.848001302084</v>
+        <v>6929.847994791667</v>
       </c>
       <c r="F198" t="n">
-        <v>6517.915737304687</v>
+        <v>6517.9157421875</v>
       </c>
       <c r="G198" t="n">
-        <v>3.671720234523868</v>
+        <v>3.671720312188187</v>
       </c>
       <c r="H198" t="n">
         <v>7832.294844565128</v>
@@ -15812,10 +15812,10 @@
         <v>1486.449109700521</v>
       </c>
       <c r="F200" t="n">
-        <v>1514.056655883789</v>
+        <v>1514.056653442383</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.1940773295977749</v>
+        <v>-0.1940774102221376</v>
       </c>
       <c r="H200" t="n">
         <v>2021.199951171875</v>
@@ -16810,13 +16810,13 @@
         <v>188.1845193481445</v>
       </c>
       <c r="E213" t="n">
-        <v>180.5304605102539</v>
+        <v>180.5304608154297</v>
       </c>
       <c r="F213" t="n">
-        <v>179.3676662445068</v>
+        <v>179.367666015625</v>
       </c>
       <c r="G213" t="n">
-        <v>0.8860907671538465</v>
+        <v>0.8860908981708215</v>
       </c>
       <c r="H213" t="n">
         <v>203.3999938964844</v>
@@ -17198,10 +17198,10 @@
         <v>1020.105819905599</v>
       </c>
       <c r="F218" t="n">
-        <v>991.6384948730469</v>
+        <v>991.6384942626953</v>
       </c>
       <c r="G218" t="n">
-        <v>1.014524638422309</v>
+        <v>1.014524796065608</v>
       </c>
       <c r="H218" t="n">
         <v>1331.075409591023</v>
@@ -17580,13 +17580,13 @@
         <v>1824.515993652344</v>
       </c>
       <c r="E223" t="n">
-        <v>1713.930037434896</v>
+        <v>1713.930034993489</v>
       </c>
       <c r="F223" t="n">
-        <v>1683.062272338867</v>
+        <v>1683.062271118164</v>
       </c>
       <c r="G223" t="n">
-        <v>0.9732296148044162</v>
+        <v>0.9732295785435108</v>
       </c>
       <c r="H223" t="n">
         <v>1983.954544928268</v>
@@ -18122,10 +18122,10 @@
         <v>165.7066747029622</v>
       </c>
       <c r="F230" t="n">
-        <v>164.9557038116455</v>
+        <v>164.9557037353516</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1915716441456716</v>
+        <v>0.1915715513773231</v>
       </c>
       <c r="H230" t="n">
         <v>181.8519567776652</v>
@@ -21122,13 +21122,13 @@
         <v>4557.957587890625</v>
       </c>
       <c r="E269" t="n">
-        <v>4236.718448893229</v>
+        <v>4236.718463541667</v>
       </c>
       <c r="F269" t="n">
-        <v>4305.386695556641</v>
+        <v>4305.386689453125</v>
       </c>
       <c r="G269" t="n">
-        <v>0.4891434989459098</v>
+        <v>0.4891431560709814</v>
       </c>
       <c r="H269" t="n">
         <v>5005.771680286142</v>
@@ -21436,7 +21436,7 @@
         <v>533.8989057922363</v>
       </c>
       <c r="G273" t="n">
-        <v>-1.148820339306866</v>
+        <v>-1.148820283452823</v>
       </c>
       <c r="H273" t="n">
         <v>663.9000244140625</v>
@@ -21510,10 +21510,10 @@
         <v>312.6840242513021</v>
       </c>
       <c r="F274" t="n">
-        <v>309.5910678100586</v>
+        <v>309.5910679626465</v>
       </c>
       <c r="G274" t="n">
-        <v>1.625423584703478</v>
+        <v>1.625423583889352</v>
       </c>
       <c r="H274" t="n">
         <v>380.4567148307952</v>
@@ -21664,13 +21664,13 @@
         <v>5124.110989583333</v>
       </c>
       <c r="F276" t="n">
-        <v>5336.029035644531</v>
+        <v>5336.029033203125</v>
       </c>
       <c r="G276" t="n">
-        <v>-1.687376385556716</v>
+        <v>-1.687376342093505</v>
       </c>
       <c r="H276" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I276" t="n">
         <v>4229.809203861739</v>
@@ -21679,7 +21679,7 @@
         <v>26.88515583870843</v>
       </c>
       <c r="K276" t="n">
-        <v>22.09156346082197</v>
+        <v>22.0915727128898</v>
       </c>
       <c r="L276" t="n">
         <v>60.44260027662517</v>
@@ -21821,7 +21821,7 @@
         <v>1139.700042724609</v>
       </c>
       <c r="G278" t="n">
-        <v>-0.6979069785932324</v>
+        <v>-0.6979069257844417</v>
       </c>
       <c r="H278" t="n">
         <v>1409.944064008135</v>
@@ -23201,13 +23201,13 @@
         <v>369.4855438232422</v>
       </c>
       <c r="E296" t="n">
-        <v>380.6355094401042</v>
+        <v>380.6355096435547</v>
       </c>
       <c r="F296" t="n">
-        <v>370.7194253540039</v>
+        <v>370.7194248962402</v>
       </c>
       <c r="G296" t="n">
-        <v>3.074776485843778</v>
+        <v>3.07477644602725</v>
       </c>
       <c r="H296" t="n">
         <v>443.3731066930094</v>
@@ -23361,7 +23361,7 @@
         <v>286.6520795440674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.142630757927421</v>
+        <v>1.142630676245759</v>
       </c>
       <c r="H298" t="n">
         <v>359.3387168134344</v>
@@ -23666,10 +23666,10 @@
         <v>1108.906597900391</v>
       </c>
       <c r="F302" t="n">
-        <v>1073.691958007812</v>
+        <v>1073.69195892334</v>
       </c>
       <c r="G302" t="n">
-        <v>0.8264183714909334</v>
+        <v>0.8264181974119156</v>
       </c>
       <c r="H302" t="n">
         <v>1238.748718225596</v>
@@ -24051,10 +24051,10 @@
         <v>429.8133170572917</v>
       </c>
       <c r="F307" t="n">
-        <v>423.6363455200195</v>
+        <v>423.6363456726074</v>
       </c>
       <c r="G307" t="n">
-        <v>1.493192357723583</v>
+        <v>1.493192468484605</v>
       </c>
       <c r="H307" t="n">
         <v>478.7148398145708</v>
@@ -24128,10 +24128,10 @@
         <v>464.7483414713542</v>
       </c>
       <c r="F308" t="n">
-        <v>459.3043811035157</v>
+        <v>459.3043795776367</v>
       </c>
       <c r="G308" t="n">
-        <v>1.746441834102952</v>
+        <v>1.74644184000623</v>
       </c>
       <c r="H308" t="n">
         <v>529.9163379046904</v>
@@ -24205,10 +24205,10 @@
         <v>1384.64213297526</v>
       </c>
       <c r="F309" t="n">
-        <v>1359.478229980469</v>
+        <v>1359.478231201172</v>
       </c>
       <c r="G309" t="n">
-        <v>1.109781708827406</v>
+        <v>1.109781616023753</v>
       </c>
       <c r="H309" t="n">
         <v>1553</v>
@@ -24282,19 +24282,19 @@
         <v>1840.429207356771</v>
       </c>
       <c r="F310" t="n">
-        <v>1804.013621826172</v>
+        <v>1804.013622436524</v>
       </c>
       <c r="G310" t="n">
-        <v>0.5137895084453392</v>
+        <v>0.5137895424521366</v>
       </c>
       <c r="H310" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I310" t="n">
-        <v>1569.365993709292</v>
+        <v>1569.36587206911</v>
       </c>
       <c r="J310" t="n">
-        <v>14.75971871565962</v>
+        <v>14.7597276105855</v>
       </c>
       <c r="K310" t="n">
         <v>13.65352717457315</v>
@@ -25825,7 +25825,7 @@
         <v>743.9646484375</v>
       </c>
       <c r="G330" t="n">
-        <v>-0.2579593800999147</v>
+        <v>-0.2579592576733791</v>
       </c>
       <c r="H330" t="n">
         <v>879.2203373423794</v>
@@ -25899,13 +25899,13 @@
         <v>742.1065291341146</v>
       </c>
       <c r="F331" t="n">
-        <v>757.6658087158203</v>
+        <v>757.6658099365235</v>
       </c>
       <c r="G331" t="n">
-        <v>-1.735075912817208</v>
+        <v>-1.73507591007025</v>
       </c>
       <c r="H331" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I331" t="n">
         <v>612.1496526863262</v>
@@ -25914,7 +25914,7 @@
         <v>27.31363518150798</v>
       </c>
       <c r="K331" t="n">
-        <v>43.3963509287129</v>
+        <v>43.39633493491082</v>
       </c>
       <c r="L331" t="n">
         <v>49.51590594744122</v>
@@ -26130,10 +26130,10 @@
         <v>36821.1171484375</v>
       </c>
       <c r="F334" t="n">
-        <v>36135.06513671875</v>
+        <v>36135.065078125</v>
       </c>
       <c r="G334" t="n">
-        <v>-0.4669435662921106</v>
+        <v>-0.4669437812341193</v>
       </c>
       <c r="H334" t="n">
         <v>43614.20556091995</v>
@@ -28671,10 +28671,10 @@
         <v>1675.677440592448</v>
       </c>
       <c r="F367" t="n">
-        <v>1681.507031860352</v>
+        <v>1681.507033081055</v>
       </c>
       <c r="G367" t="n">
-        <v>0.3794606445346904</v>
+        <v>0.3794606808320555</v>
       </c>
       <c r="H367" t="n">
         <v>1952.5</v>
@@ -29204,25 +29204,25 @@
         <v>209.4799957275391</v>
       </c>
       <c r="D374" t="n">
-        <v>211.976411743164</v>
+        <v>211.9764120483399</v>
       </c>
       <c r="E374" t="n">
-        <v>207.4759895833333</v>
+        <v>207.4759891764323</v>
       </c>
       <c r="F374" t="n">
-        <v>211.2830107116699</v>
+        <v>211.2830104064941</v>
       </c>
       <c r="G374" t="n">
-        <v>-1.198869888606802</v>
+        <v>-1.198869855068485</v>
       </c>
       <c r="H374" t="n">
         <v>252.6160882566492</v>
       </c>
       <c r="I374" t="n">
-        <v>171.6534204603822</v>
+        <v>171.6534052563282</v>
       </c>
       <c r="J374" t="n">
-        <v>22.03659860998066</v>
+        <v>22.03660941926833</v>
       </c>
       <c r="K374" t="n">
         <v>20.59198654234042</v>
@@ -29284,13 +29284,13 @@
         <v>746.3871228027343</v>
       </c>
       <c r="E375" t="n">
-        <v>739.9505952962239</v>
+        <v>739.9505973307291</v>
       </c>
       <c r="F375" t="n">
-        <v>735.0230816650391</v>
+        <v>735.0230828857422</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.7645629132528087</v>
+        <v>-0.7645627075589689</v>
       </c>
       <c r="H375" t="n">
         <v>837.8765073351432</v>
@@ -29364,19 +29364,19 @@
         <v>340.9885599772135</v>
       </c>
       <c r="F376" t="n">
-        <v>334.9584970092773</v>
+        <v>334.9584976196289</v>
       </c>
       <c r="G376" t="n">
-        <v>0.01938842038700095</v>
+        <v>0.01938837477972744</v>
       </c>
       <c r="H376" t="n">
         <v>385.3928663983843</v>
       </c>
       <c r="I376" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J376" t="n">
-        <v>10.35803269939986</v>
+        <v>10.3580209487518</v>
       </c>
       <c r="K376" t="n">
         <v>23.54314836269711</v>
@@ -29826,10 +29826,10 @@
         <v>775.2456490071614</v>
       </c>
       <c r="F382" t="n">
-        <v>787.6186895751953</v>
+        <v>787.6186874389648</v>
       </c>
       <c r="G382" t="n">
-        <v>-1.071270025254634</v>
+        <v>-1.071270066050001</v>
       </c>
       <c r="H382" t="n">
         <v>1100.079694414754</v>
@@ -30519,19 +30519,19 @@
         <v>519.6711169433594</v>
       </c>
       <c r="F391" t="n">
-        <v>526.4788571166993</v>
+        <v>526.4788578796387</v>
       </c>
       <c r="G391" t="n">
-        <v>3.429071155087748</v>
+        <v>3.429071149948149</v>
       </c>
       <c r="H391" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I391" t="n">
-        <v>306.8419898026673</v>
+        <v>306.8420198526935</v>
       </c>
       <c r="J391" t="n">
-        <v>50.61497749825472</v>
+        <v>50.6149627480454</v>
       </c>
       <c r="K391" t="n">
         <v>63.57572648378395</v>
@@ -30750,10 +30750,10 @@
         <v>159.8523378499349</v>
       </c>
       <c r="F394" t="n">
-        <v>156.3419974517822</v>
+        <v>156.3419976806641</v>
       </c>
       <c r="G394" t="n">
-        <v>1.174316713849066</v>
+        <v>1.174316662157437</v>
       </c>
       <c r="H394" t="n">
         <v>203.5447632528218</v>
@@ -30827,10 +30827,10 @@
         <v>580.927992553711</v>
       </c>
       <c r="F395" t="n">
-        <v>561.7571766662597</v>
+        <v>561.7571769714356</v>
       </c>
       <c r="G395" t="n">
-        <v>0.4895418364593063</v>
+        <v>0.4895417813336689</v>
       </c>
       <c r="H395" t="n">
         <v>784.8771245029434</v>
@@ -30904,10 +30904,10 @@
         <v>1364.227882486979</v>
       </c>
       <c r="F396" t="n">
-        <v>1364.679156494141</v>
+        <v>1364.679159545899</v>
       </c>
       <c r="G396" t="n">
-        <v>-0.09496082289986996</v>
+        <v>-0.09496073340768962</v>
       </c>
       <c r="H396" t="n">
         <v>1563.400024414062</v>
@@ -33214,10 +33214,10 @@
         <v>294.2938744099935</v>
       </c>
       <c r="F426" t="n">
-        <v>284.3707415008545</v>
+        <v>284.3707416534424</v>
       </c>
       <c r="G426" t="n">
-        <v>0.9940463538638866</v>
+        <v>0.9940462712299647</v>
       </c>
       <c r="H426" t="n">
         <v>387.4363949219129</v>
@@ -33599,10 +33599,10 @@
         <v>1144.046669514974</v>
       </c>
       <c r="F431" t="n">
-        <v>1163.140917663574</v>
+        <v>1163.140920104981</v>
       </c>
       <c r="G431" t="n">
-        <v>-0.582938887664608</v>
+        <v>-0.5829390420414415</v>
       </c>
       <c r="H431" t="n">
         <v>1378.852549646065</v>
@@ -34058,13 +34058,13 @@
         <v>500.2044964599609</v>
       </c>
       <c r="E437" t="n">
-        <v>484.4513659667969</v>
+        <v>484.4513675944011</v>
       </c>
       <c r="F437" t="n">
-        <v>489.7094738769531</v>
+        <v>489.7094758605957</v>
       </c>
       <c r="G437" t="n">
-        <v>-0.460158935551902</v>
+        <v>-0.4601589336965306</v>
       </c>
       <c r="H437" t="n">
         <v>547.7379722645398</v>
@@ -34754,10 +34754,10 @@
         <v>401.0061218261719</v>
       </c>
       <c r="F446" t="n">
-        <v>392.6871342468262</v>
+        <v>392.6871354675293</v>
       </c>
       <c r="G446" t="n">
-        <v>0.02668441254622955</v>
+        <v>0.0266845290975759</v>
       </c>
       <c r="H446" t="n">
         <v>476.8288845013619</v>
@@ -35370,13 +35370,13 @@
         <v>5419.410013020834</v>
       </c>
       <c r="F454" t="n">
-        <v>5462.95017578125</v>
+        <v>5462.950168457031</v>
       </c>
       <c r="G454" t="n">
-        <v>-0.7602441271204796</v>
+        <v>-0.7602440401053512</v>
       </c>
       <c r="H454" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I454" t="n">
         <v>5051</v>
@@ -35385,7 +35385,7 @@
         <v>3.345872104533765</v>
       </c>
       <c r="K454" t="n">
-        <v>12.55813059984443</v>
+        <v>12.55812113412642</v>
       </c>
       <c r="L454" t="n">
         <v>50.89903181189488</v>
@@ -35524,10 +35524,10 @@
         <v>1417.601162109375</v>
       </c>
       <c r="F456" t="n">
-        <v>1404.480870361328</v>
+        <v>1404.48087097168</v>
       </c>
       <c r="G456" t="n">
-        <v>-0.06927581998892318</v>
+        <v>-0.06927590675335216</v>
       </c>
       <c r="H456" t="n">
         <v>1817.803954384172</v>
@@ -35675,22 +35675,22 @@
         <v>226.836159362793</v>
       </c>
       <c r="E458" t="n">
-        <v>223.7274625651042</v>
+        <v>223.7274620564779</v>
       </c>
       <c r="F458" t="n">
-        <v>225.0226390075684</v>
+        <v>225.0226384735107</v>
       </c>
       <c r="G458" t="n">
-        <v>-1.311985696667184</v>
+        <v>-1.311985732761312</v>
       </c>
       <c r="H458" t="n">
         <v>286.0804190389319</v>
       </c>
       <c r="I458" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J458" t="n">
-        <v>18.36386358052404</v>
+        <v>18.36385315079703</v>
       </c>
       <c r="K458" t="n">
         <v>40.55933806060244</v>
@@ -35829,22 +35829,22 @@
         <v>2284.207465820312</v>
       </c>
       <c r="E460" t="n">
-        <v>2216.432093912761</v>
+        <v>2216.432121582031</v>
       </c>
       <c r="F460" t="n">
-        <v>2271.937647094726</v>
+        <v>2271.937672729492</v>
       </c>
       <c r="G460" t="n">
-        <v>-0.6063490111040126</v>
+        <v>-0.6063488450639087</v>
       </c>
       <c r="H460" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I460" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J460" t="n">
-        <v>6.129359439564164</v>
+        <v>6.129352853792192</v>
       </c>
       <c r="K460" t="n">
         <v>32.72759799183411</v>
@@ -36063,10 +36063,10 @@
         <v>1244.366759847005</v>
       </c>
       <c r="F463" t="n">
-        <v>1322.385424499512</v>
+        <v>1322.385425109863</v>
       </c>
       <c r="G463" t="n">
-        <v>-2.662996638722548</v>
+        <v>-2.662996856175404</v>
       </c>
       <c r="H463" t="n">
         <v>1729.008500794829</v>
@@ -37603,13 +37603,13 @@
         <v>419.1763724772135</v>
       </c>
       <c r="F483" t="n">
-        <v>437.5290629577637</v>
+        <v>437.5290618896485</v>
       </c>
       <c r="G483" t="n">
-        <v>-2.468049717358922</v>
+        <v>-2.468049723235333</v>
       </c>
       <c r="H483" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I483" t="n">
         <v>363.2227809620478</v>
@@ -37618,7 +37618,7 @@
         <v>11.43298857190658</v>
       </c>
       <c r="K483" t="n">
-        <v>31.86133531879123</v>
+        <v>31.86135103228087</v>
       </c>
       <c r="L483" t="n">
         <v>34.85477178423236</v>
@@ -38065,13 +38065,13 @@
         <v>612.7990930175781</v>
       </c>
       <c r="F489" t="n">
-        <v>618.0226489257813</v>
+        <v>618.0226507568359</v>
       </c>
       <c r="G489" t="n">
-        <v>-1.654526492548092</v>
+        <v>-1.654526535486145</v>
       </c>
       <c r="H489" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263661382125</v>
       </c>
       <c r="I489" t="n">
         <v>495.5999980879241</v>
@@ -38080,7 +38080,7 @@
         <v>19.01734823681185</v>
       </c>
       <c r="K489" t="n">
-        <v>43.90544689979423</v>
+        <v>43.90546770727867</v>
       </c>
       <c r="L489" t="n">
         <v>33.60995850622407</v>
@@ -40298,13 +40298,13 @@
         <v>1636.026534016927</v>
       </c>
       <c r="F518" t="n">
-        <v>1720.307622680664</v>
+        <v>1720.30762512207</v>
       </c>
       <c r="G518" t="n">
-        <v>-3.471929494258486</v>
+        <v>-3.471929621735703</v>
       </c>
       <c r="H518" t="n">
-        <v>2339.80156593166</v>
+        <v>2339.801318384509</v>
       </c>
       <c r="I518" t="n">
         <v>1322.972836511248</v>
@@ -40313,7 +40313,7 @@
         <v>17.5836670757459</v>
       </c>
       <c r="K518" t="n">
-        <v>50.41151984142598</v>
+        <v>50.41150392813496</v>
       </c>
       <c r="L518" t="n">
         <v>24.20470262793914</v>
@@ -40837,10 +40837,10 @@
         <v>1974.109081217448</v>
       </c>
       <c r="F525" t="n">
-        <v>2052.644563598633</v>
+        <v>2052.64456237793</v>
       </c>
       <c r="G525" t="n">
-        <v>-1.956366149894373</v>
+        <v>-1.95636626536636</v>
       </c>
       <c r="H525" t="n">
         <v>2486.766809421043</v>
@@ -40985,19 +40985,19 @@
         <v>474.8999938964844</v>
       </c>
       <c r="D527" t="n">
-        <v>454.6921661376953</v>
+        <v>454.6921655273438</v>
       </c>
       <c r="E527" t="n">
-        <v>493.8540329996745</v>
+        <v>493.8540364583333</v>
       </c>
       <c r="F527" t="n">
-        <v>503.4209552001953</v>
+        <v>503.4209580993652</v>
       </c>
       <c r="G527" t="n">
-        <v>-3.660040262675024</v>
+        <v>-3.660040186104396</v>
       </c>
       <c r="H527" t="n">
-        <v>758.5896367271307</v>
+        <v>758.589574672296</v>
       </c>
       <c r="I527" t="n">
         <v>400.6499938964844</v>
@@ -41006,7 +41006,7 @@
         <v>18.53238515690179</v>
       </c>
       <c r="K527" t="n">
-        <v>59.73671225030235</v>
+        <v>59.73669918337552</v>
       </c>
       <c r="L527" t="n">
         <v>19.36376210235132</v>
@@ -42528,22 +42528,22 @@
         <v>428.3811437988281</v>
       </c>
       <c r="E547" t="n">
-        <v>461.9676641845703</v>
+        <v>461.9676647949219</v>
       </c>
       <c r="F547" t="n">
-        <v>464.6142266845703</v>
+        <v>464.6142265319824</v>
       </c>
       <c r="G547" t="n">
-        <v>-1.122910779367547</v>
+        <v>-1.122910747623773</v>
       </c>
       <c r="H547" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I547" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J547" t="n">
-        <v>11.99769985607422</v>
+        <v>11.99771780081735</v>
       </c>
       <c r="K547" t="n">
         <v>30.53944613225463</v>
@@ -42608,10 +42608,10 @@
         <v>4614.810343424479</v>
       </c>
       <c r="F548" t="n">
-        <v>4757.492152099609</v>
+        <v>4757.492147216797</v>
       </c>
       <c r="G548" t="n">
-        <v>-0.1686207540290918</v>
+        <v>-0.1686207542018647</v>
       </c>
       <c r="H548" t="n">
         <v>5612.405266256894</v>
@@ -42916,10 +42916,10 @@
         <v>2610.10595703125</v>
       </c>
       <c r="F552" t="n">
-        <v>2683.637614746094</v>
+        <v>2683.637612304688</v>
       </c>
       <c r="G552" t="n">
-        <v>-1.406833015026432</v>
+        <v>-1.40683275099206</v>
       </c>
       <c r="H552" t="n">
         <v>3198.009229338596</v>
@@ -44077,7 +44077,7 @@
         <v>-1.957628234486752</v>
       </c>
       <c r="H567" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I567" t="n">
         <v>185.2067002350832</v>
@@ -44086,7 +44086,7 @@
         <v>19.147956250421</v>
       </c>
       <c r="K567" t="n">
-        <v>39.60876203060204</v>
+        <v>39.60877652129267</v>
       </c>
       <c r="L567" t="n">
         <v>30.01383125864454</v>
@@ -44228,7 +44228,7 @@
         <v>850.3161874389648</v>
       </c>
       <c r="G569" t="n">
-        <v>-1.451719278137409</v>
+        <v>-1.451719208426983</v>
       </c>
       <c r="H569" t="n">
         <v>962.6932158005569</v>
@@ -45383,10 +45383,10 @@
         <v>7767.988981933594</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.307047366891056</v>
+        <v>-1.3070473362782</v>
       </c>
       <c r="H584" t="n">
-        <v>9653.120359649309</v>
+        <v>9653.121370296873</v>
       </c>
       <c r="I584" t="n">
         <v>6860</v>
@@ -45395,7 +45395,7 @@
         <v>0.5685131195335202</v>
       </c>
       <c r="K584" t="n">
-        <v>39.92057341135396</v>
+        <v>39.92058806054315</v>
       </c>
       <c r="L584" t="n">
         <v>24.61964038727524</v>
@@ -45611,10 +45611,10 @@
         <v>903.8792028808593</v>
       </c>
       <c r="F587" t="n">
-        <v>918.1916235351563</v>
+        <v>918.1916259765625</v>
       </c>
       <c r="G587" t="n">
-        <v>-0.9223955645132453</v>
+        <v>-0.9223955620833002</v>
       </c>
       <c r="H587" t="n">
         <v>1282.80960014975</v>
@@ -45685,16 +45685,16 @@
         <v>19.07729042053223</v>
       </c>
       <c r="E588" t="n">
-        <v>20.3373218536377</v>
+        <v>20.33732182820638</v>
       </c>
       <c r="F588" t="n">
-        <v>20.4378151512146</v>
+        <v>20.43781512260437</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.425172318294454</v>
+        <v>-1.425172229577698</v>
       </c>
       <c r="H588" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I588" t="n">
         <v>16.75</v>
@@ -45703,7 +45703,7 @@
         <v>1.49253731343284</v>
       </c>
       <c r="K588" t="n">
-        <v>40.20742499370795</v>
+        <v>40.2074132287443</v>
       </c>
       <c r="L588" t="n">
         <v>23.51313969571231</v>
@@ -46073,10 +46073,10 @@
         <v>338.0373254394531</v>
       </c>
       <c r="F593" t="n">
-        <v>340.9787957763672</v>
+        <v>340.9787965393066</v>
       </c>
       <c r="G593" t="n">
-        <v>-0.9496014191292979</v>
+        <v>-0.9496011975042018</v>
       </c>
       <c r="H593" t="n">
         <v>381.3442016302781</v>
@@ -46458,10 +46458,10 @@
         <v>155.0009510294596</v>
       </c>
       <c r="F598" t="n">
-        <v>160.2469892883301</v>
+        <v>160.2469891357422</v>
       </c>
       <c r="G598" t="n">
-        <v>-2.794175567928514</v>
+        <v>-2.794175660488329</v>
       </c>
       <c r="H598" t="n">
         <v>217.0279658924327</v>
@@ -46535,10 +46535,10 @@
         <v>120.7920108032227</v>
       </c>
       <c r="F599" t="n">
-        <v>123.4624349212646</v>
+        <v>123.4624348068237</v>
       </c>
       <c r="G599" t="n">
-        <v>-2.33738894428227</v>
+        <v>-2.337388946398222</v>
       </c>
       <c r="H599" t="n">
         <v>156.8181640954093</v>
@@ -47456,16 +47456,16 @@
         <v>2275.594011230469</v>
       </c>
       <c r="E611" t="n">
-        <v>2289.339604492187</v>
+        <v>2289.339594726563</v>
       </c>
       <c r="F611" t="n">
-        <v>2463.761953125</v>
+        <v>2463.761949462891</v>
       </c>
       <c r="G611" t="n">
-        <v>-3.793826580888759</v>
+        <v>-3.793826540455691</v>
       </c>
       <c r="H611" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I611" t="n">
         <v>1966.020518717901</v>
@@ -47474,7 +47474,7 @@
         <v>5.543150757814441</v>
       </c>
       <c r="K611" t="n">
-        <v>58.41742872046736</v>
+        <v>58.41741649975183</v>
       </c>
       <c r="L611" t="n">
         <v>18.53388658367912</v>
@@ -49230,13 +49230,13 @@
         <v>284.8430511474609</v>
       </c>
       <c r="F634" t="n">
-        <v>295.8404135131836</v>
+        <v>295.8404138183594</v>
       </c>
       <c r="G634" t="n">
-        <v>-4.30203380017764</v>
+        <v>-4.302033795930771</v>
       </c>
       <c r="H634" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I634" t="n">
         <v>254.6499938964844</v>
@@ -49245,7 +49245,7 @@
         <v>0.4908698330886807</v>
       </c>
       <c r="K634" t="n">
-        <v>58.87877059594568</v>
+        <v>58.87878269317524</v>
       </c>
       <c r="L634" t="n">
         <v>14.93775933609959</v>
@@ -49612,13 +49612,13 @@
         <v>183.2720919799805</v>
       </c>
       <c r="E639" t="n">
-        <v>191.803324991862</v>
+        <v>191.8033245849609</v>
       </c>
       <c r="F639" t="n">
-        <v>194.2098810577393</v>
+        <v>194.2098805999756</v>
       </c>
       <c r="G639" t="n">
-        <v>-2.644570752414166</v>
+        <v>-2.644570721248785</v>
       </c>
       <c r="H639" t="n">
         <v>239.2186883393384</v>
@@ -49692,13 +49692,13 @@
         <v>1216.165836588542</v>
       </c>
       <c r="F640" t="n">
-        <v>1258.708755493164</v>
+        <v>1258.708758544922</v>
       </c>
       <c r="G640" t="n">
-        <v>-2.642587456550738</v>
+        <v>-2.642587266467622</v>
       </c>
       <c r="H640" t="n">
-        <v>1507.849216441457</v>
+        <v>1507.849092404508</v>
       </c>
       <c r="I640" t="n">
         <v>1015.099975585938</v>
@@ -49707,7 +49707,7 @@
         <v>2.452962763563238</v>
       </c>
       <c r="K640" t="n">
-        <v>44.9855015809093</v>
+        <v>44.98548965427958</v>
       </c>
       <c r="L640" t="n">
         <v>14.10788381742739</v>
@@ -49997,13 +49997,13 @@
         <v>274.8549694824219</v>
       </c>
       <c r="E644" t="n">
-        <v>294.731100769043</v>
+        <v>294.7311009724935</v>
       </c>
       <c r="F644" t="n">
-        <v>306.1050765228272</v>
+        <v>306.105076828003</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.530043543466021</v>
+        <v>-2.530043446291974</v>
       </c>
       <c r="H644" t="n">
         <v>396.5816333492734</v>
@@ -50237,7 +50237,7 @@
         <v>-4.140166494617914</v>
       </c>
       <c r="H647" t="n">
-        <v>3416.47279164786</v>
+        <v>3416.473037850766</v>
       </c>
       <c r="I647" t="n">
         <v>1805.687062514093</v>
@@ -50246,7 +50246,7 @@
         <v>2.437459378841722</v>
       </c>
       <c r="K647" t="n">
-        <v>84.70416185518941</v>
+        <v>84.70417516561344</v>
       </c>
       <c r="L647" t="n">
         <v>12.44813278008299</v>
@@ -50533,16 +50533,16 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D651" t="n">
-        <v>87.33972213745118</v>
+        <v>87.33972198486327</v>
       </c>
       <c r="E651" t="n">
-        <v>92.12648625691732</v>
+        <v>92.12648600260417</v>
       </c>
       <c r="F651" t="n">
-        <v>95.23410873413086</v>
+        <v>95.23410854339599</v>
       </c>
       <c r="G651" t="n">
-        <v>-3.347737771900638</v>
+        <v>-3.347737778381032</v>
       </c>
       <c r="H651" t="n">
         <v>124.8273096544699</v>
@@ -51078,13 +51078,13 @@
         <v>184.6067252604167</v>
       </c>
       <c r="F658" t="n">
-        <v>197.7207248687744</v>
+        <v>197.720725479126</v>
       </c>
       <c r="G658" t="n">
-        <v>-4.078956602965</v>
+        <v>-4.078956484377983</v>
       </c>
       <c r="H658" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I658" t="n">
         <v>156.7899932861328</v>
@@ -51093,7 +51093,7 @@
         <v>1.63276543593629</v>
       </c>
       <c r="K658" t="n">
-        <v>65.18386458646501</v>
+        <v>65.18388376795374</v>
       </c>
       <c r="L658" t="n">
         <v>10.65006915629322</v>
@@ -52233,13 +52233,13 @@
         <v>254.8142333984375</v>
       </c>
       <c r="F673" t="n">
-        <v>264.1078338623047</v>
+        <v>264.1078344726562</v>
       </c>
       <c r="G673" t="n">
-        <v>-3.590627161497062</v>
+        <v>-3.590627153497095</v>
       </c>
       <c r="H673" t="n">
-        <v>355.6598900030953</v>
+        <v>355.6599215623946</v>
       </c>
       <c r="I673" t="n">
         <v>212</v>
@@ -52248,7 +52248,7 @@
         <v>2.127355899450922</v>
       </c>
       <c r="K673" t="n">
-        <v>64.26950211384626</v>
+        <v>64.2695166902169</v>
       </c>
       <c r="L673" t="n">
         <v>8.298755186721991</v>
@@ -52387,10 +52387,10 @@
         <v>130.6906094868978</v>
       </c>
       <c r="F675" t="n">
-        <v>137.5798369979858</v>
+        <v>137.5798371505737</v>
       </c>
       <c r="G675" t="n">
-        <v>-3.471468726405846</v>
+        <v>-3.471468774360331</v>
       </c>
       <c r="H675" t="n">
         <v>183.7853835258596</v>
@@ -52464,10 +52464,10 @@
         <v>2733.925447591146</v>
       </c>
       <c r="F676" t="n">
-        <v>2843.300618896485</v>
+        <v>2843.300615234375</v>
       </c>
       <c r="G676" t="n">
-        <v>-3.815094415877551</v>
+        <v>-3.815094460323121</v>
       </c>
       <c r="H676" t="n">
         <v>3812.926349899466</v>
@@ -52618,10 +52618,10 @@
         <v>490.9401304117839</v>
       </c>
       <c r="F678" t="n">
-        <v>530.7262626647949</v>
+        <v>530.7262623596191</v>
       </c>
       <c r="G678" t="n">
-        <v>-5.31875884909806</v>
+        <v>-5.318758851993777</v>
       </c>
       <c r="H678" t="n">
         <v>799.7128098861871</v>
@@ -52778,7 +52778,7 @@
         <v>-4.501495703494141</v>
       </c>
       <c r="H680" t="n">
-        <v>605.9581737112406</v>
+        <v>605.9581114957105</v>
       </c>
       <c r="I680" t="n">
         <v>326.057353105007</v>
@@ -52787,7 +52787,7 @@
         <v>8.922553199439132</v>
       </c>
       <c r="K680" t="n">
-        <v>70.62035312546264</v>
+        <v>70.62033560736289</v>
       </c>
       <c r="L680" t="n">
         <v>6.915629322268327</v>
@@ -53311,13 +53311,13 @@
         <v>506.6396004231771</v>
       </c>
       <c r="F687" t="n">
-        <v>532.6432237243653</v>
+        <v>532.6432243347168</v>
       </c>
       <c r="G687" t="n">
-        <v>-3.722140730158774</v>
+        <v>-3.722140672943564</v>
       </c>
       <c r="H687" t="n">
-        <v>798.1970003242409</v>
+        <v>798.1971250028588</v>
       </c>
       <c r="I687" t="n">
         <v>406.117116732523</v>
@@ -53326,7 +53326,7 @@
         <v>7.456685748093261</v>
       </c>
       <c r="K687" t="n">
-        <v>82.90490639043777</v>
+        <v>82.90493496024062</v>
       </c>
       <c r="L687" t="n">
         <v>5.670816044260028</v>
@@ -53388,10 +53388,10 @@
         <v>274.7847361246745</v>
       </c>
       <c r="F688" t="n">
-        <v>287.0204006958008</v>
+        <v>287.0204014587403</v>
       </c>
       <c r="G688" t="n">
-        <v>-4.206596479181846</v>
+        <v>-4.206596468470503</v>
       </c>
       <c r="H688" t="n">
         <v>385.6351549871131</v>
@@ -55005,10 +55005,10 @@
         <v>349.3346988932292</v>
       </c>
       <c r="F709" t="n">
-        <v>354.0541575622559</v>
+        <v>354.0541578674316</v>
       </c>
       <c r="G709" t="n">
-        <v>-3.027007714632712</v>
+        <v>-3.027007590519482</v>
       </c>
       <c r="H709" t="n">
         <v>487.9415273208757</v>
@@ -55698,10 +55698,10 @@
         <v>653.3433640543619</v>
       </c>
       <c r="F718" t="n">
-        <v>752.2278590393066</v>
+        <v>752.2278617858886</v>
       </c>
       <c r="G718" t="n">
-        <v>-8.816885821480714</v>
+        <v>-8.816885859588385</v>
       </c>
       <c r="H718" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1644,10 +1644,10 @@
         <v>1920.759659016927</v>
       </c>
       <c r="F16" t="n">
-        <v>1750.461966552734</v>
+        <v>1750.461968383789</v>
       </c>
       <c r="G16" t="n">
-        <v>7.13058029594138</v>
+        <v>7.130580087861138</v>
       </c>
       <c r="H16" t="n">
         <v>2714.261178227147</v>
@@ -2568,10 +2568,10 @@
         <v>655.1678442382813</v>
       </c>
       <c r="F28" t="n">
-        <v>614.6078901672363</v>
+        <v>614.6078900146484</v>
       </c>
       <c r="G28" t="n">
-        <v>5.836161815942442</v>
+        <v>5.836161650620131</v>
       </c>
       <c r="H28" t="n">
         <v>844</v>
@@ -2796,13 +2796,13 @@
         <v>11615.185703125</v>
       </c>
       <c r="E31" t="n">
-        <v>10869.85709635417</v>
+        <v>10869.85706380208</v>
       </c>
       <c r="F31" t="n">
-        <v>10437.05026367188</v>
+        <v>10437.05025146484</v>
       </c>
       <c r="G31" t="n">
-        <v>3.312993408920728</v>
+        <v>3.312993512793239</v>
       </c>
       <c r="H31" t="n">
         <v>13996</v>
@@ -2873,13 +2873,13 @@
         <v>1352.878703613281</v>
       </c>
       <c r="E32" t="n">
-        <v>1182.01328125</v>
+        <v>1182.013286132812</v>
       </c>
       <c r="F32" t="n">
-        <v>1074.562542419434</v>
+        <v>1074.562547912598</v>
       </c>
       <c r="G32" t="n">
-        <v>8.451235548377323</v>
+        <v>8.451235334507711</v>
       </c>
       <c r="H32" t="n">
         <v>1675</v>
@@ -3726,7 +3726,7 @@
         <v>225.895284576416</v>
       </c>
       <c r="G43" t="n">
-        <v>4.592414854606131</v>
+        <v>4.592414928500821</v>
       </c>
       <c r="H43" t="n">
         <v>321.3999938964844</v>
@@ -3880,7 +3880,7 @@
         <v>3637.369436035156</v>
       </c>
       <c r="G45" t="n">
-        <v>5.519297865542794</v>
+        <v>5.51929794027648</v>
       </c>
       <c r="H45" t="n">
         <v>4843</v>
@@ -4031,10 +4031,10 @@
         <v>559.3865700276692</v>
       </c>
       <c r="F47" t="n">
-        <v>536.4425758361816</v>
+        <v>536.4425765991211</v>
       </c>
       <c r="G47" t="n">
-        <v>5.563387452234969</v>
+        <v>5.563387317092872</v>
       </c>
       <c r="H47" t="n">
         <v>795.731978165477</v>
@@ -4179,16 +4179,16 @@
         <v>230.0700073242188</v>
       </c>
       <c r="D49" t="n">
-        <v>193.0581918334961</v>
+        <v>193.0581924438476</v>
       </c>
       <c r="E49" t="n">
-        <v>155.5897733561198</v>
+        <v>155.5897725931803</v>
       </c>
       <c r="F49" t="n">
-        <v>154.3818601989746</v>
+        <v>154.3818590164184</v>
       </c>
       <c r="G49" t="n">
-        <v>3.349296551965142</v>
+        <v>3.34929663126462</v>
       </c>
       <c r="H49" t="n">
         <v>235.75</v>
@@ -4256,16 +4256,16 @@
         <v>205.0899963378906</v>
       </c>
       <c r="D50" t="n">
-        <v>185.0763528442383</v>
+        <v>185.0763525390625</v>
       </c>
       <c r="E50" t="n">
-        <v>155.9071700541178</v>
+        <v>155.9071701558431</v>
       </c>
       <c r="F50" t="n">
-        <v>154.6964866256714</v>
+        <v>154.6964870071411</v>
       </c>
       <c r="G50" t="n">
-        <v>2.533514560926253</v>
+        <v>2.533514295274952</v>
       </c>
       <c r="H50" t="n">
         <v>233.3500061035156</v>
@@ -5186,10 +5186,10 @@
         <v>1028.362920735677</v>
       </c>
       <c r="F62" t="n">
-        <v>977.1574365234375</v>
+        <v>977.157437133789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.374546655993704</v>
+        <v>3.374546553691737</v>
       </c>
       <c r="H62" t="n">
         <v>1368.900024414062</v>
@@ -5725,10 +5725,10 @@
         <v>1651.839215494792</v>
       </c>
       <c r="F69" t="n">
-        <v>1591.834495849609</v>
+        <v>1591.834501342773</v>
       </c>
       <c r="G69" t="n">
-        <v>2.992658181545882</v>
+        <v>2.992657926878128</v>
       </c>
       <c r="H69" t="n">
         <v>2038.599975585938</v>
@@ -7339,13 +7339,13 @@
         <v>1044.189058837891</v>
       </c>
       <c r="E90" t="n">
-        <v>945.8509688313802</v>
+        <v>945.850966796875</v>
       </c>
       <c r="F90" t="n">
-        <v>918.3966180419922</v>
+        <v>918.3966165161132</v>
       </c>
       <c r="G90" t="n">
-        <v>3.279131410669622</v>
+        <v>3.279131487184794</v>
       </c>
       <c r="H90" t="n">
         <v>1148</v>
@@ -9199,10 +9199,10 @@
         <v>8949.5</v>
       </c>
       <c r="I114" t="n">
-        <v>4504.255799235611</v>
+        <v>4504.255320019595</v>
       </c>
       <c r="J114" t="n">
-        <v>80.64027361369652</v>
+        <v>80.64029283234777</v>
       </c>
       <c r="K114" t="n">
         <v>9.992011307073057</v>
@@ -9957,16 +9957,16 @@
         <v>1379.86162109375</v>
       </c>
       <c r="E124" t="n">
-        <v>1417.508198242188</v>
+        <v>1417.508199869792</v>
       </c>
       <c r="F124" t="n">
-        <v>1352.940920410156</v>
+        <v>1352.940922241211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.04363559948726</v>
+        <v>3.043635786846233</v>
       </c>
       <c r="H124" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I124" t="n">
         <v>951.4121987838871</v>
@@ -9975,7 +9975,7 @@
         <v>60.87663975113826</v>
       </c>
       <c r="K124" t="n">
-        <v>15.42749359347724</v>
+        <v>15.42748523656077</v>
       </c>
       <c r="L124" t="n">
         <v>87.96680497925311</v>
@@ -10419,13 +10419,13 @@
         <v>161.9043997192383</v>
       </c>
       <c r="E130" t="n">
-        <v>141.5105689493815</v>
+        <v>141.5105687967936</v>
       </c>
       <c r="F130" t="n">
-        <v>136.1924728393555</v>
+        <v>136.1924729156494</v>
       </c>
       <c r="G130" t="n">
-        <v>3.994774102656318</v>
+        <v>3.994774191205508</v>
       </c>
       <c r="H130" t="n">
         <v>173.2700042724609</v>
@@ -11038,10 +11038,10 @@
         <v>728.6689595540364</v>
       </c>
       <c r="F138" t="n">
-        <v>733.1653762817383</v>
+        <v>733.1653747558594</v>
       </c>
       <c r="G138" t="n">
-        <v>2.500909869555779</v>
+        <v>2.500909918623329</v>
       </c>
       <c r="H138" t="n">
         <v>1002.400024414062</v>
@@ -12193,10 +12193,10 @@
         <v>4595.71060546875</v>
       </c>
       <c r="F153" t="n">
-        <v>4441.25818359375</v>
+        <v>4441.258188476562</v>
       </c>
       <c r="G153" t="n">
-        <v>3.019674840582387</v>
+        <v>3.019674807991701</v>
       </c>
       <c r="H153" t="n">
         <v>5250</v>
@@ -13120,7 +13120,7 @@
         <v>1127.398363647461</v>
       </c>
       <c r="G165" t="n">
-        <v>3.508969281979146</v>
+        <v>3.508969194973011</v>
       </c>
       <c r="H165" t="n">
         <v>1596.696405272527</v>
@@ -13659,7 +13659,7 @@
         <v>126.1247621536255</v>
       </c>
       <c r="G172" t="n">
-        <v>1.261573585811004</v>
+        <v>1.261573616824374</v>
       </c>
       <c r="H172" t="n">
         <v>150.8288738594787</v>
@@ -14811,13 +14811,13 @@
         <v>1788.325852864583</v>
       </c>
       <c r="F187" t="n">
-        <v>1779.015999145508</v>
+        <v>1779.015993652344</v>
       </c>
       <c r="G187" t="n">
-        <v>1.541715758194906</v>
+        <v>1.541715798403165</v>
       </c>
       <c r="H187" t="n">
-        <v>2256.187656125729</v>
+        <v>2256.187906504501</v>
       </c>
       <c r="I187" t="n">
         <v>1345.285007075603</v>
@@ -14826,7 +14826,7 @@
         <v>45.86500544548524</v>
       </c>
       <c r="K187" t="n">
-        <v>14.97669061737585</v>
+        <v>14.97670337682986</v>
       </c>
       <c r="L187" t="n">
         <v>61.82572614107884</v>
@@ -15655,13 +15655,13 @@
         <v>7354.229365234375</v>
       </c>
       <c r="E198" t="n">
-        <v>6929.847994791667</v>
+        <v>6929.848001302084</v>
       </c>
       <c r="F198" t="n">
-        <v>6517.9157421875</v>
+        <v>6517.915737304687</v>
       </c>
       <c r="G198" t="n">
-        <v>3.671720312188187</v>
+        <v>3.671720234523868</v>
       </c>
       <c r="H198" t="n">
         <v>7832.294844565128</v>
@@ -17198,10 +17198,10 @@
         <v>1020.105819905599</v>
       </c>
       <c r="F218" t="n">
-        <v>991.6384942626953</v>
+        <v>991.6384948730469</v>
       </c>
       <c r="G218" t="n">
-        <v>1.014524796065608</v>
+        <v>1.014524638422309</v>
       </c>
       <c r="H218" t="n">
         <v>1331.075409591023</v>
@@ -17580,13 +17580,13 @@
         <v>1824.515993652344</v>
       </c>
       <c r="E223" t="n">
-        <v>1713.930034993489</v>
+        <v>1713.930037434896</v>
       </c>
       <c r="F223" t="n">
-        <v>1683.062271118164</v>
+        <v>1683.062272338867</v>
       </c>
       <c r="G223" t="n">
-        <v>0.9732295785435108</v>
+        <v>0.9732296148044162</v>
       </c>
       <c r="H223" t="n">
         <v>1983.954544928268</v>
@@ -18122,10 +18122,10 @@
         <v>165.7066747029622</v>
       </c>
       <c r="F230" t="n">
-        <v>164.9557037353516</v>
+        <v>164.9557038116455</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1915715513773231</v>
+        <v>0.1915716441456716</v>
       </c>
       <c r="H230" t="n">
         <v>181.8519567776652</v>
@@ -20586,10 +20586,10 @@
         <v>284.540832824707</v>
       </c>
       <c r="F262" t="n">
-        <v>270.4716156768799</v>
+        <v>270.4716150665283</v>
       </c>
       <c r="G262" t="n">
-        <v>2.087910351914224</v>
+        <v>2.087910268530369</v>
       </c>
       <c r="H262" t="n">
         <v>367.499792159746</v>
@@ -20743,7 +20743,7 @@
         <v>4984.521378173828</v>
       </c>
       <c r="G264" t="n">
-        <v>1.366350826259199</v>
+        <v>1.366350675277106</v>
       </c>
       <c r="H264" t="n">
         <v>6049.821052103703</v>
@@ -21122,16 +21122,16 @@
         <v>4557.957587890625</v>
       </c>
       <c r="E269" t="n">
-        <v>4236.718463541667</v>
+        <v>4236.71845703125</v>
       </c>
       <c r="F269" t="n">
         <v>4305.386689453125</v>
       </c>
       <c r="G269" t="n">
-        <v>0.4891431560709814</v>
+        <v>0.4891434996427302</v>
       </c>
       <c r="H269" t="n">
-        <v>5005.771680286142</v>
+        <v>5005.771184298104</v>
       </c>
       <c r="I269" t="n">
         <v>3669.905008549105</v>
@@ -21140,7 +21140,7 @@
         <v>20.67342580638332</v>
       </c>
       <c r="K269" t="n">
-        <v>13.03282233442908</v>
+        <v>13.03281113477171</v>
       </c>
       <c r="L269" t="n">
         <v>65.97510373443983</v>
@@ -21433,10 +21433,10 @@
         <v>525.7173842366536</v>
       </c>
       <c r="F273" t="n">
-        <v>533.8989057922363</v>
+        <v>533.8989073181152</v>
       </c>
       <c r="G273" t="n">
-        <v>-1.148820283452823</v>
+        <v>-1.148820503623449</v>
       </c>
       <c r="H273" t="n">
         <v>663.9000244140625</v>
@@ -21510,10 +21510,10 @@
         <v>312.6840242513021</v>
       </c>
       <c r="F274" t="n">
-        <v>309.5910679626465</v>
+        <v>309.5910678100586</v>
       </c>
       <c r="G274" t="n">
-        <v>1.625423583889352</v>
+        <v>1.625423584703478</v>
       </c>
       <c r="H274" t="n">
         <v>380.4567148307952</v>
@@ -21664,13 +21664,13 @@
         <v>5124.110989583333</v>
       </c>
       <c r="F276" t="n">
-        <v>5336.029033203125</v>
+        <v>5336.029035644531</v>
       </c>
       <c r="G276" t="n">
-        <v>-1.687376342093505</v>
+        <v>-1.687376385556716</v>
       </c>
       <c r="H276" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I276" t="n">
         <v>4229.809203861739</v>
@@ -21679,7 +21679,7 @@
         <v>26.88515583870843</v>
       </c>
       <c r="K276" t="n">
-        <v>22.0915727128898</v>
+        <v>22.09156346082197</v>
       </c>
       <c r="L276" t="n">
         <v>60.44260027662517</v>
@@ -21821,7 +21821,7 @@
         <v>1139.700042724609</v>
       </c>
       <c r="G278" t="n">
-        <v>-0.6979069257844417</v>
+        <v>-0.6979069785932324</v>
       </c>
       <c r="H278" t="n">
         <v>1409.944064008135</v>
@@ -22588,10 +22588,10 @@
         <v>10436.77192708333</v>
       </c>
       <c r="F288" t="n">
-        <v>10530.33325195312</v>
+        <v>10530.33323242188</v>
       </c>
       <c r="G288" t="n">
-        <v>-0.1544794396890814</v>
+        <v>-0.1544794862010201</v>
       </c>
       <c r="H288" t="n">
         <v>13011.97571177054</v>
@@ -23358,10 +23358,10 @@
         <v>298.9324642944336</v>
       </c>
       <c r="F298" t="n">
-        <v>286.6520795440674</v>
+        <v>286.6520799255371</v>
       </c>
       <c r="G298" t="n">
-        <v>1.142630676245759</v>
+        <v>1.142630756389496</v>
       </c>
       <c r="H298" t="n">
         <v>359.3387168134344</v>
@@ -23666,10 +23666,10 @@
         <v>1108.906597900391</v>
       </c>
       <c r="F302" t="n">
-        <v>1073.69195892334</v>
+        <v>1073.691958007812</v>
       </c>
       <c r="G302" t="n">
-        <v>0.8264181974119156</v>
+        <v>0.8264183714909334</v>
       </c>
       <c r="H302" t="n">
         <v>1238.748718225596</v>
@@ -24045,19 +24045,19 @@
         <v>420.3999938964844</v>
       </c>
       <c r="D307" t="n">
-        <v>411.6664556884766</v>
+        <v>411.666455078125</v>
       </c>
       <c r="E307" t="n">
-        <v>429.8133170572917</v>
+        <v>429.8133180745443</v>
       </c>
       <c r="F307" t="n">
-        <v>423.6363456726074</v>
+        <v>423.6363459777832</v>
       </c>
       <c r="G307" t="n">
-        <v>1.493192468484605</v>
+        <v>1.493192504495178</v>
       </c>
       <c r="H307" t="n">
-        <v>478.7148398145708</v>
+        <v>478.7148709533388</v>
       </c>
       <c r="I307" t="n">
         <v>355.1755291130353</v>
@@ -24066,7 +24066,7 @@
         <v>18.36400862028174</v>
       </c>
       <c r="K307" t="n">
-        <v>13.87127658532872</v>
+        <v>13.87128399226698</v>
       </c>
       <c r="L307" t="n">
         <v>63.90041493775933</v>
@@ -24128,10 +24128,10 @@
         <v>464.7483414713542</v>
       </c>
       <c r="F308" t="n">
-        <v>459.3043795776367</v>
+        <v>459.3043811035157</v>
       </c>
       <c r="G308" t="n">
-        <v>1.74644184000623</v>
+        <v>1.746441868494997</v>
       </c>
       <c r="H308" t="n">
         <v>529.9163379046904</v>
@@ -24205,10 +24205,10 @@
         <v>1384.64213297526</v>
       </c>
       <c r="F309" t="n">
-        <v>1359.478231201172</v>
+        <v>1359.478229980469</v>
       </c>
       <c r="G309" t="n">
-        <v>1.109781616023753</v>
+        <v>1.109781708827406</v>
       </c>
       <c r="H309" t="n">
         <v>1553</v>
@@ -24282,19 +24282,19 @@
         <v>1840.429207356771</v>
       </c>
       <c r="F310" t="n">
-        <v>1804.013622436524</v>
+        <v>1804.013621826172</v>
       </c>
       <c r="G310" t="n">
-        <v>0.5137895424521366</v>
+        <v>0.5137895084453392</v>
       </c>
       <c r="H310" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I310" t="n">
-        <v>1569.36587206911</v>
+        <v>1569.365993709292</v>
       </c>
       <c r="J310" t="n">
-        <v>14.7597276105855</v>
+        <v>14.75971871565962</v>
       </c>
       <c r="K310" t="n">
         <v>13.65352717457315</v>
@@ -25206,10 +25206,10 @@
         <v>199.9031264241536</v>
       </c>
       <c r="F322" t="n">
-        <v>206.3836766815186</v>
+        <v>206.3836763000488</v>
       </c>
       <c r="G322" t="n">
-        <v>-1.828100532768395</v>
+        <v>-1.828100749852457</v>
       </c>
       <c r="H322" t="n">
         <v>278.3389924341271</v>
@@ -25825,7 +25825,7 @@
         <v>743.9646484375</v>
       </c>
       <c r="G330" t="n">
-        <v>-0.2579592576733791</v>
+        <v>-0.2579593800999147</v>
       </c>
       <c r="H330" t="n">
         <v>879.2203373423794</v>
@@ -26127,22 +26127,22 @@
         <v>37037.87546875</v>
       </c>
       <c r="E334" t="n">
-        <v>36821.1171484375</v>
+        <v>36821.11716145834</v>
       </c>
       <c r="F334" t="n">
-        <v>36135.065078125</v>
+        <v>36135.06489257813</v>
       </c>
       <c r="G334" t="n">
-        <v>-0.4669437812341193</v>
+        <v>-0.4669437836205881</v>
       </c>
       <c r="H334" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I334" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J334" t="n">
-        <v>24.16480247955331</v>
+        <v>24.16481058574358</v>
       </c>
       <c r="K334" t="n">
         <v>18.96946415962888</v>
@@ -28209,10 +28209,10 @@
         <v>2155.73273844401</v>
       </c>
       <c r="F361" t="n">
-        <v>2094.977203979492</v>
+        <v>2094.977207641602</v>
       </c>
       <c r="G361" t="n">
-        <v>0.2647896250355775</v>
+        <v>0.2647895952829549</v>
       </c>
       <c r="H361" t="n">
         <v>2625.96691593483</v>
@@ -28366,7 +28366,7 @@
         <v>335.3150723266601</v>
       </c>
       <c r="G363" t="n">
-        <v>0.9717376797128807</v>
+        <v>0.971737726107369</v>
       </c>
       <c r="H363" t="n">
         <v>428.7550602808859</v>
@@ -29204,25 +29204,25 @@
         <v>209.4799957275391</v>
       </c>
       <c r="D374" t="n">
-        <v>211.9764120483399</v>
+        <v>211.976411743164</v>
       </c>
       <c r="E374" t="n">
-        <v>207.4759891764323</v>
+        <v>207.4759895833333</v>
       </c>
       <c r="F374" t="n">
-        <v>211.2830104064941</v>
+        <v>211.2830108642578</v>
       </c>
       <c r="G374" t="n">
-        <v>-1.198869855068485</v>
+        <v>-1.198869993498974</v>
       </c>
       <c r="H374" t="n">
         <v>252.6160882566492</v>
       </c>
       <c r="I374" t="n">
-        <v>171.6534052563282</v>
+        <v>171.6534204603822</v>
       </c>
       <c r="J374" t="n">
-        <v>22.03660941926833</v>
+        <v>22.03659860998066</v>
       </c>
       <c r="K374" t="n">
         <v>20.59198654234042</v>
@@ -29284,13 +29284,13 @@
         <v>746.3871228027343</v>
       </c>
       <c r="E375" t="n">
-        <v>739.9505973307291</v>
+        <v>739.9505952962239</v>
       </c>
       <c r="F375" t="n">
-        <v>735.0230828857422</v>
+        <v>735.0230813598632</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.7645627075589689</v>
+        <v>-0.7645629135678234</v>
       </c>
       <c r="H375" t="n">
         <v>837.8765073351432</v>
@@ -29364,19 +29364,19 @@
         <v>340.9885599772135</v>
       </c>
       <c r="F376" t="n">
-        <v>334.9584976196289</v>
+        <v>334.9584970092773</v>
       </c>
       <c r="G376" t="n">
-        <v>0.01938837477972744</v>
+        <v>0.01938842038700095</v>
       </c>
       <c r="H376" t="n">
         <v>385.3928663983843</v>
       </c>
       <c r="I376" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J376" t="n">
-        <v>10.3580209487518</v>
+        <v>10.35803269939986</v>
       </c>
       <c r="K376" t="n">
         <v>23.54314836269711</v>
@@ -30519,19 +30519,19 @@
         <v>519.6711169433594</v>
       </c>
       <c r="F391" t="n">
-        <v>526.4788578796387</v>
+        <v>526.4788571166993</v>
       </c>
       <c r="G391" t="n">
-        <v>3.429071149948149</v>
+        <v>3.429071155087748</v>
       </c>
       <c r="H391" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I391" t="n">
-        <v>306.8420198526935</v>
+        <v>306.8419898026673</v>
       </c>
       <c r="J391" t="n">
-        <v>50.6149627480454</v>
+        <v>50.61497749825472</v>
       </c>
       <c r="K391" t="n">
         <v>63.57572648378395</v>
@@ -30827,10 +30827,10 @@
         <v>580.927992553711</v>
       </c>
       <c r="F395" t="n">
-        <v>561.7571769714356</v>
+        <v>561.7571766662597</v>
       </c>
       <c r="G395" t="n">
-        <v>0.4895417813336689</v>
+        <v>0.4895418364593063</v>
       </c>
       <c r="H395" t="n">
         <v>784.8771245029434</v>
@@ -30904,10 +30904,10 @@
         <v>1364.227882486979</v>
       </c>
       <c r="F396" t="n">
-        <v>1364.679159545899</v>
+        <v>1364.679156494141</v>
       </c>
       <c r="G396" t="n">
-        <v>-0.09496073340768962</v>
+        <v>-0.09496082289986996</v>
       </c>
       <c r="H396" t="n">
         <v>1563.400024414062</v>
@@ -32598,13 +32598,13 @@
         <v>1079.739299723307</v>
       </c>
       <c r="F418" t="n">
-        <v>1080.149018249512</v>
+        <v>1080.149017333984</v>
       </c>
       <c r="G418" t="n">
-        <v>-0.785583701343695</v>
+        <v>-0.7855838132481696</v>
       </c>
       <c r="H418" t="n">
-        <v>1300.436795781491</v>
+        <v>1300.436668328248</v>
       </c>
       <c r="I418" t="n">
         <v>885.652283987356</v>
@@ -32613,7 +32613,7 @@
         <v>18.03729785548514</v>
       </c>
       <c r="K418" t="n">
-        <v>24.39609387902726</v>
+        <v>24.39608168721163</v>
       </c>
       <c r="L418" t="n">
         <v>44.67496542185339</v>
@@ -33445,19 +33445,19 @@
         <v>358.0823232014974</v>
       </c>
       <c r="F429" t="n">
-        <v>354.5846725463867</v>
+        <v>354.5846722412109</v>
       </c>
       <c r="G429" t="n">
-        <v>0.2876495383028921</v>
+        <v>0.2876494519896244</v>
       </c>
       <c r="H429" t="n">
         <v>409.9712889887167</v>
       </c>
       <c r="I429" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J429" t="n">
-        <v>1.698150729798686</v>
+        <v>1.698140847692242</v>
       </c>
       <c r="K429" t="n">
         <v>30.10830880594595</v>
@@ -34064,7 +34064,7 @@
         <v>489.7094758605957</v>
       </c>
       <c r="G437" t="n">
-        <v>-0.4601589336965306</v>
+        <v>-0.4601589954420615</v>
       </c>
       <c r="H437" t="n">
         <v>547.7379722645398</v>
@@ -34138,10 +34138,10 @@
         <v>77.41940338134765</v>
       </c>
       <c r="F438" t="n">
-        <v>77.33355308532715</v>
+        <v>77.33355300903321</v>
       </c>
       <c r="G438" t="n">
-        <v>-0.06809636032345523</v>
+        <v>-0.06809621260853715</v>
       </c>
       <c r="H438" t="n">
         <v>86.59303970157107</v>
@@ -34751,13 +34751,13 @@
         <v>365.9162872314453</v>
       </c>
       <c r="E446" t="n">
-        <v>401.0061218261719</v>
+        <v>401.006123046875</v>
       </c>
       <c r="F446" t="n">
-        <v>392.6871354675293</v>
+        <v>392.6871347045898</v>
       </c>
       <c r="G446" t="n">
-        <v>0.0266845290975759</v>
+        <v>0.02668456802756847</v>
       </c>
       <c r="H446" t="n">
         <v>476.8288845013619</v>
@@ -35370,13 +35370,13 @@
         <v>5419.410013020834</v>
       </c>
       <c r="F454" t="n">
-        <v>5462.950168457031</v>
+        <v>5462.95017578125</v>
       </c>
       <c r="G454" t="n">
-        <v>-0.7602440401053512</v>
+        <v>-0.7602441271204796</v>
       </c>
       <c r="H454" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I454" t="n">
         <v>5051</v>
@@ -35385,7 +35385,7 @@
         <v>3.345872104533765</v>
       </c>
       <c r="K454" t="n">
-        <v>12.55812113412642</v>
+        <v>12.55813059984443</v>
       </c>
       <c r="L454" t="n">
         <v>50.89903181189488</v>
@@ -35524,10 +35524,10 @@
         <v>1417.601162109375</v>
       </c>
       <c r="F456" t="n">
-        <v>1404.48087097168</v>
+        <v>1404.480870361328</v>
       </c>
       <c r="G456" t="n">
-        <v>-0.06927590675335216</v>
+        <v>-0.06927581998892318</v>
       </c>
       <c r="H456" t="n">
         <v>1817.803954384172</v>
@@ -35684,7 +35684,7 @@
         <v>-1.311985732761312</v>
       </c>
       <c r="H458" t="n">
-        <v>286.0804190389319</v>
+        <v>286.08038637852</v>
       </c>
       <c r="I458" t="n">
         <v>171.952833032562</v>
@@ -35693,7 +35693,7 @@
         <v>18.36385315079703</v>
       </c>
       <c r="K458" t="n">
-        <v>40.55933806060244</v>
+        <v>40.55932201362551</v>
       </c>
       <c r="L458" t="n">
         <v>45.08990318118949</v>
@@ -35832,10 +35832,10 @@
         <v>2216.432121582031</v>
       </c>
       <c r="F460" t="n">
-        <v>2271.937672729492</v>
+        <v>2271.937671508789</v>
       </c>
       <c r="G460" t="n">
-        <v>-0.6063488450639087</v>
+        <v>-0.6063489515477305</v>
       </c>
       <c r="H460" t="n">
         <v>2765.379504159864</v>
@@ -36063,10 +36063,10 @@
         <v>1244.366759847005</v>
       </c>
       <c r="F463" t="n">
-        <v>1322.385425109863</v>
+        <v>1322.385424499512</v>
       </c>
       <c r="G463" t="n">
-        <v>-2.662996856175404</v>
+        <v>-2.662996638722548</v>
       </c>
       <c r="H463" t="n">
         <v>1729.008500794829</v>
@@ -36140,10 +36140,10 @@
         <v>286.9126793416341</v>
       </c>
       <c r="F464" t="n">
-        <v>282.8162843322754</v>
+        <v>282.8162828826904</v>
       </c>
       <c r="G464" t="n">
-        <v>-0.0009976081297602413</v>
+        <v>-0.0009977160387530937</v>
       </c>
       <c r="H464" t="n">
         <v>323.4425459044702</v>
@@ -37603,13 +37603,13 @@
         <v>419.1763724772135</v>
       </c>
       <c r="F483" t="n">
-        <v>437.5290618896485</v>
+        <v>437.5290629577637</v>
       </c>
       <c r="G483" t="n">
-        <v>-2.468049723235333</v>
+        <v>-2.468049717358922</v>
       </c>
       <c r="H483" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I483" t="n">
         <v>363.2227809620478</v>
@@ -37618,7 +37618,7 @@
         <v>11.43298857190658</v>
       </c>
       <c r="K483" t="n">
-        <v>31.86135103228087</v>
+        <v>31.86133531879123</v>
       </c>
       <c r="L483" t="n">
         <v>34.85477178423236</v>
@@ -38065,13 +38065,13 @@
         <v>612.7990930175781</v>
       </c>
       <c r="F489" t="n">
-        <v>618.0226507568359</v>
+        <v>618.0226489257813</v>
       </c>
       <c r="G489" t="n">
-        <v>-1.654526535486145</v>
+        <v>-1.654526492548092</v>
       </c>
       <c r="H489" t="n">
-        <v>848.8263661382125</v>
+        <v>848.8262434052705</v>
       </c>
       <c r="I489" t="n">
         <v>495.5999980879241</v>
@@ -38080,7 +38080,7 @@
         <v>19.01734823681185</v>
       </c>
       <c r="K489" t="n">
-        <v>43.90546770727867</v>
+        <v>43.90544689979423</v>
       </c>
       <c r="L489" t="n">
         <v>33.60995850622407</v>
@@ -39759,10 +39759,10 @@
         <v>272.8322693888346</v>
       </c>
       <c r="F511" t="n">
-        <v>284.0447898101806</v>
+        <v>284.044787979126</v>
       </c>
       <c r="G511" t="n">
-        <v>-2.836123382999134</v>
+        <v>-2.83612329933175</v>
       </c>
       <c r="H511" t="n">
         <v>390.5481555478003</v>
@@ -40298,13 +40298,13 @@
         <v>1636.026534016927</v>
       </c>
       <c r="F518" t="n">
-        <v>1720.30762512207</v>
+        <v>1720.307622680664</v>
       </c>
       <c r="G518" t="n">
-        <v>-3.471929621735703</v>
+        <v>-3.471929494258486</v>
       </c>
       <c r="H518" t="n">
-        <v>2339.801318384509</v>
+        <v>2339.80156593166</v>
       </c>
       <c r="I518" t="n">
         <v>1322.972836511248</v>
@@ -40313,7 +40313,7 @@
         <v>17.5836670757459</v>
       </c>
       <c r="K518" t="n">
-        <v>50.41150392813496</v>
+        <v>50.41151984142598</v>
       </c>
       <c r="L518" t="n">
         <v>24.20470262793914</v>
@@ -40985,19 +40985,19 @@
         <v>474.8999938964844</v>
       </c>
       <c r="D527" t="n">
-        <v>454.6921655273438</v>
+        <v>454.6921661376953</v>
       </c>
       <c r="E527" t="n">
-        <v>493.8540364583333</v>
+        <v>493.8540329996745</v>
       </c>
       <c r="F527" t="n">
-        <v>503.4209580993652</v>
+        <v>503.4209552001953</v>
       </c>
       <c r="G527" t="n">
-        <v>-3.660040186104396</v>
+        <v>-3.660040262675024</v>
       </c>
       <c r="H527" t="n">
-        <v>758.589574672296</v>
+        <v>758.5896367271307</v>
       </c>
       <c r="I527" t="n">
         <v>400.6499938964844</v>
@@ -41006,7 +41006,7 @@
         <v>18.53238515690179</v>
       </c>
       <c r="K527" t="n">
-        <v>59.73669918337552</v>
+        <v>59.73671225030235</v>
       </c>
       <c r="L527" t="n">
         <v>19.36376210235132</v>
@@ -41068,13 +41068,13 @@
         <v>2432.191010742188</v>
       </c>
       <c r="F528" t="n">
-        <v>2428.433647460938</v>
+        <v>2428.433641357422</v>
       </c>
       <c r="G528" t="n">
-        <v>-1.469135403213528</v>
+        <v>-1.46913540685174</v>
       </c>
       <c r="H528" t="n">
-        <v>2908.974119515923</v>
+        <v>2908.974368726317</v>
       </c>
       <c r="I528" t="n">
         <v>2031.199951171875</v>
@@ -41083,7 +41083,7 @@
         <v>1.614811422637219</v>
       </c>
       <c r="K528" t="n">
-        <v>40.93866858119781</v>
+        <v>40.93868065534483</v>
       </c>
       <c r="L528" t="n">
         <v>18.94882434301521</v>
@@ -41912,16 +41912,16 @@
         <v>669.7910021972656</v>
       </c>
       <c r="E539" t="n">
-        <v>667.8033024088542</v>
+        <v>667.8033040364584</v>
       </c>
       <c r="F539" t="n">
-        <v>713.0249322509766</v>
+        <v>713.0249349975586</v>
       </c>
       <c r="G539" t="n">
-        <v>-4.361509461049062</v>
+        <v>-4.361509523277451</v>
       </c>
       <c r="H539" t="n">
-        <v>1181.515387363553</v>
+        <v>1181.515511428121</v>
       </c>
       <c r="I539" t="n">
         <v>577.3964738257137</v>
@@ -41930,7 +41930,7 @@
         <v>6.166218151348324</v>
       </c>
       <c r="K539" t="n">
-        <v>92.74313007562034</v>
+        <v>92.74315031453844</v>
       </c>
       <c r="L539" t="n">
         <v>8.160442600276625</v>
@@ -42836,13 +42836,13 @@
         <v>137.3898770141602</v>
       </c>
       <c r="E551" t="n">
-        <v>140.8485832722982</v>
+        <v>140.8485831705729</v>
       </c>
       <c r="F551" t="n">
-        <v>146.5086482238769</v>
+        <v>146.5086478424072</v>
       </c>
       <c r="G551" t="n">
-        <v>-1.604611678720924</v>
+        <v>-1.60461168283188</v>
       </c>
       <c r="H551" t="n">
         <v>184.9587904135824</v>
@@ -44077,7 +44077,7 @@
         <v>-1.957628234486752</v>
       </c>
       <c r="H567" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I567" t="n">
         <v>185.2067002350832</v>
@@ -44086,7 +44086,7 @@
         <v>19.147956250421</v>
       </c>
       <c r="K567" t="n">
-        <v>39.60877652129267</v>
+        <v>39.60876203060204</v>
       </c>
       <c r="L567" t="n">
         <v>30.01383125864454</v>
@@ -44382,7 +44382,7 @@
         <v>33.69348126411438</v>
       </c>
       <c r="G571" t="n">
-        <v>-1.930656383802498</v>
+        <v>-1.930656547134746</v>
       </c>
       <c r="H571" t="n">
         <v>40.26070662850351</v>
@@ -45309,7 +45309,7 @@
         <v>-1.629643441586925</v>
       </c>
       <c r="H583" t="n">
-        <v>2308.784681838889</v>
+        <v>2308.784934113526</v>
       </c>
       <c r="I583" t="n">
         <v>1600.30999469477</v>
@@ -45318,7 +45318,7 @@
         <v>5.110883588949089</v>
       </c>
       <c r="K583" t="n">
-        <v>37.25609151350555</v>
+        <v>37.25610651110622</v>
       </c>
       <c r="L583" t="n">
         <v>25.44951590594744</v>
@@ -45383,10 +45383,10 @@
         <v>7767.988981933594</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.3070473362782</v>
+        <v>-1.307047366891056</v>
       </c>
       <c r="H584" t="n">
-        <v>9653.121370296873</v>
+        <v>9653.120359649309</v>
       </c>
       <c r="I584" t="n">
         <v>6860</v>
@@ -45395,7 +45395,7 @@
         <v>0.5685131195335202</v>
       </c>
       <c r="K584" t="n">
-        <v>39.92058806054315</v>
+        <v>39.92057341135396</v>
       </c>
       <c r="L584" t="n">
         <v>24.61964038727524</v>
@@ -45688,10 +45688,10 @@
         <v>20.33732182820638</v>
       </c>
       <c r="F588" t="n">
-        <v>20.43781512260437</v>
+        <v>20.43781509399414</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.425172229577698</v>
+        <v>-1.425172231544325</v>
       </c>
       <c r="H588" t="n">
         <v>23.83526024888653</v>
@@ -46304,13 +46304,13 @@
         <v>122.2661837259928</v>
       </c>
       <c r="F596" t="n">
-        <v>124.0379209518433</v>
+        <v>124.0379211425781</v>
       </c>
       <c r="G596" t="n">
-        <v>-2.132097517220577</v>
+        <v>-2.132097749666639</v>
       </c>
       <c r="H596" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I596" t="n">
         <v>104.1800003051758</v>
@@ -46319,7 +46319,7 @@
         <v>1.727781768559256</v>
       </c>
       <c r="K596" t="n">
-        <v>47.10318528194084</v>
+        <v>47.10320195970523</v>
       </c>
       <c r="L596" t="n">
         <v>21.30013831258644</v>
@@ -46458,10 +46458,10 @@
         <v>155.0009510294596</v>
       </c>
       <c r="F598" t="n">
-        <v>160.2469891357422</v>
+        <v>160.2469892883301</v>
       </c>
       <c r="G598" t="n">
-        <v>-2.794175660488329</v>
+        <v>-2.794175567928514</v>
       </c>
       <c r="H598" t="n">
         <v>217.0279658924327</v>
@@ -46997,13 +46997,13 @@
         <v>1467.083395182292</v>
       </c>
       <c r="F605" t="n">
-        <v>1486.22432800293</v>
+        <v>1486.224327392578</v>
       </c>
       <c r="G605" t="n">
-        <v>-1.766030763588999</v>
+        <v>-1.766030883190084</v>
       </c>
       <c r="H605" t="n">
-        <v>1918.799784355899</v>
+        <v>1918.799910904837</v>
       </c>
       <c r="I605" t="n">
         <v>1185.665549129695</v>
@@ -47012,7 +47012,7 @@
         <v>8.54663028243392</v>
       </c>
       <c r="K605" t="n">
-        <v>49.09089233534571</v>
+        <v>49.090902168208</v>
       </c>
       <c r="L605" t="n">
         <v>19.77869986168741</v>
@@ -47456,16 +47456,16 @@
         <v>2275.594011230469</v>
       </c>
       <c r="E611" t="n">
-        <v>2289.339594726563</v>
+        <v>2289.339604492187</v>
       </c>
       <c r="F611" t="n">
-        <v>2463.761949462891</v>
+        <v>2463.761960449219</v>
       </c>
       <c r="G611" t="n">
-        <v>-3.793826540455691</v>
+        <v>-3.793826524180199</v>
       </c>
       <c r="H611" t="n">
-        <v>3287.161392369851</v>
+        <v>3287.161645949698</v>
       </c>
       <c r="I611" t="n">
         <v>1966.020518717901</v>
@@ -47474,7 +47474,7 @@
         <v>5.543150757814441</v>
       </c>
       <c r="K611" t="n">
-        <v>58.41741649975183</v>
+        <v>58.41742872046736</v>
       </c>
       <c r="L611" t="n">
         <v>18.53388658367912</v>
@@ -48306,13 +48306,13 @@
         <v>122.0214933776855</v>
       </c>
       <c r="F622" t="n">
-        <v>125.0251424026489</v>
+        <v>125.0251421737671</v>
       </c>
       <c r="G622" t="n">
-        <v>-2.516126669933916</v>
+        <v>-2.516126906386995</v>
       </c>
       <c r="H622" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I622" t="n">
         <v>104.7068431385872</v>
@@ -48321,7 +48321,7 @@
         <v>1.99906696680765</v>
       </c>
       <c r="K622" t="n">
-        <v>44.29226433145664</v>
+        <v>44.29227911234857</v>
       </c>
       <c r="L622" t="n">
         <v>16.87413554633472</v>
@@ -49230,13 +49230,13 @@
         <v>284.8430511474609</v>
       </c>
       <c r="F634" t="n">
-        <v>295.8404138183594</v>
+        <v>295.8404135131836</v>
       </c>
       <c r="G634" t="n">
-        <v>-4.302033795930771</v>
+        <v>-4.30203380017764</v>
       </c>
       <c r="H634" t="n">
-        <v>406.5707952146441</v>
+        <v>406.5707642578344</v>
       </c>
       <c r="I634" t="n">
         <v>254.6499938964844</v>
@@ -49245,7 +49245,7 @@
         <v>0.4908698330886807</v>
       </c>
       <c r="K634" t="n">
-        <v>58.87878269317524</v>
+        <v>58.87877059594568</v>
       </c>
       <c r="L634" t="n">
         <v>14.93775933609959</v>
@@ -49612,16 +49612,16 @@
         <v>183.2720919799805</v>
       </c>
       <c r="E639" t="n">
-        <v>191.8033245849609</v>
+        <v>191.803324991862</v>
       </c>
       <c r="F639" t="n">
-        <v>194.2098805999756</v>
+        <v>194.2098807525635</v>
       </c>
       <c r="G639" t="n">
-        <v>-2.644570721248785</v>
+        <v>-2.644570830927784</v>
       </c>
       <c r="H639" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I639" t="n">
         <v>156.7443123050878</v>
@@ -49630,7 +49630,7 @@
         <v>3.059556618367543</v>
       </c>
       <c r="K639" t="n">
-        <v>48.08635525669163</v>
+        <v>48.08636481559228</v>
       </c>
       <c r="L639" t="n">
         <v>14.24619640387275</v>
@@ -49997,16 +49997,16 @@
         <v>274.8549694824219</v>
       </c>
       <c r="E644" t="n">
-        <v>294.7311009724935</v>
+        <v>294.731100769043</v>
       </c>
       <c r="F644" t="n">
-        <v>306.105076828003</v>
+        <v>306.1050765228272</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.530043446291974</v>
+        <v>-2.530043543466021</v>
       </c>
       <c r="H644" t="n">
-        <v>396.5816333492734</v>
+        <v>396.5816020628056</v>
       </c>
       <c r="I644" t="n">
         <v>243.9284560598348</v>
@@ -50015,7 +50015,7 @@
         <v>5.440757655572992</v>
       </c>
       <c r="K644" t="n">
-        <v>54.19191855638324</v>
+        <v>54.19190639212732</v>
       </c>
       <c r="L644" t="n">
         <v>12.86307053941909</v>
@@ -50542,10 +50542,10 @@
         <v>95.23410854339599</v>
       </c>
       <c r="G651" t="n">
-        <v>-3.347737778381032</v>
+        <v>-3.347737740962087</v>
       </c>
       <c r="H651" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I651" t="n">
         <v>76.06999969482422</v>
@@ -50554,7 +50554,7 @@
         <v>1.748392055199632</v>
       </c>
       <c r="K651" t="n">
-        <v>61.27559068940533</v>
+        <v>61.27558052873785</v>
       </c>
       <c r="L651" t="n">
         <v>11.75656984785615</v>
@@ -50924,10 +50924,10 @@
         <v>512.2982283528646</v>
       </c>
       <c r="F656" t="n">
-        <v>543.4354055786133</v>
+        <v>543.4354052734375</v>
       </c>
       <c r="G656" t="n">
-        <v>-4.132199212208654</v>
+        <v>-4.13219905959834</v>
       </c>
       <c r="H656" t="n">
         <v>725.6811213920008</v>
@@ -52233,13 +52233,13 @@
         <v>254.8142333984375</v>
       </c>
       <c r="F673" t="n">
-        <v>264.1078344726562</v>
+        <v>264.1078338623047</v>
       </c>
       <c r="G673" t="n">
-        <v>-3.590627153497095</v>
+        <v>-3.590627161497062</v>
       </c>
       <c r="H673" t="n">
-        <v>355.6599215623946</v>
+        <v>355.6598900030953</v>
       </c>
       <c r="I673" t="n">
         <v>212</v>
@@ -52248,7 +52248,7 @@
         <v>2.127355899450922</v>
       </c>
       <c r="K673" t="n">
-        <v>64.2695166902169</v>
+        <v>64.26950211384626</v>
       </c>
       <c r="L673" t="n">
         <v>8.298755186721991</v>
@@ -52387,10 +52387,10 @@
         <v>130.6906094868978</v>
       </c>
       <c r="F675" t="n">
-        <v>137.5798371505737</v>
+        <v>137.5798369979858</v>
       </c>
       <c r="G675" t="n">
-        <v>-3.471468774360331</v>
+        <v>-3.471468726405846</v>
       </c>
       <c r="H675" t="n">
         <v>183.7853835258596</v>
@@ -52778,7 +52778,7 @@
         <v>-4.501495703494141</v>
       </c>
       <c r="H680" t="n">
-        <v>605.9581114957105</v>
+        <v>605.9581737112406</v>
       </c>
       <c r="I680" t="n">
         <v>326.057353105007</v>
@@ -52787,7 +52787,7 @@
         <v>8.922553199439132</v>
       </c>
       <c r="K680" t="n">
-        <v>70.62033560736289</v>
+        <v>70.62035312546264</v>
       </c>
       <c r="L680" t="n">
         <v>6.915629322268327</v>
@@ -53311,13 +53311,13 @@
         <v>506.6396004231771</v>
       </c>
       <c r="F687" t="n">
-        <v>532.6432243347168</v>
+        <v>532.6432228088379</v>
       </c>
       <c r="G687" t="n">
-        <v>-3.722140672943564</v>
+        <v>-3.722140630100812</v>
       </c>
       <c r="H687" t="n">
-        <v>798.1971250028588</v>
+        <v>798.1970626635499</v>
       </c>
       <c r="I687" t="n">
         <v>406.117116732523</v>
@@ -53326,7 +53326,7 @@
         <v>7.456685748093261</v>
       </c>
       <c r="K687" t="n">
-        <v>82.90493496024062</v>
+        <v>82.90492067533921</v>
       </c>
       <c r="L687" t="n">
         <v>5.670816044260028</v>
@@ -53388,10 +53388,10 @@
         <v>274.7847361246745</v>
       </c>
       <c r="F688" t="n">
-        <v>287.0204014587403</v>
+        <v>287.0204006958008</v>
       </c>
       <c r="G688" t="n">
-        <v>-4.206596468470503</v>
+        <v>-4.206596479181846</v>
       </c>
       <c r="H688" t="n">
         <v>385.6351549871131</v>
@@ -54466,10 +54466,10 @@
         <v>246.5253459676107</v>
       </c>
       <c r="F702" t="n">
-        <v>267.1915885162354</v>
+        <v>267.1915883636474</v>
       </c>
       <c r="G702" t="n">
-        <v>-4.305497797095626</v>
+        <v>-4.305497747152209</v>
       </c>
       <c r="H702" t="n">
         <v>398.2045017598045</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1499,10 +1499,10 @@
         <v>2055.300048828125</v>
       </c>
       <c r="I14" t="n">
-        <v>841.4671897137645</v>
+        <v>841.4672483994065</v>
       </c>
       <c r="J14" t="n">
-        <v>135.7786523649107</v>
+        <v>135.7786359212266</v>
       </c>
       <c r="K14" t="n">
         <v>3.593752461095012</v>
@@ -2568,10 +2568,10 @@
         <v>655.1678442382813</v>
       </c>
       <c r="F28" t="n">
-        <v>614.6078900146484</v>
+        <v>614.6078901672363</v>
       </c>
       <c r="G28" t="n">
-        <v>5.836161650620131</v>
+        <v>5.836161815942442</v>
       </c>
       <c r="H28" t="n">
         <v>844</v>
@@ -2796,13 +2796,13 @@
         <v>11615.185703125</v>
       </c>
       <c r="E31" t="n">
-        <v>10869.85706380208</v>
+        <v>10869.85709635417</v>
       </c>
       <c r="F31" t="n">
-        <v>10437.05025146484</v>
+        <v>10437.05027587891</v>
       </c>
       <c r="G31" t="n">
-        <v>3.312993512793239</v>
+        <v>3.312993504786843</v>
       </c>
       <c r="H31" t="n">
         <v>13996</v>
@@ -2873,13 +2873,13 @@
         <v>1352.878703613281</v>
       </c>
       <c r="E32" t="n">
-        <v>1182.013286132812</v>
+        <v>1182.01328125</v>
       </c>
       <c r="F32" t="n">
-        <v>1074.562547912598</v>
+        <v>1074.562542419434</v>
       </c>
       <c r="G32" t="n">
-        <v>8.451235334507711</v>
+        <v>8.451235548377323</v>
       </c>
       <c r="H32" t="n">
         <v>1675</v>
@@ -3726,7 +3726,7 @@
         <v>225.895284576416</v>
       </c>
       <c r="G43" t="n">
-        <v>4.592414928500821</v>
+        <v>4.592414854606131</v>
       </c>
       <c r="H43" t="n">
         <v>321.3999938964844</v>
@@ -3880,7 +3880,7 @@
         <v>3637.369436035156</v>
       </c>
       <c r="G45" t="n">
-        <v>5.51929794027648</v>
+        <v>5.519297865542794</v>
       </c>
       <c r="H45" t="n">
         <v>4843</v>
@@ -4031,10 +4031,10 @@
         <v>559.3865700276692</v>
       </c>
       <c r="F47" t="n">
-        <v>536.4425765991211</v>
+        <v>536.4425758361816</v>
       </c>
       <c r="G47" t="n">
-        <v>5.563387317092872</v>
+        <v>5.563387452234969</v>
       </c>
       <c r="H47" t="n">
         <v>795.731978165477</v>
@@ -4179,16 +4179,16 @@
         <v>230.0700073242188</v>
       </c>
       <c r="D49" t="n">
-        <v>193.0581924438476</v>
+        <v>193.0581918334961</v>
       </c>
       <c r="E49" t="n">
-        <v>155.5897725931803</v>
+        <v>155.5897733561198</v>
       </c>
       <c r="F49" t="n">
-        <v>154.3818590164184</v>
+        <v>154.3818601989746</v>
       </c>
       <c r="G49" t="n">
-        <v>3.34929663126462</v>
+        <v>3.349296551965142</v>
       </c>
       <c r="H49" t="n">
         <v>235.75</v>
@@ -4256,16 +4256,16 @@
         <v>205.0899963378906</v>
       </c>
       <c r="D50" t="n">
-        <v>185.0763525390625</v>
+        <v>185.0763528442383</v>
       </c>
       <c r="E50" t="n">
-        <v>155.9071701558431</v>
+        <v>155.9071700541178</v>
       </c>
       <c r="F50" t="n">
-        <v>154.6964870071411</v>
+        <v>154.6964868545532</v>
       </c>
       <c r="G50" t="n">
-        <v>2.533514295274952</v>
+        <v>2.533514401535464</v>
       </c>
       <c r="H50" t="n">
         <v>233.3500061035156</v>
@@ -5722,22 +5722,22 @@
         <v>1911.439594726563</v>
       </c>
       <c r="E69" t="n">
-        <v>1651.839215494792</v>
+        <v>1651.839222005208</v>
       </c>
       <c r="F69" t="n">
-        <v>1591.834501342773</v>
+        <v>1591.834497680664</v>
       </c>
       <c r="G69" t="n">
-        <v>2.992657926878128</v>
+        <v>2.992657933968945</v>
       </c>
       <c r="H69" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I69" t="n">
-        <v>1266.161452106784</v>
+        <v>1266.16157090969</v>
       </c>
       <c r="J69" t="n">
-        <v>58.36052916076562</v>
+        <v>58.36051430192655</v>
       </c>
       <c r="K69" t="n">
         <v>1.670739634327245</v>
@@ -7108,13 +7108,13 @@
         <v>419.4775427246093</v>
       </c>
       <c r="E87" t="n">
-        <v>395.6617582194011</v>
+        <v>395.6617584228516</v>
       </c>
       <c r="F87" t="n">
         <v>383.1982881164551</v>
       </c>
       <c r="G87" t="n">
-        <v>3.092122289207522</v>
+        <v>3.092122162247013</v>
       </c>
       <c r="H87" t="n">
         <v>480.9477017568404</v>
@@ -7339,13 +7339,13 @@
         <v>1044.189058837891</v>
       </c>
       <c r="E90" t="n">
-        <v>945.850966796875</v>
+        <v>945.8509688313802</v>
       </c>
       <c r="F90" t="n">
-        <v>918.3966165161132</v>
+        <v>918.3966180419922</v>
       </c>
       <c r="G90" t="n">
-        <v>3.279131487184794</v>
+        <v>3.279131410669622</v>
       </c>
       <c r="H90" t="n">
         <v>1148</v>
@@ -7810,7 +7810,7 @@
         <v>1.521165090685828</v>
       </c>
       <c r="H96" t="n">
-        <v>1278.952725191461</v>
+        <v>1278.952852189353</v>
       </c>
       <c r="I96" t="n">
         <v>865.2617122743181</v>
@@ -7819,7 +7819,7 @@
         <v>41.58721670068974</v>
       </c>
       <c r="K96" t="n">
-        <v>4.395784073031805</v>
+        <v>4.39579443936069</v>
       </c>
       <c r="L96" t="n">
         <v>72.19917012448133</v>
@@ -8494,13 +8494,13 @@
         <v>1369.864624023438</v>
       </c>
       <c r="E105" t="n">
-        <v>1140.439417317708</v>
+        <v>1140.439417724609</v>
       </c>
       <c r="F105" t="n">
-        <v>1060.21904876709</v>
+        <v>1060.219048156738</v>
       </c>
       <c r="G105" t="n">
-        <v>5.843866403920517</v>
+        <v>5.843866439728096</v>
       </c>
       <c r="H105" t="n">
         <v>1677.5</v>
@@ -9110,13 +9110,13 @@
         <v>340.3660192871094</v>
       </c>
       <c r="E113" t="n">
-        <v>259.0081261189779</v>
+        <v>259.0081260172526</v>
       </c>
       <c r="F113" t="n">
-        <v>244.313228302002</v>
+        <v>244.313228225708</v>
       </c>
       <c r="G113" t="n">
-        <v>7.16614373990101</v>
+        <v>7.166143742299202</v>
       </c>
       <c r="H113" t="n">
         <v>388.75</v>
@@ -9960,19 +9960,19 @@
         <v>1417.508199869792</v>
       </c>
       <c r="F124" t="n">
-        <v>1352.940922241211</v>
+        <v>1352.940924682617</v>
       </c>
       <c r="G124" t="n">
-        <v>3.043635786846233</v>
+        <v>3.043635781186782</v>
       </c>
       <c r="H124" t="n">
         <v>1766.733060850261</v>
       </c>
       <c r="I124" t="n">
-        <v>951.4121987838871</v>
+        <v>951.4122590151433</v>
       </c>
       <c r="J124" t="n">
-        <v>60.87663975113826</v>
+        <v>60.87662956648696</v>
       </c>
       <c r="K124" t="n">
         <v>15.42748523656077</v>
@@ -11038,10 +11038,10 @@
         <v>728.6689595540364</v>
       </c>
       <c r="F138" t="n">
-        <v>733.1653747558594</v>
+        <v>733.1653762817383</v>
       </c>
       <c r="G138" t="n">
-        <v>2.500909918623329</v>
+        <v>2.500909869555779</v>
       </c>
       <c r="H138" t="n">
         <v>1002.400024414062</v>
@@ -11423,10 +11423,10 @@
         <v>78.53252817789713</v>
       </c>
       <c r="F143" t="n">
-        <v>74.65392724990845</v>
+        <v>74.65392719268799</v>
       </c>
       <c r="G143" t="n">
-        <v>4.041248524268637</v>
+        <v>4.041248499835404</v>
       </c>
       <c r="H143" t="n">
         <v>94.5</v>
@@ -12193,10 +12193,10 @@
         <v>4595.71060546875</v>
       </c>
       <c r="F153" t="n">
-        <v>4441.258188476562</v>
+        <v>4441.25818359375</v>
       </c>
       <c r="G153" t="n">
-        <v>3.019674807991701</v>
+        <v>3.019674840582387</v>
       </c>
       <c r="H153" t="n">
         <v>5250</v>
@@ -13425,10 +13425,10 @@
         <v>621.9713570149739</v>
       </c>
       <c r="F169" t="n">
-        <v>610.6802890014649</v>
+        <v>610.6802893066406</v>
       </c>
       <c r="G169" t="n">
-        <v>1.836747846076192</v>
+        <v>1.836747845141429</v>
       </c>
       <c r="H169" t="n">
         <v>769</v>
@@ -14811,13 +14811,13 @@
         <v>1788.325852864583</v>
       </c>
       <c r="F187" t="n">
-        <v>1779.015993652344</v>
+        <v>1779.015996704102</v>
       </c>
       <c r="G187" t="n">
-        <v>1.541715798403165</v>
+        <v>1.541715654220055</v>
       </c>
       <c r="H187" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I187" t="n">
         <v>1345.285007075603</v>
@@ -14826,7 +14826,7 @@
         <v>45.86500544548524</v>
       </c>
       <c r="K187" t="n">
-        <v>14.97670337682986</v>
+        <v>14.97669061737585</v>
       </c>
       <c r="L187" t="n">
         <v>61.82572614107884</v>
@@ -15655,13 +15655,13 @@
         <v>7354.229365234375</v>
       </c>
       <c r="E198" t="n">
-        <v>6929.848001302084</v>
+        <v>6929.847994791667</v>
       </c>
       <c r="F198" t="n">
-        <v>6517.915737304687</v>
+        <v>6517.9157421875</v>
       </c>
       <c r="G198" t="n">
-        <v>3.671720234523868</v>
+        <v>3.671720312188187</v>
       </c>
       <c r="H198" t="n">
         <v>7832.294844565128</v>
@@ -17580,13 +17580,13 @@
         <v>1824.515993652344</v>
       </c>
       <c r="E223" t="n">
-        <v>1713.930037434896</v>
+        <v>1713.930034993489</v>
       </c>
       <c r="F223" t="n">
-        <v>1683.062272338867</v>
+        <v>1683.062272949219</v>
       </c>
       <c r="G223" t="n">
-        <v>0.9732296148044162</v>
+        <v>0.973229614448079</v>
       </c>
       <c r="H223" t="n">
         <v>1983.954544928268</v>
@@ -18122,10 +18122,10 @@
         <v>165.7066747029622</v>
       </c>
       <c r="F230" t="n">
-        <v>164.9557038116455</v>
+        <v>164.9557037353516</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1915716441456716</v>
+        <v>0.1915715513773231</v>
       </c>
       <c r="H230" t="n">
         <v>181.8519567776652</v>
@@ -20589,7 +20589,7 @@
         <v>270.4716150665283</v>
       </c>
       <c r="G262" t="n">
-        <v>2.087910268530369</v>
+        <v>2.08791032732627</v>
       </c>
       <c r="H262" t="n">
         <v>367.499792159746</v>
@@ -20743,7 +20743,7 @@
         <v>4984.521378173828</v>
       </c>
       <c r="G264" t="n">
-        <v>1.366350675277106</v>
+        <v>1.366350826259199</v>
       </c>
       <c r="H264" t="n">
         <v>6049.821052103703</v>
@@ -21122,16 +21122,16 @@
         <v>4557.957587890625</v>
       </c>
       <c r="E269" t="n">
-        <v>4236.71845703125</v>
+        <v>4236.718458658855</v>
       </c>
       <c r="F269" t="n">
-        <v>4305.386689453125</v>
+        <v>4305.386700439453</v>
       </c>
       <c r="G269" t="n">
-        <v>0.4891434996427302</v>
+        <v>0.4891432693406417</v>
       </c>
       <c r="H269" t="n">
-        <v>5005.771184298104</v>
+        <v>5005.771680286142</v>
       </c>
       <c r="I269" t="n">
         <v>3669.905008549105</v>
@@ -21140,7 +21140,7 @@
         <v>20.67342580638332</v>
       </c>
       <c r="K269" t="n">
-        <v>13.03281113477171</v>
+        <v>13.03282233442908</v>
       </c>
       <c r="L269" t="n">
         <v>65.97510373443983</v>
@@ -21433,10 +21433,10 @@
         <v>525.7173842366536</v>
       </c>
       <c r="F273" t="n">
-        <v>533.8989073181152</v>
+        <v>533.8989057922363</v>
       </c>
       <c r="G273" t="n">
-        <v>-1.148820503623449</v>
+        <v>-1.148820339306866</v>
       </c>
       <c r="H273" t="n">
         <v>663.9000244140625</v>
@@ -21510,10 +21510,10 @@
         <v>312.6840242513021</v>
       </c>
       <c r="F274" t="n">
-        <v>309.5910678100586</v>
+        <v>309.5910679626465</v>
       </c>
       <c r="G274" t="n">
-        <v>1.625423584703478</v>
+        <v>1.625423583889352</v>
       </c>
       <c r="H274" t="n">
         <v>380.4567148307952</v>
@@ -21664,13 +21664,13 @@
         <v>5124.110989583333</v>
       </c>
       <c r="F276" t="n">
-        <v>5336.029035644531</v>
+        <v>5336.029033203125</v>
       </c>
       <c r="G276" t="n">
-        <v>-1.687376385556716</v>
+        <v>-1.687376342093505</v>
       </c>
       <c r="H276" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I276" t="n">
         <v>4229.809203861739</v>
@@ -21679,7 +21679,7 @@
         <v>26.88515583870843</v>
       </c>
       <c r="K276" t="n">
-        <v>22.09156346082197</v>
+        <v>22.0915727128898</v>
       </c>
       <c r="L276" t="n">
         <v>60.44260027662517</v>
@@ -21818,10 +21818,10 @@
         <v>1101.919091796875</v>
       </c>
       <c r="F278" t="n">
-        <v>1139.700042724609</v>
+        <v>1139.700039672852</v>
       </c>
       <c r="G278" t="n">
-        <v>-0.6979069785932324</v>
+        <v>-0.6979069804489813</v>
       </c>
       <c r="H278" t="n">
         <v>1409.944064008135</v>
@@ -23201,22 +23201,22 @@
         <v>369.4855438232422</v>
       </c>
       <c r="E296" t="n">
-        <v>380.6355096435547</v>
+        <v>380.6355094401042</v>
       </c>
       <c r="F296" t="n">
-        <v>370.7194248962402</v>
+        <v>370.7194253540039</v>
       </c>
       <c r="G296" t="n">
-        <v>3.07477644602725</v>
+        <v>3.074776595168816</v>
       </c>
       <c r="H296" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I296" t="n">
-        <v>202.9799435043193</v>
+        <v>202.9799285514176</v>
       </c>
       <c r="J296" t="n">
-        <v>64.9916677060056</v>
+        <v>64.99167986042995</v>
       </c>
       <c r="K296" t="n">
         <v>32.38970282873561</v>
@@ -23355,13 +23355,13 @@
         <v>293.6379992675782</v>
       </c>
       <c r="E298" t="n">
-        <v>298.9324642944336</v>
+        <v>298.9324639892578</v>
       </c>
       <c r="F298" t="n">
-        <v>286.6520799255371</v>
+        <v>286.6520789337158</v>
       </c>
       <c r="G298" t="n">
-        <v>1.142630756389496</v>
+        <v>1.142630733160943</v>
       </c>
       <c r="H298" t="n">
         <v>359.3387168134344</v>
@@ -23666,10 +23666,10 @@
         <v>1108.906597900391</v>
       </c>
       <c r="F302" t="n">
-        <v>1073.691958007812</v>
+        <v>1073.69195892334</v>
       </c>
       <c r="G302" t="n">
-        <v>0.8264183714909334</v>
+        <v>0.8264181974119156</v>
       </c>
       <c r="H302" t="n">
         <v>1238.748718225596</v>
@@ -24128,10 +24128,10 @@
         <v>464.7483414713542</v>
       </c>
       <c r="F308" t="n">
-        <v>459.3043811035157</v>
+        <v>459.3043795776367</v>
       </c>
       <c r="G308" t="n">
-        <v>1.746441868494997</v>
+        <v>1.746441805614163</v>
       </c>
       <c r="H308" t="n">
         <v>529.9163379046904</v>
@@ -24898,19 +24898,19 @@
         <v>403.3336702473958</v>
       </c>
       <c r="F318" t="n">
-        <v>399.5480657958984</v>
+        <v>399.5480656433106</v>
       </c>
       <c r="G318" t="n">
-        <v>0.7872973756856583</v>
+        <v>0.7872975311640218</v>
       </c>
       <c r="H318" t="n">
         <v>489.5369231157038</v>
       </c>
       <c r="I318" t="n">
-        <v>331.4688402352409</v>
+        <v>331.4688100886702</v>
       </c>
       <c r="J318" t="n">
-        <v>20.41855687346379</v>
+        <v>20.4185678253435</v>
       </c>
       <c r="K318" t="n">
         <v>22.64485296288401</v>
@@ -25825,7 +25825,7 @@
         <v>743.9646484375</v>
       </c>
       <c r="G330" t="n">
-        <v>-0.2579593800999147</v>
+        <v>-0.2579592576733791</v>
       </c>
       <c r="H330" t="n">
         <v>879.2203373423794</v>
@@ -25899,13 +25899,13 @@
         <v>742.1065291341146</v>
       </c>
       <c r="F331" t="n">
-        <v>757.6658099365235</v>
+        <v>757.6658087158203</v>
       </c>
       <c r="G331" t="n">
-        <v>-1.73507591007025</v>
+        <v>-1.735075912817208</v>
       </c>
       <c r="H331" t="n">
-        <v>1117.559301306357</v>
+        <v>1117.559425954049</v>
       </c>
       <c r="I331" t="n">
         <v>612.1496526863262</v>
@@ -25914,7 +25914,7 @@
         <v>27.31363518150798</v>
       </c>
       <c r="K331" t="n">
-        <v>43.39633493491082</v>
+        <v>43.3963509287129</v>
       </c>
       <c r="L331" t="n">
         <v>49.51590594744122</v>
@@ -26130,10 +26130,10 @@
         <v>36821.11716145834</v>
       </c>
       <c r="F334" t="n">
-        <v>36135.06489257813</v>
+        <v>36135.06499023437</v>
       </c>
       <c r="G334" t="n">
-        <v>-0.4669437836205881</v>
+        <v>-0.4669438894587485</v>
       </c>
       <c r="H334" t="n">
         <v>43614.20556091995</v>
@@ -28055,10 +28055,10 @@
         <v>667.8129199218751</v>
       </c>
       <c r="F359" t="n">
-        <v>666.3894036865235</v>
+        <v>666.3894030761719</v>
       </c>
       <c r="G359" t="n">
-        <v>-0.7313260551655598</v>
+        <v>-0.7313260558304946</v>
       </c>
       <c r="H359" t="n">
         <v>792.3323631991859</v>
@@ -28209,10 +28209,10 @@
         <v>2155.73273844401</v>
       </c>
       <c r="F361" t="n">
-        <v>2094.977207641602</v>
+        <v>2094.977203979492</v>
       </c>
       <c r="G361" t="n">
-        <v>0.2647895952829549</v>
+        <v>0.2647896250355775</v>
       </c>
       <c r="H361" t="n">
         <v>2625.96691593483</v>
@@ -28671,10 +28671,10 @@
         <v>1675.677440592448</v>
       </c>
       <c r="F367" t="n">
-        <v>1681.507033081055</v>
+        <v>1681.507031860352</v>
       </c>
       <c r="G367" t="n">
-        <v>0.3794606808320555</v>
+        <v>0.3794606445346904</v>
       </c>
       <c r="H367" t="n">
         <v>1952.5</v>
@@ -29284,13 +29284,13 @@
         <v>746.3871228027343</v>
       </c>
       <c r="E375" t="n">
-        <v>739.9505952962239</v>
+        <v>739.9505973307291</v>
       </c>
       <c r="F375" t="n">
-        <v>735.0230813598632</v>
+        <v>735.0230822753906</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.7645629135678234</v>
+        <v>-0.7645627490757589</v>
       </c>
       <c r="H375" t="n">
         <v>837.8765073351432</v>
@@ -30217,7 +30217,7 @@
         <v>-1.457260824110795</v>
       </c>
       <c r="H387" t="n">
-        <v>623.6463522815318</v>
+        <v>623.6462906209067</v>
       </c>
       <c r="I387" t="n">
         <v>351.0001816860465</v>
@@ -30226,7 +30226,7 @@
         <v>25.35606046881187</v>
       </c>
       <c r="K387" t="n">
-        <v>41.73780733671178</v>
+        <v>41.73779332293335</v>
       </c>
       <c r="L387" t="n">
         <v>31.8118948824343</v>
@@ -30519,19 +30519,19 @@
         <v>519.6711169433594</v>
       </c>
       <c r="F391" t="n">
-        <v>526.4788571166993</v>
+        <v>526.4788578796387</v>
       </c>
       <c r="G391" t="n">
-        <v>3.429071155087748</v>
+        <v>3.429071149948149</v>
       </c>
       <c r="H391" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I391" t="n">
-        <v>306.8419898026673</v>
+        <v>306.8420198526935</v>
       </c>
       <c r="J391" t="n">
-        <v>50.61497749825472</v>
+        <v>50.6149627480454</v>
       </c>
       <c r="K391" t="n">
         <v>63.57572648378395</v>
@@ -30750,10 +30750,10 @@
         <v>159.8523378499349</v>
       </c>
       <c r="F394" t="n">
-        <v>156.3419976806641</v>
+        <v>156.3419974517822</v>
       </c>
       <c r="G394" t="n">
-        <v>1.174316662157437</v>
+        <v>1.174316713849066</v>
       </c>
       <c r="H394" t="n">
         <v>203.5447632528218</v>
@@ -30904,10 +30904,10 @@
         <v>1364.227882486979</v>
       </c>
       <c r="F396" t="n">
-        <v>1364.679156494141</v>
+        <v>1364.679159545899</v>
       </c>
       <c r="G396" t="n">
-        <v>-0.09496082289986996</v>
+        <v>-0.09496073340768962</v>
       </c>
       <c r="H396" t="n">
         <v>1563.400024414062</v>
@@ -32598,13 +32598,13 @@
         <v>1079.739299723307</v>
       </c>
       <c r="F418" t="n">
-        <v>1080.149017333984</v>
+        <v>1080.149018249512</v>
       </c>
       <c r="G418" t="n">
-        <v>-0.7855838132481696</v>
+        <v>-0.785583701343695</v>
       </c>
       <c r="H418" t="n">
-        <v>1300.436668328248</v>
+        <v>1300.436795781491</v>
       </c>
       <c r="I418" t="n">
         <v>885.652283987356</v>
@@ -32613,7 +32613,7 @@
         <v>18.03729785548514</v>
       </c>
       <c r="K418" t="n">
-        <v>24.39608168721163</v>
+        <v>24.39609387902726</v>
       </c>
       <c r="L418" t="n">
         <v>44.67496542185339</v>
@@ -33445,19 +33445,19 @@
         <v>358.0823232014974</v>
       </c>
       <c r="F429" t="n">
-        <v>354.5846722412109</v>
+        <v>354.5846725463867</v>
       </c>
       <c r="G429" t="n">
-        <v>0.2876494519896244</v>
+        <v>0.2876495383028921</v>
       </c>
       <c r="H429" t="n">
         <v>409.9712889887167</v>
       </c>
       <c r="I429" t="n">
-        <v>309.838511773213</v>
+        <v>309.8384816659088</v>
       </c>
       <c r="J429" t="n">
-        <v>1.698140847692242</v>
+        <v>1.698150729798686</v>
       </c>
       <c r="K429" t="n">
         <v>30.10830880594595</v>
@@ -34064,10 +34064,10 @@
         <v>489.7094758605957</v>
       </c>
       <c r="G437" t="n">
-        <v>-0.4601589954420615</v>
+        <v>-0.4601589645692905</v>
       </c>
       <c r="H437" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I437" t="n">
         <v>419.3328127807616</v>
@@ -34076,7 +34076,7 @@
         <v>5.405536253870347</v>
       </c>
       <c r="K437" t="n">
-        <v>23.92261815939816</v>
+        <v>23.92263215418482</v>
       </c>
       <c r="L437" t="n">
         <v>35.68464730290457</v>
@@ -34138,10 +34138,10 @@
         <v>77.41940338134765</v>
       </c>
       <c r="F438" t="n">
-        <v>77.33355300903321</v>
+        <v>77.33355308532715</v>
       </c>
       <c r="G438" t="n">
-        <v>-0.06809621260853715</v>
+        <v>-0.06809636032345523</v>
       </c>
       <c r="H438" t="n">
         <v>86.59303970157107</v>
@@ -34757,7 +34757,7 @@
         <v>392.6871347045898</v>
       </c>
       <c r="G446" t="n">
-        <v>0.02668456802756847</v>
+        <v>0.02668468466187068</v>
       </c>
       <c r="H446" t="n">
         <v>476.8288845013619</v>
@@ -34831,10 +34831,10 @@
         <v>382.9580814615886</v>
       </c>
       <c r="F447" t="n">
-        <v>393.4175930786133</v>
+        <v>393.417593383789</v>
       </c>
       <c r="G447" t="n">
-        <v>-3.234237279870167</v>
+        <v>-3.234237386393446</v>
       </c>
       <c r="H447" t="n">
         <v>541.0236304500187</v>
@@ -35370,13 +35370,13 @@
         <v>5419.410013020834</v>
       </c>
       <c r="F454" t="n">
-        <v>5462.95017578125</v>
+        <v>5462.950168457031</v>
       </c>
       <c r="G454" t="n">
-        <v>-0.7602441271204796</v>
+        <v>-0.7602440401053512</v>
       </c>
       <c r="H454" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I454" t="n">
         <v>5051</v>
@@ -35385,7 +35385,7 @@
         <v>3.345872104533765</v>
       </c>
       <c r="K454" t="n">
-        <v>12.55813059984443</v>
+        <v>12.55812113412642</v>
       </c>
       <c r="L454" t="n">
         <v>50.89903181189488</v>
@@ -35675,25 +35675,25 @@
         <v>226.836159362793</v>
       </c>
       <c r="E458" t="n">
-        <v>223.7274620564779</v>
+        <v>223.7274625651042</v>
       </c>
       <c r="F458" t="n">
-        <v>225.0226384735107</v>
+        <v>225.0226387023926</v>
       </c>
       <c r="G458" t="n">
-        <v>-1.311985732761312</v>
+        <v>-1.311985764465529</v>
       </c>
       <c r="H458" t="n">
-        <v>286.08038637852</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I458" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J458" t="n">
-        <v>18.36385315079703</v>
+        <v>18.36386358052404</v>
       </c>
       <c r="K458" t="n">
-        <v>40.55932201362551</v>
+        <v>40.55935410757932</v>
       </c>
       <c r="L458" t="n">
         <v>45.08990318118949</v>
@@ -35829,22 +35829,22 @@
         <v>2284.207465820312</v>
       </c>
       <c r="E460" t="n">
-        <v>2216.432121582031</v>
+        <v>2216.432093912761</v>
       </c>
       <c r="F460" t="n">
-        <v>2271.937671508789</v>
+        <v>2271.937654418945</v>
       </c>
       <c r="G460" t="n">
-        <v>-0.6063489515477305</v>
+        <v>-0.6063489030011304</v>
       </c>
       <c r="H460" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I460" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J460" t="n">
-        <v>6.129352853792192</v>
+        <v>6.129359439564164</v>
       </c>
       <c r="K460" t="n">
         <v>32.72759799183411</v>
@@ -36140,10 +36140,10 @@
         <v>286.9126793416341</v>
       </c>
       <c r="F464" t="n">
-        <v>282.8162828826904</v>
+        <v>282.8162843322754</v>
       </c>
       <c r="G464" t="n">
-        <v>-0.0009977160387530937</v>
+        <v>-0.0009976081297602413</v>
       </c>
       <c r="H464" t="n">
         <v>323.4425459044702</v>
@@ -36602,10 +36602,10 @@
         <v>962.2528597005208</v>
       </c>
       <c r="F470" t="n">
-        <v>940.5948147583008</v>
+        <v>940.5948138427734</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.6987681465104867</v>
+        <v>-0.6987681151927383</v>
       </c>
       <c r="H470" t="n">
         <v>1224.741935222577</v>
@@ -38065,13 +38065,13 @@
         <v>612.7990930175781</v>
       </c>
       <c r="F489" t="n">
-        <v>618.0226489257813</v>
+        <v>618.0226507568359</v>
       </c>
       <c r="G489" t="n">
-        <v>-1.654526492548092</v>
+        <v>-1.654526583245042</v>
       </c>
       <c r="H489" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I489" t="n">
         <v>495.5999980879241</v>
@@ -38080,7 +38080,7 @@
         <v>19.01734823681185</v>
       </c>
       <c r="K489" t="n">
-        <v>43.90544689979423</v>
+        <v>43.90545730353645</v>
       </c>
       <c r="L489" t="n">
         <v>33.60995850622407</v>
@@ -38139,13 +38139,13 @@
         <v>13139.58146484375</v>
       </c>
       <c r="E490" t="n">
-        <v>12641.38913411458</v>
+        <v>12641.38909505208</v>
       </c>
       <c r="F490" t="n">
-        <v>12859.11881835937</v>
+        <v>12859.11876953125</v>
       </c>
       <c r="G490" t="n">
-        <v>-0.9480554066830793</v>
+        <v>-0.9480552239737539</v>
       </c>
       <c r="H490" t="n">
         <v>17800.41999866643</v>
@@ -38681,10 +38681,10 @@
         <v>410.9997347005208</v>
       </c>
       <c r="F497" t="n">
-        <v>415.147279510498</v>
+        <v>415.1472807312012</v>
       </c>
       <c r="G497" t="n">
-        <v>-1.387466544342453</v>
+        <v>-1.387466361607992</v>
       </c>
       <c r="H497" t="n">
         <v>684.5682054144123</v>
@@ -39756,13 +39756,13 @@
         <v>295.7471743774414</v>
       </c>
       <c r="E511" t="n">
-        <v>272.8322693888346</v>
+        <v>272.8322684733073</v>
       </c>
       <c r="F511" t="n">
-        <v>284.044787979126</v>
+        <v>284.0447880554199</v>
       </c>
       <c r="G511" t="n">
-        <v>-2.83612329933175</v>
+        <v>-2.836123146444325</v>
       </c>
       <c r="H511" t="n">
         <v>390.5481555478003</v>
@@ -40221,10 +40221,10 @@
         <v>2572.741672363281</v>
       </c>
       <c r="F517" t="n">
-        <v>2537.378749389648</v>
+        <v>2537.378753051758</v>
       </c>
       <c r="G517" t="n">
-        <v>-0.9768509353802579</v>
+        <v>-0.9768507924636349</v>
       </c>
       <c r="H517" t="n">
         <v>3329.438873827357</v>
@@ -40760,10 +40760,10 @@
         <v>2835.448185221354</v>
       </c>
       <c r="F524" t="n">
-        <v>2744.072935791015</v>
+        <v>2744.072932128906</v>
       </c>
       <c r="G524" t="n">
-        <v>-0.8479424074299358</v>
+        <v>-0.8479423648180773</v>
       </c>
       <c r="H524" t="n">
         <v>3333.383184200957</v>
@@ -42528,22 +42528,22 @@
         <v>428.3811437988281</v>
       </c>
       <c r="E547" t="n">
-        <v>461.9676647949219</v>
+        <v>461.9676641845703</v>
       </c>
       <c r="F547" t="n">
-        <v>464.6142265319824</v>
+        <v>464.6142266845703</v>
       </c>
       <c r="G547" t="n">
-        <v>-1.122910747623773</v>
+        <v>-1.122910779367547</v>
       </c>
       <c r="H547" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I547" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J547" t="n">
-        <v>11.99771780081735</v>
+        <v>11.99769985607422</v>
       </c>
       <c r="K547" t="n">
         <v>30.53944613225463</v>
@@ -42836,13 +42836,13 @@
         <v>137.3898770141602</v>
       </c>
       <c r="E551" t="n">
-        <v>140.8485831705729</v>
+        <v>140.8485832722982</v>
       </c>
       <c r="F551" t="n">
-        <v>146.5086478424072</v>
+        <v>146.5086482238769</v>
       </c>
       <c r="G551" t="n">
-        <v>-1.60461168283188</v>
+        <v>-1.604611628304009</v>
       </c>
       <c r="H551" t="n">
         <v>184.9587904135824</v>
@@ -43307,7 +43307,7 @@
         <v>-2.163350573368494</v>
       </c>
       <c r="H557" t="n">
-        <v>163308.5022863474</v>
+        <v>163308.4863287346</v>
       </c>
       <c r="I557" t="n">
         <v>121787.4350540836</v>
@@ -43316,7 +43316,7 @@
         <v>1.582728912108533</v>
       </c>
       <c r="K557" t="n">
-        <v>32.00380090235415</v>
+        <v>32.00378800366537</v>
       </c>
       <c r="L557" t="n">
         <v>33.0567081604426</v>
@@ -44077,7 +44077,7 @@
         <v>-1.957628234486752</v>
       </c>
       <c r="H567" t="n">
-        <v>308.0746526166167</v>
+        <v>308.0746845932235</v>
       </c>
       <c r="I567" t="n">
         <v>185.2067002350832</v>
@@ -44086,7 +44086,7 @@
         <v>19.147956250421</v>
       </c>
       <c r="K567" t="n">
-        <v>39.60876203060204</v>
+        <v>39.60877652129267</v>
       </c>
       <c r="L567" t="n">
         <v>30.01383125864454</v>
@@ -44382,7 +44382,7 @@
         <v>33.69348126411438</v>
       </c>
       <c r="G571" t="n">
-        <v>-1.930656547134746</v>
+        <v>-1.930656383802498</v>
       </c>
       <c r="H571" t="n">
         <v>40.26070662850351</v>
@@ -45383,10 +45383,10 @@
         <v>7767.988981933594</v>
       </c>
       <c r="G584" t="n">
-        <v>-1.307047366891056</v>
+        <v>-1.3070473362782</v>
       </c>
       <c r="H584" t="n">
-        <v>9653.120359649309</v>
+        <v>9653.121370296873</v>
       </c>
       <c r="I584" t="n">
         <v>6860</v>
@@ -45395,7 +45395,7 @@
         <v>0.5685131195335202</v>
       </c>
       <c r="K584" t="n">
-        <v>39.92057341135396</v>
+        <v>39.92058806054315</v>
       </c>
       <c r="L584" t="n">
         <v>24.61964038727524</v>
@@ -45611,10 +45611,10 @@
         <v>903.8792028808593</v>
       </c>
       <c r="F587" t="n">
-        <v>918.1916259765625</v>
+        <v>918.1916235351563</v>
       </c>
       <c r="G587" t="n">
-        <v>-0.9223955620833002</v>
+        <v>-0.9223955645132453</v>
       </c>
       <c r="H587" t="n">
         <v>1282.80960014975</v>
@@ -45688,10 +45688,10 @@
         <v>20.33732182820638</v>
       </c>
       <c r="F588" t="n">
-        <v>20.43781509399414</v>
+        <v>20.43781512260437</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.425172231544325</v>
+        <v>-1.425171957527582</v>
       </c>
       <c r="H588" t="n">
         <v>23.83526024888653</v>
@@ -46067,16 +46067,16 @@
         <v>287.75</v>
       </c>
       <c r="D593" t="n">
-        <v>329.1180627441406</v>
+        <v>329.1180633544922</v>
       </c>
       <c r="E593" t="n">
-        <v>338.0373254394531</v>
+        <v>338.0373232014974</v>
       </c>
       <c r="F593" t="n">
-        <v>340.9787965393066</v>
+        <v>340.9787945556641</v>
       </c>
       <c r="G593" t="n">
-        <v>-0.9496011975042018</v>
+        <v>-0.9496010712637171</v>
       </c>
       <c r="H593" t="n">
         <v>381.3442016302781</v>
@@ -46997,13 +46997,13 @@
         <v>1467.083395182292</v>
       </c>
       <c r="F605" t="n">
-        <v>1486.224327392578</v>
+        <v>1486.22432800293</v>
       </c>
       <c r="G605" t="n">
-        <v>-1.766030883190084</v>
+        <v>-1.766030763588999</v>
       </c>
       <c r="H605" t="n">
-        <v>1918.799910904837</v>
+        <v>1918.799784355899</v>
       </c>
       <c r="I605" t="n">
         <v>1185.665549129695</v>
@@ -47012,7 +47012,7 @@
         <v>8.54663028243392</v>
       </c>
       <c r="K605" t="n">
-        <v>49.090902168208</v>
+        <v>49.09089233534571</v>
       </c>
       <c r="L605" t="n">
         <v>19.77869986168741</v>
@@ -47074,10 +47074,10 @@
         <v>1058.395497233073</v>
       </c>
       <c r="F606" t="n">
-        <v>1084.438327026367</v>
+        <v>1084.438325805664</v>
       </c>
       <c r="G606" t="n">
-        <v>-2.273789204115551</v>
+        <v>-2.27378920661685</v>
       </c>
       <c r="H606" t="n">
         <v>1395.129939548488</v>
@@ -47382,10 +47382,10 @@
         <v>2983.657810872396</v>
       </c>
       <c r="F610" t="n">
-        <v>3135.230418701172</v>
+        <v>3135.230411376953</v>
       </c>
       <c r="G610" t="n">
-        <v>-2.646244248959762</v>
+        <v>-2.646244328781411</v>
       </c>
       <c r="H610" t="n">
         <v>3923.39201752828</v>
@@ -47456,16 +47456,16 @@
         <v>2275.594011230469</v>
       </c>
       <c r="E611" t="n">
-        <v>2289.339604492187</v>
+        <v>2289.339594726563</v>
       </c>
       <c r="F611" t="n">
-        <v>2463.761960449219</v>
+        <v>2463.761944580078</v>
       </c>
       <c r="G611" t="n">
-        <v>-3.793826524180199</v>
+        <v>-3.793826501831032</v>
       </c>
       <c r="H611" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I611" t="n">
         <v>1966.020518717901</v>
@@ -47474,7 +47474,7 @@
         <v>5.543150757814441</v>
       </c>
       <c r="K611" t="n">
-        <v>58.41742872046736</v>
+        <v>58.41741649975183</v>
       </c>
       <c r="L611" t="n">
         <v>18.53388658367912</v>
@@ -48306,13 +48306,13 @@
         <v>122.0214933776855</v>
       </c>
       <c r="F622" t="n">
-        <v>125.0251421737671</v>
+        <v>125.0251424026489</v>
       </c>
       <c r="G622" t="n">
-        <v>-2.516126906386995</v>
+        <v>-2.516126669933916</v>
       </c>
       <c r="H622" t="n">
-        <v>154.1041584954392</v>
+        <v>154.1041427094461</v>
       </c>
       <c r="I622" t="n">
         <v>104.7068431385872</v>
@@ -48321,7 +48321,7 @@
         <v>1.99906696680765</v>
       </c>
       <c r="K622" t="n">
-        <v>44.29227911234857</v>
+        <v>44.29226433145664</v>
       </c>
       <c r="L622" t="n">
         <v>16.87413554633472</v>
@@ -49230,13 +49230,13 @@
         <v>284.8430511474609</v>
       </c>
       <c r="F634" t="n">
-        <v>295.8404135131836</v>
+        <v>295.8404138183594</v>
       </c>
       <c r="G634" t="n">
-        <v>-4.30203380017764</v>
+        <v>-4.302033795930771</v>
       </c>
       <c r="H634" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I634" t="n">
         <v>254.6499938964844</v>
@@ -49245,7 +49245,7 @@
         <v>0.4908698330886807</v>
       </c>
       <c r="K634" t="n">
-        <v>58.87877059594568</v>
+        <v>58.87878269317524</v>
       </c>
       <c r="L634" t="n">
         <v>14.93775933609959</v>
@@ -49612,25 +49612,25 @@
         <v>183.2720919799805</v>
       </c>
       <c r="E639" t="n">
-        <v>191.803324991862</v>
+        <v>191.8033244832357</v>
       </c>
       <c r="F639" t="n">
-        <v>194.2098807525635</v>
+        <v>194.2098808288574</v>
       </c>
       <c r="G639" t="n">
-        <v>-2.644570830927784</v>
+        <v>-2.644570792682399</v>
       </c>
       <c r="H639" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I639" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J639" t="n">
-        <v>3.059556618367543</v>
+        <v>3.059566614574738</v>
       </c>
       <c r="K639" t="n">
-        <v>48.08636481559228</v>
+        <v>48.08634569779095</v>
       </c>
       <c r="L639" t="n">
         <v>14.24619640387275</v>
@@ -49997,16 +49997,16 @@
         <v>274.8549694824219</v>
       </c>
       <c r="E644" t="n">
-        <v>294.731100769043</v>
+        <v>294.7311009724935</v>
       </c>
       <c r="F644" t="n">
-        <v>306.1050765228272</v>
+        <v>306.105076828003</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.530043543466021</v>
+        <v>-2.530043446291974</v>
       </c>
       <c r="H644" t="n">
-        <v>396.5816020628056</v>
+        <v>396.5816646357411</v>
       </c>
       <c r="I644" t="n">
         <v>243.9284560598348</v>
@@ -50015,7 +50015,7 @@
         <v>5.440757655572992</v>
       </c>
       <c r="K644" t="n">
-        <v>54.19190639212732</v>
+        <v>54.19193072063917</v>
       </c>
       <c r="L644" t="n">
         <v>12.86307053941909</v>
@@ -50237,7 +50237,7 @@
         <v>-4.140166494617914</v>
       </c>
       <c r="H647" t="n">
-        <v>3416.473037850766</v>
+        <v>3416.47279164786</v>
       </c>
       <c r="I647" t="n">
         <v>1805.687062514093</v>
@@ -50246,7 +50246,7 @@
         <v>2.437459378841722</v>
       </c>
       <c r="K647" t="n">
-        <v>84.70417516561344</v>
+        <v>84.70416185518941</v>
       </c>
       <c r="L647" t="n">
         <v>12.44813278008299</v>
@@ -50459,16 +50459,16 @@
         <v>934.5485815429688</v>
       </c>
       <c r="E650" t="n">
-        <v>1007.661026204427</v>
+        <v>1007.661029459635</v>
       </c>
       <c r="F650" t="n">
-        <v>1054.162872924805</v>
+        <v>1054.162874145508</v>
       </c>
       <c r="G650" t="n">
-        <v>-2.580716956612894</v>
+        <v>-2.580716788853665</v>
       </c>
       <c r="H650" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I650" t="n">
         <v>838</v>
@@ -50477,7 +50477,7 @@
         <v>0.2386634844868674</v>
       </c>
       <c r="K650" t="n">
-        <v>49.42598908526264</v>
+        <v>49.42600392259955</v>
       </c>
       <c r="L650" t="n">
         <v>11.89488243430152</v>
@@ -50542,10 +50542,10 @@
         <v>95.23410854339599</v>
       </c>
       <c r="G651" t="n">
-        <v>-3.347737740962087</v>
+        <v>-3.347737778381032</v>
       </c>
       <c r="H651" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I651" t="n">
         <v>76.06999969482422</v>
@@ -50554,7 +50554,7 @@
         <v>1.748392055199632</v>
       </c>
       <c r="K651" t="n">
-        <v>61.27558052873785</v>
+        <v>61.27559068940533</v>
       </c>
       <c r="L651" t="n">
         <v>11.75656984785615</v>
@@ -50924,10 +50924,10 @@
         <v>512.2982283528646</v>
       </c>
       <c r="F656" t="n">
-        <v>543.4354052734375</v>
+        <v>543.4354055786133</v>
       </c>
       <c r="G656" t="n">
-        <v>-4.13219905959834</v>
+        <v>-4.132199212208654</v>
       </c>
       <c r="H656" t="n">
         <v>725.6811213920008</v>
@@ -51078,13 +51078,13 @@
         <v>184.6067252604167</v>
       </c>
       <c r="F658" t="n">
-        <v>197.720725479126</v>
+        <v>197.7207248687744</v>
       </c>
       <c r="G658" t="n">
-        <v>-4.078956484377983</v>
+        <v>-4.078956602965</v>
       </c>
       <c r="H658" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I658" t="n">
         <v>156.7899932861328</v>
@@ -51093,7 +51093,7 @@
         <v>1.63276543593629</v>
       </c>
       <c r="K658" t="n">
-        <v>65.18388376795374</v>
+        <v>65.18386458646501</v>
       </c>
       <c r="L658" t="n">
         <v>10.65006915629322</v>
@@ -52233,13 +52233,13 @@
         <v>254.8142333984375</v>
       </c>
       <c r="F673" t="n">
-        <v>264.1078338623047</v>
+        <v>264.1078344726562</v>
       </c>
       <c r="G673" t="n">
-        <v>-3.590627161497062</v>
+        <v>-3.590627153497095</v>
       </c>
       <c r="H673" t="n">
-        <v>355.6598900030953</v>
+        <v>355.6599215623946</v>
       </c>
       <c r="I673" t="n">
         <v>212</v>
@@ -52248,7 +52248,7 @@
         <v>2.127355899450922</v>
       </c>
       <c r="K673" t="n">
-        <v>64.26950211384626</v>
+        <v>64.2695166902169</v>
       </c>
       <c r="L673" t="n">
         <v>8.298755186721991</v>
@@ -52464,10 +52464,10 @@
         <v>2733.925447591146</v>
       </c>
       <c r="F676" t="n">
-        <v>2843.300615234375</v>
+        <v>2843.300618896485</v>
       </c>
       <c r="G676" t="n">
-        <v>-3.815094460323121</v>
+        <v>-3.815094415877551</v>
       </c>
       <c r="H676" t="n">
         <v>3812.926349899466</v>
@@ -52769,13 +52769,13 @@
         <v>356.1151885986328</v>
       </c>
       <c r="E680" t="n">
-        <v>413.0611358642578</v>
+        <v>413.0611360677083</v>
       </c>
       <c r="F680" t="n">
-        <v>441.5389633178711</v>
+        <v>441.5389642333984</v>
       </c>
       <c r="G680" t="n">
-        <v>-4.501495703494141</v>
+        <v>-4.501495694580493</v>
       </c>
       <c r="H680" t="n">
         <v>605.9581737112406</v>
@@ -53305,25 +53305,25 @@
         <v>436.3999938964844</v>
       </c>
       <c r="D687" t="n">
-        <v>502.4733087158203</v>
+        <v>502.4733099365234</v>
       </c>
       <c r="E687" t="n">
-        <v>506.6396004231771</v>
+        <v>506.639599609375</v>
       </c>
       <c r="F687" t="n">
-        <v>532.6432228088379</v>
+        <v>532.6432208251953</v>
       </c>
       <c r="G687" t="n">
-        <v>-3.722140630100812</v>
+        <v>-3.722140802773077</v>
       </c>
       <c r="H687" t="n">
         <v>798.1970626635499</v>
       </c>
       <c r="I687" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J687" t="n">
-        <v>7.456685748093261</v>
+        <v>7.456677768489084</v>
       </c>
       <c r="K687" t="n">
         <v>82.90492067533921</v>
@@ -53388,10 +53388,10 @@
         <v>274.7847361246745</v>
       </c>
       <c r="F688" t="n">
-        <v>287.0204006958008</v>
+        <v>287.0204014587403</v>
       </c>
       <c r="G688" t="n">
-        <v>-4.206596479181846</v>
+        <v>-4.206596468470503</v>
       </c>
       <c r="H688" t="n">
         <v>385.6351549871131</v>
@@ -54466,10 +54466,10 @@
         <v>246.5253459676107</v>
       </c>
       <c r="F702" t="n">
-        <v>267.1915883636474</v>
+        <v>267.1915885162354</v>
       </c>
       <c r="G702" t="n">
-        <v>-4.305497747152209</v>
+        <v>-4.305497797095626</v>
       </c>
       <c r="H702" t="n">
         <v>398.2045017598045</v>
@@ -55698,10 +55698,10 @@
         <v>653.3433640543619</v>
       </c>
       <c r="F718" t="n">
-        <v>752.2278617858886</v>
+        <v>752.2278590393066</v>
       </c>
       <c r="G718" t="n">
-        <v>-8.816885859588385</v>
+        <v>-8.816885821480714</v>
       </c>
       <c r="H718" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2029,10 +2029,10 @@
         <v>1152.465091959635</v>
       </c>
       <c r="F21" t="n">
-        <v>1069.466468505859</v>
+        <v>1069.466467895508</v>
       </c>
       <c r="G21" t="n">
-        <v>5.938308520267088</v>
+        <v>5.93830852385735</v>
       </c>
       <c r="H21" t="n">
         <v>1677.5</v>
@@ -2192,10 +2192,10 @@
         <v>1357.900024414062</v>
       </c>
       <c r="I23" t="n">
-        <v>594.6744698202933</v>
+        <v>594.6745299041222</v>
       </c>
       <c r="J23" t="n">
-        <v>115.4287834103719</v>
+        <v>115.4287616442032</v>
       </c>
       <c r="K23" t="n">
         <v>5.994852103013959</v>
@@ -3732,10 +3732,10 @@
         <v>8949.5</v>
       </c>
       <c r="I43" t="n">
-        <v>4504.255799235611</v>
+        <v>4504.255320019595</v>
       </c>
       <c r="J43" t="n">
-        <v>85.43573838362934</v>
+        <v>85.43575811247892</v>
       </c>
       <c r="K43" t="n">
         <v>7.147560610595627</v>
@@ -4567,13 +4567,13 @@
         <v>265.6028851318359</v>
       </c>
       <c r="E54" t="n">
-        <v>239.4038417561849</v>
+        <v>239.4038415527344</v>
       </c>
       <c r="F54" t="n">
-        <v>227.5020847320557</v>
+        <v>227.5020845794678</v>
       </c>
       <c r="G54" t="n">
-        <v>4.916182229911636</v>
+        <v>4.916182307198835</v>
       </c>
       <c r="H54" t="n">
         <v>321.3999938964844</v>
@@ -5494,10 +5494,10 @@
         <v>1036.274944661458</v>
       </c>
       <c r="F66" t="n">
-        <v>982.9050402832031</v>
+        <v>982.9050405883789</v>
       </c>
       <c r="G66" t="n">
-        <v>3.774019961164221</v>
+        <v>3.774019826203778</v>
       </c>
       <c r="H66" t="n">
         <v>1368.900024414062</v>
@@ -5953,22 +5953,22 @@
         <v>1922.426003417969</v>
       </c>
       <c r="E72" t="n">
-        <v>1663.554341634115</v>
+        <v>1663.5543359375</v>
       </c>
       <c r="F72" t="n">
-        <v>1600.597966918945</v>
+        <v>1600.597972412109</v>
       </c>
       <c r="G72" t="n">
-        <v>3.092936568398863</v>
+        <v>3.092936395343604</v>
       </c>
       <c r="H72" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I72" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J72" t="n">
-        <v>52.71352566771694</v>
+        <v>52.71353999670363</v>
       </c>
       <c r="K72" t="n">
         <v>5.430285546429103</v>
@@ -8038,7 +8038,7 @@
         <v>246.5629221343994</v>
       </c>
       <c r="G99" t="n">
-        <v>6.796229810429666</v>
+        <v>6.79622977513783</v>
       </c>
       <c r="H99" t="n">
         <v>388.75</v>
@@ -9110,25 +9110,25 @@
         <v>1395.578447265625</v>
       </c>
       <c r="E113" t="n">
-        <v>1420.626493326823</v>
+        <v>1420.626495768229</v>
       </c>
       <c r="F113" t="n">
-        <v>1356.434479980469</v>
+        <v>1356.434478759766</v>
       </c>
       <c r="G113" t="n">
-        <v>3.399319172111825</v>
+        <v>3.399319175274984</v>
       </c>
       <c r="H113" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I113" t="n">
-        <v>969.6358757670704</v>
+        <v>969.6359336843161</v>
       </c>
       <c r="J113" t="n">
-        <v>58.17277284202984</v>
+        <v>58.17276339422472</v>
       </c>
       <c r="K113" t="n">
-        <v>15.19418693410601</v>
+        <v>15.19417859408085</v>
       </c>
       <c r="L113" t="n">
         <v>86.99861687413555</v>
@@ -9267,10 +9267,10 @@
         <v>564.4769486490885</v>
       </c>
       <c r="F115" t="n">
-        <v>540.2359443664551</v>
+        <v>540.2359436035156</v>
       </c>
       <c r="G115" t="n">
-        <v>5.346708213895801</v>
+        <v>5.346708315887527</v>
       </c>
       <c r="H115" t="n">
         <v>795.731978165477</v>
@@ -10650,13 +10650,13 @@
         <v>2631.878286132813</v>
       </c>
       <c r="E133" t="n">
-        <v>2238.462375488281</v>
+        <v>2238.462371419271</v>
       </c>
       <c r="F133" t="n">
-        <v>2127.708236694336</v>
+        <v>2127.708236083985</v>
       </c>
       <c r="G133" t="n">
-        <v>4.212615408885956</v>
+        <v>4.212615347838056</v>
       </c>
       <c r="H133" t="n">
         <v>2990</v>
@@ -14349,10 +14349,10 @@
         <v>1500.507991536458</v>
       </c>
       <c r="F181" t="n">
-        <v>1521.33590637207</v>
+        <v>1521.335908813477</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.3660709844439336</v>
+        <v>-0.3660709042061061</v>
       </c>
       <c r="H181" t="n">
         <v>2021.199951171875</v>
@@ -14503,10 +14503,10 @@
         <v>157.6066696675618</v>
       </c>
       <c r="F183" t="n">
-        <v>155.7515455245972</v>
+        <v>155.7515458297729</v>
       </c>
       <c r="G183" t="n">
-        <v>2.894129195707018</v>
+        <v>2.894129034289916</v>
       </c>
       <c r="H183" t="n">
         <v>233.3500061035156</v>
@@ -14577,13 +14577,13 @@
         <v>7321.86771484375</v>
       </c>
       <c r="E184" t="n">
-        <v>6930.701979166667</v>
+        <v>6930.701988932292</v>
       </c>
       <c r="F184" t="n">
-        <v>6522.995600585938</v>
+        <v>6522.995595703125</v>
       </c>
       <c r="G184" t="n">
-        <v>3.458910563756867</v>
+        <v>3.458910446250685</v>
       </c>
       <c r="H184" t="n">
         <v>7832.294844565128</v>
@@ -15963,13 +15963,13 @@
         <v>337.5905517578125</v>
       </c>
       <c r="E202" t="n">
-        <v>312.6794970703125</v>
+        <v>312.6794974772135</v>
       </c>
       <c r="F202" t="n">
-        <v>309.57515625</v>
+        <v>309.5751567077637</v>
       </c>
       <c r="G202" t="n">
-        <v>1.407416145796203</v>
+        <v>1.407415890252617</v>
       </c>
       <c r="H202" t="n">
         <v>380.4567148307952</v>
@@ -16197,10 +16197,10 @@
         <v>622.5934993489583</v>
       </c>
       <c r="F205" t="n">
-        <v>610.8240585327148</v>
+        <v>610.824058227539</v>
       </c>
       <c r="G205" t="n">
-        <v>1.593188181393934</v>
+        <v>1.593188130636625</v>
       </c>
       <c r="H205" t="n">
         <v>769</v>
@@ -17349,16 +17349,16 @@
         <v>1944.388962402344</v>
       </c>
       <c r="E220" t="n">
-        <v>1793.613325195312</v>
+        <v>1793.613319498698</v>
       </c>
       <c r="F220" t="n">
-        <v>1782.974750366211</v>
+        <v>1782.974748535156</v>
       </c>
       <c r="G220" t="n">
-        <v>1.513915637995589</v>
+        <v>1.513915745403516</v>
       </c>
       <c r="H220" t="n">
-        <v>2256.187656125729</v>
+        <v>2256.187906504501</v>
       </c>
       <c r="I220" t="n">
         <v>1345.285007075603</v>
@@ -17367,7 +17367,7 @@
         <v>40.84004067588598</v>
       </c>
       <c r="K220" t="n">
-        <v>19.0788892315257</v>
+        <v>19.07890244621819</v>
       </c>
       <c r="L220" t="n">
         <v>57.95297372060858</v>
@@ -17891,10 +17891,10 @@
         <v>284.2952432250976</v>
       </c>
       <c r="F227" t="n">
-        <v>270.5788997650146</v>
+        <v>270.5788991546631</v>
       </c>
       <c r="G227" t="n">
-        <v>2.129083609458426</v>
+        <v>2.129083584953317</v>
       </c>
       <c r="H227" t="n">
         <v>367.499792159746</v>
@@ -18042,13 +18042,13 @@
         <v>292.5769989013672</v>
       </c>
       <c r="E229" t="n">
-        <v>298.6359089152018</v>
+        <v>298.635908610026</v>
       </c>
       <c r="F229" t="n">
-        <v>286.3550670623779</v>
+        <v>286.3550663757324</v>
       </c>
       <c r="G229" t="n">
-        <v>1.195623113970923</v>
+        <v>1.195623007735991</v>
       </c>
       <c r="H229" t="n">
         <v>359.3387168134344</v>
@@ -20891,16 +20891,16 @@
         <v>4562.245986328125</v>
       </c>
       <c r="E266" t="n">
-        <v>4245.175914713542</v>
+        <v>4245.175908203125</v>
       </c>
       <c r="F266" t="n">
-        <v>4311.861713867187</v>
+        <v>4311.861721191406</v>
       </c>
       <c r="G266" t="n">
-        <v>0.3716467078415553</v>
+        <v>0.3716468212926038</v>
       </c>
       <c r="H266" t="n">
-        <v>5005.771680286142</v>
+        <v>5005.772176274182</v>
       </c>
       <c r="I266" t="n">
         <v>3669.905008549105</v>
@@ -20909,7 +20909,7 @@
         <v>20.54262424728117</v>
       </c>
       <c r="K266" t="n">
-        <v>13.15547496028142</v>
+        <v>13.15548617209166</v>
       </c>
       <c r="L266" t="n">
         <v>63.07053941908713</v>
@@ -21202,10 +21202,10 @@
         <v>1716.342147623698</v>
       </c>
       <c r="F270" t="n">
-        <v>1684.047633666992</v>
+        <v>1684.047631835937</v>
       </c>
       <c r="G270" t="n">
-        <v>0.8604279767471024</v>
+        <v>0.8604279408211957</v>
       </c>
       <c r="H270" t="n">
         <v>1983.954544928268</v>
@@ -21282,7 +21282,7 @@
         <v>1141.952951049805</v>
       </c>
       <c r="G271" t="n">
-        <v>-0.9618365097926906</v>
+        <v>-0.9618364049430395</v>
       </c>
       <c r="H271" t="n">
         <v>1409.944064008135</v>
@@ -22354,13 +22354,13 @@
         <v>367.6356274414063</v>
       </c>
       <c r="E285" t="n">
-        <v>379.0023659261068</v>
+        <v>379.0023655192057</v>
       </c>
       <c r="F285" t="n">
-        <v>369.8846578979492</v>
+        <v>369.8846586608886</v>
       </c>
       <c r="G285" t="n">
-        <v>2.744382610743701</v>
+        <v>2.744382474283125</v>
       </c>
       <c r="H285" t="n">
         <v>443.3731066930094</v>
@@ -22588,10 +22588,10 @@
         <v>1382.492112630208</v>
       </c>
       <c r="F288" t="n">
-        <v>1358.18283996582</v>
+        <v>1358.182841186524</v>
       </c>
       <c r="G288" t="n">
-        <v>0.9669244234431718</v>
+        <v>0.9669243309415654</v>
       </c>
       <c r="H288" t="n">
         <v>1553</v>
@@ -22745,7 +22745,7 @@
         <v>8033.545246582031</v>
       </c>
       <c r="G290" t="n">
-        <v>1.909621541855588</v>
+        <v>1.909621573417475</v>
       </c>
       <c r="H290" t="n">
         <v>9070.5</v>
@@ -22819,10 +22819,10 @@
         <v>463.9691103108724</v>
       </c>
       <c r="F291" t="n">
-        <v>459.1777590942383</v>
+        <v>459.1777577209473</v>
       </c>
       <c r="G291" t="n">
-        <v>1.545969745780407</v>
+        <v>1.545969784741619</v>
       </c>
       <c r="H291" t="n">
         <v>529.9163379046904</v>
@@ -24436,19 +24436,19 @@
         <v>36878.0729296875</v>
       </c>
       <c r="F312" t="n">
-        <v>36135.84942382813</v>
+        <v>36135.84953125</v>
       </c>
       <c r="G312" t="n">
-        <v>-0.2925467224369926</v>
+        <v>-0.2925467753036037</v>
       </c>
       <c r="H312" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I312" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J312" t="n">
-        <v>24.89300028230481</v>
+        <v>24.89299212857414</v>
       </c>
       <c r="K312" t="n">
         <v>18.27581169063035</v>
@@ -27054,10 +27054,10 @@
         <v>1671.659571126302</v>
       </c>
       <c r="F346" t="n">
-        <v>1678.786267700195</v>
+        <v>1678.786268920898</v>
       </c>
       <c r="G346" t="n">
-        <v>0.0005590967108615175</v>
+        <v>0.0005591330675569495</v>
       </c>
       <c r="H346" t="n">
         <v>1952.5</v>
@@ -27901,10 +27901,10 @@
         <v>775.9822493489584</v>
       </c>
       <c r="F357" t="n">
-        <v>787.4050061035156</v>
+        <v>787.4050082397461</v>
       </c>
       <c r="G357" t="n">
-        <v>-1.170466994336516</v>
+        <v>-1.17046695334303</v>
       </c>
       <c r="H357" t="n">
         <v>1100.079694414754</v>
@@ -28517,13 +28517,13 @@
         <v>1636.842416178386</v>
       </c>
       <c r="F365" t="n">
-        <v>1718.093669433594</v>
+        <v>1718.093666992188</v>
       </c>
       <c r="G365" t="n">
-        <v>-3.556123419202217</v>
+        <v>-3.556123225816354</v>
       </c>
       <c r="H365" t="n">
-        <v>2339.801318384509</v>
+        <v>2339.80156593166</v>
       </c>
       <c r="I365" t="n">
         <v>1322.972836511248</v>
@@ -28532,7 +28532,7 @@
         <v>26.97917735363726</v>
       </c>
       <c r="K365" t="n">
-        <v>39.28217658075308</v>
+        <v>39.28219131657951</v>
       </c>
       <c r="L365" t="n">
         <v>36.65283540802213</v>
@@ -28979,10 +28979,10 @@
         <v>154.0327819824219</v>
       </c>
       <c r="F371" t="n">
-        <v>150.7346167755127</v>
+        <v>150.7346166992187</v>
       </c>
       <c r="G371" t="n">
-        <v>1.202054297001554</v>
+        <v>1.20205450497286</v>
       </c>
       <c r="H371" t="n">
         <v>196.4205715539644</v>
@@ -29441,10 +29441,10 @@
         <v>200.1467339070638</v>
       </c>
       <c r="F377" t="n">
-        <v>206.3609925079346</v>
+        <v>206.3609921264649</v>
       </c>
       <c r="G377" t="n">
-        <v>-2.042265583114999</v>
+        <v>-2.042265799671716</v>
       </c>
       <c r="H377" t="n">
         <v>278.3389924341271</v>
@@ -31212,10 +31212,10 @@
         <v>2150.704470214844</v>
       </c>
       <c r="F400" t="n">
-        <v>2090.827896728515</v>
+        <v>2090.827900390625</v>
       </c>
       <c r="G400" t="n">
-        <v>0.2527634114814825</v>
+        <v>0.2527633816980401</v>
       </c>
       <c r="H400" t="n">
         <v>2625.96691593483</v>
@@ -31289,13 +31289,13 @@
         <v>1076.412305908203</v>
       </c>
       <c r="F401" t="n">
-        <v>1078.720033569336</v>
+        <v>1078.720035095215</v>
       </c>
       <c r="G401" t="n">
-        <v>-0.7606993568851528</v>
+        <v>-0.7606991886466963</v>
       </c>
       <c r="H401" t="n">
-        <v>1300.436668328248</v>
+        <v>1300.436795781491</v>
       </c>
       <c r="I401" t="n">
         <v>885.652283987356</v>
@@ -31304,7 +31304,7 @@
         <v>17.74373167460974</v>
       </c>
       <c r="K401" t="n">
-        <v>24.70623393138971</v>
+        <v>24.70624615360275</v>
       </c>
       <c r="L401" t="n">
         <v>46.33471645919779</v>
@@ -31446,7 +31446,7 @@
         <v>743.5796044921875</v>
       </c>
       <c r="G403" t="n">
-        <v>-0.3278043735201686</v>
+        <v>-0.3278042919745539</v>
       </c>
       <c r="H403" t="n">
         <v>879.2203373423794</v>
@@ -31597,10 +31597,10 @@
         <v>667.2407759602864</v>
       </c>
       <c r="F405" t="n">
-        <v>665.4453070068359</v>
+        <v>665.4453076171875</v>
       </c>
       <c r="G405" t="n">
-        <v>-0.8775536305657194</v>
+        <v>-0.8775536297678799</v>
       </c>
       <c r="H405" t="n">
         <v>792.3323631991859</v>
@@ -31677,7 +31677,7 @@
         <v>82.26331275939941</v>
       </c>
       <c r="G406" t="n">
-        <v>0.768211832272625</v>
+        <v>0.7682117851856241</v>
       </c>
       <c r="H406" t="n">
         <v>96.1838663751024</v>
@@ -32059,10 +32059,10 @@
         <v>1142.408075764974</v>
       </c>
       <c r="F411" t="n">
-        <v>1161.615496520996</v>
+        <v>1161.615498352051</v>
       </c>
       <c r="G411" t="n">
-        <v>-0.8502421319526943</v>
+        <v>-0.8502423372384493</v>
       </c>
       <c r="H411" t="n">
         <v>1378.852549646065</v>
@@ -32213,10 +32213,10 @@
         <v>738.0826025390625</v>
       </c>
       <c r="F413" t="n">
-        <v>733.361408996582</v>
+        <v>733.3614093017578</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.9137135151970566</v>
+        <v>-0.9137135965328946</v>
       </c>
       <c r="H413" t="n">
         <v>837.8765073351432</v>
@@ -32290,19 +32290,19 @@
         <v>340.0530466715495</v>
       </c>
       <c r="F414" t="n">
-        <v>334.3344020080567</v>
+        <v>334.3344026184082</v>
       </c>
       <c r="G414" t="n">
-        <v>-0.00961281246039114</v>
+        <v>-0.009612858073382302</v>
       </c>
       <c r="H414" t="n">
         <v>385.3928663983843</v>
       </c>
       <c r="I414" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J414" t="n">
-        <v>9.332095925581839</v>
+        <v>9.332084284172982</v>
       </c>
       <c r="K414" t="n">
         <v>24.7024370234104</v>
@@ -32444,10 +32444,10 @@
         <v>356.3050866699219</v>
       </c>
       <c r="F416" t="n">
-        <v>353.5636616516113</v>
+        <v>353.5636613464355</v>
       </c>
       <c r="G416" t="n">
-        <v>0.1914135833801067</v>
+        <v>0.1914134969006609</v>
       </c>
       <c r="H416" t="n">
         <v>409.9712889887167</v>
@@ -32521,10 +32521,10 @@
         <v>77.20693344116211</v>
       </c>
       <c r="F417" t="n">
-        <v>77.18057178497314</v>
+        <v>77.18057174682617</v>
       </c>
       <c r="G417" t="n">
-        <v>-0.150582421292067</v>
+        <v>-0.1505822735357487</v>
       </c>
       <c r="H417" t="n">
         <v>86.59303970157107</v>
@@ -32909,10 +32909,10 @@
         <v>488.5623118591309</v>
       </c>
       <c r="G422" t="n">
-        <v>-0.7674907936617514</v>
+        <v>-0.7674909166795807</v>
       </c>
       <c r="H422" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I422" t="n">
         <v>419.3328127807616</v>
@@ -32921,7 +32921,7 @@
         <v>5.405536253870347</v>
       </c>
       <c r="K422" t="n">
-        <v>23.92261815939816</v>
+        <v>23.92263215418482</v>
       </c>
       <c r="L422" t="n">
         <v>38.0359612724758</v>
@@ -34600,10 +34600,10 @@
         <v>5155.841748046875</v>
       </c>
       <c r="F444" t="n">
-        <v>5246.337229003906</v>
+        <v>5246.337231445313</v>
       </c>
       <c r="G444" t="n">
-        <v>-1.331976200999674</v>
+        <v>-1.33197638160415</v>
       </c>
       <c r="H444" t="n">
         <v>6175.521739453033</v>
@@ -35062,10 +35062,10 @@
         <v>255.9502903238932</v>
       </c>
       <c r="F450" t="n">
-        <v>253.9920562744141</v>
+        <v>253.9920560455322</v>
       </c>
       <c r="G450" t="n">
-        <v>-0.1914956361542597</v>
+        <v>-0.1914957560184671</v>
       </c>
       <c r="H450" t="n">
         <v>306.197022156633</v>
@@ -35447,10 +35447,10 @@
         <v>1408.740965983073</v>
       </c>
       <c r="F455" t="n">
-        <v>1399.355314331055</v>
+        <v>1399.355314941406</v>
       </c>
       <c r="G455" t="n">
-        <v>-0.164630680399569</v>
+        <v>-0.1646307672741432</v>
       </c>
       <c r="H455" t="n">
         <v>1817.803954384172</v>
@@ -35598,13 +35598,13 @@
         <v>1289.520002441406</v>
       </c>
       <c r="E457" t="n">
-        <v>1244.364006754557</v>
+        <v>1244.364000244141</v>
       </c>
       <c r="F457" t="n">
-        <v>1321.149825134277</v>
+        <v>1321.149817810058</v>
       </c>
       <c r="G457" t="n">
-        <v>-2.842497536881572</v>
+        <v>-2.842497508582476</v>
       </c>
       <c r="H457" t="n">
         <v>1729.008500794829</v>
@@ -36140,10 +36140,10 @@
         <v>2208.13845296224</v>
       </c>
       <c r="F464" t="n">
-        <v>2266.120416870117</v>
+        <v>2266.120425415039</v>
       </c>
       <c r="G464" t="n">
-        <v>-0.8929558733572596</v>
+        <v>-0.8929556583810228</v>
       </c>
       <c r="H464" t="n">
         <v>2765.379504159864</v>
@@ -36525,10 +36525,10 @@
         <v>207.2537642415365</v>
       </c>
       <c r="F469" t="n">
-        <v>211.0798310089111</v>
+        <v>211.079831237793</v>
       </c>
       <c r="G469" t="n">
-        <v>-1.246292618960598</v>
+        <v>-1.246292511878211</v>
       </c>
       <c r="H469" t="n">
         <v>252.6160882566492</v>
@@ -36602,13 +36602,13 @@
         <v>418.5872133382161</v>
       </c>
       <c r="F470" t="n">
-        <v>436.8794020080566</v>
+        <v>436.8794007873535</v>
       </c>
       <c r="G470" t="n">
-        <v>-2.590126214962407</v>
+        <v>-2.590126222012135</v>
       </c>
       <c r="H470" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I470" t="n">
         <v>363.2227809620478</v>
@@ -36617,7 +36617,7 @@
         <v>10.13901350938913</v>
       </c>
       <c r="K470" t="n">
-        <v>33.41051643251367</v>
+        <v>33.41053233061422</v>
       </c>
       <c r="L470" t="n">
         <v>35.26970954356847</v>
@@ -37603,13 +37603,13 @@
         <v>611.9190600585938</v>
       </c>
       <c r="F483" t="n">
-        <v>616.6395175170899</v>
+        <v>616.6395156860351</v>
       </c>
       <c r="G483" t="n">
-        <v>-1.575196912479737</v>
+        <v>-1.5751968211969</v>
       </c>
       <c r="H483" t="n">
-        <v>848.8263047717415</v>
+        <v>848.8262434052705</v>
       </c>
       <c r="I483" t="n">
         <v>495.5999980879241</v>
@@ -37618,7 +37618,7 @@
         <v>19.20903754486199</v>
       </c>
       <c r="K483" t="n">
-        <v>43.67405590895031</v>
+        <v>43.67404552193739</v>
       </c>
       <c r="L483" t="n">
         <v>31.3969571230982</v>
@@ -38059,16 +38059,16 @@
         <v>327.7999877929688</v>
       </c>
       <c r="D489" t="n">
-        <v>358.3678228759766</v>
+        <v>358.367822265625</v>
       </c>
       <c r="E489" t="n">
         <v>398.1887921142578</v>
       </c>
       <c r="F489" t="n">
-        <v>390.9700430297851</v>
+        <v>390.9700425720215</v>
       </c>
       <c r="G489" t="n">
-        <v>-0.0970617546961261</v>
+        <v>-0.09706191061885638</v>
       </c>
       <c r="H489" t="n">
         <v>476.8288845013619</v>
@@ -38373,10 +38373,10 @@
         <v>411.0669832356771</v>
       </c>
       <c r="F493" t="n">
-        <v>414.9975332641602</v>
+        <v>414.9975320434571</v>
       </c>
       <c r="G493" t="n">
-        <v>-1.31801187437206</v>
+        <v>-1.318012057225582</v>
       </c>
       <c r="H493" t="n">
         <v>684.5682054144123</v>
@@ -40150,7 +40150,7 @@
         <v>-1.779575527019328</v>
       </c>
       <c r="H516" t="n">
-        <v>2908.974119515923</v>
+        <v>2908.974368726317</v>
       </c>
       <c r="I516" t="n">
         <v>1987.699951171875</v>
@@ -40159,7 +40159,7 @@
         <v>1.121902167124245</v>
       </c>
       <c r="K516" t="n">
-        <v>44.72508057293147</v>
+        <v>44.72509297145857</v>
       </c>
       <c r="L516" t="n">
         <v>18.25726141078838</v>
@@ -40988,16 +40988,16 @@
         <v>357.6204089355469</v>
       </c>
       <c r="E527" t="n">
-        <v>410.6158723958333</v>
+        <v>410.6158721923828</v>
       </c>
       <c r="F527" t="n">
-        <v>439.5273533630371</v>
+        <v>439.5273524475098</v>
       </c>
       <c r="G527" t="n">
-        <v>-4.390985018694971</v>
+        <v>-4.390985090908728</v>
       </c>
       <c r="H527" t="n">
-        <v>605.9581737112406</v>
+        <v>605.9581114957105</v>
       </c>
       <c r="I527" t="n">
         <v>326.057353105007</v>
@@ -41006,7 +41006,7 @@
         <v>10.54803971586804</v>
       </c>
       <c r="K527" t="n">
-        <v>68.11156975719483</v>
+        <v>68.11155249667935</v>
       </c>
       <c r="L527" t="n">
         <v>9.95850622406639</v>
@@ -41915,10 +41915,10 @@
         <v>2605.984680989583</v>
       </c>
       <c r="F539" t="n">
-        <v>2678.223513183594</v>
+        <v>2678.223515625</v>
       </c>
       <c r="G539" t="n">
-        <v>-1.517589888490478</v>
+        <v>-1.517590196569607</v>
       </c>
       <c r="H539" t="n">
         <v>3198.009229338596</v>
@@ -42066,22 +42066,22 @@
         <v>220.8836917114258</v>
       </c>
       <c r="E541" t="n">
-        <v>222.8660999552409</v>
+        <v>222.8661004638672</v>
       </c>
       <c r="F541" t="n">
-        <v>224.2614191436768</v>
+        <v>224.2614192962646</v>
       </c>
       <c r="G541" t="n">
-        <v>-1.314518309843482</v>
+        <v>-1.314518308960844</v>
       </c>
       <c r="H541" t="n">
         <v>286.0804190389319</v>
       </c>
       <c r="I541" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J541" t="n">
-        <v>17.28216081834251</v>
+        <v>17.28217115275532</v>
       </c>
       <c r="K541" t="n">
         <v>41.85571559299233</v>
@@ -42223,10 +42223,10 @@
         <v>415.5020284016927</v>
       </c>
       <c r="F543" t="n">
-        <v>416.6231359863281</v>
+        <v>416.6231356811523</v>
       </c>
       <c r="G543" t="n">
-        <v>-0.2976555571110095</v>
+        <v>-0.2976555209211806</v>
       </c>
       <c r="H543" t="n">
         <v>472.8081629796919</v>
@@ -42377,10 +42377,10 @@
         <v>4598.175008138021</v>
       </c>
       <c r="F545" t="n">
-        <v>4748.620787353516</v>
+        <v>4748.620792236328</v>
       </c>
       <c r="G545" t="n">
-        <v>-0.3876886314753358</v>
+        <v>-0.3876886310782535</v>
       </c>
       <c r="H545" t="n">
         <v>5612.405266256894</v>
@@ -42528,13 +42528,13 @@
         <v>136.4532609558105</v>
       </c>
       <c r="E547" t="n">
-        <v>140.1806429545085</v>
+        <v>140.1806430562337</v>
       </c>
       <c r="F547" t="n">
-        <v>146.1266688919067</v>
+        <v>146.1266692733765</v>
       </c>
       <c r="G547" t="n">
-        <v>-1.718753443132726</v>
+        <v>-1.718753640448967</v>
       </c>
       <c r="H547" t="n">
         <v>184.9587904135824</v>
@@ -42916,10 +42916,10 @@
         <v>130131.19140625</v>
       </c>
       <c r="F552" t="n">
-        <v>133963.907421875</v>
+        <v>133963.907578125</v>
       </c>
       <c r="G552" t="n">
-        <v>-2.273530573367033</v>
+        <v>-2.273530737864571</v>
       </c>
       <c r="H552" t="n">
         <v>163308.4863287346</v>
@@ -43612,7 +43612,7 @@
         <v>847.2104202270508</v>
       </c>
       <c r="G561" t="n">
-        <v>-1.682951667702892</v>
+        <v>-1.682951598064875</v>
       </c>
       <c r="H561" t="n">
         <v>962.6932158005569</v>
@@ -43766,7 +43766,7 @@
         <v>33.62466212272644</v>
       </c>
       <c r="G563" t="n">
-        <v>-1.935275953894044</v>
+        <v>-1.935276062994795</v>
       </c>
       <c r="H563" t="n">
         <v>40.26070662850351</v>
@@ -43914,13 +43914,13 @@
         <v>323.670146484375</v>
       </c>
       <c r="E565" t="n">
-        <v>336.6633241780599</v>
+        <v>336.6633243815104</v>
       </c>
       <c r="F565" t="n">
-        <v>340.0451419067383</v>
+        <v>340.0451425170899</v>
       </c>
       <c r="G565" t="n">
-        <v>-1.041343703228348</v>
+        <v>-1.041343745321832</v>
       </c>
       <c r="H565" t="n">
         <v>381.3442016302781</v>
@@ -44071,13 +44071,13 @@
         <v>20.22101926167806</v>
       </c>
       <c r="F567" t="n">
-        <v>20.35237322807312</v>
+        <v>20.35237323760986</v>
       </c>
       <c r="G567" t="n">
-        <v>-1.634394168562592</v>
+        <v>-1.634394213148216</v>
       </c>
       <c r="H567" t="n">
-        <v>23.83526024888653</v>
+        <v>23.83526224893035</v>
       </c>
       <c r="I567" t="n">
         <v>16.75</v>
@@ -44086,7 +44086,7 @@
         <v>4.358206222306427</v>
       </c>
       <c r="K567" t="n">
-        <v>36.3573276492039</v>
+        <v>36.35733909110248</v>
       </c>
       <c r="L567" t="n">
         <v>29.87551867219917</v>
@@ -44225,10 +44225,10 @@
         <v>1055.335689290365</v>
       </c>
       <c r="F569" t="n">
-        <v>1081.164976806641</v>
+        <v>1081.164978027344</v>
       </c>
       <c r="G569" t="n">
-        <v>-2.354029441318473</v>
+        <v>-2.354029438723193</v>
       </c>
       <c r="H569" t="n">
         <v>1395.129939548488</v>
@@ -44687,10 +44687,10 @@
         <v>154.3519301350912</v>
       </c>
       <c r="F575" t="n">
-        <v>159.6699295043945</v>
+        <v>159.6699293518066</v>
       </c>
       <c r="G575" t="n">
-        <v>-2.85762636156166</v>
+        <v>-2.857626454395357</v>
       </c>
       <c r="H575" t="n">
         <v>217.0279658924327</v>
@@ -45072,10 +45072,10 @@
         <v>895.559550374349</v>
       </c>
       <c r="F580" t="n">
-        <v>914.5640176391602</v>
+        <v>914.5640200805664</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.182653700293279</v>
+        <v>-1.182653664589717</v>
       </c>
       <c r="H580" t="n">
         <v>1282.80960014975</v>
@@ -46227,13 +46227,13 @@
         <v>121.6738223775228</v>
       </c>
       <c r="F595" t="n">
-        <v>123.5300846099854</v>
+        <v>123.5300848007202</v>
       </c>
       <c r="G595" t="n">
-        <v>-2.401067573139504</v>
+        <v>-2.401067804845847</v>
       </c>
       <c r="H595" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I595" t="n">
         <v>103.5</v>
@@ -46242,7 +46242,7 @@
         <v>1.236713796422095</v>
       </c>
       <c r="K595" t="n">
-        <v>48.78790085533089</v>
+        <v>48.78791772409923</v>
       </c>
       <c r="L595" t="n">
         <v>22.82157676348548</v>
@@ -47234,7 +47234,7 @@
         <v>-0.6169167058190927</v>
       </c>
       <c r="H608" t="n">
-        <v>509.5710426414886</v>
+        <v>509.5710734571873</v>
       </c>
       <c r="I608" t="n">
         <v>371.25</v>
@@ -47243,7 +47243,7 @@
         <v>0.8215455334595889</v>
       </c>
       <c r="K608" t="n">
-        <v>36.13974332356658</v>
+        <v>36.13975155645453</v>
       </c>
       <c r="L608" t="n">
         <v>19.91701244813278</v>
@@ -47841,13 +47841,13 @@
         <v>918.1975402832031</v>
       </c>
       <c r="E616" t="n">
-        <v>1001.708784586589</v>
+        <v>1001.708787841797</v>
       </c>
       <c r="F616" t="n">
-        <v>1049.910986633301</v>
+        <v>1049.910987243652</v>
       </c>
       <c r="G616" t="n">
-        <v>-2.64344340330982</v>
+        <v>-2.643443236511289</v>
       </c>
       <c r="H616" t="n">
         <v>1255.178432949836</v>
@@ -47998,13 +47998,13 @@
         <v>1210.195720621745</v>
       </c>
       <c r="F618" t="n">
-        <v>1254.252859191894</v>
+        <v>1254.252862243652</v>
       </c>
       <c r="G618" t="n">
-        <v>-2.838696454520917</v>
+        <v>-2.838696264054041</v>
       </c>
       <c r="H618" t="n">
-        <v>1507.849216441457</v>
+        <v>1507.849092404508</v>
       </c>
       <c r="I618" t="n">
         <v>1015.099975585938</v>
@@ -48013,7 +48013,7 @@
         <v>2.600731459856842</v>
       </c>
       <c r="K618" t="n">
-        <v>44.77668904862764</v>
+        <v>44.77667713917501</v>
       </c>
       <c r="L618" t="n">
         <v>17.28907330567082</v>
@@ -48768,13 +48768,13 @@
         <v>121.3956878662109</v>
       </c>
       <c r="F628" t="n">
-        <v>124.5019654846191</v>
+        <v>124.5019652557373</v>
       </c>
       <c r="G628" t="n">
-        <v>-2.594452679804116</v>
+        <v>-2.59445291701329</v>
       </c>
       <c r="H628" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I628" t="n">
         <v>103.0999984741211</v>
@@ -48783,7 +48783,7 @@
         <v>1.299712887601556</v>
       </c>
       <c r="K628" t="n">
-        <v>47.55279500869685</v>
+        <v>47.55281012358832</v>
       </c>
       <c r="L628" t="n">
         <v>15.62932226832642</v>
@@ -48922,10 +48922,10 @@
         <v>190.601543375651</v>
       </c>
       <c r="F630" t="n">
-        <v>193.2109911346436</v>
+        <v>193.2109908294678</v>
       </c>
       <c r="G630" t="n">
-        <v>-2.806849665263922</v>
+        <v>-2.806849594969341</v>
       </c>
       <c r="H630" t="n">
         <v>239.2186728978909</v>
@@ -48999,10 +48999,10 @@
         <v>510.0540405273438</v>
       </c>
       <c r="F631" t="n">
-        <v>541.2885366821289</v>
+        <v>541.2885372924804</v>
       </c>
       <c r="G631" t="n">
-        <v>-4.187475453228173</v>
+        <v>-4.187475552217368</v>
       </c>
       <c r="H631" t="n">
         <v>725.6811213920008</v>
@@ -49852,7 +49852,7 @@
         <v>-3.027442804377789</v>
       </c>
       <c r="H642" t="n">
-        <v>541.0236304500187</v>
+        <v>541.0235690240457</v>
       </c>
       <c r="I642" t="n">
         <v>271.5615990811692</v>
@@ -49861,7 +49861,7 @@
         <v>19.78865527881108</v>
       </c>
       <c r="K642" t="n">
-        <v>66.31529380638752</v>
+        <v>66.31527492351779</v>
       </c>
       <c r="L642" t="n">
         <v>13.13969571230982</v>
@@ -50699,7 +50699,7 @@
         <v>-4.316373705022536</v>
       </c>
       <c r="H653" t="n">
-        <v>3416.47279164786</v>
+        <v>3416.473037850766</v>
       </c>
       <c r="I653" t="n">
         <v>1770</v>
@@ -50708,7 +50708,7 @@
         <v>2.440675207450571</v>
       </c>
       <c r="K653" t="n">
-        <v>88.42228566351913</v>
+        <v>88.42229924188408</v>
       </c>
       <c r="L653" t="n">
         <v>11.61825726141079</v>
@@ -50847,13 +50847,13 @@
         <v>253.3609162394206</v>
       </c>
       <c r="F655" t="n">
-        <v>262.8633069610595</v>
+        <v>262.863306350708</v>
       </c>
       <c r="G655" t="n">
-        <v>-3.743911991291726</v>
+        <v>-3.743911999659377</v>
       </c>
       <c r="H655" t="n">
-        <v>355.6599215623946</v>
+        <v>355.6598900030953</v>
       </c>
       <c r="I655" t="n">
         <v>212</v>
@@ -50862,7 +50862,7 @@
         <v>1.995281003556171</v>
       </c>
       <c r="K655" t="n">
-        <v>64.48223123055712</v>
+        <v>64.48221663531135</v>
       </c>
       <c r="L655" t="n">
         <v>11.34163208852006</v>
@@ -51383,16 +51383,16 @@
         <v>664.9514306640625</v>
       </c>
       <c r="E662" t="n">
-        <v>665.348671875</v>
+        <v>665.3486730957031</v>
       </c>
       <c r="F662" t="n">
-        <v>710.4667471313477</v>
+        <v>710.4667495727539</v>
       </c>
       <c r="G662" t="n">
-        <v>-4.507774049968017</v>
+        <v>-4.507774113513996</v>
       </c>
       <c r="H662" t="n">
-        <v>1181.515387363553</v>
+        <v>1181.515511428121</v>
       </c>
       <c r="I662" t="n">
         <v>577.3964738257137</v>
@@ -51401,7 +51401,7 @@
         <v>6.209515956467149</v>
       </c>
       <c r="K662" t="n">
-        <v>92.6645556238977</v>
+        <v>92.66457585456511</v>
       </c>
       <c r="L662" t="n">
         <v>10.09681881051176</v>
@@ -51463,10 +51463,10 @@
         <v>91.51076380411784</v>
       </c>
       <c r="F663" t="n">
-        <v>94.68913734436035</v>
+        <v>94.68913722991944</v>
       </c>
       <c r="G663" t="n">
-        <v>-3.570854520649036</v>
+        <v>-3.570854562271397</v>
       </c>
       <c r="H663" t="n">
         <v>124.8273096544699</v>
@@ -51540,10 +51540,10 @@
         <v>489.8323311360677</v>
       </c>
       <c r="F664" t="n">
-        <v>529.1072601318359</v>
+        <v>529.1072598266602</v>
       </c>
       <c r="G664" t="n">
-        <v>-5.371774929183792</v>
+        <v>-5.371774932115658</v>
       </c>
       <c r="H664" t="n">
         <v>799.7128098861871</v>
@@ -52772,10 +52772,10 @@
         <v>129.6957116190592</v>
       </c>
       <c r="F680" t="n">
-        <v>136.8005149459839</v>
+        <v>136.8005151748657</v>
       </c>
       <c r="G680" t="n">
-        <v>-3.617517741524801</v>
+        <v>-3.617517787499458</v>
       </c>
       <c r="H680" t="n">
         <v>183.7853835258596</v>
@@ -53619,10 +53619,10 @@
         <v>272.6526349894206</v>
       </c>
       <c r="F691" t="n">
-        <v>285.2244116973877</v>
+        <v>285.2244124603271</v>
       </c>
       <c r="G691" t="n">
-        <v>-4.379796592717843</v>
+        <v>-4.379796581515571</v>
       </c>
       <c r="H691" t="n">
         <v>385.6351549871131</v>
@@ -54078,25 +54078,25 @@
         <v>491.2330346679688</v>
       </c>
       <c r="E697" t="n">
-        <v>503.8039514160157</v>
+        <v>503.8039506022135</v>
       </c>
       <c r="F697" t="n">
-        <v>529.6811337280274</v>
+        <v>529.681131439209</v>
       </c>
       <c r="G697" t="n">
-        <v>-4.075126351658131</v>
+        <v>-4.075126474579493</v>
       </c>
       <c r="H697" t="n">
-        <v>792.3207894535917</v>
+        <v>792.3208515948488</v>
       </c>
       <c r="I697" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J697" t="n">
-        <v>2.605872798382536</v>
+        <v>2.60586517899386</v>
       </c>
       <c r="K697" t="n">
-        <v>90.14177255649776</v>
+        <v>90.14178746920601</v>
       </c>
       <c r="L697" t="n">
         <v>4.426002766251729</v>
@@ -54466,10 +54466,10 @@
         <v>244.2642803955078</v>
       </c>
       <c r="F702" t="n">
-        <v>265.5459422302246</v>
+        <v>265.5459420776367</v>
       </c>
       <c r="G702" t="n">
-        <v>-4.423414943919157</v>
+        <v>-4.423414841366857</v>
       </c>
       <c r="H702" t="n">
         <v>398.2045017598045</v>
@@ -54774,10 +54774,10 @@
         <v>344.0852469889323</v>
       </c>
       <c r="F706" t="n">
-        <v>350.3366284179688</v>
+        <v>350.3366282653809</v>
       </c>
       <c r="G706" t="n">
-        <v>-3.344639879458544</v>
+        <v>-3.344639962246343</v>
       </c>
       <c r="H706" t="n">
         <v>487.9415273208757</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1499,10 +1499,10 @@
         <v>2065.199951171875</v>
       </c>
       <c r="I14" t="n">
-        <v>841.4671897137645</v>
+        <v>841.4672483994065</v>
       </c>
       <c r="J14" t="n">
-        <v>142.0296359123298</v>
+        <v>142.0296190326894</v>
       </c>
       <c r="K14" t="n">
         <v>1.404300104526368</v>
@@ -1952,10 +1952,10 @@
         <v>1931.128490397135</v>
       </c>
       <c r="F20" t="n">
-        <v>1759.078101806641</v>
+        <v>1759.078099365234</v>
       </c>
       <c r="G20" t="n">
-        <v>7.095025504510555</v>
+        <v>7.095025634442687</v>
       </c>
       <c r="H20" t="n">
         <v>2714.261178227147</v>
@@ -2029,10 +2029,10 @@
         <v>1152.465091959635</v>
       </c>
       <c r="F21" t="n">
-        <v>1069.466467895508</v>
+        <v>1069.466468505859</v>
       </c>
       <c r="G21" t="n">
-        <v>5.93830852385735</v>
+        <v>5.938308520267088</v>
       </c>
       <c r="H21" t="n">
         <v>1677.5</v>
@@ -3794,16 +3794,16 @@
         <v>239.75</v>
       </c>
       <c r="D44" t="n">
-        <v>197.9789566040039</v>
+        <v>197.9789556884766</v>
       </c>
       <c r="E44" t="n">
-        <v>158.3966682434082</v>
+        <v>158.3966691080729</v>
       </c>
       <c r="F44" t="n">
-        <v>156.4289477157593</v>
+        <v>156.4289489746094</v>
       </c>
       <c r="G44" t="n">
-        <v>4.191364638619266</v>
+        <v>4.191364603475844</v>
       </c>
       <c r="H44" t="n">
         <v>248.1000061035156</v>
@@ -4573,7 +4573,7 @@
         <v>227.5020845794678</v>
       </c>
       <c r="G54" t="n">
-        <v>4.916182307198835</v>
+        <v>4.916182270284963</v>
       </c>
       <c r="H54" t="n">
         <v>321.3999938964844</v>
@@ -5417,10 +5417,10 @@
         <v>78.58881174723307</v>
       </c>
       <c r="F65" t="n">
-        <v>74.78907178878784</v>
+        <v>74.7890718460083</v>
       </c>
       <c r="G65" t="n">
-        <v>3.963264302157699</v>
+        <v>3.96326432656986</v>
       </c>
       <c r="H65" t="n">
         <v>94.5</v>
@@ -5494,10 +5494,10 @@
         <v>1036.274944661458</v>
       </c>
       <c r="F66" t="n">
-        <v>982.9050405883789</v>
+        <v>982.9050402832031</v>
       </c>
       <c r="G66" t="n">
-        <v>3.774019826203778</v>
+        <v>3.774019961164221</v>
       </c>
       <c r="H66" t="n">
         <v>1368.900024414062</v>
@@ -6261,13 +6261,13 @@
         <v>423.9595428466797</v>
       </c>
       <c r="E76" t="n">
-        <v>397.2492622884114</v>
+        <v>397.2492618815104</v>
       </c>
       <c r="F76" t="n">
-        <v>384.6608699035644</v>
+        <v>384.6608697509766</v>
       </c>
       <c r="G76" t="n">
-        <v>3.36035078123591</v>
+        <v>3.360350909750487</v>
       </c>
       <c r="H76" t="n">
         <v>480.9477017568404</v>
@@ -8038,7 +8038,7 @@
         <v>246.5629221343994</v>
       </c>
       <c r="G99" t="n">
-        <v>6.79622977513783</v>
+        <v>6.796229810429666</v>
       </c>
       <c r="H99" t="n">
         <v>388.75</v>
@@ -9113,19 +9113,19 @@
         <v>1420.626495768229</v>
       </c>
       <c r="F113" t="n">
-        <v>1356.434478759766</v>
+        <v>1356.434479980469</v>
       </c>
       <c r="G113" t="n">
-        <v>3.399319175274984</v>
+        <v>3.399319124003908</v>
       </c>
       <c r="H113" t="n">
         <v>1766.733060850261</v>
       </c>
       <c r="I113" t="n">
-        <v>969.6359336843161</v>
+        <v>969.6358757670704</v>
       </c>
       <c r="J113" t="n">
-        <v>58.17276339422472</v>
+        <v>58.17277284202984</v>
       </c>
       <c r="K113" t="n">
         <v>15.19417859408085</v>
@@ -9495,13 +9495,13 @@
         <v>162.4833996582031</v>
       </c>
       <c r="E118" t="n">
-        <v>141.977395324707</v>
+        <v>141.9773951721191</v>
       </c>
       <c r="F118" t="n">
-        <v>136.6111602401733</v>
+        <v>136.6111603546143</v>
       </c>
       <c r="G118" t="n">
-        <v>3.823344415029983</v>
+        <v>3.823344532103956</v>
       </c>
       <c r="H118" t="n">
         <v>173.2700042724609</v>
@@ -11654,10 +11654,10 @@
         <v>4602.525237630209</v>
       </c>
       <c r="F146" t="n">
-        <v>4449.304226074219</v>
+        <v>4449.304222412109</v>
       </c>
       <c r="G146" t="n">
-        <v>2.886412693684814</v>
+        <v>2.886412725171605</v>
       </c>
       <c r="H146" t="n">
         <v>5250</v>
@@ -14349,10 +14349,10 @@
         <v>1500.507991536458</v>
       </c>
       <c r="F181" t="n">
-        <v>1521.335908813477</v>
+        <v>1521.33590637207</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.3660709042061061</v>
+        <v>-0.3660709844439336</v>
       </c>
       <c r="H181" t="n">
         <v>2021.199951171875</v>
@@ -15963,13 +15963,13 @@
         <v>337.5905517578125</v>
       </c>
       <c r="E202" t="n">
-        <v>312.6794974772135</v>
+        <v>312.6794970703125</v>
       </c>
       <c r="F202" t="n">
-        <v>309.5751567077637</v>
+        <v>309.5751560974121</v>
       </c>
       <c r="G202" t="n">
-        <v>1.407415890252617</v>
+        <v>1.407416247872928</v>
       </c>
       <c r="H202" t="n">
         <v>380.4567148307952</v>
@@ -16197,10 +16197,10 @@
         <v>622.5934993489583</v>
       </c>
       <c r="F205" t="n">
-        <v>610.824058227539</v>
+        <v>610.8240585327148</v>
       </c>
       <c r="G205" t="n">
-        <v>1.593188130636625</v>
+        <v>1.593188181393934</v>
       </c>
       <c r="H205" t="n">
         <v>769</v>
@@ -16348,13 +16348,13 @@
         <v>189.8907135009766</v>
       </c>
       <c r="E207" t="n">
-        <v>181.1049206542969</v>
+        <v>181.1049203491211</v>
       </c>
       <c r="F207" t="n">
-        <v>179.8175574493408</v>
+        <v>179.8175576782227</v>
       </c>
       <c r="G207" t="n">
-        <v>1.047633663278269</v>
+        <v>1.047633531964287</v>
       </c>
       <c r="H207" t="n">
         <v>203.3999938964844</v>
@@ -17349,16 +17349,16 @@
         <v>1944.388962402344</v>
       </c>
       <c r="E220" t="n">
-        <v>1793.613319498698</v>
+        <v>1793.613325195312</v>
       </c>
       <c r="F220" t="n">
-        <v>1782.974748535156</v>
+        <v>1782.974753417969</v>
       </c>
       <c r="G220" t="n">
-        <v>1.513915745403516</v>
+        <v>1.513915776471308</v>
       </c>
       <c r="H220" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I220" t="n">
         <v>1345.285007075603</v>
@@ -17367,7 +17367,7 @@
         <v>40.84004067588598</v>
       </c>
       <c r="K220" t="n">
-        <v>19.07890244621819</v>
+        <v>19.0788892315257</v>
       </c>
       <c r="L220" t="n">
         <v>57.95297372060858</v>
@@ -18048,7 +18048,7 @@
         <v>286.3550663757324</v>
       </c>
       <c r="G229" t="n">
-        <v>1.195623007735991</v>
+        <v>1.195623089588116</v>
       </c>
       <c r="H229" t="n">
         <v>359.3387168134344</v>
@@ -18199,10 +18199,10 @@
         <v>528.4815938313802</v>
       </c>
       <c r="F231" t="n">
-        <v>536.4562445068359</v>
+        <v>536.4562435913086</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.377392651995323</v>
+        <v>-0.377392652636932</v>
       </c>
       <c r="H231" t="n">
         <v>663.9000244140625</v>
@@ -18664,10 +18664,10 @@
         <v>5342.792736816406</v>
       </c>
       <c r="G237" t="n">
-        <v>-1.722786238636353</v>
+        <v>-1.722786326905201</v>
       </c>
       <c r="H237" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I237" t="n">
         <v>4229.809203861739</v>
@@ -18676,7 +18676,7 @@
         <v>36.41277234755873</v>
       </c>
       <c r="K237" t="n">
-        <v>13.56420636916456</v>
+        <v>13.56419776329836</v>
       </c>
       <c r="L237" t="n">
         <v>69.29460580912863</v>
@@ -19200,19 +19200,19 @@
         <v>403.2619087727865</v>
       </c>
       <c r="F244" t="n">
-        <v>399.5287298583984</v>
+        <v>399.5287295532227</v>
       </c>
       <c r="G244" t="n">
-        <v>0.5972257987564511</v>
+        <v>0.5972258765143845</v>
       </c>
       <c r="H244" t="n">
         <v>489.5369231157038</v>
       </c>
       <c r="I244" t="n">
-        <v>331.4688402352409</v>
+        <v>331.4688100886702</v>
       </c>
       <c r="J244" t="n">
-        <v>23.10357362803057</v>
+        <v>23.10358482410837</v>
       </c>
       <c r="K244" t="n">
         <v>19.96984138229623</v>
@@ -19511,7 +19511,7 @@
         <v>164.9752424621582</v>
       </c>
       <c r="G248" t="n">
-        <v>0.1600209797839591</v>
+        <v>0.1600210261777812</v>
       </c>
       <c r="H248" t="n">
         <v>181.8519567776652</v>
@@ -20047,19 +20047,19 @@
         <v>1961.036067708333</v>
       </c>
       <c r="F255" t="n">
-        <v>1857.170776977539</v>
+        <v>1857.170778198242</v>
       </c>
       <c r="G255" t="n">
-        <v>3.179668680053349</v>
+        <v>3.179668572933547</v>
       </c>
       <c r="H255" t="n">
         <v>2295</v>
       </c>
       <c r="I255" t="n">
-        <v>1174.489600842614</v>
+        <v>1174.48971989473</v>
       </c>
       <c r="J255" t="n">
-        <v>54.69698693888512</v>
+        <v>54.69697125802961</v>
       </c>
       <c r="K255" t="n">
         <v>26.3140497089333</v>
@@ -20364,10 +20364,10 @@
         <v>1153.699951171875</v>
       </c>
       <c r="I259" t="n">
-        <v>628.5921729640716</v>
+        <v>628.5921128551213</v>
       </c>
       <c r="J259" t="n">
-        <v>49.61210983147011</v>
+        <v>49.61212413808751</v>
       </c>
       <c r="K259" t="n">
         <v>22.67530822445232</v>
@@ -20891,16 +20891,16 @@
         <v>4562.245986328125</v>
       </c>
       <c r="E266" t="n">
-        <v>4245.175908203125</v>
+        <v>4245.175913085937</v>
       </c>
       <c r="F266" t="n">
-        <v>4311.861721191406</v>
+        <v>4311.861705322266</v>
       </c>
       <c r="G266" t="n">
-        <v>0.3716468212926038</v>
+        <v>0.3716469367501807</v>
       </c>
       <c r="H266" t="n">
-        <v>5005.772176274182</v>
+        <v>5005.771184298104</v>
       </c>
       <c r="I266" t="n">
         <v>3669.905008549105</v>
@@ -20909,7 +20909,7 @@
         <v>20.54262424728117</v>
       </c>
       <c r="K266" t="n">
-        <v>13.15548617209166</v>
+        <v>13.15546374847121</v>
       </c>
       <c r="L266" t="n">
         <v>63.07053941908713</v>
@@ -21199,13 +21199,13 @@
         <v>1815.319997558594</v>
       </c>
       <c r="E270" t="n">
-        <v>1716.342147623698</v>
+        <v>1716.342149251302</v>
       </c>
       <c r="F270" t="n">
-        <v>1684.047631835937</v>
+        <v>1684.047630615234</v>
       </c>
       <c r="G270" t="n">
-        <v>0.8604279408211957</v>
+        <v>0.8604279045807406</v>
       </c>
       <c r="H270" t="n">
         <v>1983.954544928268</v>
@@ -21282,7 +21282,7 @@
         <v>1141.952951049805</v>
       </c>
       <c r="G271" t="n">
-        <v>-0.9618364049430395</v>
+        <v>-0.9618365097926906</v>
       </c>
       <c r="H271" t="n">
         <v>1409.944064008135</v>
@@ -21353,13 +21353,13 @@
         <v>11124.67068359375</v>
       </c>
       <c r="E272" t="n">
-        <v>10442.61658854167</v>
+        <v>10442.61659505208</v>
       </c>
       <c r="F272" t="n">
-        <v>10533.4008203125</v>
+        <v>10533.40080078125</v>
       </c>
       <c r="G272" t="n">
-        <v>-0.1899150577523101</v>
+        <v>-0.1899151504630048</v>
       </c>
       <c r="H272" t="n">
         <v>13011.97571177054</v>
@@ -22354,22 +22354,22 @@
         <v>367.6356274414063</v>
       </c>
       <c r="E285" t="n">
-        <v>379.0023655192057</v>
+        <v>379.0023659261068</v>
       </c>
       <c r="F285" t="n">
-        <v>369.8846586608886</v>
+        <v>369.8846585083008</v>
       </c>
       <c r="G285" t="n">
-        <v>2.744382474283125</v>
+        <v>2.744382497220443</v>
       </c>
       <c r="H285" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I285" t="n">
-        <v>207.1322344190421</v>
+        <v>207.1322492183286</v>
       </c>
       <c r="J285" t="n">
-        <v>52.51126642963641</v>
+        <v>52.51125553293669</v>
       </c>
       <c r="K285" t="n">
         <v>40.35236317171187</v>
@@ -22511,10 +22511,10 @@
         <v>1107.627470703125</v>
       </c>
       <c r="F287" t="n">
-        <v>1072.847935791016</v>
+        <v>1072.847936706543</v>
       </c>
       <c r="G287" t="n">
-        <v>0.7511540475679368</v>
+        <v>0.7511539314247972</v>
       </c>
       <c r="H287" t="n">
         <v>1238.748718225596</v>
@@ -22588,10 +22588,10 @@
         <v>1382.492112630208</v>
       </c>
       <c r="F288" t="n">
-        <v>1358.182841186524</v>
+        <v>1358.18283996582</v>
       </c>
       <c r="G288" t="n">
-        <v>0.9669243309415654</v>
+        <v>0.9669244234431718</v>
       </c>
       <c r="H288" t="n">
         <v>1553</v>
@@ -23207,16 +23207,16 @@
         <v>1802.848343505859</v>
       </c>
       <c r="G296" t="n">
-        <v>0.3390703348574498</v>
+        <v>0.3390703007726259</v>
       </c>
       <c r="H296" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I296" t="n">
-        <v>1569.36587206911</v>
+        <v>1569.365993709292</v>
       </c>
       <c r="J296" t="n">
-        <v>12.14720743732953</v>
+        <v>12.1471987448978</v>
       </c>
       <c r="K296" t="n">
         <v>16.301137750799</v>
@@ -23281,10 +23281,10 @@
         <v>1364.278681640625</v>
       </c>
       <c r="F297" t="n">
-        <v>1364.530263671875</v>
+        <v>1364.530266723633</v>
       </c>
       <c r="G297" t="n">
-        <v>-0.2775101642423117</v>
+        <v>-0.277510074659626</v>
       </c>
       <c r="H297" t="n">
         <v>1563.400024414062</v>
@@ -24439,7 +24439,7 @@
         <v>36135.84953125</v>
       </c>
       <c r="G312" t="n">
-        <v>-0.2925467753036037</v>
+        <v>-0.2925469365048117</v>
       </c>
       <c r="H312" t="n">
         <v>43614.20556091995</v>
@@ -25979,16 +25979,16 @@
         <v>687.0817398071289</v>
       </c>
       <c r="G332" t="n">
-        <v>2.79464686559443</v>
+        <v>2.794647076795043</v>
       </c>
       <c r="H332" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I332" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J332" t="n">
-        <v>35.81728891578191</v>
+        <v>35.81727297160234</v>
       </c>
       <c r="K332" t="n">
         <v>63.88747701936459</v>
@@ -26207,10 +26207,10 @@
         <v>429.0226479085287</v>
       </c>
       <c r="F335" t="n">
-        <v>423.2914460754395</v>
+        <v>423.2914463806152</v>
       </c>
       <c r="G335" t="n">
-        <v>1.47873807978407</v>
+        <v>1.478738078702202</v>
       </c>
       <c r="H335" t="n">
         <v>478.7148709533388</v>
@@ -27054,10 +27054,10 @@
         <v>1671.659571126302</v>
       </c>
       <c r="F346" t="n">
-        <v>1678.786268920898</v>
+        <v>1678.786267700195</v>
       </c>
       <c r="G346" t="n">
-        <v>0.0005591330675569495</v>
+        <v>0.0005590967108615175</v>
       </c>
       <c r="H346" t="n">
         <v>1952.5</v>
@@ -27901,10 +27901,10 @@
         <v>775.9822493489584</v>
       </c>
       <c r="F357" t="n">
-        <v>787.4050082397461</v>
+        <v>787.4050061035156</v>
       </c>
       <c r="G357" t="n">
-        <v>-1.17046695334303</v>
+        <v>-1.170466994336516</v>
       </c>
       <c r="H357" t="n">
         <v>1100.079694414754</v>
@@ -28973,19 +28973,19 @@
         <v>148</v>
       </c>
       <c r="D371" t="n">
-        <v>152.8213845825195</v>
+        <v>152.8213842773438</v>
       </c>
       <c r="E371" t="n">
-        <v>154.0327819824219</v>
+        <v>154.032780863444</v>
       </c>
       <c r="F371" t="n">
-        <v>150.7346166992187</v>
+        <v>150.7346156311035</v>
       </c>
       <c r="G371" t="n">
-        <v>1.20205450497286</v>
+        <v>1.202054409915276</v>
       </c>
       <c r="H371" t="n">
-        <v>196.4205715539644</v>
+        <v>196.4205869556906</v>
       </c>
       <c r="I371" t="n">
         <v>125.7825892411346</v>
@@ -28994,7 +28994,7 @@
         <v>17.66334346661678</v>
       </c>
       <c r="K371" t="n">
-        <v>32.71660240132728</v>
+        <v>32.71661280789906</v>
       </c>
       <c r="L371" t="n">
         <v>63.6237897648686</v>
@@ -31212,10 +31212,10 @@
         <v>2150.704470214844</v>
       </c>
       <c r="F400" t="n">
-        <v>2090.827900390625</v>
+        <v>2090.827896728515</v>
       </c>
       <c r="G400" t="n">
-        <v>0.2527633816980401</v>
+        <v>0.2527634114814825</v>
       </c>
       <c r="H400" t="n">
         <v>2625.96691593483</v>
@@ -31597,10 +31597,10 @@
         <v>667.2407759602864</v>
       </c>
       <c r="F405" t="n">
-        <v>665.4453076171875</v>
+        <v>665.4453070068359</v>
       </c>
       <c r="G405" t="n">
-        <v>-0.8775536297678799</v>
+        <v>-0.8775536305657194</v>
       </c>
       <c r="H405" t="n">
         <v>792.3323631991859</v>
@@ -32059,10 +32059,10 @@
         <v>1142.408075764974</v>
       </c>
       <c r="F411" t="n">
-        <v>1161.615498352051</v>
+        <v>1161.615496520996</v>
       </c>
       <c r="G411" t="n">
-        <v>-0.8502423372384493</v>
+        <v>-0.8502421319526943</v>
       </c>
       <c r="H411" t="n">
         <v>1378.852549646065</v>
@@ -32213,10 +32213,10 @@
         <v>738.0826025390625</v>
       </c>
       <c r="F413" t="n">
-        <v>733.3614093017578</v>
+        <v>733.3614096069336</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.9137135965328946</v>
+        <v>-0.9137135961561516</v>
       </c>
       <c r="H413" t="n">
         <v>837.8765073351432</v>
@@ -32444,10 +32444,10 @@
         <v>356.3050866699219</v>
       </c>
       <c r="F416" t="n">
-        <v>353.5636613464355</v>
+        <v>353.5636616516113</v>
       </c>
       <c r="G416" t="n">
-        <v>0.1914134969006609</v>
+        <v>0.1914135833801067</v>
       </c>
       <c r="H416" t="n">
         <v>409.9712889887167</v>
@@ -32521,10 +32521,10 @@
         <v>77.20693344116211</v>
       </c>
       <c r="F417" t="n">
-        <v>77.18057174682617</v>
+        <v>77.18057178497314</v>
       </c>
       <c r="G417" t="n">
-        <v>-0.1505822735357487</v>
+        <v>-0.150582421292067</v>
       </c>
       <c r="H417" t="n">
         <v>86.59303970157107</v>
@@ -32903,16 +32903,16 @@
         <v>493.7788781738281</v>
       </c>
       <c r="E422" t="n">
-        <v>482.9044889322917</v>
+        <v>482.9044903564453</v>
       </c>
       <c r="F422" t="n">
-        <v>488.5623118591309</v>
+        <v>488.5623132324219</v>
       </c>
       <c r="G422" t="n">
-        <v>-0.7674909166795807</v>
+        <v>-0.767490730012077</v>
       </c>
       <c r="H422" t="n">
-        <v>547.7380341214969</v>
+        <v>547.7379722645398</v>
       </c>
       <c r="I422" t="n">
         <v>419.3328127807616</v>
@@ -32921,7 +32921,7 @@
         <v>5.405536253870347</v>
       </c>
       <c r="K422" t="n">
-        <v>23.92263215418482</v>
+        <v>23.92261815939816</v>
       </c>
       <c r="L422" t="n">
         <v>38.0359612724758</v>
@@ -34058,22 +34058,22 @@
         <v>427.9660003662109</v>
       </c>
       <c r="E437" t="n">
-        <v>460.4484403483073</v>
+        <v>460.4484407552083</v>
       </c>
       <c r="F437" t="n">
-        <v>463.3778805541992</v>
+        <v>463.3778802490235</v>
       </c>
       <c r="G437" t="n">
-        <v>-0.9871417968641549</v>
+        <v>-0.9871420234857764</v>
       </c>
       <c r="H437" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I437" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J437" t="n">
-        <v>16.1321115780791</v>
+        <v>16.1321301852551</v>
       </c>
       <c r="K437" t="n">
         <v>25.89211983344397</v>
@@ -34138,13 +34138,13 @@
         <v>5415.404371744792</v>
       </c>
       <c r="F438" t="n">
-        <v>5460.052202148438</v>
+        <v>5460.052211914062</v>
       </c>
       <c r="G438" t="n">
-        <v>-0.7156279626771234</v>
+        <v>-0.7156280054826381</v>
       </c>
       <c r="H438" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I438" t="n">
         <v>5051</v>
@@ -34153,7 +34153,7 @@
         <v>4.513957632152055</v>
       </c>
       <c r="K438" t="n">
-        <v>11.30013114607689</v>
+        <v>11.30014050600263</v>
       </c>
       <c r="L438" t="n">
         <v>54.77178423236515</v>
@@ -36063,10 +36063,10 @@
         <v>285.5558247884115</v>
       </c>
       <c r="F463" t="n">
-        <v>281.9999481964111</v>
+        <v>281.9999468994141</v>
       </c>
       <c r="G463" t="n">
-        <v>-0.1084101232810553</v>
+        <v>-0.1084101777710678</v>
       </c>
       <c r="H463" t="n">
         <v>323.4425459044702</v>
@@ -36137,22 +36137,22 @@
         <v>2281.764560546875</v>
       </c>
       <c r="E464" t="n">
-        <v>2208.13845296224</v>
+        <v>2208.138475748698</v>
       </c>
       <c r="F464" t="n">
-        <v>2266.120425415039</v>
+        <v>2266.12044128418</v>
       </c>
       <c r="G464" t="n">
-        <v>-0.8929556583810228</v>
+        <v>-0.8929557050934789</v>
       </c>
       <c r="H464" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I464" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J464" t="n">
-        <v>2.400699046533927</v>
+        <v>2.400692692140982</v>
       </c>
       <c r="K464" t="n">
         <v>37.56053509384836</v>
@@ -36522,25 +36522,25 @@
         <v>210.9872253417969</v>
       </c>
       <c r="E469" t="n">
-        <v>207.2537642415365</v>
+        <v>207.2537646484375</v>
       </c>
       <c r="F469" t="n">
-        <v>211.079831237793</v>
+        <v>211.0798315429687</v>
       </c>
       <c r="G469" t="n">
-        <v>-1.246292511878211</v>
+        <v>-1.246292615846623</v>
       </c>
       <c r="H469" t="n">
-        <v>252.6160882566492</v>
+        <v>252.6161043110497</v>
       </c>
       <c r="I469" t="n">
-        <v>171.6534052563282</v>
+        <v>171.6534204603822</v>
       </c>
       <c r="J469" t="n">
-        <v>15.73321447684217</v>
+        <v>15.73320422587228</v>
       </c>
       <c r="K469" t="n">
-        <v>27.16001389303857</v>
+        <v>27.1600219743837</v>
       </c>
       <c r="L469" t="n">
         <v>35.40802213001383</v>
@@ -36602,13 +36602,13 @@
         <v>418.5872133382161</v>
       </c>
       <c r="F470" t="n">
-        <v>436.8794007873535</v>
+        <v>436.8794020080566</v>
       </c>
       <c r="G470" t="n">
-        <v>-2.590126222012135</v>
+        <v>-2.590126214962407</v>
       </c>
       <c r="H470" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I470" t="n">
         <v>363.2227809620478</v>
@@ -36617,7 +36617,7 @@
         <v>10.13901350938913</v>
       </c>
       <c r="K470" t="n">
-        <v>33.41053233061422</v>
+        <v>33.41051643251367</v>
       </c>
       <c r="L470" t="n">
         <v>35.26970954356847</v>
@@ -37603,13 +37603,13 @@
         <v>611.9190600585938</v>
       </c>
       <c r="F483" t="n">
-        <v>616.6395156860351</v>
+        <v>616.6395175170899</v>
       </c>
       <c r="G483" t="n">
-        <v>-1.5751968211969</v>
+        <v>-1.575196960423031</v>
       </c>
       <c r="H483" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I483" t="n">
         <v>495.5999980879241</v>
@@ -37618,7 +37618,7 @@
         <v>19.20903754486199</v>
       </c>
       <c r="K483" t="n">
-        <v>43.67404552193739</v>
+        <v>43.67405590895031</v>
       </c>
       <c r="L483" t="n">
         <v>31.3969571230982</v>
@@ -38068,7 +38068,7 @@
         <v>390.9700425720215</v>
       </c>
       <c r="G489" t="n">
-        <v>-0.09706191061885638</v>
+        <v>-0.09706171585734946</v>
       </c>
       <c r="H489" t="n">
         <v>476.8288845013619</v>
@@ -39149,7 +39149,7 @@
         <v>-1.352064802675967</v>
       </c>
       <c r="H503" t="n">
-        <v>623.6462906209067</v>
+        <v>623.6463522815318</v>
       </c>
       <c r="I503" t="n">
         <v>351.0001816860465</v>
@@ -39158,7 +39158,7 @@
         <v>18.63241548659225</v>
       </c>
       <c r="K503" t="n">
-        <v>49.77096536075911</v>
+        <v>49.77098016878649</v>
       </c>
       <c r="L503" t="n">
         <v>24.75795297372061</v>
@@ -39679,16 +39679,16 @@
         <v>455.1960125732422</v>
       </c>
       <c r="E510" t="n">
-        <v>492.5644270833333</v>
+        <v>492.5644246419271</v>
       </c>
       <c r="F510" t="n">
-        <v>502.339488067627</v>
+        <v>502.3394856262207</v>
       </c>
       <c r="G510" t="n">
-        <v>-3.371946477588283</v>
+        <v>-3.371946493423594</v>
       </c>
       <c r="H510" t="n">
-        <v>758.589574672296</v>
+        <v>758.5896367271307</v>
       </c>
       <c r="I510" t="n">
         <v>400.6499938964844</v>
@@ -39697,7 +39697,7 @@
         <v>15.97404242480425</v>
       </c>
       <c r="K510" t="n">
-        <v>63.26042927728865</v>
+        <v>63.26044263246688</v>
       </c>
       <c r="L510" t="n">
         <v>21.16182572614108</v>
@@ -40298,10 +40298,10 @@
         <v>2815.910304361979</v>
       </c>
       <c r="F518" t="n">
-        <v>2730.126700439453</v>
+        <v>2730.126696777344</v>
       </c>
       <c r="G518" t="n">
-        <v>-1.09127723547372</v>
+        <v>-1.091277236921551</v>
       </c>
       <c r="H518" t="n">
         <v>3333.383184200957</v>
@@ -40997,7 +40997,7 @@
         <v>-4.390985090908728</v>
       </c>
       <c r="H527" t="n">
-        <v>605.9581114957105</v>
+        <v>605.9581737112406</v>
       </c>
       <c r="I527" t="n">
         <v>326.057353105007</v>
@@ -41006,7 +41006,7 @@
         <v>10.54803971586804</v>
       </c>
       <c r="K527" t="n">
-        <v>68.11155249667935</v>
+        <v>68.11156975719483</v>
       </c>
       <c r="L527" t="n">
         <v>9.95850622406639</v>
@@ -42066,25 +42066,25 @@
         <v>220.8836917114258</v>
       </c>
       <c r="E541" t="n">
-        <v>222.8661004638672</v>
+        <v>222.8660999552409</v>
       </c>
       <c r="F541" t="n">
-        <v>224.2614192962646</v>
+        <v>224.2614192199707</v>
       </c>
       <c r="G541" t="n">
-        <v>-1.314518308960844</v>
+        <v>-1.31451830940218</v>
       </c>
       <c r="H541" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I541" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J541" t="n">
-        <v>17.28217115275532</v>
+        <v>17.28216081834251</v>
       </c>
       <c r="K541" t="n">
-        <v>41.85571559299233</v>
+        <v>41.85573178797035</v>
       </c>
       <c r="L541" t="n">
         <v>40.66390041493776</v>
@@ -42223,10 +42223,10 @@
         <v>415.5020284016927</v>
       </c>
       <c r="F543" t="n">
-        <v>416.6231356811523</v>
+        <v>416.6231359863281</v>
       </c>
       <c r="G543" t="n">
-        <v>-0.2976555209211806</v>
+        <v>-0.2976555571110095</v>
       </c>
       <c r="H543" t="n">
         <v>472.8081629796919</v>
@@ -42377,10 +42377,10 @@
         <v>4598.175008138021</v>
       </c>
       <c r="F545" t="n">
-        <v>4748.620792236328</v>
+        <v>4748.620787353516</v>
       </c>
       <c r="G545" t="n">
-        <v>-0.3876886310782535</v>
+        <v>-0.3876886314753358</v>
       </c>
       <c r="H545" t="n">
         <v>5612.405266256894</v>
@@ -42454,13 +42454,13 @@
         <v>741.3644563802084</v>
       </c>
       <c r="F546" t="n">
-        <v>756.7293496704101</v>
+        <v>756.7293508911133</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.375245146120985</v>
+        <v>-1.375245143933024</v>
       </c>
       <c r="H546" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I546" t="n">
         <v>612.1496526863262</v>
@@ -42469,7 +42469,7 @@
         <v>17.46310475510793</v>
       </c>
       <c r="K546" t="n">
-        <v>55.42165981870799</v>
+        <v>55.42164248365553</v>
       </c>
       <c r="L546" t="n">
         <v>36.7911479944675</v>
@@ -42528,13 +42528,13 @@
         <v>136.4532609558105</v>
       </c>
       <c r="E547" t="n">
-        <v>140.1806430562337</v>
+        <v>140.1806429545085</v>
       </c>
       <c r="F547" t="n">
-        <v>146.1266692733765</v>
+        <v>146.1266688919067</v>
       </c>
       <c r="G547" t="n">
-        <v>-1.718753640448967</v>
+        <v>-1.718753543995732</v>
       </c>
       <c r="H547" t="n">
         <v>184.9587904135824</v>
@@ -42916,10 +42916,10 @@
         <v>130131.19140625</v>
       </c>
       <c r="F552" t="n">
-        <v>133963.907578125</v>
+        <v>133963.907421875</v>
       </c>
       <c r="G552" t="n">
-        <v>-2.273530737864571</v>
+        <v>-2.273530573367033</v>
       </c>
       <c r="H552" t="n">
         <v>163308.4863287346</v>
@@ -43914,13 +43914,13 @@
         <v>323.670146484375</v>
       </c>
       <c r="E565" t="n">
-        <v>336.6633243815104</v>
+        <v>336.6633256022135</v>
       </c>
       <c r="F565" t="n">
-        <v>340.0451425170899</v>
+        <v>340.0451431274414</v>
       </c>
       <c r="G565" t="n">
-        <v>-1.041343745321832</v>
+        <v>-1.041343743472178</v>
       </c>
       <c r="H565" t="n">
         <v>381.3442016302781</v>
@@ -44071,13 +44071,13 @@
         <v>20.22101926167806</v>
       </c>
       <c r="F567" t="n">
-        <v>20.35237323760986</v>
+        <v>20.35237322807312</v>
       </c>
       <c r="G567" t="n">
-        <v>-1.634394213148216</v>
+        <v>-1.634394168562592</v>
       </c>
       <c r="H567" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I567" t="n">
         <v>16.75</v>
@@ -44086,7 +44086,7 @@
         <v>4.358206222306427</v>
       </c>
       <c r="K567" t="n">
-        <v>36.35733909110248</v>
+        <v>36.3573276492039</v>
       </c>
       <c r="L567" t="n">
         <v>29.87551867219917</v>
@@ -45072,10 +45072,10 @@
         <v>895.559550374349</v>
       </c>
       <c r="F580" t="n">
-        <v>914.5640200805664</v>
+        <v>914.5640176391602</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.182653664589717</v>
+        <v>-1.182653700293279</v>
       </c>
       <c r="H580" t="n">
         <v>1282.80960014975</v>
@@ -45303,10 +45303,10 @@
         <v>2282.375971679688</v>
       </c>
       <c r="F583" t="n">
-        <v>2455.973533935547</v>
+        <v>2455.973541259766</v>
       </c>
       <c r="G583" t="n">
-        <v>-3.998597251006941</v>
+        <v>-3.998597239559143</v>
       </c>
       <c r="H583" t="n">
         <v>3287.161645949698</v>
@@ -46227,13 +46227,13 @@
         <v>121.6738223775228</v>
       </c>
       <c r="F595" t="n">
-        <v>123.5300848007202</v>
+        <v>123.5300846099854</v>
       </c>
       <c r="G595" t="n">
-        <v>-2.401067804845847</v>
+        <v>-2.401067573139504</v>
       </c>
       <c r="H595" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I595" t="n">
         <v>103.5</v>
@@ -46242,7 +46242,7 @@
         <v>1.236713796422095</v>
       </c>
       <c r="K595" t="n">
-        <v>48.78791772409923</v>
+        <v>48.78790085533089</v>
       </c>
       <c r="L595" t="n">
         <v>22.82157676348548</v>
@@ -47841,13 +47841,13 @@
         <v>918.1975402832031</v>
       </c>
       <c r="E616" t="n">
-        <v>1001.708787841797</v>
+        <v>1001.708784586589</v>
       </c>
       <c r="F616" t="n">
-        <v>1049.910987243652</v>
+        <v>1049.910986633301</v>
       </c>
       <c r="G616" t="n">
-        <v>-2.643443236511289</v>
+        <v>-2.64344340330982</v>
       </c>
       <c r="H616" t="n">
         <v>1255.178432949836</v>
@@ -47921,10 +47921,10 @@
         <v>1965.82451171875</v>
       </c>
       <c r="F617" t="n">
-        <v>2046.269184570313</v>
+        <v>2046.269187011719</v>
       </c>
       <c r="G617" t="n">
-        <v>-2.202395707882643</v>
+        <v>-2.202395534143875</v>
       </c>
       <c r="H617" t="n">
         <v>2486.766809421043</v>
@@ -48460,13 +48460,13 @@
         <v>1458.223601074219</v>
       </c>
       <c r="F624" t="n">
-        <v>1479.541417236328</v>
+        <v>1479.54141784668</v>
       </c>
       <c r="G624" t="n">
-        <v>-2.054416659235569</v>
+        <v>-2.054416579255169</v>
       </c>
       <c r="H624" t="n">
-        <v>1879.129413417229</v>
+        <v>1879.129289477992</v>
       </c>
       <c r="I624" t="n">
         <v>1185.665549129695</v>
@@ -48475,7 +48475,7 @@
         <v>3.739203766428689</v>
       </c>
       <c r="K624" t="n">
-        <v>52.7747490583113</v>
+        <v>52.77473898195053</v>
       </c>
       <c r="L624" t="n">
         <v>16.18257261410788</v>
@@ -48919,16 +48919,16 @@
         <v>180.3262930297851</v>
       </c>
       <c r="E630" t="n">
-        <v>190.601543375651</v>
+        <v>190.6015436808268</v>
       </c>
       <c r="F630" t="n">
-        <v>193.2109908294678</v>
+        <v>193.2109910583496</v>
       </c>
       <c r="G630" t="n">
-        <v>-2.806849594969341</v>
+        <v>-2.80684966634116</v>
       </c>
       <c r="H630" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I630" t="n">
         <v>155.8000030517578</v>
@@ -48937,7 +48937,7 @@
         <v>2.535299660379331</v>
       </c>
       <c r="K630" t="n">
-        <v>49.74564813639495</v>
+        <v>49.74566746841058</v>
       </c>
       <c r="L630" t="n">
         <v>15.35269709543569</v>
@@ -48999,10 +48999,10 @@
         <v>510.0540405273438</v>
       </c>
       <c r="F631" t="n">
-        <v>541.2885372924804</v>
+        <v>541.2885366821289</v>
       </c>
       <c r="G631" t="n">
-        <v>-4.187475552217368</v>
+        <v>-4.187475453228173</v>
       </c>
       <c r="H631" t="n">
         <v>725.6811213920008</v>
@@ -49076,13 +49076,13 @@
         <v>183.7249064127604</v>
       </c>
       <c r="F632" t="n">
-        <v>196.7943488311768</v>
+        <v>196.7943495178223</v>
       </c>
       <c r="G632" t="n">
-        <v>-4.28709620582759</v>
+        <v>-4.28709604944838</v>
       </c>
       <c r="H632" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I632" t="n">
         <v>156.7899932861328</v>
@@ -49091,7 +49091,7 @@
         <v>3.686468706926815</v>
       </c>
       <c r="K632" t="n">
-        <v>61.91209106339377</v>
+        <v>61.91210986495748</v>
       </c>
       <c r="L632" t="n">
         <v>14.66113416320885</v>
@@ -49846,13 +49846,13 @@
         <v>380.8495965576172</v>
       </c>
       <c r="F642" t="n">
-        <v>391.6834391784668</v>
+        <v>391.6834394836426</v>
       </c>
       <c r="G642" t="n">
-        <v>-3.027442804377789</v>
+        <v>-3.0274428753581</v>
       </c>
       <c r="H642" t="n">
-        <v>541.0235690240457</v>
+        <v>541.0236304500187</v>
       </c>
       <c r="I642" t="n">
         <v>271.5615990811692</v>
@@ -49861,7 +49861,7 @@
         <v>19.78865527881108</v>
       </c>
       <c r="K642" t="n">
-        <v>66.31527492351779</v>
+        <v>66.31529380638752</v>
       </c>
       <c r="L642" t="n">
         <v>13.13969571230982</v>
@@ -50699,7 +50699,7 @@
         <v>-4.316373705022536</v>
       </c>
       <c r="H653" t="n">
-        <v>3416.473037850766</v>
+        <v>3416.47279164786</v>
       </c>
       <c r="I653" t="n">
         <v>1770</v>
@@ -50708,7 +50708,7 @@
         <v>2.440675207450571</v>
       </c>
       <c r="K653" t="n">
-        <v>88.42229924188408</v>
+        <v>88.42228566351913</v>
       </c>
       <c r="L653" t="n">
         <v>11.61825726141079</v>
@@ -51463,13 +51463,13 @@
         <v>91.51076380411784</v>
       </c>
       <c r="F663" t="n">
-        <v>94.68913722991944</v>
+        <v>94.6891372680664</v>
       </c>
       <c r="G663" t="n">
-        <v>-3.570854562271397</v>
+        <v>-3.57085452342345</v>
       </c>
       <c r="H663" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I663" t="n">
         <v>73.90000152587891</v>
@@ -51478,7 +51478,7 @@
         <v>0.7577774655358471</v>
       </c>
       <c r="K663" t="n">
-        <v>67.64344774280357</v>
+        <v>67.64343718094908</v>
       </c>
       <c r="L663" t="n">
         <v>9.820193637621024</v>
@@ -52849,10 +52849,10 @@
         <v>2713.770517578125</v>
       </c>
       <c r="F681" t="n">
-        <v>2827.76771484375</v>
+        <v>2827.767711181641</v>
       </c>
       <c r="G681" t="n">
-        <v>-3.955126158926014</v>
+        <v>-3.955126163845535</v>
       </c>
       <c r="H681" t="n">
         <v>3812.926349899466</v>
@@ -54078,25 +54078,25 @@
         <v>491.2330346679688</v>
       </c>
       <c r="E697" t="n">
-        <v>503.8039506022135</v>
+        <v>503.8039514160157</v>
       </c>
       <c r="F697" t="n">
-        <v>529.681131439209</v>
+        <v>529.6811331176758</v>
       </c>
       <c r="G697" t="n">
-        <v>-4.075126474579493</v>
+        <v>-4.075126409177443</v>
       </c>
       <c r="H697" t="n">
-        <v>792.3208515948488</v>
+        <v>792.3207894535917</v>
       </c>
       <c r="I697" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J697" t="n">
-        <v>2.60586517899386</v>
+        <v>2.605872798382536</v>
       </c>
       <c r="K697" t="n">
-        <v>90.14178746920601</v>
+        <v>90.14177255649776</v>
       </c>
       <c r="L697" t="n">
         <v>4.426002766251729</v>
@@ -56006,10 +56006,10 @@
         <v>645.6343157958985</v>
       </c>
       <c r="F722" t="n">
-        <v>744.4869035339356</v>
+        <v>744.4869013977051</v>
       </c>
       <c r="G722" t="n">
-        <v>-9.122751554268394</v>
+        <v>-9.12275144264324</v>
       </c>
       <c r="H722" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2177,16 +2177,16 @@
         <v>246.25</v>
       </c>
       <c r="D23" t="n">
-        <v>202.3687438964844</v>
+        <v>202.3687442016601</v>
       </c>
       <c r="E23" t="n">
-        <v>162.1920184326172</v>
+        <v>162.192017364502</v>
       </c>
       <c r="F23" t="n">
-        <v>158.5442430114746</v>
+        <v>158.5442418289184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.975186364374129</v>
+        <v>4.975186456358438</v>
       </c>
       <c r="H23" t="n">
         <v>248.3999938964844</v>
@@ -2408,16 +2408,16 @@
         <v>13774</v>
       </c>
       <c r="D26" t="n">
-        <v>12256.936171875</v>
+        <v>12256.93615234375</v>
       </c>
       <c r="E26" t="n">
-        <v>11090.68893880208</v>
+        <v>11090.68897135417</v>
       </c>
       <c r="F26" t="n">
-        <v>10638.51543701172</v>
+        <v>10638.51545654297</v>
       </c>
       <c r="G26" t="n">
-        <v>4.38790339241093</v>
+        <v>4.387903484029199</v>
       </c>
       <c r="H26" t="n">
         <v>14498</v>
@@ -5032,10 +5032,10 @@
         <v>159.833235168457</v>
       </c>
       <c r="F60" t="n">
-        <v>156.3067573165894</v>
+        <v>156.3067572402954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.838844560477627</v>
+        <v>2.838844303797416</v>
       </c>
       <c r="H60" t="n">
         <v>233.3500061035156</v>
@@ -6033,10 +6033,10 @@
         <v>741.2964436848958</v>
       </c>
       <c r="F73" t="n">
-        <v>740.9988119506836</v>
+        <v>740.9988131713867</v>
       </c>
       <c r="G73" t="n">
-        <v>2.677447241484909</v>
+        <v>2.677447193536775</v>
       </c>
       <c r="H73" t="n">
         <v>1002.400024414062</v>
@@ -6954,13 +6954,13 @@
         <v>1418.404001464844</v>
       </c>
       <c r="E85" t="n">
-        <v>1170.398424886068</v>
+        <v>1170.398425292969</v>
       </c>
       <c r="F85" t="n">
         <v>1085.251582641602</v>
       </c>
       <c r="G85" t="n">
-        <v>6.060298225259264</v>
+        <v>6.060298256891161</v>
       </c>
       <c r="H85" t="n">
         <v>1677.5</v>
@@ -7724,13 +7724,13 @@
         <v>343.9190014648437</v>
       </c>
       <c r="E95" t="n">
-        <v>267.061186319987</v>
+        <v>267.0611861165365</v>
       </c>
       <c r="F95" t="n">
-        <v>249.9069130706787</v>
+        <v>249.9069129943848</v>
       </c>
       <c r="G95" t="n">
-        <v>6.591772869164525</v>
+        <v>6.591772767250403</v>
       </c>
       <c r="H95" t="n">
         <v>388.75</v>
@@ -8340,13 +8340,13 @@
         <v>163.2757998657227</v>
       </c>
       <c r="E103" t="n">
-        <v>143.1894893391927</v>
+        <v>143.1894893900553</v>
       </c>
       <c r="F103" t="n">
-        <v>137.6178078842163</v>
+        <v>137.6178078079224</v>
       </c>
       <c r="G103" t="n">
-        <v>3.550083378886937</v>
+        <v>3.550083321479791</v>
       </c>
       <c r="H103" t="n">
         <v>173.2700042724609</v>
@@ -9190,10 +9190,10 @@
         <v>1426.770304361979</v>
       </c>
       <c r="F114" t="n">
-        <v>1367.572243652344</v>
+        <v>1367.57224609375</v>
       </c>
       <c r="G114" t="n">
-        <v>3.623398834960811</v>
+        <v>3.623398684488399</v>
       </c>
       <c r="H114" t="n">
         <v>1766.733060850261</v>
@@ -9264,13 +9264,13 @@
         <v>2161.481472167969</v>
       </c>
       <c r="E115" t="n">
-        <v>1932.446788736979</v>
+        <v>1932.446783040365</v>
       </c>
       <c r="F115" t="n">
-        <v>1828.775318603516</v>
+        <v>1828.775313720703</v>
       </c>
       <c r="G115" t="n">
-        <v>4.249120964385367</v>
+        <v>4.249121085026797</v>
       </c>
       <c r="H115" t="n">
         <v>2264.114307176184</v>
@@ -9883,10 +9883,10 @@
         <v>572.2041699218749</v>
       </c>
       <c r="F123" t="n">
-        <v>545.245952758789</v>
+        <v>545.2459536743164</v>
       </c>
       <c r="G123" t="n">
-        <v>5.033784764277582</v>
+        <v>5.033784693652876</v>
       </c>
       <c r="H123" t="n">
         <v>795.731978165477</v>
@@ -10191,10 +10191,10 @@
         <v>1525.751455891927</v>
       </c>
       <c r="F127" t="n">
-        <v>1524.064555053711</v>
+        <v>1524.064552001953</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.2522259604311516</v>
+        <v>-0.2522260007807753</v>
       </c>
       <c r="H127" t="n">
         <v>2021.199951171875</v>
@@ -10342,22 +10342,22 @@
         <v>1924.474001464844</v>
       </c>
       <c r="E129" t="n">
-        <v>1682.017319335938</v>
+        <v>1682.017312825521</v>
       </c>
       <c r="F129" t="n">
-        <v>1613.566029052734</v>
+        <v>1613.566032714844</v>
       </c>
       <c r="G129" t="n">
-        <v>3.351370826055677</v>
+        <v>3.351370454557379</v>
       </c>
       <c r="H129" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I129" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J129" t="n">
-        <v>46.89278739345986</v>
+        <v>46.89280117629138</v>
       </c>
       <c r="K129" t="n">
         <v>9.608040691766329</v>
@@ -10887,7 +10887,7 @@
         <v>990.532312927246</v>
       </c>
       <c r="G136" t="n">
-        <v>3.930202610762401</v>
+        <v>3.930202477648037</v>
       </c>
       <c r="H136" t="n">
         <v>1368.900024414062</v>
@@ -12421,13 +12421,13 @@
         <v>333.5491583251953</v>
       </c>
       <c r="E156" t="n">
-        <v>314.5854672241211</v>
+        <v>314.5854669189453</v>
       </c>
       <c r="F156" t="n">
-        <v>310.2953793334961</v>
+        <v>310.2953787231446</v>
       </c>
       <c r="G156" t="n">
-        <v>1.24973252652949</v>
+        <v>1.249732680253945</v>
       </c>
       <c r="H156" t="n">
         <v>380.4567148307952</v>
@@ -13117,10 +13117,10 @@
         <v>626.8444034830729</v>
       </c>
       <c r="F165" t="n">
-        <v>612.2530038452148</v>
+        <v>612.2530047607422</v>
       </c>
       <c r="G165" t="n">
-        <v>1.393173946850701</v>
+        <v>1.393174047224877</v>
       </c>
       <c r="H165" t="n">
         <v>769</v>
@@ -13733,10 +13733,10 @@
         <v>1953.621872558594</v>
       </c>
       <c r="F173" t="n">
-        <v>1780.163165893555</v>
+        <v>1780.163162841797</v>
       </c>
       <c r="G173" t="n">
-        <v>6.702417949335859</v>
+        <v>6.702418039668667</v>
       </c>
       <c r="H173" t="n">
         <v>2714.261178227147</v>
@@ -14731,13 +14731,13 @@
         <v>293.3799981689453</v>
       </c>
       <c r="E186" t="n">
-        <v>301.512431640625</v>
+        <v>301.5124314371745</v>
       </c>
       <c r="F186" t="n">
-        <v>287.8015929412842</v>
+        <v>287.8015922546386</v>
       </c>
       <c r="G186" t="n">
-        <v>1.458957012864293</v>
+        <v>1.458956961819147</v>
       </c>
       <c r="H186" t="n">
         <v>359.3387168134344</v>
@@ -14811,10 +14811,10 @@
         <v>4611.431552734375</v>
       </c>
       <c r="F187" t="n">
-        <v>4470.228138427734</v>
+        <v>4470.228142089843</v>
       </c>
       <c r="G187" t="n">
-        <v>2.640331342588254</v>
+        <v>2.640331369136595</v>
       </c>
       <c r="H187" t="n">
         <v>5250</v>
@@ -16117,13 +16117,13 @@
         <v>191.3807949829101</v>
       </c>
       <c r="E204" t="n">
-        <v>181.8001528930664</v>
+        <v>181.8001529947917</v>
       </c>
       <c r="F204" t="n">
-        <v>180.3593455505371</v>
+        <v>180.3593453216553</v>
       </c>
       <c r="G204" t="n">
-        <v>1.228297049285176</v>
+        <v>1.2282971375563</v>
       </c>
       <c r="H204" t="n">
         <v>203.3999938964844</v>
@@ -17426,16 +17426,16 @@
         <v>1969.641245117188</v>
       </c>
       <c r="E221" t="n">
-        <v>1805.40054280599</v>
+        <v>1805.400537923177</v>
       </c>
       <c r="F221" t="n">
-        <v>1788.036298217773</v>
+        <v>1788.036293945313</v>
       </c>
       <c r="G221" t="n">
-        <v>1.626275178565306</v>
+        <v>1.626275076750661</v>
       </c>
       <c r="H221" t="n">
-        <v>2256.187656125729</v>
+        <v>2256.187906504501</v>
       </c>
       <c r="I221" t="n">
         <v>1345.285007075603</v>
@@ -17444,7 +17444,7 @@
         <v>46.325870700005</v>
       </c>
       <c r="K221" t="n">
-        <v>14.61456216031134</v>
+        <v>14.6145748795784</v>
       </c>
       <c r="L221" t="n">
         <v>63.39779005524861</v>
@@ -19967,13 +19967,13 @@
         <v>1274.807282714844</v>
       </c>
       <c r="E254" t="n">
-        <v>1233.511090901693</v>
+        <v>1233.511084391276</v>
       </c>
       <c r="F254" t="n">
-        <v>1302.538609924316</v>
+        <v>1302.538603820801</v>
       </c>
       <c r="G254" t="n">
-        <v>-2.765604852309467</v>
+        <v>-2.765604599094673</v>
       </c>
       <c r="H254" t="n">
         <v>1713.752567939176</v>
@@ -20663,19 +20663,19 @@
         <v>1959.745737304688</v>
       </c>
       <c r="F263" t="n">
-        <v>1867.353186035156</v>
+        <v>1867.353186645508</v>
       </c>
       <c r="G263" t="n">
-        <v>2.968043805261966</v>
+        <v>2.968043630990991</v>
       </c>
       <c r="H263" t="n">
         <v>2295</v>
       </c>
       <c r="I263" t="n">
-        <v>1174.489600842614</v>
+        <v>1174.48971989473</v>
       </c>
       <c r="J263" t="n">
-        <v>56.23807981641696</v>
+        <v>56.23806397934861</v>
       </c>
       <c r="K263" t="n">
         <v>25.06811989100817</v>
@@ -21969,13 +21969,13 @@
         <v>1804.289997558594</v>
       </c>
       <c r="E280" t="n">
-        <v>1724.227218424479</v>
+        <v>1724.227216796875</v>
       </c>
       <c r="F280" t="n">
-        <v>1685.229197387695</v>
+        <v>1685.229195556641</v>
       </c>
       <c r="G280" t="n">
-        <v>0.7875203441608303</v>
+        <v>0.7875204553944526</v>
       </c>
       <c r="H280" t="n">
         <v>1983.954544928268</v>
@@ -24362,16 +24362,16 @@
         <v>370.8467485046387</v>
       </c>
       <c r="G311" t="n">
-        <v>2.180790221241447</v>
+        <v>2.180790178281478</v>
       </c>
       <c r="H311" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I311" t="n">
-        <v>213.7662776812263</v>
+        <v>213.7662626939249</v>
       </c>
       <c r="J311" t="n">
-        <v>51.68435523002828</v>
+        <v>51.68436586472396</v>
       </c>
       <c r="K311" t="n">
         <v>36.73804369869218</v>
@@ -25052,19 +25052,19 @@
         <v>1838.69591796875</v>
       </c>
       <c r="F320" t="n">
-        <v>1803.476480712891</v>
+        <v>1803.476481323242</v>
       </c>
       <c r="G320" t="n">
-        <v>0.2383577867182796</v>
+        <v>0.238357854646587</v>
       </c>
       <c r="H320" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I320" t="n">
-        <v>1569.365993709292</v>
+        <v>1569.36587206911</v>
       </c>
       <c r="J320" t="n">
-        <v>12.07073785708164</v>
+        <v>12.07074654358695</v>
       </c>
       <c r="K320" t="n">
         <v>16.3804848526071</v>
@@ -25363,7 +25363,7 @@
         <v>8054.078349609375</v>
       </c>
       <c r="G324" t="n">
-        <v>1.697051283316942</v>
+        <v>1.697051220616452</v>
       </c>
       <c r="H324" t="n">
         <v>9070.5</v>
@@ -26210,7 +26210,7 @@
         <v>741.7763342285157</v>
       </c>
       <c r="G335" t="n">
-        <v>-0.560679762144678</v>
+        <v>-0.5606798841881755</v>
       </c>
       <c r="H335" t="n">
         <v>879.2203373423794</v>
@@ -26897,13 +26897,13 @@
         <v>2230.523427734375</v>
       </c>
       <c r="E344" t="n">
-        <v>2263.199811197916</v>
+        <v>2263.199800618489</v>
       </c>
       <c r="F344" t="n">
-        <v>2421.274553222656</v>
+        <v>2421.274544067383</v>
       </c>
       <c r="G344" t="n">
-        <v>-4.105215344718882</v>
+        <v>-4.105215591410916</v>
       </c>
       <c r="H344" t="n">
         <v>3269.779000999862</v>
@@ -27516,19 +27516,19 @@
         <v>736.6810538736979</v>
       </c>
       <c r="F352" t="n">
-        <v>690.4943719482421</v>
+        <v>690.4943716430664</v>
       </c>
       <c r="G352" t="n">
-        <v>2.635442181061731</v>
+        <v>2.635442252092668</v>
       </c>
       <c r="H352" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I352" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J352" t="n">
-        <v>29.69050423161068</v>
+        <v>29.69048900668088</v>
       </c>
       <c r="K352" t="n">
         <v>71.6297808223979</v>
@@ -29980,19 +29980,19 @@
         <v>5203.916031901042</v>
       </c>
       <c r="F384" t="n">
-        <v>4982.66357788086</v>
+        <v>4982.663582763672</v>
       </c>
       <c r="G384" t="n">
-        <v>1.003684881640954</v>
+        <v>1.003684780674474</v>
       </c>
       <c r="H384" t="n">
         <v>6049.821052103703</v>
       </c>
       <c r="I384" t="n">
-        <v>3833.724641126707</v>
+        <v>3833.724882458191</v>
       </c>
       <c r="J384" t="n">
-        <v>20.19642596568278</v>
+        <v>20.1964183993647</v>
       </c>
       <c r="K384" t="n">
         <v>31.28951935988937</v>
@@ -30060,7 +30060,7 @@
         <v>151.1833417510986</v>
       </c>
       <c r="G385" t="n">
-        <v>1.318806784289794</v>
+        <v>1.318806680681073</v>
       </c>
       <c r="H385" t="n">
         <v>196.4205715539644</v>
@@ -31058,10 +31058,10 @@
         <v>1142.182380777995</v>
       </c>
       <c r="F398" t="n">
-        <v>1157.517626037598</v>
+        <v>1157.517627258301</v>
       </c>
       <c r="G398" t="n">
-        <v>-1.035510044899335</v>
+        <v>-1.035510250390514</v>
       </c>
       <c r="H398" t="n">
         <v>1351.914027099318</v>
@@ -31366,19 +31366,19 @@
         <v>37066.92645833334</v>
       </c>
       <c r="F402" t="n">
-        <v>36159.3273828125</v>
+        <v>36159.32717773438</v>
       </c>
       <c r="G402" t="n">
-        <v>-0.01803550946101184</v>
+        <v>-0.01803561755316929</v>
       </c>
       <c r="H402" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I402" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J402" t="n">
-        <v>22.42053425050339</v>
+        <v>22.42054224281784</v>
       </c>
       <c r="K402" t="n">
         <v>20.66456096533391</v>
@@ -31982,10 +31982,10 @@
         <v>579.8880885823568</v>
       </c>
       <c r="F410" t="n">
-        <v>559.2201235961915</v>
+        <v>559.2201229858398</v>
       </c>
       <c r="G410" t="n">
-        <v>0.09776336287223852</v>
+        <v>0.09776325362216287</v>
       </c>
       <c r="H410" t="n">
         <v>784.8771245029434</v>
@@ -32213,10 +32213,10 @@
         <v>1074.885148111979</v>
       </c>
       <c r="F413" t="n">
-        <v>1076.823356628418</v>
+        <v>1076.823357543945</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.6957715334936276</v>
+        <v>-0.6957714211166754</v>
       </c>
       <c r="H413" t="n">
         <v>1294.204229651688</v>
@@ -32752,10 +32752,10 @@
         <v>83.21109186808268</v>
       </c>
       <c r="F420" t="n">
-        <v>82.1520080947876</v>
+        <v>82.15200805664062</v>
       </c>
       <c r="G420" t="n">
-        <v>0.2835531090932486</v>
+        <v>0.2835531092252763</v>
       </c>
       <c r="H420" t="n">
         <v>96.1838663751024</v>
@@ -33451,7 +33451,7 @@
         <v>-0.9851636520986862</v>
       </c>
       <c r="H429" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I429" t="n">
         <v>419.3328127807616</v>
@@ -33460,7 +33460,7 @@
         <v>6.824459845271269</v>
       </c>
       <c r="K429" t="n">
-        <v>22.27658384600939</v>
+        <v>22.27659765490666</v>
       </c>
       <c r="L429" t="n">
         <v>33.56353591160221</v>
@@ -35752,22 +35752,22 @@
         <v>427.2370001220703</v>
       </c>
       <c r="E459" t="n">
-        <v>460.3070855712891</v>
+        <v>460.3070849609375</v>
       </c>
       <c r="F459" t="n">
-        <v>462.3656211853028</v>
+        <v>462.3656214904785</v>
       </c>
       <c r="G459" t="n">
-        <v>-0.9908920844358904</v>
+        <v>-0.9908919543852202</v>
       </c>
       <c r="H459" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I459" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J459" t="n">
-        <v>13.36706130241054</v>
+        <v>13.36707038448381</v>
       </c>
       <c r="K459" t="n">
         <v>28.96265934157676</v>
@@ -36294,10 +36294,10 @@
         <v>1399.738943684896</v>
       </c>
       <c r="F466" t="n">
-        <v>1398.193536376953</v>
+        <v>1398.193536987305</v>
       </c>
       <c r="G466" t="n">
-        <v>-0.2611647225762792</v>
+        <v>-0.2611648527380162</v>
       </c>
       <c r="H466" t="n">
         <v>1817.803954384172</v>
@@ -36445,22 +36445,22 @@
         <v>2238.850017089844</v>
       </c>
       <c r="E468" t="n">
-        <v>2200.055686848958</v>
+        <v>2200.055706380208</v>
       </c>
       <c r="F468" t="n">
-        <v>2258.561375732422</v>
+        <v>2258.561395263672</v>
       </c>
       <c r="G468" t="n">
-        <v>-1.115992360137852</v>
+        <v>-1.115992192050208</v>
       </c>
       <c r="H468" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I468" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J468" t="n">
-        <v>4.565564789841581</v>
+        <v>4.565558301109629</v>
       </c>
       <c r="K468" t="n">
         <v>34.71256032649291</v>
@@ -37757,10 +37757,10 @@
         <v>284.0430090332031</v>
       </c>
       <c r="F485" t="n">
-        <v>281.7401094055176</v>
+        <v>281.7401105499268</v>
       </c>
       <c r="G485" t="n">
-        <v>-0.1596924110520148</v>
+        <v>-0.1596924643906372</v>
       </c>
       <c r="H485" t="n">
         <v>323.4425459044702</v>
@@ -38145,7 +38145,7 @@
         <v>1075.538448181152</v>
       </c>
       <c r="G490" t="n">
-        <v>-2.433800640856543</v>
+        <v>-2.43380069487632</v>
       </c>
       <c r="H490" t="n">
         <v>1395.129939548488</v>
@@ -38296,13 +38296,13 @@
         <v>417.5957645670573</v>
       </c>
       <c r="F492" t="n">
-        <v>434.4822557067871</v>
+        <v>434.4822567749023</v>
       </c>
       <c r="G492" t="n">
-        <v>-2.586643986786563</v>
+        <v>-2.586644080570566</v>
       </c>
       <c r="H492" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I492" t="n">
         <v>363.2227809620478</v>
@@ -38311,7 +38311,7 @@
         <v>12.56177407722543</v>
       </c>
       <c r="K492" t="n">
-        <v>30.53902661995522</v>
+        <v>30.53901106404269</v>
       </c>
       <c r="L492" t="n">
         <v>34.94475138121548</v>
@@ -38524,13 +38524,13 @@
         <v>13019.0030859375</v>
       </c>
       <c r="E495" t="n">
-        <v>12603.92580078125</v>
+        <v>12603.9258203125</v>
       </c>
       <c r="F495" t="n">
-        <v>12794.28542480469</v>
+        <v>12794.28547363281</v>
       </c>
       <c r="G495" t="n">
-        <v>-1.117522601216514</v>
+        <v>-1.117522746262456</v>
       </c>
       <c r="H495" t="n">
         <v>17441.42261795032</v>
@@ -38838,7 +38838,7 @@
         <v>33.49055790901184</v>
       </c>
       <c r="G499" t="n">
-        <v>-1.823120635516751</v>
+        <v>-1.823120525728428</v>
       </c>
       <c r="H499" t="n">
         <v>40.26070662850351</v>
@@ -38989,10 +38989,10 @@
         <v>949.4929280598958</v>
       </c>
       <c r="F501" t="n">
-        <v>933.0681048583984</v>
+        <v>933.0681060791015</v>
       </c>
       <c r="G501" t="n">
-        <v>-1.109264244474228</v>
+        <v>-1.109264275024235</v>
       </c>
       <c r="H501" t="n">
         <v>1224.741935222577</v>
@@ -39140,13 +39140,13 @@
         <v>317.6682745361328</v>
       </c>
       <c r="E503" t="n">
-        <v>336.0394712320963</v>
+        <v>336.0394706217448</v>
       </c>
       <c r="F503" t="n">
-        <v>339.4040826416016</v>
+        <v>339.4040809631348</v>
       </c>
       <c r="G503" t="n">
-        <v>-0.9969361827882772</v>
+        <v>-0.996936363931944</v>
       </c>
       <c r="H503" t="n">
         <v>381.3442016302781</v>
@@ -39602,13 +39602,13 @@
         <v>350.6960168457031</v>
       </c>
       <c r="E509" t="n">
-        <v>396.4461897786458</v>
+        <v>396.4461895751953</v>
       </c>
       <c r="F509" t="n">
-        <v>391.1680894470215</v>
+        <v>391.168090057373</v>
       </c>
       <c r="G509" t="n">
-        <v>-0.03492036717225311</v>
+        <v>-0.03492036711780777</v>
       </c>
       <c r="H509" t="n">
         <v>476.8288845013619</v>
@@ -40375,10 +40375,10 @@
         <v>411.8420340983073</v>
       </c>
       <c r="F519" t="n">
-        <v>413.6338316345215</v>
+        <v>413.6338307189941</v>
       </c>
       <c r="G519" t="n">
-        <v>-1.145234103342474</v>
+        <v>-1.145234141897777</v>
       </c>
       <c r="H519" t="n">
         <v>684.5682054144123</v>
@@ -40831,16 +40831,16 @@
         <v>138.3000030517578</v>
       </c>
       <c r="D525" t="n">
-        <v>154.9780004882813</v>
+        <v>154.2920004272461</v>
       </c>
       <c r="E525" t="n">
-        <v>151.6920000203451</v>
+        <v>151.6180000813802</v>
       </c>
       <c r="F525" t="n">
-        <v>155.507500076294</v>
+        <v>155.3755001068115</v>
       </c>
       <c r="G525" t="n">
-        <v>-1.785460603045186</v>
+        <v>-1.743474645070442</v>
       </c>
       <c r="H525" t="n">
         <v>205</v>
@@ -40991,10 +40991,10 @@
         <v>2411.758968098958</v>
       </c>
       <c r="F527" t="n">
-        <v>2408.797993164063</v>
+        <v>2408.79798828125</v>
       </c>
       <c r="G527" t="n">
-        <v>-1.764856206419452</v>
+        <v>-1.764856161029926</v>
       </c>
       <c r="H527" t="n">
         <v>2908.974368726317</v>
@@ -41296,13 +41296,13 @@
         <v>452.5751684570312</v>
       </c>
       <c r="E531" t="n">
-        <v>491.1339984130859</v>
+        <v>491.1339961751302</v>
       </c>
       <c r="F531" t="n">
-        <v>499.4604647827148</v>
+        <v>499.4604623413086</v>
       </c>
       <c r="G531" t="n">
-        <v>-2.906483273241633</v>
+        <v>-2.906483229434931</v>
       </c>
       <c r="H531" t="n">
         <v>756.7099518871578</v>
@@ -41761,10 +41761,10 @@
         <v>2797.888134765625</v>
       </c>
       <c r="F537" t="n">
-        <v>2720.245623779297</v>
+        <v>2720.245622558594</v>
       </c>
       <c r="G537" t="n">
-        <v>-1.13712514218699</v>
+        <v>-1.137125098831471</v>
       </c>
       <c r="H537" t="n">
         <v>3333.383184200957</v>
@@ -41992,13 +41992,13 @@
         <v>406.339267985026</v>
       </c>
       <c r="F540" t="n">
-        <v>435.0193458557129</v>
+        <v>435.0193467712402</v>
       </c>
       <c r="G540" t="n">
-        <v>-4.150591015282179</v>
+        <v>-4.150590878010307</v>
       </c>
       <c r="H540" t="n">
-        <v>605.9581114957105</v>
+        <v>605.9581737112406</v>
       </c>
       <c r="I540" t="n">
         <v>326.057353105007</v>
@@ -42007,7 +42007,7 @@
         <v>12.64888961871673</v>
       </c>
       <c r="K540" t="n">
-        <v>64.97634947847129</v>
+        <v>64.97636641708611</v>
       </c>
       <c r="L540" t="n">
         <v>12.98342541436464</v>
@@ -42454,10 +42454,10 @@
         <v>222.562045694987</v>
       </c>
       <c r="F546" t="n">
-        <v>223.5631102752685</v>
+        <v>223.5631106567383</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.330180532595227</v>
+        <v>-1.330180430682171</v>
       </c>
       <c r="H546" t="n">
         <v>286.0804190389319</v>
@@ -42916,10 +42916,10 @@
         <v>138.8841742960612</v>
       </c>
       <c r="F552" t="n">
-        <v>145.3429368591309</v>
+        <v>145.3429372406006</v>
       </c>
       <c r="G552" t="n">
-        <v>-1.822403881064383</v>
+        <v>-1.822403876368461</v>
       </c>
       <c r="H552" t="n">
         <v>184.9587904135824</v>
@@ -42999,7 +42999,7 @@
         <v>-1.470052161386193</v>
       </c>
       <c r="H553" t="n">
-        <v>834.5473213853697</v>
+        <v>834.5473868842978</v>
       </c>
       <c r="I553" t="n">
         <v>495.5999980879241</v>
@@ -43008,7 +43008,7 @@
         <v>21.98345240625199</v>
       </c>
       <c r="K553" t="n">
-        <v>38.04438644222829</v>
+        <v>38.0443972765562</v>
       </c>
       <c r="L553" t="n">
         <v>36.18784530386741</v>
@@ -43073,7 +43073,7 @@
         <v>842.4343572998047</v>
       </c>
       <c r="G554" t="n">
-        <v>-1.981970830327262</v>
+        <v>-1.981970865131011</v>
       </c>
       <c r="H554" t="n">
         <v>962.6932158005569</v>
@@ -43378,13 +43378,13 @@
         <v>7593.6013671875</v>
       </c>
       <c r="F558" t="n">
-        <v>7733.318310546875</v>
+        <v>7733.318305664063</v>
       </c>
       <c r="G558" t="n">
-        <v>-1.346337639461237</v>
+        <v>-1.346337548123022</v>
       </c>
       <c r="H558" t="n">
-        <v>9391.700937170743</v>
+        <v>9391.699890478567</v>
       </c>
       <c r="I558" t="n">
         <v>6860</v>
@@ -43393,7 +43393,7 @@
         <v>5.342565597667637</v>
       </c>
       <c r="K558" t="n">
-        <v>29.96195858535589</v>
+        <v>29.96194410127402</v>
       </c>
       <c r="L558" t="n">
         <v>33.42541436464088</v>
@@ -44687,10 +44687,10 @@
         <v>129636.1808854167</v>
       </c>
       <c r="F575" t="n">
-        <v>133208.09640625</v>
+        <v>133208.0965625</v>
       </c>
       <c r="G575" t="n">
-        <v>-2.362631962750816</v>
+        <v>-2.362632015955257</v>
       </c>
       <c r="H575" t="n">
         <v>163308.4863287346</v>
@@ -44764,10 +44764,10 @@
         <v>884.7556599934895</v>
       </c>
       <c r="F576" t="n">
-        <v>910.8992602539063</v>
+        <v>910.8992587280273</v>
       </c>
       <c r="G576" t="n">
-        <v>-1.600471290550021</v>
+        <v>-1.6004711958715</v>
       </c>
       <c r="H576" t="n">
         <v>1282.80960014975</v>
@@ -45069,16 +45069,16 @@
         <v>18.62360000610352</v>
       </c>
       <c r="E580" t="n">
-        <v>20.14443482716878</v>
+        <v>20.1444348526001</v>
       </c>
       <c r="F580" t="n">
-        <v>20.27678071022034</v>
+        <v>20.27678067207336</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.721833100033443</v>
+        <v>-1.721833375779669</v>
       </c>
       <c r="H580" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I580" t="n">
         <v>16.75</v>
@@ -45087,7 +45087,7 @@
         <v>5.194034861094909</v>
       </c>
       <c r="K580" t="n">
-        <v>35.27389962353353</v>
+        <v>35.27388827254756</v>
       </c>
       <c r="L580" t="n">
         <v>26.24309392265193</v>
@@ -46079,7 +46079,7 @@
         <v>-1.964394458875585</v>
       </c>
       <c r="H593" t="n">
-        <v>2308.784934113526</v>
+        <v>2308.784681838889</v>
       </c>
       <c r="I593" t="n">
         <v>1580</v>
@@ -46088,7 +46088,7 @@
         <v>6.6075964819027</v>
       </c>
       <c r="K593" t="n">
-        <v>37.06868324919805</v>
+        <v>37.06866827207662</v>
       </c>
       <c r="L593" t="n">
         <v>23.61878453038674</v>
@@ -46458,13 +46458,13 @@
         <v>1202.318788655599</v>
       </c>
       <c r="F598" t="n">
-        <v>1246.489169616699</v>
+        <v>1246.489167175293</v>
       </c>
       <c r="G598" t="n">
-        <v>-2.841589809228739</v>
+        <v>-2.841589907080977</v>
       </c>
       <c r="H598" t="n">
-        <v>1507.849092404508</v>
+        <v>1507.849216441457</v>
       </c>
       <c r="I598" t="n">
         <v>1015.099975585938</v>
@@ -46473,7 +46473,7 @@
         <v>10.43247236341767</v>
       </c>
       <c r="K598" t="n">
-        <v>34.50928567390792</v>
+        <v>34.50929673875618</v>
       </c>
       <c r="L598" t="n">
         <v>22.51381215469613</v>
@@ -46920,13 +46920,13 @@
         <v>121.2708986409505</v>
       </c>
       <c r="F604" t="n">
-        <v>122.7790681457519</v>
+        <v>122.779068107605</v>
       </c>
       <c r="G604" t="n">
-        <v>-2.600972153646652</v>
+        <v>-2.600971682843312</v>
       </c>
       <c r="H604" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I604" t="n">
         <v>103.0500030517578</v>
@@ -46935,7 +46935,7 @@
         <v>4.36681209775398</v>
       </c>
       <c r="K604" t="n">
-        <v>44.95581027554825</v>
+        <v>44.9557938412435</v>
       </c>
       <c r="L604" t="n">
         <v>20.44198895027624</v>
@@ -47767,10 +47767,10 @@
         <v>153.8962880452474</v>
       </c>
       <c r="F615" t="n">
-        <v>158.5334973907471</v>
+        <v>158.5334972381592</v>
       </c>
       <c r="G615" t="n">
-        <v>-2.853053153992635</v>
+        <v>-2.853053292914132</v>
       </c>
       <c r="H615" t="n">
         <v>212.7553783484557</v>
@@ -48158,7 +48158,7 @@
         <v>-4.856901309859274</v>
       </c>
       <c r="H620" t="n">
-        <v>523.0941269255326</v>
+        <v>523.09418899518</v>
       </c>
       <c r="I620" t="n">
         <v>299</v>
@@ -48167,7 +48167,7 @@
         <v>12.34113508243624</v>
       </c>
       <c r="K620" t="n">
-        <v>55.72912665391014</v>
+        <v>55.72914513251943</v>
       </c>
       <c r="L620" t="n">
         <v>16.9889502762431</v>
@@ -48614,13 +48614,13 @@
         <v>252.2240498860677</v>
       </c>
       <c r="F626" t="n">
-        <v>260.4150134277344</v>
+        <v>260.4150129699707</v>
       </c>
       <c r="G626" t="n">
-        <v>-3.89524632174193</v>
+        <v>-3.895246220085868</v>
       </c>
       <c r="H626" t="n">
-        <v>345.9511213302791</v>
+        <v>345.9510897219776</v>
       </c>
       <c r="I626" t="n">
         <v>212</v>
@@ -48629,7 +48629,7 @@
         <v>7.325471122309857</v>
       </c>
       <c r="K626" t="n">
-        <v>52.04637770241902</v>
+        <v>52.04636381049195</v>
       </c>
       <c r="L626" t="n">
         <v>15.60773480662983</v>
@@ -49153,13 +49153,13 @@
         <v>993.2585257975261</v>
       </c>
       <c r="F633" t="n">
-        <v>1042.194985656738</v>
+        <v>1042.194986877441</v>
       </c>
       <c r="G633" t="n">
-        <v>-2.799108634517522</v>
+        <v>-2.799108741993528</v>
       </c>
       <c r="H633" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I633" t="n">
         <v>832.5999755859375</v>
@@ -49168,7 +49168,7 @@
         <v>2.690370534577369</v>
       </c>
       <c r="K633" t="n">
-        <v>46.80449508185218</v>
+        <v>46.80448050481942</v>
       </c>
       <c r="L633" t="n">
         <v>14.22651933701657</v>
@@ -49227,16 +49227,16 @@
         <v>176.8348574829102</v>
       </c>
       <c r="E634" t="n">
-        <v>190.2435905965169</v>
+        <v>190.2435909016927</v>
       </c>
       <c r="F634" t="n">
-        <v>192.0990494537353</v>
+        <v>192.0990498352051</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.694384437157848</v>
+        <v>-2.694384544765238</v>
       </c>
       <c r="H634" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I634" t="n">
         <v>155.8000030517578</v>
@@ -49245,7 +49245,7 @@
         <v>3.395374314835831</v>
       </c>
       <c r="K634" t="n">
-        <v>48.50002717584694</v>
+        <v>48.50003676144992</v>
       </c>
       <c r="L634" t="n">
         <v>14.08839779005525</v>
@@ -51155,13 +51155,13 @@
         <v>379.9771179199219</v>
       </c>
       <c r="F659" t="n">
-        <v>389.2492016601562</v>
+        <v>389.2492022705078</v>
       </c>
       <c r="G659" t="n">
-        <v>-2.611727786751439</v>
+        <v>-2.611727745583481</v>
       </c>
       <c r="H659" t="n">
-        <v>541.0235690240457</v>
+        <v>541.0236304500187</v>
       </c>
       <c r="I659" t="n">
         <v>271.5615990811692</v>
@@ -51170,7 +51170,7 @@
         <v>17.76333210402889</v>
       </c>
       <c r="K659" t="n">
-        <v>69.1756065276313</v>
+        <v>69.17562573525333</v>
       </c>
       <c r="L659" t="n">
         <v>9.668508287292818</v>
@@ -51383,16 +51383,16 @@
         <v>83.92279052734375</v>
       </c>
       <c r="E662" t="n">
-        <v>91.18646672566732</v>
+        <v>91.18646697998047</v>
       </c>
       <c r="F662" t="n">
-        <v>93.7601276397705</v>
+        <v>93.76012783050537</v>
       </c>
       <c r="G662" t="n">
-        <v>-3.77673381695649</v>
+        <v>-3.776733847234259</v>
       </c>
       <c r="H662" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I662" t="n">
         <v>73.90000152587891</v>
@@ -51401,7 +51401,7 @@
         <v>2.178620537359199</v>
       </c>
       <c r="K662" t="n">
-        <v>65.31228462855059</v>
+        <v>65.31227421356375</v>
       </c>
       <c r="L662" t="n">
         <v>9.25414364640884</v>
@@ -51922,22 +51922,22 @@
         <v>481.3466955566406</v>
       </c>
       <c r="E669" t="n">
-        <v>502.6339693196614</v>
+        <v>502.6339683024088</v>
       </c>
       <c r="F669" t="n">
-        <v>522.9714303588867</v>
+        <v>522.9714292907715</v>
       </c>
       <c r="G669" t="n">
-        <v>-4.575324577819306</v>
+        <v>-4.575324586736373</v>
       </c>
       <c r="H669" t="n">
         <v>756.8456624851057</v>
       </c>
       <c r="I669" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J669" t="n">
-        <v>10.5223068938356</v>
+        <v>10.52229868658205</v>
       </c>
       <c r="K669" t="n">
         <v>68.61883751663775</v>
@@ -53080,10 +53080,10 @@
         <v>128.6862941996256</v>
       </c>
       <c r="F684" t="n">
-        <v>135.5109524154663</v>
+        <v>135.5109527206421</v>
       </c>
       <c r="G684" t="n">
-        <v>-3.698135176885564</v>
+        <v>-3.698135221079002</v>
       </c>
       <c r="H684" t="n">
         <v>183.7853835258596</v>
@@ -53234,10 +53234,10 @@
         <v>270.028515218099</v>
       </c>
       <c r="F686" t="n">
-        <v>282.0782897949219</v>
+        <v>282.0782901000977</v>
       </c>
       <c r="G686" t="n">
-        <v>-4.468323860176615</v>
+        <v>-4.468324003662283</v>
       </c>
       <c r="H686" t="n">
         <v>385.6351549871131</v>
@@ -53930,7 +53930,7 @@
         <v>262.2869714355469</v>
       </c>
       <c r="G695" t="n">
-        <v>-4.626065948865765</v>
+        <v>-4.626065843029926</v>
       </c>
       <c r="H695" t="n">
         <v>398.2045017598045</v>
@@ -54620,10 +54620,10 @@
         <v>639.1963462320964</v>
       </c>
       <c r="F704" t="n">
-        <v>727.4957774353028</v>
+        <v>727.4957801818848</v>
       </c>
       <c r="G704" t="n">
-        <v>-9.475348951702179</v>
+        <v>-9.475348781815285</v>
       </c>
       <c r="H704" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2414,10 +2414,10 @@
         <v>11090.68897135417</v>
       </c>
       <c r="F26" t="n">
-        <v>10638.51545654297</v>
+        <v>10638.51546142578</v>
       </c>
       <c r="G26" t="n">
-        <v>4.387903484029199</v>
+        <v>4.387903381899405</v>
       </c>
       <c r="H26" t="n">
         <v>14498</v>
@@ -2719,13 +2719,13 @@
         <v>1431.348356933594</v>
       </c>
       <c r="E30" t="n">
-        <v>1217.522702636719</v>
+        <v>1217.522706298828</v>
       </c>
       <c r="F30" t="n">
-        <v>1104.636867675781</v>
+        <v>1104.636871948242</v>
       </c>
       <c r="G30" t="n">
-        <v>8.898175234364558</v>
+        <v>8.898175000313646</v>
       </c>
       <c r="H30" t="n">
         <v>1681</v>
@@ -4567,13 +4567,13 @@
         <v>1057.192004394531</v>
       </c>
       <c r="E54" t="n">
-        <v>960.7331079101563</v>
+        <v>960.7331095377605</v>
       </c>
       <c r="F54" t="n">
-        <v>929.5291012573242</v>
+        <v>929.5291033935547</v>
       </c>
       <c r="G54" t="n">
-        <v>3.432444743422902</v>
+        <v>3.432444665016288</v>
       </c>
       <c r="H54" t="n">
         <v>1223</v>
@@ -4878,10 +4878,10 @@
         <v>242.1920374552409</v>
       </c>
       <c r="F58" t="n">
-        <v>229.7379677581787</v>
+        <v>229.7379676055908</v>
       </c>
       <c r="G58" t="n">
-        <v>5.054038357000756</v>
+        <v>5.054038323876475</v>
       </c>
       <c r="H58" t="n">
         <v>321.3999938964844</v>
@@ -5032,10 +5032,10 @@
         <v>159.833235168457</v>
       </c>
       <c r="F60" t="n">
-        <v>156.3067572402954</v>
+        <v>156.3067570114136</v>
       </c>
       <c r="G60" t="n">
-        <v>2.838844303797416</v>
+        <v>2.838844411314434</v>
       </c>
       <c r="H60" t="n">
         <v>233.3500061035156</v>
@@ -6954,13 +6954,13 @@
         <v>1418.404001464844</v>
       </c>
       <c r="E85" t="n">
-        <v>1170.398425292969</v>
+        <v>1170.398424886068</v>
       </c>
       <c r="F85" t="n">
         <v>1085.251582641602</v>
       </c>
       <c r="G85" t="n">
-        <v>6.060298256891161</v>
+        <v>6.060298225259264</v>
       </c>
       <c r="H85" t="n">
         <v>1677.5</v>
@@ -7265,10 +7265,10 @@
         <v>670.5830324300131</v>
       </c>
       <c r="F89" t="n">
-        <v>626.9189421081543</v>
+        <v>626.9189418029786</v>
       </c>
       <c r="G89" t="n">
-        <v>5.83898731955943</v>
+        <v>5.838987186244449</v>
       </c>
       <c r="H89" t="n">
         <v>844</v>
@@ -7724,13 +7724,13 @@
         <v>343.9190014648437</v>
       </c>
       <c r="E95" t="n">
-        <v>267.0611861165365</v>
+        <v>267.061186319987</v>
       </c>
       <c r="F95" t="n">
-        <v>249.9069129943848</v>
+        <v>249.9069130706787</v>
       </c>
       <c r="G95" t="n">
-        <v>6.591772767250403</v>
+        <v>6.591772869164525</v>
       </c>
       <c r="H95" t="n">
         <v>388.75</v>
@@ -8340,13 +8340,13 @@
         <v>163.2757998657227</v>
       </c>
       <c r="E103" t="n">
-        <v>143.1894893900553</v>
+        <v>143.1894893391927</v>
       </c>
       <c r="F103" t="n">
-        <v>137.6178078079224</v>
+        <v>137.6178078842163</v>
       </c>
       <c r="G103" t="n">
-        <v>3.550083321479791</v>
+        <v>3.550083378886937</v>
       </c>
       <c r="H103" t="n">
         <v>173.2700042724609</v>
@@ -9264,13 +9264,13 @@
         <v>2161.481472167969</v>
       </c>
       <c r="E115" t="n">
-        <v>1932.446783040365</v>
+        <v>1932.446788736979</v>
       </c>
       <c r="F115" t="n">
-        <v>1828.775313720703</v>
+        <v>1828.775318603516</v>
       </c>
       <c r="G115" t="n">
-        <v>4.249121085026797</v>
+        <v>4.249120964385367</v>
       </c>
       <c r="H115" t="n">
         <v>2264.114307176184</v>
@@ -10040,7 +10040,7 @@
         <v>75.44904144287109</v>
       </c>
       <c r="G125" t="n">
-        <v>3.955123155098472</v>
+        <v>3.955123100460045</v>
       </c>
       <c r="H125" t="n">
         <v>94.5</v>
@@ -10191,10 +10191,10 @@
         <v>1525.751455891927</v>
       </c>
       <c r="F127" t="n">
-        <v>1524.064552001953</v>
+        <v>1524.064555053711</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.2522260007807753</v>
+        <v>-0.2522259604311516</v>
       </c>
       <c r="H127" t="n">
         <v>2021.199951171875</v>
@@ -10345,10 +10345,10 @@
         <v>1682.017312825521</v>
       </c>
       <c r="F129" t="n">
-        <v>1613.566032714844</v>
+        <v>1613.566029663086</v>
       </c>
       <c r="G129" t="n">
-        <v>3.351370454557379</v>
+        <v>3.351370824745503</v>
       </c>
       <c r="H129" t="n">
         <v>2038.599975585938</v>
@@ -10887,7 +10887,7 @@
         <v>990.532312927246</v>
       </c>
       <c r="G136" t="n">
-        <v>3.930202477648037</v>
+        <v>3.930202610762401</v>
       </c>
       <c r="H136" t="n">
         <v>1368.900024414062</v>
@@ -12116,10 +12116,10 @@
         <v>1031.978623453776</v>
       </c>
       <c r="F152" t="n">
-        <v>997.1892303466797</v>
+        <v>997.1892315673828</v>
       </c>
       <c r="G152" t="n">
-        <v>1.184580290618831</v>
+        <v>1.184580257818624</v>
       </c>
       <c r="H152" t="n">
         <v>1331.075409591023</v>
@@ -12424,10 +12424,10 @@
         <v>314.5854669189453</v>
       </c>
       <c r="F156" t="n">
-        <v>310.2953787231446</v>
+        <v>310.2953784179688</v>
       </c>
       <c r="G156" t="n">
-        <v>1.249732680253945</v>
+        <v>1.249732731910269</v>
       </c>
       <c r="H156" t="n">
         <v>380.4567148307952</v>
@@ -13117,10 +13117,10 @@
         <v>626.8444034830729</v>
       </c>
       <c r="F165" t="n">
-        <v>612.2530047607422</v>
+        <v>612.2530038452148</v>
       </c>
       <c r="G165" t="n">
-        <v>1.393174047224877</v>
+        <v>1.393173946850701</v>
       </c>
       <c r="H165" t="n">
         <v>769</v>
@@ -14965,10 +14965,10 @@
         <v>530.0145731608073</v>
       </c>
       <c r="F189" t="n">
-        <v>538.6586685180664</v>
+        <v>538.658667602539</v>
       </c>
       <c r="G189" t="n">
-        <v>0.3896022769497076</v>
+        <v>0.3896022205173821</v>
       </c>
       <c r="H189" t="n">
         <v>673.9500122070312</v>
@@ -16117,13 +16117,13 @@
         <v>191.3807949829101</v>
       </c>
       <c r="E204" t="n">
-        <v>181.8001529947917</v>
+        <v>181.8001528930664</v>
       </c>
       <c r="F204" t="n">
-        <v>180.3593453216553</v>
+        <v>180.3593455505371</v>
       </c>
       <c r="G204" t="n">
-        <v>1.2282971375563</v>
+        <v>1.228297049285176</v>
       </c>
       <c r="H204" t="n">
         <v>203.3999938964844</v>
@@ -17429,13 +17429,13 @@
         <v>1805.400537923177</v>
       </c>
       <c r="F221" t="n">
-        <v>1788.036293945313</v>
+        <v>1788.036292114258</v>
       </c>
       <c r="G221" t="n">
-        <v>1.626275076750661</v>
+        <v>1.626275219461504</v>
       </c>
       <c r="H221" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I221" t="n">
         <v>1345.285007075603</v>
@@ -17444,7 +17444,7 @@
         <v>46.325870700005</v>
       </c>
       <c r="K221" t="n">
-        <v>14.6145748795784</v>
+        <v>14.61456216031134</v>
       </c>
       <c r="L221" t="n">
         <v>63.39779005524861</v>
@@ -19046,13 +19046,13 @@
         <v>5181.613190104166</v>
       </c>
       <c r="F242" t="n">
-        <v>5329.781801757813</v>
+        <v>5329.781804199219</v>
       </c>
       <c r="G242" t="n">
-        <v>-1.626053131890992</v>
+        <v>-1.626053175487563</v>
       </c>
       <c r="H242" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I242" t="n">
         <v>4229.809203861739</v>
@@ -19061,7 +19061,7 @@
         <v>35.72716222657446</v>
       </c>
       <c r="K242" t="n">
-        <v>14.13786287233574</v>
+        <v>14.137854222998</v>
       </c>
       <c r="L242" t="n">
         <v>65.88397790055248</v>
@@ -19967,22 +19967,22 @@
         <v>1274.807282714844</v>
       </c>
       <c r="E254" t="n">
-        <v>1233.511084391276</v>
+        <v>1233.511082356771</v>
       </c>
       <c r="F254" t="n">
-        <v>1302.538603820801</v>
+        <v>1302.538596801758</v>
       </c>
       <c r="G254" t="n">
-        <v>-2.765604599094673</v>
+        <v>-2.765605056611709</v>
       </c>
       <c r="H254" t="n">
         <v>1713.752567939176</v>
       </c>
       <c r="I254" t="n">
-        <v>1010.594326763664</v>
+        <v>1010.594387550952</v>
       </c>
       <c r="J254" t="n">
-        <v>36.5533096172551</v>
+        <v>36.55330140356863</v>
       </c>
       <c r="K254" t="n">
         <v>24.18496869124462</v>
@@ -21664,10 +21664,10 @@
         <v>1365.35015218099</v>
       </c>
       <c r="F276" t="n">
-        <v>1363.836433105469</v>
+        <v>1363.836429443359</v>
       </c>
       <c r="G276" t="n">
-        <v>-0.3195208438461772</v>
+        <v>-0.3195208447014153</v>
       </c>
       <c r="H276" t="n">
         <v>1563.400024414062</v>
@@ -21747,7 +21747,7 @@
         <v>-1.054467626912103</v>
       </c>
       <c r="H277" t="n">
-        <v>1409.944064008135</v>
+        <v>1409.944189808421</v>
       </c>
       <c r="I277" t="n">
         <v>905.5050975494345</v>
@@ -21756,7 +21756,7 @@
         <v>39.71207660891953</v>
       </c>
       <c r="K277" t="n">
-        <v>11.44922071120211</v>
+        <v>11.44923065510284</v>
       </c>
       <c r="L277" t="n">
         <v>62.98342541436463</v>
@@ -22049,13 +22049,13 @@
         <v>4253.469314778646</v>
       </c>
       <c r="F281" t="n">
-        <v>4317.245635986328</v>
+        <v>4317.24564819336</v>
       </c>
       <c r="G281" t="n">
-        <v>0.4036618907008682</v>
+        <v>0.4036616615247013</v>
       </c>
       <c r="H281" t="n">
-        <v>5005.771184298104</v>
+        <v>5005.771680286142</v>
       </c>
       <c r="I281" t="n">
         <v>3669.905008549105</v>
@@ -22064,7 +22064,7 @@
         <v>23.92418582359328</v>
       </c>
       <c r="K281" t="n">
-        <v>10.06775196873597</v>
+        <v>10.06776287460569</v>
       </c>
       <c r="L281" t="n">
         <v>60.6353591160221</v>
@@ -24362,7 +24362,7 @@
         <v>370.8467485046387</v>
       </c>
       <c r="G311" t="n">
-        <v>2.180790178281478</v>
+        <v>2.180790221241447</v>
       </c>
       <c r="H311" t="n">
         <v>443.3731066930094</v>
@@ -24436,10 +24436,10 @@
         <v>428.5723400878906</v>
       </c>
       <c r="F312" t="n">
-        <v>424.1940910339355</v>
+        <v>424.1940914916992</v>
       </c>
       <c r="G312" t="n">
-        <v>1.321200202019579</v>
+        <v>1.321200274431034</v>
       </c>
       <c r="H312" t="n">
         <v>478.7148709533388</v>
@@ -24744,10 +24744,10 @@
         <v>462.7146718343099</v>
       </c>
       <c r="F316" t="n">
-        <v>460.3243093872071</v>
+        <v>460.324308013916</v>
       </c>
       <c r="G316" t="n">
-        <v>1.390269237366759</v>
+        <v>1.390269343800044</v>
       </c>
       <c r="H316" t="n">
         <v>529.9163379046904</v>
@@ -25052,19 +25052,19 @@
         <v>1838.69591796875</v>
       </c>
       <c r="F320" t="n">
-        <v>1803.476481323242</v>
+        <v>1803.476480712891</v>
       </c>
       <c r="G320" t="n">
-        <v>0.238357854646587</v>
+        <v>0.2383577867182796</v>
       </c>
       <c r="H320" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I320" t="n">
-        <v>1569.36587206911</v>
+        <v>1569.365993709292</v>
       </c>
       <c r="J320" t="n">
-        <v>12.07074654358695</v>
+        <v>12.07073785708164</v>
       </c>
       <c r="K320" t="n">
         <v>16.3804848526071</v>
@@ -25283,13 +25283,13 @@
         <v>744.0869934082032</v>
       </c>
       <c r="F323" t="n">
-        <v>753.9871234130859</v>
+        <v>753.9871240234374</v>
       </c>
       <c r="G323" t="n">
-        <v>-1.063928500714328</v>
+        <v>-1.063928499862243</v>
       </c>
       <c r="H323" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I323" t="n">
         <v>612.1496526863262</v>
@@ -25298,7 +25298,7 @@
         <v>36.10234372557586</v>
       </c>
       <c r="K323" t="n">
-        <v>34.13663724489548</v>
+        <v>34.13662228388142</v>
       </c>
       <c r="L323" t="n">
         <v>60.77348066298342</v>
@@ -25514,10 +25514,10 @@
         <v>1384.819230143229</v>
       </c>
       <c r="F326" t="n">
-        <v>1360.158920898438</v>
+        <v>1360.158922729492</v>
       </c>
       <c r="G326" t="n">
-        <v>0.8827066029901243</v>
+        <v>0.8827066017913054</v>
       </c>
       <c r="H326" t="n">
         <v>1553</v>
@@ -26210,7 +26210,7 @@
         <v>741.7763342285157</v>
       </c>
       <c r="G335" t="n">
-        <v>-0.5606798841881755</v>
+        <v>-0.560679762144678</v>
       </c>
       <c r="H335" t="n">
         <v>879.2203373423794</v>
@@ -26897,13 +26897,13 @@
         <v>2230.523427734375</v>
       </c>
       <c r="E344" t="n">
-        <v>2263.199800618489</v>
+        <v>2263.199816080729</v>
       </c>
       <c r="F344" t="n">
-        <v>2421.274544067383</v>
+        <v>2421.274552001953</v>
       </c>
       <c r="G344" t="n">
-        <v>-4.105215591410916</v>
+        <v>-4.105215207619583</v>
       </c>
       <c r="H344" t="n">
         <v>3269.779000999862</v>
@@ -27516,19 +27516,19 @@
         <v>736.6810538736979</v>
       </c>
       <c r="F352" t="n">
-        <v>690.4943716430664</v>
+        <v>690.4943719482421</v>
       </c>
       <c r="G352" t="n">
-        <v>2.635442252092668</v>
+        <v>2.635442181061731</v>
       </c>
       <c r="H352" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I352" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J352" t="n">
-        <v>29.69048900668088</v>
+        <v>29.69050423161068</v>
       </c>
       <c r="K352" t="n">
         <v>71.6297808223979</v>
@@ -28286,19 +28286,19 @@
         <v>339.748002726237</v>
       </c>
       <c r="F362" t="n">
-        <v>334.3615377807617</v>
+        <v>334.3615374755859</v>
       </c>
       <c r="G362" t="n">
-        <v>0.05145202949812244</v>
+        <v>0.0514521665928358</v>
       </c>
       <c r="H362" t="n">
         <v>385.3928663983843</v>
       </c>
       <c r="I362" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J362" t="n">
-        <v>15.57610315839051</v>
+        <v>15.57611546464699</v>
       </c>
       <c r="K362" t="n">
         <v>17.96536639066888</v>
@@ -29441,13 +29441,13 @@
         <v>207.4728631591797</v>
       </c>
       <c r="F377" t="n">
-        <v>210.5249073791504</v>
+        <v>210.5249073028564</v>
       </c>
       <c r="G377" t="n">
-        <v>-1.111951212786833</v>
+        <v>-1.111951390377364</v>
       </c>
       <c r="H377" t="n">
-        <v>252.6161043110497</v>
+        <v>252.6160882566492</v>
       </c>
       <c r="I377" t="n">
         <v>171.6534204603822</v>
@@ -29456,7 +29456,7 @@
         <v>22.21719364721459</v>
       </c>
       <c r="K377" t="n">
-        <v>20.41380065564249</v>
+        <v>20.41379300303701</v>
       </c>
       <c r="L377" t="n">
         <v>41.85082872928177</v>
@@ -29980,19 +29980,19 @@
         <v>5203.916031901042</v>
       </c>
       <c r="F384" t="n">
-        <v>4982.663582763672</v>
+        <v>4982.66357788086</v>
       </c>
       <c r="G384" t="n">
-        <v>1.003684780674474</v>
+        <v>1.003684881640954</v>
       </c>
       <c r="H384" t="n">
         <v>6049.821052103703</v>
       </c>
       <c r="I384" t="n">
-        <v>3833.724882458191</v>
+        <v>3833.724641126707</v>
       </c>
       <c r="J384" t="n">
-        <v>20.1964183993647</v>
+        <v>20.19642596568278</v>
       </c>
       <c r="K384" t="n">
         <v>31.28951935988937</v>
@@ -30051,19 +30051,19 @@
         <v>149.9299926757812</v>
       </c>
       <c r="D385" t="n">
-        <v>152.3344348144531</v>
+        <v>152.3344345092773</v>
       </c>
       <c r="E385" t="n">
-        <v>154.5325894165039</v>
+        <v>154.532588297526</v>
       </c>
       <c r="F385" t="n">
-        <v>151.1833417510986</v>
+        <v>151.1833409118652</v>
       </c>
       <c r="G385" t="n">
-        <v>1.318806680681073</v>
+        <v>1.318806429076691</v>
       </c>
       <c r="H385" t="n">
-        <v>196.4205715539644</v>
+        <v>196.4205869556906</v>
       </c>
       <c r="I385" t="n">
         <v>125.7825892411346</v>
@@ -30072,7 +30072,7 @@
         <v>19.19773124430937</v>
       </c>
       <c r="K385" t="n">
-        <v>31.00819125544647</v>
+        <v>31.00820152805834</v>
       </c>
       <c r="L385" t="n">
         <v>66.02209944751381</v>
@@ -30827,10 +30827,10 @@
         <v>1669.609126790365</v>
       </c>
       <c r="F395" t="n">
-        <v>1677.015997924805</v>
+        <v>1677.015996704102</v>
       </c>
       <c r="G395" t="n">
-        <v>-0.3335958885330781</v>
+        <v>-0.3335959249277654</v>
       </c>
       <c r="H395" t="n">
         <v>1952.5</v>
@@ -31289,10 +31289,10 @@
         <v>739.9110229492187</v>
       </c>
       <c r="F401" t="n">
-        <v>732.0420303344727</v>
+        <v>732.0420297241211</v>
       </c>
       <c r="G401" t="n">
-        <v>-0.8831947009678154</v>
+        <v>-0.8831947836080101</v>
       </c>
       <c r="H401" t="n">
         <v>837.8765073351432</v>
@@ -31366,10 +31366,10 @@
         <v>37066.92645833334</v>
       </c>
       <c r="F402" t="n">
-        <v>36159.32717773438</v>
+        <v>36159.32729492187</v>
       </c>
       <c r="G402" t="n">
-        <v>-0.01803561755316929</v>
+        <v>-0.01803540151499305</v>
       </c>
       <c r="H402" t="n">
         <v>43614.20556091995</v>
@@ -31982,10 +31982,10 @@
         <v>579.8880885823568</v>
       </c>
       <c r="F410" t="n">
-        <v>559.2201229858398</v>
+        <v>559.2201235961915</v>
       </c>
       <c r="G410" t="n">
-        <v>0.09776325362216287</v>
+        <v>0.09776336287223852</v>
       </c>
       <c r="H410" t="n">
         <v>784.8771245029434</v>
@@ -32213,10 +32213,10 @@
         <v>1074.885148111979</v>
       </c>
       <c r="F413" t="n">
-        <v>1076.823357543945</v>
+        <v>1076.823356628418</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.6957714211166754</v>
+        <v>-0.6957715334936276</v>
       </c>
       <c r="H413" t="n">
         <v>1294.204229651688</v>
@@ -32444,10 +32444,10 @@
         <v>354.3472393798828</v>
       </c>
       <c r="F416" t="n">
-        <v>353.5069059753418</v>
+        <v>353.5069058227539</v>
       </c>
       <c r="G416" t="n">
-        <v>0.08884551410439645</v>
+        <v>0.08884542766121051</v>
       </c>
       <c r="H416" t="n">
         <v>409.9712889887167</v>
@@ -32752,10 +32752,10 @@
         <v>83.21109186808268</v>
       </c>
       <c r="F420" t="n">
-        <v>82.15200805664062</v>
+        <v>82.1520080947876</v>
       </c>
       <c r="G420" t="n">
-        <v>0.2835531092252763</v>
+        <v>0.2835531090932486</v>
       </c>
       <c r="H420" t="n">
         <v>96.1838663751024</v>
@@ -32829,10 +32829,10 @@
         <v>777.6781604003907</v>
       </c>
       <c r="F421" t="n">
-        <v>784.9243908691407</v>
+        <v>784.9243887329102</v>
       </c>
       <c r="G421" t="n">
-        <v>-1.203543304061305</v>
+        <v>-1.203543307297417</v>
       </c>
       <c r="H421" t="n">
         <v>1089.356915377717</v>
@@ -33442,13 +33442,13 @@
         <v>486.5100677490234</v>
       </c>
       <c r="E429" t="n">
-        <v>482.0436838785807</v>
+        <v>482.0436850992838</v>
       </c>
       <c r="F429" t="n">
-        <v>487.2318054199219</v>
+        <v>487.2318072509765</v>
       </c>
       <c r="G429" t="n">
-        <v>-0.9851636520986862</v>
+        <v>-0.9851636177295453</v>
       </c>
       <c r="H429" t="n">
         <v>547.7380341214969</v>
@@ -35752,22 +35752,22 @@
         <v>427.2370001220703</v>
       </c>
       <c r="E459" t="n">
-        <v>460.3070849609375</v>
+        <v>460.307084757487</v>
       </c>
       <c r="F459" t="n">
-        <v>462.3656214904785</v>
+        <v>462.3656211853028</v>
       </c>
       <c r="G459" t="n">
-        <v>-0.9908919543852202</v>
+        <v>-0.9908917932788253</v>
       </c>
       <c r="H459" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I459" t="n">
-        <v>379.7399002549519</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J459" t="n">
-        <v>13.36707038448381</v>
+        <v>13.36706130241054</v>
       </c>
       <c r="K459" t="n">
         <v>28.96265934157676</v>
@@ -36294,10 +36294,10 @@
         <v>1399.738943684896</v>
       </c>
       <c r="F466" t="n">
-        <v>1398.193536987305</v>
+        <v>1398.193536376953</v>
       </c>
       <c r="G466" t="n">
-        <v>-0.2611648527380162</v>
+        <v>-0.2611647225762792</v>
       </c>
       <c r="H466" t="n">
         <v>1817.803954384172</v>
@@ -36448,10 +36448,10 @@
         <v>2200.055706380208</v>
       </c>
       <c r="F468" t="n">
-        <v>2258.561395263672</v>
+        <v>2258.561396484375</v>
       </c>
       <c r="G468" t="n">
-        <v>-1.115992192050208</v>
+        <v>-1.115992191453763</v>
       </c>
       <c r="H468" t="n">
         <v>2765.379504159864</v>
@@ -36602,10 +36602,10 @@
         <v>254.186355082194</v>
       </c>
       <c r="F470" t="n">
-        <v>253.8828430175781</v>
+        <v>253.882843170166</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.1806587984453878</v>
+        <v>-0.1806587384522773</v>
       </c>
       <c r="H470" t="n">
         <v>306.197022156633</v>
@@ -38145,7 +38145,7 @@
         <v>1075.538448181152</v>
       </c>
       <c r="G490" t="n">
-        <v>-2.43380069487632</v>
+        <v>-2.433800640856543</v>
       </c>
       <c r="H490" t="n">
         <v>1395.129939548488</v>
@@ -38524,13 +38524,13 @@
         <v>13019.0030859375</v>
       </c>
       <c r="E495" t="n">
-        <v>12603.9258203125</v>
+        <v>12603.92580078125</v>
       </c>
       <c r="F495" t="n">
-        <v>12794.28547363281</v>
+        <v>12794.28542480469</v>
       </c>
       <c r="G495" t="n">
-        <v>-1.117522746262456</v>
+        <v>-1.117522601216514</v>
       </c>
       <c r="H495" t="n">
         <v>17441.42261795032</v>
@@ -38838,7 +38838,7 @@
         <v>33.49055790901184</v>
       </c>
       <c r="G499" t="n">
-        <v>-1.823120525728428</v>
+        <v>-1.823120635516751</v>
       </c>
       <c r="H499" t="n">
         <v>40.26070662850351</v>
@@ -39140,13 +39140,13 @@
         <v>317.6682745361328</v>
       </c>
       <c r="E503" t="n">
-        <v>336.0394706217448</v>
+        <v>336.0394691975911</v>
       </c>
       <c r="F503" t="n">
-        <v>339.4040809631348</v>
+        <v>339.4040811157226</v>
       </c>
       <c r="G503" t="n">
-        <v>-0.996936363931944</v>
+        <v>-0.9969363634882211</v>
       </c>
       <c r="H503" t="n">
         <v>381.3442016302781</v>
@@ -39602,13 +39602,13 @@
         <v>350.6960168457031</v>
       </c>
       <c r="E509" t="n">
-        <v>396.4461895751953</v>
+        <v>396.4461897786458</v>
       </c>
       <c r="F509" t="n">
-        <v>391.168090057373</v>
+        <v>391.1680906677246</v>
       </c>
       <c r="G509" t="n">
-        <v>-0.03492036711780777</v>
+        <v>-0.03492025012025168</v>
       </c>
       <c r="H509" t="n">
         <v>476.8288845013619</v>
@@ -40375,10 +40375,10 @@
         <v>411.8420340983073</v>
       </c>
       <c r="F519" t="n">
-        <v>413.6338307189941</v>
+        <v>413.6338316345215</v>
       </c>
       <c r="G519" t="n">
-        <v>-1.145234141897777</v>
+        <v>-1.145234103342474</v>
       </c>
       <c r="H519" t="n">
         <v>684.5682054144123</v>
@@ -40991,13 +40991,13 @@
         <v>2411.758968098958</v>
       </c>
       <c r="F527" t="n">
-        <v>2408.79798828125</v>
+        <v>2408.797993164063</v>
       </c>
       <c r="G527" t="n">
-        <v>-1.764856161029926</v>
+        <v>-1.764856206419452</v>
       </c>
       <c r="H527" t="n">
-        <v>2908.974368726317</v>
+        <v>2908.974119515923</v>
       </c>
       <c r="I527" t="n">
         <v>1987.699951171875</v>
@@ -41006,7 +41006,7 @@
         <v>5.247273300310407</v>
       </c>
       <c r="K527" t="n">
-        <v>39.05231208060789</v>
+        <v>39.05230016806514</v>
       </c>
       <c r="L527" t="n">
         <v>19.75138121546961</v>
@@ -41296,13 +41296,13 @@
         <v>452.5751684570312</v>
       </c>
       <c r="E531" t="n">
-        <v>491.1339961751302</v>
+        <v>491.1339984130859</v>
       </c>
       <c r="F531" t="n">
-        <v>499.4604623413086</v>
+        <v>499.4604647827148</v>
       </c>
       <c r="G531" t="n">
-        <v>-2.906483229434931</v>
+        <v>-2.906483273241633</v>
       </c>
       <c r="H531" t="n">
         <v>756.7099518871578</v>
@@ -42451,25 +42451,25 @@
         <v>215.1626062011719</v>
       </c>
       <c r="E546" t="n">
-        <v>222.562045694987</v>
+        <v>222.5620462036133</v>
       </c>
       <c r="F546" t="n">
-        <v>223.5631106567383</v>
+        <v>223.5631107330322</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.330180430682171</v>
+        <v>-1.330180496683275</v>
       </c>
       <c r="H546" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I546" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J546" t="n">
-        <v>22.63828467593729</v>
+        <v>22.63829548230931</v>
       </c>
       <c r="K546" t="n">
-        <v>35.66028661556074</v>
+        <v>35.66030210323672</v>
       </c>
       <c r="L546" t="n">
         <v>46.68508287292818</v>
@@ -42839,10 +42839,10 @@
         <v>412.9404331461589</v>
       </c>
       <c r="F551" t="n">
-        <v>416.272568359375</v>
+        <v>416.2725682067871</v>
       </c>
       <c r="G551" t="n">
-        <v>-0.3018804949447507</v>
+        <v>-0.301880458620285</v>
       </c>
       <c r="H551" t="n">
         <v>472.8081629796919</v>
@@ -42916,10 +42916,10 @@
         <v>138.8841742960612</v>
       </c>
       <c r="F552" t="n">
-        <v>145.3429372406006</v>
+        <v>145.3429368591309</v>
       </c>
       <c r="G552" t="n">
-        <v>-1.822403876368461</v>
+        <v>-1.822403931660954</v>
       </c>
       <c r="H552" t="n">
         <v>184.9587904135824</v>
@@ -42993,10 +42993,10 @@
         <v>613.0833870442708</v>
       </c>
       <c r="F553" t="n">
-        <v>614.5254061889649</v>
+        <v>614.5254049682617</v>
       </c>
       <c r="G553" t="n">
-        <v>-1.470052161386193</v>
+        <v>-1.470052067841265</v>
       </c>
       <c r="H553" t="n">
         <v>834.5473868842978</v>
@@ -43378,13 +43378,13 @@
         <v>7593.6013671875</v>
       </c>
       <c r="F558" t="n">
-        <v>7733.318305664063</v>
+        <v>7733.318310546875</v>
       </c>
       <c r="G558" t="n">
-        <v>-1.346337548123022</v>
+        <v>-1.346337639461237</v>
       </c>
       <c r="H558" t="n">
-        <v>9391.699890478567</v>
+        <v>9391.700937170743</v>
       </c>
       <c r="I558" t="n">
         <v>6860</v>
@@ -43393,7 +43393,7 @@
         <v>5.342565597667637</v>
       </c>
       <c r="K558" t="n">
-        <v>29.96194410127402</v>
+        <v>29.96195858535589</v>
       </c>
       <c r="L558" t="n">
         <v>33.42541436464088</v>
@@ -44687,10 +44687,10 @@
         <v>129636.1808854167</v>
       </c>
       <c r="F575" t="n">
-        <v>133208.0965625</v>
+        <v>133208.09640625</v>
       </c>
       <c r="G575" t="n">
-        <v>-2.362632015955257</v>
+        <v>-2.362631962750816</v>
       </c>
       <c r="H575" t="n">
         <v>163308.4863287346</v>
@@ -45075,7 +45075,7 @@
         <v>20.27678067207336</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.721833375779669</v>
+        <v>-1.721833239498338</v>
       </c>
       <c r="H580" t="n">
         <v>23.83526024888653</v>
@@ -46387,7 +46387,7 @@
         <v>-2.065107220057638</v>
       </c>
       <c r="H597" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I597" t="n">
         <v>185.2067002350832</v>
@@ -46396,7 +46396,7 @@
         <v>14.68267272560047</v>
       </c>
       <c r="K597" t="n">
-        <v>45.0445826017148</v>
+        <v>45.04456754681476</v>
       </c>
       <c r="L597" t="n">
         <v>22.79005524861878</v>
@@ -46689,10 +46689,10 @@
         <v>2955.507115885417</v>
       </c>
       <c r="F601" t="n">
-        <v>3104.83740234375</v>
+        <v>3104.837409667969</v>
       </c>
       <c r="G601" t="n">
-        <v>-3.037177737482666</v>
+        <v>-3.037177693571425</v>
       </c>
       <c r="H601" t="n">
         <v>3923.39201752828</v>
@@ -47074,13 +47074,13 @@
         <v>282.6006042480469</v>
       </c>
       <c r="F606" t="n">
-        <v>291.7218782043457</v>
+        <v>291.7218783569336</v>
       </c>
       <c r="G606" t="n">
-        <v>-4.318351796303843</v>
+        <v>-4.318351842028612</v>
       </c>
       <c r="H606" t="n">
-        <v>406.5707642578344</v>
+        <v>406.5707952146441</v>
       </c>
       <c r="I606" t="n">
         <v>253.1499938964844</v>
@@ -47089,7 +47089,7 @@
         <v>4.088487597494406</v>
       </c>
       <c r="K606" t="n">
-        <v>54.29630522118953</v>
+        <v>54.29631696950439</v>
       </c>
       <c r="L606" t="n">
         <v>20.02762430939226</v>
@@ -47767,10 +47767,10 @@
         <v>153.8962880452474</v>
       </c>
       <c r="F615" t="n">
-        <v>158.5334972381592</v>
+        <v>158.5334973907471</v>
       </c>
       <c r="G615" t="n">
-        <v>-2.853053292914132</v>
+        <v>-2.853053153992635</v>
       </c>
       <c r="H615" t="n">
         <v>212.7553783484557</v>
@@ -48537,13 +48537,13 @@
         <v>121.0992464192708</v>
       </c>
       <c r="F625" t="n">
-        <v>123.692388343811</v>
+        <v>123.6923881912231</v>
       </c>
       <c r="G625" t="n">
-        <v>-2.564556660344242</v>
+        <v>-2.564556780541349</v>
       </c>
       <c r="H625" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I625" t="n">
         <v>103.0999984741211</v>
@@ -48552,7 +48552,7 @@
         <v>1.629486256100643</v>
       </c>
       <c r="K625" t="n">
-        <v>47.07400697154335</v>
+        <v>47.07402203738915</v>
       </c>
       <c r="L625" t="n">
         <v>15.74585635359116</v>
@@ -48614,13 +48614,13 @@
         <v>252.2240498860677</v>
       </c>
       <c r="F626" t="n">
-        <v>260.4150129699707</v>
+        <v>260.4150134277344</v>
       </c>
       <c r="G626" t="n">
-        <v>-3.895246220085868</v>
+        <v>-3.89524632174193</v>
       </c>
       <c r="H626" t="n">
-        <v>345.9510897219776</v>
+        <v>345.9511213302791</v>
       </c>
       <c r="I626" t="n">
         <v>212</v>
@@ -48629,7 +48629,7 @@
         <v>7.325471122309857</v>
       </c>
       <c r="K626" t="n">
-        <v>52.04636381049195</v>
+        <v>52.04637770241902</v>
       </c>
       <c r="L626" t="n">
         <v>15.60773480662983</v>
@@ -49227,16 +49227,16 @@
         <v>176.8348574829102</v>
       </c>
       <c r="E634" t="n">
-        <v>190.2435909016927</v>
+        <v>190.2435905965169</v>
       </c>
       <c r="F634" t="n">
-        <v>192.0990498352051</v>
+        <v>192.0990495300293</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.694384544765238</v>
+        <v>-2.694384398511995</v>
       </c>
       <c r="H634" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I634" t="n">
         <v>155.8000030517578</v>
@@ -49245,7 +49245,7 @@
         <v>3.395374314835831</v>
       </c>
       <c r="K634" t="n">
-        <v>48.50003676144992</v>
+        <v>48.50001759024396</v>
       </c>
       <c r="L634" t="n">
         <v>14.08839779005525</v>
@@ -49621,7 +49621,7 @@
         <v>-4.133323136753441</v>
       </c>
       <c r="H639" t="n">
-        <v>725.6811828531856</v>
+        <v>725.6811213920008</v>
       </c>
       <c r="I639" t="n">
         <v>446.0256812201048</v>
@@ -49630,7 +49630,7 @@
         <v>4.624019096829057</v>
       </c>
       <c r="K639" t="n">
-        <v>55.50866652623623</v>
+        <v>55.50865335551178</v>
       </c>
       <c r="L639" t="n">
         <v>13.25966850828729</v>
@@ -50613,13 +50613,13 @@
         <v>268.2837411499024</v>
       </c>
       <c r="E652" t="n">
-        <v>291.9248217773438</v>
+        <v>291.9248219807943</v>
       </c>
       <c r="F652" t="n">
-        <v>302.4900537109375</v>
+        <v>302.4900541687012</v>
       </c>
       <c r="G652" t="n">
-        <v>-2.672243051328471</v>
+        <v>-2.672242999608587</v>
       </c>
       <c r="H652" t="n">
         <v>387.9339558462079</v>
@@ -51155,10 +51155,10 @@
         <v>379.9771179199219</v>
       </c>
       <c r="F659" t="n">
-        <v>389.2492022705078</v>
+        <v>389.2492016601562</v>
       </c>
       <c r="G659" t="n">
-        <v>-2.611727745583481</v>
+        <v>-2.611727786751439</v>
       </c>
       <c r="H659" t="n">
         <v>541.0236304500187</v>
@@ -51389,10 +51389,10 @@
         <v>93.76012783050537</v>
       </c>
       <c r="G662" t="n">
-        <v>-3.776733847234259</v>
+        <v>-3.776733696552015</v>
       </c>
       <c r="H662" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I662" t="n">
         <v>73.90000152587891</v>
@@ -51401,7 +51401,7 @@
         <v>2.178620537359199</v>
       </c>
       <c r="K662" t="n">
-        <v>65.31227421356375</v>
+        <v>65.31228462855059</v>
       </c>
       <c r="L662" t="n">
         <v>9.25414364640884</v>
@@ -51925,13 +51925,13 @@
         <v>502.6339683024088</v>
       </c>
       <c r="F669" t="n">
-        <v>522.9714292907715</v>
+        <v>522.9714283752442</v>
       </c>
       <c r="G669" t="n">
-        <v>-4.575324586736373</v>
+        <v>-4.575324541243009</v>
       </c>
       <c r="H669" t="n">
-        <v>756.8456624851057</v>
+        <v>756.8455981427298</v>
       </c>
       <c r="I669" t="n">
         <v>406.1171468902937</v>
@@ -51940,7 +51940,7 @@
         <v>10.52229868658205</v>
       </c>
       <c r="K669" t="n">
-        <v>68.61883751663775</v>
+        <v>68.61882318169847</v>
       </c>
       <c r="L669" t="n">
         <v>8.287292817679557</v>
@@ -53080,10 +53080,10 @@
         <v>128.6862941996256</v>
       </c>
       <c r="F684" t="n">
-        <v>135.5109527206421</v>
+        <v>135.5109524154663</v>
       </c>
       <c r="G684" t="n">
-        <v>-3.698135221079002</v>
+        <v>-3.698135176885564</v>
       </c>
       <c r="H684" t="n">
         <v>183.7853835258596</v>
@@ -53234,10 +53234,10 @@
         <v>270.028515218099</v>
       </c>
       <c r="F686" t="n">
-        <v>282.0782901000977</v>
+        <v>282.0782897949219</v>
       </c>
       <c r="G686" t="n">
-        <v>-4.468324003662283</v>
+        <v>-4.468323860176615</v>
       </c>
       <c r="H686" t="n">
         <v>385.6351549871131</v>
@@ -53311,10 +53311,10 @@
         <v>69.06859842936198</v>
       </c>
       <c r="F687" t="n">
-        <v>70.2572854232788</v>
+        <v>70.25728546142578</v>
       </c>
       <c r="G687" t="n">
-        <v>-2.124545174847448</v>
+        <v>-2.124545069691364</v>
       </c>
       <c r="H687" t="n">
         <v>89.48512107833052</v>
@@ -56086,7 +56086,7 @@
         <v>439.4220953369141</v>
       </c>
       <c r="G723" t="n">
-        <v>-6.328281879950692</v>
+        <v>-6.328281788544343</v>
       </c>
       <c r="H723" t="n">
         <v>779.4908805849697</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2177,16 +2177,16 @@
         <v>246.25</v>
       </c>
       <c r="D23" t="n">
-        <v>202.3687442016601</v>
+        <v>202.3687438964844</v>
       </c>
       <c r="E23" t="n">
-        <v>162.192017364502</v>
+        <v>162.1920184326172</v>
       </c>
       <c r="F23" t="n">
-        <v>158.5442418289184</v>
+        <v>158.5442430114746</v>
       </c>
       <c r="G23" t="n">
-        <v>4.975186456358438</v>
+        <v>4.975186364374129</v>
       </c>
       <c r="H23" t="n">
         <v>248.3999938964844</v>
@@ -2414,10 +2414,10 @@
         <v>11090.68897135417</v>
       </c>
       <c r="F26" t="n">
-        <v>10638.51546142578</v>
+        <v>10638.51545654297</v>
       </c>
       <c r="G26" t="n">
-        <v>4.387903381899405</v>
+        <v>4.387903484029199</v>
       </c>
       <c r="H26" t="n">
         <v>14498</v>
@@ -2719,13 +2719,13 @@
         <v>1431.348356933594</v>
       </c>
       <c r="E30" t="n">
-        <v>1217.522706298828</v>
+        <v>1217.522702636719</v>
       </c>
       <c r="F30" t="n">
-        <v>1104.636871948242</v>
+        <v>1104.636867675781</v>
       </c>
       <c r="G30" t="n">
-        <v>8.898175000313646</v>
+        <v>8.898175234364558</v>
       </c>
       <c r="H30" t="n">
         <v>1681</v>
@@ -4881,7 +4881,7 @@
         <v>229.7379676055908</v>
       </c>
       <c r="G58" t="n">
-        <v>5.054038323876475</v>
+        <v>5.054038397177973</v>
       </c>
       <c r="H58" t="n">
         <v>321.3999938964844</v>
@@ -5032,10 +5032,10 @@
         <v>159.833235168457</v>
       </c>
       <c r="F60" t="n">
-        <v>156.3067570114136</v>
+        <v>156.3067573165894</v>
       </c>
       <c r="G60" t="n">
-        <v>2.838844411314434</v>
+        <v>2.838844560477627</v>
       </c>
       <c r="H60" t="n">
         <v>233.3500061035156</v>
@@ -6341,10 +6341,10 @@
         <v>4479.306918945313</v>
       </c>
       <c r="F77" t="n">
-        <v>4419.151257324219</v>
+        <v>4419.151268310547</v>
       </c>
       <c r="G77" t="n">
-        <v>1.071816720169561</v>
+        <v>1.071816322419727</v>
       </c>
       <c r="H77" t="n">
         <v>5149.89990234375</v>
@@ -6954,13 +6954,13 @@
         <v>1418.404001464844</v>
       </c>
       <c r="E85" t="n">
-        <v>1170.398424886068</v>
+        <v>1170.398425292969</v>
       </c>
       <c r="F85" t="n">
         <v>1085.251582641602</v>
       </c>
       <c r="G85" t="n">
-        <v>6.060298225259264</v>
+        <v>6.060298256891161</v>
       </c>
       <c r="H85" t="n">
         <v>1677.5</v>
@@ -7265,10 +7265,10 @@
         <v>670.5830324300131</v>
       </c>
       <c r="F89" t="n">
-        <v>626.9189418029786</v>
+        <v>626.9189421081543</v>
       </c>
       <c r="G89" t="n">
-        <v>5.838987186244449</v>
+        <v>5.83898731955943</v>
       </c>
       <c r="H89" t="n">
         <v>844</v>
@@ -7724,13 +7724,13 @@
         <v>343.9190014648437</v>
       </c>
       <c r="E95" t="n">
-        <v>267.061186319987</v>
+        <v>267.0611861165365</v>
       </c>
       <c r="F95" t="n">
-        <v>249.9069130706787</v>
+        <v>249.9069129943848</v>
       </c>
       <c r="G95" t="n">
-        <v>6.591772869164525</v>
+        <v>6.591772732564016</v>
       </c>
       <c r="H95" t="n">
         <v>388.75</v>
@@ -8340,13 +8340,13 @@
         <v>163.2757998657227</v>
       </c>
       <c r="E103" t="n">
-        <v>143.1894893391927</v>
+        <v>143.1894893900553</v>
       </c>
       <c r="F103" t="n">
-        <v>137.6178078842163</v>
+        <v>137.6178078079224</v>
       </c>
       <c r="G103" t="n">
-        <v>3.550083378886937</v>
+        <v>3.550083321479791</v>
       </c>
       <c r="H103" t="n">
         <v>173.2700042724609</v>
@@ -9199,10 +9199,10 @@
         <v>1766.733060850261</v>
       </c>
       <c r="I114" t="n">
-        <v>971.816928508411</v>
+        <v>971.816868681665</v>
       </c>
       <c r="J114" t="n">
-        <v>55.11152154219921</v>
+        <v>55.11153109113573</v>
       </c>
       <c r="K114" t="n">
         <v>17.20399576993525</v>
@@ -10040,7 +10040,7 @@
         <v>75.44904144287109</v>
       </c>
       <c r="G125" t="n">
-        <v>3.955123100460045</v>
+        <v>3.955123155098472</v>
       </c>
       <c r="H125" t="n">
         <v>94.5</v>
@@ -10345,10 +10345,10 @@
         <v>1682.017312825521</v>
       </c>
       <c r="F129" t="n">
-        <v>1613.566029663086</v>
+        <v>1613.566032714844</v>
       </c>
       <c r="G129" t="n">
-        <v>3.351370824745503</v>
+        <v>3.351370454557379</v>
       </c>
       <c r="H129" t="n">
         <v>2038.599975585938</v>
@@ -12116,10 +12116,10 @@
         <v>1031.978623453776</v>
       </c>
       <c r="F152" t="n">
-        <v>997.1892315673828</v>
+        <v>997.1892303466797</v>
       </c>
       <c r="G152" t="n">
-        <v>1.184580257818624</v>
+        <v>1.184580290618831</v>
       </c>
       <c r="H152" t="n">
         <v>1331.075409591023</v>
@@ -12421,13 +12421,13 @@
         <v>333.5491583251953</v>
       </c>
       <c r="E156" t="n">
-        <v>314.5854669189453</v>
+        <v>314.5854672241211</v>
       </c>
       <c r="F156" t="n">
-        <v>310.2953784179688</v>
+        <v>310.2953793334961</v>
       </c>
       <c r="G156" t="n">
-        <v>1.249732731910269</v>
+        <v>1.24973252652949</v>
       </c>
       <c r="H156" t="n">
         <v>380.4567148307952</v>
@@ -12960,13 +12960,13 @@
         <v>426.6450189208985</v>
       </c>
       <c r="E163" t="n">
-        <v>400.186890258789</v>
+        <v>400.1868904622396</v>
       </c>
       <c r="F163" t="n">
-        <v>387.8213980102539</v>
+        <v>387.8213981628418</v>
       </c>
       <c r="G163" t="n">
-        <v>3.472410324763153</v>
+        <v>3.472410281224736</v>
       </c>
       <c r="H163" t="n">
         <v>480.9477017568404</v>
@@ -13117,10 +13117,10 @@
         <v>626.8444034830729</v>
       </c>
       <c r="F165" t="n">
-        <v>612.2530038452148</v>
+        <v>612.2530047607422</v>
       </c>
       <c r="G165" t="n">
-        <v>1.393173946850701</v>
+        <v>1.393174047224877</v>
       </c>
       <c r="H165" t="n">
         <v>769</v>
@@ -14811,10 +14811,10 @@
         <v>4611.431552734375</v>
       </c>
       <c r="F187" t="n">
-        <v>4470.228142089843</v>
+        <v>4470.228138427734</v>
       </c>
       <c r="G187" t="n">
-        <v>2.640331369136595</v>
+        <v>2.640331342588254</v>
       </c>
       <c r="H187" t="n">
         <v>5250</v>
@@ -14965,10 +14965,10 @@
         <v>530.0145731608073</v>
       </c>
       <c r="F189" t="n">
-        <v>538.658667602539</v>
+        <v>538.6586682128906</v>
       </c>
       <c r="G189" t="n">
-        <v>0.3896022205173821</v>
+        <v>0.3896023342683463</v>
       </c>
       <c r="H189" t="n">
         <v>673.9500122070312</v>
@@ -15270,13 +15270,13 @@
         <v>2612.066586914063</v>
       </c>
       <c r="E193" t="n">
-        <v>2261.393789876302</v>
+        <v>2261.393790690104</v>
       </c>
       <c r="F193" t="n">
-        <v>2137.795877685547</v>
+        <v>2137.795878295899</v>
       </c>
       <c r="G193" t="n">
-        <v>3.685386048578776</v>
+        <v>3.685386108875166</v>
       </c>
       <c r="H193" t="n">
         <v>2990</v>
@@ -16117,13 +16117,13 @@
         <v>191.3807949829101</v>
       </c>
       <c r="E204" t="n">
-        <v>181.8001528930664</v>
+        <v>181.8001529947917</v>
       </c>
       <c r="F204" t="n">
-        <v>180.3593455505371</v>
+        <v>180.3593453216553</v>
       </c>
       <c r="G204" t="n">
-        <v>1.228297049285176</v>
+        <v>1.2282971375563</v>
       </c>
       <c r="H204" t="n">
         <v>203.3999938964844</v>
@@ -17426,13 +17426,13 @@
         <v>1969.641245117188</v>
       </c>
       <c r="E221" t="n">
-        <v>1805.400537923177</v>
+        <v>1805.40054280599</v>
       </c>
       <c r="F221" t="n">
-        <v>1788.036292114258</v>
+        <v>1788.036299438477</v>
       </c>
       <c r="G221" t="n">
-        <v>1.626275219461504</v>
+        <v>1.626275177436964</v>
       </c>
       <c r="H221" t="n">
         <v>2256.187656125729</v>
@@ -17583,10 +17583,10 @@
         <v>166.1009068806966</v>
       </c>
       <c r="F223" t="n">
-        <v>165.0537364959717</v>
+        <v>165.0537364196777</v>
       </c>
       <c r="G223" t="n">
-        <v>0.2608909872427789</v>
+        <v>0.2608908944332855</v>
       </c>
       <c r="H223" t="n">
         <v>181.8519567776652</v>
@@ -19046,13 +19046,13 @@
         <v>5181.613190104166</v>
       </c>
       <c r="F242" t="n">
-        <v>5329.781804199219</v>
+        <v>5329.781801757813</v>
       </c>
       <c r="G242" t="n">
-        <v>-1.626053175487563</v>
+        <v>-1.626053131890992</v>
       </c>
       <c r="H242" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I242" t="n">
         <v>4229.809203861739</v>
@@ -19061,7 +19061,7 @@
         <v>35.72716222657446</v>
       </c>
       <c r="K242" t="n">
-        <v>14.137854222998</v>
+        <v>14.13786287233574</v>
       </c>
       <c r="L242" t="n">
         <v>65.88397790055248</v>
@@ -19967,22 +19967,22 @@
         <v>1274.807282714844</v>
       </c>
       <c r="E254" t="n">
-        <v>1233.511082356771</v>
+        <v>1233.511084391276</v>
       </c>
       <c r="F254" t="n">
-        <v>1302.538596801758</v>
+        <v>1302.538600769043</v>
       </c>
       <c r="G254" t="n">
-        <v>-2.765605056611709</v>
+        <v>-2.765604915513342</v>
       </c>
       <c r="H254" t="n">
         <v>1713.752567939176</v>
       </c>
       <c r="I254" t="n">
-        <v>1010.594387550952</v>
+        <v>1010.594326763664</v>
       </c>
       <c r="J254" t="n">
-        <v>36.55330140356863</v>
+        <v>36.5533096172551</v>
       </c>
       <c r="K254" t="n">
         <v>24.18496869124462</v>
@@ -20663,19 +20663,19 @@
         <v>1959.745737304688</v>
       </c>
       <c r="F263" t="n">
-        <v>1867.353186645508</v>
+        <v>1867.353186035156</v>
       </c>
       <c r="G263" t="n">
-        <v>2.968043630990991</v>
+        <v>2.968043805261966</v>
       </c>
       <c r="H263" t="n">
         <v>2295</v>
       </c>
       <c r="I263" t="n">
-        <v>1174.48971989473</v>
+        <v>1174.489600842614</v>
       </c>
       <c r="J263" t="n">
-        <v>56.23806397934861</v>
+        <v>56.23807981641696</v>
       </c>
       <c r="K263" t="n">
         <v>25.06811989100817</v>
@@ -20740,10 +20740,10 @@
         <v>285.67044921875</v>
       </c>
       <c r="F264" t="n">
-        <v>272.4303128051758</v>
+        <v>272.4303134155273</v>
       </c>
       <c r="G264" t="n">
-        <v>2.443987207434328</v>
+        <v>2.443987260606084</v>
       </c>
       <c r="H264" t="n">
         <v>367.499792159746</v>
@@ -21747,7 +21747,7 @@
         <v>-1.054467626912103</v>
       </c>
       <c r="H277" t="n">
-        <v>1409.944189808421</v>
+        <v>1409.944064008135</v>
       </c>
       <c r="I277" t="n">
         <v>905.5050975494345</v>
@@ -21756,7 +21756,7 @@
         <v>39.71207660891953</v>
       </c>
       <c r="K277" t="n">
-        <v>11.44923065510284</v>
+        <v>11.44922071120211</v>
       </c>
       <c r="L277" t="n">
         <v>62.98342541436463</v>
@@ -24362,7 +24362,7 @@
         <v>370.8467485046387</v>
       </c>
       <c r="G311" t="n">
-        <v>2.180790221241447</v>
+        <v>2.180790178281478</v>
       </c>
       <c r="H311" t="n">
         <v>443.3731066930094</v>
@@ -24436,10 +24436,10 @@
         <v>428.5723400878906</v>
       </c>
       <c r="F312" t="n">
-        <v>424.1940914916992</v>
+        <v>424.1940910339355</v>
       </c>
       <c r="G312" t="n">
-        <v>1.321200274431034</v>
+        <v>1.321200202019579</v>
       </c>
       <c r="H312" t="n">
         <v>478.7148709533388</v>
@@ -24744,10 +24744,10 @@
         <v>462.7146718343099</v>
       </c>
       <c r="F316" t="n">
-        <v>460.324308013916</v>
+        <v>460.3243093872071</v>
       </c>
       <c r="G316" t="n">
-        <v>1.390269343800044</v>
+        <v>1.390269237366759</v>
       </c>
       <c r="H316" t="n">
         <v>529.9163379046904</v>
@@ -25052,19 +25052,19 @@
         <v>1838.69591796875</v>
       </c>
       <c r="F320" t="n">
-        <v>1803.476480712891</v>
+        <v>1803.476481323242</v>
       </c>
       <c r="G320" t="n">
-        <v>0.2383577867182796</v>
+        <v>0.238357854646587</v>
       </c>
       <c r="H320" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I320" t="n">
-        <v>1569.365993709292</v>
+        <v>1569.36587206911</v>
       </c>
       <c r="J320" t="n">
-        <v>12.07073785708164</v>
+        <v>12.07074654358695</v>
       </c>
       <c r="K320" t="n">
         <v>16.3804848526071</v>
@@ -25363,7 +25363,7 @@
         <v>8054.078349609375</v>
       </c>
       <c r="G324" t="n">
-        <v>1.697051220616452</v>
+        <v>1.697051283316942</v>
       </c>
       <c r="H324" t="n">
         <v>9070.5</v>
@@ -25437,10 +25437,10 @@
         <v>339.6221103922526</v>
       </c>
       <c r="F325" t="n">
-        <v>335.6499215698242</v>
+        <v>335.6499212646484</v>
       </c>
       <c r="G325" t="n">
-        <v>0.6550520813418226</v>
+        <v>0.6550519898253837</v>
       </c>
       <c r="H325" t="n">
         <v>428.7550602808859</v>
@@ -26210,7 +26210,7 @@
         <v>741.7763342285157</v>
       </c>
       <c r="G335" t="n">
-        <v>-0.560679762144678</v>
+        <v>-0.5606798841881755</v>
       </c>
       <c r="H335" t="n">
         <v>879.2203373423794</v>
@@ -26669,10 +26669,10 @@
         <v>200.6220212809245</v>
       </c>
       <c r="F341" t="n">
-        <v>205.6012381744385</v>
+        <v>205.6012377929688</v>
       </c>
       <c r="G341" t="n">
-        <v>-2.111945881145161</v>
+        <v>-2.111946098322193</v>
       </c>
       <c r="H341" t="n">
         <v>278.3389924341271</v>
@@ -26897,16 +26897,16 @@
         <v>2230.523427734375</v>
       </c>
       <c r="E344" t="n">
-        <v>2263.199816080729</v>
+        <v>2263.199809570312</v>
       </c>
       <c r="F344" t="n">
-        <v>2421.274552001953</v>
+        <v>2421.274547119141</v>
       </c>
       <c r="G344" t="n">
-        <v>-4.105215207619583</v>
+        <v>-4.105215401003781</v>
       </c>
       <c r="H344" t="n">
-        <v>3269.779000999862</v>
+        <v>3269.779254579709</v>
       </c>
       <c r="I344" t="n">
         <v>1955.624263494112</v>
@@ -26915,7 +26915,7 @@
         <v>26.04670774516706</v>
       </c>
       <c r="K344" t="n">
-        <v>32.64823533467997</v>
+        <v>32.64824562189488</v>
       </c>
       <c r="L344" t="n">
         <v>42.12707182320442</v>
@@ -29438,22 +29438,22 @@
         <v>209.9827197265625</v>
       </c>
       <c r="E377" t="n">
-        <v>207.4728631591797</v>
+        <v>207.4728628540039</v>
       </c>
       <c r="F377" t="n">
-        <v>210.5249073028564</v>
+        <v>210.5249069213867</v>
       </c>
       <c r="G377" t="n">
-        <v>-1.111951390377364</v>
+        <v>-1.111951250616161</v>
       </c>
       <c r="H377" t="n">
         <v>252.6160882566492</v>
       </c>
       <c r="I377" t="n">
-        <v>171.6534204603822</v>
+        <v>171.6534052563282</v>
       </c>
       <c r="J377" t="n">
-        <v>22.21719364721459</v>
+        <v>22.21720447249831</v>
       </c>
       <c r="K377" t="n">
         <v>20.41379300303701</v>
@@ -30051,19 +30051,19 @@
         <v>149.9299926757812</v>
       </c>
       <c r="D385" t="n">
-        <v>152.3344345092773</v>
+        <v>152.3344348144531</v>
       </c>
       <c r="E385" t="n">
-        <v>154.532588297526</v>
+        <v>154.5325894165039</v>
       </c>
       <c r="F385" t="n">
-        <v>151.1833409118652</v>
+        <v>151.1833417510986</v>
       </c>
       <c r="G385" t="n">
-        <v>1.318806429076691</v>
+        <v>1.318806680681073</v>
       </c>
       <c r="H385" t="n">
-        <v>196.4205869556906</v>
+        <v>196.4205715539644</v>
       </c>
       <c r="I385" t="n">
         <v>125.7825892411346</v>
@@ -30072,7 +30072,7 @@
         <v>19.19773124430937</v>
       </c>
       <c r="K385" t="n">
-        <v>31.00820152805834</v>
+        <v>31.00819125544647</v>
       </c>
       <c r="L385" t="n">
         <v>66.02209944751381</v>
@@ -31058,10 +31058,10 @@
         <v>1142.182380777995</v>
       </c>
       <c r="F398" t="n">
-        <v>1157.517627258301</v>
+        <v>1157.517626037598</v>
       </c>
       <c r="G398" t="n">
-        <v>-1.035510250390514</v>
+        <v>-1.035510044899335</v>
       </c>
       <c r="H398" t="n">
         <v>1351.914027099318</v>
@@ -31286,13 +31286,13 @@
         <v>727.5302124023438</v>
       </c>
       <c r="E401" t="n">
-        <v>739.9110229492187</v>
+        <v>739.9110241699219</v>
       </c>
       <c r="F401" t="n">
-        <v>732.0420297241211</v>
+        <v>732.0420318603516</v>
       </c>
       <c r="G401" t="n">
-        <v>-0.8831947836080101</v>
+        <v>-0.8831945353224846</v>
       </c>
       <c r="H401" t="n">
         <v>837.8765073351432</v>
@@ -31366,10 +31366,10 @@
         <v>37066.92645833334</v>
       </c>
       <c r="F402" t="n">
-        <v>36159.32729492187</v>
+        <v>36159.32717773438</v>
       </c>
       <c r="G402" t="n">
-        <v>-0.01803540151499305</v>
+        <v>-0.01803561755316929</v>
       </c>
       <c r="H402" t="n">
         <v>43614.20556091995</v>
@@ -31751,10 +31751,10 @@
         <v>2156.845852864583</v>
       </c>
       <c r="F407" t="n">
-        <v>2093.151411743164</v>
+        <v>2093.151408691406</v>
       </c>
       <c r="G407" t="n">
-        <v>0.2455427311808256</v>
+        <v>0.245542819448219</v>
       </c>
       <c r="H407" t="n">
         <v>2625.96691593483</v>
@@ -32213,10 +32213,10 @@
         <v>1074.885148111979</v>
       </c>
       <c r="F413" t="n">
-        <v>1076.823356628418</v>
+        <v>1076.823357543945</v>
       </c>
       <c r="G413" t="n">
-        <v>-0.6957715334936276</v>
+        <v>-0.6957714211166754</v>
       </c>
       <c r="H413" t="n">
         <v>1294.204229651688</v>
@@ -32290,10 +32290,10 @@
         <v>292.5334693400065</v>
       </c>
       <c r="F414" t="n">
-        <v>283.4000550079346</v>
+        <v>283.4000548553467</v>
       </c>
       <c r="G414" t="n">
-        <v>0.7115932849222517</v>
+        <v>0.7115933399189922</v>
       </c>
       <c r="H414" t="n">
         <v>387.4363949219129</v>
@@ -32444,10 +32444,10 @@
         <v>354.3472393798828</v>
       </c>
       <c r="F416" t="n">
-        <v>353.5069058227539</v>
+        <v>353.5069059753418</v>
       </c>
       <c r="G416" t="n">
-        <v>0.08884542766121051</v>
+        <v>0.08884551410439645</v>
       </c>
       <c r="H416" t="n">
         <v>409.9712889887167</v>
@@ -32829,10 +32829,10 @@
         <v>777.6781604003907</v>
       </c>
       <c r="F421" t="n">
-        <v>784.9243887329102</v>
+        <v>784.9243908691407</v>
       </c>
       <c r="G421" t="n">
-        <v>-1.203543307297417</v>
+        <v>-1.203543304061305</v>
       </c>
       <c r="H421" t="n">
         <v>1089.356915377717</v>
@@ -33442,13 +33442,13 @@
         <v>486.5100677490234</v>
       </c>
       <c r="E429" t="n">
-        <v>482.0436850992838</v>
+        <v>482.0436838785807</v>
       </c>
       <c r="F429" t="n">
-        <v>487.2318072509765</v>
+        <v>487.2318060302734</v>
       </c>
       <c r="G429" t="n">
-        <v>-0.9851636177295453</v>
+        <v>-0.9851636201734459</v>
       </c>
       <c r="H429" t="n">
         <v>547.7380341214969</v>
@@ -33756,7 +33756,7 @@
         <v>77.11687595367431</v>
       </c>
       <c r="G433" t="n">
-        <v>-0.1876492659144913</v>
+        <v>-0.1876490195096725</v>
       </c>
       <c r="H433" t="n">
         <v>86.59303970157107</v>
@@ -33830,13 +33830,13 @@
         <v>182.973776957194</v>
       </c>
       <c r="F434" t="n">
-        <v>194.6355020141602</v>
+        <v>194.6355015563965</v>
       </c>
       <c r="G434" t="n">
-        <v>-4.551431400731976</v>
+        <v>-4.551431410949281</v>
       </c>
       <c r="H434" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I434" t="n">
         <v>156.7899932861328</v>
@@ -33845,7 +33845,7 @@
         <v>17.60954256816945</v>
       </c>
       <c r="K434" t="n">
-        <v>42.74432623572708</v>
+        <v>42.74430965996543</v>
       </c>
       <c r="L434" t="n">
         <v>28.7292817679558</v>
@@ -34677,10 +34677,10 @@
         <v>487.997592976888</v>
       </c>
       <c r="F445" t="n">
-        <v>523.2713038635254</v>
+        <v>523.2713041687011</v>
       </c>
       <c r="G445" t="n">
-        <v>-5.33008403141414</v>
+        <v>-5.330084028471305</v>
       </c>
       <c r="H445" t="n">
         <v>799.7128098861871</v>
@@ -35752,22 +35752,22 @@
         <v>427.2370001220703</v>
       </c>
       <c r="E459" t="n">
-        <v>460.307084757487</v>
+        <v>460.3070849609375</v>
       </c>
       <c r="F459" t="n">
-        <v>462.3656211853028</v>
+        <v>462.3656207275391</v>
       </c>
       <c r="G459" t="n">
-        <v>-0.9908917932788253</v>
+        <v>-0.9908920530564247</v>
       </c>
       <c r="H459" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I459" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J459" t="n">
-        <v>13.36706130241054</v>
+        <v>13.36707946655855</v>
       </c>
       <c r="K459" t="n">
         <v>28.96265934157676</v>
@@ -36294,10 +36294,10 @@
         <v>1399.738943684896</v>
       </c>
       <c r="F466" t="n">
-        <v>1398.193536376953</v>
+        <v>1398.193536987305</v>
       </c>
       <c r="G466" t="n">
-        <v>-0.2611647225762792</v>
+        <v>-0.2611648527380162</v>
       </c>
       <c r="H466" t="n">
         <v>1817.803954384172</v>
@@ -36448,10 +36448,10 @@
         <v>2200.055706380208</v>
       </c>
       <c r="F468" t="n">
-        <v>2258.561396484375</v>
+        <v>2258.561395263672</v>
       </c>
       <c r="G468" t="n">
-        <v>-1.115992191453763</v>
+        <v>-1.115992192050208</v>
       </c>
       <c r="H468" t="n">
         <v>2765.379504159864</v>
@@ -37757,10 +37757,10 @@
         <v>284.0430090332031</v>
       </c>
       <c r="F485" t="n">
-        <v>281.7401105499268</v>
+        <v>281.7401094055176</v>
       </c>
       <c r="G485" t="n">
-        <v>-0.1596924643906372</v>
+        <v>-0.1596924110520148</v>
       </c>
       <c r="H485" t="n">
         <v>323.4425459044702</v>
@@ -38145,7 +38145,7 @@
         <v>1075.538448181152</v>
       </c>
       <c r="G490" t="n">
-        <v>-2.433800640856543</v>
+        <v>-2.43380069487632</v>
       </c>
       <c r="H490" t="n">
         <v>1395.129939548488</v>
@@ -38524,13 +38524,13 @@
         <v>13019.0030859375</v>
       </c>
       <c r="E495" t="n">
-        <v>12603.92580078125</v>
+        <v>12603.9258203125</v>
       </c>
       <c r="F495" t="n">
-        <v>12794.28542480469</v>
+        <v>12794.28547363281</v>
       </c>
       <c r="G495" t="n">
-        <v>-1.117522601216514</v>
+        <v>-1.117522746262456</v>
       </c>
       <c r="H495" t="n">
         <v>17441.42261795032</v>
@@ -38838,7 +38838,7 @@
         <v>33.49055790901184</v>
       </c>
       <c r="G499" t="n">
-        <v>-1.823120635516751</v>
+        <v>-1.823120525728428</v>
       </c>
       <c r="H499" t="n">
         <v>40.26070662850351</v>
@@ -38989,10 +38989,10 @@
         <v>949.4929280598958</v>
       </c>
       <c r="F501" t="n">
-        <v>933.0681060791015</v>
+        <v>933.0681048583984</v>
       </c>
       <c r="G501" t="n">
-        <v>-1.109264275024235</v>
+        <v>-1.109264244474228</v>
       </c>
       <c r="H501" t="n">
         <v>1224.741935222577</v>
@@ -39140,13 +39140,13 @@
         <v>317.6682745361328</v>
       </c>
       <c r="E503" t="n">
-        <v>336.0394691975911</v>
+        <v>336.0394689941406</v>
       </c>
       <c r="F503" t="n">
-        <v>339.4040811157226</v>
+        <v>339.4040802001953</v>
       </c>
       <c r="G503" t="n">
-        <v>-0.9969363634882211</v>
+        <v>-0.9969362780192781</v>
       </c>
       <c r="H503" t="n">
         <v>381.3442016302781</v>
@@ -39602,13 +39602,13 @@
         <v>350.6960168457031</v>
       </c>
       <c r="E509" t="n">
-        <v>396.4461897786458</v>
+        <v>396.4461895751953</v>
       </c>
       <c r="F509" t="n">
-        <v>391.1680906677246</v>
+        <v>391.168090057373</v>
       </c>
       <c r="G509" t="n">
-        <v>-0.03492025012025168</v>
+        <v>-0.03492032813676715</v>
       </c>
       <c r="H509" t="n">
         <v>476.8288845013619</v>
@@ -40375,10 +40375,10 @@
         <v>411.8420340983073</v>
       </c>
       <c r="F519" t="n">
-        <v>413.6338316345215</v>
+        <v>413.6338307189941</v>
       </c>
       <c r="G519" t="n">
-        <v>-1.145234103342474</v>
+        <v>-1.145234141897777</v>
       </c>
       <c r="H519" t="n">
         <v>684.5682054144123</v>
@@ -40529,10 +40529,10 @@
         <v>2544.812492675781</v>
       </c>
       <c r="F521" t="n">
-        <v>2518.95313293457</v>
+        <v>2518.953129272461</v>
       </c>
       <c r="G521" t="n">
-        <v>-1.118922469056371</v>
+        <v>-1.118922518047205</v>
       </c>
       <c r="H521" t="n">
         <v>3329.438873827357</v>
@@ -40997,7 +40997,7 @@
         <v>-1.764856206419452</v>
       </c>
       <c r="H527" t="n">
-        <v>2908.974119515923</v>
+        <v>2908.974368726317</v>
       </c>
       <c r="I527" t="n">
         <v>1987.699951171875</v>
@@ -41006,7 +41006,7 @@
         <v>5.247273300310407</v>
       </c>
       <c r="K527" t="n">
-        <v>39.05230016806514</v>
+        <v>39.05231208060789</v>
       </c>
       <c r="L527" t="n">
         <v>19.75138121546961</v>
@@ -41912,13 +41912,13 @@
         <v>282.7053494262695</v>
       </c>
       <c r="E539" t="n">
-        <v>272.2048740641276</v>
+        <v>272.204873453776</v>
       </c>
       <c r="F539" t="n">
-        <v>280.808969116211</v>
+        <v>280.808967666626</v>
       </c>
       <c r="G539" t="n">
-        <v>-3.219069951140707</v>
+        <v>-3.219069814533426</v>
       </c>
       <c r="H539" t="n">
         <v>390.5481555478003</v>
@@ -41992,13 +41992,13 @@
         <v>406.339267985026</v>
       </c>
       <c r="F540" t="n">
-        <v>435.0193467712402</v>
+        <v>435.0193458557129</v>
       </c>
       <c r="G540" t="n">
-        <v>-4.150590878010307</v>
+        <v>-4.150591015282179</v>
       </c>
       <c r="H540" t="n">
-        <v>605.9581737112406</v>
+        <v>605.9581114957105</v>
       </c>
       <c r="I540" t="n">
         <v>326.057353105007</v>
@@ -42007,7 +42007,7 @@
         <v>12.64888961871673</v>
       </c>
       <c r="K540" t="n">
-        <v>64.97636641708611</v>
+        <v>64.97634947847129</v>
       </c>
       <c r="L540" t="n">
         <v>12.98342541436464</v>
@@ -42451,22 +42451,22 @@
         <v>215.1626062011719</v>
       </c>
       <c r="E546" t="n">
-        <v>222.5620462036133</v>
+        <v>222.562045694987</v>
       </c>
       <c r="F546" t="n">
-        <v>223.5631107330322</v>
+        <v>223.5631105804443</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.330180496683275</v>
+        <v>-1.330180530803604</v>
       </c>
       <c r="H546" t="n">
         <v>286.0804516993438</v>
       </c>
       <c r="I546" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J546" t="n">
-        <v>22.63829548230931</v>
+        <v>22.63828467593729</v>
       </c>
       <c r="K546" t="n">
         <v>35.66030210323672</v>
@@ -42839,10 +42839,10 @@
         <v>412.9404331461589</v>
       </c>
       <c r="F551" t="n">
-        <v>416.2725682067871</v>
+        <v>416.272568359375</v>
       </c>
       <c r="G551" t="n">
-        <v>-0.301880458620285</v>
+        <v>-0.3018804949447507</v>
       </c>
       <c r="H551" t="n">
         <v>472.8081629796919</v>
@@ -42919,7 +42919,7 @@
         <v>145.3429368591309</v>
       </c>
       <c r="G552" t="n">
-        <v>-1.822403931660954</v>
+        <v>-1.822403881064383</v>
       </c>
       <c r="H552" t="n">
         <v>184.9587904135824</v>
@@ -42993,13 +42993,13 @@
         <v>613.0833870442708</v>
       </c>
       <c r="F553" t="n">
-        <v>614.5254049682617</v>
+        <v>614.5254061889649</v>
       </c>
       <c r="G553" t="n">
-        <v>-1.470052067841265</v>
+        <v>-1.470052161386193</v>
       </c>
       <c r="H553" t="n">
-        <v>834.5473868842978</v>
+        <v>834.5473213853697</v>
       </c>
       <c r="I553" t="n">
         <v>495.5999980879241</v>
@@ -43008,7 +43008,7 @@
         <v>21.98345240625199</v>
       </c>
       <c r="K553" t="n">
-        <v>38.0443972765562</v>
+        <v>38.04438644222829</v>
       </c>
       <c r="L553" t="n">
         <v>36.18784530386741</v>
@@ -43378,13 +43378,13 @@
         <v>7593.6013671875</v>
       </c>
       <c r="F558" t="n">
-        <v>7733.318310546875</v>
+        <v>7733.318305664063</v>
       </c>
       <c r="G558" t="n">
-        <v>-1.346337639461237</v>
+        <v>-1.346337548123022</v>
       </c>
       <c r="H558" t="n">
-        <v>9391.700937170743</v>
+        <v>9391.699890478567</v>
       </c>
       <c r="I558" t="n">
         <v>6860</v>
@@ -43393,7 +43393,7 @@
         <v>5.342565597667637</v>
       </c>
       <c r="K558" t="n">
-        <v>29.96195858535589</v>
+        <v>29.96194410127402</v>
       </c>
       <c r="L558" t="n">
         <v>33.42541436464088</v>
@@ -44074,7 +44074,7 @@
         <v>2663.524438476562</v>
       </c>
       <c r="G567" t="n">
-        <v>-1.77832535639213</v>
+        <v>-1.778325665895997</v>
       </c>
       <c r="H567" t="n">
         <v>3198.009229338596</v>
@@ -44693,7 +44693,7 @@
         <v>-2.362631962750816</v>
       </c>
       <c r="H575" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I575" t="n">
         <v>121310</v>
@@ -44702,7 +44702,7 @@
         <v>1.220014838018302</v>
       </c>
       <c r="K575" t="n">
-        <v>32.99819718929442</v>
+        <v>32.99821018515144</v>
       </c>
       <c r="L575" t="n">
         <v>28.03867403314917</v>
@@ -45069,16 +45069,16 @@
         <v>18.62360000610352</v>
       </c>
       <c r="E580" t="n">
-        <v>20.1444348526001</v>
+        <v>20.14443482716878</v>
       </c>
       <c r="F580" t="n">
-        <v>20.27678067207336</v>
+        <v>20.27678068161011</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.721833239498338</v>
+        <v>-1.721833238702453</v>
       </c>
       <c r="H580" t="n">
-        <v>23.83526024888653</v>
+        <v>23.83526224893035</v>
       </c>
       <c r="I580" t="n">
         <v>16.75</v>
@@ -45087,7 +45087,7 @@
         <v>5.194034861094909</v>
       </c>
       <c r="K580" t="n">
-        <v>35.27388827254756</v>
+        <v>35.27389962353353</v>
       </c>
       <c r="L580" t="n">
         <v>26.24309392265193</v>
@@ -46920,13 +46920,13 @@
         <v>121.2708986409505</v>
       </c>
       <c r="F604" t="n">
-        <v>122.779068107605</v>
+        <v>122.7790681457519</v>
       </c>
       <c r="G604" t="n">
-        <v>-2.600971682843312</v>
+        <v>-2.600972153646652</v>
       </c>
       <c r="H604" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I604" t="n">
         <v>103.0500030517578</v>
@@ -46935,7 +46935,7 @@
         <v>4.36681209775398</v>
       </c>
       <c r="K604" t="n">
-        <v>44.9557938412435</v>
+        <v>44.95581027554825</v>
       </c>
       <c r="L604" t="n">
         <v>20.44198895027624</v>
@@ -47767,10 +47767,10 @@
         <v>153.8962880452474</v>
       </c>
       <c r="F615" t="n">
-        <v>158.5334973907471</v>
+        <v>158.5334972381592</v>
       </c>
       <c r="G615" t="n">
-        <v>-2.853053153992635</v>
+        <v>-2.853053292914132</v>
       </c>
       <c r="H615" t="n">
         <v>212.7553783484557</v>
@@ -48614,13 +48614,13 @@
         <v>252.2240498860677</v>
       </c>
       <c r="F626" t="n">
-        <v>260.4150134277344</v>
+        <v>260.4150129699707</v>
       </c>
       <c r="G626" t="n">
-        <v>-3.89524632174193</v>
+        <v>-3.895246220085868</v>
       </c>
       <c r="H626" t="n">
-        <v>345.9511213302791</v>
+        <v>345.9510897219776</v>
       </c>
       <c r="I626" t="n">
         <v>212</v>
@@ -48629,7 +48629,7 @@
         <v>7.325471122309857</v>
       </c>
       <c r="K626" t="n">
-        <v>52.04637770241902</v>
+        <v>52.04636381049195</v>
       </c>
       <c r="L626" t="n">
         <v>15.60773480662983</v>
@@ -49150,16 +49150,16 @@
         <v>898.0040734863281</v>
       </c>
       <c r="E633" t="n">
-        <v>993.2585257975261</v>
+        <v>993.2585282389323</v>
       </c>
       <c r="F633" t="n">
-        <v>1042.194986877441</v>
+        <v>1042.194989318848</v>
       </c>
       <c r="G633" t="n">
-        <v>-2.799108741993528</v>
+        <v>-2.799108680288609</v>
       </c>
       <c r="H633" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I633" t="n">
         <v>832.5999755859375</v>
@@ -49168,7 +49168,7 @@
         <v>2.690370534577369</v>
       </c>
       <c r="K633" t="n">
-        <v>46.80448050481942</v>
+        <v>46.80449508185218</v>
       </c>
       <c r="L633" t="n">
         <v>14.22651933701657</v>
@@ -49227,16 +49227,16 @@
         <v>176.8348574829102</v>
       </c>
       <c r="E634" t="n">
-        <v>190.2435905965169</v>
+        <v>190.2435909016927</v>
       </c>
       <c r="F634" t="n">
-        <v>192.0990495300293</v>
+        <v>192.0990496063232</v>
       </c>
       <c r="G634" t="n">
-        <v>-2.694384398511995</v>
+        <v>-2.694384435075314</v>
       </c>
       <c r="H634" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I634" t="n">
         <v>155.8000030517578</v>
@@ -49245,7 +49245,7 @@
         <v>3.395374314835831</v>
       </c>
       <c r="K634" t="n">
-        <v>48.50001759024396</v>
+        <v>48.50002717584694</v>
       </c>
       <c r="L634" t="n">
         <v>14.08839779005525</v>
@@ -49621,7 +49621,7 @@
         <v>-4.133323136753441</v>
       </c>
       <c r="H639" t="n">
-        <v>725.6811213920008</v>
+        <v>725.6811828531856</v>
       </c>
       <c r="I639" t="n">
         <v>446.0256812201048</v>
@@ -49630,7 +49630,7 @@
         <v>4.624019096829057</v>
       </c>
       <c r="K639" t="n">
-        <v>55.50865335551178</v>
+        <v>55.50866652623623</v>
       </c>
       <c r="L639" t="n">
         <v>13.25966850828729</v>
@@ -50693,10 +50693,10 @@
         <v>662.4260811360678</v>
       </c>
       <c r="F653" t="n">
-        <v>703.3488009643555</v>
+        <v>703.3488034057617</v>
       </c>
       <c r="G653" t="n">
-        <v>-4.472492993144028</v>
+        <v>-4.472493017908452</v>
       </c>
       <c r="H653" t="n">
         <v>1140.477361200229</v>
@@ -51155,10 +51155,10 @@
         <v>379.9771179199219</v>
       </c>
       <c r="F659" t="n">
-        <v>389.2492016601562</v>
+        <v>389.2492022705078</v>
       </c>
       <c r="G659" t="n">
-        <v>-2.611727786751439</v>
+        <v>-2.611727745583481</v>
       </c>
       <c r="H659" t="n">
         <v>541.0236304500187</v>
@@ -51383,16 +51383,16 @@
         <v>83.92279052734375</v>
       </c>
       <c r="E662" t="n">
-        <v>91.18646697998047</v>
+        <v>91.18646672566732</v>
       </c>
       <c r="F662" t="n">
-        <v>93.76012783050537</v>
+        <v>93.7601276397705</v>
       </c>
       <c r="G662" t="n">
-        <v>-3.776733696552015</v>
+        <v>-3.776733703944812</v>
       </c>
       <c r="H662" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I662" t="n">
         <v>73.90000152587891</v>
@@ -51401,7 +51401,7 @@
         <v>2.178620537359199</v>
       </c>
       <c r="K662" t="n">
-        <v>65.31228462855059</v>
+        <v>65.31227421356375</v>
       </c>
       <c r="L662" t="n">
         <v>9.25414364640884</v>
@@ -51922,25 +51922,25 @@
         <v>481.3466955566406</v>
       </c>
       <c r="E669" t="n">
-        <v>502.6339683024088</v>
+        <v>502.6339693196614</v>
       </c>
       <c r="F669" t="n">
-        <v>522.9714283752442</v>
+        <v>522.9714303588867</v>
       </c>
       <c r="G669" t="n">
-        <v>-4.575324541243009</v>
+        <v>-4.575324577819306</v>
       </c>
       <c r="H669" t="n">
-        <v>756.8455981427298</v>
+        <v>756.8456624851057</v>
       </c>
       <c r="I669" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J669" t="n">
-        <v>10.52229868658205</v>
+        <v>10.5223068938356</v>
       </c>
       <c r="K669" t="n">
-        <v>68.61882318169847</v>
+        <v>68.61883751663775</v>
       </c>
       <c r="L669" t="n">
         <v>8.287292817679557</v>
@@ -53080,10 +53080,10 @@
         <v>128.6862941996256</v>
       </c>
       <c r="F684" t="n">
-        <v>135.5109524154663</v>
+        <v>135.5109527206421</v>
       </c>
       <c r="G684" t="n">
-        <v>-3.698135176885564</v>
+        <v>-3.698135221079002</v>
       </c>
       <c r="H684" t="n">
         <v>183.7853835258596</v>
@@ -53234,10 +53234,10 @@
         <v>270.028515218099</v>
       </c>
       <c r="F686" t="n">
-        <v>282.0782897949219</v>
+        <v>282.0782901000977</v>
       </c>
       <c r="G686" t="n">
-        <v>-4.468323860176615</v>
+        <v>-4.468324003662283</v>
       </c>
       <c r="H686" t="n">
         <v>385.6351549871131</v>
@@ -53773,10 +53773,10 @@
         <v>339.488252360026</v>
       </c>
       <c r="F693" t="n">
-        <v>347.0402711486817</v>
+        <v>347.0402709960937</v>
       </c>
       <c r="G693" t="n">
-        <v>-3.612347200525678</v>
+        <v>-3.612347283754902</v>
       </c>
       <c r="H693" t="n">
         <v>487.9415273208757</v>
@@ -54620,10 +54620,10 @@
         <v>639.1963462320964</v>
       </c>
       <c r="F704" t="n">
-        <v>727.4957801818848</v>
+        <v>727.4957774353028</v>
       </c>
       <c r="G704" t="n">
-        <v>-9.475348781815285</v>
+        <v>-9.475348951702179</v>
       </c>
       <c r="H704" t="n">
         <v>1271.244922552079</v>
@@ -56086,7 +56086,7 @@
         <v>439.4220953369141</v>
       </c>
       <c r="G723" t="n">
-        <v>-6.328281788544343</v>
+        <v>-6.328281879950692</v>
       </c>
       <c r="H723" t="n">
         <v>779.4908805849697</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1025,13 +1025,13 @@
         <v>1430.808000488281</v>
       </c>
       <c r="E8" t="n">
-        <v>1185.626040852865</v>
+        <v>1185.626040445964</v>
       </c>
       <c r="F8" t="n">
-        <v>1098.686553649902</v>
+        <v>1098.686553955078</v>
       </c>
       <c r="G8" t="n">
-        <v>6.283494859693151</v>
+        <v>6.283494826461422</v>
       </c>
       <c r="H8" t="n">
         <v>1677.5</v>
@@ -1561,16 +1561,16 @@
         <v>225.5</v>
       </c>
       <c r="D15" t="n">
-        <v>206.6969711303711</v>
+        <v>206.6969708251953</v>
       </c>
       <c r="E15" t="n">
-        <v>165.0934430440267</v>
+        <v>165.0934440104167</v>
       </c>
       <c r="F15" t="n">
-        <v>160.0688949203491</v>
+        <v>160.0688959503174</v>
       </c>
       <c r="G15" t="n">
-        <v>5.344496185626668</v>
+        <v>5.344495937823179</v>
       </c>
       <c r="H15" t="n">
         <v>248.3999938964844</v>
@@ -1718,13 +1718,13 @@
         <v>2168.989235839844</v>
       </c>
       <c r="E17" t="n">
-        <v>1950.100589192708</v>
+        <v>1950.100593261719</v>
       </c>
       <c r="F17" t="n">
-        <v>1842.204440307617</v>
+        <v>1842.20444519043</v>
       </c>
       <c r="G17" t="n">
-        <v>4.10128886798371</v>
+        <v>4.101288713047446</v>
       </c>
       <c r="H17" t="n">
         <v>2264.114307176184</v>
@@ -2026,13 +2026,13 @@
         <v>1072.110004882813</v>
       </c>
       <c r="E21" t="n">
-        <v>971.6688570149739</v>
+        <v>971.6688586425781</v>
       </c>
       <c r="F21" t="n">
-        <v>936.774873046875</v>
+        <v>936.7748754882813</v>
       </c>
       <c r="G21" t="n">
-        <v>3.628409431590485</v>
+        <v>3.628409421791079</v>
       </c>
       <c r="H21" t="n">
         <v>1240.5</v>
@@ -3184,10 +3184,10 @@
         <v>677.6434802246093</v>
       </c>
       <c r="F36" t="n">
-        <v>632.7774433898926</v>
+        <v>632.7774435424805</v>
       </c>
       <c r="G36" t="n">
-        <v>5.817060179639721</v>
+        <v>5.817060259158513</v>
       </c>
       <c r="H36" t="n">
         <v>844</v>
@@ -4031,19 +4031,19 @@
         <v>11171.19533203125</v>
       </c>
       <c r="F47" t="n">
-        <v>10705.86284423828</v>
+        <v>10705.86282226562</v>
       </c>
       <c r="G47" t="n">
-        <v>4.434433972604301</v>
+        <v>4.434433783135328</v>
       </c>
       <c r="H47" t="n">
         <v>14498</v>
       </c>
       <c r="I47" t="n">
-        <v>7621.135634822365</v>
+        <v>7621.136115884997</v>
       </c>
       <c r="J47" t="n">
-        <v>61.34078422403773</v>
+        <v>61.34077403985769</v>
       </c>
       <c r="K47" t="n">
         <v>17.90826284970721</v>
@@ -4650,16 +4650,16 @@
         <v>1376.168594970703</v>
       </c>
       <c r="G55" t="n">
-        <v>3.692858614572181</v>
+        <v>3.692858376133823</v>
       </c>
       <c r="H55" t="n">
         <v>1766.733060850261</v>
       </c>
       <c r="I55" t="n">
-        <v>971.816928508411</v>
+        <v>971.8169883351571</v>
       </c>
       <c r="J55" t="n">
-        <v>54.00019609485373</v>
+        <v>54.00018661433348</v>
       </c>
       <c r="K55" t="n">
         <v>18.04978549184879</v>
@@ -6036,7 +6036,7 @@
         <v>1621.725526123047</v>
       </c>
       <c r="G73" t="n">
-        <v>3.383635583007027</v>
+        <v>3.383635663458917</v>
       </c>
       <c r="H73" t="n">
         <v>2038.599975585938</v>
@@ -6803,19 +6803,19 @@
         <v>340.4082891845703</v>
       </c>
       <c r="F83" t="n">
-        <v>334.6648670959473</v>
+        <v>334.664867401123</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1437447818124937</v>
+        <v>0.1437446902303963</v>
       </c>
       <c r="H83" t="n">
         <v>388.5</v>
       </c>
       <c r="I83" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J83" t="n">
-        <v>34.83879417798654</v>
+        <v>34.83877982068808</v>
       </c>
       <c r="K83" t="n">
         <v>1.928376287869438</v>
@@ -7496,10 +7496,10 @@
         <v>745.5265991210938</v>
       </c>
       <c r="F92" t="n">
-        <v>742.8253869628907</v>
+        <v>742.8253872680664</v>
       </c>
       <c r="G92" t="n">
-        <v>2.554687678444956</v>
+        <v>2.55468741811451</v>
       </c>
       <c r="H92" t="n">
         <v>1002.400024414062</v>
@@ -7801,13 +7801,13 @@
         <v>4577.49</v>
       </c>
       <c r="E96" t="n">
-        <v>4266.073771158854</v>
+        <v>4266.073772786458</v>
       </c>
       <c r="F96" t="n">
-        <v>4326.074368896484</v>
+        <v>4326.074367675781</v>
       </c>
       <c r="G96" t="n">
-        <v>0.530640080232847</v>
+        <v>0.5306401374185921</v>
       </c>
       <c r="H96" t="n">
         <v>5005.771680286142</v>
@@ -8035,10 +8035,10 @@
         <v>4502.45759765625</v>
       </c>
       <c r="F99" t="n">
-        <v>4429.626120605469</v>
+        <v>4429.626131591797</v>
       </c>
       <c r="G99" t="n">
-        <v>1.159942207746334</v>
+        <v>1.159941922828955</v>
       </c>
       <c r="H99" t="n">
         <v>5149.89990234375</v>
@@ -8808,7 +8808,7 @@
         <v>252.2203276062012</v>
       </c>
       <c r="G109" t="n">
-        <v>6.249394047595391</v>
+        <v>6.249394013447573</v>
       </c>
       <c r="H109" t="n">
         <v>388.75</v>
@@ -9264,13 +9264,13 @@
         <v>1447.603981933594</v>
       </c>
       <c r="E115" t="n">
-        <v>1232.616171061198</v>
+        <v>1232.616174723307</v>
       </c>
       <c r="F115" t="n">
-        <v>1117.495632324219</v>
+        <v>1117.495636901856</v>
       </c>
       <c r="G115" t="n">
-        <v>8.582233465895573</v>
+        <v>8.58223329893284</v>
       </c>
       <c r="H115" t="n">
         <v>1681</v>
@@ -11115,10 +11115,10 @@
         <v>531.0733719889323</v>
       </c>
       <c r="F139" t="n">
-        <v>539.5183615112305</v>
+        <v>539.5183612060547</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8666070480100041</v>
+        <v>0.8666071636026729</v>
       </c>
       <c r="H139" t="n">
         <v>673.9500122070312</v>
@@ -11651,13 +11651,13 @@
         <v>188.8985327148438</v>
       </c>
       <c r="E146" t="n">
-        <v>161.0964747111003</v>
+        <v>161.096474609375</v>
       </c>
       <c r="F146" t="n">
-        <v>156.585650062561</v>
+        <v>156.585650138855</v>
       </c>
       <c r="G146" t="n">
-        <v>2.317501624293894</v>
+        <v>2.317501776162456</v>
       </c>
       <c r="H146" t="n">
         <v>233.3500061035156</v>
@@ -11805,16 +11805,16 @@
         <v>1976.217802734375</v>
       </c>
       <c r="E148" t="n">
-        <v>1813.873228352865</v>
+        <v>1813.873224283854</v>
       </c>
       <c r="F148" t="n">
-        <v>1789.139586791992</v>
+        <v>1789.139586181641</v>
       </c>
       <c r="G148" t="n">
-        <v>1.439513831158812</v>
+        <v>1.439513936967396</v>
       </c>
       <c r="H148" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I148" t="n">
         <v>1345.285007075603</v>
@@ -11823,7 +11823,7 @@
         <v>37.61396574637396</v>
       </c>
       <c r="K148" t="n">
-        <v>21.87046113528006</v>
+        <v>21.87044761079642</v>
       </c>
       <c r="L148" t="n">
         <v>62.08791208791209</v>
@@ -13043,7 +13043,7 @@
         <v>994.9437686157227</v>
       </c>
       <c r="G164" t="n">
-        <v>3.826345945656739</v>
+        <v>3.826345813397292</v>
       </c>
       <c r="H164" t="n">
         <v>1368.900024414062</v>
@@ -14192,22 +14192,22 @@
         <v>1280.438725585937</v>
       </c>
       <c r="E179" t="n">
-        <v>1236.5363671875</v>
+        <v>1236.536364339193</v>
       </c>
       <c r="F179" t="n">
-        <v>1299.570640869141</v>
+        <v>1299.570631408691</v>
       </c>
       <c r="G179" t="n">
-        <v>-2.554692239285028</v>
+        <v>-2.554692391197133</v>
       </c>
       <c r="H179" t="n">
         <v>1713.752567939176</v>
       </c>
       <c r="I179" t="n">
-        <v>1010.594387550952</v>
+        <v>1010.594326763664</v>
       </c>
       <c r="J179" t="n">
-        <v>40.72905694819828</v>
+        <v>40.72906541305661</v>
       </c>
       <c r="K179" t="n">
         <v>20.50011438455368</v>
@@ -14426,13 +14426,13 @@
         <v>5209.301298828125</v>
       </c>
       <c r="F182" t="n">
-        <v>5320.821633300781</v>
+        <v>5320.821628417969</v>
       </c>
       <c r="G182" t="n">
-        <v>-1.462887033897453</v>
+        <v>-1.462887079771646</v>
       </c>
       <c r="H182" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I182" t="n">
         <v>4229.809203861739</v>
@@ -14441,7 +14441,7 @@
         <v>35.40799889439214</v>
       </c>
       <c r="K182" t="n">
-        <v>14.40688277507316</v>
+        <v>14.40689144479781</v>
       </c>
       <c r="L182" t="n">
         <v>69.0934065934066</v>
@@ -14971,7 +14971,7 @@
         <v>1.755074939903611</v>
       </c>
       <c r="H189" t="n">
-        <v>1278.952725191461</v>
+        <v>1278.952852189353</v>
       </c>
       <c r="I189" t="n">
         <v>865.2617122743181</v>
@@ -14980,7 +14980,7 @@
         <v>31.35909742249126</v>
       </c>
       <c r="K189" t="n">
-        <v>12.52443715143825</v>
+        <v>12.52444832492894</v>
       </c>
       <c r="L189" t="n">
         <v>62.91208791208791</v>
@@ -15427,10 +15427,10 @@
         <v>79.37681729634603</v>
       </c>
       <c r="F195" t="n">
-        <v>75.8667673110962</v>
+        <v>75.8667672920227</v>
       </c>
       <c r="G195" t="n">
-        <v>3.842103743060932</v>
+        <v>3.842103662734742</v>
       </c>
       <c r="H195" t="n">
         <v>94.5</v>
@@ -17044,10 +17044,10 @@
         <v>630.1421089680989</v>
       </c>
       <c r="F216" t="n">
-        <v>613.1097012329102</v>
+        <v>613.1097006225586</v>
       </c>
       <c r="G216" t="n">
-        <v>1.223349494083004</v>
+        <v>1.223349444315391</v>
       </c>
       <c r="H216" t="n">
         <v>769</v>
@@ -17820,7 +17820,7 @@
         <v>-1.168610449928753</v>
       </c>
       <c r="H226" t="n">
-        <v>1409.944064008135</v>
+        <v>1409.944189808421</v>
       </c>
       <c r="I226" t="n">
         <v>905.5050975494345</v>
@@ -17829,7 +17829,7 @@
         <v>31.031841036679</v>
       </c>
       <c r="K226" t="n">
-        <v>18.83220092778217</v>
+        <v>18.83221153041898</v>
       </c>
       <c r="L226" t="n">
         <v>62.5</v>
@@ -18507,10 +18507,10 @@
         <v>1959.427457682292</v>
       </c>
       <c r="F235" t="n">
-        <v>1873.624813842773</v>
+        <v>1873.62481262207</v>
       </c>
       <c r="G235" t="n">
-        <v>2.727090660510756</v>
+        <v>2.727090731089876</v>
       </c>
       <c r="H235" t="n">
         <v>2295</v>
@@ -19286,10 +19286,10 @@
         <v>1153.699951171875</v>
       </c>
       <c r="I245" t="n">
-        <v>654.5363800389173</v>
+        <v>654.5364401437979</v>
       </c>
       <c r="J245" t="n">
-        <v>32.15460994674872</v>
+        <v>32.15459781123331</v>
       </c>
       <c r="K245" t="n">
         <v>33.37571689848266</v>
@@ -19585,19 +19585,19 @@
         <v>1837.012530924479</v>
       </c>
       <c r="F249" t="n">
-        <v>1804.375181274414</v>
+        <v>1804.375180664063</v>
       </c>
       <c r="G249" t="n">
-        <v>0.2134537387452617</v>
+        <v>0.213453670876107</v>
       </c>
       <c r="H249" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I249" t="n">
-        <v>1569.36587206911</v>
+        <v>1569.365993709292</v>
       </c>
       <c r="J249" t="n">
-        <v>11.38256738662047</v>
+        <v>11.38255875345531</v>
       </c>
       <c r="K249" t="n">
         <v>17.0995437307816</v>
@@ -20891,16 +20891,16 @@
         <v>2238.142978515625</v>
       </c>
       <c r="E266" t="n">
-        <v>2266.075244140625</v>
+        <v>2266.075249023438</v>
       </c>
       <c r="F266" t="n">
-        <v>2409.172103271485</v>
+        <v>2409.172108154297</v>
       </c>
       <c r="G266" t="n">
-        <v>-3.924399357584785</v>
+        <v>-3.92439934994312</v>
       </c>
       <c r="H266" t="n">
-        <v>3269.779254579709</v>
+        <v>3269.779000999862</v>
       </c>
       <c r="I266" t="n">
         <v>1955.624263494112</v>
@@ -20909,7 +20909,7 @@
         <v>29.3704546025447</v>
       </c>
       <c r="K266" t="n">
-        <v>29.24028674228099</v>
+        <v>29.24027671936211</v>
       </c>
       <c r="L266" t="n">
         <v>59.75274725274725</v>
@@ -20968,22 +20968,22 @@
         <v>1790.585524902344</v>
       </c>
       <c r="E267" t="n">
-        <v>1726.580901692708</v>
+        <v>1726.580900878906</v>
       </c>
       <c r="F267" t="n">
-        <v>1682.756887207031</v>
+        <v>1682.756887817383</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6202642557826099</v>
+        <v>0.6202643657230666</v>
       </c>
       <c r="H267" t="n">
         <v>1981.513102925086</v>
       </c>
       <c r="I267" t="n">
-        <v>1386.27210129059</v>
+        <v>1386.27198097588</v>
       </c>
       <c r="J267" t="n">
-        <v>16.33357907661026</v>
+        <v>16.33358917321537</v>
       </c>
       <c r="K267" t="n">
         <v>22.86929763253305</v>
@@ -22129,16 +22129,16 @@
         <v>165.7395127868652</v>
       </c>
       <c r="G282" t="n">
-        <v>1.595450877212423</v>
+        <v>1.595450972238432</v>
       </c>
       <c r="H282" t="n">
         <v>208.3389342898026</v>
       </c>
       <c r="I282" t="n">
-        <v>130.9092394450487</v>
+        <v>130.9092542320289</v>
       </c>
       <c r="J282" t="n">
-        <v>23.94083159279763</v>
+        <v>23.94081759294227</v>
       </c>
       <c r="K282" t="n">
         <v>28.40612282884598</v>
@@ -22277,25 +22277,25 @@
         <v>291.8554602050781</v>
       </c>
       <c r="E284" t="n">
-        <v>302.100251566569</v>
+        <v>302.1002519734701</v>
       </c>
       <c r="F284" t="n">
-        <v>287.5597003173828</v>
+        <v>287.5597009277344</v>
       </c>
       <c r="G284" t="n">
-        <v>1.655991398019263</v>
+        <v>1.655991504116217</v>
       </c>
       <c r="H284" t="n">
-        <v>357.6229001129018</v>
+        <v>357.6229312128765</v>
       </c>
       <c r="I284" t="n">
-        <v>205.4947627274531</v>
+        <v>205.494747960586</v>
       </c>
       <c r="J284" t="n">
-        <v>35.76988352254828</v>
+        <v>35.76989327898173</v>
       </c>
       <c r="K284" t="n">
-        <v>28.18025093652394</v>
+        <v>28.18026208346829</v>
       </c>
       <c r="L284" t="n">
         <v>69.5054945054945</v>
@@ -22591,7 +22591,7 @@
         <v>424.596901550293</v>
       </c>
       <c r="G288" t="n">
-        <v>1.150854066324003</v>
+        <v>1.150854103093035</v>
       </c>
       <c r="H288" t="n">
         <v>478.7148709533388</v>
@@ -23663,13 +23663,13 @@
         <v>328.6148284912109</v>
       </c>
       <c r="E302" t="n">
-        <v>315.8006858317057</v>
+        <v>315.8006854248047</v>
       </c>
       <c r="F302" t="n">
-        <v>310.1694563293457</v>
+        <v>310.1694561767578</v>
       </c>
       <c r="G302" t="n">
-        <v>0.9784517764029887</v>
+        <v>0.9784518772138817</v>
       </c>
       <c r="H302" t="n">
         <v>380.4567148307952</v>
@@ -25609,7 +25609,7 @@
         <v>69.73533615923837</v>
       </c>
       <c r="L327" t="n">
-        <v>20.05494505494505</v>
+        <v>20.19230769230769</v>
       </c>
       <c r="M327" t="n">
         <v>3</v>
@@ -25822,10 +25822,10 @@
         <v>286.0308180745442</v>
       </c>
       <c r="F330" t="n">
-        <v>273.0385107421875</v>
+        <v>273.038511352539</v>
       </c>
       <c r="G330" t="n">
-        <v>2.320512546343756</v>
+        <v>2.320512570290534</v>
       </c>
       <c r="H330" t="n">
         <v>367.499792159746</v>
@@ -25976,19 +25976,19 @@
         <v>5198.972395833333</v>
       </c>
       <c r="F332" t="n">
-        <v>4985.197320556641</v>
+        <v>4985.197313232422</v>
       </c>
       <c r="G332" t="n">
-        <v>0.7789795288617229</v>
+        <v>0.7789794802760319</v>
       </c>
       <c r="H332" t="n">
         <v>6049.821052103703</v>
       </c>
       <c r="I332" t="n">
-        <v>3833.724882458191</v>
+        <v>3833.724641126707</v>
       </c>
       <c r="J332" t="n">
-        <v>13.31538721492689</v>
+        <v>13.31539434808673</v>
       </c>
       <c r="K332" t="n">
         <v>39.26202246921331</v>
@@ -26130,10 +26130,10 @@
         <v>5136.551207682292</v>
       </c>
       <c r="F334" t="n">
-        <v>5227.852768554688</v>
+        <v>5227.852780761718</v>
       </c>
       <c r="G334" t="n">
-        <v>-1.223272714117141</v>
+        <v>-1.223272802424624</v>
       </c>
       <c r="H334" t="n">
         <v>6175.521739453033</v>
@@ -26435,16 +26435,16 @@
         <v>150.0775961303711</v>
       </c>
       <c r="E338" t="n">
-        <v>154.7109349568685</v>
+        <v>154.7109357706706</v>
       </c>
       <c r="F338" t="n">
-        <v>151.3329470825195</v>
+        <v>151.3329485321045</v>
       </c>
       <c r="G338" t="n">
-        <v>1.210379735312728</v>
+        <v>1.21037972357847</v>
       </c>
       <c r="H338" t="n">
-        <v>196.4205869556906</v>
+        <v>196.4205715539644</v>
       </c>
       <c r="I338" t="n">
         <v>125.7825892411346</v>
@@ -26453,7 +26453,7 @@
         <v>6.032159078477273</v>
       </c>
       <c r="K338" t="n">
-        <v>47.27494500026246</v>
+        <v>47.27493345214309</v>
       </c>
       <c r="L338" t="n">
         <v>58.92857142857143</v>
@@ -26746,10 +26746,10 @@
         <v>340.401630452474</v>
       </c>
       <c r="F342" t="n">
-        <v>335.7981439208984</v>
+        <v>335.7981440734864</v>
       </c>
       <c r="G342" t="n">
-        <v>0.5117193183955315</v>
+        <v>0.5117193640684192</v>
       </c>
       <c r="H342" t="n">
         <v>428.7550602808859</v>
@@ -27208,19 +27208,19 @@
         <v>511.9502278645833</v>
       </c>
       <c r="F348" t="n">
-        <v>525.9838604736328</v>
+        <v>525.9838595581055</v>
       </c>
       <c r="G348" t="n">
-        <v>1.528371578768972</v>
+        <v>1.528371641276971</v>
       </c>
       <c r="H348" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I348" t="n">
-        <v>306.8420198526935</v>
+        <v>306.8419898026673</v>
       </c>
       <c r="J348" t="n">
-        <v>30.05063256477771</v>
+        <v>30.05064530105583</v>
       </c>
       <c r="K348" t="n">
         <v>89.44123119561152</v>
@@ -28591,22 +28591,22 @@
         <v>36163.7459375</v>
       </c>
       <c r="E366" t="n">
-        <v>37172.16876302083</v>
+        <v>37172.16875</v>
       </c>
       <c r="F366" t="n">
-        <v>36138.4726953125</v>
+        <v>36138.47262695312</v>
       </c>
       <c r="G366" t="n">
-        <v>0.08572860772477764</v>
+        <v>0.08572855374877619</v>
       </c>
       <c r="H366" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I366" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J366" t="n">
-        <v>14.579794541279</v>
+        <v>14.57980202170501</v>
       </c>
       <c r="K366" t="n">
         <v>28.92168359716212</v>
@@ -29287,13 +29287,13 @@
         <v>182.6896445719401</v>
       </c>
       <c r="F375" t="n">
-        <v>193.2972239685058</v>
+        <v>193.2972235107422</v>
       </c>
       <c r="G375" t="n">
-        <v>-4.518805731995002</v>
+        <v>-4.518805706229568</v>
       </c>
       <c r="H375" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I375" t="n">
         <v>156.7899932861328</v>
@@ -29302,7 +29302,7 @@
         <v>21.07915330504762</v>
       </c>
       <c r="K375" t="n">
-        <v>38.65388429409784</v>
+        <v>38.65386819332664</v>
       </c>
       <c r="L375" t="n">
         <v>42.30769230769231</v>
@@ -30999,7 +30999,7 @@
         <v>56.73910152710122</v>
       </c>
       <c r="L397" t="n">
-        <v>21.01648351648352</v>
+        <v>21.15384615384615</v>
       </c>
       <c r="M397" t="n">
         <v>2</v>
@@ -31076,7 +31076,7 @@
         <v>44.29203472210086</v>
       </c>
       <c r="L398" t="n">
-        <v>20.87912087912088</v>
+        <v>21.01648351648352</v>
       </c>
       <c r="M398" t="n">
         <v>2</v>
@@ -31153,7 +31153,7 @@
         <v>58.63837440666966</v>
       </c>
       <c r="L399" t="n">
-        <v>19.50549450549451</v>
+        <v>19.64285714285714</v>
       </c>
       <c r="M399" t="n">
         <v>2</v>
@@ -32367,10 +32367,10 @@
         <v>1142.22318359375</v>
       </c>
       <c r="F415" t="n">
-        <v>1153.466192321777</v>
+        <v>1153.466194152832</v>
       </c>
       <c r="G415" t="n">
-        <v>-1.250948306463395</v>
+        <v>-1.250948459299361</v>
       </c>
       <c r="H415" t="n">
         <v>1351.914027099318</v>
@@ -33060,10 +33060,10 @@
         <v>1668.680072428386</v>
       </c>
       <c r="F424" t="n">
-        <v>1673.440249023437</v>
+        <v>1673.440248413086</v>
       </c>
       <c r="G424" t="n">
-        <v>-0.6178726799366485</v>
+        <v>-0.6178727161841424</v>
       </c>
       <c r="H424" t="n">
         <v>1952.5</v>
@@ -33288,13 +33288,13 @@
         <v>436.2198443603515</v>
       </c>
       <c r="E427" t="n">
-        <v>461.956514078776</v>
+        <v>461.9565120442708</v>
       </c>
       <c r="F427" t="n">
-        <v>451.9435159301758</v>
+        <v>451.9435145568848</v>
       </c>
       <c r="G427" t="n">
-        <v>-0.7141407067868477</v>
+        <v>-0.7141406423771701</v>
       </c>
       <c r="H427" t="n">
         <v>576.7288135834383</v>
@@ -34221,7 +34221,7 @@
         <v>-1.538058944766652</v>
       </c>
       <c r="H439" t="n">
-        <v>834.5473868842978</v>
+        <v>834.5473213853697</v>
       </c>
       <c r="I439" t="n">
         <v>495.5999980879241</v>
@@ -34230,7 +34230,7 @@
         <v>12.67151464253982</v>
       </c>
       <c r="K439" t="n">
-        <v>49.45332206244095</v>
+        <v>49.45331033269076</v>
       </c>
       <c r="L439" t="n">
         <v>42.17032967032967</v>
@@ -34366,13 +34366,13 @@
         <v>1568.81724609375</v>
       </c>
       <c r="E441" t="n">
-        <v>1690.28457438151</v>
+        <v>1690.2845703125</v>
       </c>
       <c r="F441" t="n">
-        <v>1736.732779541016</v>
+        <v>1736.732775268555</v>
       </c>
       <c r="G441" t="n">
-        <v>-2.105864421431014</v>
+        <v>-2.105864392823353</v>
       </c>
       <c r="H441" t="n">
         <v>2048.271405606928</v>
@@ -35062,10 +35062,10 @@
         <v>201.0005732218424</v>
       </c>
       <c r="F450" t="n">
-        <v>204.994845123291</v>
+        <v>204.9948448944092</v>
       </c>
       <c r="G450" t="n">
-        <v>-2.089795099458136</v>
+        <v>-2.089795173099118</v>
       </c>
       <c r="H450" t="n">
         <v>278.3389924341271</v>
@@ -35293,13 +35293,13 @@
         <v>207.4939163208008</v>
       </c>
       <c r="F453" t="n">
-        <v>209.7035088348389</v>
+        <v>209.7035089111328</v>
       </c>
       <c r="G453" t="n">
-        <v>-1.248340170082618</v>
+        <v>-1.248340205113252</v>
       </c>
       <c r="H453" t="n">
-        <v>252.6161043110497</v>
+        <v>252.6160882566492</v>
       </c>
       <c r="I453" t="n">
         <v>171.6534052563282</v>
@@ -35308,7 +35308,7 @@
         <v>10.33861729317598</v>
       </c>
       <c r="K453" t="n">
-        <v>33.37703930925986</v>
+        <v>33.37703083280734</v>
       </c>
       <c r="L453" t="n">
         <v>36.53846153846153</v>
@@ -35367,13 +35367,13 @@
         <v>12898.168984375</v>
       </c>
       <c r="E454" t="n">
-        <v>12592.29762369792</v>
+        <v>12592.2976171875</v>
       </c>
       <c r="F454" t="n">
-        <v>12757.60178710938</v>
+        <v>12757.60175292969</v>
       </c>
       <c r="G454" t="n">
-        <v>-1.260314801290807</v>
+        <v>-1.260314543419216</v>
       </c>
       <c r="H454" t="n">
         <v>17441.42261795032</v>
@@ -36063,10 +36063,10 @@
         <v>579.7319146728515</v>
       </c>
       <c r="F463" t="n">
-        <v>557.7230964660645</v>
+        <v>557.723097076416</v>
       </c>
       <c r="G463" t="n">
-        <v>-0.2401941401946162</v>
+        <v>-0.2401940310211681</v>
       </c>
       <c r="H463" t="n">
         <v>784.8771245029434</v>
@@ -36140,13 +36140,13 @@
         <v>778.0079960123697</v>
       </c>
       <c r="F464" t="n">
-        <v>782.3041510009766</v>
+        <v>782.3041488647461</v>
       </c>
       <c r="G464" t="n">
-        <v>-1.336971672529519</v>
+        <v>-1.336971676131582</v>
       </c>
       <c r="H464" t="n">
-        <v>1062.152879449244</v>
+        <v>1062.152756470788</v>
       </c>
       <c r="I464" t="n">
         <v>648.9423872407145</v>
@@ -36155,7 +36155,7 @@
         <v>9.948126987633321</v>
       </c>
       <c r="K464" t="n">
-        <v>48.86515479316671</v>
+        <v>48.86513755722321</v>
       </c>
       <c r="L464" t="n">
         <v>32.69230769230769</v>
@@ -36599,13 +36599,13 @@
         <v>345.0306695556641</v>
       </c>
       <c r="E470" t="n">
-        <v>394.5023258463542</v>
+        <v>394.5023252360026</v>
       </c>
       <c r="F470" t="n">
-        <v>390.8937550354004</v>
+        <v>390.8937545776367</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.08454863345909169</v>
+        <v>-0.08454863355800146</v>
       </c>
       <c r="H470" t="n">
         <v>476.8288845013619</v>
@@ -36756,10 +36756,10 @@
         <v>412.2620546468099</v>
       </c>
       <c r="F472" t="n">
-        <v>412.4930705261231</v>
+        <v>412.4930699157715</v>
       </c>
       <c r="G472" t="n">
-        <v>-1.134812444279099</v>
+        <v>-1.134812482096004</v>
       </c>
       <c r="H472" t="n">
         <v>680.1768451010124</v>
@@ -37929,7 +37929,7 @@
         <v>59.04223877470589</v>
       </c>
       <c r="L487" t="n">
-        <v>21.29120879120879</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="M487" t="n">
         <v>1</v>
@@ -38006,7 +38006,7 @@
         <v>89.49998455479688</v>
       </c>
       <c r="L488" t="n">
-        <v>20.32967032967033</v>
+        <v>20.46703296703297</v>
       </c>
       <c r="M488" t="n">
         <v>1</v>
@@ -38083,7 +38083,7 @@
         <v>59.23469313160479</v>
       </c>
       <c r="L489" t="n">
-        <v>20.19230769230769</v>
+        <v>20.32967032967033</v>
       </c>
       <c r="M489" t="n">
         <v>1</v>
@@ -38160,7 +38160,7 @@
         <v>56.41068418186437</v>
       </c>
       <c r="L490" t="n">
-        <v>19.78021978021978</v>
+        <v>19.91758241758242</v>
       </c>
       <c r="M490" t="n">
         <v>1</v>
@@ -38237,7 +38237,7 @@
         <v>68.31404289362474</v>
       </c>
       <c r="L491" t="n">
-        <v>18.26923076923077</v>
+        <v>18.40659340659341</v>
       </c>
       <c r="M491" t="n">
         <v>1</v>
@@ -38314,7 +38314,7 @@
         <v>57.19345287431354</v>
       </c>
       <c r="L492" t="n">
-        <v>18.13186813186813</v>
+        <v>18.26923076923077</v>
       </c>
       <c r="M492" t="n">
         <v>1</v>
@@ -38391,7 +38391,7 @@
         <v>67.7972002198253</v>
       </c>
       <c r="L493" t="n">
-        <v>17.99450549450549</v>
+        <v>18.13186813186813</v>
       </c>
       <c r="M493" t="n">
         <v>1</v>
@@ -38533,7 +38533,7 @@
         <v>-3.524386812568592</v>
       </c>
       <c r="H495" t="n">
-        <v>390.5481869352945</v>
+        <v>390.5481555478003</v>
       </c>
       <c r="I495" t="n">
         <v>203.5784807586748</v>
@@ -38542,7 +38542,7 @@
         <v>14.03464306803563</v>
       </c>
       <c r="K495" t="n">
-        <v>68.23097015003145</v>
+        <v>68.23095662968039</v>
       </c>
       <c r="L495" t="n">
         <v>16.62087912087912</v>
@@ -38915,7 +38915,7 @@
         <v>2710.704836425781</v>
       </c>
       <c r="G500" t="n">
-        <v>-1.302299970820298</v>
+        <v>-1.302299839218113</v>
       </c>
       <c r="H500" t="n">
         <v>3333.383184200957</v>
@@ -39066,13 +39066,13 @@
         <v>2399.490704752604</v>
       </c>
       <c r="F502" t="n">
-        <v>2398.04636352539</v>
+        <v>2398.046368408203</v>
       </c>
       <c r="G502" t="n">
-        <v>-1.865114962483672</v>
+        <v>-1.86511500777975</v>
       </c>
       <c r="H502" t="n">
-        <v>2861.413278334028</v>
+        <v>2861.413025289686</v>
       </c>
       <c r="I502" t="n">
         <v>1845</v>
@@ -39081,7 +39081,7 @@
         <v>0.8130081300812941</v>
       </c>
       <c r="K502" t="n">
-        <v>53.83942356634562</v>
+        <v>53.83940996181109</v>
       </c>
       <c r="L502" t="n">
         <v>14.14835164835165</v>
@@ -39220,10 +39220,10 @@
         <v>2533.216212565104</v>
       </c>
       <c r="F504" t="n">
-        <v>2509.673229980469</v>
+        <v>2509.673233642578</v>
       </c>
       <c r="G504" t="n">
-        <v>-1.180783888022585</v>
+        <v>-1.180783886319958</v>
       </c>
       <c r="H504" t="n">
         <v>3329.438873827357</v>
@@ -40606,10 +40606,10 @@
         <v>253.0735110473633</v>
       </c>
       <c r="F522" t="n">
-        <v>253.804504776001</v>
+        <v>253.804504699707</v>
       </c>
       <c r="G522" t="n">
-        <v>-0.1799758178170796</v>
+        <v>-0.1799757879190733</v>
       </c>
       <c r="H522" t="n">
         <v>306.197022156633</v>
@@ -40914,10 +40914,10 @@
         <v>1075.124559733073</v>
       </c>
       <c r="F526" t="n">
-        <v>1075.622707519531</v>
+        <v>1075.622708435058</v>
       </c>
       <c r="G526" t="n">
-        <v>-0.6205466665373582</v>
+        <v>-0.6205466099705292</v>
       </c>
       <c r="H526" t="n">
         <v>1294.204229651688</v>
@@ -41145,10 +41145,10 @@
         <v>138.165812479655</v>
       </c>
       <c r="F529" t="n">
-        <v>144.7598886108399</v>
+        <v>144.7598881530762</v>
       </c>
       <c r="G529" t="n">
-        <v>-1.952075143840881</v>
+        <v>-1.952075099227069</v>
       </c>
       <c r="H529" t="n">
         <v>184.9587904135824</v>
@@ -41376,10 +41376,10 @@
         <v>410.7201291910807</v>
       </c>
       <c r="F532" t="n">
-        <v>415.768350982666</v>
+        <v>415.7683512878418</v>
       </c>
       <c r="G532" t="n">
-        <v>-0.3413383894616651</v>
+        <v>-0.3413383892119648</v>
       </c>
       <c r="H532" t="n">
         <v>472.8081629796919</v>
@@ -41607,10 +41607,10 @@
         <v>4527.454114583334</v>
       </c>
       <c r="F535" t="n">
-        <v>4709.337634277344</v>
+        <v>4709.337629394531</v>
       </c>
       <c r="G535" t="n">
-        <v>-1.241286627346072</v>
+        <v>-1.241286729742697</v>
       </c>
       <c r="H535" t="n">
         <v>5612.405266256894</v>
@@ -41684,10 +41684,10 @@
         <v>352.3257368977864</v>
       </c>
       <c r="F536" t="n">
-        <v>353.1676733398438</v>
+        <v>353.1676731872558</v>
       </c>
       <c r="G536" t="n">
-        <v>-0.04490551894171801</v>
+        <v>-0.04490547579441007</v>
       </c>
       <c r="H536" t="n">
         <v>409.9712889887167</v>
@@ -42383,7 +42383,7 @@
         <v>-1.407564550890272</v>
       </c>
       <c r="H545" t="n">
-        <v>286.0804516993438</v>
+        <v>286.0804190389319</v>
       </c>
       <c r="I545" t="n">
         <v>171.952833032562</v>
@@ -42392,7 +42392,7 @@
         <v>9.029896408881367</v>
       </c>
       <c r="K545" t="n">
-        <v>52.59252091892448</v>
+        <v>52.59250349817955</v>
       </c>
       <c r="L545" t="n">
         <v>38.04945054945055</v>
@@ -42451,22 +42451,22 @@
         <v>424.363999633789</v>
       </c>
       <c r="E546" t="n">
-        <v>459.975796101888</v>
+        <v>459.9757965087891</v>
       </c>
       <c r="F546" t="n">
-        <v>460.8226998901367</v>
+        <v>460.822699584961</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.126037559789705</v>
+        <v>-1.126037722379769</v>
       </c>
       <c r="H546" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I546" t="n">
-        <v>379.7399002549519</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J546" t="n">
-        <v>4.044901744128326</v>
+        <v>4.044893408873484</v>
       </c>
       <c r="K546" t="n">
         <v>40.51739809895889</v>
@@ -42999,7 +42999,7 @@
         <v>-2.386097951285937</v>
       </c>
       <c r="H553" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I553" t="n">
         <v>116700</v>
@@ -43008,7 +43008,7 @@
         <v>1.041131105398452</v>
       </c>
       <c r="K553" t="n">
-        <v>38.49678694715229</v>
+        <v>38.49680048030144</v>
       </c>
       <c r="L553" t="n">
         <v>33.7912087912088</v>
@@ -43991,16 +43991,16 @@
         <v>480.0395788574219</v>
       </c>
       <c r="E566" t="n">
-        <v>481.0377701822917</v>
+        <v>481.0377714029948</v>
       </c>
       <c r="F566" t="n">
-        <v>485.4500984191894</v>
+        <v>485.4500994873047</v>
       </c>
       <c r="G566" t="n">
-        <v>-1.28023239928694</v>
+        <v>-1.280232580301699</v>
       </c>
       <c r="H566" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I566" t="n">
         <v>406.2999877929688</v>
@@ -44009,7 +44009,7 @@
         <v>0.9475772136811944</v>
       </c>
       <c r="K566" t="n">
-        <v>33.54577116067947</v>
+        <v>33.54578624222475</v>
       </c>
       <c r="L566" t="n">
         <v>30.63186813186813</v>
@@ -45688,10 +45688,10 @@
         <v>20.03525355021159</v>
       </c>
       <c r="F588" t="n">
-        <v>20.19595464706421</v>
+        <v>20.19595467567444</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.844783812813433</v>
+        <v>-1.844783673763639</v>
       </c>
       <c r="H588" t="n">
         <v>23.83526224893035</v>
@@ -45925,7 +45925,7 @@
         <v>-2.222165156022349</v>
       </c>
       <c r="H591" t="n">
-        <v>2308.784934113526</v>
+        <v>2308.784681838889</v>
       </c>
       <c r="I591" t="n">
         <v>1580</v>
@@ -45934,7 +45934,7 @@
         <v>0.7151929638053778</v>
       </c>
       <c r="K591" t="n">
-        <v>45.08796979009557</v>
+        <v>45.08795393672855</v>
       </c>
       <c r="L591" t="n">
         <v>25</v>
@@ -46150,10 +46150,10 @@
         <v>2940.584458007812</v>
       </c>
       <c r="F594" t="n">
-        <v>3085.240656738281</v>
+        <v>3085.240662841797</v>
       </c>
       <c r="G594" t="n">
-        <v>-3.122186917884207</v>
+        <v>-3.122186911900449</v>
       </c>
       <c r="H594" t="n">
         <v>3923.39201752828</v>
@@ -46535,13 +46535,13 @@
         <v>987.8182104492188</v>
       </c>
       <c r="F599" t="n">
-        <v>1035.42939453125</v>
+        <v>1035.429395751953</v>
       </c>
       <c r="G599" t="n">
-        <v>-2.96040491752072</v>
+        <v>-2.960404914133918</v>
       </c>
       <c r="H599" t="n">
-        <v>1255.178432949836</v>
+        <v>1255.178308316206</v>
       </c>
       <c r="I599" t="n">
         <v>832.5999755859375</v>
@@ -46550,7 +46550,7 @@
         <v>2.852510292627142</v>
       </c>
       <c r="K599" t="n">
-        <v>46.57306810699791</v>
+        <v>46.57305355294483</v>
       </c>
       <c r="L599" t="n">
         <v>23.62637362637362</v>
@@ -46997,10 +46997,10 @@
         <v>1195.100937093099</v>
       </c>
       <c r="F605" t="n">
-        <v>1239.750849304199</v>
+        <v>1239.750851745605</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.885211239554175</v>
+        <v>-2.885211187604464</v>
       </c>
       <c r="H605" t="n">
         <v>1504.476256003898</v>
@@ -47441,7 +47441,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -47450,41 +47450,41 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>431</v>
+        <v>595.1500244140625</v>
       </c>
       <c r="D611" t="n">
-        <v>477.6159979248047</v>
+        <v>651.8819995117187</v>
       </c>
       <c r="E611" t="n">
-        <v>503.562455851237</v>
+        <v>773.0350032552084</v>
       </c>
       <c r="F611" t="n">
-        <v>539.9441944885253</v>
+        <v>787.7417523193359</v>
       </c>
       <c r="G611" t="n">
-        <v>-3.506762247591344</v>
+        <v>-2.431345789636719</v>
       </c>
       <c r="H611" t="n">
-        <v>704.3556293706895</v>
+        <v>1022.200012207031</v>
       </c>
       <c r="I611" t="n">
-        <v>422.5499877929688</v>
+        <v>576.2999877929688</v>
       </c>
       <c r="J611" t="n">
-        <v>1.999766288283844</v>
+        <v>3.270872292273141</v>
       </c>
       <c r="K611" t="n">
-        <v>63.423579900392</v>
+        <v>71.75501474832473</v>
       </c>
       <c r="L611" t="n">
-        <v>21.42857142857143</v>
+        <v>21.29120879120879</v>
       </c>
       <c r="M611" t="n">
         <v>0</v>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/ICICIPRULI/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/MEDPLUS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O611" t="b">
@@ -47518,7 +47518,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -47527,41 +47527,41 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>595.1500244140625</v>
+        <v>817.0499877929688</v>
       </c>
       <c r="D612" t="n">
-        <v>651.8819995117187</v>
+        <v>889.9760021972656</v>
       </c>
       <c r="E612" t="n">
-        <v>773.0350032552084</v>
+        <v>910.0160847981771</v>
       </c>
       <c r="F612" t="n">
-        <v>787.7417523193359</v>
+        <v>933.5243692016602</v>
       </c>
       <c r="G612" t="n">
-        <v>-2.431345789636719</v>
+        <v>-2.329084505798229</v>
       </c>
       <c r="H612" t="n">
-        <v>1022.200012207031</v>
+        <v>1354.175046192178</v>
       </c>
       <c r="I612" t="n">
-        <v>576.2999877929688</v>
+        <v>807.4500122070312</v>
       </c>
       <c r="J612" t="n">
-        <v>3.270872292273141</v>
+        <v>1.188925065428825</v>
       </c>
       <c r="K612" t="n">
-        <v>71.75501474832473</v>
+        <v>65.73955895282512</v>
       </c>
       <c r="L612" t="n">
-        <v>21.15384615384615</v>
+        <v>20.87912087912088</v>
       </c>
       <c r="M612" t="n">
         <v>0</v>
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/MEDPLUS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/UTIAMC/?exchange=NSE</t>
         </is>
       </c>
       <c r="O612" t="b">
@@ -47595,7 +47595,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -47604,31 +47604,31 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>817.0499877929688</v>
+        <v>1114.099975585938</v>
       </c>
       <c r="D613" t="n">
-        <v>889.9760021972656</v>
+        <v>1272.464006347656</v>
       </c>
       <c r="E613" t="n">
-        <v>910.0160847981771</v>
+        <v>1330.495338541667</v>
       </c>
       <c r="F613" t="n">
-        <v>933.5243692016602</v>
+        <v>1336.807503662109</v>
       </c>
       <c r="G613" t="n">
-        <v>-2.329084505798229</v>
+        <v>-2.265793406714789</v>
       </c>
       <c r="H613" t="n">
-        <v>1354.175046192178</v>
+        <v>1771.900024414062</v>
       </c>
       <c r="I613" t="n">
-        <v>807.4500122070312</v>
+        <v>1060.400024414062</v>
       </c>
       <c r="J613" t="n">
-        <v>1.188925065428825</v>
+        <v>5.064122023341855</v>
       </c>
       <c r="K613" t="n">
-        <v>65.73955895282512</v>
+        <v>59.04317953890708</v>
       </c>
       <c r="L613" t="n">
         <v>20.74175824175824</v>
@@ -47638,7 +47638,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/UTIAMC/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/AAVAS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O613" t="b">
@@ -47672,7 +47672,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -47681,31 +47681,31 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>1114.099975585938</v>
+        <v>205.0299987792969</v>
       </c>
       <c r="D614" t="n">
-        <v>1272.464006347656</v>
+        <v>229.2635992431641</v>
       </c>
       <c r="E614" t="n">
-        <v>1330.495338541667</v>
+        <v>236.4154852294922</v>
       </c>
       <c r="F614" t="n">
-        <v>1336.807503662109</v>
+        <v>243.3898638916015</v>
       </c>
       <c r="G614" t="n">
-        <v>-2.265793406714789</v>
+        <v>-3.471288970815378</v>
       </c>
       <c r="H614" t="n">
-        <v>1771.900024414062</v>
+        <v>316.1097009027144</v>
       </c>
       <c r="I614" t="n">
-        <v>1060.400024414062</v>
+        <v>202.5099945068359</v>
       </c>
       <c r="J614" t="n">
-        <v>5.064122023341855</v>
+        <v>1.244385136939941</v>
       </c>
       <c r="K614" t="n">
-        <v>59.04317953890708</v>
+        <v>54.17729248634904</v>
       </c>
       <c r="L614" t="n">
         <v>20.6043956043956</v>
@@ -47715,7 +47715,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/AAVAS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/JIOFIN/?exchange=NSE</t>
         </is>
       </c>
       <c r="O614" t="b">
@@ -47749,7 +47749,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -47758,41 +47758,41 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>205.0299987792969</v>
+        <v>815</v>
       </c>
       <c r="D615" t="n">
-        <v>229.2635992431641</v>
+        <v>969.6379992675782</v>
       </c>
       <c r="E615" t="n">
-        <v>236.4154852294922</v>
+        <v>1012.658130696615</v>
       </c>
       <c r="F615" t="n">
-        <v>243.3898638916015</v>
+        <v>1017.981219482422</v>
       </c>
       <c r="G615" t="n">
-        <v>-3.471288970815378</v>
+        <v>-1.719214785884893</v>
       </c>
       <c r="H615" t="n">
-        <v>316.1097009027144</v>
+        <v>1219.732372328196</v>
       </c>
       <c r="I615" t="n">
-        <v>202.5099945068359</v>
+        <v>797</v>
       </c>
       <c r="J615" t="n">
-        <v>1.244385136939941</v>
+        <v>2.258469259723972</v>
       </c>
       <c r="K615" t="n">
-        <v>54.17729248634904</v>
+        <v>49.66041378260076</v>
       </c>
       <c r="L615" t="n">
-        <v>20.46703296703297</v>
+        <v>20.05494505494505</v>
       </c>
       <c r="M615" t="n">
         <v>0</v>
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/JIOFIN/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/MAXHEALTH/?exchange=NSE</t>
         </is>
       </c>
       <c r="O615" t="b">
@@ -47826,7 +47826,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -47835,41 +47835,41 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>815</v>
+        <v>189.1499938964844</v>
       </c>
       <c r="D616" t="n">
-        <v>969.6379992675782</v>
+        <v>212.1275988769531</v>
       </c>
       <c r="E616" t="n">
-        <v>1012.658130696615</v>
+        <v>226.6395947265625</v>
       </c>
       <c r="F616" t="n">
-        <v>1017.981219482422</v>
+        <v>234.0411203765869</v>
       </c>
       <c r="G616" t="n">
-        <v>-1.719214785884893</v>
+        <v>-2.799758446026923</v>
       </c>
       <c r="H616" t="n">
-        <v>1219.732372328196</v>
+        <v>285.8408427878384</v>
       </c>
       <c r="I616" t="n">
-        <v>797</v>
+        <v>182.1600036621094</v>
       </c>
       <c r="J616" t="n">
-        <v>2.258469259723972</v>
+        <v>3.837280464344306</v>
       </c>
       <c r="K616" t="n">
-        <v>49.66041378260076</v>
+        <v>51.11861063250667</v>
       </c>
       <c r="L616" t="n">
-        <v>19.91758241758242</v>
+        <v>19.78021978021978</v>
       </c>
       <c r="M616" t="n">
         <v>0</v>
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/MAXHEALTH/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/CAMPUS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O616" t="b">
@@ -47903,7 +47903,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -47912,41 +47912,41 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>189.1499938964844</v>
+        <v>739.4000244140625</v>
       </c>
       <c r="D617" t="n">
-        <v>212.1275988769531</v>
+        <v>859.795</v>
       </c>
       <c r="E617" t="n">
-        <v>226.6395947265625</v>
+        <v>902.4742163085938</v>
       </c>
       <c r="F617" t="n">
-        <v>234.0411203765869</v>
+        <v>950.7048034667969</v>
       </c>
       <c r="G617" t="n">
-        <v>-2.799758446026923</v>
+        <v>-2.403507199847377</v>
       </c>
       <c r="H617" t="n">
-        <v>285.8408427878384</v>
+        <v>1211.194575505031</v>
       </c>
       <c r="I617" t="n">
-        <v>182.1600036621094</v>
+        <v>730.8499755859375</v>
       </c>
       <c r="J617" t="n">
-        <v>3.837280464344306</v>
+        <v>1.169877418586518</v>
       </c>
       <c r="K617" t="n">
-        <v>51.11861063250667</v>
+        <v>63.80775432957846</v>
       </c>
       <c r="L617" t="n">
-        <v>19.64285714285714</v>
+        <v>19.50549450549451</v>
       </c>
       <c r="M617" t="n">
         <v>0</v>
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/CAMPUS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/RAMCOCEM/?exchange=NSE</t>
         </is>
       </c>
       <c r="O617" t="b">
@@ -47980,7 +47980,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -47989,31 +47989,31 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>739.4000244140625</v>
+        <v>633.8499755859375</v>
       </c>
       <c r="D618" t="n">
-        <v>859.795</v>
+        <v>653.9640441894531</v>
       </c>
       <c r="E618" t="n">
-        <v>902.4742163085938</v>
+        <v>661.2129813639323</v>
       </c>
       <c r="F618" t="n">
-        <v>950.7048034667969</v>
+        <v>698.0316757202148</v>
       </c>
       <c r="G618" t="n">
-        <v>-2.403507199847377</v>
+        <v>-4.361821339171234</v>
       </c>
       <c r="H618" t="n">
-        <v>1211.194575505031</v>
+        <v>1140.477361200229</v>
       </c>
       <c r="I618" t="n">
-        <v>730.8499755859375</v>
+        <v>577.3964738257137</v>
       </c>
       <c r="J618" t="n">
-        <v>1.169877418586518</v>
+        <v>9.777250869956688</v>
       </c>
       <c r="K618" t="n">
-        <v>63.80775432957846</v>
+        <v>79.92859590251777</v>
       </c>
       <c r="L618" t="n">
         <v>19.36813186813187</v>
@@ -48023,7 +48023,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/RAMCOCEM/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/BATAINDIA/?exchange=NSE</t>
         </is>
       </c>
       <c r="O618" t="b">
@@ -48057,7 +48057,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -48066,31 +48066,31 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>633.8499755859375</v>
+        <v>1279.5</v>
       </c>
       <c r="D619" t="n">
-        <v>653.9640441894531</v>
+        <v>1467.551994628906</v>
       </c>
       <c r="E619" t="n">
-        <v>661.2129813639323</v>
+        <v>1536.396207682292</v>
       </c>
       <c r="F619" t="n">
-        <v>698.0316757202148</v>
+        <v>1578.640587768555</v>
       </c>
       <c r="G619" t="n">
-        <v>-4.361821339171234</v>
+        <v>-3.260035925348637</v>
       </c>
       <c r="H619" t="n">
-        <v>1140.477361200229</v>
+        <v>2062.371871375786</v>
       </c>
       <c r="I619" t="n">
-        <v>577.3964738257137</v>
+        <v>1270</v>
       </c>
       <c r="J619" t="n">
-        <v>9.777250869956688</v>
+        <v>0.7480314960629952</v>
       </c>
       <c r="K619" t="n">
-        <v>79.92859590251777</v>
+        <v>61.18576564093679</v>
       </c>
       <c r="L619" t="n">
         <v>19.23076923076923</v>
@@ -48100,7 +48100,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/BATAINDIA/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/CHOLAHLDNG/?exchange=NSE</t>
         </is>
       </c>
       <c r="O619" t="b">
@@ -48134,7 +48134,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -48143,31 +48143,31 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1279.5</v>
+        <v>1605</v>
       </c>
       <c r="D620" t="n">
-        <v>1467.551994628906</v>
+        <v>1833.420007324219</v>
       </c>
       <c r="E620" t="n">
-        <v>1536.396207682292</v>
+        <v>1963.762901204427</v>
       </c>
       <c r="F620" t="n">
-        <v>1578.640587768555</v>
+        <v>2001.456430664063</v>
       </c>
       <c r="G620" t="n">
-        <v>-3.260035925348637</v>
+        <v>-1.707679009250007</v>
       </c>
       <c r="H620" t="n">
-        <v>2062.371871375786</v>
+        <v>2278.114761044847</v>
       </c>
       <c r="I620" t="n">
-        <v>1270</v>
+        <v>1580</v>
       </c>
       <c r="J620" t="n">
-        <v>0.7480314960629952</v>
+        <v>1.582278481012667</v>
       </c>
       <c r="K620" t="n">
-        <v>61.18576564093679</v>
+        <v>41.93861439531761</v>
       </c>
       <c r="L620" t="n">
         <v>19.09340659340659</v>
@@ -48177,7 +48177,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/CHOLAHLDNG/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/COLPAL/?exchange=NSE</t>
         </is>
       </c>
       <c r="O620" t="b">
@@ -48211,7 +48211,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -48220,31 +48220,31 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1605</v>
+        <v>687.2000122070312</v>
       </c>
       <c r="D621" t="n">
-        <v>1833.420007324219</v>
+        <v>820.7400024414062</v>
       </c>
       <c r="E621" t="n">
-        <v>1963.762901204427</v>
+        <v>831.2864522298177</v>
       </c>
       <c r="F621" t="n">
-        <v>2001.456430664063</v>
+        <v>836.1683938598633</v>
       </c>
       <c r="G621" t="n">
-        <v>-1.707679009250007</v>
+        <v>-2.283350382858529</v>
       </c>
       <c r="H621" t="n">
-        <v>2278.114761044847</v>
+        <v>1017.299987792969</v>
       </c>
       <c r="I621" t="n">
-        <v>1580</v>
+        <v>666.0087356197063</v>
       </c>
       <c r="J621" t="n">
-        <v>1.582278481012667</v>
+        <v>3.181831626818976</v>
       </c>
       <c r="K621" t="n">
-        <v>41.93861439531761</v>
+        <v>48.03550199683188</v>
       </c>
       <c r="L621" t="n">
         <v>18.95604395604396</v>
@@ -48254,7 +48254,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/COLPAL/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/ARE&amp;M/?exchange=NSE</t>
         </is>
       </c>
       <c r="O621" t="b">
@@ -48288,7 +48288,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -48297,31 +48297,31 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>687.2000122070312</v>
+        <v>1572.800048828125</v>
       </c>
       <c r="D622" t="n">
-        <v>820.7400024414062</v>
+        <v>1675.796005859375</v>
       </c>
       <c r="E622" t="n">
-        <v>831.2864522298177</v>
+        <v>1857.661948242187</v>
       </c>
       <c r="F622" t="n">
-        <v>836.1683938598633</v>
+        <v>1923.90457824707</v>
       </c>
       <c r="G622" t="n">
-        <v>-2.283350382858529</v>
+        <v>-3.207484584988862</v>
       </c>
       <c r="H622" t="n">
-        <v>1017.299987792969</v>
+        <v>2455.004088492464</v>
       </c>
       <c r="I622" t="n">
-        <v>666.0087356197063</v>
+        <v>1540</v>
       </c>
       <c r="J622" t="n">
-        <v>3.181831626818976</v>
+        <v>2.129873300527607</v>
       </c>
       <c r="K622" t="n">
-        <v>48.03550199683188</v>
+        <v>56.09130291683668</v>
       </c>
       <c r="L622" t="n">
         <v>18.81868131868132</v>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/ARE&amp;M/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/INDIAMART/?exchange=NSE</t>
         </is>
       </c>
       <c r="O622" t="b">
@@ -48365,7 +48365,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -48374,31 +48374,31 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>1572.800048828125</v>
+        <v>1095.5</v>
       </c>
       <c r="D623" t="n">
-        <v>1675.796005859375</v>
+        <v>1261.853999023438</v>
       </c>
       <c r="E623" t="n">
-        <v>1857.661948242187</v>
+        <v>1341.130109863281</v>
       </c>
       <c r="F623" t="n">
-        <v>1923.90457824707</v>
+        <v>1357.395094604492</v>
       </c>
       <c r="G623" t="n">
-        <v>-3.207484584988862</v>
+        <v>-2.969057556170762</v>
       </c>
       <c r="H623" t="n">
-        <v>2455.004088492464</v>
+        <v>1730.712625699126</v>
       </c>
       <c r="I623" t="n">
-        <v>1540</v>
+        <v>1087.900024414062</v>
       </c>
       <c r="J623" t="n">
-        <v>2.129873300527607</v>
+        <v>0.6985913609139693</v>
       </c>
       <c r="K623" t="n">
-        <v>56.09130291683668</v>
+        <v>57.98380882693983</v>
       </c>
       <c r="L623" t="n">
         <v>18.68131868131868</v>
@@ -48408,7 +48408,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/INDIAMART/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/ERIS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O623" t="b">
@@ -48442,7 +48442,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -48451,31 +48451,31 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>1095.5</v>
+        <v>576.7999877929688</v>
       </c>
       <c r="D624" t="n">
-        <v>1261.853999023438</v>
+        <v>639.8270007324219</v>
       </c>
       <c r="E624" t="n">
-        <v>1341.130109863281</v>
+        <v>681.6198921712239</v>
       </c>
       <c r="F624" t="n">
-        <v>1357.395094604492</v>
+        <v>688.9288272094726</v>
       </c>
       <c r="G624" t="n">
-        <v>-2.969057556170762</v>
+        <v>-2.037859981913759</v>
       </c>
       <c r="H624" t="n">
-        <v>1730.712625699126</v>
+        <v>919.857266212225</v>
       </c>
       <c r="I624" t="n">
-        <v>1087.900024414062</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="J624" t="n">
-        <v>0.6985913609139693</v>
+        <v>1.184106682667174</v>
       </c>
       <c r="K624" t="n">
-        <v>57.98380882693983</v>
+        <v>59.47595105400558</v>
       </c>
       <c r="L624" t="n">
         <v>18.54395604395604</v>
@@ -48485,7 +48485,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/ERIS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/TATACHEM/?exchange=NSE</t>
         </is>
       </c>
       <c r="O624" t="b">
@@ -48519,7 +48519,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -48528,41 +48528,41 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>576.7999877929688</v>
+        <v>101.8499984741211</v>
       </c>
       <c r="D625" t="n">
-        <v>639.8270007324219</v>
+        <v>120.5975999450684</v>
       </c>
       <c r="E625" t="n">
-        <v>681.6198921712239</v>
+        <v>131.0434666442871</v>
       </c>
       <c r="F625" t="n">
-        <v>688.9288272094726</v>
+        <v>132.3976999282837</v>
       </c>
       <c r="G625" t="n">
-        <v>-2.037859981913759</v>
+        <v>-1.65437446986082</v>
       </c>
       <c r="H625" t="n">
-        <v>919.857266212225</v>
+        <v>163.8500061035156</v>
       </c>
       <c r="I625" t="n">
-        <v>570.0499877929688</v>
+        <v>100.9100036621094</v>
       </c>
       <c r="J625" t="n">
-        <v>1.184106682667174</v>
+        <v>0.9315179644222793</v>
       </c>
       <c r="K625" t="n">
-        <v>59.47595105400558</v>
+        <v>60.87384247251415</v>
       </c>
       <c r="L625" t="n">
-        <v>18.40659340659341</v>
+        <v>17.99450549450549</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/TATACHEM/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/HEMIPROP/?exchange=NSE</t>
         </is>
       </c>
       <c r="O625" t="b">
@@ -48596,7 +48596,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -48605,31 +48605,31 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>101.8499984741211</v>
+        <v>642.5999755859375</v>
       </c>
       <c r="D626" t="n">
-        <v>120.5975999450684</v>
+        <v>749.6599963378907</v>
       </c>
       <c r="E626" t="n">
-        <v>131.0434666442871</v>
+        <v>875.6489530436198</v>
       </c>
       <c r="F626" t="n">
-        <v>132.3976999282837</v>
+        <v>907.5170733642578</v>
       </c>
       <c r="G626" t="n">
-        <v>-1.65437446986082</v>
+        <v>-1.804771771167624</v>
       </c>
       <c r="H626" t="n">
-        <v>163.8500061035156</v>
+        <v>1282.80960014975</v>
       </c>
       <c r="I626" t="n">
-        <v>100.9100036621094</v>
+        <v>631.3499755859375</v>
       </c>
       <c r="J626" t="n">
-        <v>0.9315179644222793</v>
+        <v>1.781896006182504</v>
       </c>
       <c r="K626" t="n">
-        <v>60.87384247251415</v>
+        <v>99.62801881217854</v>
       </c>
       <c r="L626" t="n">
         <v>17.85714285714286</v>
@@ -48639,7 +48639,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/HEMIPROP/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/SHARDACROP/?exchange=NSE</t>
         </is>
       </c>
       <c r="O626" t="b">
@@ -48673,7 +48673,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -48682,31 +48682,31 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>642.5999755859375</v>
+        <v>428.7999877929688</v>
       </c>
       <c r="D627" t="n">
-        <v>749.6599963378907</v>
+        <v>450.4660632324219</v>
       </c>
       <c r="E627" t="n">
-        <v>875.6489530436198</v>
+        <v>489.6504225667318</v>
       </c>
       <c r="F627" t="n">
-        <v>907.5170745849609</v>
+        <v>497.2640130615234</v>
       </c>
       <c r="G627" t="n">
-        <v>-1.80477189848266</v>
+        <v>-2.462913457890448</v>
       </c>
       <c r="H627" t="n">
-        <v>1282.80960014975</v>
+        <v>749.8838143552388</v>
       </c>
       <c r="I627" t="n">
-        <v>631.3499755859375</v>
+        <v>400.6499938964844</v>
       </c>
       <c r="J627" t="n">
-        <v>1.781896006182504</v>
+        <v>7.026081199381595</v>
       </c>
       <c r="K627" t="n">
-        <v>99.62801881217854</v>
+        <v>74.87962586353763</v>
       </c>
       <c r="L627" t="n">
         <v>17.71978021978022</v>
@@ -48716,7 +48716,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/SHARDACROP/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/TRANSRAILL/?exchange=NSE</t>
         </is>
       </c>
       <c r="O627" t="b">
@@ -48750,7 +48750,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -48759,31 +48759,31 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>428.7999877929688</v>
+        <v>264.5</v>
       </c>
       <c r="D628" t="n">
-        <v>450.4660632324219</v>
+        <v>294.5290008544922</v>
       </c>
       <c r="E628" t="n">
-        <v>489.6504201253255</v>
+        <v>304.5709995524089</v>
       </c>
       <c r="F628" t="n">
-        <v>497.2640103149414</v>
+        <v>320.7430001831055</v>
       </c>
       <c r="G628" t="n">
-        <v>-2.462913529544208</v>
+        <v>-2.704170091677327</v>
       </c>
       <c r="H628" t="n">
-        <v>749.8838766016545</v>
+        <v>447.2999877929688</v>
       </c>
       <c r="I628" t="n">
-        <v>400.6499938964844</v>
+        <v>260.6499938964844</v>
       </c>
       <c r="J628" t="n">
-        <v>7.026081199381595</v>
+        <v>1.477078915660601</v>
       </c>
       <c r="K628" t="n">
-        <v>74.87964037995962</v>
+        <v>69.11152657579159</v>
       </c>
       <c r="L628" t="n">
         <v>17.58241758241758</v>
@@ -48793,7 +48793,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/TRANSRAILL/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/VIPIND/?exchange=NSE</t>
         </is>
       </c>
       <c r="O628" t="b">
@@ -48827,7 +48827,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -48836,31 +48836,31 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>264.5</v>
+        <v>422.2000122070312</v>
       </c>
       <c r="D629" t="n">
-        <v>294.5290008544922</v>
+        <v>476.0299981689453</v>
       </c>
       <c r="E629" t="n">
-        <v>304.5709995524089</v>
+        <v>502.4989149983724</v>
       </c>
       <c r="F629" t="n">
-        <v>320.7430001831055</v>
+        <v>538.7254997253418</v>
       </c>
       <c r="G629" t="n">
-        <v>-2.704170091677327</v>
+        <v>-3.617240183370263</v>
       </c>
       <c r="H629" t="n">
-        <v>447.2999877929688</v>
+        <v>704.3556293706895</v>
       </c>
       <c r="I629" t="n">
-        <v>260.6499938964844</v>
+        <v>413.3999938964844</v>
       </c>
       <c r="J629" t="n">
-        <v>1.477078915660601</v>
+        <v>2.128693381826796</v>
       </c>
       <c r="K629" t="n">
-        <v>69.11152657579159</v>
+        <v>66.82984580902844</v>
       </c>
       <c r="L629" t="n">
         <v>17.44505494505495</v>
@@ -48870,7 +48870,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/VIPIND/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/ICICIPRULI/?exchange=NSE</t>
         </is>
       </c>
       <c r="O629" t="b">
@@ -49390,7 +49390,7 @@
         <v>-4.142725469058838</v>
       </c>
       <c r="H636" t="n">
-        <v>605.9581737112406</v>
+        <v>605.9581114957105</v>
       </c>
       <c r="I636" t="n">
         <v>326.057353105007</v>
@@ -49399,7 +49399,7 @@
         <v>7.266404719712849</v>
       </c>
       <c r="K636" t="n">
-        <v>73.25466010328539</v>
+        <v>73.25464231471351</v>
       </c>
       <c r="L636" t="n">
         <v>15.93406593406593</v>
@@ -49538,13 +49538,13 @@
         <v>504.8909067789713</v>
       </c>
       <c r="F638" t="n">
-        <v>531.4516557312012</v>
+        <v>531.4516560363769</v>
       </c>
       <c r="G638" t="n">
-        <v>-4.24440752828813</v>
+        <v>-4.24440752595433</v>
       </c>
       <c r="H638" t="n">
-        <v>725.6811213920008</v>
+        <v>725.6811828531856</v>
       </c>
       <c r="I638" t="n">
         <v>437.4500122070312</v>
@@ -49553,7 +49553,7 @@
         <v>0.9029561273811826</v>
       </c>
       <c r="K638" t="n">
-        <v>64.40442488138889</v>
+        <v>64.40443880553607</v>
       </c>
       <c r="L638" t="n">
         <v>15.52197802197802</v>
@@ -49612,13 +49612,13 @@
         <v>111.2349839782715</v>
       </c>
       <c r="E639" t="n">
-        <v>119.6876489766439</v>
+        <v>119.6876490783691</v>
       </c>
       <c r="F639" t="n">
-        <v>121.6343118286133</v>
+        <v>121.6343117141724</v>
       </c>
       <c r="G639" t="n">
-        <v>-2.327443139276797</v>
+        <v>-2.327443081577352</v>
       </c>
       <c r="H639" t="n">
         <v>154.8912966301784</v>
@@ -49689,16 +49689,16 @@
         <v>235.8212628173828</v>
       </c>
       <c r="E640" t="n">
-        <v>243.9094573974609</v>
+        <v>243.9094576009115</v>
       </c>
       <c r="F640" t="n">
-        <v>247.6625965881348</v>
+        <v>247.6625973510742</v>
       </c>
       <c r="G640" t="n">
-        <v>-2.968579067453836</v>
+        <v>-2.968579058580423</v>
       </c>
       <c r="H640" t="n">
-        <v>345.1977086145358</v>
+        <v>345.1977393758356</v>
       </c>
       <c r="I640" t="n">
         <v>202.1900024414062</v>
@@ -49707,7 +49707,7 @@
         <v>1.112814665825046</v>
       </c>
       <c r="K640" t="n">
-        <v>68.85037394453737</v>
+        <v>68.85038899115226</v>
       </c>
       <c r="L640" t="n">
         <v>15.10989010989011</v>
@@ -49769,10 +49769,10 @@
         <v>251.3467742919922</v>
       </c>
       <c r="F641" t="n">
-        <v>258.4341523742676</v>
+        <v>258.434151763916</v>
       </c>
       <c r="G641" t="n">
-        <v>-4.002319430624879</v>
+        <v>-4.002319439698954</v>
       </c>
       <c r="H641" t="n">
         <v>340.0564252807892</v>
@@ -50154,10 +50154,10 @@
         <v>1444.625733235677</v>
       </c>
       <c r="F646" t="n">
-        <v>1461.838257446289</v>
+        <v>1461.838256835938</v>
       </c>
       <c r="G646" t="n">
-        <v>-2.447349704763246</v>
+        <v>-2.447349745493754</v>
       </c>
       <c r="H646" t="n">
         <v>1853.278860564699</v>
@@ -50391,7 +50391,7 @@
         <v>-4.800792770341056</v>
       </c>
       <c r="H649" t="n">
-        <v>523.0941269255326</v>
+        <v>523.09418899518</v>
       </c>
       <c r="I649" t="n">
         <v>299</v>
@@ -50400,7 +50400,7 @@
         <v>0.7190615038409343</v>
       </c>
       <c r="K649" t="n">
-        <v>73.69886685282087</v>
+        <v>73.69888746369544</v>
       </c>
       <c r="L649" t="n">
         <v>12.63736263736264</v>
@@ -50921,16 +50921,16 @@
         <v>173.1591482543945</v>
       </c>
       <c r="E656" t="n">
-        <v>189.6886681111654</v>
+        <v>189.6886680094401</v>
       </c>
       <c r="F656" t="n">
-        <v>190.759981918335</v>
+        <v>190.7599819946289</v>
       </c>
       <c r="G656" t="n">
-        <v>-2.792131064981374</v>
+        <v>-2.792131063895864</v>
       </c>
       <c r="H656" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I656" t="n">
         <v>144.1399993896484</v>
@@ -50939,7 +50939,7 @@
         <v>1.304290891337079</v>
       </c>
       <c r="K656" t="n">
-        <v>63.8259699629762</v>
+        <v>63.82595938809123</v>
       </c>
       <c r="L656" t="n">
         <v>11.26373626373626</v>
@@ -51540,13 +51540,13 @@
         <v>120.4781903076172</v>
       </c>
       <c r="F664" t="n">
-        <v>122.8329398345947</v>
+        <v>122.8329397583008</v>
       </c>
       <c r="G664" t="n">
-        <v>-2.783428704103919</v>
+        <v>-2.783428823189427</v>
       </c>
       <c r="H664" t="n">
-        <v>154.1041427094461</v>
+        <v>154.1041584954392</v>
       </c>
       <c r="I664" t="n">
         <v>93.25</v>
@@ -51555,7 +51555,7 @@
         <v>1.222519452706106</v>
       </c>
       <c r="K664" t="n">
-        <v>63.26320977426177</v>
+        <v>63.26322649848377</v>
       </c>
       <c r="L664" t="n">
         <v>10.02747252747253</v>
@@ -51848,10 +51848,10 @@
         <v>89.42943984985351</v>
       </c>
       <c r="F668" t="n">
-        <v>94.7670626449585</v>
+        <v>94.76706253051758</v>
       </c>
       <c r="G668" t="n">
-        <v>-4.119226228948902</v>
+        <v>-4.119226344734739</v>
       </c>
       <c r="H668" t="n">
         <v>133.7014439272579</v>
@@ -52307,25 +52307,25 @@
         <v>473.2200091552734</v>
       </c>
       <c r="E674" t="n">
-        <v>501.535874633789</v>
+        <v>501.5358754475911</v>
       </c>
       <c r="F674" t="n">
-        <v>517.7844271850586</v>
+        <v>517.7844291687012</v>
       </c>
       <c r="G674" t="n">
-        <v>-4.905698028318895</v>
+        <v>-4.905697957149135</v>
       </c>
       <c r="H674" t="n">
-        <v>756.8457268274816</v>
+        <v>756.8455981427298</v>
       </c>
       <c r="I674" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J674" t="n">
-        <v>2.433498113876964</v>
+        <v>2.433505720465856</v>
       </c>
       <c r="K674" t="n">
-        <v>81.93406894891385</v>
+        <v>81.93403801507928</v>
       </c>
       <c r="L674" t="n">
         <v>8.653846153846153</v>
@@ -52692,16 +52692,16 @@
         <v>82.04140151977539</v>
       </c>
       <c r="E679" t="n">
-        <v>90.80596557617187</v>
+        <v>90.80596537272136</v>
       </c>
       <c r="F679" t="n">
-        <v>92.75849937438964</v>
+        <v>92.7584992980957</v>
       </c>
       <c r="G679" t="n">
-        <v>-4.129238011700931</v>
+        <v>-4.129237825962672</v>
       </c>
       <c r="H679" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I679" t="n">
         <v>67.30000305175781</v>
@@ -52710,7 +52710,7 @@
         <v>0.8915281529179975</v>
       </c>
       <c r="K679" t="n">
-        <v>83.83992172208448</v>
+        <v>83.83991013982144</v>
       </c>
       <c r="L679" t="n">
         <v>7.829670329670329</v>
@@ -53465,10 +53465,10 @@
         <v>2660.802996419271</v>
       </c>
       <c r="F689" t="n">
-        <v>2779.434033203125</v>
+        <v>2779.434030761719</v>
       </c>
       <c r="G689" t="n">
-        <v>-3.994814788473777</v>
+        <v>-3.994814751362341</v>
       </c>
       <c r="H689" t="n">
         <v>3812.926349899466</v>
@@ -54392,7 +54392,7 @@
         <v>258.7240942382812</v>
       </c>
       <c r="G701" t="n">
-        <v>-5.121411167647261</v>
+        <v>-5.121411273828946</v>
       </c>
       <c r="H701" t="n">
         <v>398.2045017598045</v>
@@ -54466,10 +54466,10 @@
         <v>68.49998133341471</v>
       </c>
       <c r="F702" t="n">
-        <v>69.790775680542</v>
+        <v>69.79077575683594</v>
       </c>
       <c r="G702" t="n">
-        <v>-2.430192444692414</v>
+        <v>-2.430192285996291</v>
       </c>
       <c r="H702" t="n">
         <v>89.37738100905904</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1561,16 +1561,16 @@
         <v>225.5</v>
       </c>
       <c r="D15" t="n">
-        <v>206.6969708251953</v>
+        <v>206.6969711303711</v>
       </c>
       <c r="E15" t="n">
-        <v>165.0934440104167</v>
+        <v>165.0934430440267</v>
       </c>
       <c r="F15" t="n">
-        <v>160.0688959503174</v>
+        <v>160.0688949203491</v>
       </c>
       <c r="G15" t="n">
-        <v>5.344495937823179</v>
+        <v>5.344496185626668</v>
       </c>
       <c r="H15" t="n">
         <v>248.3999938964844</v>
@@ -2106,19 +2106,19 @@
         <v>637.7582503255209</v>
       </c>
       <c r="F22" t="n">
-        <v>611.297085571289</v>
+        <v>611.2970849609375</v>
       </c>
       <c r="G22" t="n">
-        <v>2.636647046222618</v>
+        <v>2.636647101514522</v>
       </c>
       <c r="H22" t="n">
         <v>778.17849291017</v>
       </c>
       <c r="I22" t="n">
-        <v>474.4105170606431</v>
+        <v>474.4105474900205</v>
       </c>
       <c r="J22" t="n">
-        <v>51.14546621682703</v>
+        <v>51.14545652213862</v>
       </c>
       <c r="K22" t="n">
         <v>8.524999115522004</v>
@@ -2337,10 +2337,10 @@
         <v>1547.41833984375</v>
       </c>
       <c r="F25" t="n">
-        <v>1529.27548034668</v>
+        <v>1529.275483398437</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1778686619981595</v>
+        <v>0.1778687016958491</v>
       </c>
       <c r="H25" t="n">
         <v>2021.199951171875</v>
@@ -3184,10 +3184,10 @@
         <v>677.6434802246093</v>
       </c>
       <c r="F36" t="n">
-        <v>632.7774435424805</v>
+        <v>632.7774433898926</v>
       </c>
       <c r="G36" t="n">
-        <v>5.817060259158513</v>
+        <v>5.817060179639721</v>
       </c>
       <c r="H36" t="n">
         <v>844</v>
@@ -4031,10 +4031,10 @@
         <v>11171.19533203125</v>
       </c>
       <c r="F47" t="n">
-        <v>10705.86282226562</v>
+        <v>10705.86283935547</v>
       </c>
       <c r="G47" t="n">
-        <v>4.434433783135328</v>
+        <v>4.434433775742708</v>
       </c>
       <c r="H47" t="n">
         <v>14498</v>
@@ -4647,19 +4647,19 @@
         <v>1429.280594075521</v>
       </c>
       <c r="F55" t="n">
-        <v>1376.168594970703</v>
+        <v>1376.168597412109</v>
       </c>
       <c r="G55" t="n">
-        <v>3.692858376133823</v>
+        <v>3.69285851240353</v>
       </c>
       <c r="H55" t="n">
         <v>1766.733060850261</v>
       </c>
       <c r="I55" t="n">
-        <v>971.8169883351571</v>
+        <v>971.816928508411</v>
       </c>
       <c r="J55" t="n">
-        <v>54.00018661433348</v>
+        <v>54.00019609485373</v>
       </c>
       <c r="K55" t="n">
         <v>18.04978549184879</v>
@@ -4801,10 +4801,10 @@
         <v>144.157819925944</v>
       </c>
       <c r="F57" t="n">
-        <v>138.3449015808106</v>
+        <v>138.3449016952515</v>
       </c>
       <c r="G57" t="n">
-        <v>3.345410614745159</v>
+        <v>3.345410641334801</v>
       </c>
       <c r="H57" t="n">
         <v>173.2700042724609</v>
@@ -6030,22 +6030,22 @@
         <v>1916.437998046875</v>
       </c>
       <c r="E73" t="n">
-        <v>1694.514658203125</v>
+        <v>1694.514664713542</v>
       </c>
       <c r="F73" t="n">
-        <v>1621.725526123047</v>
+        <v>1621.725525512695</v>
       </c>
       <c r="G73" t="n">
-        <v>3.383635663458917</v>
+        <v>3.383635544097618</v>
       </c>
       <c r="H73" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I73" t="n">
-        <v>1266.161452106784</v>
+        <v>1266.16157090969</v>
       </c>
       <c r="J73" t="n">
-        <v>45.17895392513076</v>
+        <v>45.17894030310814</v>
       </c>
       <c r="K73" t="n">
         <v>10.90197093555057</v>
@@ -7804,13 +7804,13 @@
         <v>4266.073772786458</v>
       </c>
       <c r="F96" t="n">
-        <v>4326.074367675781</v>
+        <v>4326.074370117188</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5306401374185921</v>
+        <v>0.5306400230471464</v>
       </c>
       <c r="H96" t="n">
-        <v>5005.771680286142</v>
+        <v>5005.772176274182</v>
       </c>
       <c r="I96" t="n">
         <v>3669.905008549105</v>
@@ -7819,7 +7819,7 @@
         <v>29.46111920031942</v>
       </c>
       <c r="K96" t="n">
-        <v>5.360265567873923</v>
+        <v>5.360276007309617</v>
       </c>
       <c r="L96" t="n">
         <v>73.35164835164835</v>
@@ -8805,10 +8805,10 @@
         <v>270.5692627970378</v>
       </c>
       <c r="F109" t="n">
-        <v>252.2203276062012</v>
+        <v>252.2203274536133</v>
       </c>
       <c r="G109" t="n">
-        <v>6.249394013447573</v>
+        <v>6.249394017464605</v>
       </c>
       <c r="H109" t="n">
         <v>388.75</v>
@@ -9264,13 +9264,13 @@
         <v>1447.603981933594</v>
       </c>
       <c r="E115" t="n">
-        <v>1232.616174723307</v>
+        <v>1232.616171061198</v>
       </c>
       <c r="F115" t="n">
-        <v>1117.495636901856</v>
+        <v>1117.495632324219</v>
       </c>
       <c r="G115" t="n">
-        <v>8.58223329893284</v>
+        <v>8.582233465895573</v>
       </c>
       <c r="H115" t="n">
         <v>1681</v>
@@ -10499,19 +10499,19 @@
         <v>4615.380185546875</v>
       </c>
       <c r="F131" t="n">
-        <v>4485.748026123047</v>
+        <v>4485.748029785156</v>
       </c>
       <c r="G131" t="n">
-        <v>2.446630762965296</v>
+        <v>2.44663078947982</v>
       </c>
       <c r="H131" t="n">
         <v>5250</v>
       </c>
       <c r="I131" t="n">
-        <v>3474.721889686419</v>
+        <v>3474.722128459666</v>
       </c>
       <c r="J131" t="n">
-        <v>30.20897919263577</v>
+        <v>30.20897024503661</v>
       </c>
       <c r="K131" t="n">
         <v>16.03748813804835</v>
@@ -11654,10 +11654,10 @@
         <v>161.096474609375</v>
       </c>
       <c r="F146" t="n">
-        <v>156.585650138855</v>
+        <v>156.5856502151489</v>
       </c>
       <c r="G146" t="n">
-        <v>2.317501776162456</v>
+        <v>2.317502081054879</v>
       </c>
       <c r="H146" t="n">
         <v>233.3500061035156</v>
@@ -11805,13 +11805,13 @@
         <v>1976.217802734375</v>
       </c>
       <c r="E148" t="n">
-        <v>1813.873224283854</v>
+        <v>1813.873228352865</v>
       </c>
       <c r="F148" t="n">
-        <v>1789.139586181641</v>
+        <v>1789.139591674805</v>
       </c>
       <c r="G148" t="n">
-        <v>1.439513936967396</v>
+        <v>1.439513862277098</v>
       </c>
       <c r="H148" t="n">
         <v>2256.187656125729</v>
@@ -12655,10 +12655,10 @@
         <v>243.8010990397135</v>
       </c>
       <c r="F159" t="n">
-        <v>230.88173828125</v>
+        <v>230.8817382049561</v>
       </c>
       <c r="G159" t="n">
-        <v>4.877224267524083</v>
+        <v>4.877224160174798</v>
       </c>
       <c r="H159" t="n">
         <v>321.3999938964844</v>
@@ -12963,10 +12963,10 @@
         <v>577.0992980957031</v>
       </c>
       <c r="F163" t="n">
-        <v>547.2160285949707</v>
+        <v>547.2160296630859</v>
       </c>
       <c r="G163" t="n">
-        <v>4.456752957141563</v>
+        <v>4.456752887204152</v>
       </c>
       <c r="H163" t="n">
         <v>795.731978165477</v>
@@ -13579,10 +13579,10 @@
         <v>1037.063870442708</v>
       </c>
       <c r="F171" t="n">
-        <v>999.2296383666992</v>
+        <v>999.2296395874023</v>
       </c>
       <c r="G171" t="n">
-        <v>1.307608484858491</v>
+        <v>1.307608451895126</v>
       </c>
       <c r="H171" t="n">
         <v>1331.075409591023</v>
@@ -14192,13 +14192,13 @@
         <v>1280.438725585937</v>
       </c>
       <c r="E179" t="n">
-        <v>1236.536364339193</v>
+        <v>1236.536370849609</v>
       </c>
       <c r="F179" t="n">
-        <v>1299.570631408691</v>
+        <v>1299.570643005371</v>
       </c>
       <c r="G179" t="n">
-        <v>-2.554692391197133</v>
+        <v>-2.554692101403044</v>
       </c>
       <c r="H179" t="n">
         <v>1713.752567939176</v>
@@ -14426,13 +14426,13 @@
         <v>5209.301298828125</v>
       </c>
       <c r="F182" t="n">
-        <v>5320.821628417969</v>
+        <v>5320.821633300781</v>
       </c>
       <c r="G182" t="n">
-        <v>-1.462887079771646</v>
+        <v>-1.462887033897453</v>
       </c>
       <c r="H182" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I182" t="n">
         <v>4229.809203861739</v>
@@ -14441,7 +14441,7 @@
         <v>35.40799889439214</v>
       </c>
       <c r="K182" t="n">
-        <v>14.40689144479781</v>
+        <v>14.40688277507316</v>
       </c>
       <c r="L182" t="n">
         <v>69.0934065934066</v>
@@ -14971,7 +14971,7 @@
         <v>1.755074939903611</v>
       </c>
       <c r="H189" t="n">
-        <v>1278.952852189353</v>
+        <v>1278.952725191461</v>
       </c>
       <c r="I189" t="n">
         <v>865.2617122743181</v>
@@ -14980,7 +14980,7 @@
         <v>31.35909742249126</v>
       </c>
       <c r="K189" t="n">
-        <v>12.52444832492894</v>
+        <v>12.52443715143825</v>
       </c>
       <c r="L189" t="n">
         <v>62.91208791208791</v>
@@ -15042,10 +15042,10 @@
         <v>1965.222227376302</v>
       </c>
       <c r="F190" t="n">
-        <v>1793.036875610352</v>
+        <v>1793.036874389648</v>
       </c>
       <c r="G190" t="n">
-        <v>6.234208724040591</v>
+        <v>6.234208882216086</v>
       </c>
       <c r="H190" t="n">
         <v>2714.261178227147</v>
@@ -15427,10 +15427,10 @@
         <v>79.37681729634603</v>
       </c>
       <c r="F195" t="n">
-        <v>75.8667672920227</v>
+        <v>75.8667673110962</v>
       </c>
       <c r="G195" t="n">
-        <v>3.842103662734742</v>
+        <v>3.842103743060932</v>
       </c>
       <c r="H195" t="n">
         <v>94.5</v>
@@ -17820,7 +17820,7 @@
         <v>-1.168610449928753</v>
       </c>
       <c r="H226" t="n">
-        <v>1409.944189808421</v>
+        <v>1409.944064008135</v>
       </c>
       <c r="I226" t="n">
         <v>905.5050975494345</v>
@@ -17829,7 +17829,7 @@
         <v>31.031841036679</v>
       </c>
       <c r="K226" t="n">
-        <v>18.83221153041898</v>
+        <v>18.83220092778217</v>
       </c>
       <c r="L226" t="n">
         <v>62.5</v>
@@ -18199,13 +18199,13 @@
         <v>1649.964755859375</v>
       </c>
       <c r="F231" t="n">
-        <v>1703.075806884766</v>
+        <v>1703.075805053711</v>
       </c>
       <c r="G231" t="n">
-        <v>-2.919929818419964</v>
+        <v>-2.919929449933345</v>
       </c>
       <c r="H231" t="n">
-        <v>2339.801318384509</v>
+        <v>2339.80156593166</v>
       </c>
       <c r="I231" t="n">
         <v>1322.972836511248</v>
@@ -18214,7 +18214,7 @@
         <v>33.15465948880507</v>
       </c>
       <c r="K231" t="n">
-        <v>32.82251083173704</v>
+        <v>32.82252488414137</v>
       </c>
       <c r="L231" t="n">
         <v>53.7087912087912</v>
@@ -18507,10 +18507,10 @@
         <v>1959.427457682292</v>
       </c>
       <c r="F235" t="n">
-        <v>1873.62481262207</v>
+        <v>1873.624813842773</v>
       </c>
       <c r="G235" t="n">
-        <v>2.727090731089876</v>
+        <v>2.727090660510756</v>
       </c>
       <c r="H235" t="n">
         <v>2295</v>
@@ -20586,10 +20586,10 @@
         <v>166.5695239257813</v>
       </c>
       <c r="F262" t="n">
-        <v>165.0803565979004</v>
+        <v>165.0803566741943</v>
       </c>
       <c r="G262" t="n">
-        <v>0.314079913885501</v>
+        <v>0.3140798672328859</v>
       </c>
       <c r="H262" t="n">
         <v>181.8519567776652</v>
@@ -20891,13 +20891,13 @@
         <v>2238.142978515625</v>
       </c>
       <c r="E266" t="n">
-        <v>2266.075249023438</v>
+        <v>2266.07525390625</v>
       </c>
       <c r="F266" t="n">
-        <v>2409.172108154297</v>
+        <v>2409.172111816406</v>
       </c>
       <c r="G266" t="n">
-        <v>-3.92439934994312</v>
+        <v>-3.92439939098197</v>
       </c>
       <c r="H266" t="n">
         <v>3269.779000999862</v>
@@ -21202,13 +21202,13 @@
         <v>747.1143282063803</v>
       </c>
       <c r="F270" t="n">
-        <v>751.4212274169922</v>
+        <v>751.4212280273438</v>
       </c>
       <c r="G270" t="n">
-        <v>-1.047392486226295</v>
+        <v>-1.047392525151292</v>
       </c>
       <c r="H270" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I270" t="n">
         <v>612.1496526863262</v>
@@ -21217,7 +21217,7 @@
         <v>25.76172708872204</v>
       </c>
       <c r="K270" t="n">
-        <v>45.16587145482052</v>
+        <v>45.16585526365387</v>
       </c>
       <c r="L270" t="n">
         <v>58.37912087912088</v>
@@ -22129,16 +22129,16 @@
         <v>165.7395127868652</v>
       </c>
       <c r="G282" t="n">
-        <v>1.595450972238432</v>
+        <v>1.595450877212423</v>
       </c>
       <c r="H282" t="n">
         <v>208.3389342898026</v>
       </c>
       <c r="I282" t="n">
-        <v>130.9092542320289</v>
+        <v>130.9092394450487</v>
       </c>
       <c r="J282" t="n">
-        <v>23.94081759294227</v>
+        <v>23.94083159279763</v>
       </c>
       <c r="K282" t="n">
         <v>28.40612282884598</v>
@@ -22277,16 +22277,16 @@
         <v>291.8554602050781</v>
       </c>
       <c r="E284" t="n">
-        <v>302.1002519734701</v>
+        <v>302.100251566569</v>
       </c>
       <c r="F284" t="n">
         <v>287.5597009277344</v>
       </c>
       <c r="G284" t="n">
-        <v>1.655991504116217</v>
+        <v>1.65599133961114</v>
       </c>
       <c r="H284" t="n">
-        <v>357.6229312128765</v>
+        <v>357.6229001129018</v>
       </c>
       <c r="I284" t="n">
         <v>205.494747960586</v>
@@ -22295,7 +22295,7 @@
         <v>35.76989327898173</v>
       </c>
       <c r="K284" t="n">
-        <v>28.18026208346829</v>
+        <v>28.18025093652394</v>
       </c>
       <c r="L284" t="n">
         <v>69.5054945054945</v>
@@ -23663,13 +23663,13 @@
         <v>328.6148284912109</v>
       </c>
       <c r="E302" t="n">
-        <v>315.8006854248047</v>
+        <v>315.8006858317057</v>
       </c>
       <c r="F302" t="n">
-        <v>310.1694561767578</v>
+        <v>310.1694563293457</v>
       </c>
       <c r="G302" t="n">
-        <v>0.9784518772138817</v>
+        <v>0.9784517764029887</v>
       </c>
       <c r="H302" t="n">
         <v>380.4567148307952</v>
@@ -25822,10 +25822,10 @@
         <v>286.0308180745442</v>
       </c>
       <c r="F330" t="n">
-        <v>273.038511352539</v>
+        <v>273.0385107421875</v>
       </c>
       <c r="G330" t="n">
-        <v>2.320512570290534</v>
+        <v>2.320512546343756</v>
       </c>
       <c r="H330" t="n">
         <v>367.499792159746</v>
@@ -26130,10 +26130,10 @@
         <v>5136.551207682292</v>
       </c>
       <c r="F334" t="n">
-        <v>5227.852780761718</v>
+        <v>5227.852768554688</v>
       </c>
       <c r="G334" t="n">
-        <v>-1.223272802424624</v>
+        <v>-1.223272714117141</v>
       </c>
       <c r="H334" t="n">
         <v>6175.521739453033</v>
@@ -26284,19 +26284,19 @@
         <v>737.9984777832032</v>
       </c>
       <c r="F336" t="n">
-        <v>692.2140863037109</v>
+        <v>692.2140869140625</v>
       </c>
       <c r="G336" t="n">
-        <v>2.391673665811722</v>
+        <v>2.391673779204839</v>
       </c>
       <c r="H336" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I336" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J336" t="n">
-        <v>19.01440414300723</v>
+        <v>19.01441811462505</v>
       </c>
       <c r="K336" t="n">
         <v>87.02568284272733</v>
@@ -26435,16 +26435,16 @@
         <v>150.0775961303711</v>
       </c>
       <c r="E338" t="n">
-        <v>154.7109357706706</v>
+        <v>154.7109349568685</v>
       </c>
       <c r="F338" t="n">
-        <v>151.3329485321045</v>
+        <v>151.3329473876953</v>
       </c>
       <c r="G338" t="n">
-        <v>1.21037972357847</v>
+        <v>1.210379784484794</v>
       </c>
       <c r="H338" t="n">
-        <v>196.4205715539644</v>
+        <v>196.4205869556906</v>
       </c>
       <c r="I338" t="n">
         <v>125.7825892411346</v>
@@ -26453,7 +26453,7 @@
         <v>6.032159078477273</v>
       </c>
       <c r="K338" t="n">
-        <v>47.27493345214309</v>
+        <v>47.27494500026246</v>
       </c>
       <c r="L338" t="n">
         <v>58.92857142857143</v>
@@ -26746,10 +26746,10 @@
         <v>340.401630452474</v>
       </c>
       <c r="F342" t="n">
-        <v>335.7981440734864</v>
+        <v>335.7981439208984</v>
       </c>
       <c r="G342" t="n">
-        <v>0.5117193640684192</v>
+        <v>0.5117193183955315</v>
       </c>
       <c r="H342" t="n">
         <v>428.7550602808859</v>
@@ -28206,22 +28206,22 @@
         <v>1098.784118652344</v>
       </c>
       <c r="E361" t="n">
-        <v>1082.538330891927</v>
+        <v>1082.538331298828</v>
       </c>
       <c r="F361" t="n">
-        <v>1089.817180786133</v>
+        <v>1089.817180480957</v>
       </c>
       <c r="G361" t="n">
-        <v>-0.8836226197429409</v>
+        <v>-0.883622675007778</v>
       </c>
       <c r="H361" t="n">
         <v>1220.261047806783</v>
       </c>
       <c r="I361" t="n">
-        <v>894.3679138887208</v>
+        <v>894.3678543773916</v>
       </c>
       <c r="J361" t="n">
-        <v>11.48655492911599</v>
+        <v>11.48656234744285</v>
       </c>
       <c r="K361" t="n">
         <v>22.38101270534145</v>
@@ -28591,22 +28591,22 @@
         <v>36163.7459375</v>
       </c>
       <c r="E366" t="n">
-        <v>37172.16875</v>
+        <v>37172.16876302083</v>
       </c>
       <c r="F366" t="n">
-        <v>36138.47262695312</v>
+        <v>36138.4726953125</v>
       </c>
       <c r="G366" t="n">
-        <v>0.08572855374877619</v>
+        <v>0.08572860772477764</v>
       </c>
       <c r="H366" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I366" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J366" t="n">
-        <v>14.57980202170501</v>
+        <v>14.579794541279</v>
       </c>
       <c r="K366" t="n">
         <v>28.92168359716212</v>
@@ -29518,10 +29518,10 @@
         <v>77.13446248372396</v>
       </c>
       <c r="F378" t="n">
-        <v>77.01193534851075</v>
+        <v>77.01193531036377</v>
       </c>
       <c r="G378" t="n">
-        <v>-0.3319097888130007</v>
+        <v>-0.3319100842103184</v>
       </c>
       <c r="H378" t="n">
         <v>86.59303970157107</v>
@@ -31671,22 +31671,22 @@
         <v>2206.356015625</v>
       </c>
       <c r="E406" t="n">
-        <v>2196.307940266927</v>
+        <v>2196.307958170573</v>
       </c>
       <c r="F406" t="n">
-        <v>2254.304647827149</v>
+        <v>2254.304673461914</v>
       </c>
       <c r="G406" t="n">
-        <v>-1.21556621063208</v>
+        <v>-1.215565932770213</v>
       </c>
       <c r="H406" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I406" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J406" t="n">
-        <v>7.469031786748292</v>
+        <v>7.469025117844041</v>
       </c>
       <c r="K406" t="n">
         <v>31.07306096119753</v>
@@ -32521,10 +32521,10 @@
         <v>943.7706384277344</v>
       </c>
       <c r="F417" t="n">
-        <v>930.9175985717774</v>
+        <v>930.91759765625</v>
       </c>
       <c r="G417" t="n">
-        <v>-1.203692376660281</v>
+        <v>-1.203692313834204</v>
       </c>
       <c r="H417" t="n">
         <v>1224.741935222577</v>
@@ -33137,10 +33137,10 @@
         <v>726.2880399576823</v>
       </c>
       <c r="F425" t="n">
-        <v>739.8810321044922</v>
+        <v>739.8810317993164</v>
       </c>
       <c r="G425" t="n">
-        <v>-0.7615509793732933</v>
+        <v>-0.7615510609265574</v>
       </c>
       <c r="H425" t="n">
         <v>879.2203373423794</v>
@@ -33904,13 +33904,13 @@
         <v>718.2069982910157</v>
       </c>
       <c r="E435" t="n">
-        <v>740.2758577473959</v>
+        <v>740.275858968099</v>
       </c>
       <c r="F435" t="n">
-        <v>730.8825631713867</v>
+        <v>730.8825646972656</v>
       </c>
       <c r="G435" t="n">
-        <v>-0.8758971986251751</v>
+        <v>-0.875897032707873</v>
       </c>
       <c r="H435" t="n">
         <v>837.8765073351432</v>
@@ -35062,10 +35062,10 @@
         <v>201.0005732218424</v>
       </c>
       <c r="F450" t="n">
-        <v>204.9948448944092</v>
+        <v>204.994845123291</v>
       </c>
       <c r="G450" t="n">
-        <v>-2.089795173099118</v>
+        <v>-2.089795099458136</v>
       </c>
       <c r="H450" t="n">
         <v>278.3389924341271</v>
@@ -35290,25 +35290,25 @@
         <v>207.5157498168945</v>
       </c>
       <c r="E453" t="n">
-        <v>207.4939163208008</v>
+        <v>207.4939165242513</v>
       </c>
       <c r="F453" t="n">
-        <v>209.7035089111328</v>
+        <v>209.7035093688965</v>
       </c>
       <c r="G453" t="n">
-        <v>-1.248340205113252</v>
+        <v>-1.248340166943118</v>
       </c>
       <c r="H453" t="n">
-        <v>252.6160882566492</v>
+        <v>252.6161043110497</v>
       </c>
       <c r="I453" t="n">
-        <v>171.6534052563282</v>
+        <v>171.6534204603822</v>
       </c>
       <c r="J453" t="n">
-        <v>10.33861729317598</v>
+        <v>10.33860752002789</v>
       </c>
       <c r="K453" t="n">
-        <v>33.37703083280734</v>
+        <v>33.37703930925986</v>
       </c>
       <c r="L453" t="n">
         <v>36.53846153846153</v>
@@ -35909,10 +35909,10 @@
         <v>4184.767843424479</v>
       </c>
       <c r="F461" t="n">
-        <v>4461.86279663086</v>
+        <v>4461.86278930664</v>
       </c>
       <c r="G461" t="n">
-        <v>-4.67848281861728</v>
+        <v>-4.678482875654888</v>
       </c>
       <c r="H461" t="n">
         <v>6307.364089958675</v>
@@ -36063,10 +36063,10 @@
         <v>579.7319146728515</v>
       </c>
       <c r="F463" t="n">
-        <v>557.723097076416</v>
+        <v>557.7230964660645</v>
       </c>
       <c r="G463" t="n">
-        <v>-0.2401940310211681</v>
+        <v>-0.2401941401946162</v>
       </c>
       <c r="H463" t="n">
         <v>784.8771245029434</v>
@@ -36140,13 +36140,13 @@
         <v>778.0079960123697</v>
       </c>
       <c r="F464" t="n">
-        <v>782.3041488647461</v>
+        <v>782.3041510009766</v>
       </c>
       <c r="G464" t="n">
-        <v>-1.336971676131582</v>
+        <v>-1.336971672529519</v>
       </c>
       <c r="H464" t="n">
-        <v>1062.152756470788</v>
+        <v>1062.152879449244</v>
       </c>
       <c r="I464" t="n">
         <v>648.9423872407145</v>
@@ -36155,7 +36155,7 @@
         <v>9.948126987633321</v>
       </c>
       <c r="K464" t="n">
-        <v>48.86513755722321</v>
+        <v>48.86515479316671</v>
       </c>
       <c r="L464" t="n">
         <v>32.69230769230769</v>
@@ -36602,10 +36602,10 @@
         <v>394.5023252360026</v>
       </c>
       <c r="F470" t="n">
-        <v>390.8937545776367</v>
+        <v>390.8937544250488</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.08454863355800146</v>
+        <v>-0.08454871153031895</v>
       </c>
       <c r="H470" t="n">
         <v>476.8288845013619</v>
@@ -36756,10 +36756,10 @@
         <v>412.2620546468099</v>
       </c>
       <c r="F472" t="n">
-        <v>412.4930699157715</v>
+        <v>412.4930705261231</v>
       </c>
       <c r="G472" t="n">
-        <v>-1.134812482096004</v>
+        <v>-1.134812444279099</v>
       </c>
       <c r="H472" t="n">
         <v>680.1768451010124</v>
@@ -38527,10 +38527,10 @@
         <v>272.1744295247396</v>
       </c>
       <c r="F495" t="n">
-        <v>278.5210661315918</v>
+        <v>278.5210659790039</v>
       </c>
       <c r="G495" t="n">
-        <v>-3.524386812568592</v>
+        <v>-3.524386916414235</v>
       </c>
       <c r="H495" t="n">
         <v>390.5481555478003</v>
@@ -38915,7 +38915,7 @@
         <v>2710.704836425781</v>
       </c>
       <c r="G500" t="n">
-        <v>-1.302299839218113</v>
+        <v>-1.302299970820298</v>
       </c>
       <c r="H500" t="n">
         <v>3333.383184200957</v>
@@ -39220,10 +39220,10 @@
         <v>2533.216212565104</v>
       </c>
       <c r="F504" t="n">
-        <v>2509.673233642578</v>
+        <v>2509.673229980469</v>
       </c>
       <c r="G504" t="n">
-        <v>-1.180783886319958</v>
+        <v>-1.180783888022585</v>
       </c>
       <c r="H504" t="n">
         <v>3329.438873827357</v>
@@ -40606,10 +40606,10 @@
         <v>253.0735110473633</v>
       </c>
       <c r="F522" t="n">
-        <v>253.804504699707</v>
+        <v>253.804504776001</v>
       </c>
       <c r="G522" t="n">
-        <v>-0.1799757879190733</v>
+        <v>-0.1799758178170796</v>
       </c>
       <c r="H522" t="n">
         <v>306.197022156633</v>
@@ -41145,10 +41145,10 @@
         <v>138.165812479655</v>
       </c>
       <c r="F529" t="n">
-        <v>144.7598881530762</v>
+        <v>144.7598886108399</v>
       </c>
       <c r="G529" t="n">
-        <v>-1.952075099227069</v>
+        <v>-1.952075093174654</v>
       </c>
       <c r="H529" t="n">
         <v>184.9587904135824</v>
@@ -41684,10 +41684,10 @@
         <v>352.3257368977864</v>
       </c>
       <c r="F536" t="n">
-        <v>353.1676731872558</v>
+        <v>353.1676733398438</v>
       </c>
       <c r="G536" t="n">
-        <v>-0.04490547579441007</v>
+        <v>-0.04490551894171801</v>
       </c>
       <c r="H536" t="n">
         <v>409.9712889887167</v>
@@ -42146,10 +42146,10 @@
         <v>1055.131530354818</v>
       </c>
       <c r="F542" t="n">
-        <v>1070.530737915039</v>
+        <v>1070.530738525391</v>
       </c>
       <c r="G542" t="n">
-        <v>-2.492381034359592</v>
+        <v>-2.492380924559345</v>
       </c>
       <c r="H542" t="n">
         <v>1395.129939548488</v>
@@ -42380,10 +42380,10 @@
         <v>222.9214659881592</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.407564550890272</v>
+        <v>-1.407564650693971</v>
       </c>
       <c r="H545" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I545" t="n">
         <v>171.952833032562</v>
@@ -42392,7 +42392,7 @@
         <v>9.029896408881367</v>
       </c>
       <c r="K545" t="n">
-        <v>52.59250349817955</v>
+        <v>52.59252091892448</v>
       </c>
       <c r="L545" t="n">
         <v>38.04945054945055</v>
@@ -42451,22 +42451,22 @@
         <v>424.363999633789</v>
       </c>
       <c r="E546" t="n">
-        <v>459.9757965087891</v>
+        <v>459.9757969156901</v>
       </c>
       <c r="F546" t="n">
         <v>460.822699584961</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.126037722379769</v>
+        <v>-1.126037657638668</v>
       </c>
       <c r="H546" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I546" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7399002549519</v>
       </c>
       <c r="J546" t="n">
-        <v>4.044893408873484</v>
+        <v>4.044901744128326</v>
       </c>
       <c r="K546" t="n">
         <v>40.51739809895889</v>
@@ -43452,13 +43452,13 @@
         <v>313.4540447998047</v>
       </c>
       <c r="E559" t="n">
-        <v>335.3147192382813</v>
+        <v>335.3147212727865</v>
       </c>
       <c r="F559" t="n">
-        <v>338.5598431396484</v>
+        <v>338.559845123291</v>
       </c>
       <c r="G559" t="n">
-        <v>-1.051148304631733</v>
+        <v>-1.051148430919246</v>
       </c>
       <c r="H559" t="n">
         <v>381.3442016302781</v>
@@ -43763,10 +43763,10 @@
         <v>1947.699000651042</v>
       </c>
       <c r="F563" t="n">
-        <v>2020.332461547852</v>
+        <v>2020.332462768555</v>
       </c>
       <c r="G563" t="n">
-        <v>-2.744866111622268</v>
+        <v>-2.744866110009314</v>
       </c>
       <c r="H563" t="n">
         <v>2486.766809421043</v>
@@ -43994,13 +43994,13 @@
         <v>481.0377714029948</v>
       </c>
       <c r="F566" t="n">
-        <v>485.4500994873047</v>
+        <v>485.4500999450684</v>
       </c>
       <c r="G566" t="n">
-        <v>-1.280232580301699</v>
+        <v>-1.280232548477345</v>
       </c>
       <c r="H566" t="n">
-        <v>547.7380341214969</v>
+        <v>547.7379722645398</v>
       </c>
       <c r="I566" t="n">
         <v>406.2999877929688</v>
@@ -44009,7 +44009,7 @@
         <v>0.9475772136811944</v>
       </c>
       <c r="K566" t="n">
-        <v>33.54578624222475</v>
+        <v>33.54577116067947</v>
       </c>
       <c r="L566" t="n">
         <v>30.63186813186813</v>
@@ -45303,13 +45303,13 @@
         <v>120.830052947998</v>
       </c>
       <c r="F583" t="n">
-        <v>122.2416555786133</v>
+        <v>122.2416556167603</v>
       </c>
       <c r="G583" t="n">
-        <v>-2.671432427184139</v>
+        <v>-2.671431953394143</v>
       </c>
       <c r="H583" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I583" t="n">
         <v>100.3499984741211</v>
@@ -45318,7 +45318,7 @@
         <v>0.8470338685060419</v>
       </c>
       <c r="K583" t="n">
-        <v>54.05136667621247</v>
+        <v>54.0513492107028</v>
       </c>
       <c r="L583" t="n">
         <v>26.37362637362638</v>
@@ -45685,16 +45685,16 @@
         <v>18.39580001831055</v>
       </c>
       <c r="E588" t="n">
-        <v>20.03525355021159</v>
+        <v>20.0352535756429</v>
       </c>
       <c r="F588" t="n">
-        <v>20.19595467567444</v>
+        <v>20.19595463752746</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.844783673763639</v>
+        <v>-1.84478376817363</v>
       </c>
       <c r="H588" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I588" t="n">
         <v>16.09000015258789</v>
@@ -45703,7 +45703,7 @@
         <v>0.9322536799736936</v>
       </c>
       <c r="K588" t="n">
-        <v>46.76885828114293</v>
+        <v>46.76884596560198</v>
       </c>
       <c r="L588" t="n">
         <v>25.54945054945055</v>
@@ -45925,7 +45925,7 @@
         <v>-2.222165156022349</v>
       </c>
       <c r="H591" t="n">
-        <v>2308.784681838889</v>
+        <v>2308.784934113526</v>
       </c>
       <c r="I591" t="n">
         <v>1580</v>
@@ -45934,7 +45934,7 @@
         <v>0.7151929638053778</v>
       </c>
       <c r="K591" t="n">
-        <v>45.08795393672855</v>
+        <v>45.08796979009557</v>
       </c>
       <c r="L591" t="n">
         <v>25</v>
@@ -46150,10 +46150,10 @@
         <v>2940.584458007812</v>
       </c>
       <c r="F594" t="n">
-        <v>3085.240662841797</v>
+        <v>3085.240656738281</v>
       </c>
       <c r="G594" t="n">
-        <v>-3.122186911900449</v>
+        <v>-3.122186917884207</v>
       </c>
       <c r="H594" t="n">
         <v>3923.39201752828</v>
@@ -46532,16 +46532,16 @@
         <v>883.2090002441406</v>
       </c>
       <c r="E599" t="n">
-        <v>987.8182104492188</v>
+        <v>987.8182137044271</v>
       </c>
       <c r="F599" t="n">
-        <v>1035.429395751953</v>
+        <v>1035.429396972656</v>
       </c>
       <c r="G599" t="n">
-        <v>-2.960404914133918</v>
+        <v>-2.960405021763612</v>
       </c>
       <c r="H599" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I599" t="n">
         <v>832.5999755859375</v>
@@ -46550,7 +46550,7 @@
         <v>2.852510292627142</v>
       </c>
       <c r="K599" t="n">
-        <v>46.57305355294483</v>
+        <v>46.57306810699791</v>
       </c>
       <c r="L599" t="n">
         <v>23.62637362637362</v>
@@ -47995,13 +47995,13 @@
         <v>653.9640441894531</v>
       </c>
       <c r="E618" t="n">
-        <v>661.2129813639323</v>
+        <v>661.2129805501302</v>
       </c>
       <c r="F618" t="n">
-        <v>698.0316757202148</v>
+        <v>698.0316781616211</v>
       </c>
       <c r="G618" t="n">
-        <v>-4.361821339171234</v>
+        <v>-4.361821404558364</v>
       </c>
       <c r="H618" t="n">
         <v>1140.477361200229</v>
@@ -48688,16 +48688,16 @@
         <v>450.4660632324219</v>
       </c>
       <c r="E627" t="n">
-        <v>489.6504225667318</v>
+        <v>489.6504201253255</v>
       </c>
       <c r="F627" t="n">
-        <v>497.2640130615234</v>
+        <v>497.2640103149414</v>
       </c>
       <c r="G627" t="n">
-        <v>-2.462913457890448</v>
+        <v>-2.462913529544208</v>
       </c>
       <c r="H627" t="n">
-        <v>749.8838143552388</v>
+        <v>749.8838766016545</v>
       </c>
       <c r="I627" t="n">
         <v>400.6499938964844</v>
@@ -48706,7 +48706,7 @@
         <v>7.026081199381595</v>
       </c>
       <c r="K627" t="n">
-        <v>74.87962586353763</v>
+        <v>74.87964037995962</v>
       </c>
       <c r="L627" t="n">
         <v>17.71978021978022</v>
@@ -49384,13 +49384,13 @@
         <v>402.8493454996745</v>
       </c>
       <c r="F636" t="n">
-        <v>431.3614131164551</v>
+        <v>431.3614122009278</v>
       </c>
       <c r="G636" t="n">
-        <v>-4.142725469058838</v>
+        <v>-4.142725607500807</v>
       </c>
       <c r="H636" t="n">
-        <v>605.9581114957105</v>
+        <v>605.9581737112406</v>
       </c>
       <c r="I636" t="n">
         <v>326.057353105007</v>
@@ -49399,7 +49399,7 @@
         <v>7.266404719712849</v>
       </c>
       <c r="K636" t="n">
-        <v>73.25464231471351</v>
+        <v>73.25466010328539</v>
       </c>
       <c r="L636" t="n">
         <v>15.93406593406593</v>
@@ -49538,13 +49538,13 @@
         <v>504.8909067789713</v>
       </c>
       <c r="F638" t="n">
-        <v>531.4516560363769</v>
+        <v>531.4516557312012</v>
       </c>
       <c r="G638" t="n">
-        <v>-4.24440752595433</v>
+        <v>-4.24440752828813</v>
       </c>
       <c r="H638" t="n">
-        <v>725.6811828531856</v>
+        <v>725.6811213920008</v>
       </c>
       <c r="I638" t="n">
         <v>437.4500122070312</v>
@@ -49553,7 +49553,7 @@
         <v>0.9029561273811826</v>
       </c>
       <c r="K638" t="n">
-        <v>64.40443880553607</v>
+        <v>64.40442488138889</v>
       </c>
       <c r="L638" t="n">
         <v>15.52197802197802</v>
@@ -49698,7 +49698,7 @@
         <v>-2.968579058580423</v>
       </c>
       <c r="H640" t="n">
-        <v>345.1977393758356</v>
+        <v>345.1977086145358</v>
       </c>
       <c r="I640" t="n">
         <v>202.1900024414062</v>
@@ -49707,7 +49707,7 @@
         <v>1.112814665825046</v>
       </c>
       <c r="K640" t="n">
-        <v>68.85038899115226</v>
+        <v>68.85037394453737</v>
       </c>
       <c r="L640" t="n">
         <v>15.10989010989011</v>
@@ -50930,7 +50930,7 @@
         <v>-2.792131063895864</v>
       </c>
       <c r="H656" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I656" t="n">
         <v>144.1399993896484</v>
@@ -50939,7 +50939,7 @@
         <v>1.304290891337079</v>
       </c>
       <c r="K656" t="n">
-        <v>63.82595938809123</v>
+        <v>63.8259699629762</v>
       </c>
       <c r="L656" t="n">
         <v>11.26373626373626</v>
@@ -51694,10 +51694,10 @@
         <v>336.1929863484701</v>
       </c>
       <c r="F666" t="n">
-        <v>344.0491481781006</v>
+        <v>344.0491483306885</v>
       </c>
       <c r="G666" t="n">
-        <v>-3.816345399075571</v>
+        <v>-3.816345315387493</v>
       </c>
       <c r="H666" t="n">
         <v>487.9415273208757</v>
@@ -52079,10 +52079,10 @@
         <v>290.7818336995443</v>
       </c>
       <c r="F671" t="n">
-        <v>299.8909379577637</v>
+        <v>299.8909385681152</v>
       </c>
       <c r="G671" t="n">
-        <v>-3.011343301537417</v>
+        <v>-3.011343295593172</v>
       </c>
       <c r="H671" t="n">
         <v>387.9339558462079</v>
@@ -53465,10 +53465,10 @@
         <v>2660.802996419271</v>
       </c>
       <c r="F689" t="n">
-        <v>2779.434030761719</v>
+        <v>2779.434033203125</v>
       </c>
       <c r="G689" t="n">
-        <v>-3.994814751362341</v>
+        <v>-3.994814788473777</v>
       </c>
       <c r="H689" t="n">
         <v>3812.926349899466</v>
@@ -54312,10 +54312,10 @@
         <v>635.6451438395183</v>
       </c>
       <c r="F700" t="n">
-        <v>714.8494511413575</v>
+        <v>714.8494532775879</v>
       </c>
       <c r="G700" t="n">
-        <v>-9.601275655839725</v>
+        <v>-9.601275769449281</v>
       </c>
       <c r="H700" t="n">
         <v>1271.244922552079</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1561,16 +1561,16 @@
         <v>225.5</v>
       </c>
       <c r="D15" t="n">
-        <v>206.6969711303711</v>
+        <v>206.6969708251953</v>
       </c>
       <c r="E15" t="n">
-        <v>165.0934430440267</v>
+        <v>165.0934440104167</v>
       </c>
       <c r="F15" t="n">
-        <v>160.0688949203491</v>
+        <v>160.0688959503174</v>
       </c>
       <c r="G15" t="n">
-        <v>5.344496185626668</v>
+        <v>5.344495937823179</v>
       </c>
       <c r="H15" t="n">
         <v>248.3999938964844</v>
@@ -1718,13 +1718,13 @@
         <v>2168.989235839844</v>
       </c>
       <c r="E17" t="n">
-        <v>1950.100593261719</v>
+        <v>1950.100589192708</v>
       </c>
       <c r="F17" t="n">
-        <v>1842.20444519043</v>
+        <v>1842.204440307617</v>
       </c>
       <c r="G17" t="n">
-        <v>4.101288713047446</v>
+        <v>4.10128886798371</v>
       </c>
       <c r="H17" t="n">
         <v>2264.114307176184</v>
@@ -2026,13 +2026,13 @@
         <v>1072.110004882813</v>
       </c>
       <c r="E21" t="n">
-        <v>971.6688586425781</v>
+        <v>971.6688570149739</v>
       </c>
       <c r="F21" t="n">
-        <v>936.7748754882813</v>
+        <v>936.774873046875</v>
       </c>
       <c r="G21" t="n">
-        <v>3.628409421791079</v>
+        <v>3.628409431590485</v>
       </c>
       <c r="H21" t="n">
         <v>1240.5</v>
@@ -3184,10 +3184,10 @@
         <v>677.6434802246093</v>
       </c>
       <c r="F36" t="n">
-        <v>632.7774433898926</v>
+        <v>632.7774435424805</v>
       </c>
       <c r="G36" t="n">
-        <v>5.817060179639721</v>
+        <v>5.817060259158513</v>
       </c>
       <c r="H36" t="n">
         <v>844</v>
@@ -4025,16 +4025,16 @@
         <v>12296</v>
       </c>
       <c r="D47" t="n">
-        <v>12392.4308203125</v>
+        <v>12392.43083984375</v>
       </c>
       <c r="E47" t="n">
-        <v>11171.19533203125</v>
+        <v>11171.19530598958</v>
       </c>
       <c r="F47" t="n">
-        <v>10705.86283935547</v>
+        <v>10705.86279785156</v>
       </c>
       <c r="G47" t="n">
-        <v>4.434433775742708</v>
+        <v>4.43443369420935</v>
       </c>
       <c r="H47" t="n">
         <v>14498</v>
@@ -4647,10 +4647,10 @@
         <v>1429.280594075521</v>
       </c>
       <c r="F55" t="n">
-        <v>1376.168597412109</v>
+        <v>1376.168594970703</v>
       </c>
       <c r="G55" t="n">
-        <v>3.69285851240353</v>
+        <v>3.692858614572181</v>
       </c>
       <c r="H55" t="n">
         <v>1766.733060850261</v>
@@ -5645,13 +5645,13 @@
         <v>1577.877224121094</v>
       </c>
       <c r="E68" t="n">
-        <v>1481.9148828125</v>
+        <v>1481.914881184896</v>
       </c>
       <c r="F68" t="n">
-        <v>1485.849411621094</v>
+        <v>1485.849410400391</v>
       </c>
       <c r="G68" t="n">
-        <v>0.381095256545283</v>
+        <v>0.3810950912943145</v>
       </c>
       <c r="H68" t="n">
         <v>1845</v>
@@ -6033,10 +6033,10 @@
         <v>1694.514664713542</v>
       </c>
       <c r="F73" t="n">
-        <v>1621.725525512695</v>
+        <v>1621.725527954102</v>
       </c>
       <c r="G73" t="n">
-        <v>3.383635544097618</v>
+        <v>3.383635418153563</v>
       </c>
       <c r="H73" t="n">
         <v>2038.599975585938</v>
@@ -6803,19 +6803,19 @@
         <v>340.4082891845703</v>
       </c>
       <c r="F83" t="n">
-        <v>334.664867401123</v>
+        <v>334.6648670959473</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1437446902303963</v>
+        <v>0.1437447818124937</v>
       </c>
       <c r="H83" t="n">
         <v>388.5</v>
       </c>
       <c r="I83" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J83" t="n">
-        <v>34.83877982068808</v>
+        <v>34.83879417798654</v>
       </c>
       <c r="K83" t="n">
         <v>1.928376287869438</v>
@@ -7496,10 +7496,10 @@
         <v>745.5265991210938</v>
       </c>
       <c r="F92" t="n">
-        <v>742.8253872680664</v>
+        <v>742.8253869628907</v>
       </c>
       <c r="G92" t="n">
-        <v>2.55468741811451</v>
+        <v>2.554687678444956</v>
       </c>
       <c r="H92" t="n">
         <v>1002.400024414062</v>
@@ -7801,16 +7801,16 @@
         <v>4577.49</v>
       </c>
       <c r="E96" t="n">
-        <v>4266.073772786458</v>
+        <v>4266.073766276042</v>
       </c>
       <c r="F96" t="n">
-        <v>4326.074370117188</v>
+        <v>4326.074365234375</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5306400230471464</v>
+        <v>0.5306402517900599</v>
       </c>
       <c r="H96" t="n">
-        <v>5005.772176274182</v>
+        <v>5005.771184298104</v>
       </c>
       <c r="I96" t="n">
         <v>3669.905008549105</v>
@@ -7819,7 +7819,7 @@
         <v>29.46111920031942</v>
       </c>
       <c r="K96" t="n">
-        <v>5.360276007309617</v>
+        <v>5.360255128438252</v>
       </c>
       <c r="L96" t="n">
         <v>73.35164835164835</v>
@@ -8035,10 +8035,10 @@
         <v>4502.45759765625</v>
       </c>
       <c r="F99" t="n">
-        <v>4429.626131591797</v>
+        <v>4429.626120605469</v>
       </c>
       <c r="G99" t="n">
-        <v>1.159941922828955</v>
+        <v>1.159942207746334</v>
       </c>
       <c r="H99" t="n">
         <v>5149.89990234375</v>
@@ -8805,10 +8805,10 @@
         <v>270.5692627970378</v>
       </c>
       <c r="F109" t="n">
-        <v>252.2203274536133</v>
+        <v>252.2203276062012</v>
       </c>
       <c r="G109" t="n">
-        <v>6.249394017464605</v>
+        <v>6.249394013447573</v>
       </c>
       <c r="H109" t="n">
         <v>388.75</v>
@@ -10499,19 +10499,19 @@
         <v>4615.380185546875</v>
       </c>
       <c r="F131" t="n">
-        <v>4485.748029785156</v>
+        <v>4485.748026123047</v>
       </c>
       <c r="G131" t="n">
-        <v>2.44663078947982</v>
+        <v>2.446630762965296</v>
       </c>
       <c r="H131" t="n">
         <v>5250</v>
       </c>
       <c r="I131" t="n">
-        <v>3474.722128459666</v>
+        <v>3474.721889686419</v>
       </c>
       <c r="J131" t="n">
-        <v>30.20897024503661</v>
+        <v>30.20897919263577</v>
       </c>
       <c r="K131" t="n">
         <v>16.03748813804835</v>
@@ -11115,10 +11115,10 @@
         <v>531.0733719889323</v>
       </c>
       <c r="F139" t="n">
-        <v>539.5183612060547</v>
+        <v>539.5183605957031</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8666071636026729</v>
+        <v>0.8666069343951088</v>
       </c>
       <c r="H139" t="n">
         <v>673.9500122070312</v>
@@ -11651,13 +11651,13 @@
         <v>188.8985327148438</v>
       </c>
       <c r="E146" t="n">
-        <v>161.096474609375</v>
+        <v>161.0964747111003</v>
       </c>
       <c r="F146" t="n">
-        <v>156.5856502151489</v>
+        <v>156.585650062561</v>
       </c>
       <c r="G146" t="n">
-        <v>2.317502081054879</v>
+        <v>2.317501624293894</v>
       </c>
       <c r="H146" t="n">
         <v>233.3500061035156</v>
@@ -11808,10 +11808,10 @@
         <v>1813.873228352865</v>
       </c>
       <c r="F148" t="n">
-        <v>1789.139591674805</v>
+        <v>1789.13958984375</v>
       </c>
       <c r="G148" t="n">
-        <v>1.439513862277098</v>
+        <v>1.439513828668071</v>
       </c>
       <c r="H148" t="n">
         <v>2256.187656125729</v>
@@ -12963,10 +12963,10 @@
         <v>577.0992980957031</v>
       </c>
       <c r="F163" t="n">
-        <v>547.2160296630859</v>
+        <v>547.2160285949707</v>
       </c>
       <c r="G163" t="n">
-        <v>4.456752887204152</v>
+        <v>4.456752957141563</v>
       </c>
       <c r="H163" t="n">
         <v>795.731978165477</v>
@@ -13043,7 +13043,7 @@
         <v>994.9437686157227</v>
       </c>
       <c r="G164" t="n">
-        <v>3.826345813397292</v>
+        <v>3.826345945656739</v>
       </c>
       <c r="H164" t="n">
         <v>1368.900024414062</v>
@@ -13117,10 +13117,10 @@
         <v>2276.401332194011</v>
       </c>
       <c r="F165" t="n">
-        <v>2145.493082885742</v>
+        <v>2145.493084106445</v>
       </c>
       <c r="G165" t="n">
-        <v>3.292042427120401</v>
+        <v>3.292042516241556</v>
       </c>
       <c r="H165" t="n">
         <v>2990</v>
@@ -13579,10 +13579,10 @@
         <v>1037.063870442708</v>
       </c>
       <c r="F171" t="n">
-        <v>999.2296395874023</v>
+        <v>999.2296383666992</v>
       </c>
       <c r="G171" t="n">
-        <v>1.307608451895126</v>
+        <v>1.307608484858491</v>
       </c>
       <c r="H171" t="n">
         <v>1331.075409591023</v>
@@ -14192,22 +14192,22 @@
         <v>1280.438725585937</v>
       </c>
       <c r="E179" t="n">
-        <v>1236.536370849609</v>
+        <v>1236.5363671875</v>
       </c>
       <c r="F179" t="n">
-        <v>1299.570643005371</v>
+        <v>1299.570637817383</v>
       </c>
       <c r="G179" t="n">
-        <v>-2.554692101403044</v>
+        <v>-2.554692111341039</v>
       </c>
       <c r="H179" t="n">
         <v>1713.752567939176</v>
       </c>
       <c r="I179" t="n">
-        <v>1010.594326763664</v>
+        <v>1010.594387550952</v>
       </c>
       <c r="J179" t="n">
-        <v>40.72906541305661</v>
+        <v>40.72905694819828</v>
       </c>
       <c r="K179" t="n">
         <v>20.50011438455368</v>
@@ -14426,13 +14426,13 @@
         <v>5209.301298828125</v>
       </c>
       <c r="F182" t="n">
-        <v>5320.821633300781</v>
+        <v>5320.821628417969</v>
       </c>
       <c r="G182" t="n">
-        <v>-1.462887033897453</v>
+        <v>-1.462887079771646</v>
       </c>
       <c r="H182" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I182" t="n">
         <v>4229.809203861739</v>
@@ -14441,7 +14441,7 @@
         <v>35.40799889439214</v>
       </c>
       <c r="K182" t="n">
-        <v>14.40688277507316</v>
+        <v>14.40689144479781</v>
       </c>
       <c r="L182" t="n">
         <v>69.0934065934066</v>
@@ -14500,13 +14500,13 @@
         <v>11074.667734375</v>
       </c>
       <c r="E183" t="n">
-        <v>10499.59069010417</v>
+        <v>10499.59070963542</v>
       </c>
       <c r="F183" t="n">
-        <v>10536.93834960937</v>
+        <v>10536.93833496094</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.003107599834040187</v>
+        <v>-0.003107507164190615</v>
       </c>
       <c r="H183" t="n">
         <v>13011.97571177054</v>
@@ -15042,10 +15042,10 @@
         <v>1965.222227376302</v>
       </c>
       <c r="F190" t="n">
-        <v>1793.036874389648</v>
+        <v>1793.036875610352</v>
       </c>
       <c r="G190" t="n">
-        <v>6.234208882216086</v>
+        <v>6.234208724040591</v>
       </c>
       <c r="H190" t="n">
         <v>2714.261178227147</v>
@@ -15427,10 +15427,10 @@
         <v>79.37681729634603</v>
       </c>
       <c r="F195" t="n">
-        <v>75.8667673110962</v>
+        <v>75.8667672920227</v>
       </c>
       <c r="G195" t="n">
-        <v>3.842103743060932</v>
+        <v>3.842103662734742</v>
       </c>
       <c r="H195" t="n">
         <v>94.5</v>
@@ -16117,13 +16117,13 @@
         <v>7180.88</v>
       </c>
       <c r="E204" t="n">
-        <v>6973.080833333333</v>
+        <v>6973.080823567709</v>
       </c>
       <c r="F204" t="n">
-        <v>6596.91927734375</v>
+        <v>6596.919279785157</v>
       </c>
       <c r="G204" t="n">
-        <v>3.027683183906604</v>
+        <v>3.02768326131857</v>
       </c>
       <c r="H204" t="n">
         <v>7832.294844565128</v>
@@ -16813,10 +16813,10 @@
         <v>462.104897664388</v>
       </c>
       <c r="F213" t="n">
-        <v>461.2792251586914</v>
+        <v>461.2792262268067</v>
       </c>
       <c r="G213" t="n">
-        <v>1.296002611538305</v>
+        <v>1.296002404844887</v>
       </c>
       <c r="H213" t="n">
         <v>529.9163379046904</v>
@@ -17044,10 +17044,10 @@
         <v>630.1421089680989</v>
       </c>
       <c r="F216" t="n">
-        <v>613.1097006225586</v>
+        <v>613.1097012329102</v>
       </c>
       <c r="G216" t="n">
-        <v>1.223349444315391</v>
+        <v>1.223349494083004</v>
       </c>
       <c r="H216" t="n">
         <v>769</v>
@@ -17814,10 +17814,10 @@
         <v>1123.69690633138</v>
       </c>
       <c r="F226" t="n">
-        <v>1136.570598754883</v>
+        <v>1136.570600585937</v>
       </c>
       <c r="G226" t="n">
-        <v>-1.168610449928753</v>
+        <v>-1.168610500521472</v>
       </c>
       <c r="H226" t="n">
         <v>1409.944064008135</v>
@@ -17959,31 +17959,31 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>590.7999877929688</v>
+        <v>581.2999877929688</v>
       </c>
       <c r="D228" t="n">
-        <v>536.31099609375</v>
+        <v>527.6871685791016</v>
       </c>
       <c r="E228" t="n">
-        <v>513.2006231689453</v>
+        <v>504.9484084065755</v>
       </c>
       <c r="F228" t="n">
-        <v>535.536354675293</v>
+        <v>526.9249826049804</v>
       </c>
       <c r="G228" t="n">
-        <v>-4.122758788752511</v>
+        <v>-4.122758735733834</v>
       </c>
       <c r="H228" t="n">
-        <v>792.7687780924847</v>
+        <v>780.0211285904064</v>
       </c>
       <c r="I228" t="n">
-        <v>392.7775648630645</v>
+        <v>386.4617377898469</v>
       </c>
       <c r="J228" t="n">
-        <v>50.41592001288097</v>
+        <v>50.41592244484301</v>
       </c>
       <c r="K228" t="n">
-        <v>34.18564564532303</v>
+        <v>34.18564338043863</v>
       </c>
       <c r="L228" t="n">
         <v>61.40109890109891</v>
@@ -19286,10 +19286,10 @@
         <v>1153.699951171875</v>
       </c>
       <c r="I245" t="n">
-        <v>654.5364401437979</v>
+        <v>654.5363800389173</v>
       </c>
       <c r="J245" t="n">
-        <v>32.15459781123331</v>
+        <v>32.15460994674872</v>
       </c>
       <c r="K245" t="n">
         <v>33.37571689848266</v>
@@ -20512,7 +20512,7 @@
         <v>8066.237434082032</v>
       </c>
       <c r="G261" t="n">
-        <v>1.465389555353847</v>
+        <v>1.465389617674906</v>
       </c>
       <c r="H261" t="n">
         <v>9070.5</v>
@@ -20666,7 +20666,7 @@
         <v>388.737534790039</v>
       </c>
       <c r="G263" t="n">
-        <v>3.265264470361151</v>
+        <v>3.265264386646383</v>
       </c>
       <c r="H263" t="n">
         <v>480.9477017568404</v>
@@ -20891,16 +20891,16 @@
         <v>2238.142978515625</v>
       </c>
       <c r="E266" t="n">
-        <v>2266.07525390625</v>
+        <v>2266.075246582031</v>
       </c>
       <c r="F266" t="n">
-        <v>2409.172111816406</v>
+        <v>2409.172111206055</v>
       </c>
       <c r="G266" t="n">
-        <v>-3.92439939098197</v>
+        <v>-3.924399158086622</v>
       </c>
       <c r="H266" t="n">
-        <v>3269.779000999862</v>
+        <v>3269.779254579709</v>
       </c>
       <c r="I266" t="n">
         <v>1955.624263494112</v>
@@ -20909,7 +20909,7 @@
         <v>29.3704546025447</v>
       </c>
       <c r="K266" t="n">
-        <v>29.24027671936211</v>
+        <v>29.24028674228099</v>
       </c>
       <c r="L266" t="n">
         <v>59.75274725274725</v>
@@ -20968,22 +20968,22 @@
         <v>1790.585524902344</v>
       </c>
       <c r="E267" t="n">
-        <v>1726.580900878906</v>
+        <v>1726.580895996094</v>
       </c>
       <c r="F267" t="n">
-        <v>1682.756887817383</v>
+        <v>1682.756882324219</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6202643657230666</v>
+        <v>0.6202642943158532</v>
       </c>
       <c r="H267" t="n">
         <v>1981.513102925086</v>
       </c>
       <c r="I267" t="n">
-        <v>1386.27198097588</v>
+        <v>1386.27210129059</v>
       </c>
       <c r="J267" t="n">
-        <v>16.33358917321537</v>
+        <v>16.33357907661026</v>
       </c>
       <c r="K267" t="n">
         <v>22.86929763253305</v>
@@ -22277,13 +22277,13 @@
         <v>291.8554602050781</v>
       </c>
       <c r="E284" t="n">
-        <v>302.100251566569</v>
+        <v>302.1002513631185</v>
       </c>
       <c r="F284" t="n">
-        <v>287.5597009277344</v>
+        <v>287.5597005462647</v>
       </c>
       <c r="G284" t="n">
-        <v>1.65599133961114</v>
+        <v>1.655991451514383</v>
       </c>
       <c r="H284" t="n">
         <v>357.6229001129018</v>
@@ -22588,13 +22588,13 @@
         <v>427.4952034505208</v>
       </c>
       <c r="F288" t="n">
-        <v>424.596901550293</v>
+        <v>424.5969021606445</v>
       </c>
       <c r="G288" t="n">
-        <v>1.150854103093035</v>
+        <v>1.150854174957749</v>
       </c>
       <c r="H288" t="n">
-        <v>478.7148709533388</v>
+        <v>478.7148398145708</v>
       </c>
       <c r="I288" t="n">
         <v>355.1755291130353</v>
@@ -22603,7 +22603,7 @@
         <v>11.90241996670385</v>
       </c>
       <c r="K288" t="n">
-        <v>20.44656088826002</v>
+        <v>20.44655305362244</v>
       </c>
       <c r="L288" t="n">
         <v>66.89560439560439</v>
@@ -23663,13 +23663,13 @@
         <v>328.6148284912109</v>
       </c>
       <c r="E302" t="n">
-        <v>315.8006858317057</v>
+        <v>315.8006854248047</v>
       </c>
       <c r="F302" t="n">
-        <v>310.1694563293457</v>
+        <v>310.1694561767578</v>
       </c>
       <c r="G302" t="n">
-        <v>0.9784517764029887</v>
+        <v>0.9784518772138817</v>
       </c>
       <c r="H302" t="n">
         <v>380.4567148307952</v>
@@ -25976,19 +25976,19 @@
         <v>5198.972395833333</v>
       </c>
       <c r="F332" t="n">
-        <v>4985.197313232422</v>
+        <v>4985.197320556641</v>
       </c>
       <c r="G332" t="n">
-        <v>0.7789794802760319</v>
+        <v>0.7789795288617229</v>
       </c>
       <c r="H332" t="n">
         <v>6049.821052103703</v>
       </c>
       <c r="I332" t="n">
-        <v>3833.724641126707</v>
+        <v>3833.724882458191</v>
       </c>
       <c r="J332" t="n">
-        <v>13.31539434808673</v>
+        <v>13.31538721492689</v>
       </c>
       <c r="K332" t="n">
         <v>39.26202246921331</v>
@@ -26438,10 +26438,10 @@
         <v>154.7109349568685</v>
       </c>
       <c r="F338" t="n">
-        <v>151.3329473876953</v>
+        <v>151.3329470825195</v>
       </c>
       <c r="G338" t="n">
-        <v>1.210379784484794</v>
+        <v>1.210379735312728</v>
       </c>
       <c r="H338" t="n">
         <v>196.4205869556906</v>
@@ -26515,19 +26515,19 @@
         <v>1106.568574625651</v>
       </c>
       <c r="F339" t="n">
-        <v>1075.249447631836</v>
+        <v>1075.249448547363</v>
       </c>
       <c r="G339" t="n">
-        <v>0.6350930856878101</v>
+        <v>0.6350929701695929</v>
       </c>
       <c r="H339" t="n">
         <v>1238.748718225596</v>
       </c>
       <c r="I339" t="n">
-        <v>819.3978345806181</v>
+        <v>819.3977749884298</v>
       </c>
       <c r="J339" t="n">
-        <v>10.7520622707618</v>
+        <v>10.75207032540628</v>
       </c>
       <c r="K339" t="n">
         <v>36.50123616810974</v>
@@ -27208,19 +27208,19 @@
         <v>511.9502278645833</v>
       </c>
       <c r="F348" t="n">
-        <v>525.9838595581055</v>
+        <v>525.9838604736328</v>
       </c>
       <c r="G348" t="n">
-        <v>1.528371641276971</v>
+        <v>1.528371578768972</v>
       </c>
       <c r="H348" t="n">
         <v>755.9652099609375</v>
       </c>
       <c r="I348" t="n">
-        <v>306.8419898026673</v>
+        <v>306.8420198526935</v>
       </c>
       <c r="J348" t="n">
-        <v>30.05064530105583</v>
+        <v>30.05063256477771</v>
       </c>
       <c r="K348" t="n">
         <v>89.44123119561152</v>
@@ -28597,7 +28597,7 @@
         <v>36138.4726953125</v>
       </c>
       <c r="G366" t="n">
-        <v>0.08572860772477764</v>
+        <v>0.0857283370333084</v>
       </c>
       <c r="H366" t="n">
         <v>43614.20556091995</v>
@@ -29518,10 +29518,10 @@
         <v>77.13446248372396</v>
       </c>
       <c r="F378" t="n">
-        <v>77.01193531036377</v>
+        <v>77.01193534851075</v>
       </c>
       <c r="G378" t="n">
-        <v>-0.3319100842103184</v>
+        <v>-0.3319097888130007</v>
       </c>
       <c r="H378" t="n">
         <v>86.59303970157107</v>
@@ -29903,10 +29903,10 @@
         <v>292.0511680094401</v>
       </c>
       <c r="F383" t="n">
-        <v>283.150842666626</v>
+        <v>283.1508423614502</v>
       </c>
       <c r="G383" t="n">
-        <v>0.4647770767027826</v>
+        <v>0.4647770228147108</v>
       </c>
       <c r="H383" t="n">
         <v>387.4363949219129</v>
@@ -31674,10 +31674,10 @@
         <v>2196.307958170573</v>
       </c>
       <c r="F406" t="n">
-        <v>2254.304673461914</v>
+        <v>2254.304677124023</v>
       </c>
       <c r="G406" t="n">
-        <v>-1.215565932770213</v>
+        <v>-1.215566089343811</v>
       </c>
       <c r="H406" t="n">
         <v>2765.379504159864</v>
@@ -33288,13 +33288,13 @@
         <v>436.2198443603515</v>
       </c>
       <c r="E427" t="n">
-        <v>461.9565120442708</v>
+        <v>461.956514078776</v>
       </c>
       <c r="F427" t="n">
-        <v>451.9435145568848</v>
+        <v>451.9435159301758</v>
       </c>
       <c r="G427" t="n">
-        <v>-0.7141406423771701</v>
+        <v>-0.7141407067868477</v>
       </c>
       <c r="H427" t="n">
         <v>576.7288135834383</v>
@@ -33599,10 +33599,10 @@
         <v>282.7221836344401</v>
       </c>
       <c r="F431" t="n">
-        <v>281.5590560913086</v>
+        <v>281.5590567779541</v>
       </c>
       <c r="G431" t="n">
-        <v>-0.2025180045018615</v>
+        <v>-0.2025183278568154</v>
       </c>
       <c r="H431" t="n">
         <v>323.4425459044702</v>
@@ -33907,10 +33907,10 @@
         <v>740.275858968099</v>
       </c>
       <c r="F435" t="n">
-        <v>730.8825646972656</v>
+        <v>730.8825659179688</v>
       </c>
       <c r="G435" t="n">
-        <v>-0.875897032707873</v>
+        <v>-0.8758970312577663</v>
       </c>
       <c r="H435" t="n">
         <v>837.8765073351432</v>
@@ -34221,7 +34221,7 @@
         <v>-1.538058944766652</v>
       </c>
       <c r="H439" t="n">
-        <v>834.5473213853697</v>
+        <v>834.5473868842978</v>
       </c>
       <c r="I439" t="n">
         <v>495.5999980879241</v>
@@ -34230,7 +34230,7 @@
         <v>12.67151464253982</v>
       </c>
       <c r="K439" t="n">
-        <v>49.45331033269076</v>
+        <v>49.45332206244095</v>
       </c>
       <c r="L439" t="n">
         <v>42.17032967032967</v>
@@ -34366,13 +34366,13 @@
         <v>1568.81724609375</v>
       </c>
       <c r="E441" t="n">
-        <v>1690.2845703125</v>
+        <v>1690.28457438151</v>
       </c>
       <c r="F441" t="n">
-        <v>1736.732775268555</v>
+        <v>1736.732779541016</v>
       </c>
       <c r="G441" t="n">
-        <v>-2.105864392823353</v>
+        <v>-2.105864421431014</v>
       </c>
       <c r="H441" t="n">
         <v>2048.271405606928</v>
@@ -34757,7 +34757,7 @@
         <v>81.94864665985108</v>
       </c>
       <c r="G446" t="n">
-        <v>-0.1670256088060151</v>
+        <v>-0.1670255624115491</v>
       </c>
       <c r="H446" t="n">
         <v>96.1838663751024</v>
@@ -35062,10 +35062,10 @@
         <v>201.0005732218424</v>
       </c>
       <c r="F450" t="n">
-        <v>204.994845123291</v>
+        <v>204.9948448944092</v>
       </c>
       <c r="G450" t="n">
-        <v>-2.089795099458136</v>
+        <v>-2.089795173099118</v>
       </c>
       <c r="H450" t="n">
         <v>278.3389924341271</v>
@@ -35290,25 +35290,25 @@
         <v>207.5157498168945</v>
       </c>
       <c r="E453" t="n">
-        <v>207.4939165242513</v>
+        <v>207.4939163208008</v>
       </c>
       <c r="F453" t="n">
-        <v>209.7035093688965</v>
+        <v>209.7035089111328</v>
       </c>
       <c r="G453" t="n">
-        <v>-1.248340166943118</v>
+        <v>-1.248340205113252</v>
       </c>
       <c r="H453" t="n">
-        <v>252.6161043110497</v>
+        <v>252.6160882566492</v>
       </c>
       <c r="I453" t="n">
-        <v>171.6534204603822</v>
+        <v>171.6534052563282</v>
       </c>
       <c r="J453" t="n">
-        <v>10.33860752002789</v>
+        <v>10.33861729317598</v>
       </c>
       <c r="K453" t="n">
-        <v>33.37703930925986</v>
+        <v>33.37703083280734</v>
       </c>
       <c r="L453" t="n">
         <v>36.53846153846153</v>
@@ -35367,13 +35367,13 @@
         <v>12898.168984375</v>
       </c>
       <c r="E454" t="n">
-        <v>12592.2976171875</v>
+        <v>12592.29762369792</v>
       </c>
       <c r="F454" t="n">
-        <v>12757.60175292969</v>
+        <v>12757.60178710938</v>
       </c>
       <c r="G454" t="n">
-        <v>-1.260314543419216</v>
+        <v>-1.260314801290807</v>
       </c>
       <c r="H454" t="n">
         <v>17441.42261795032</v>
@@ -36602,10 +36602,10 @@
         <v>394.5023252360026</v>
       </c>
       <c r="F470" t="n">
-        <v>390.8937544250488</v>
+        <v>390.8937545776367</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.08454871153031895</v>
+        <v>-0.08454863355800146</v>
       </c>
       <c r="H470" t="n">
         <v>476.8288845013619</v>
@@ -38915,7 +38915,7 @@
         <v>2710.704836425781</v>
       </c>
       <c r="G500" t="n">
-        <v>-1.302299970820298</v>
+        <v>-1.302299839218113</v>
       </c>
       <c r="H500" t="n">
         <v>3333.383184200957</v>
@@ -39066,13 +39066,13 @@
         <v>2399.490704752604</v>
       </c>
       <c r="F502" t="n">
-        <v>2398.046368408203</v>
+        <v>2398.04636352539</v>
       </c>
       <c r="G502" t="n">
-        <v>-1.86511500777975</v>
+        <v>-1.865114962483672</v>
       </c>
       <c r="H502" t="n">
-        <v>2861.413025289686</v>
+        <v>2861.413278334028</v>
       </c>
       <c r="I502" t="n">
         <v>1845</v>
@@ -39081,7 +39081,7 @@
         <v>0.8130081300812941</v>
       </c>
       <c r="K502" t="n">
-        <v>53.83940996181109</v>
+        <v>53.83942356634562</v>
       </c>
       <c r="L502" t="n">
         <v>14.14835164835165</v>
@@ -39220,10 +39220,10 @@
         <v>2533.216212565104</v>
       </c>
       <c r="F504" t="n">
-        <v>2509.673229980469</v>
+        <v>2509.673233642578</v>
       </c>
       <c r="G504" t="n">
-        <v>-1.180783888022585</v>
+        <v>-1.180783886319958</v>
       </c>
       <c r="H504" t="n">
         <v>3329.438873827357</v>
@@ -40606,10 +40606,10 @@
         <v>253.0735110473633</v>
       </c>
       <c r="F522" t="n">
-        <v>253.804504776001</v>
+        <v>253.804504699707</v>
       </c>
       <c r="G522" t="n">
-        <v>-0.1799758178170796</v>
+        <v>-0.1799757879190733</v>
       </c>
       <c r="H522" t="n">
         <v>306.197022156633</v>
@@ -41145,10 +41145,10 @@
         <v>138.165812479655</v>
       </c>
       <c r="F529" t="n">
-        <v>144.7598886108399</v>
+        <v>144.7598881530762</v>
       </c>
       <c r="G529" t="n">
-        <v>-1.952075093174654</v>
+        <v>-1.952075099227069</v>
       </c>
       <c r="H529" t="n">
         <v>184.9587904135824</v>
@@ -41607,10 +41607,10 @@
         <v>4527.454114583334</v>
       </c>
       <c r="F535" t="n">
-        <v>4709.337629394531</v>
+        <v>4709.337634277344</v>
       </c>
       <c r="G535" t="n">
-        <v>-1.241286729742697</v>
+        <v>-1.241286627346072</v>
       </c>
       <c r="H535" t="n">
         <v>5612.405266256894</v>
@@ -42146,10 +42146,10 @@
         <v>1055.131530354818</v>
       </c>
       <c r="F542" t="n">
-        <v>1070.530738525391</v>
+        <v>1070.530737915039</v>
       </c>
       <c r="G542" t="n">
-        <v>-2.492380924559345</v>
+        <v>-2.492381034359592</v>
       </c>
       <c r="H542" t="n">
         <v>1395.129939548488</v>
@@ -42380,10 +42380,10 @@
         <v>222.9214659881592</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.407564650693971</v>
+        <v>-1.407564550890272</v>
       </c>
       <c r="H545" t="n">
-        <v>286.0804516993438</v>
+        <v>286.0804190389319</v>
       </c>
       <c r="I545" t="n">
         <v>171.952833032562</v>
@@ -42392,7 +42392,7 @@
         <v>9.029896408881367</v>
       </c>
       <c r="K545" t="n">
-        <v>52.59252091892448</v>
+        <v>52.59250349817955</v>
       </c>
       <c r="L545" t="n">
         <v>38.04945054945055</v>
@@ -42451,13 +42451,13 @@
         <v>424.363999633789</v>
       </c>
       <c r="E546" t="n">
-        <v>459.9757969156901</v>
+        <v>459.975796101888</v>
       </c>
       <c r="F546" t="n">
-        <v>460.822699584961</v>
+        <v>460.8226998901367</v>
       </c>
       <c r="G546" t="n">
-        <v>-1.126037657638668</v>
+        <v>-1.126037559789705</v>
       </c>
       <c r="H546" t="n">
         <v>555.1842484654879</v>
@@ -42993,13 +42993,13 @@
         <v>129196.49515625</v>
       </c>
       <c r="F553" t="n">
-        <v>132603.746015625</v>
+        <v>132603.74625</v>
       </c>
       <c r="G553" t="n">
-        <v>-2.386097951285937</v>
+        <v>-2.386097947169152</v>
       </c>
       <c r="H553" t="n">
-        <v>163308.5022863474</v>
+        <v>163308.4863287346</v>
       </c>
       <c r="I553" t="n">
         <v>116700</v>
@@ -43008,7 +43008,7 @@
         <v>1.041131105398452</v>
       </c>
       <c r="K553" t="n">
-        <v>38.49680048030144</v>
+        <v>38.49678694715229</v>
       </c>
       <c r="L553" t="n">
         <v>33.7912087912088</v>
@@ -43452,13 +43452,13 @@
         <v>313.4540447998047</v>
       </c>
       <c r="E559" t="n">
-        <v>335.3147212727865</v>
+        <v>335.3147192382813</v>
       </c>
       <c r="F559" t="n">
-        <v>338.559845123291</v>
+        <v>338.5598422241211</v>
       </c>
       <c r="G559" t="n">
-        <v>-1.051148430919246</v>
+        <v>-1.051148219189979</v>
       </c>
       <c r="H559" t="n">
         <v>381.3442016302781</v>
@@ -43763,10 +43763,10 @@
         <v>1947.699000651042</v>
       </c>
       <c r="F563" t="n">
-        <v>2020.332462768555</v>
+        <v>2020.332461547852</v>
       </c>
       <c r="G563" t="n">
-        <v>-2.744866110009314</v>
+        <v>-2.744866111622268</v>
       </c>
       <c r="H563" t="n">
         <v>2486.766809421043</v>
@@ -43991,13 +43991,13 @@
         <v>480.0395788574219</v>
       </c>
       <c r="E566" t="n">
-        <v>481.0377714029948</v>
+        <v>481.0377701822917</v>
       </c>
       <c r="F566" t="n">
-        <v>485.4500999450684</v>
+        <v>485.4500984191894</v>
       </c>
       <c r="G566" t="n">
-        <v>-1.280232548477345</v>
+        <v>-1.28023239928694</v>
       </c>
       <c r="H566" t="n">
         <v>547.7379722645398</v>
@@ -44456,10 +44456,10 @@
         <v>2598.272430013021</v>
       </c>
       <c r="F572" t="n">
-        <v>2649.187995605469</v>
+        <v>2649.187996826172</v>
       </c>
       <c r="G572" t="n">
-        <v>-2.079454306662576</v>
+        <v>-2.079454570816042</v>
       </c>
       <c r="H572" t="n">
         <v>3198.009229338596</v>
@@ -45688,10 +45688,10 @@
         <v>20.0352535756429</v>
       </c>
       <c r="F588" t="n">
-        <v>20.19595463752746</v>
+        <v>20.19595462799072</v>
       </c>
       <c r="G588" t="n">
-        <v>-1.84478376817363</v>
+        <v>-1.844783814523554</v>
       </c>
       <c r="H588" t="n">
         <v>23.83526024888653</v>
@@ -45925,7 +45925,7 @@
         <v>-2.222165156022349</v>
       </c>
       <c r="H591" t="n">
-        <v>2308.784934113526</v>
+        <v>2308.784681838889</v>
       </c>
       <c r="I591" t="n">
         <v>1580</v>
@@ -45934,7 +45934,7 @@
         <v>0.7151929638053778</v>
       </c>
       <c r="K591" t="n">
-        <v>45.08796979009557</v>
+        <v>45.08795393672855</v>
       </c>
       <c r="L591" t="n">
         <v>25</v>
@@ -46150,10 +46150,10 @@
         <v>2940.584458007812</v>
       </c>
       <c r="F594" t="n">
-        <v>3085.240656738281</v>
+        <v>3085.240662841797</v>
       </c>
       <c r="G594" t="n">
-        <v>-3.122186917884207</v>
+        <v>-3.122186911900449</v>
       </c>
       <c r="H594" t="n">
         <v>3923.39201752828</v>
@@ -46532,13 +46532,13 @@
         <v>883.2090002441406</v>
       </c>
       <c r="E599" t="n">
-        <v>987.8182137044271</v>
+        <v>987.8182104492188</v>
       </c>
       <c r="F599" t="n">
-        <v>1035.429396972656</v>
+        <v>1035.429395751953</v>
       </c>
       <c r="G599" t="n">
-        <v>-2.960405021763612</v>
+        <v>-2.960405080658668</v>
       </c>
       <c r="H599" t="n">
         <v>1255.178432949836</v>
@@ -49390,7 +49390,7 @@
         <v>-4.142725607500807</v>
       </c>
       <c r="H636" t="n">
-        <v>605.9581737112406</v>
+        <v>605.9581114957105</v>
       </c>
       <c r="I636" t="n">
         <v>326.057353105007</v>
@@ -49399,7 +49399,7 @@
         <v>7.266404719712849</v>
       </c>
       <c r="K636" t="n">
-        <v>73.25466010328539</v>
+        <v>73.25464231471351</v>
       </c>
       <c r="L636" t="n">
         <v>15.93406593406593</v>
@@ -49538,13 +49538,13 @@
         <v>504.8909067789713</v>
       </c>
       <c r="F638" t="n">
-        <v>531.4516557312012</v>
+        <v>531.4516560363769</v>
       </c>
       <c r="G638" t="n">
-        <v>-4.24440752828813</v>
+        <v>-4.24440752595433</v>
       </c>
       <c r="H638" t="n">
-        <v>725.6811213920008</v>
+        <v>725.6811828531856</v>
       </c>
       <c r="I638" t="n">
         <v>437.4500122070312</v>
@@ -49553,7 +49553,7 @@
         <v>0.9029561273811826</v>
       </c>
       <c r="K638" t="n">
-        <v>64.40442488138889</v>
+        <v>64.40443880553607</v>
       </c>
       <c r="L638" t="n">
         <v>15.52197802197802</v>
@@ -49689,13 +49689,13 @@
         <v>235.8212628173828</v>
       </c>
       <c r="E640" t="n">
-        <v>243.9094576009115</v>
+        <v>243.9094573974609</v>
       </c>
       <c r="F640" t="n">
-        <v>247.6625973510742</v>
+        <v>247.6625965881348</v>
       </c>
       <c r="G640" t="n">
-        <v>-2.968579058580423</v>
+        <v>-2.968579067453836</v>
       </c>
       <c r="H640" t="n">
         <v>345.1977086145358</v>
@@ -49769,10 +49769,10 @@
         <v>251.3467742919922</v>
       </c>
       <c r="F641" t="n">
-        <v>258.434151763916</v>
+        <v>258.4341523742676</v>
       </c>
       <c r="G641" t="n">
-        <v>-4.002319439698954</v>
+        <v>-4.002319430624879</v>
       </c>
       <c r="H641" t="n">
         <v>340.0564252807892</v>
@@ -50391,7 +50391,7 @@
         <v>-4.800792770341056</v>
       </c>
       <c r="H649" t="n">
-        <v>523.09418899518</v>
+        <v>523.0941269255326</v>
       </c>
       <c r="I649" t="n">
         <v>299</v>
@@ -50400,7 +50400,7 @@
         <v>0.7190615038409343</v>
       </c>
       <c r="K649" t="n">
-        <v>73.69888746369544</v>
+        <v>73.69886685282087</v>
       </c>
       <c r="L649" t="n">
         <v>12.63736263736264</v>
@@ -50921,16 +50921,16 @@
         <v>173.1591482543945</v>
       </c>
       <c r="E656" t="n">
-        <v>189.6886680094401</v>
+        <v>189.6886681111654</v>
       </c>
       <c r="F656" t="n">
-        <v>190.7599819946289</v>
+        <v>190.7599822235107</v>
       </c>
       <c r="G656" t="n">
-        <v>-2.792131063895864</v>
+        <v>-2.792131098431783</v>
       </c>
       <c r="H656" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I656" t="n">
         <v>144.1399993896484</v>
@@ -50939,7 +50939,7 @@
         <v>1.304290891337079</v>
       </c>
       <c r="K656" t="n">
-        <v>63.8259699629762</v>
+        <v>63.82595938809123</v>
       </c>
       <c r="L656" t="n">
         <v>11.26373626373626</v>
@@ -51694,10 +51694,10 @@
         <v>336.1929863484701</v>
       </c>
       <c r="F666" t="n">
-        <v>344.0491483306885</v>
+        <v>344.0491481781006</v>
       </c>
       <c r="G666" t="n">
-        <v>-3.816345315387493</v>
+        <v>-3.816345399075571</v>
       </c>
       <c r="H666" t="n">
         <v>487.9415273208757</v>
@@ -52307,22 +52307,22 @@
         <v>473.2200091552734</v>
       </c>
       <c r="E674" t="n">
-        <v>501.5358754475911</v>
+        <v>501.535874633789</v>
       </c>
       <c r="F674" t="n">
-        <v>517.7844291687012</v>
+        <v>517.7844262695312</v>
       </c>
       <c r="G674" t="n">
-        <v>-4.905697957149135</v>
+        <v>-4.905697983269541</v>
       </c>
       <c r="H674" t="n">
         <v>756.8455981427298</v>
       </c>
       <c r="I674" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J674" t="n">
-        <v>2.433505720465856</v>
+        <v>2.433498113876964</v>
       </c>
       <c r="K674" t="n">
         <v>81.93403801507928</v>
@@ -53465,10 +53465,10 @@
         <v>2660.802996419271</v>
       </c>
       <c r="F689" t="n">
-        <v>2779.434033203125</v>
+        <v>2779.434030761719</v>
       </c>
       <c r="G689" t="n">
-        <v>-3.994814788473777</v>
+        <v>-3.994814751362341</v>
       </c>
       <c r="H689" t="n">
         <v>3812.926349899466</v>
@@ -53696,10 +53696,10 @@
         <v>127.7733609008789</v>
       </c>
       <c r="F692" t="n">
-        <v>134.0759814453125</v>
+        <v>134.0759811401367</v>
       </c>
       <c r="G692" t="n">
-        <v>-4.027444260326584</v>
+        <v>-4.027444269124414</v>
       </c>
       <c r="H692" t="n">
         <v>183.7853835258596</v>
@@ -53927,10 +53927,10 @@
         <v>267.7131261189779</v>
       </c>
       <c r="F695" t="n">
-        <v>279.5021050262451</v>
+        <v>279.502105178833</v>
       </c>
       <c r="G695" t="n">
-        <v>-4.597046814205741</v>
+        <v>-4.597046960877882</v>
       </c>
       <c r="H695" t="n">
         <v>385.6351549871131</v>
@@ -54392,7 +54392,7 @@
         <v>258.7240942382812</v>
       </c>
       <c r="G701" t="n">
-        <v>-5.121411273828946</v>
+        <v>-5.121411167647261</v>
       </c>
       <c r="H701" t="n">
         <v>398.2045017598045</v>
@@ -56388,13 +56388,13 @@
         <v>259.0379275512695</v>
       </c>
       <c r="E727" t="n">
-        <v>357.9363683064778</v>
+        <v>357.9363687133789</v>
       </c>
       <c r="F727" t="n">
         <v>432.5371807098389</v>
       </c>
       <c r="G727" t="n">
-        <v>-6.831464866890558</v>
+        <v>-6.831464897512673</v>
       </c>
       <c r="H727" t="n">
         <v>779.4908805849697</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1256,22 +1256,22 @@
         <v>1423.585224609375</v>
       </c>
       <c r="E11" t="n">
-        <v>1184.152833658854</v>
+        <v>1184.152834065755</v>
       </c>
       <c r="F11" t="n">
         <v>1098.992200622559</v>
       </c>
       <c r="G11" t="n">
-        <v>6.797674123559427</v>
+        <v>6.797674091887185</v>
       </c>
       <c r="H11" t="n">
         <v>1649.759898897937</v>
       </c>
       <c r="I11" t="n">
-        <v>697.4814587422627</v>
+        <v>697.4813995979774</v>
       </c>
       <c r="J11" t="n">
-        <v>116.7082695969611</v>
+        <v>116.7082879731583</v>
       </c>
       <c r="K11" t="n">
         <v>9.147198074623674</v>
@@ -2180,13 +2180,13 @@
         <v>213.8280087280274</v>
       </c>
       <c r="E23" t="n">
-        <v>169.2462217712402</v>
+        <v>169.2462209065755</v>
       </c>
       <c r="F23" t="n">
-        <v>162.068395614624</v>
+        <v>162.0683945083618</v>
       </c>
       <c r="G23" t="n">
-        <v>5.69314757397128</v>
+        <v>5.693147615044514</v>
       </c>
       <c r="H23" t="n">
         <v>249.6999969482422</v>
@@ -2414,19 +2414,19 @@
         <v>646.2460925292969</v>
       </c>
       <c r="F26" t="n">
-        <v>617.1391528320313</v>
+        <v>617.1391525268555</v>
       </c>
       <c r="G26" t="n">
-        <v>3.114948737197398</v>
+        <v>3.114948791364469</v>
       </c>
       <c r="H26" t="n">
         <v>808.7999877929688</v>
       </c>
       <c r="I26" t="n">
-        <v>474.4105170606431</v>
+        <v>474.4105474900205</v>
       </c>
       <c r="J26" t="n">
-        <v>64.84668017867754</v>
+        <v>64.84666960517349</v>
       </c>
       <c r="K26" t="n">
         <v>3.420497464042094</v>
@@ -2488,25 +2488,25 @@
         <v>1453.42599609375</v>
       </c>
       <c r="E27" t="n">
-        <v>1435.063744303385</v>
+        <v>1435.06374593099</v>
       </c>
       <c r="F27" t="n">
-        <v>1388.347904663086</v>
+        <v>1388.347905273437</v>
       </c>
       <c r="G27" t="n">
-        <v>3.799997308565195</v>
+        <v>3.799997212097028</v>
       </c>
       <c r="H27" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I27" t="n">
-        <v>971.816928508411</v>
+        <v>971.8169883351571</v>
       </c>
       <c r="J27" t="n">
-        <v>63.98149989338706</v>
+        <v>63.98148979840037</v>
       </c>
       <c r="K27" t="n">
-        <v>10.86428312171797</v>
+        <v>10.86427509517658</v>
       </c>
       <c r="L27" t="n">
         <v>92.04389574759945</v>
@@ -2873,13 +2873,13 @@
         <v>2176.248361816406</v>
       </c>
       <c r="E32" t="n">
-        <v>1974.719970703125</v>
+        <v>1974.719973958333</v>
       </c>
       <c r="F32" t="n">
-        <v>1859.699465332031</v>
+        <v>1859.699470214844</v>
       </c>
       <c r="G32" t="n">
-        <v>4.060599857688829</v>
+        <v>4.060599775515672</v>
       </c>
       <c r="H32" t="n">
         <v>2290</v>
@@ -5029,16 +5029,16 @@
         <v>1981.590939941406</v>
       </c>
       <c r="E60" t="n">
-        <v>1828.827708333333</v>
+        <v>1828.827704264323</v>
       </c>
       <c r="F60" t="n">
         <v>1791.877995605469</v>
       </c>
       <c r="G60" t="n">
-        <v>1.169143463793509</v>
+        <v>1.169143568383224</v>
       </c>
       <c r="H60" t="n">
-        <v>2256.187906504501</v>
+        <v>2256.187656125729</v>
       </c>
       <c r="I60" t="n">
         <v>1345.285007075603</v>
@@ -5047,7 +5047,7 @@
         <v>47.81997607397561</v>
       </c>
       <c r="K60" t="n">
-        <v>13.4560964600092</v>
+        <v>13.45608386930341</v>
       </c>
       <c r="L60" t="n">
         <v>71.33058984910838</v>
@@ -7185,13 +7185,13 @@
         <v>12494.65328125</v>
       </c>
       <c r="E88" t="n">
-        <v>11256.24953776042</v>
+        <v>11256.24956380208</v>
       </c>
       <c r="F88" t="n">
-        <v>10777.26514648437</v>
+        <v>10777.26518310547</v>
       </c>
       <c r="G88" t="n">
-        <v>4.127807697702157</v>
+        <v>4.127807879593437</v>
       </c>
       <c r="H88" t="n">
         <v>14498</v>
@@ -7570,22 +7570,22 @@
         <v>1914.059995117188</v>
       </c>
       <c r="E93" t="n">
-        <v>1713.703068847656</v>
+        <v>1713.70306233724</v>
       </c>
       <c r="F93" t="n">
-        <v>1632.29878112793</v>
+        <v>1632.298784179688</v>
       </c>
       <c r="G93" t="n">
-        <v>3.346316694924911</v>
+        <v>3.346316368966962</v>
       </c>
       <c r="H93" t="n">
         <v>2038.599975585938</v>
       </c>
       <c r="I93" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J93" t="n">
-        <v>50.56530447724654</v>
+        <v>50.56531860466735</v>
       </c>
       <c r="K93" t="n">
         <v>6.934533648702979</v>
@@ -7727,10 +7727,10 @@
         <v>79.94439748128255</v>
       </c>
       <c r="F95" t="n">
-        <v>76.30965503692627</v>
+        <v>76.30965497970581</v>
       </c>
       <c r="G95" t="n">
-        <v>3.475731640192214</v>
+        <v>3.475731455551179</v>
       </c>
       <c r="H95" t="n">
         <v>94.5</v>
@@ -8962,16 +8962,16 @@
         <v>166.5912521362305</v>
       </c>
       <c r="G111" t="n">
-        <v>1.948146139741147</v>
+        <v>1.948146092142311</v>
       </c>
       <c r="H111" t="n">
         <v>208.3389342898026</v>
       </c>
       <c r="I111" t="n">
-        <v>130.9092542320289</v>
+        <v>130.9092394450487</v>
       </c>
       <c r="J111" t="n">
-        <v>32.2671914313913</v>
+        <v>32.2672063717603</v>
       </c>
       <c r="K111" t="n">
         <v>20.32280775843141</v>
@@ -11192,10 +11192,10 @@
         <v>275.4558675130208</v>
       </c>
       <c r="F140" t="n">
-        <v>255.0943980407715</v>
+        <v>255.0943982696533</v>
       </c>
       <c r="G140" t="n">
-        <v>5.756458447408086</v>
+        <v>5.756458575747914</v>
       </c>
       <c r="H140" t="n">
         <v>388.75</v>
@@ -12344,13 +12344,13 @@
         <v>2567.266669921875</v>
       </c>
       <c r="E155" t="n">
-        <v>2300.229503580729</v>
+        <v>2300.229504394531</v>
       </c>
       <c r="F155" t="n">
-        <v>2158.169033813477</v>
+        <v>2158.169032592773</v>
       </c>
       <c r="G155" t="n">
-        <v>2.787560047295079</v>
+        <v>2.787559959276731</v>
       </c>
       <c r="H155" t="n">
         <v>2990</v>
@@ -12806,22 +12806,22 @@
         <v>3496.817890625</v>
       </c>
       <c r="E161" t="n">
-        <v>3430.314417317708</v>
+        <v>3430.3144140625</v>
       </c>
       <c r="F161" t="n">
-        <v>3467.599499511719</v>
+        <v>3467.599494628906</v>
       </c>
       <c r="G161" t="n">
-        <v>-2.602769450810594</v>
+        <v>-2.60276938759133</v>
       </c>
       <c r="H161" t="n">
         <v>4650.142830834745</v>
       </c>
       <c r="I161" t="n">
-        <v>2961.686398774635</v>
+        <v>2961.686184535032</v>
       </c>
       <c r="J161" t="n">
-        <v>44.51902122666955</v>
+        <v>44.51903168074733</v>
       </c>
       <c r="K161" t="n">
         <v>8.64311524324004</v>
@@ -13425,10 +13425,10 @@
         <v>162.8357535807292</v>
       </c>
       <c r="F169" t="n">
-        <v>156.9912807846069</v>
+        <v>156.9912809371948</v>
       </c>
       <c r="G169" t="n">
-        <v>1.713879434641696</v>
+        <v>1.713879533502638</v>
       </c>
       <c r="H169" t="n">
         <v>233.3500061035156</v>
@@ -15969,7 +15969,7 @@
         <v>180.9195341491699</v>
       </c>
       <c r="G202" t="n">
-        <v>1.157415732566269</v>
+        <v>1.157415603110534</v>
       </c>
       <c r="H202" t="n">
         <v>203.3999938964844</v>
@@ -16271,25 +16271,25 @@
         <v>1288.646323242187</v>
       </c>
       <c r="E206" t="n">
-        <v>1240.970009765625</v>
+        <v>1240.970010172526</v>
       </c>
       <c r="F206" t="n">
-        <v>1295.986798095703</v>
+        <v>1295.986792907715</v>
       </c>
       <c r="G206" t="n">
-        <v>-2.212735586419234</v>
+        <v>-2.212735775218544</v>
       </c>
       <c r="H206" t="n">
-        <v>1713.752439762833</v>
+        <v>1713.752567939176</v>
       </c>
       <c r="I206" t="n">
-        <v>1010.594387550952</v>
+        <v>1010.594326763664</v>
       </c>
       <c r="J206" t="n">
-        <v>41.31287420334458</v>
+        <v>41.31288270331952</v>
       </c>
       <c r="K206" t="n">
-        <v>20.00227358450131</v>
+        <v>20.00228255980729</v>
       </c>
       <c r="L206" t="n">
         <v>67.2153635116598</v>
@@ -18735,16 +18735,16 @@
         <v>4578.9912890625</v>
       </c>
       <c r="E238" t="n">
-        <v>4273.684150390625</v>
+        <v>4273.684137369792</v>
       </c>
       <c r="F238" t="n">
-        <v>4314.986455078125</v>
+        <v>4314.986435546875</v>
       </c>
       <c r="G238" t="n">
-        <v>0.536191900369265</v>
+        <v>0.536191788433138</v>
       </c>
       <c r="H238" t="n">
-        <v>4987.55453561271</v>
+        <v>4987.555031600749</v>
       </c>
       <c r="I238" t="n">
         <v>3656.549863940299</v>
@@ -18753,7 +18753,7 @@
         <v>23.52081239743196</v>
       </c>
       <c r="K238" t="n">
-        <v>10.42718920811359</v>
+        <v>10.42720018956043</v>
       </c>
       <c r="L238" t="n">
         <v>64.4718792866941</v>
@@ -19046,10 +19046,10 @@
         <v>1131.190528564453</v>
       </c>
       <c r="F242" t="n">
-        <v>1132.84065612793</v>
+        <v>1132.840654907227</v>
       </c>
       <c r="G242" t="n">
-        <v>-1.259534314095845</v>
+        <v>-1.259534105318794</v>
       </c>
       <c r="H242" t="n">
         <v>1409.944064008135</v>
@@ -19123,10 +19123,10 @@
         <v>77.07862263997396</v>
       </c>
       <c r="F243" t="n">
-        <v>76.84976734161377</v>
+        <v>76.84976730346679</v>
       </c>
       <c r="G243" t="n">
-        <v>-0.5546628742420956</v>
+        <v>-0.5546630708728961</v>
       </c>
       <c r="H243" t="n">
         <v>86.59303970157107</v>
@@ -20044,22 +20044,22 @@
         <v>349.7688482666015</v>
       </c>
       <c r="E255" t="n">
-        <v>372.7549544270833</v>
+        <v>372.7549550374349</v>
       </c>
       <c r="F255" t="n">
-        <v>370.691286315918</v>
+        <v>370.6912855529785</v>
       </c>
       <c r="G255" t="n">
-        <v>0.9255317302922172</v>
+        <v>0.9255317322147461</v>
       </c>
       <c r="H255" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I255" t="n">
-        <v>220.1685431538753</v>
+        <v>220.1685579751763</v>
       </c>
       <c r="J255" t="n">
-        <v>42.86781539592166</v>
+        <v>42.86780577834999</v>
       </c>
       <c r="K255" t="n">
         <v>40.9547365758697</v>
@@ -20121,22 +20121,22 @@
         <v>291.6864624023438</v>
       </c>
       <c r="E256" t="n">
-        <v>304.2577508544922</v>
+        <v>304.2577507527669</v>
       </c>
       <c r="F256" t="n">
-        <v>288.8852950286865</v>
+        <v>288.8852958679199</v>
       </c>
       <c r="G256" t="n">
-        <v>1.896701619765984</v>
+        <v>1.896701586730298</v>
       </c>
       <c r="H256" t="n">
         <v>357.6229001129018</v>
       </c>
       <c r="I256" t="n">
-        <v>205.4947627274531</v>
+        <v>205.494747960586</v>
       </c>
       <c r="J256" t="n">
-        <v>37.35143234494356</v>
+        <v>37.3514422150272</v>
       </c>
       <c r="K256" t="n">
         <v>26.70430473442047</v>
@@ -20737,22 +20737,22 @@
         <v>1766.965949707031</v>
       </c>
       <c r="E264" t="n">
-        <v>1732.403217773438</v>
+        <v>1732.403221028646</v>
       </c>
       <c r="F264" t="n">
-        <v>1680.405113525391</v>
+        <v>1680.405119018555</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1691084621014083</v>
+        <v>0.1691083157691065</v>
       </c>
       <c r="H264" t="n">
         <v>1981.513102925086</v>
       </c>
       <c r="I264" t="n">
-        <v>1386.27198097588</v>
+        <v>1386.27210129059</v>
       </c>
       <c r="J264" t="n">
-        <v>18.77178667644495</v>
+        <v>18.77177636822838</v>
       </c>
       <c r="K264" t="n">
         <v>20.34698469025729</v>
@@ -20891,13 +20891,13 @@
         <v>769.5727429199219</v>
       </c>
       <c r="E266" t="n">
-        <v>732.5583447265625</v>
+        <v>732.5583439127604</v>
       </c>
       <c r="F266" t="n">
-        <v>701.2578108215332</v>
+        <v>701.2578088378906</v>
       </c>
       <c r="G266" t="n">
-        <v>2.041522897763715</v>
+        <v>2.041523084909858</v>
       </c>
       <c r="H266" t="n">
         <v>895.8500093227013</v>
@@ -21587,13 +21587,13 @@
         <v>182.6890484619141</v>
       </c>
       <c r="F275" t="n">
-        <v>191.6041847229004</v>
+        <v>191.6041843414307</v>
       </c>
       <c r="G275" t="n">
-        <v>-4.396813462742233</v>
+        <v>-4.396813434717084</v>
       </c>
       <c r="H275" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I275" t="n">
         <v>156.7899932861328</v>
@@ -21602,7 +21602,7 @@
         <v>26.48128455282812</v>
       </c>
       <c r="K275" t="n">
-        <v>32.73185018747525</v>
+        <v>32.73183477438268</v>
       </c>
       <c r="L275" t="n">
         <v>53.360768175583</v>
@@ -21738,13 +21738,13 @@
         <v>2255.250126953125</v>
       </c>
       <c r="E277" t="n">
-        <v>2271.217107747396</v>
+        <v>2271.217102864583</v>
       </c>
       <c r="F277" t="n">
-        <v>2393.667282714844</v>
+        <v>2393.667279052735</v>
       </c>
       <c r="G277" t="n">
-        <v>-3.604965621500811</v>
+        <v>-3.604965816363692</v>
       </c>
       <c r="H277" t="n">
         <v>3269.779000999862</v>
@@ -22588,19 +22588,19 @@
         <v>1836.567232259115</v>
       </c>
       <c r="F288" t="n">
-        <v>1805.102838745117</v>
+        <v>1805.10283996582</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1715018213202635</v>
+        <v>0.1715018551327274</v>
       </c>
       <c r="H288" t="n">
         <v>2046.900024414062</v>
       </c>
       <c r="I288" t="n">
-        <v>1569.365993709292</v>
+        <v>1569.36587206911</v>
       </c>
       <c r="J288" t="n">
-        <v>13.27503962094736</v>
+        <v>13.27504840079707</v>
       </c>
       <c r="K288" t="n">
         <v>15.14316704935097</v>
@@ -23281,10 +23281,10 @@
         <v>1363.03594156901</v>
       </c>
       <c r="F297" t="n">
-        <v>1359.177285766601</v>
+        <v>1359.177288208008</v>
       </c>
       <c r="G297" t="n">
-        <v>-0.5954327050633812</v>
+        <v>-0.5954327483729815</v>
       </c>
       <c r="H297" t="n">
         <v>1563.400024414062</v>
@@ -23435,10 +23435,10 @@
         <v>425.7331455485026</v>
       </c>
       <c r="F299" t="n">
-        <v>424.3140989685058</v>
+        <v>424.3140992736816</v>
       </c>
       <c r="G299" t="n">
-        <v>0.7203685759651357</v>
+        <v>0.7203686484053895</v>
       </c>
       <c r="H299" t="n">
         <v>478.7148709533388</v>
@@ -23509,13 +23509,13 @@
         <v>1095.752781982422</v>
       </c>
       <c r="E300" t="n">
-        <v>1078.404221598307</v>
+        <v>1078.404223632813</v>
       </c>
       <c r="F300" t="n">
-        <v>1026.657869262695</v>
+        <v>1026.657868652344</v>
       </c>
       <c r="G300" t="n">
-        <v>1.669986160607118</v>
+        <v>1.669986130890222</v>
       </c>
       <c r="H300" t="n">
         <v>1256.710710050442</v>
@@ -24128,10 +24128,10 @@
         <v>281.3362634277344</v>
       </c>
       <c r="F308" t="n">
-        <v>281.3298345947265</v>
+        <v>281.3298351287842</v>
       </c>
       <c r="G308" t="n">
-        <v>-0.3023933595500683</v>
+        <v>-0.3023937363515916</v>
       </c>
       <c r="H308" t="n">
         <v>323.4425459044702</v>
@@ -24205,10 +24205,10 @@
         <v>286.4576858520508</v>
       </c>
       <c r="F309" t="n">
-        <v>273.5561461639404</v>
+        <v>273.556146774292</v>
       </c>
       <c r="G309" t="n">
-        <v>2.028000141318054</v>
+        <v>2.028000165733834</v>
       </c>
       <c r="H309" t="n">
         <v>367.499792159746</v>
@@ -24282,19 +24282,19 @@
         <v>404.3598347981771</v>
       </c>
       <c r="F310" t="n">
-        <v>400.0470664978027</v>
+        <v>400.0470663452148</v>
       </c>
       <c r="G310" t="n">
-        <v>0.3131278570519536</v>
+        <v>0.3131279723169511</v>
       </c>
       <c r="H310" t="n">
         <v>489.5369231157038</v>
       </c>
       <c r="I310" t="n">
-        <v>331.4688402352409</v>
+        <v>331.4688100886702</v>
       </c>
       <c r="J310" t="n">
-        <v>14.49039968000365</v>
+        <v>14.49041009272671</v>
       </c>
       <c r="K310" t="n">
         <v>28.99523665762944</v>
@@ -26515,19 +26515,19 @@
         <v>5196.772408854166</v>
       </c>
       <c r="F339" t="n">
-        <v>4991.389813232422</v>
+        <v>4991.389818115234</v>
       </c>
       <c r="G339" t="n">
-        <v>0.6467211129718597</v>
+        <v>0.6467211618821578</v>
       </c>
       <c r="H339" t="n">
         <v>6049.821052103703</v>
       </c>
       <c r="I339" t="n">
-        <v>3833.724641126707</v>
+        <v>3833.724882458191</v>
       </c>
       <c r="J339" t="n">
-        <v>16.14292925189485</v>
+        <v>16.14292194074278</v>
       </c>
       <c r="K339" t="n">
         <v>35.87164621606584</v>
@@ -27439,10 +27439,10 @@
         <v>154.6856940714518</v>
       </c>
       <c r="F351" t="n">
-        <v>151.27848487854</v>
+        <v>151.2784851837158</v>
       </c>
       <c r="G351" t="n">
-        <v>0.8616984428551744</v>
+        <v>0.8616983384905241</v>
       </c>
       <c r="H351" t="n">
         <v>196.4205869556906</v>
@@ -28591,13 +28591,13 @@
         <v>10993.297265625</v>
       </c>
       <c r="E366" t="n">
-        <v>10535.04647135417</v>
+        <v>10535.04649739583</v>
       </c>
       <c r="F366" t="n">
-        <v>10524.95581542969</v>
+        <v>10524.95580078125</v>
       </c>
       <c r="G366" t="n">
-        <v>-0.1354570511647335</v>
+        <v>-0.1354569125516569</v>
       </c>
       <c r="H366" t="n">
         <v>13011.97571177054</v>
@@ -28671,10 +28671,10 @@
         <v>340.7041481526693</v>
       </c>
       <c r="F367" t="n">
-        <v>335.1501812744141</v>
+        <v>335.1501811218262</v>
       </c>
       <c r="G367" t="n">
-        <v>0.1283679697648088</v>
+        <v>0.128367924178141</v>
       </c>
       <c r="H367" t="n">
         <v>428.7550602808859</v>
@@ -28822,22 +28822,22 @@
         <v>1081.345750732422</v>
       </c>
       <c r="E369" t="n">
-        <v>1081.18344930013</v>
+        <v>1081.183449707031</v>
       </c>
       <c r="F369" t="n">
-        <v>1085.155635681152</v>
+        <v>1085.155634765625</v>
       </c>
       <c r="G369" t="n">
-        <v>-1.130117260330121</v>
+        <v>-1.13011737123565</v>
       </c>
       <c r="H369" t="n">
         <v>1220.261047806783</v>
       </c>
       <c r="I369" t="n">
-        <v>894.3679138887208</v>
+        <v>894.3678543773916</v>
       </c>
       <c r="J369" t="n">
-        <v>10.13364686991174</v>
+        <v>10.13365419821595</v>
       </c>
       <c r="K369" t="n">
         <v>23.88437033571398</v>
@@ -29364,10 +29364,10 @@
         <v>1383.874962565104</v>
       </c>
       <c r="F376" t="n">
-        <v>1356.100333862305</v>
+        <v>1356.100334472656</v>
       </c>
       <c r="G376" t="n">
-        <v>0.165777717497928</v>
+        <v>0.1657777174231878</v>
       </c>
       <c r="H376" t="n">
         <v>1553</v>
@@ -29521,16 +29521,16 @@
         <v>693.0164813232421</v>
       </c>
       <c r="G378" t="n">
-        <v>1.857389079144811</v>
+        <v>1.857389056301351</v>
       </c>
       <c r="H378" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I378" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J378" t="n">
-        <v>9.600331022298469</v>
+        <v>9.600318155841103</v>
       </c>
       <c r="K378" t="n">
         <v>103.0901969765858</v>
@@ -29592,13 +29592,13 @@
         <v>4246.449692382813</v>
       </c>
       <c r="E379" t="n">
-        <v>4183.280997721354</v>
+        <v>4183.281000976563</v>
       </c>
       <c r="F379" t="n">
-        <v>4415.964349365235</v>
+        <v>4415.964339599609</v>
       </c>
       <c r="G379" t="n">
-        <v>-4.629312493796101</v>
+        <v>-4.629312553845299</v>
       </c>
       <c r="H379" t="n">
         <v>6307.364089958675</v>
@@ -29826,10 +29826,10 @@
         <v>509.7827541097005</v>
       </c>
       <c r="F382" t="n">
-        <v>522.680520477295</v>
+        <v>522.6805194091797</v>
       </c>
       <c r="G382" t="n">
-        <v>-3.847233540564332</v>
+        <v>-3.847233332201605</v>
       </c>
       <c r="H382" t="n">
         <v>780.0211285904064</v>
@@ -29980,10 +29980,10 @@
         <v>413.645430094401</v>
       </c>
       <c r="F384" t="n">
-        <v>411.4360977172852</v>
+        <v>411.436098022461</v>
       </c>
       <c r="G384" t="n">
-        <v>-1.24602503169422</v>
+        <v>-1.2460251392861</v>
       </c>
       <c r="H384" t="n">
         <v>680.1768451010124</v>
@@ -30365,13 +30365,13 @@
         <v>779.2827697753906</v>
       </c>
       <c r="F389" t="n">
-        <v>779.1980673217773</v>
+        <v>779.198069152832</v>
       </c>
       <c r="G389" t="n">
-        <v>-1.491432859744601</v>
+        <v>-1.491432970309614</v>
       </c>
       <c r="H389" t="n">
-        <v>1062.152756470788</v>
+        <v>1062.152879449244</v>
       </c>
       <c r="I389" t="n">
         <v>648.9423872407145</v>
@@ -30380,7 +30380,7 @@
         <v>10.27172668264886</v>
       </c>
       <c r="K389" t="n">
-        <v>48.42828293853569</v>
+        <v>48.42830012389916</v>
       </c>
       <c r="L389" t="n">
         <v>30.8641975308642</v>
@@ -30596,10 +30596,10 @@
         <v>2153.261160481771</v>
       </c>
       <c r="F392" t="n">
-        <v>2091.660554199219</v>
+        <v>2091.660552978516</v>
       </c>
       <c r="G392" t="n">
-        <v>0.05490155250154061</v>
+        <v>0.05490164017045718</v>
       </c>
       <c r="H392" t="n">
         <v>2625.96691593483</v>
@@ -32521,13 +32521,13 @@
         <v>614.7234143066406</v>
       </c>
       <c r="F417" t="n">
-        <v>610.2823443603515</v>
+        <v>610.2823434448242</v>
       </c>
       <c r="G417" t="n">
-        <v>-1.636669084227893</v>
+        <v>-1.636668941496366</v>
       </c>
       <c r="H417" t="n">
-        <v>834.5473868842978</v>
+        <v>834.5473213853697</v>
       </c>
       <c r="I417" t="n">
         <v>495.5999980879241</v>
@@ -32536,7 +32536,7 @@
         <v>15.75867926158698</v>
       </c>
       <c r="K417" t="n">
-        <v>45.46755606188386</v>
+        <v>45.467544644954</v>
       </c>
       <c r="L417" t="n">
         <v>51.16598079561042</v>
@@ -32672,22 +32672,22 @@
         <v>35897.4</v>
       </c>
       <c r="E419" t="n">
-        <v>37284.24171875</v>
+        <v>37284.24173177083</v>
       </c>
       <c r="F419" t="n">
-        <v>36113.234921875</v>
+        <v>36113.23485351563</v>
       </c>
       <c r="G419" t="n">
-        <v>-0.005605101330530271</v>
+        <v>-0.005605101341144003</v>
       </c>
       <c r="H419" t="n">
         <v>43614.20556091995</v>
       </c>
       <c r="I419" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J419" t="n">
-        <v>16.84903670334394</v>
+        <v>16.8490443319191</v>
       </c>
       <c r="K419" t="n">
         <v>26.41798713310128</v>
@@ -33750,13 +33750,13 @@
         <v>435.26236328125</v>
       </c>
       <c r="E433" t="n">
-        <v>463.4046358235677</v>
+        <v>463.404633585612</v>
       </c>
       <c r="F433" t="n">
-        <v>450.3053355407715</v>
+        <v>450.3053343200684</v>
       </c>
       <c r="G433" t="n">
-        <v>-0.9402374039181649</v>
+        <v>-0.9402372734381492</v>
       </c>
       <c r="H433" t="n">
         <v>576.7288135834383</v>
@@ -33907,10 +33907,10 @@
         <v>938.5136983235677</v>
       </c>
       <c r="F435" t="n">
-        <v>927.9358657836914</v>
+        <v>927.9358651733398</v>
       </c>
       <c r="G435" t="n">
-        <v>-1.253018477357049</v>
+        <v>-1.253018414033735</v>
       </c>
       <c r="H435" t="n">
         <v>1224.741935222577</v>
@@ -34446,10 +34446,10 @@
         <v>82.6104285176595</v>
       </c>
       <c r="F442" t="n">
-        <v>81.61705844879151</v>
+        <v>81.61705856323242</v>
       </c>
       <c r="G442" t="n">
-        <v>-0.759437301388266</v>
+        <v>-0.7594370701727082</v>
       </c>
       <c r="H442" t="n">
         <v>96.1838663751024</v>
@@ -35429,7 +35429,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -35438,31 +35438,31 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>11615</v>
+        <v>420.1000061035156</v>
       </c>
       <c r="D455" t="n">
-        <v>12772.65927734375</v>
+        <v>456.0640002441406</v>
       </c>
       <c r="E455" t="n">
-        <v>12576.65469401042</v>
+        <v>479.6639994303385</v>
       </c>
       <c r="F455" t="n">
-        <v>12712.33519042969</v>
+        <v>477.5557495117188</v>
       </c>
       <c r="G455" t="n">
-        <v>-1.464777328083544</v>
+        <v>-0.9997341621318712</v>
       </c>
       <c r="H455" t="n">
-        <v>16988.98681567603</v>
+        <v>563</v>
       </c>
       <c r="I455" t="n">
-        <v>10721.75870458774</v>
+        <v>418</v>
       </c>
       <c r="J455" t="n">
-        <v>8.331107983525566</v>
+        <v>0.5023938046688103</v>
       </c>
       <c r="K455" t="n">
-        <v>46.2676436993201</v>
+        <v>34.01570859803149</v>
       </c>
       <c r="L455" t="n">
         <v>37.17421124828532</v>
@@ -35472,7 +35472,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/MAHSCOOTER/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/AADHARHFC/?exchange=NSE</t>
         </is>
       </c>
       <c r="O455" t="b">
@@ -35485,10 +35485,10 @@
         <v>0</v>
       </c>
       <c r="R455" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S455" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T455" t="b">
         <v>0</v>
@@ -35506,7 +35506,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -35515,31 +35515,31 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>420.1000061035156</v>
+        <v>11615</v>
       </c>
       <c r="D456" t="n">
-        <v>456.0640002441406</v>
+        <v>12743.52203125</v>
       </c>
       <c r="E456" t="n">
-        <v>479.6639994303385</v>
+        <v>12572.51177734375</v>
       </c>
       <c r="F456" t="n">
-        <v>477.5557495117188</v>
+        <v>12702.63816894531</v>
       </c>
       <c r="G456" t="n">
-        <v>-0.9997341621318712</v>
+        <v>-1.482260140204961</v>
       </c>
       <c r="H456" t="n">
-        <v>563</v>
+        <v>16692.93554128411</v>
       </c>
       <c r="I456" t="n">
-        <v>418</v>
+        <v>10721.75870458774</v>
       </c>
       <c r="J456" t="n">
-        <v>0.5023938046688103</v>
+        <v>8.331107983525566</v>
       </c>
       <c r="K456" t="n">
-        <v>34.01570859803149</v>
+        <v>43.71877349362124</v>
       </c>
       <c r="L456" t="n">
         <v>37.03703703703704</v>
@@ -35549,7 +35549,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/AADHARHFC/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/MAHSCOOTER/?exchange=NSE</t>
         </is>
       </c>
       <c r="O456" t="b">
@@ -35562,10 +35562,10 @@
         <v>0</v>
       </c>
       <c r="R456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S456" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T456" t="b">
         <v>0</v>
@@ -36753,13 +36753,13 @@
         <v>339.5174810791016</v>
       </c>
       <c r="E472" t="n">
-        <v>391.5735327148437</v>
+        <v>391.5735333251953</v>
       </c>
       <c r="F472" t="n">
-        <v>389.825821685791</v>
+        <v>389.8258221435547</v>
       </c>
       <c r="G472" t="n">
-        <v>-0.3412118421938226</v>
+        <v>-0.3412118417945087</v>
       </c>
       <c r="H472" t="n">
         <v>476.8288845013619</v>
@@ -36990,10 +36990,10 @@
         <v>287.4653456115723</v>
       </c>
       <c r="G475" t="n">
-        <v>-4.048116476322772</v>
+        <v>-4.048116378582945</v>
       </c>
       <c r="H475" t="n">
-        <v>406.5707952146441</v>
+        <v>406.5707642578344</v>
       </c>
       <c r="I475" t="n">
         <v>252.8000030517578</v>
@@ -37002,7 +37002,7 @@
         <v>5.063292285300003</v>
       </c>
       <c r="K475" t="n">
-        <v>53.07635010226097</v>
+        <v>53.0763384468359</v>
       </c>
       <c r="L475" t="n">
         <v>28.66941015089163</v>
@@ -38065,10 +38065,10 @@
         <v>399.0093839518229</v>
       </c>
       <c r="F489" t="n">
-        <v>426.3823936462402</v>
+        <v>426.3823945617676</v>
       </c>
       <c r="G489" t="n">
-        <v>-4.478706498569429</v>
+        <v>-4.478706358772033</v>
       </c>
       <c r="H489" t="n">
         <v>605.9581114957105</v>
@@ -38373,10 +38373,10 @@
         <v>2519.664899902344</v>
       </c>
       <c r="F493" t="n">
-        <v>2495.883143920898</v>
+        <v>2495.883142700195</v>
       </c>
       <c r="G493" t="n">
-        <v>-1.497999320375676</v>
+        <v>-1.497999226188684</v>
       </c>
       <c r="H493" t="n">
         <v>3329.438873827357</v>
@@ -38681,13 +38681,13 @@
         <v>1651.504771321614</v>
       </c>
       <c r="F497" t="n">
-        <v>1688.666903686523</v>
+        <v>1688.666904296875</v>
       </c>
       <c r="G497" t="n">
-        <v>-2.92894985397979</v>
+        <v>-2.928950159471622</v>
       </c>
       <c r="H497" t="n">
-        <v>2339.80156593166</v>
+        <v>2339.801318384509</v>
       </c>
       <c r="I497" t="n">
         <v>1322.972836511248</v>
@@ -38696,7 +38696,7 @@
         <v>8.059662007564095</v>
       </c>
       <c r="K497" t="n">
-        <v>63.66827125697638</v>
+        <v>63.66825394114288</v>
       </c>
       <c r="L497" t="n">
         <v>17.14677640603567</v>
@@ -39759,13 +39759,13 @@
         <v>188.8699223836263</v>
       </c>
       <c r="F511" t="n">
-        <v>188.8587001037598</v>
+        <v>188.8587000274658</v>
       </c>
       <c r="G511" t="n">
-        <v>-3.145600884053967</v>
+        <v>-3.145601150555755</v>
       </c>
       <c r="H511" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I511" t="n">
         <v>141.8099975585938</v>
@@ -39774,7 +39774,7 @@
         <v>0.8885197005270351</v>
       </c>
       <c r="K511" t="n">
-        <v>67.20395018830143</v>
+        <v>67.20392860243898</v>
       </c>
       <c r="L511" t="n">
         <v>10.69958847736626</v>
@@ -40769,10 +40769,10 @@
         <v>1144.692594896378</v>
       </c>
       <c r="I524" t="n">
-        <v>696.4967731361992</v>
+        <v>696.4968330370129</v>
       </c>
       <c r="J524" t="n">
-        <v>18.18432707269648</v>
+        <v>18.18431690849038</v>
       </c>
       <c r="K524" t="n">
         <v>39.06245045806776</v>
@@ -41530,10 +41530,10 @@
         <v>251.8419986979167</v>
       </c>
       <c r="F534" t="n">
-        <v>253.6466763305664</v>
+        <v>253.6466761779785</v>
       </c>
       <c r="G534" t="n">
-        <v>-0.2399265322696631</v>
+        <v>-0.2399265922829796</v>
       </c>
       <c r="H534" t="n">
         <v>306.197022156633</v>
@@ -41684,10 +41684,10 @@
         <v>408.5120603434245</v>
       </c>
       <c r="F536" t="n">
-        <v>414.7794552612305</v>
+        <v>414.7794548034668</v>
       </c>
       <c r="G536" t="n">
-        <v>-0.492684966439938</v>
+        <v>-0.492685076259336</v>
       </c>
       <c r="H536" t="n">
         <v>472.8081629796919</v>
@@ -41758,22 +41758,22 @@
         <v>2175.812021484375</v>
       </c>
       <c r="E537" t="n">
-        <v>2195.304934082031</v>
+        <v>2195.304919433594</v>
       </c>
       <c r="F537" t="n">
-        <v>2247.905494995117</v>
+        <v>2247.905464477539</v>
       </c>
       <c r="G537" t="n">
-        <v>-1.289293139123537</v>
+        <v>-1.289293368052413</v>
       </c>
       <c r="H537" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I537" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J537" t="n">
-        <v>5.574133472025111</v>
+        <v>5.574140023343377</v>
       </c>
       <c r="K537" t="n">
         <v>33.42561873306031</v>
@@ -42223,13 +42223,13 @@
         <v>207.6455415852865</v>
       </c>
       <c r="F543" t="n">
-        <v>208.6084120941162</v>
+        <v>208.6084120178223</v>
       </c>
       <c r="G543" t="n">
-        <v>-1.497431660885518</v>
+        <v>-1.49743159045358</v>
       </c>
       <c r="H543" t="n">
-        <v>252.6160882566492</v>
+        <v>252.6161043110497</v>
       </c>
       <c r="I543" t="n">
         <v>171.6534204603822</v>
@@ -42238,7 +42238,7 @@
         <v>9.68613283342763</v>
       </c>
       <c r="K543" t="n">
-        <v>34.17043227877197</v>
+        <v>34.17044080564717</v>
       </c>
       <c r="L543" t="n">
         <v>38.13443072702332</v>
@@ -42303,7 +42303,7 @@
         <v>1391.618693847656</v>
       </c>
       <c r="G544" t="n">
-        <v>-0.6401007522076729</v>
+        <v>-0.6401008821059428</v>
       </c>
       <c r="H544" t="n">
         <v>1817.803954384172</v>
@@ -42377,10 +42377,10 @@
         <v>4495.208455403646</v>
       </c>
       <c r="F545" t="n">
-        <v>4675.588548583984</v>
+        <v>4675.588541259765</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.892357824027169</v>
+        <v>-1.89235797771089</v>
       </c>
       <c r="H545" t="n">
         <v>5612.405266256894</v>
@@ -42454,13 +42454,13 @@
         <v>2593.559165039062</v>
       </c>
       <c r="F546" t="n">
-        <v>2631.294787597656</v>
+        <v>2631.294788818359</v>
       </c>
       <c r="G546" t="n">
-        <v>-2.446806662098266</v>
+        <v>-2.446806793438738</v>
       </c>
       <c r="H546" t="n">
-        <v>3131.259661761027</v>
+        <v>3131.259414361633</v>
       </c>
       <c r="I546" t="n">
         <v>2178.300048828125</v>
@@ -42469,7 +42469,7 @@
         <v>7.216634423547164</v>
       </c>
       <c r="K546" t="n">
-        <v>34.07234689621181</v>
+        <v>34.072336303217</v>
       </c>
       <c r="L546" t="n">
         <v>36.89986282578875</v>
@@ -43455,13 +43455,13 @@
         <v>416.0592423502604</v>
       </c>
       <c r="F559" t="n">
-        <v>429.7771429443359</v>
+        <v>429.7771440124512</v>
       </c>
       <c r="G559" t="n">
-        <v>-2.547276492020156</v>
+        <v>-2.547276519568953</v>
       </c>
       <c r="H559" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I559" t="n">
         <v>363.2227809620478</v>
@@ -43470,7 +43470,7 @@
         <v>4.467569793393267</v>
       </c>
       <c r="K559" t="n">
-        <v>40.65326159798899</v>
+        <v>40.65324483679586</v>
       </c>
       <c r="L559" t="n">
         <v>33.88203017832647</v>
@@ -43840,13 +43840,13 @@
         <v>128745.4940625</v>
       </c>
       <c r="F564" t="n">
-        <v>131773.379375</v>
+        <v>131773.37921875</v>
       </c>
       <c r="G564" t="n">
-        <v>-2.484578127531467</v>
+        <v>-2.484578074026433</v>
       </c>
       <c r="H564" t="n">
-        <v>163308.4863287346</v>
+        <v>163308.5022863474</v>
       </c>
       <c r="I564" t="n">
         <v>115190</v>
@@ -43855,7 +43855,7 @@
         <v>1.375987498914832</v>
       </c>
       <c r="K564" t="n">
-        <v>39.84884292762545</v>
+        <v>39.84885659289012</v>
       </c>
       <c r="L564" t="n">
         <v>32.23593964334705</v>
@@ -43991,16 +43991,16 @@
         <v>304.9462518310547</v>
       </c>
       <c r="E566" t="n">
-        <v>330.1465490722656</v>
+        <v>330.1465513102214</v>
       </c>
       <c r="F566" t="n">
-        <v>332.7428878784179</v>
+        <v>332.7428884887696</v>
       </c>
       <c r="G566" t="n">
-        <v>-1.352489016376057</v>
+        <v>-1.352488835426535</v>
       </c>
       <c r="H566" t="n">
-        <v>376.837311604795</v>
+        <v>376.8373424487648</v>
       </c>
       <c r="I566" t="n">
         <v>280.2977204410031</v>
@@ -44009,7 +44009,7 @@
         <v>1.891662070661959</v>
       </c>
       <c r="K566" t="n">
-        <v>31.94583457684186</v>
+        <v>31.94584537655096</v>
       </c>
       <c r="L566" t="n">
         <v>31.68724279835391</v>
@@ -44225,13 +44225,13 @@
         <v>480.0209075927734</v>
       </c>
       <c r="F569" t="n">
-        <v>482.8169706726074</v>
+        <v>482.8169709777832</v>
       </c>
       <c r="G569" t="n">
-        <v>-1.61524355997914</v>
+        <v>-1.615243558974666</v>
       </c>
       <c r="H569" t="n">
-        <v>547.7379722645398</v>
+        <v>547.7380341214969</v>
       </c>
       <c r="I569" t="n">
         <v>404.25</v>
@@ -44240,7 +44240,7 @@
         <v>2.374769598890691</v>
       </c>
       <c r="K569" t="n">
-        <v>32.35180963789453</v>
+        <v>32.35182458460373</v>
       </c>
       <c r="L569" t="n">
         <v>30.31550068587105</v>
@@ -44847,7 +44847,7 @@
         <v>-2.187241053313926</v>
       </c>
       <c r="H577" t="n">
-        <v>2538.029794005612</v>
+        <v>2538.030044704785</v>
       </c>
       <c r="I577" t="n">
         <v>1758.199951171875</v>
@@ -44856,7 +44856,7 @@
         <v>6.051645283185492</v>
       </c>
       <c r="K577" t="n">
-        <v>36.1165841058243</v>
+        <v>36.11659755102308</v>
       </c>
       <c r="L577" t="n">
         <v>28.80658436213992</v>
@@ -45226,10 +45226,10 @@
         <v>152.9966533406576</v>
       </c>
       <c r="F582" t="n">
-        <v>156.4847807312012</v>
+        <v>156.4847804260254</v>
       </c>
       <c r="G582" t="n">
-        <v>-2.89929070790369</v>
+        <v>-2.899290851300218</v>
       </c>
       <c r="H582" t="n">
         <v>212.7553783484557</v>
@@ -47151,13 +47151,13 @@
         <v>1045.908940836588</v>
       </c>
       <c r="F607" t="n">
-        <v>1057.706166992187</v>
+        <v>1057.706166381836</v>
       </c>
       <c r="G607" t="n">
-        <v>-2.706130505084281</v>
+        <v>-2.706130342730662</v>
       </c>
       <c r="H607" t="n">
-        <v>1389.004661008472</v>
+        <v>1389.004402405139</v>
       </c>
       <c r="I607" t="n">
         <v>866.5999755859375</v>
@@ -47166,7 +47166,7 @@
         <v>0.8539146806528786</v>
       </c>
       <c r="K607" t="n">
-        <v>58.92501842202198</v>
+        <v>58.92498883353998</v>
       </c>
       <c r="L607" t="n">
         <v>21.94787379972565</v>
@@ -47382,10 +47382,10 @@
         <v>865.2513671875</v>
       </c>
       <c r="F610" t="n">
-        <v>903.1968527221679</v>
+        <v>903.1968536376953</v>
       </c>
       <c r="G610" t="n">
-        <v>-1.959423829726559</v>
+        <v>-1.959424022642853</v>
       </c>
       <c r="H610" t="n">
         <v>1282.80960014975</v>
@@ -47536,10 +47536,10 @@
         <v>1185.608982747396</v>
       </c>
       <c r="F612" t="n">
-        <v>1228.897401123047</v>
+        <v>1228.897399291992</v>
       </c>
       <c r="G612" t="n">
-        <v>-3.115219023837901</v>
+        <v>-3.115219028334981</v>
       </c>
       <c r="H612" t="n">
         <v>1504.476256003898</v>
@@ -47918,16 +47918,16 @@
         <v>18.07760000228882</v>
       </c>
       <c r="E617" t="n">
-        <v>19.87987178166707</v>
+        <v>19.87987181981405</v>
       </c>
       <c r="F617" t="n">
-        <v>20.07122610569</v>
+        <v>20.07122608661652</v>
       </c>
       <c r="G617" t="n">
-        <v>-2.023844233805105</v>
+        <v>-2.02384423568942</v>
       </c>
       <c r="H617" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I617" t="n">
         <v>15.68000030517578</v>
@@ -47936,7 +47936,7 @@
         <v>0.3188726791289787</v>
       </c>
       <c r="K617" t="n">
-        <v>51.52741857957932</v>
+        <v>51.52740586474221</v>
       </c>
       <c r="L617" t="n">
         <v>19.89026063100137</v>
@@ -48768,10 +48768,10 @@
         <v>250.4305823771159</v>
       </c>
       <c r="F628" t="n">
-        <v>255.9801156616211</v>
+        <v>255.9801148986816</v>
       </c>
       <c r="G628" t="n">
-        <v>-4.01859171366481</v>
+        <v>-4.018591780075386</v>
       </c>
       <c r="H628" t="n">
         <v>340.0564252807892</v>
@@ -49002,7 +49002,7 @@
         <v>245.2073197174072</v>
       </c>
       <c r="G631" t="n">
-        <v>-3.368209766455554</v>
+        <v>-3.368209940775846</v>
       </c>
       <c r="H631" t="n">
         <v>345.1977086145358</v>
@@ -49227,16 +49227,16 @@
         <v>873.2840002441407</v>
       </c>
       <c r="E634" t="n">
-        <v>981.2651973470053</v>
+        <v>981.2651997884115</v>
       </c>
       <c r="F634" t="n">
-        <v>1025.458537902832</v>
+        <v>1025.458539123535</v>
       </c>
       <c r="G634" t="n">
-        <v>-3.35531080720135</v>
+        <v>-3.355310803341205</v>
       </c>
       <c r="H634" t="n">
-        <v>1255.178308316206</v>
+        <v>1255.178432949836</v>
       </c>
       <c r="I634" t="n">
         <v>777.2000122070312</v>
@@ -49245,7 +49245,7 @@
         <v>5.24961234587582</v>
       </c>
       <c r="K634" t="n">
-        <v>53.44478096775136</v>
+        <v>53.44479620413644</v>
       </c>
       <c r="L634" t="n">
         <v>17.00960219478738</v>
@@ -49304,13 +49304,13 @@
         <v>109.6980303955078</v>
       </c>
       <c r="E635" t="n">
-        <v>119.2040149434408</v>
+        <v>119.2040148417155</v>
       </c>
       <c r="F635" t="n">
-        <v>120.5905585479736</v>
+        <v>120.5905585861206</v>
       </c>
       <c r="G635" t="n">
-        <v>-2.688635115997529</v>
+        <v>-2.688635234991144</v>
       </c>
       <c r="H635" t="n">
         <v>154.8912966301784</v>
@@ -49766,22 +49766,22 @@
         <v>466.3780004882813</v>
       </c>
       <c r="E641" t="n">
-        <v>500.8350132242838</v>
+        <v>500.8350140380859</v>
       </c>
       <c r="F641" t="n">
-        <v>511.5051348876953</v>
+        <v>511.5051356506348</v>
       </c>
       <c r="G641" t="n">
-        <v>-5.133207991234867</v>
+        <v>-5.133207930277073</v>
       </c>
       <c r="H641" t="n">
         <v>756.8456624851057</v>
       </c>
       <c r="I641" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J641" t="n">
-        <v>8.010705102037697</v>
+        <v>8.010713122783297</v>
       </c>
       <c r="K641" t="n">
         <v>72.53976359651135</v>
@@ -50382,13 +50382,13 @@
         <v>622.6937097167969</v>
       </c>
       <c r="E649" t="n">
-        <v>657.178750406901</v>
+        <v>657.1787491861979</v>
       </c>
       <c r="F649" t="n">
-        <v>668.2377725219726</v>
+        <v>668.2377703857422</v>
       </c>
       <c r="G649" t="n">
-        <v>-3.175524798741458</v>
+        <v>-3.175524808570629</v>
       </c>
       <c r="H649" t="n">
         <v>791.3161855529985</v>
@@ -50539,10 +50539,10 @@
         <v>272.1467555745443</v>
       </c>
       <c r="F651" t="n">
-        <v>275.4014311218262</v>
+        <v>275.4014309692383</v>
       </c>
       <c r="G651" t="n">
-        <v>-3.995922908106275</v>
+        <v>-3.995923012364122</v>
       </c>
       <c r="H651" t="n">
         <v>390.5481555478003</v>
@@ -51158,10 +51158,10 @@
         <v>121.6364585494995</v>
       </c>
       <c r="G659" t="n">
-        <v>-3.219492958695103</v>
+        <v>-3.219493017444319</v>
       </c>
       <c r="H659" t="n">
-        <v>154.1041584954392</v>
+        <v>154.1041427094461</v>
       </c>
       <c r="I659" t="n">
         <v>93.11000061035156</v>
@@ -51170,7 +51170,7 @@
         <v>0.558475609126563</v>
       </c>
       <c r="K659" t="n">
-        <v>64.58844709601186</v>
+        <v>64.58843023603802</v>
       </c>
       <c r="L659" t="n">
         <v>12.07133058984911</v>
@@ -51232,10 +51232,10 @@
         <v>90.35259140014648</v>
       </c>
       <c r="F660" t="n">
-        <v>91.54078800201415</v>
+        <v>91.54078792572021</v>
       </c>
       <c r="G660" t="n">
-        <v>-4.623247034113398</v>
+        <v>-4.623247227328287</v>
       </c>
       <c r="H660" t="n">
         <v>124.8273096544699</v>
@@ -51315,7 +51315,7 @@
         <v>-4.656827948881082</v>
       </c>
       <c r="H661" t="n">
-        <v>523.09418899518</v>
+        <v>523.0941269255326</v>
       </c>
       <c r="I661" t="n">
         <v>295.1000061035156</v>
@@ -51324,7 +51324,7 @@
         <v>0.8641097052618285</v>
       </c>
       <c r="K661" t="n">
-        <v>75.74137400355528</v>
+        <v>75.74135315032203</v>
       </c>
       <c r="L661" t="n">
         <v>11.79698216735254</v>
@@ -51925,10 +51925,10 @@
         <v>88.75408081054688</v>
       </c>
       <c r="F669" t="n">
-        <v>93.52531677246094</v>
+        <v>93.52531665802002</v>
       </c>
       <c r="G669" t="n">
-        <v>-4.556367095091895</v>
+        <v>-4.556367174724496</v>
       </c>
       <c r="H669" t="n">
         <v>133.7014439272579</v>
@@ -52079,10 +52079,10 @@
         <v>221.1647806803385</v>
       </c>
       <c r="F671" t="n">
-        <v>221.5121977996826</v>
+        <v>221.5121975708008</v>
       </c>
       <c r="G671" t="n">
-        <v>-1.747552726478019</v>
+        <v>-1.747552728252144</v>
       </c>
       <c r="H671" t="n">
         <v>286.0804190389319</v>
@@ -52310,10 +52310,10 @@
         <v>288.0327958170573</v>
       </c>
       <c r="F674" t="n">
-        <v>295.0754335021973</v>
+        <v>295.075432434082</v>
       </c>
       <c r="G674" t="n">
-        <v>-3.60949617796934</v>
+        <v>-3.609496046425975</v>
       </c>
       <c r="H674" t="n">
         <v>386.2487546084972</v>
@@ -52926,13 +52926,13 @@
         <v>2379.588235677084</v>
       </c>
       <c r="F682" t="n">
-        <v>2380.033093261719</v>
+        <v>2380.033098144531</v>
       </c>
       <c r="G682" t="n">
-        <v>-2.166212976408299</v>
+        <v>-2.166213021151742</v>
       </c>
       <c r="H682" t="n">
-        <v>2861.413278334028</v>
+        <v>2861.413025289686</v>
       </c>
       <c r="I682" t="n">
         <v>1687.5</v>
@@ -52941,7 +52941,7 @@
         <v>1.054817708333333</v>
       </c>
       <c r="K682" t="n">
-        <v>67.79529680424154</v>
+        <v>67.7952819655425</v>
       </c>
       <c r="L682" t="n">
         <v>7.544581618655692</v>
@@ -53234,10 +53234,10 @@
         <v>2633.548990885417</v>
       </c>
       <c r="F686" t="n">
-        <v>2750.221197509766</v>
+        <v>2750.221199951172</v>
       </c>
       <c r="G686" t="n">
-        <v>-4.190331777717504</v>
+        <v>-4.190331814897319</v>
       </c>
       <c r="H686" t="n">
         <v>3812.926349899466</v>
@@ -53619,10 +53619,10 @@
         <v>126.8953200785319</v>
       </c>
       <c r="F691" t="n">
-        <v>132.1657142257691</v>
+        <v>132.1657139205932</v>
       </c>
       <c r="G691" t="n">
-        <v>-4.602264005097922</v>
+        <v>-4.602264120305355</v>
       </c>
       <c r="H691" t="n">
         <v>183.7853835258596</v>
@@ -54004,10 +54004,10 @@
         <v>343.7913184611003</v>
       </c>
       <c r="F696" t="n">
-        <v>423.4824997711182</v>
+        <v>423.4825000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>-7.523938395543162</v>
+        <v>-7.523938236460815</v>
       </c>
       <c r="H696" t="n">
         <v>779.4908805849697</v>
@@ -54312,10 +54312,10 @@
         <v>374.7167936197916</v>
       </c>
       <c r="F700" t="n">
-        <v>381.2885372924804</v>
+        <v>381.2885368347168</v>
       </c>
       <c r="G700" t="n">
-        <v>-3.361641270162352</v>
+        <v>-3.361641311436181</v>
       </c>
       <c r="H700" t="n">
         <v>541.0236304500187</v>
@@ -54620,10 +54620,10 @@
         <v>236.1900033569336</v>
       </c>
       <c r="F704" t="n">
-        <v>254.3271213531494</v>
+        <v>254.3271215057373</v>
       </c>
       <c r="G704" t="n">
-        <v>-5.825620843099733</v>
+        <v>-5.825620946228094</v>
       </c>
       <c r="H704" t="n">
         <v>398.2045017598045</v>
@@ -55005,10 +55005,10 @@
         <v>631.8366717529296</v>
       </c>
       <c r="F709" t="n">
-        <v>699.4827516174316</v>
+        <v>699.4827500915527</v>
       </c>
       <c r="G709" t="n">
-        <v>-9.461385528275812</v>
+        <v>-9.461385332381111</v>
       </c>
       <c r="H709" t="n">
         <v>1271.244922552079</v>
